--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="2125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="2126">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765724182129</t>
+    <t xml:space="preserve">11.0765733718872</t>
   </si>
   <si>
     <t xml:space="preserve">MONC.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">10.9698104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8452529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986358642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.987603187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744394302368</t>
+    <t xml:space="preserve">10.8452548980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744384765625</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573602676392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6281766891479</t>
+    <t xml:space="preserve">11.6281757354736</t>
   </si>
   <si>
     <t xml:space="preserve">11.4769296646118</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">11.1566438674927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5481042861938</t>
+    <t xml:space="preserve">11.5481052398682</t>
   </si>
   <si>
     <t xml:space="preserve">11.734938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239078521729</t>
@@ -86,34 +86,34 @@
     <t xml:space="preserve">12.1175031661987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0018434524536</t>
+    <t xml:space="preserve">12.0018444061279</t>
   </si>
   <si>
     <t xml:space="preserve">12.1263999938965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0997104644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7260427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9484634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616300582886</t>
+    <t xml:space="preserve">12.0997085571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7260417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908117294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9484624862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950815200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616310119629</t>
   </si>
   <si>
     <t xml:space="preserve">11.9128761291504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4146528244019</t>
+    <t xml:space="preserve">11.4146537780762</t>
   </si>
   <si>
     <t xml:space="preserve">11.2723026275635</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">11.0409851074219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.254508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431200027466</t>
+    <t xml:space="preserve">11.2545099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431190490723</t>
   </si>
   <si>
     <t xml:space="preserve">11.2989940643311</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">11.6726608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772897720337</t>
+    <t xml:space="preserve">11.8772888183594</t>
   </si>
   <si>
     <t xml:space="preserve">12.4110984802246</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">12.2509565353394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2687511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4022026062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7972183227539</t>
+    <t xml:space="preserve">12.2687482833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4022016525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7972164154053</t>
   </si>
   <si>
     <t xml:space="preserve">12.1975755691528</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">12.7669734954834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2118158340454</t>
+    <t xml:space="preserve">13.2118148803711</t>
   </si>
   <si>
     <t xml:space="preserve">13.407546043396</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">13.7100381851196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363723754883</t>
+    <t xml:space="preserve">13.3363704681396</t>
   </si>
   <si>
     <t xml:space="preserve">13.0427751541138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605697631836</t>
+    <t xml:space="preserve">13.0605688095093</t>
   </si>
   <si>
     <t xml:space="preserve">12.9893941879272</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0160865783691</t>
+    <t xml:space="preserve">13.0160856246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.9449110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.096155166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5143070220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1228466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9804973602295</t>
+    <t xml:space="preserve">13.0961570739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.514307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9804983139038</t>
   </si>
   <si>
     <t xml:space="preserve">12.927116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.589035987854</t>
+    <t xml:space="preserve">12.5890350341797</t>
   </si>
   <si>
     <t xml:space="preserve">12.7936639785767</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">12.8292512893677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0338773727417</t>
+    <t xml:space="preserve">13.033878326416</t>
   </si>
   <si>
     <t xml:space="preserve">12.8737363815308</t>
@@ -239,178 +239,178 @@
     <t xml:space="preserve">13.1495370864868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.202919960022</t>
+    <t xml:space="preserve">13.2029190063477</t>
   </si>
   <si>
     <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1673316955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089664459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5979328155518</t>
+    <t xml:space="preserve">13.1673307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089654922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5979318618774</t>
   </si>
   <si>
     <t xml:space="preserve">12.9716005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9982900619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3185768127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9324588775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947366714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6388635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676898956299</t>
+    <t xml:space="preserve">12.9982919692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3185777664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9324607849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6388645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676889419556</t>
   </si>
   <si>
     <t xml:space="preserve">13.3630619049072</t>
   </si>
   <si>
+    <t xml:space="preserve">13.3452701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5608043670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2734222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709959030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4620170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4979372024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6685705184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7314357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7404165267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3003635406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1566743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7256021499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105569839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.860312461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6775531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8571662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2253742218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6986598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9950218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6178340911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8513317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8782730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9680795669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9231758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9591007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9501190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7705068588257</t>
+  </si>
+  <si>
     <t xml:space="preserve">13.345269203186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2285194396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5608053207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4440546035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2734222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709978103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4620170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4979381561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6685724258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7314367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7404165267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3003644943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1566734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7256021499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105588912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8603105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6775531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8571653366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2253742218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321565628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6986618041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476917266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.995023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6178331375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8513317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8782739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9680795669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9231777191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746349334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9591007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9501180648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7705059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3452672958374</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.8302230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1714887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0637197494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3690643310547</t>
+    <t xml:space="preserve">14.1714878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0637216567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3690633773804</t>
   </si>
   <si>
     <t xml:space="preserve">14.0816841125488</t>
@@ -422,37 +422,37 @@
     <t xml:space="preserve">13.5069198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6057081222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9290103912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0277976989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.018816947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8481855392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0457620620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9918746948242</t>
+    <t xml:space="preserve">13.6057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9290113449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0277986526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0188179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8481864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0457611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9918756484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.9200305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7673587799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0008573532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7583789825439</t>
+    <t xml:space="preserve">13.7673597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0008563995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7583780288696</t>
   </si>
   <si>
     <t xml:space="preserve">13.6955146789551</t>
@@ -461,247 +461,247 @@
     <t xml:space="preserve">13.5877447128296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248804092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.354248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4171123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159015655518</t>
+    <t xml:space="preserve">13.524881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4171133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159006118774</t>
   </si>
   <si>
     <t xml:space="preserve">13.7224559783936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5338611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7044944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9110479354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146869659424</t>
+    <t xml:space="preserve">13.533860206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.704493522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9110507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146879196167</t>
   </si>
   <si>
     <t xml:space="preserve">14.0098371505737</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0727014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4530353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6506109237671</t>
+    <t xml:space="preserve">14.0727005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4530363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6506118774414</t>
   </si>
   <si>
     <t xml:space="preserve">13.6416292190552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7853212356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4799776077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.839204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0996446609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8930892944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9649333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8751268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7943000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.62366771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3991527557373</t>
+    <t xml:space="preserve">13.7853202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4799785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8392038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0996427536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8930883407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8751258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.79430103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6236696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3991508483887</t>
   </si>
   <si>
     <t xml:space="preserve">13.3901710510254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4889583587646</t>
+    <t xml:space="preserve">13.488959312439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3362874984741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6326494216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3273077011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763395309448</t>
+    <t xml:space="preserve">13.6326484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3273067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763404846191</t>
   </si>
   <si>
     <t xml:space="preserve">13.8661451339722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0547389984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6474637985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6384840011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9168863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964994430542</t>
+    <t xml:space="preserve">14.0547409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6474618911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.638482093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9168844223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964965820312</t>
   </si>
   <si>
     <t xml:space="preserve">15.0426120758057</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8989229202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.548677444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7372722625732</t>
+    <t xml:space="preserve">14.8989238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5486764907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7372713088989</t>
   </si>
   <si>
     <t xml:space="preserve">14.7731952667236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8719778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6833868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450412750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0875177383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7103290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6744070053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9528064727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377603530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6892213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251443862915</t>
+    <t xml:space="preserve">14.8719787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.683388710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013483047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8450393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.087516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9707670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7103271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6744060516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9528074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6892194747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251453399658</t>
   </si>
   <si>
     <t xml:space="preserve">15.482666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7790279388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0933532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1651973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2011184692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.192138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2460250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9855842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6353340148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9316987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766054153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9586410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867979049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1741790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.102331161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0484466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8957786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676246643066</t>
+    <t xml:space="preserve">15.7790260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0933494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1651954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2011203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1921405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2460231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9855833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137382507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6353359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9317026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9766035079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9586391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406805038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867959976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1741752624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1023292541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0484504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8957738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.967622756958</t>
   </si>
   <si>
     <t xml:space="preserve">16.1831588745117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0991859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2608394622803</t>
+    <t xml:space="preserve">17.0991878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.260835647583</t>
   </si>
   <si>
     <t xml:space="preserve">17.1620502471924</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">17.3326854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5122966766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5661811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6559867858887</t>
+    <t xml:space="preserve">17.5122947692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5661792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.65598487854</t>
   </si>
   <si>
     <t xml:space="preserve">17.6021022796631</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">18.0062351226807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1768646240234</t>
+    <t xml:space="preserve">18.1768665313721</t>
   </si>
   <si>
     <t xml:space="preserve">17.8805027008057</t>
@@ -746,16 +746,16 @@
     <t xml:space="preserve">18.3205547332764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2666702270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4103584289551</t>
+    <t xml:space="preserve">18.2666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4103622436523</t>
   </si>
   <si>
     <t xml:space="preserve">18.1678829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">18.27565574646</t>
+    <t xml:space="preserve">18.2756519317627</t>
   </si>
   <si>
     <t xml:space="preserve">18.4373054504395</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">18.6169166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9312419891357</t>
+    <t xml:space="preserve">18.9312400817871</t>
   </si>
   <si>
     <t xml:space="preserve">19.2276039123535</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">19.2365837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2006587982178</t>
+    <t xml:space="preserve">19.2006607055664</t>
   </si>
   <si>
     <t xml:space="preserve">19.4790630340576</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">19.1108531951904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2096405029297</t>
+    <t xml:space="preserve">19.209644317627</t>
   </si>
   <si>
     <t xml:space="preserve">19.3174095153809</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">19.5329456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6945991516113</t>
+    <t xml:space="preserve">19.6945972442627</t>
   </si>
   <si>
     <t xml:space="preserve">19.4610977172852</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">19.5149841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.188533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310111999512</t>
+    <t xml:space="preserve">20.1885318756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310131072998</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6645107269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8351421356201</t>
+    <t xml:space="preserve">20.6645088195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8351459503174</t>
   </si>
   <si>
     <t xml:space="preserve">21.1135425567627</t>
@@ -857,46 +857,46 @@
     <t xml:space="preserve">19.7229614257812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6052398681641</t>
+    <t xml:space="preserve">19.6052417755127</t>
   </si>
   <si>
     <t xml:space="preserve">19.4875183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0127391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2339630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6324062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7048511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2792415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9260768890381</t>
+    <t xml:space="preserve">20.0127372741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.233959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6324081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7048530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.279239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9260749816895</t>
   </si>
   <si>
     <t xml:space="preserve">19.0075740814209</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9713535308838</t>
+    <t xml:space="preserve">18.9713516235352</t>
   </si>
   <si>
     <t xml:space="preserve">19.0800189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5819664001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1252975463867</t>
+    <t xml:space="preserve">18.5819644927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1252994537354</t>
   </si>
   <si>
     <t xml:space="preserve">19.0437965393066</t>
@@ -908,31 +908,31 @@
     <t xml:space="preserve">19.2249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6142959594727</t>
+    <t xml:space="preserve">19.614294052124</t>
   </si>
   <si>
     <t xml:space="preserve">19.2158508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1524639129639</t>
+    <t xml:space="preserve">19.1524658203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.1434078216553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.324520111084</t>
+    <t xml:space="preserve">19.3245162963867</t>
   </si>
   <si>
     <t xml:space="preserve">18.944185256958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.373685836792</t>
+    <t xml:space="preserve">18.3736877441406</t>
   </si>
   <si>
     <t xml:space="preserve">18.5638523101807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6362953186035</t>
+    <t xml:space="preserve">18.6362972259521</t>
   </si>
   <si>
     <t xml:space="preserve">18.600076675415</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">18.8083534240723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7359085083008</t>
+    <t xml:space="preserve">18.7359104156494</t>
   </si>
   <si>
     <t xml:space="preserve">18.609130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1071853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.288293838501</t>
+    <t xml:space="preserve">19.1071834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2882957458496</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4060192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4512958526611</t>
+    <t xml:space="preserve">19.4060173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4512920379639</t>
   </si>
   <si>
     <t xml:space="preserve">19.4331836700439</t>
@@ -968,46 +968,46 @@
     <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1977405548096</t>
+    <t xml:space="preserve">19.1977443695068</t>
   </si>
   <si>
     <t xml:space="preserve">20.2391300201416</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4655151367188</t>
+    <t xml:space="preserve">20.4655170440674</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560741424561</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2572402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3930702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3296813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3749599456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4021282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3477935791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8458480834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.144681930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5431270599365</t>
+    <t xml:space="preserve">20.3568477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2572383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3930740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.329683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.374963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4021263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3477954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8458499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1446800231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5431289672852</t>
   </si>
   <si>
     <t xml:space="preserve">21.380126953125</t>
@@ -1019,46 +1019,46 @@
     <t xml:space="preserve">21.4254035949707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3710689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2805137634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2080707550049</t>
+    <t xml:space="preserve">21.3710708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2805156707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2080726623535</t>
   </si>
   <si>
     <t xml:space="preserve">20.8730144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2714595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8962917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7423496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7966804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9959011077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1589031219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4305667877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3671798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5935649871826</t>
+    <t xml:space="preserve">21.2714576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.615571975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8962936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7423439025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7966785430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9959030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.158899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4305686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3671779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5935668945312</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116790771484</t>
@@ -1067,22 +1067,22 @@
     <t xml:space="preserve">22.5030136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2404003143311</t>
+    <t xml:space="preserve">22.2404022216797</t>
   </si>
   <si>
     <t xml:space="preserve">22.385290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2313442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2132358551025</t>
+    <t xml:space="preserve">22.2313480377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2132377624512</t>
   </si>
   <si>
     <t xml:space="preserve">22.2494583129883</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9596786499023</t>
+    <t xml:space="preserve">21.9596767425537</t>
   </si>
   <si>
     <t xml:space="preserve">21.8238487243652</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">22.0683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1136226654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1407928466797</t>
+    <t xml:space="preserve">22.1136245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1407909393311</t>
   </si>
   <si>
     <t xml:space="preserve">21.8419589996338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7514057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4706802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1498470306396</t>
+    <t xml:space="preserve">21.7514019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.470682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1498432159424</t>
   </si>
   <si>
     <t xml:space="preserve">22.2766246795654</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">22.0592918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2856826782227</t>
+    <t xml:space="preserve">22.285680770874</t>
   </si>
   <si>
     <t xml:space="preserve">22.3490657806396</t>
@@ -1124,37 +1124,37 @@
     <t xml:space="preserve">22.3943462371826</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9868469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4396228790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5573444366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3581237792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1226787567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0774040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.004955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9415664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8510112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7695121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6466274261475</t>
+    <t xml:space="preserve">21.9868488311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.439624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5573425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3581218719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1226806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0774002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0049591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9415683746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8510131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7695140838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466255187988</t>
   </si>
   <si>
     <t xml:space="preserve">21.0631828308105</t>
@@ -1163,85 +1163,85 @@
     <t xml:space="preserve">21.0088481903076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6737957000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7734069824219</t>
+    <t xml:space="preserve">20.6737937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7734050750732</t>
   </si>
   <si>
     <t xml:space="preserve">20.6556835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0994033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0903511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1356239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8277378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8005714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8820705413818</t>
+    <t xml:space="preserve">21.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1356258392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8277359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.800573348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8820686340332</t>
   </si>
   <si>
     <t xml:space="preserve">21.4344596862793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9506244659424</t>
+    <t xml:space="preserve">21.4163494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9506225585938</t>
   </si>
   <si>
     <t xml:space="preserve">22.4667892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5120697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8833446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290119171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8108997344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0916194915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6530647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9066219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6168403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1821746826172</t>
+    <t xml:space="preserve">22.5120677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8833465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3219013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8109016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0916213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6530666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9066200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6168422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">23.6349544525146</t>
@@ -1250,34 +1250,34 @@
     <t xml:space="preserve">23.4900684356689</t>
   </si>
   <si>
-    <t xml:space="preserve">23.544397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.200288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8199596405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7837333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0372905731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8160667419434</t>
+    <t xml:space="preserve">23.5443992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2002925872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8199558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7837352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0372886657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8160629272461</t>
   </si>
   <si>
     <t xml:space="preserve">24.3412857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4861736297607</t>
+    <t xml:space="preserve">24.4861755371094</t>
   </si>
   <si>
     <t xml:space="preserve">24.250732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3775062561035</t>
+    <t xml:space="preserve">24.3775081634521</t>
   </si>
   <si>
     <t xml:space="preserve">24.5042839050293</t>
@@ -1295,43 +1295,43 @@
     <t xml:space="preserve">24.0333995819092</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2145080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5625114440918</t>
+    <t xml:space="preserve">24.214506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5625095367432</t>
   </si>
   <si>
     <t xml:space="preserve">23.4628982543945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3593978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2908420562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0424518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6582317352295</t>
+    <t xml:space="preserve">24.359395980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.290843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0424537658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6582298278809</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724491119385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7630062103271</t>
+    <t xml:space="preserve">25.7630081176758</t>
   </si>
   <si>
     <t xml:space="preserve">25.4279518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5637836456299</t>
+    <t xml:space="preserve">25.5637817382812</t>
   </si>
   <si>
     <t xml:space="preserve">25.5818939208984</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4641723632812</t>
+    <t xml:space="preserve">25.4641742706299</t>
   </si>
   <si>
     <t xml:space="preserve">25.3917293548584</t>
@@ -1343,34 +1343,34 @@
     <t xml:space="preserve">26.1342830657959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9893970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3192844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2649478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6996154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728397369385</t>
+    <t xml:space="preserve">25.9893951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3192825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.264949798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6996173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728416442871</t>
   </si>
   <si>
     <t xml:space="preserve">26.215784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4059505462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.505558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6685600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4874515533447</t>
+    <t xml:space="preserve">26.405948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5055618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6685619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4874496459961</t>
   </si>
   <si>
     <t xml:space="preserve">26.8134498596191</t>
@@ -1382,37 +1382,37 @@
     <t xml:space="preserve">26.9583377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">27.465446472168</t>
+    <t xml:space="preserve">27.4654445648193</t>
   </si>
   <si>
     <t xml:space="preserve">27.9453926086426</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5741157531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7190017700195</t>
+    <t xml:space="preserve">27.5741138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7190036773682</t>
   </si>
   <si>
     <t xml:space="preserve">27.6737232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9182224273682</t>
+    <t xml:space="preserve">27.9182262420654</t>
   </si>
   <si>
     <t xml:space="preserve">27.9816131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">29.765552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4304962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8108291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549434661865</t>
+    <t xml:space="preserve">29.7655544281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4304981231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8108310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549415588379</t>
   </si>
   <si>
     <t xml:space="preserve">30.2364406585693</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">29.9104442596436</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5624408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4809379577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2053852081299</t>
+    <t xml:space="preserve">30.562442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250541687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4809455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2053813934326</t>
   </si>
   <si>
     <t xml:space="preserve">31.902660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7124938964844</t>
+    <t xml:space="preserve">31.7124977111816</t>
   </si>
   <si>
     <t xml:space="preserve">32.0203857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9207763671875</t>
+    <t xml:space="preserve">31.920768737793</t>
   </si>
   <si>
     <t xml:space="preserve">32.618049621582</t>
@@ -1457,46 +1457,46 @@
     <t xml:space="preserve">33.4602127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110450744629</t>
+    <t xml:space="preserve">33.9039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110488891602</t>
   </si>
   <si>
     <t xml:space="preserve">33.0527153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3011016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0346031188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0798835754395</t>
+    <t xml:space="preserve">32.3011054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0798873901367</t>
   </si>
   <si>
     <t xml:space="preserve">33.3153266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6866073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0759887695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0941047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.392936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2351036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.678825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4416961669922</t>
+    <t xml:space="preserve">33.6866035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0759925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3929328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2350997924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4416923522949</t>
   </si>
   <si>
     <t xml:space="preserve">34.4749336242676</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">33.7270660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5023002624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8065071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0071487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8671035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1589584350586</t>
+    <t xml:space="preserve">34.5022926330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8065032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.007152557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8671073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1589546203613</t>
   </si>
   <si>
     <t xml:space="preserve">35.8156280517578</t>
@@ -1538,28 +1538,28 @@
     <t xml:space="preserve">36.2534027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2748832702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5940971374512</t>
+    <t xml:space="preserve">37.2748756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5940933227539</t>
   </si>
   <si>
     <t xml:space="preserve">37.9041862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4696464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3602027893066</t>
+    <t xml:space="preserve">38.4696502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3602066040039</t>
   </si>
   <si>
     <t xml:space="preserve">37.8221054077148</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6546974182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3446083068848</t>
+    <t xml:space="preserve">36.6546936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3446044921875</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807655334473</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">36.0892333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4143333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3960876464844</t>
+    <t xml:space="preserve">35.4143295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3960914611816</t>
   </si>
   <si>
     <t xml:space="preserve">35.5146522521973</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">35.1042404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5693778991699</t>
+    <t xml:space="preserve">35.5693817138672</t>
   </si>
   <si>
     <t xml:space="preserve">35.3504867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5205345153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9550704956055</t>
+    <t xml:space="preserve">34.5205307006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9550743103027</t>
   </si>
   <si>
     <t xml:space="preserve">33.745304107666</t>
@@ -1598,25 +1598,25 @@
     <t xml:space="preserve">34.2925262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0586395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1830825805664</t>
+    <t xml:space="preserve">35.0586357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1830787658691</t>
   </si>
   <si>
     <t xml:space="preserve">34.8397445678711</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5967407226562</t>
+    <t xml:space="preserve">35.596736907959</t>
   </si>
   <si>
     <t xml:space="preserve">35.1224784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.624095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4690551757812</t>
+    <t xml:space="preserve">35.6241035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.469051361084</t>
   </si>
   <si>
     <t xml:space="preserve">35.3869705200195</t>
@@ -1625,25 +1625,25 @@
     <t xml:space="preserve">35.241039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1622047424316</t>
+    <t xml:space="preserve">36.1622009277344</t>
   </si>
   <si>
     <t xml:space="preserve">34.8853492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6938247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8091468811035</t>
+    <t xml:space="preserve">34.6938209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8091430664062</t>
   </si>
   <si>
     <t xml:space="preserve">34.401969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2013206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4169692993164</t>
+    <t xml:space="preserve">34.2013244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4169731140137</t>
   </si>
   <si>
     <t xml:space="preserve">34.2651672363281</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">34.5387763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7303009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6208534240723</t>
+    <t xml:space="preserve">34.7303047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6208572387695</t>
   </si>
   <si>
     <t xml:space="preserve">34.018913269043</t>
@@ -1670,22 +1670,22 @@
     <t xml:space="preserve">34.484058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7941436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5784912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169151306152</t>
+    <t xml:space="preserve">34.7941474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5784873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169189453125</t>
   </si>
   <si>
     <t xml:space="preserve">36.1530799865723</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5328941345215</t>
+    <t xml:space="preserve">36.3172416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5328903198242</t>
   </si>
   <si>
     <t xml:space="preserve">35.5055351257324</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">34.3016471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7850227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9824295043945</t>
+    <t xml:space="preserve">34.785026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9824333190918</t>
   </si>
   <si>
     <t xml:space="preserve">34.6117401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4202156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5934944152832</t>
+    <t xml:space="preserve">34.4202117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5934982299805</t>
   </si>
   <si>
     <t xml:space="preserve">34.511417388916</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">34.0827560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4110908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664657592773</t>
+    <t xml:space="preserve">34.4110946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664619445801</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228050231934</t>
@@ -1739,28 +1739,28 @@
     <t xml:space="preserve">34.940071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">32.979190826416</t>
+    <t xml:space="preserve">32.9791946411133</t>
   </si>
   <si>
     <t xml:space="preserve">31.8300342559814</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4593353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9388809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5284671783447</t>
+    <t xml:space="preserve">32.4593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9388790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5284652709961</t>
   </si>
   <si>
     <t xml:space="preserve">28.2001304626465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2639713287354</t>
+    <t xml:space="preserve">27.6529102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.263973236084</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007778167725</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">28.4554996490479</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7258720397949</t>
+    <t xml:space="preserve">27.7258701324463</t>
   </si>
   <si>
     <t xml:space="preserve">27.7988338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6587905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2698554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5708274841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1786518096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5434665679932</t>
+    <t xml:space="preserve">26.6587924957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5708255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1786499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5434684753418</t>
   </si>
   <si>
     <t xml:space="preserve">27.9994850158691</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">29.5499439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1942501068115</t>
+    <t xml:space="preserve">29.1942462921143</t>
   </si>
   <si>
     <t xml:space="preserve">28.9753608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1304054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4522590637207</t>
+    <t xml:space="preserve">29.130407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.692626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.452262878418</t>
   </si>
   <si>
     <t xml:space="preserve">29.0392036437988</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">28.0359649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3519382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2666187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.85032081604</t>
+    <t xml:space="preserve">27.351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2666149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503170013428</t>
   </si>
   <si>
     <t xml:space="preserve">26.813835144043</t>
@@ -1841,25 +1841,25 @@
     <t xml:space="preserve">27.4340229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2060108184814</t>
+    <t xml:space="preserve">27.2060127258301</t>
   </si>
   <si>
     <t xml:space="preserve">26.7317543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9141616821289</t>
+    <t xml:space="preserve">26.9141597747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.2483768463135</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8079566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.768238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3063354492188</t>
+    <t xml:space="preserve">27.8079528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7682361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3063373565674</t>
   </si>
   <si>
     <t xml:space="preserve">26.5128650665283</t>
@@ -1868,28 +1868,28 @@
     <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4822654724121</t>
+    <t xml:space="preserve">25.4822673797607</t>
   </si>
   <si>
     <t xml:space="preserve">25.327220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9565238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265716552734</t>
+    <t xml:space="preserve">25.956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265697479248</t>
   </si>
   <si>
     <t xml:space="preserve">24.6431922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.172176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7011528015137</t>
+    <t xml:space="preserve">25.1721725463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7011566162109</t>
   </si>
   <si>
     <t xml:space="preserve">25.144811630249</t>
@@ -1898,109 +1898,109 @@
     <t xml:space="preserve">25.3454608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5825901031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.385181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.59494972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3637008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.467264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1877727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6014289855957</t>
+    <t xml:space="preserve">25.5825881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3851795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5949478149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3637027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4672660827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1877708435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">28.1454086303711</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0600872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0327243804932</t>
+    <t xml:space="preserve">27.0600833892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0327262878418</t>
   </si>
   <si>
     <t xml:space="preserve">27.3336963653564</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4066600799561</t>
+    <t xml:space="preserve">27.4066581726074</t>
   </si>
   <si>
     <t xml:space="preserve">27.6711502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8991603851318</t>
+    <t xml:space="preserve">27.8991584777832</t>
   </si>
   <si>
     <t xml:space="preserve">27.3792991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.95387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.880916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2366123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9147567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0059642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.598783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7994327545166</t>
+    <t xml:space="preserve">27.9538803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8809185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9147548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0059623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5987815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.799430847168</t>
   </si>
   <si>
     <t xml:space="preserve">31.2007293701172</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4437389373779</t>
+    <t xml:space="preserve">30.4437408447266</t>
   </si>
   <si>
     <t xml:space="preserve">30.6443862915039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9362373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121208190918</t>
+    <t xml:space="preserve">30.9362392425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023410797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121189117432</t>
   </si>
   <si>
     <t xml:space="preserve">31.6020202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3284130096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7753086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6567459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476249694824</t>
+    <t xml:space="preserve">31.3284111022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8117923736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7753067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6567401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476287841797</t>
   </si>
   <si>
     <t xml:space="preserve">31.4743366241455</t>
@@ -2009,28 +2009,28 @@
     <t xml:space="preserve">31.9668388366699</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9029941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538299560547</t>
+    <t xml:space="preserve">31.9029922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538280487061</t>
   </si>
   <si>
     <t xml:space="preserve">34.1557235717773</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7909088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9244766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8332672119141</t>
+    <t xml:space="preserve">33.7909049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9244728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8332710266113</t>
   </si>
   <si>
     <t xml:space="preserve">32.696460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5140609741211</t>
+    <t xml:space="preserve">32.5140571594238</t>
   </si>
   <si>
     <t xml:space="preserve">32.5778999328613</t>
@@ -2042,22 +2042,22 @@
     <t xml:space="preserve">32.9153518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0065574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5264205932617</t>
+    <t xml:space="preserve">33.0065536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5264167785645</t>
   </si>
   <si>
     <t xml:space="preserve">33.1980857849121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2313270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7388286590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.441089630127</t>
+    <t xml:space="preserve">32.2313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7388248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4410934448242</t>
   </si>
   <si>
     <t xml:space="preserve">32.7603073120117</t>
@@ -2066,25 +2066,25 @@
     <t xml:space="preserve">33.5081787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6084938049316</t>
+    <t xml:space="preserve">33.6085014343262</t>
   </si>
   <si>
     <t xml:space="preserve">34.1283569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9277153015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8638687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8150291442871</t>
+    <t xml:space="preserve">33.9277114868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8638725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8150253295898</t>
   </si>
   <si>
     <t xml:space="preserve">32.659984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2163238525391</t>
+    <t xml:space="preserve">33.2163200378418</t>
   </si>
   <si>
     <t xml:space="preserve">33.2892875671387</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">33.1160011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3075256347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8729934692383</t>
+    <t xml:space="preserve">33.3075332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.872989654541</t>
   </si>
   <si>
     <t xml:space="preserve">33.6814651489258</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">33.2345657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1616020202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.550537109375</t>
+    <t xml:space="preserve">33.9185905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1616058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5505409240723</t>
   </si>
   <si>
     <t xml:space="preserve">32.404613494873</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">33.4443321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9485931396484</t>
+    <t xml:space="preserve">31.9485969543457</t>
   </si>
   <si>
     <t xml:space="preserve">32.6873474121094</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">32.1310043334961</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5596618652344</t>
+    <t xml:space="preserve">32.5596542358398</t>
   </si>
   <si>
     <t xml:space="preserve">31.5911712646484</t>
@@ -2162,79 +2162,79 @@
     <t xml:space="preserve">32.2552795410156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2829513549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7848663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887115478516</t>
+    <t xml:space="preserve">32.2829475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7848701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">30.6226844787598</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4382095336914</t>
+    <t xml:space="preserve">30.4382057189941</t>
   </si>
   <si>
     <t xml:space="preserve">30.5581169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1207618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0062408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6649646759033</t>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0062370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6649684906006</t>
   </si>
   <si>
     <t xml:space="preserve">32.1169242858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7387504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290596008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6519012451172</t>
+    <t xml:space="preserve">31.7387466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6518974304199</t>
   </si>
   <si>
     <t xml:space="preserve">33.6480560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7679672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7087783813477</t>
+    <t xml:space="preserve">33.7679634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7087860107422</t>
   </si>
   <si>
     <t xml:space="preserve">34.5058631896973</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4136276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7864074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5189247131348</t>
+    <t xml:space="preserve">34.4136238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7864112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5189208984375</t>
   </si>
   <si>
     <t xml:space="preserve">34.2568206787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6811103820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500602722168</t>
+    <t xml:space="preserve">34.6811065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500526428223</t>
   </si>
   <si>
     <t xml:space="preserve">34.9762687683105</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">35.5112457275391</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6127090454102</t>
+    <t xml:space="preserve">35.6127014160156</t>
   </si>
   <si>
     <t xml:space="preserve">35.5204658508301</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">35.5296897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.280647277832</t>
+    <t xml:space="preserve">35.2806549072266</t>
   </si>
   <si>
     <t xml:space="preserve">35.3544425964355</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">35.4927978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0408401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1330680847168</t>
+    <t xml:space="preserve">35.0408363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1330718994141</t>
   </si>
   <si>
     <t xml:space="preserve">35.2253112792969</t>
@@ -2276,55 +2276,55 @@
     <t xml:space="preserve">35.2437553405762</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6588249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9263153076172</t>
+    <t xml:space="preserve">35.658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6403770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9263114929199</t>
   </si>
   <si>
     <t xml:space="preserve">35.9908752441406</t>
   </si>
   <si>
-    <t xml:space="preserve">35.963207244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6903381347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2844886779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4451370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4620418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4989376068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2314491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7572002410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6926307678223</t>
+    <t xml:space="preserve">35.9632110595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6903343200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2844924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4451332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4620380401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343719482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4989318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2314472198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7571964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6926345825195</t>
   </si>
   <si>
     <t xml:space="preserve">32.7072410583496</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">31.3605804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3052349090576</t>
+    <t xml:space="preserve">31.3052368164062</t>
   </si>
   <si>
     <t xml:space="preserve">31.4435901641846</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">31.6465167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3382949829102</t>
+    <t xml:space="preserve">32.3382911682129</t>
   </si>
   <si>
     <t xml:space="preserve">33.0761871337891</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1684265136719</t>
+    <t xml:space="preserve">33.1684188842773</t>
   </si>
   <si>
     <t xml:space="preserve">32.7349090576172</t>
@@ -2363,40 +2363,40 @@
     <t xml:space="preserve">32.5412101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6242218017578</t>
+    <t xml:space="preserve">32.6242256164551</t>
   </si>
   <si>
     <t xml:space="preserve">32.6426734924316</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3751831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6372909545898</t>
+    <t xml:space="preserve">32.375186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6372871398926</t>
   </si>
   <si>
     <t xml:space="preserve">31.4804878234863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2760200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9493522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0877094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7279834747314</t>
+    <t xml:space="preserve">29.2760219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9493541717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0877075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6080760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7279815673828</t>
   </si>
   <si>
     <t xml:space="preserve">29.6449699401855</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8478946685791</t>
+    <t xml:space="preserve">29.8478908538818</t>
   </si>
   <si>
     <t xml:space="preserve">30.3367481231689</t>
@@ -2405,25 +2405,25 @@
     <t xml:space="preserve">30.1614990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8294448852539</t>
+    <t xml:space="preserve">29.8294429779053</t>
   </si>
   <si>
     <t xml:space="preserve">29.1376686096191</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6173000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0139217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1983947753906</t>
+    <t xml:space="preserve">29.6172981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.198392868042</t>
   </si>
   <si>
     <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6134605407715</t>
+    <t xml:space="preserve">30.6134586334229</t>
   </si>
   <si>
     <t xml:space="preserve">31.1945514678955</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">31.803316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5450534820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4251403808594</t>
+    <t xml:space="preserve">31.545051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.425142288208</t>
   </si>
   <si>
     <t xml:space="preserve">31.0285263061523</t>
@@ -2447,25 +2447,25 @@
     <t xml:space="preserve">29.6726398468018</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9770221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7740993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6910858154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9678020477295</t>
+    <t xml:space="preserve">29.9770240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7741031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.691089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9678001403809</t>
   </si>
   <si>
     <t xml:space="preserve">33.3621215820312</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7441329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.98779296875</t>
+    <t xml:space="preserve">32.7441291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9877891540527</t>
   </si>
   <si>
     <t xml:space="preserve">32.4397506713867</t>
@@ -2480,28 +2480,28 @@
     <t xml:space="preserve">34.2291488647461</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7180023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3121643066406</t>
+    <t xml:space="preserve">34.7180061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3121604919434</t>
   </si>
   <si>
     <t xml:space="preserve">34.0907897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0077781677246</t>
+    <t xml:space="preserve">34.0077819824219</t>
   </si>
   <si>
     <t xml:space="preserve">33.6111602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7218475341797</t>
+    <t xml:space="preserve">33.721851348877</t>
   </si>
   <si>
     <t xml:space="preserve">33.980110168457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2199287414551</t>
+    <t xml:space="preserve">34.2199249267578</t>
   </si>
   <si>
     <t xml:space="preserve">34.819465637207</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">36.0462188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1476783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6826553344727</t>
+    <t xml:space="preserve">36.1476745605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0239334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6826477050781</t>
   </si>
   <si>
     <t xml:space="preserve">35.7787322998047</t>
@@ -2540,22 +2540,22 @@
     <t xml:space="preserve">38.8225517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0938758850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8171653747559</t>
+    <t xml:space="preserve">38.093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8171691894531</t>
   </si>
   <si>
     <t xml:space="preserve">37.7249336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1530609130859</t>
+    <t xml:space="preserve">37.1530570983887</t>
   </si>
   <si>
     <t xml:space="preserve">37.3006401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0423736572266</t>
+    <t xml:space="preserve">37.0423774719238</t>
   </si>
   <si>
     <t xml:space="preserve">37.1899566650391</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">37.715705871582</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6234741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4758911132812</t>
+    <t xml:space="preserve">37.6234664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4758949279785</t>
   </si>
   <si>
     <t xml:space="preserve">36.9593658447266</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">37.9463005065918</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5496788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6326942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3613700866699</t>
+    <t xml:space="preserve">37.5496826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.632698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3613662719727</t>
   </si>
   <si>
     <t xml:space="preserve">39.4036445617676</t>
@@ -2603,37 +2603,37 @@
     <t xml:space="preserve">39.3667526245117</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3852005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1399955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2914123535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2691307067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2084007263184</t>
+    <t xml:space="preserve">39.385196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1399917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2914161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2691345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2084045410156</t>
   </si>
   <si>
     <t xml:space="preserve">37.402099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8432998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2360725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.488956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9724311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3690490722656</t>
+    <t xml:space="preserve">35.8432960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2360763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4889602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9724273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3690452575684</t>
   </si>
   <si>
     <t xml:space="preserve">36.8579025268555</t>
@@ -2642,40 +2642,40 @@
     <t xml:space="preserve">37.2729721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5166282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7049369812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6495971679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2583656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1422996520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2898712158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0093231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2660484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4305229187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4028587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9286079406738</t>
+    <t xml:space="preserve">36.5166244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7049407958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.649600982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1422958374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0093269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.266040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9286117553711</t>
   </si>
   <si>
     <t xml:space="preserve">32.522762298584</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">32.4858665466309</t>
   </si>
   <si>
-    <t xml:space="preserve">31.10231590271</t>
+    <t xml:space="preserve">31.1023197174072</t>
   </si>
   <si>
     <t xml:space="preserve">28.1507320404053</t>
@@ -2693,19 +2693,19 @@
     <t xml:space="preserve">27.8002300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0807838439941</t>
+    <t xml:space="preserve">27.0807819366455</t>
   </si>
   <si>
     <t xml:space="preserve">23.9816188812256</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3943881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2637119293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9039897918701</t>
+    <t xml:space="preserve">27.3943901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2637138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9039878845215</t>
   </si>
   <si>
     <t xml:space="preserve">25.3651733398438</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">24.9224376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9977684020996</t>
+    <t xml:space="preserve">26.9977703094482</t>
   </si>
   <si>
     <t xml:space="preserve">26.3797817230225</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">29.9309062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4528141021729</t>
+    <t xml:space="preserve">31.4528160095215</t>
   </si>
   <si>
     <t xml:space="preserve">31.7295265197754</t>
@@ -2738,31 +2738,31 @@
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857070922852</t>
+    <t xml:space="preserve">28.6857032775879</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688003540039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1061534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2998523712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6319046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8402099609375</t>
+    <t xml:space="preserve">30.1061553955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2998504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.083869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6319065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8402137756348</t>
   </si>
   <si>
     <t xml:space="preserve">32.513542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8901691436768</t>
+    <t xml:space="preserve">30.8901748657227</t>
   </si>
   <si>
     <t xml:space="preserve">30.576566696167</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">31.5081577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7756462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.272180557251</t>
+    <t xml:space="preserve">31.7756404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2721824645996</t>
   </si>
   <si>
     <t xml:space="preserve">30.7702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9124584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2352848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7833271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2260646820068</t>
+    <t xml:space="preserve">29.9124565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2352867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7833251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2260627746582</t>
   </si>
   <si>
     <t xml:space="preserve">29.4143772125244</t>
@@ -2813,19 +2813,19 @@
     <t xml:space="preserve">29.3682594299316</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7979354858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.39208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1630401611328</t>
+    <t xml:space="preserve">30.7979335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3920936584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1630439758301</t>
   </si>
   <si>
     <t xml:space="preserve">30.8532752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0746421813965</t>
+    <t xml:space="preserve">31.0746402740479</t>
   </si>
   <si>
     <t xml:space="preserve">31.8955535888672</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">31.0377502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3790245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9693431854248</t>
+    <t xml:space="preserve">31.3790264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9693393707275</t>
   </si>
   <si>
     <t xml:space="preserve">32.4950904846191</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">33.0577392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0892524719238</t>
+    <t xml:space="preserve">32.0892562866211</t>
   </si>
   <si>
     <t xml:space="preserve">31.7203006744385</t>
@@ -2864,58 +2864,58 @@
     <t xml:space="preserve">32.126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3974761962891</t>
+    <t xml:space="preserve">31.3974742889404</t>
   </si>
   <si>
     <t xml:space="preserve">31.6003932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9508972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591171264648</t>
+    <t xml:space="preserve">31.9509010314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">31.9601192474365</t>
   </si>
   <si>
-    <t xml:space="preserve">31.489709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6503505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824066162109</t>
+    <t xml:space="preserve">31.4897117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.351354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.650354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824085235596</t>
   </si>
   <si>
     <t xml:space="preserve">31.0100765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5950107574463</t>
+    <t xml:space="preserve">30.5950088500977</t>
   </si>
   <si>
     <t xml:space="preserve">30.0692596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0969314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4236011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5804042816162</t>
+    <t xml:space="preserve">30.0969295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4236030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5804061889648</t>
   </si>
   <si>
     <t xml:space="preserve">29.488166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8809471130371</t>
+    <t xml:space="preserve">30.8809452056885</t>
   </si>
   <si>
     <t xml:space="preserve">30.3275260925293</t>
@@ -2927,19 +2927,19 @@
     <t xml:space="preserve">29.5342864990234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8571128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0046920776367</t>
+    <t xml:space="preserve">29.5527362823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8571147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0046939849854</t>
   </si>
   <si>
     <t xml:space="preserve">30.585786819458</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8847885131836</t>
+    <t xml:space="preserve">29.884786605835</t>
   </si>
   <si>
     <t xml:space="preserve">29.9585762023926</t>
@@ -2948,34 +2948,34 @@
     <t xml:space="preserve">31.1484355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7940902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4766464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8878707885742</t>
+    <t xml:space="preserve">31.7940940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1814842224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4766426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8878746032715</t>
   </si>
   <si>
     <t xml:space="preserve">34.9854927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3306121826172</t>
+    <t xml:space="preserve">34.3306159973145</t>
   </si>
   <si>
     <t xml:space="preserve">33.66650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4674263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0431327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.448974609375</t>
+    <t xml:space="preserve">32.4674224853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0431365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4489784240723</t>
   </si>
   <si>
     <t xml:space="preserve">32.2644996643066</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">32.7164649963379</t>
   </si>
   <si>
-    <t xml:space="preserve">33.601936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8509788513184</t>
+    <t xml:space="preserve">33.6019401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8509750366211</t>
   </si>
   <si>
     <t xml:space="preserve">33.2237701416016</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5650444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9339904785156</t>
+    <t xml:space="preserve">33.5650405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9339942932129</t>
   </si>
   <si>
     <t xml:space="preserve">34.0354537963867</t>
@@ -3017,19 +3017,19 @@
     <t xml:space="preserve">34.4043998718262</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9170837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.127685546875</t>
+    <t xml:space="preserve">35.9170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1276893615723</t>
   </si>
   <si>
     <t xml:space="preserve">32.1907157897949</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3936347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2053146362305</t>
+    <t xml:space="preserve">32.3936309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2053184509277</t>
   </si>
   <si>
     <t xml:space="preserve">33.5465965270996</t>
@@ -3044,40 +3044,40 @@
     <t xml:space="preserve">36.5996398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">36.627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3467597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.719554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8909606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6142463684082</t>
+    <t xml:space="preserve">36.6273078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3467636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7195472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8909568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8725090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6142425537109</t>
   </si>
   <si>
     <t xml:space="preserve">37.4482192993164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4535980224609</t>
+    <t xml:space="preserve">38.4536018371582</t>
   </si>
   <si>
     <t xml:space="preserve">38.7118682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6473045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2414588928223</t>
+    <t xml:space="preserve">38.6473007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.241455078125</t>
   </si>
   <si>
     <t xml:space="preserve">37.8263893127441</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">37.9001808166504</t>
   </si>
   <si>
-    <t xml:space="preserve">38.472053527832</t>
+    <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
     <t xml:space="preserve">39.2837371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">39.846378326416</t>
+    <t xml:space="preserve">39.8463859558105</t>
   </si>
   <si>
     <t xml:space="preserve">40.5842781066895</t>
@@ -3101,13 +3101,13 @@
     <t xml:space="preserve">41.4144134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9916687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8533096313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8863639831543</t>
+    <t xml:space="preserve">42.9916648864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8533058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8863677978516</t>
   </si>
   <si>
     <t xml:space="preserve">44.1630744934082</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">44.928638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1961288452148</t>
+    <t xml:space="preserve">45.1961326599121</t>
   </si>
   <si>
     <t xml:space="preserve">44.7349433898926</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4674530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8694534301758</t>
+    <t xml:space="preserve">44.467456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.869457244873</t>
   </si>
   <si>
     <t xml:space="preserve">46.3952102661133</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">46.2476272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1184959411621</t>
+    <t xml:space="preserve">46.1184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">44.8456268310547</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">44.1077270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.273754119873</t>
+    <t xml:space="preserve">44.3290977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2737579345703</t>
   </si>
   <si>
     <t xml:space="preserve">43.3882827758789</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0708312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6742172241211</t>
+    <t xml:space="preserve">44.0708351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6742134094238</t>
   </si>
   <si>
     <t xml:space="preserve">44.6703758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">43.950927734375</t>
+    <t xml:space="preserve">43.9509315490723</t>
   </si>
   <si>
     <t xml:space="preserve">44.8917427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7403297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6649894714355</t>
+    <t xml:space="preserve">45.7403259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6649971008301</t>
   </si>
   <si>
     <t xml:space="preserve">43.5912017822266</t>
@@ -3197,31 +3197,31 @@
     <t xml:space="preserve">43.7756767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1999702453613</t>
+    <t xml:space="preserve">44.1999664306641</t>
   </si>
   <si>
     <t xml:space="preserve">44.2091903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1369438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8932914733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5758399963379</t>
+    <t xml:space="preserve">46.1369476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8932876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">48.0739250183105</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6496315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9447898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2622413635254</t>
+    <t xml:space="preserve">47.6496353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9447860717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2622337341309</t>
   </si>
   <si>
     <t xml:space="preserve">48.1477127075195</t>
@@ -3233,52 +3233,52 @@
     <t xml:space="preserve">46.7088165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6534767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1807670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8710021972656</t>
+    <t xml:space="preserve">46.6534729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1807632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8709983825684</t>
   </si>
   <si>
     <t xml:space="preserve">47.2437934875488</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0408668518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.169994354248</t>
+    <t xml:space="preserve">47.0408706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1699981689453</t>
   </si>
   <si>
     <t xml:space="preserve">47.3175773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1108169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4613189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6865272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6165733337402</t>
+    <t xml:space="preserve">48.1108207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4613151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6865310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6165771484375</t>
   </si>
   <si>
     <t xml:space="preserve">45.7034301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8602409362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4136543273926</t>
+    <t xml:space="preserve">45.860237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4136505126953</t>
   </si>
   <si>
     <t xml:space="preserve">45.7587776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0001335144043</t>
+    <t xml:space="preserve">48.0001373291016</t>
   </si>
   <si>
     <t xml:space="preserve">47.3360252380371</t>
@@ -3287,64 +3287,64 @@
     <t xml:space="preserve">47.4467086791992</t>
   </si>
   <si>
-    <t xml:space="preserve">46.837947845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2107391357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6019744873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3806037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2276382446289</t>
+    <t xml:space="preserve">46.8379440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2107315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6019706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3805999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2276420593262</t>
   </si>
   <si>
     <t xml:space="preserve">44.4397888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">44.485897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3898277282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0762176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8417930603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6573181152344</t>
+    <t xml:space="preserve">44.4859008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3898239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0762214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8417816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6573143005371</t>
   </si>
   <si>
     <t xml:space="preserve">46.4505500793457</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5981330871582</t>
+    <t xml:space="preserve">46.5981292724609</t>
   </si>
   <si>
     <t xml:space="preserve">46.5243377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5020561218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3544769287109</t>
+    <t xml:space="preserve">47.5020523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3544692993164</t>
   </si>
   <si>
     <t xml:space="preserve">46.321418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2952919006348</t>
+    <t xml:space="preserve">48.2952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">49.346794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9670753479004</t>
+    <t xml:space="preserve">46.9670791625977</t>
   </si>
   <si>
     <t xml:space="preserve">47.0039749145508</t>
@@ -3353,19 +3353,19 @@
     <t xml:space="preserve">47.0593185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4836044311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3767623901367</t>
+    <t xml:space="preserve">47.4836082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3767585754395</t>
   </si>
   <si>
     <t xml:space="preserve">47.4282608032227</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2806816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7234230041504</t>
+    <t xml:space="preserve">47.2806854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7234191894531</t>
   </si>
   <si>
     <t xml:space="preserve">46.985523223877</t>
@@ -3377,16 +3377,16 @@
     <t xml:space="preserve">47.9263381958008</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6642379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4244232177734</t>
+    <t xml:space="preserve">48.664234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4244270324707</t>
   </si>
   <si>
     <t xml:space="preserve">49.1623191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">49.420581817627</t>
+    <t xml:space="preserve">49.4205856323242</t>
   </si>
   <si>
     <t xml:space="preserve">50.490291595459</t>
@@ -3401,22 +3401,22 @@
     <t xml:space="preserve">53.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9877777099609</t>
+    <t xml:space="preserve">53.9877738952637</t>
   </si>
   <si>
     <t xml:space="preserve">54.0621910095215</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4482688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6343078613281</t>
+    <t xml:space="preserve">53.4482727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6343116760254</t>
   </si>
   <si>
     <t xml:space="preserve">54.1180038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2296257019043</t>
+    <t xml:space="preserve">54.229621887207</t>
   </si>
   <si>
     <t xml:space="preserve">55.1039962768555</t>
@@ -3425,19 +3425,19 @@
     <t xml:space="preserve">54.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">53.578498840332</t>
+    <t xml:space="preserve">53.5784950256348</t>
   </si>
   <si>
     <t xml:space="preserve">52.8343505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8715629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1320114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8947525024414</t>
+    <t xml:space="preserve">52.8715591430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8947563171387</t>
   </si>
   <si>
     <t xml:space="preserve">54.2482261657715</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">54.508674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0435829162598</t>
+    <t xml:space="preserve">54.043586730957</t>
   </si>
   <si>
     <t xml:space="preserve">54.1738166809082</t>
@@ -3455,22 +3455,22 @@
     <t xml:space="preserve">54.2110214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2250328063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6901168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.597095489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0762023925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4668769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3180503845215</t>
+    <t xml:space="preserve">53.225025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6901206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5970993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0761985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4668731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3180465698242</t>
   </si>
   <si>
     <t xml:space="preserve">52.815746307373</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">53.038990020752</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3366470336914</t>
+    <t xml:space="preserve">53.3366508483887</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
@@ -3491,31 +3491,31 @@
     <t xml:space="preserve">53.2808380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7273254394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3598480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7785415649414</t>
+    <t xml:space="preserve">53.7273216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3598518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7785453796387</t>
   </si>
   <si>
     <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1878204345703</t>
+    <t xml:space="preserve">53.1878242492676</t>
   </si>
   <si>
     <t xml:space="preserve">53.7459259033203</t>
   </si>
   <si>
-    <t xml:space="preserve">54.620304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4388618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7551193237305</t>
+    <t xml:space="preserve">54.6203002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4388580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.755126953125</t>
   </si>
   <si>
     <t xml:space="preserve">55.4946746826172</t>
@@ -3524,46 +3524,46 @@
     <t xml:space="preserve">53.8761558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9505653381348</t>
+    <t xml:space="preserve">53.9505729675293</t>
   </si>
   <si>
     <t xml:space="preserve">54.6389083862305</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6947174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5272827148438</t>
+    <t xml:space="preserve">54.6947135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5272789001465</t>
   </si>
   <si>
     <t xml:space="preserve">55.5876884460449</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9271507263184</t>
+    <t xml:space="preserve">56.9271545410156</t>
   </si>
   <si>
     <t xml:space="preserve">57.2992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7271118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5596771240234</t>
+    <t xml:space="preserve">57.7271156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5596809387207</t>
   </si>
   <si>
     <t xml:space="preserve">56.4248542785645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8667449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3970527648926</t>
+    <t xml:space="preserve">55.8667411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3970565795898</t>
   </si>
   <si>
     <t xml:space="preserve">51.067008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1554260253906</t>
+    <t xml:space="preserve">50.1554222106934</t>
   </si>
   <si>
     <t xml:space="preserve">50.8437614440918</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">50.7693481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">50.397274017334</t>
+    <t xml:space="preserve">50.3972702026367</t>
   </si>
   <si>
     <t xml:space="preserve">50.5461044311523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8065528869629</t>
+    <t xml:space="preserve">50.8065567016602</t>
   </si>
   <si>
     <t xml:space="preserve">50.4158782958984</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">51.7181282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4018707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3274574279785</t>
+    <t xml:space="preserve">51.4018669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3274536132812</t>
   </si>
   <si>
     <t xml:space="preserve">50.8251571655273</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">48.0904235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3182640075684</t>
+    <t xml:space="preserve">49.3182601928711</t>
   </si>
   <si>
     <t xml:space="preserve">48.0532150268555</t>
@@ -3629,22 +3629,22 @@
     <t xml:space="preserve">50.5647048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3832664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1600227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0624084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6113243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2438430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7553405761719</t>
+    <t xml:space="preserve">51.3832702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1600189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0624046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6113204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2438468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7553367614746</t>
   </si>
   <si>
     <t xml:space="preserve">51.9785842895508</t>
@@ -3653,28 +3653,28 @@
     <t xml:space="preserve">52.9831771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4994850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4622802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7133178710938</t>
+    <t xml:space="preserve">52.4994812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4622764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.713321685791</t>
   </si>
   <si>
     <t xml:space="preserve">54.4714736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5690841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7597198486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8341331481934</t>
+    <t xml:space="preserve">55.5690879821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0341835021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7597236633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8341293334961</t>
   </si>
   <si>
     <t xml:space="preserve">56.3876457214355</t>
@@ -3692,19 +3692,19 @@
     <t xml:space="preserve">59.438648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5084648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2340049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.652473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8803176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4012222290039</t>
+    <t xml:space="preserve">58.5084686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.234001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6524772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8803253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4012298583984</t>
   </si>
   <si>
     <t xml:space="preserve">61.4106254577637</t>
@@ -3713,67 +3713,67 @@
     <t xml:space="preserve">60.7409019470215</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8199081420898</t>
+    <t xml:space="preserve">61.8199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7546882629395</t>
+    <t xml:space="preserve">63.7546920776367</t>
   </si>
   <si>
     <t xml:space="preserve">64.3314056396484</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5686531066895</t>
+    <t xml:space="preserve">64.2197875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5686492919922</t>
   </si>
   <si>
     <t xml:space="preserve">63.0663566589355</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9129333496094</t>
+    <t xml:space="preserve">63.9593238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9129257202148</t>
   </si>
   <si>
     <t xml:space="preserve">62.3222122192383</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3410301208496</t>
+    <t xml:space="preserve">58.3410339355469</t>
   </si>
   <si>
     <t xml:space="preserve">60.089771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6060791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0385627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9455375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5920677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6896820068359</t>
+    <t xml:space="preserve">59.6060829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0385589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9455337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5920715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6896858215332</t>
   </si>
   <si>
     <t xml:space="preserve">64.4430313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4710464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1547775268555</t>
+    <t xml:space="preserve">62.4710388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1547813415527</t>
   </si>
   <si>
     <t xml:space="preserve">61.4478340148926</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">60.6292762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6758995056152</t>
+    <t xml:space="preserve">58.675895690918</t>
   </si>
   <si>
     <t xml:space="preserve">60.182788848877</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">58.2294082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8573379516602</t>
+    <t xml:space="preserve">57.8573341369629</t>
   </si>
   <si>
     <t xml:space="preserve">58.3224296569824</t>
@@ -3812,10 +3812,10 @@
     <t xml:space="preserve">60.0711708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5502662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.8107223510742</t>
+    <t xml:space="preserve">59.5502624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.810718536377</t>
   </si>
   <si>
     <t xml:space="preserve">60.4618453979492</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">60.9269332885742</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4154396057129</t>
+    <t xml:space="preserve">58.4154434204102</t>
   </si>
   <si>
     <t xml:space="preserve">56.9643630981445</t>
@@ -3833,25 +3833,25 @@
     <t xml:space="preserve">56.1644020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7923316955566</t>
+    <t xml:space="preserve">55.7923278808594</t>
   </si>
   <si>
     <t xml:space="preserve">54.8807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8901596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7087211608887</t>
+    <t xml:space="preserve">52.8901634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7087249755859</t>
   </si>
   <si>
     <t xml:space="preserve">52.6111068725586</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3040351867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3412475585938</t>
+    <t xml:space="preserve">54.3040390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3412437438965</t>
   </si>
   <si>
     <t xml:space="preserve">51.6995315551758</t>
@@ -3872,19 +3872,19 @@
     <t xml:space="preserve">52.4064674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8993530273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.271427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8389511108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0993957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6437187194824</t>
+    <t xml:space="preserve">54.899356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2714233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8389472961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0993995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6437149047852</t>
   </si>
   <si>
     <t xml:space="preserve">50.6391181945801</t>
@@ -3899,73 +3899,73 @@
     <t xml:space="preserve">50.9739875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9181747436523</t>
+    <t xml:space="preserve">50.9181785583496</t>
   </si>
   <si>
     <t xml:space="preserve">50.8809700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4624977111816</t>
+    <t xml:space="preserve">48.4624938964844</t>
   </si>
   <si>
     <t xml:space="preserve">45.802173614502</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1230316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9464073181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8768081665039</t>
+    <t xml:space="preserve">47.1230354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.946403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8768043518066</t>
   </si>
   <si>
     <t xml:space="preserve">42.146556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4954299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9743118286133</t>
+    <t xml:space="preserve">41.495433807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.974308013916</t>
   </si>
   <si>
     <t xml:space="preserve">43.9976196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6208457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6487426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2441711425781</t>
+    <t xml:space="preserve">44.6208419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6487503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2441749572754</t>
   </si>
   <si>
     <t xml:space="preserve">45.7091522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7881698608398</t>
+    <t xml:space="preserve">46.7881660461426</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044311523438</t>
+    <t xml:space="preserve">47.1044273376465</t>
   </si>
   <si>
     <t xml:space="preserve">46.2951736450195</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8207740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2021484375</t>
+    <t xml:space="preserve">45.8207778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2021522521973</t>
   </si>
   <si>
     <t xml:space="preserve">46.2765655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8717727661133</t>
+    <t xml:space="preserve">48.8717765808105</t>
   </si>
   <si>
     <t xml:space="preserve">47.1974487304688</t>
@@ -3977,22 +3977,22 @@
     <t xml:space="preserve">48.9275856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2810554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9556045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9882125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4392929077148</t>
+    <t xml:space="preserve">49.2810516357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9556007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.988208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4392967224121</t>
   </si>
   <si>
     <t xml:space="preserve">45.1603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0254173278809</t>
+    <t xml:space="preserve">46.0254135131836</t>
   </si>
   <si>
     <t xml:space="preserve">46.4533004760742</t>
@@ -4001,25 +4001,25 @@
     <t xml:space="preserve">47.0300140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1835479736328</t>
+    <t xml:space="preserve">46.1835517883301</t>
   </si>
   <si>
     <t xml:space="preserve">47.5881233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5277137756348</t>
+    <t xml:space="preserve">46.527717590332</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8301887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.430103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.267261505127</t>
+    <t xml:space="preserve">43.8301849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2672653198242</t>
   </si>
   <si>
     <t xml:space="preserve">46.7695617675781</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">45.5696296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6115379333496</t>
+    <t xml:space="preserve">44.6115417480469</t>
   </si>
   <si>
     <t xml:space="preserve">43.9604110717773</t>
@@ -4043,19 +4043,19 @@
     <t xml:space="preserve">38.9095268249512</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8676147460938</t>
+    <t xml:space="preserve">39.8676109313965</t>
   </si>
   <si>
     <t xml:space="preserve">41.6163520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8070907592773</t>
+    <t xml:space="preserve">40.8070945739746</t>
   </si>
   <si>
     <t xml:space="preserve">42.1930656433105</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2814865112305</t>
+    <t xml:space="preserve">41.281494140625</t>
   </si>
   <si>
     <t xml:space="preserve">42.1093482971191</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">40.6489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0908508300781</t>
+    <t xml:space="preserve">40.0908546447754</t>
   </si>
   <si>
     <t xml:space="preserve">39.3095016479492</t>
@@ -4076,19 +4076,19 @@
     <t xml:space="preserve">38.5640716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6018142700195</t>
+    <t xml:space="preserve">38.6018180847168</t>
   </si>
   <si>
     <t xml:space="preserve">39.819034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.658821105957</t>
+    <t xml:space="preserve">40.6588172912598</t>
   </si>
   <si>
     <t xml:space="preserve">42.3572616577148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1779823303223</t>
+    <t xml:space="preserve">42.177978515625</t>
   </si>
   <si>
     <t xml:space="preserve">43.6499633789062</t>
@@ -4097,10 +4097,10 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801216125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.234790802002</t>
+    <t xml:space="preserve">43.4801177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2347869873047</t>
   </si>
   <si>
     <t xml:space="preserve">42.1119346618652</t>
@@ -4118,13 +4118,13 @@
     <t xml:space="preserve">36.2145614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5166969299316</t>
+    <t xml:space="preserve">37.5167007446289</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0917015075684</t>
+    <t xml:space="preserve">35.0916976928711</t>
   </si>
   <si>
     <t xml:space="preserve">34.9690399169922</t>
@@ -4142,25 +4142,25 @@
     <t xml:space="preserve">37.4600868225098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7054176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.394229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4980201721191</t>
+    <t xml:space="preserve">37.7054138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3942260742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4980239868164</t>
   </si>
   <si>
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639762878418</t>
+    <t xml:space="preserve">38.0639801025391</t>
   </si>
   <si>
     <t xml:space="preserve">37.3751640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8943252563477</t>
+    <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
     <t xml:space="preserve">39.0547332763672</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">37.8280830383301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1587219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3474388122559</t>
+    <t xml:space="preserve">38.5735092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1587257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3474349975586</t>
   </si>
   <si>
     <t xml:space="preserve">40.7531776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1494789123535</t>
+    <t xml:space="preserve">41.1494827270508</t>
   </si>
   <si>
     <t xml:space="preserve">41.5552215576172</t>
@@ -4205,25 +4205,25 @@
     <t xml:space="preserve">39.6586265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7248725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9990921020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9239921569824</t>
+    <t xml:space="preserve">40.7248687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9990882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9239883422852</t>
   </si>
   <si>
     <t xml:space="preserve">45.9806060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0464630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3389701843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5278816223145</t>
+    <t xml:space="preserve">45.046459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3389663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5278854370117</t>
   </si>
   <si>
     <t xml:space="preserve">46.5184440612793</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">46.4995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8579406738281</t>
+    <t xml:space="preserve">45.8579368591309</t>
   </si>
   <si>
     <t xml:space="preserve">46.7165946960449</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">46.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0089149475098</t>
+    <t xml:space="preserve">46.0089111328125</t>
   </si>
   <si>
     <t xml:space="preserve">46.754337310791</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">44.8388748168945</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2163009643555</t>
+    <t xml:space="preserve">45.2163047790527</t>
   </si>
   <si>
     <t xml:space="preserve">45.2729225158691</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">43.046070098877</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1496734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3100814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1213645935059</t>
+    <t xml:space="preserve">42.1496696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3100852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1213684082031</t>
   </si>
   <si>
     <t xml:space="preserve">41.0456848144531</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">41.1777877807617</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3948059082031</t>
+    <t xml:space="preserve">41.3948097229004</t>
   </si>
   <si>
     <t xml:space="preserve">41.6967544555664</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4704895019531</t>
+    <t xml:space="preserve">42.4704856872559</t>
   </si>
   <si>
     <t xml:space="preserve">42.998893737793</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">41.5646553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.923023223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4891662597656</t>
+    <t xml:space="preserve">40.9230194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4891700744629</t>
   </si>
   <si>
     <t xml:space="preserve">41.8005523681641</t>
@@ -4325,28 +4325,28 @@
     <t xml:space="preserve">42.4610557556152</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9511337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2623252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6210784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5644645690918</t>
+    <t xml:space="preserve">39.9511375427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.262321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6210746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5644607543945</t>
   </si>
   <si>
     <t xml:space="preserve">41.0645599365234</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8095970153809</t>
+    <t xml:space="preserve">39.8095932006836</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9794387817383</t>
+    <t xml:space="preserve">39.9794425964355</t>
   </si>
   <si>
     <t xml:space="preserve">43.2064819335938</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">41.8666000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0271987915039</t>
+    <t xml:space="preserve">43.0272026062012</t>
   </si>
   <si>
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252578735352</t>
+    <t xml:space="preserve">42.7252540588379</t>
   </si>
   <si>
     <t xml:space="preserve">43.8009376525879</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">44.0557022094727</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7160186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6690292358398</t>
+    <t xml:space="preserve">43.7160148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6690330505371</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4391,31 +4391,31 @@
     <t xml:space="preserve">43.4329414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1693229675293</t>
+    <t xml:space="preserve">46.169319152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.6692237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7443237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7346954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2249641418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6873168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0173835754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8756446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8290519714355</t>
+    <t xml:space="preserve">43.7443199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.734691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.224967956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6873207092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0173797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8756484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8290481567383</t>
   </si>
   <si>
     <t xml:space="preserve">42.9422760009766</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7732086181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6131935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6129951477051</t>
+    <t xml:space="preserve">46.7732124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6131896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6129989624023</t>
   </si>
   <si>
     <t xml:space="preserve">47.7639694213867</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">47.1978225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0657196044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0185394287109</t>
+    <t xml:space="preserve">47.0657234191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0185432434082</t>
   </si>
   <si>
     <t xml:space="preserve">45.6314811706543</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">45.4144592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2917900085449</t>
+    <t xml:space="preserve">45.2917938232422</t>
   </si>
   <si>
     <t xml:space="preserve">44.8200035095215</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.546558380127</t>
+    <t xml:space="preserve">45.5465621948242</t>
   </si>
   <si>
     <t xml:space="preserve">45.5937347412109</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">45.7447090148926</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5844917297363</t>
+    <t xml:space="preserve">46.5844955444336</t>
   </si>
   <si>
     <t xml:space="preserve">47.2544403076172</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">46.4146499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7918853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9049263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1504516601562</t>
+    <t xml:space="preserve">45.7918891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9049224853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.150447845459</t>
   </si>
   <si>
     <t xml:space="preserve">45.3861465454102</t>
@@ -4517,10 +4517,10 @@
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5563850402832</t>
+    <t xml:space="preserve">47.8017158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5563812255859</t>
   </si>
   <si>
     <t xml:space="preserve">48.5565757751465</t>
@@ -4529,19 +4529,19 @@
     <t xml:space="preserve">49.3869247436523</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7077407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.971752166748</t>
+    <t xml:space="preserve">49.7077445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9717483520508</t>
   </si>
   <si>
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8779754638672</t>
+    <t xml:space="preserve">50.4814796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8779716491699</t>
   </si>
   <si>
     <t xml:space="preserve">52.3497619628906</t>
@@ -4556,25 +4556,25 @@
     <t xml:space="preserve">51.915714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0480155944824</t>
+    <t xml:space="preserve">53.0480117797852</t>
   </si>
   <si>
     <t xml:space="preserve">53.3310852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1046257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2555999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5199966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0859527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9727172851562</t>
+    <t xml:space="preserve">53.1046295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2555961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5199928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0859489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9727210998535</t>
   </si>
   <si>
     <t xml:space="preserve">53.8406181335449</t>
@@ -4583,19 +4583,19 @@
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4447059631348</t>
+    <t xml:space="preserve">55.4447021484375</t>
   </si>
   <si>
     <t xml:space="preserve">54.1991767883301</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0293350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4254417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.198787689209</t>
+    <t xml:space="preserve">54.0293312072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4254455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1987915039062</t>
   </si>
   <si>
     <t xml:space="preserve">53.0291404724121</t>
@@ -4604,13 +4604,13 @@
     <t xml:space="preserve">53.5009307861328</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9349746704102</t>
+    <t xml:space="preserve">53.9349784851074</t>
   </si>
   <si>
     <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4067649841309</t>
+    <t xml:space="preserve">54.4067687988281</t>
   </si>
   <si>
     <t xml:space="preserve">54.4445114135742</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">55.0106544494629</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5388679504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3316688537598</t>
+    <t xml:space="preserve">54.5388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">57.3507347106934</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1431465148926</t>
+    <t xml:space="preserve">57.1431427001953</t>
   </si>
   <si>
     <t xml:space="preserve">57.7470359802246</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">57.1808853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4071502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8789443969727</t>
+    <t xml:space="preserve">56.407154083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8789405822754</t>
   </si>
   <si>
     <t xml:space="preserve">54.8974266052246</t>
@@ -4664,16 +4664,16 @@
     <t xml:space="preserve">57.0676612854004</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2748565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6526756286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2184371948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2939224243164</t>
+    <t xml:space="preserve">55.2748603820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6526718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2184410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2939262390137</t>
   </si>
   <si>
     <t xml:space="preserve">57.5017051696777</t>
@@ -4685,16 +4685,16 @@
     <t xml:space="preserve">58.1433410644531</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2186317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2752456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9170722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8981971740723</t>
+    <t xml:space="preserve">57.2186279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2752494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9170761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8982009887695</t>
   </si>
   <si>
     <t xml:space="preserve">59.9550132751465</t>
@@ -4715,76 +4715,76 @@
     <t xml:space="preserve">59.8417778015137</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4266052246094</t>
+    <t xml:space="preserve">59.4266090393066</t>
   </si>
   <si>
     <t xml:space="preserve">62.0686264038086</t>
   </si>
   <si>
-    <t xml:space="preserve">62.2196006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9929466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8044242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2007255554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1443061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4085006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8614273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7293281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.993522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3707733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6917724609375</t>
+    <t xml:space="preserve">62.2196083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9929504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8044204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2007293701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.408504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8614234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7293319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9935264587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3707656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.691780090332</t>
   </si>
   <si>
     <t xml:space="preserve">63.5028686523438</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9933395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4649314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8987846374512</t>
+    <t xml:space="preserve">62.9933319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4649276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8987808227539</t>
   </si>
   <si>
     <t xml:space="preserve">63.01220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9178466796875</t>
+    <t xml:space="preserve">62.9178504943848</t>
   </si>
   <si>
     <t xml:space="preserve">61.5024795532227</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5968322753906</t>
+    <t xml:space="preserve">61.5968360900879</t>
   </si>
   <si>
     <t xml:space="preserve">60.8608436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7287445068359</t>
+    <t xml:space="preserve">60.7287483215332</t>
   </si>
   <si>
     <t xml:space="preserve">62.1307678222656</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">60.8631858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2293930053711</t>
+    <t xml:space="preserve">60.2293968200684</t>
   </si>
   <si>
     <t xml:space="preserve">60.9784202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8055686950684</t>
+    <t xml:space="preserve">60.8055648803711</t>
   </si>
   <si>
     <t xml:space="preserve">59.4227523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8042678833008</t>
+    <t xml:space="preserve">61.804271697998</t>
   </si>
   <si>
     <t xml:space="preserve">60.9015960693359</t>
@@ -4823,16 +4823,16 @@
     <t xml:space="preserve">61.2665061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.4982719421387</t>
+    <t xml:space="preserve">60.4982757568359</t>
   </si>
   <si>
     <t xml:space="preserve">61.9963264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1102638244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.071849822998</t>
+    <t xml:space="preserve">63.1102676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">62.898998260498</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">60.9976272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9605102539062</t>
+    <t xml:space="preserve">59.9605140686035</t>
   </si>
   <si>
     <t xml:space="preserve">59.8068656921387</t>
@@ -4868,22 +4868,22 @@
     <t xml:space="preserve">60.3638343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8247756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4214477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7671546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4022445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.865779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.153865814209</t>
+    <t xml:space="preserve">60.8247718811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4214515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7671585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4022483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8657836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1538696289062</t>
   </si>
   <si>
     <t xml:space="preserve">60.1717758178711</t>
@@ -4895,10 +4895,10 @@
     <t xml:space="preserve">62.8797950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">63.379150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2831153869629</t>
+    <t xml:space="preserve">63.3791427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2831192016602</t>
   </si>
   <si>
     <t xml:space="preserve">61.4393577575684</t>
@@ -4907,13 +4907,13 @@
     <t xml:space="preserve">60.5750999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5379867553711</t>
+    <t xml:space="preserve">59.5379829406738</t>
   </si>
   <si>
     <t xml:space="preserve">59.3843383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7492523193359</t>
+    <t xml:space="preserve">59.7492485046387</t>
   </si>
   <si>
     <t xml:space="preserve">59.9028968811035</t>
@@ -4922,10 +4922,10 @@
     <t xml:space="preserve">60.3254203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2883148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.302318572998</t>
+    <t xml:space="preserve">59.2883110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3023223876953</t>
   </si>
   <si>
     <t xml:space="preserve">62.783763885498</t>
@@ -4937,25 +4937,25 @@
     <t xml:space="preserve">60.6135101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1922836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3651351928711</t>
+    <t xml:space="preserve">59.1922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3651313781738</t>
   </si>
   <si>
     <t xml:space="preserve">61.4969787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5161781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7850570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9797172546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8439826965332</t>
+    <t xml:space="preserve">61.5161819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7850608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9797210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8439788818359</t>
   </si>
   <si>
     <t xml:space="preserve">60.5558929443359</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">59.5763969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5571937561035</t>
+    <t xml:space="preserve">59.5571899414062</t>
   </si>
   <si>
     <t xml:space="preserve">59.8836898803711</t>
@@ -4982,28 +4982,28 @@
     <t xml:space="preserve">60.1525688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1333618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1346626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.196174621582</t>
+    <t xml:space="preserve">60.1333656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1346664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1961784362793</t>
   </si>
   <si>
     <t xml:space="preserve">56.080940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1769676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8683815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2153816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7915573120117</t>
+    <t xml:space="preserve">56.1769714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8683776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2153854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7915534973145</t>
   </si>
   <si>
     <t xml:space="preserve">57.4061393737793</t>
@@ -5015,22 +5015,22 @@
     <t xml:space="preserve">55.4087409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">55.447151184082</t>
+    <t xml:space="preserve">55.4471473693848</t>
   </si>
   <si>
     <t xml:space="preserve">54.2948036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1974754333496</t>
+    <t xml:space="preserve">55.1974716186523</t>
   </si>
   <si>
     <t xml:space="preserve">54.0451240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1437492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2218742370605</t>
+    <t xml:space="preserve">52.1437530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2218704223633</t>
   </si>
   <si>
     <t xml:space="preserve">52.3742218017578</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">52.4510459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6431045532227</t>
+    <t xml:space="preserve">52.6431007385254</t>
   </si>
   <si>
     <t xml:space="preserve">53.7954521179199</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">50.7417259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">51.068229675293</t>
+    <t xml:space="preserve">51.0682258605957</t>
   </si>
   <si>
     <t xml:space="preserve">50.8377571105957</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">50.8761711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9337882995605</t>
+    <t xml:space="preserve">50.9337844848633</t>
   </si>
   <si>
     <t xml:space="preserve">51.0106086730957</t>
@@ -5096,22 +5096,22 @@
     <t xml:space="preserve">49.8006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.583667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8237457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9965972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5823707580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1668510437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9747924804688</t>
+    <t xml:space="preserve">46.5836715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8237419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9965934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5823745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1668548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.974796295166</t>
   </si>
   <si>
     <t xml:space="preserve">48.7827339172363</t>
@@ -5129,19 +5129,19 @@
     <t xml:space="preserve">47.4959449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7552223205566</t>
+    <t xml:space="preserve">47.7552261352539</t>
   </si>
   <si>
     <t xml:space="preserve">49.4165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4946479797363</t>
+    <t xml:space="preserve">48.4946517944336</t>
   </si>
   <si>
     <t xml:space="preserve">48.4370307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5701751708984</t>
+    <t xml:space="preserve">49.5701713562012</t>
   </si>
   <si>
     <t xml:space="preserve">48.9363822937012</t>
@@ -5156,16 +5156,16 @@
     <t xml:space="preserve">49.5125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2628784179688</t>
+    <t xml:space="preserve">49.262882232666</t>
   </si>
   <si>
     <t xml:space="preserve">48.7059135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9939994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.859561920166</t>
+    <t xml:space="preserve">48.9940032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8595581054688</t>
   </si>
   <si>
     <t xml:space="preserve">48.6675033569336</t>
@@ -5174,13 +5174,13 @@
     <t xml:space="preserve">49.4549407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8774681091309</t>
+    <t xml:space="preserve">49.8774642944336</t>
   </si>
   <si>
     <t xml:space="preserve">50.2999954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">51.529167175293</t>
+    <t xml:space="preserve">51.5291633605957</t>
   </si>
   <si>
     <t xml:space="preserve">52.4318389892578</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">52.9696006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5265693664551</t>
+    <t xml:space="preserve">53.5265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">54.0259208679199</t>
@@ -5210,13 +5210,13 @@
     <t xml:space="preserve">53.7762451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7378349304199</t>
+    <t xml:space="preserve">53.7378311157227</t>
   </si>
   <si>
     <t xml:space="preserve">53.3537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4881553649902</t>
+    <t xml:space="preserve">53.4881591796875</t>
   </si>
   <si>
     <t xml:space="preserve">53.4305381774902</t>
@@ -5252,34 +5252,34 @@
     <t xml:space="preserve">49.1092338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4933547973633</t>
+    <t xml:space="preserve">49.493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">49.3973197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8390579223633</t>
+    <t xml:space="preserve">49.839054107666</t>
   </si>
   <si>
     <t xml:space="preserve">49.896671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6020927429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0054168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0246238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4279441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0617332458496</t>
+    <t xml:space="preserve">54.6020965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0054130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0246200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8901824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4279479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0617370605469</t>
   </si>
   <si>
     <t xml:space="preserve">55.8312644958496</t>
@@ -5294,10 +5294,10 @@
     <t xml:space="preserve">57.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0028190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3293190002441</t>
+    <t xml:space="preserve">57.0028228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">60.0373344421387</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">61.1896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5545921325684</t>
+    <t xml:space="preserve">61.5545959472656</t>
   </si>
   <si>
     <t xml:space="preserve">61.1512718200684</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">64.2626113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3599433898926</t>
+    <t xml:space="preserve">63.3599395751953</t>
   </si>
   <si>
     <t xml:space="preserve">63.9937286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3394317626953</t>
+    <t xml:space="preserve">64.3394393920898</t>
   </si>
   <si>
     <t xml:space="preserve">64.4354629516602</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5686111450195</t>
+    <t xml:space="preserve">65.568603515625</t>
   </si>
   <si>
     <t xml:space="preserve">66.6249237060547</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">66.8746032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5467987060547</t>
+    <t xml:space="preserve">67.5468063354492</t>
   </si>
   <si>
     <t xml:space="preserve">66.5096969604492</t>
@@ -5357,16 +5357,16 @@
     <t xml:space="preserve">66.4712829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7798767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5301971435547</t>
+    <t xml:space="preserve">65.7798690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5301895141602</t>
   </si>
   <si>
     <t xml:space="preserve">65.4533767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2997207641602</t>
+    <t xml:space="preserve">65.2997283935547</t>
   </si>
   <si>
     <t xml:space="preserve">65.799072265625</t>
@@ -5393,7 +5393,7 @@
     <t xml:space="preserve">62.0155372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0539512634277</t>
+    <t xml:space="preserve">62.0539474487305</t>
   </si>
   <si>
     <t xml:space="preserve">61.6122131347656</t>
@@ -5405,28 +5405,28 @@
     <t xml:space="preserve">63.4367599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8413887023926</t>
+    <t xml:space="preserve">63.0334396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8413848876953</t>
   </si>
   <si>
     <t xml:space="preserve">62.668529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2254905700684</t>
+    <t xml:space="preserve">63.2254981994629</t>
   </si>
   <si>
     <t xml:space="preserve">64.1473770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1883888244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3420295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9579162597656</t>
+    <t xml:space="preserve">62.1883850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3420333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9579124450684</t>
   </si>
   <si>
     <t xml:space="preserve">61.573802947998</t>
@@ -6387,6 +6387,9 @@
   </si>
   <si>
     <t xml:space="preserve">49.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6399993896484</t>
   </si>
 </sst>
 </file>
@@ -71387,7 +71390,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.652025463</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>588993</v>
@@ -71408,6 +71411,32 @@
         <v>2124</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6503587963</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>1235216</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>49.5299987792969</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>47.8300018310547</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>49.4599990844727</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>48.6399993896484</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2125</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="2129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="2130">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698104858398</t>
+    <t xml:space="preserve">10.9698095321655</t>
   </si>
   <si>
     <t xml:space="preserve">10.845253944397</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">10.8986358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.987606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744384765625</t>
+    <t xml:space="preserve">10.9876041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744375228882</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573602676392</t>
@@ -71,22 +71,22 @@
     <t xml:space="preserve">11.156644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5481052398682</t>
+    <t xml:space="preserve">11.5481061935425</t>
   </si>
   <si>
     <t xml:space="preserve">11.734938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018424987793</t>
+    <t xml:space="preserve">11.4057569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8239068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018453598022</t>
   </si>
   <si>
     <t xml:space="preserve">12.1263999938965</t>
@@ -95,37 +95,37 @@
     <t xml:space="preserve">12.0997104644775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7260408401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908117294312</t>
+    <t xml:space="preserve">11.7260417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908126831055</t>
   </si>
   <si>
     <t xml:space="preserve">11.9484634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8950824737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616300582886</t>
+    <t xml:space="preserve">11.8950815200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616291046143</t>
   </si>
   <si>
     <t xml:space="preserve">11.9128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4146518707275</t>
+    <t xml:space="preserve">11.4146537780762</t>
   </si>
   <si>
     <t xml:space="preserve">11.2723035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0409841537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2545080184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431190490723</t>
+    <t xml:space="preserve">11.0409851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.254508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431209564209</t>
   </si>
   <si>
     <t xml:space="preserve">11.2989931106567</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">11.672661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772878646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110984802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2509546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2687520980835</t>
+    <t xml:space="preserve">11.8772897720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.250955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2687492370605</t>
   </si>
   <si>
     <t xml:space="preserve">12.4022026062012</t>
@@ -155,31 +155,31 @@
     <t xml:space="preserve">12.1975755691528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7402820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.962703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7669725418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2118167877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075441360474</t>
+    <t xml:space="preserve">12.7402830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9627017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7669734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2118148803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.407546043396</t>
   </si>
   <si>
     <t xml:space="preserve">13.478720664978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9680471420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4520301818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210718154907</t>
+    <t xml:space="preserve">13.9680461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4520282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210708618164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7100391387939</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">13.336371421814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0427751541138</t>
+    <t xml:space="preserve">13.0427761077881</t>
   </si>
   <si>
     <t xml:space="preserve">13.060567855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9893951416016</t>
+    <t xml:space="preserve">12.9893932342529</t>
   </si>
   <si>
     <t xml:space="preserve">12.9004259109497</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">13.0160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9449110031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.096155166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.514307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1228475570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9804964065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.927116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5890369415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7936639785767</t>
+    <t xml:space="preserve">12.9449100494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0961561203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5143070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1228456497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9804973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9271154403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.589035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7936630249023</t>
   </si>
   <si>
     <t xml:space="preserve">12.8292512893677</t>
@@ -242,61 +242,61 @@
     <t xml:space="preserve">13.2029190063477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3897523880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1673307418823</t>
+    <t xml:space="preserve">13.3897533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1673316955566</t>
   </si>
   <si>
     <t xml:space="preserve">12.6869010925293</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5089654922485</t>
+    <t xml:space="preserve">12.5089645385742</t>
   </si>
   <si>
     <t xml:space="preserve">12.5979328155518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9715995788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9982929229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3185768127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9324607849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947385787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502544403076</t>
+    <t xml:space="preserve">12.9716014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9982891082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3185777664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9324598312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570154190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502553939819</t>
   </si>
   <si>
     <t xml:space="preserve">13.6388635635376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5676889419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3630619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.345269203186</t>
+    <t xml:space="preserve">13.5676898956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3630638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452682495117</t>
   </si>
   <si>
     <t xml:space="preserve">13.2285184860229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5608043670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4440546035767</t>
+    <t xml:space="preserve">13.5608034133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4440565109253</t>
   </si>
   <si>
     <t xml:space="preserve">13.2734222412109</t>
@@ -305,70 +305,70 @@
     <t xml:space="preserve">13.4709968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5967254638672</t>
+    <t xml:space="preserve">13.5967264175415</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620161056519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4979391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183250427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7314376831055</t>
+    <t xml:space="preserve">13.4979381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6685724258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
     <t xml:space="preserve">13.7404174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.300365447998</t>
+    <t xml:space="preserve">13.3003644943237</t>
   </si>
   <si>
     <t xml:space="preserve">13.1566734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7256021499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.860312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6775522232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8571662902832</t>
+    <t xml:space="preserve">12.7256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8603115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6775531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8571672439575</t>
   </si>
   <si>
     <t xml:space="preserve">14.2253732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9321556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6986608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9950218200684</t>
+    <t xml:space="preserve">12.9321565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6986598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476926803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9950227737427</t>
   </si>
   <si>
     <t xml:space="preserve">12.6178340911865</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">12.8782730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9680786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9231767654419</t>
+    <t xml:space="preserve">12.9680776596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9231748580933</t>
   </si>
   <si>
     <t xml:space="preserve">13.1746349334717</t>
@@ -398,28 +398,28 @@
     <t xml:space="preserve">12.7705059051514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3452682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8302230834961</t>
+    <t xml:space="preserve">13.3452672958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8302240371704</t>
   </si>
   <si>
     <t xml:space="preserve">14.1714887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0637216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3690633773804</t>
+    <t xml:space="preserve">14.063720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3690624237061</t>
   </si>
   <si>
     <t xml:space="preserve">14.0816831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9559516906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069189071655</t>
+    <t xml:space="preserve">13.9559526443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069198608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.6057071685791</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">13.8481855392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0457601547241</t>
+    <t xml:space="preserve">14.0457611083984</t>
   </si>
   <si>
     <t xml:space="preserve">13.9918756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9200296401978</t>
+    <t xml:space="preserve">13.9200305938721</t>
   </si>
   <si>
     <t xml:space="preserve">13.7673597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0008563995361</t>
+    <t xml:space="preserve">14.0008554458618</t>
   </si>
   <si>
     <t xml:space="preserve">13.7583780288696</t>
@@ -458,52 +458,52 @@
     <t xml:space="preserve">13.6955137252808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5877456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5248804092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.354248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4171123504639</t>
+    <t xml:space="preserve">13.5877447128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.524881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4171133041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159006118774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7224559783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5338611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7044944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9110498428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0098361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4530344009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6506090164185</t>
+    <t xml:space="preserve">13.7224550247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.533860206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7044954299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9110488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.009838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4530363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6506109237671</t>
   </si>
   <si>
     <t xml:space="preserve">13.6416292190552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7853221893311</t>
+    <t xml:space="preserve">13.7853202819824</t>
   </si>
   <si>
     <t xml:space="preserve">13.4799776077271</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">13.8392038345337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8930883407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9649333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8751268386841</t>
+    <t xml:space="preserve">14.0996446609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8930892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8751277923584</t>
   </si>
   <si>
     <t xml:space="preserve">13.79430103302</t>
@@ -530,28 +530,28 @@
     <t xml:space="preserve">13.6236686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3991527557373</t>
+    <t xml:space="preserve">13.3991537094116</t>
   </si>
   <si>
     <t xml:space="preserve">13.3901700973511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4889583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6326484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3273077011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763414382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8661470413208</t>
+    <t xml:space="preserve">13.4889602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6326494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3273067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8661451339722</t>
   </si>
   <si>
     <t xml:space="preserve">14.0547399520874</t>
@@ -560,25 +560,25 @@
     <t xml:space="preserve">14.6474637985229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6384840011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9168863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964994430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0426139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989229202271</t>
+    <t xml:space="preserve">14.6384830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9168853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0426120758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989210128784</t>
   </si>
   <si>
     <t xml:space="preserve">14.548677444458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7372694015503</t>
+    <t xml:space="preserve">14.7372722625732</t>
   </si>
   <si>
     <t xml:space="preserve">14.7731943130493</t>
@@ -587,25 +587,25 @@
     <t xml:space="preserve">14.8719797134399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7911539077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6833877563477</t>
+    <t xml:space="preserve">14.7911548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564455032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6833868026733</t>
   </si>
   <si>
     <t xml:space="preserve">14.7013483047485</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8450384140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0875177383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9707670211792</t>
+    <t xml:space="preserve">14.8450403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0875158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9707689285278</t>
   </si>
   <si>
     <t xml:space="preserve">14.7103281021118</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">14.6744070053101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9528064727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377632141113</t>
+    <t xml:space="preserve">14.9528074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.437762260437</t>
   </si>
   <si>
     <t xml:space="preserve">15.4736862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6892204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4826669692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790279388428</t>
+    <t xml:space="preserve">15.6892232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251453399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.482666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790269851685</t>
   </si>
   <si>
     <t xml:space="preserve">16.0933513641357</t>
@@ -644,103 +644,103 @@
     <t xml:space="preserve">16.2011184692383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1921405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.246021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9855842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6353349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9317007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766025543213</t>
+    <t xml:space="preserve">16.192138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2460231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9855813980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137392044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6353387832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9316997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9766044616699</t>
   </si>
   <si>
     <t xml:space="preserve">15.9586420059204</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9406795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867959976196</t>
+    <t xml:space="preserve">15.9406805038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867931365967</t>
   </si>
   <si>
     <t xml:space="preserve">16.1741790771484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.102331161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0484485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8957796096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.967625617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0991859436035</t>
+    <t xml:space="preserve">16.1023330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0484504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8957777023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9676237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831607818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0991878509521</t>
   </si>
   <si>
     <t xml:space="preserve">17.2608375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">17.162052154541</t>
+    <t xml:space="preserve">17.1620502471924</t>
   </si>
   <si>
     <t xml:space="preserve">17.296760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3326816558838</t>
+    <t xml:space="preserve">17.3326797485352</t>
   </si>
   <si>
     <t xml:space="preserve">17.5122947692871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5661811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.65598487854</t>
+    <t xml:space="preserve">17.5661792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6559867858887</t>
   </si>
   <si>
     <t xml:space="preserve">17.6021022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8535594940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.006233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1768665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8805046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.060115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0870590209961</t>
+    <t xml:space="preserve">17.8535614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1768646240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8805027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0601196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0870571136475</t>
   </si>
   <si>
     <t xml:space="preserve">18.320556640625</t>
@@ -764,28 +764,28 @@
     <t xml:space="preserve">18.6169166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9312400817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2276039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2365818023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2006587982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.479061126709</t>
+    <t xml:space="preserve">18.9312419891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2276058197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2365856170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.200662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4790630340576</t>
   </si>
   <si>
     <t xml:space="preserve">19.5598888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1108531951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2096424102783</t>
+    <t xml:space="preserve">19.1108570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2096385955811</t>
   </si>
   <si>
     <t xml:space="preserve">19.3174114227295</t>
@@ -794,34 +794,34 @@
     <t xml:space="preserve">19.5329456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4611015319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5778503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5149841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1885299682617</t>
+    <t xml:space="preserve">19.6945991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5778484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5149822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.188533782959</t>
   </si>
   <si>
     <t xml:space="preserve">20.4310111999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3501892089844</t>
+    <t xml:space="preserve">20.3501873016357</t>
   </si>
   <si>
     <t xml:space="preserve">20.6645107269287</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8351440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1135425567627</t>
+    <t xml:space="preserve">20.8351402282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1135444641113</t>
   </si>
   <si>
     <t xml:space="preserve">20.4759140014648</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">19.7844066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9999408721924</t>
+    <t xml:space="preserve">19.9999389648438</t>
   </si>
   <si>
     <t xml:space="preserve">19.8921718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9819774627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.874210357666</t>
+    <t xml:space="preserve">19.9819793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8742084503174</t>
   </si>
   <si>
     <t xml:space="preserve">19.9909610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3892555236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5509052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6505184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6052379608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4875164031982</t>
+    <t xml:space="preserve">19.389253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5509090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.650520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6052398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4875183105469</t>
   </si>
   <si>
     <t xml:space="preserve">20.0127391815186</t>
@@ -869,25 +869,25 @@
     <t xml:space="preserve">19.2339611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6324100494385</t>
+    <t xml:space="preserve">19.6324081420898</t>
   </si>
   <si>
     <t xml:space="preserve">19.7048530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2792415618896</t>
+    <t xml:space="preserve">19.279239654541</t>
   </si>
   <si>
     <t xml:space="preserve">18.9260749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0075740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9713554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0800170898438</t>
+    <t xml:space="preserve">19.0075759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9713535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.080020904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.5819664001465</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">18.8355178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1252956390381</t>
+    <t xml:space="preserve">19.1252975463867</t>
   </si>
   <si>
     <t xml:space="preserve">19.0437984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3426265716553</t>
+    <t xml:space="preserve">19.3426284790039</t>
   </si>
   <si>
     <t xml:space="preserve">19.2249069213867</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">19.6142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2158508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1524639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1434078216553</t>
+    <t xml:space="preserve">19.2158527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1524620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1434059143066</t>
   </si>
   <si>
     <t xml:space="preserve">19.3245162963867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9441871643066</t>
+    <t xml:space="preserve">18.944185256958</t>
   </si>
   <si>
     <t xml:space="preserve">18.3736877441406</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5638523101807</t>
+    <t xml:space="preserve">18.5638542175293</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362972259521</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">18.600076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7359066009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6091327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1071872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2882957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.378849029541</t>
+    <t xml:space="preserve">18.8083534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7359085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.609130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1071853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.288293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060192108154</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">19.4331855773926</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2701835632324</t>
+    <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
     <t xml:space="preserve">19.1977405548096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.239128112793</t>
+    <t xml:space="preserve">20.2391300201416</t>
   </si>
   <si>
     <t xml:space="preserve">20.4655151367188</t>
@@ -980,61 +980,61 @@
     <t xml:space="preserve">20.5560722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568458557129</t>
+    <t xml:space="preserve">20.3568496704102</t>
   </si>
   <si>
     <t xml:space="preserve">20.2572402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3930702209473</t>
+    <t xml:space="preserve">20.3930721282959</t>
   </si>
   <si>
     <t xml:space="preserve">20.329683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3749599456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4021282196045</t>
+    <t xml:space="preserve">20.3749618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4021263122559</t>
   </si>
   <si>
     <t xml:space="preserve">20.3477935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8458461761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1446800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3439025878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4254016876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3710689544678</t>
+    <t xml:space="preserve">20.8458499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.144681930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5431289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.380126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.343900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4254055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.371072769165</t>
   </si>
   <si>
     <t xml:space="preserve">21.2805156707764</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2080726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8730144500732</t>
+    <t xml:space="preserve">21.2080707550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8730163574219</t>
   </si>
   <si>
     <t xml:space="preserve">21.2714576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.615571975708</t>
+    <t xml:space="preserve">21.6155700683594</t>
   </si>
   <si>
     <t xml:space="preserve">21.8962917327881</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">21.7423458099365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7966804504395</t>
+    <t xml:space="preserve">21.7966785430908</t>
   </si>
   <si>
     <t xml:space="preserve">21.9959030151367</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">22.158899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4305686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3671798706055</t>
+    <t xml:space="preserve">22.430570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3671779632568</t>
   </si>
   <si>
     <t xml:space="preserve">22.5935668945312</t>
@@ -1067,34 +1067,34 @@
     <t xml:space="preserve">22.5030136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2404022216797</t>
+    <t xml:space="preserve">22.2404003143311</t>
   </si>
   <si>
     <t xml:space="preserve">22.3852882385254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2313442230225</t>
+    <t xml:space="preserve">22.2313423156738</t>
   </si>
   <si>
     <t xml:space="preserve">22.2132358551025</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2494564056396</t>
+    <t xml:space="preserve">22.249454498291</t>
   </si>
   <si>
     <t xml:space="preserve">21.959680557251</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8238468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0683460235596</t>
+    <t xml:space="preserve">21.8238487243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0683441162109</t>
   </si>
   <si>
     <t xml:space="preserve">22.1136245727539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1407928466797</t>
+    <t xml:space="preserve">22.1407909393311</t>
   </si>
   <si>
     <t xml:space="preserve">21.8419570922852</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">21.470682144165</t>
   </si>
   <si>
-    <t xml:space="preserve">22.149845123291</t>
+    <t xml:space="preserve">22.1498470306396</t>
   </si>
   <si>
     <t xml:space="preserve">22.2766227722168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.059289932251</t>
+    <t xml:space="preserve">22.0592918395996</t>
   </si>
   <si>
     <t xml:space="preserve">22.285680770874</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">22.3943462371826</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9868488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.439624786377</t>
+    <t xml:space="preserve">21.9868469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4396228790283</t>
   </si>
   <si>
     <t xml:space="preserve">22.5573463439941</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">22.0774021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0049571990967</t>
+    <t xml:space="preserve">22.0049591064453</t>
   </si>
   <si>
     <t xml:space="preserve">21.9415683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8510131835938</t>
+    <t xml:space="preserve">21.8510112762451</t>
   </si>
   <si>
     <t xml:space="preserve">21.7695140838623</t>
@@ -1160,49 +1160,49 @@
     <t xml:space="preserve">21.0631828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0088500976562</t>
+    <t xml:space="preserve">21.008846282959</t>
   </si>
   <si>
     <t xml:space="preserve">20.6737937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7734050750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6556797027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0994052886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0903511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.135627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8277359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549022674561</t>
+    <t xml:space="preserve">20.7734031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6556854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0994033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1356239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8277378082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549041748047</t>
   </si>
   <si>
     <t xml:space="preserve">20.8005714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8820686340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4344596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4163475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9506225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4667892456055</t>
+    <t xml:space="preserve">20.8820705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4344577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4163455963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9506244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4667911529541</t>
   </si>
   <si>
     <t xml:space="preserve">22.5120697021484</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">22.8833465576172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3218994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014568328857</t>
+    <t xml:space="preserve">22.3219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290119171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014549255371</t>
   </si>
   <si>
     <t xml:space="preserve">22.8108997344971</t>
@@ -1229,31 +1229,31 @@
     <t xml:space="preserve">23.2546195983887</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6530666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.906623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6168441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1821765899658</t>
+    <t xml:space="preserve">23.6530647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9066219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6168422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1821784973145</t>
   </si>
   <si>
     <t xml:space="preserve">23.6349563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4900665283203</t>
+    <t xml:space="preserve">23.4900646209717</t>
   </si>
   <si>
     <t xml:space="preserve">23.5443992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2002906799316</t>
+    <t xml:space="preserve">23.2002868652344</t>
   </si>
   <si>
     <t xml:space="preserve">22.8199577331543</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">22.7837352752686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0372905731201</t>
+    <t xml:space="preserve">23.0372886657715</t>
   </si>
   <si>
     <t xml:space="preserve">23.8160648345947</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">24.341287612915</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4861736297607</t>
+    <t xml:space="preserve">24.4861755371094</t>
   </si>
   <si>
     <t xml:space="preserve">24.2507305145264</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">24.3775081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5042839050293</t>
+    <t xml:space="preserve">24.5042858123779</t>
   </si>
   <si>
     <t xml:space="preserve">24.5223960876465</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">24.2869529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1148948669434</t>
+    <t xml:space="preserve">24.1148986816406</t>
   </si>
   <si>
     <t xml:space="preserve">24.0333976745605</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2145080566406</t>
+    <t xml:space="preserve">24.214506149292</t>
   </si>
   <si>
     <t xml:space="preserve">23.5625114440918</t>
@@ -1307,31 +1307,31 @@
     <t xml:space="preserve">24.3593978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2908420562744</t>
+    <t xml:space="preserve">23.2908401489258</t>
   </si>
   <si>
     <t xml:space="preserve">24.0424518585205</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6582317352295</t>
+    <t xml:space="preserve">24.6582279205322</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7630043029785</t>
+    <t xml:space="preserve">25.7630081176758</t>
   </si>
   <si>
     <t xml:space="preserve">25.4279518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5637817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5818939208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4641742706299</t>
+    <t xml:space="preserve">25.5637836456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5818958282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4641761779785</t>
   </si>
   <si>
     <t xml:space="preserve">25.391731262207</t>
@@ -1343,76 +1343,76 @@
     <t xml:space="preserve">26.1342849731445</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9893932342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3192825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.264949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.699613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728397369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2157821655273</t>
+    <t xml:space="preserve">25.9893951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3192806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2649517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6996154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728416442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.215784072876</t>
   </si>
   <si>
     <t xml:space="preserve">26.405948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5055618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6685600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4874496459961</t>
+    <t xml:space="preserve">26.5055599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6685619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4874515533447</t>
   </si>
   <si>
     <t xml:space="preserve">26.8134498596191</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7500591278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9583377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4654483795166</t>
+    <t xml:space="preserve">26.7500610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9583358764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.465446472168</t>
   </si>
   <si>
     <t xml:space="preserve">27.9453926086426</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5741119384766</t>
+    <t xml:space="preserve">27.5741138458252</t>
   </si>
   <si>
     <t xml:space="preserve">27.7190017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9816131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7655582427979</t>
+    <t xml:space="preserve">27.6737232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9182224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7655563354492</t>
   </si>
   <si>
     <t xml:space="preserve">29.4304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8108329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549415588379</t>
+    <t xml:space="preserve">29.810827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549434661865</t>
   </si>
   <si>
     <t xml:space="preserve">30.2364387512207</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">30.5624408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8250560760498</t>
+    <t xml:space="preserve">30.8250484466553</t>
   </si>
   <si>
     <t xml:space="preserve">30.4809379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2053852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9026622772217</t>
+    <t xml:space="preserve">31.2053871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9026565551758</t>
   </si>
   <si>
     <t xml:space="preserve">31.712495803833</t>
@@ -1445,28 +1445,28 @@
     <t xml:space="preserve">31.9207706451416</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6180534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6904945373535</t>
+    <t xml:space="preserve">32.618049621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6904907226562</t>
   </si>
   <si>
     <t xml:space="preserve">32.962158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4602127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110412597656</t>
+    <t xml:space="preserve">33.4602165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.903938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110450744629</t>
   </si>
   <si>
     <t xml:space="preserve">33.0527191162109</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3011093139648</t>
+    <t xml:space="preserve">32.3011016845703</t>
   </si>
   <si>
     <t xml:space="preserve">33.0345993041992</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">33.6866035461426</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0759925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0941009521484</t>
+    <t xml:space="preserve">34.0759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0941047668457</t>
   </si>
   <si>
     <t xml:space="preserve">34.3929328918457</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">35.2350997924805</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6788215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4416923522949</t>
+    <t xml:space="preserve">35.678825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4416885375977</t>
   </si>
   <si>
     <t xml:space="preserve">34.4749336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7270622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5022926330566</t>
+    <t xml:space="preserve">33.7270660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5022964477539</t>
   </si>
   <si>
     <t xml:space="preserve">35.8065032958984</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">36.007152557373</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8671073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1589584350586</t>
+    <t xml:space="preserve">34.8671035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1589622497559</t>
   </si>
   <si>
     <t xml:space="preserve">35.8156280517578</t>
@@ -1526,34 +1526,34 @@
     <t xml:space="preserve">35.8429870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3354797363281</t>
+    <t xml:space="preserve">36.3354835510254</t>
   </si>
   <si>
     <t xml:space="preserve">37.703540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2931251525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2534065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2748794555664</t>
+    <t xml:space="preserve">37.2931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2534027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2748832702637</t>
   </si>
   <si>
     <t xml:space="preserve">37.5940933227539</t>
   </si>
   <si>
-    <t xml:space="preserve">37.904182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4696464538574</t>
+    <t xml:space="preserve">37.9041862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4696502685547</t>
   </si>
   <si>
     <t xml:space="preserve">38.3602066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8221054077148</t>
+    <t xml:space="preserve">37.8221015930176</t>
   </si>
   <si>
     <t xml:space="preserve">36.6546936035156</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">36.3446044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2807655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0892372131348</t>
+    <t xml:space="preserve">36.28076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0892333984375</t>
   </si>
   <si>
     <t xml:space="preserve">35.4143333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3960876464844</t>
+    <t xml:space="preserve">35.3960914611816</t>
   </si>
   <si>
     <t xml:space="preserve">35.5146560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1042442321777</t>
+    <t xml:space="preserve">35.1042404174805</t>
   </si>
   <si>
     <t xml:space="preserve">35.5693740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3504867553711</t>
+    <t xml:space="preserve">35.3504829406738</t>
   </si>
   <si>
     <t xml:space="preserve">34.5205307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9550704956055</t>
+    <t xml:space="preserve">33.9550743103027</t>
   </si>
   <si>
     <t xml:space="preserve">33.745304107666</t>
@@ -1607,31 +1607,31 @@
     <t xml:space="preserve">34.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.596736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1224822998047</t>
+    <t xml:space="preserve">35.5967407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1224784851074</t>
   </si>
   <si>
     <t xml:space="preserve">35.624095916748</t>
   </si>
   <si>
-    <t xml:space="preserve">35.469051361084</t>
+    <t xml:space="preserve">35.4690551757812</t>
   </si>
   <si>
     <t xml:space="preserve">35.3869705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">35.241039276123</t>
+    <t xml:space="preserve">35.2410430908203</t>
   </si>
   <si>
     <t xml:space="preserve">36.1622047424316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8853492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6938209533691</t>
+    <t xml:space="preserve">34.8853530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6938247680664</t>
   </si>
   <si>
     <t xml:space="preserve">33.8091468811035</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">34.4019737243652</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2013206481934</t>
+    <t xml:space="preserve">34.2013244628906</t>
   </si>
   <si>
     <t xml:space="preserve">33.4169692993164</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">34.2651672363281</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3746032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5387725830078</t>
+    <t xml:space="preserve">34.3746070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5387763977051</t>
   </si>
   <si>
     <t xml:space="preserve">34.7303047180176</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">34.6208610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0189170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8215065002441</t>
+    <t xml:space="preserve">34.018913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8215103149414</t>
   </si>
   <si>
     <t xml:space="preserve">34.4840545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7941474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5784912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169189453125</t>
+    <t xml:space="preserve">34.7941436767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169151306152</t>
   </si>
   <si>
     <t xml:space="preserve">36.153076171875</t>
@@ -1688,55 +1688,55 @@
     <t xml:space="preserve">35.5328941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5055274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.113353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8365097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2834053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3381271362305</t>
+    <t xml:space="preserve">35.5055351257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1133575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8365020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2834014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3381309509277</t>
   </si>
   <si>
     <t xml:space="preserve">34.3016471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7850227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9824333190918</t>
+    <t xml:space="preserve">34.785026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9824371337891</t>
   </si>
   <si>
     <t xml:space="preserve">34.6117401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4202117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5934982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.511417388916</t>
+    <t xml:space="preserve">34.4202079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5934944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5114135742188</t>
   </si>
   <si>
     <t xml:space="preserve">34.0827560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4110908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664657592773</t>
+    <t xml:space="preserve">34.4110946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664619445801</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9400749206543</t>
+    <t xml:space="preserve">34.940071105957</t>
   </si>
   <si>
     <t xml:space="preserve">32.9791946411133</t>
@@ -1745,43 +1745,43 @@
     <t xml:space="preserve">31.8300323486328</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4593391418457</t>
+    <t xml:space="preserve">32.4593353271484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9388790130615</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5284633636475</t>
+    <t xml:space="preserve">28.5284671783447</t>
   </si>
   <si>
     <t xml:space="preserve">28.2001304626465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2639713287354</t>
+    <t xml:space="preserve">27.6529102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.263973236084</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4554996490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7258701324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7988357543945</t>
+    <t xml:space="preserve">28.4555015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7258739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7988338470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.6587905883789</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2698554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082813262939</t>
+    <t xml:space="preserve">27.2698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082775115967</t>
   </si>
   <si>
     <t xml:space="preserve">27.5708274841309</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">27.5434665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9994850158691</t>
+    <t xml:space="preserve">27.9994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">28.0906848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5499439239502</t>
+    <t xml:space="preserve">29.5499458312988</t>
   </si>
   <si>
     <t xml:space="preserve">29.1942481994629</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">28.9753608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1304054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.452262878418</t>
+    <t xml:space="preserve">29.1304092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4522609710693</t>
   </si>
   <si>
     <t xml:space="preserve">29.0392036437988</t>
@@ -1823,37 +1823,37 @@
     <t xml:space="preserve">28.0268440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0359649658203</t>
+    <t xml:space="preserve">28.0359630584717</t>
   </si>
   <si>
     <t xml:space="preserve">27.351936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2666130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8503189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8138370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4340209960938</t>
+    <t xml:space="preserve">26.2666149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.813835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.434024810791</t>
   </si>
   <si>
     <t xml:space="preserve">27.2060127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7317523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9141597747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.807954788208</t>
+    <t xml:space="preserve">26.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9141616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079528808594</t>
   </si>
   <si>
     <t xml:space="preserve">26.7682361602783</t>
@@ -1865,31 +1865,31 @@
     <t xml:space="preserve">26.512866973877</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8594398498535</t>
+    <t xml:space="preserve">26.8594417572021</t>
   </si>
   <si>
     <t xml:space="preserve">25.4822673797607</t>
   </si>
   <si>
-    <t xml:space="preserve">25.327220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.956521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6431922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1721744537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7011528015137</t>
+    <t xml:space="preserve">25.3272190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9565238952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646709442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6431941986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1721725463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7011547088623</t>
   </si>
   <si>
     <t xml:space="preserve">25.144811630249</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">25.5825881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.385181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5949478149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3637027740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.467264175415</t>
+    <t xml:space="preserve">26.3851795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5949459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3636989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4672622680664</t>
   </si>
   <si>
     <t xml:space="preserve">27.1877727508545</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">28.6014270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1454105377197</t>
+    <t xml:space="preserve">28.1454124450684</t>
   </si>
   <si>
     <t xml:space="preserve">27.0600852966309</t>
@@ -1931,25 +1931,25 @@
     <t xml:space="preserve">27.0327262878418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3336963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4066619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6711502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8991603851318</t>
+    <t xml:space="preserve">27.3336982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4066600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6711483001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8991622924805</t>
   </si>
   <si>
     <t xml:space="preserve">27.3792991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.95387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.880916595459</t>
+    <t xml:space="preserve">27.9538803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8809185028076</t>
   </si>
   <si>
     <t xml:space="preserve">28.2366123199463</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">29.9147567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0059623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5987815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7994327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2007255554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4437389373779</t>
+    <t xml:space="preserve">30.0059642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5987796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7994289398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2007236480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4437408447266</t>
   </si>
   <si>
     <t xml:space="preserve">30.6443862915039</t>
@@ -1979,85 +1979,85 @@
     <t xml:space="preserve">30.9362373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7023410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020240783691</t>
+    <t xml:space="preserve">31.7023429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020221710205</t>
   </si>
   <si>
     <t xml:space="preserve">31.3284111022949</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8117961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7753086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6567401885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9668388366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9029960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538318634033</t>
+    <t xml:space="preserve">31.8117923736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7753105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6567440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743347167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9668350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9029922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538299560547</t>
   </si>
   <si>
     <t xml:space="preserve">34.1557235717773</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7909088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9244766235352</t>
+    <t xml:space="preserve">33.7909049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9244728088379</t>
   </si>
   <si>
     <t xml:space="preserve">32.8332710266113</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6964645385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5140609741211</t>
+    <t xml:space="preserve">32.6964683532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5140571594238</t>
   </si>
   <si>
     <t xml:space="preserve">32.5779037475586</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4319801330566</t>
+    <t xml:space="preserve">32.4319763183594</t>
   </si>
   <si>
     <t xml:space="preserve">32.915355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0065574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5264129638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1980819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2313270568848</t>
+    <t xml:space="preserve">33.0065536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5264167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1980857849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2313232421875</t>
   </si>
   <si>
     <t xml:space="preserve">31.7388286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">32.441089630127</t>
+    <t xml:space="preserve">32.4410934448242</t>
   </si>
   <si>
     <t xml:space="preserve">32.7603034973145</t>
@@ -2066,25 +2066,25 @@
     <t xml:space="preserve">33.5081748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6085052490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1283569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9277153015137</t>
+    <t xml:space="preserve">33.6085014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9277114868164</t>
   </si>
   <si>
     <t xml:space="preserve">33.8638687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8150329589844</t>
+    <t xml:space="preserve">32.8150253295898</t>
   </si>
   <si>
     <t xml:space="preserve">32.659984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2163238525391</t>
+    <t xml:space="preserve">33.2163276672363</t>
   </si>
   <si>
     <t xml:space="preserve">33.2892913818359</t>
@@ -2105,31 +2105,31 @@
     <t xml:space="preserve">33.8729934692383</t>
   </si>
   <si>
-    <t xml:space="preserve">33.681468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.061279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3440132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531303405762</t>
+    <t xml:space="preserve">33.6814651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0612754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3440093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531341552734</t>
   </si>
   <si>
     <t xml:space="preserve">33.234561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.918586730957</t>
+    <t xml:space="preserve">33.9185943603516</t>
   </si>
   <si>
     <t xml:space="preserve">33.1616020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5505409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4046096801758</t>
+    <t xml:space="preserve">32.5505332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.404613494873</t>
   </si>
   <si>
     <t xml:space="preserve">33.4443283081055</t>
@@ -2141,40 +2141,40 @@
     <t xml:space="preserve">32.6873435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1310043334961</t>
+    <t xml:space="preserve">32.1310005187988</t>
   </si>
   <si>
     <t xml:space="preserve">32.5596580505371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5911750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863258361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8363647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2552757263184</t>
+    <t xml:space="preserve">31.5911712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.836368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8586559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2552795410156</t>
   </si>
   <si>
     <t xml:space="preserve">32.2829475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7848701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382076263428</t>
+    <t xml:space="preserve">31.7848663330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.43821144104</t>
   </si>
   <si>
     <t xml:space="preserve">30.5581169128418</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">31.8217620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0062408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6649627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7387504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125419616699</t>
+    <t xml:space="preserve">32.006233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6649589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125381469727</t>
   </si>
   <si>
     <t xml:space="preserve">32.3290672302246</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">32.6518974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6480560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7679634094238</t>
+    <t xml:space="preserve">33.6480522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7679672241211</t>
   </si>
   <si>
     <t xml:space="preserve">34.7087821960449</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">34.505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4136238098145</t>
+    <t xml:space="preserve">34.4136276245117</t>
   </si>
   <si>
     <t xml:space="preserve">33.7864112854004</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">33.5189247131348</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2568244934082</t>
+    <t xml:space="preserve">34.2568206787109</t>
   </si>
   <si>
     <t xml:space="preserve">34.6811103820801</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0500602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9762687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5112457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6127014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5204696655273</t>
+    <t xml:space="preserve">35.0500564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9762649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5112419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6127052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5204658508301</t>
   </si>
   <si>
     <t xml:space="preserve">35.5296897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.280647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3544464111328</t>
+    <t xml:space="preserve">35.2806549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3544425964355</t>
   </si>
   <si>
     <t xml:space="preserve">35.0961799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">35.492790222168</t>
+    <t xml:space="preserve">35.4927978515625</t>
   </si>
   <si>
     <t xml:space="preserve">35.0408363342285</t>
@@ -2273,124 +2273,124 @@
     <t xml:space="preserve">35.2253074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2437515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.658821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9263076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9908714294434</t>
+    <t xml:space="preserve">35.2437591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6403732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9263153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9908752441406</t>
   </si>
   <si>
     <t xml:space="preserve">35.963207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6903381347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2844886779785</t>
+    <t xml:space="preserve">34.6903305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2844924926758</t>
   </si>
   <si>
     <t xml:space="preserve">33.4451332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4620418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343681335449</t>
+    <t xml:space="preserve">31.4620399475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343700408936</t>
   </si>
   <si>
     <t xml:space="preserve">31.8309841156006</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4120788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475189208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4989337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2314472198486</t>
+    <t xml:space="preserve">32.4120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4989356994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2314434051514</t>
   </si>
   <si>
     <t xml:space="preserve">31.7571964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6926326751709</t>
+    <t xml:space="preserve">31.6926364898682</t>
   </si>
   <si>
     <t xml:space="preserve">32.7072372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7479705810547</t>
+    <t xml:space="preserve">31.747974395752</t>
   </si>
   <si>
     <t xml:space="preserve">31.5542755126953</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3605766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3052387237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6465129852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3382911682129</t>
+    <t xml:space="preserve">31.3605785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.305233001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6465167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3382949829102</t>
   </si>
   <si>
     <t xml:space="preserve">33.0761909484863</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1684226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7349166870117</t>
+    <t xml:space="preserve">33.1684265136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7349128723145</t>
   </si>
   <si>
     <t xml:space="preserve">32.5412101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6242218017578</t>
+    <t xml:space="preserve">32.6242294311523</t>
   </si>
   <si>
     <t xml:space="preserve">32.6426696777344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3751831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6372890472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4804878234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2760238647461</t>
+    <t xml:space="preserve">32.3751907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6372871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4804859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2760219573975</t>
   </si>
   <si>
     <t xml:space="preserve">29.9493541717529</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0877056121826</t>
+    <t xml:space="preserve">30.0877075195312</t>
   </si>
   <si>
     <t xml:space="preserve">29.6080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7279834747314</t>
+    <t xml:space="preserve">29.7279853820801</t>
   </si>
   <si>
     <t xml:space="preserve">29.6449718475342</t>
@@ -2402,46 +2402,46 @@
     <t xml:space="preserve">30.3367481231689</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8294429779053</t>
+    <t xml:space="preserve">30.1614971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8294448852539</t>
   </si>
   <si>
     <t xml:space="preserve">29.1376686096191</t>
   </si>
   <si>
-    <t xml:space="preserve">29.617301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0139198303223</t>
+    <t xml:space="preserve">29.6172981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0139179229736</t>
   </si>
   <si>
     <t xml:space="preserve">30.1983947753906</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0508136749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6134567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1945533752441</t>
+    <t xml:space="preserve">30.050817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6134586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1945514678955</t>
   </si>
   <si>
     <t xml:space="preserve">31.803316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">31.545051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4251461029053</t>
+    <t xml:space="preserve">31.5450496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4251441955566</t>
   </si>
   <si>
     <t xml:space="preserve">31.0285224914551</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7241439819336</t>
+    <t xml:space="preserve">30.724142074585</t>
   </si>
   <si>
     <t xml:space="preserve">29.6726398468018</t>
@@ -2462,37 +2462,37 @@
     <t xml:space="preserve">33.362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7441368103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9877910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.439754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5504379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3106231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2291488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180061340332</t>
+    <t xml:space="preserve">32.7441329956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.98779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5504417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.310619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2291450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180099487305</t>
   </si>
   <si>
     <t xml:space="preserve">34.3121643066406</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0907936096191</t>
+    <t xml:space="preserve">34.0907974243164</t>
   </si>
   <si>
     <t xml:space="preserve">34.0077781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6111640930176</t>
+    <t xml:space="preserve">33.6111602783203</t>
   </si>
   <si>
     <t xml:space="preserve">33.7218437194824</t>
@@ -2504,34 +2504,34 @@
     <t xml:space="preserve">34.2199249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">34.819465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5243072509766</t>
+    <t xml:space="preserve">34.8194694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5243110656738</t>
   </si>
   <si>
     <t xml:space="preserve">36.0462226867676</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1476783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.02392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6826515197754</t>
+    <t xml:space="preserve">36.1476821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6826553344727</t>
   </si>
   <si>
     <t xml:space="preserve">35.7787322998047</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6772727966309</t>
+    <t xml:space="preserve">35.6772689819336</t>
   </si>
   <si>
     <t xml:space="preserve">38.1492195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.924015045166</t>
+    <t xml:space="preserve">38.9240112304688</t>
   </si>
   <si>
     <t xml:space="preserve">38.545841217041</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">38.8225517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">38.093879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8171653747559</t>
+    <t xml:space="preserve">38.0938758850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">37.7249336242676</t>
@@ -2552,46 +2552,46 @@
     <t xml:space="preserve">37.1530609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3006401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0423812866211</t>
+    <t xml:space="preserve">37.3006362915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0423774719238</t>
   </si>
   <si>
     <t xml:space="preserve">37.1899566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.715705871582</t>
+    <t xml:space="preserve">37.7157096862793</t>
   </si>
   <si>
     <t xml:space="preserve">37.6234703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4758911132812</t>
+    <t xml:space="preserve">37.4758949279785</t>
   </si>
   <si>
     <t xml:space="preserve">36.9593620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4389953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1438331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9647483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5496788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6326942443848</t>
+    <t xml:space="preserve">37.4389991760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9778137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1438369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9647521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9462966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5496826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6326904296875</t>
   </si>
   <si>
     <t xml:space="preserve">38.3613662719727</t>
@@ -2600,28 +2600,28 @@
     <t xml:space="preserve">39.4036483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3667488098145</t>
+    <t xml:space="preserve">39.366756439209</t>
   </si>
   <si>
     <t xml:space="preserve">39.385196685791</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1399955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2914199829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2691268920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2084045410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.402099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8432960510254</t>
+    <t xml:space="preserve">38.1399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2914161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2691307067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2084083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4021034240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8432922363281</t>
   </si>
   <si>
     <t xml:space="preserve">37.2360763549805</t>
@@ -2633,76 +2633,76 @@
     <t xml:space="preserve">35.9724273681641</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3690414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8579063415527</t>
+    <t xml:space="preserve">36.3690452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8579025268555</t>
   </si>
   <si>
     <t xml:space="preserve">37.2729682922363</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5166282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457595825195</t>
+    <t xml:space="preserve">36.5166244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7049369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457557678223</t>
   </si>
   <si>
     <t xml:space="preserve">35.649600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2583618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1422958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2898750305176</t>
+    <t xml:space="preserve">36.2583656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1422920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2898712158203</t>
   </si>
   <si>
     <t xml:space="preserve">36.0093231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2660484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4305305480957</t>
+    <t xml:space="preserve">34.2660446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4305267333984</t>
   </si>
   <si>
     <t xml:space="preserve">32.4028587341309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9286079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.522762298584</t>
+    <t xml:space="preserve">32.9286117553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5227661132812</t>
   </si>
   <si>
     <t xml:space="preserve">32.4858703613281</t>
   </si>
   <si>
-    <t xml:space="preserve">31.10231590271</t>
+    <t xml:space="preserve">31.1023139953613</t>
   </si>
   <si>
     <t xml:space="preserve">28.1507320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8002281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0807819366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.981616973877</t>
+    <t xml:space="preserve">27.8002300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0807838439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9816188812256</t>
   </si>
   <si>
     <t xml:space="preserve">27.3943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2637119293213</t>
+    <t xml:space="preserve">25.2637100219727</t>
   </si>
   <si>
     <t xml:space="preserve">24.9039878845215</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">24.922435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9977684020996</t>
+    <t xml:space="preserve">26.9977703094482</t>
   </si>
   <si>
     <t xml:space="preserve">26.3797817230225</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">29.9309043884277</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4528102874756</t>
+    <t xml:space="preserve">31.4528160095215</t>
   </si>
   <si>
     <t xml:space="preserve">31.729528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7056941986084</t>
+    <t xml:space="preserve">30.705696105957</t>
   </si>
   <si>
     <t xml:space="preserve">29.8755626678467</t>
@@ -2738,22 +2738,22 @@
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857070922852</t>
+    <t xml:space="preserve">28.6857032775879</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688003540039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1061534881592</t>
+    <t xml:space="preserve">30.1061553955078</t>
   </si>
   <si>
     <t xml:space="preserve">30.2998504638672</t>
   </si>
   <si>
-    <t xml:space="preserve">31.083869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6319065093994</t>
+    <t xml:space="preserve">31.0838661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6319046020508</t>
   </si>
   <si>
     <t xml:space="preserve">31.8402118682861</t>
@@ -2762,25 +2762,25 @@
     <t xml:space="preserve">32.513542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8901691436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.576566696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5081558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.272180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7702617645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9124565124512</t>
+    <t xml:space="preserve">30.8901710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5765628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5081539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2721824645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.770263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9124584197998</t>
   </si>
   <si>
     <t xml:space="preserve">30.2352848052979</t>
@@ -2792,31 +2792,31 @@
     <t xml:space="preserve">30.2260646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4143772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7041549682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6211395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7372074127197</t>
+    <t xml:space="preserve">29.414379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7041530609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6211414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7372093200684</t>
   </si>
   <si>
     <t xml:space="preserve">29.866340637207</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8056125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3682594299316</t>
+    <t xml:space="preserve">28.8056144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.368257522583</t>
   </si>
   <si>
     <t xml:space="preserve">30.7979335784912</t>
   </si>
   <si>
-    <t xml:space="preserve">30.39208984375</t>
+    <t xml:space="preserve">30.3920936584473</t>
   </si>
   <si>
     <t xml:space="preserve">32.1630401611328</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">30.8532752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955535888672</t>
+    <t xml:space="preserve">31.0746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955554962158</t>
   </si>
   <si>
     <t xml:space="preserve">32.0339088439941</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">31.0377521514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3790264129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9693450927734</t>
+    <t xml:space="preserve">31.3790283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9693431854248</t>
   </si>
   <si>
     <t xml:space="preserve">32.4950904846191</t>
@@ -2867,94 +2867,94 @@
     <t xml:space="preserve">31.3974742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6003971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591209411621</t>
+    <t xml:space="preserve">31.6003952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591190338135</t>
   </si>
   <si>
     <t xml:space="preserve">31.9601211547852</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4897060394287</t>
+    <t xml:space="preserve">31.4897079467773</t>
   </si>
   <si>
     <t xml:space="preserve">31.3513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6503524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0100765228271</t>
+    <t xml:space="preserve">30.6503505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654220581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0100746154785</t>
   </si>
   <si>
     <t xml:space="preserve">30.5950088500977</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0692596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0969314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4236030578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.488166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8809452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3275241851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0784854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5342864990234</t>
+    <t xml:space="preserve">30.0692577362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0969352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4236011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5804023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4881687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.327522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0784873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5342884063721</t>
   </si>
   <si>
     <t xml:space="preserve">29.552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8571147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0046920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5857887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8847885131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9585781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1484317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7940921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1814842224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4766502380371</t>
+    <t xml:space="preserve">29.8571128845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0046939849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5857906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.884786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1484355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.794095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4766464233398</t>
   </si>
   <si>
     <t xml:space="preserve">33.8878746032715</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">34.3306121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6665000915527</t>
+    <t xml:space="preserve">33.66650390625</t>
   </si>
   <si>
     <t xml:space="preserve">32.4674224853516</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0431365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4489707946777</t>
+    <t xml:space="preserve">32.0431289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4489822387695</t>
   </si>
   <si>
     <t xml:space="preserve">32.2644996643066</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">33.601936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8509788513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2237663269043</t>
+    <t xml:space="preserve">33.8509750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.223762512207</t>
   </si>
   <si>
     <t xml:space="preserve">33.5650444030762</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">34.0354537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6057777404785</t>
+    <t xml:space="preserve">32.6057739257812</t>
   </si>
   <si>
     <t xml:space="preserve">33.9432144165039</t>
   </si>
   <si>
-    <t xml:space="preserve">34.948600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4043960571289</t>
+    <t xml:space="preserve">34.9485969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4043998718262</t>
   </si>
   <si>
     <t xml:space="preserve">35.9170837402344</t>
@@ -3026,43 +3026,43 @@
     <t xml:space="preserve">32.1907119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3936347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2053184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5465965270996</t>
+    <t xml:space="preserve">32.3936309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.205322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5465927124023</t>
   </si>
   <si>
     <t xml:space="preserve">34.8840293884277</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6349945068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5996398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6273078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3467636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088638305664</t>
+    <t xml:space="preserve">34.6349906921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.627311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3467559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088676452637</t>
   </si>
   <si>
     <t xml:space="preserve">36.7195472717285</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8909530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6142501831055</t>
+    <t xml:space="preserve">37.8909645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8725090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6142463684082</t>
   </si>
   <si>
     <t xml:space="preserve">37.4482154846191</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">38.7118682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6473007202148</t>
+    <t xml:space="preserve">38.6473045349121</t>
   </si>
   <si>
     <t xml:space="preserve">38.241455078125</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">37.8263893127441</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9001770019531</t>
+    <t xml:space="preserve">37.9001808166504</t>
   </si>
   <si>
     <t xml:space="preserve">38.4720497131348</t>
@@ -3092,61 +3092,61 @@
     <t xml:space="preserve">39.2837333679199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8463821411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5842819213867</t>
+    <t xml:space="preserve">39.8463859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5842781066895</t>
   </si>
   <si>
     <t xml:space="preserve">41.4144134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9916610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8533096313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8863677978516</t>
+    <t xml:space="preserve">42.9916687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8533058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8863639831543</t>
   </si>
   <si>
     <t xml:space="preserve">44.1630744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0116577148438</t>
+    <t xml:space="preserve">45.0116500854492</t>
   </si>
   <si>
     <t xml:space="preserve">44.928638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1961250305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7349433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8679161071777</t>
+    <t xml:space="preserve">45.1961288452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7349472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8679122924805</t>
   </si>
   <si>
     <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4674530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.869457244873</t>
+    <t xml:space="preserve">44.467456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8694610595703</t>
   </si>
   <si>
     <t xml:space="preserve">46.3952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2476272583008</t>
+    <t xml:space="preserve">46.247631072998</t>
   </si>
   <si>
     <t xml:space="preserve">46.1184959411621</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8456230163574</t>
+    <t xml:space="preserve">44.8456268310547</t>
   </si>
   <si>
     <t xml:space="preserve">44.864070892334</t>
@@ -3167,28 +3167,28 @@
     <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0708351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6742134094238</t>
+    <t xml:space="preserve">44.0708312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6742172241211</t>
   </si>
   <si>
     <t xml:space="preserve">44.6703758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9509315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8917388916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7403221130371</t>
+    <t xml:space="preserve">43.950927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8917427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7403259277344</t>
   </si>
   <si>
     <t xml:space="preserve">43.6649971008301</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5912017822266</t>
+    <t xml:space="preserve">43.5912055969238</t>
   </si>
   <si>
     <t xml:space="preserve">44.3567733764648</t>
@@ -3197,16 +3197,16 @@
     <t xml:space="preserve">43.7756767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1999664306641</t>
+    <t xml:space="preserve">44.1999702453613</t>
   </si>
   <si>
     <t xml:space="preserve">44.2091903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1369514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8932914733887</t>
+    <t xml:space="preserve">46.1369476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8932876586914</t>
   </si>
   <si>
     <t xml:space="preserve">47.5758438110352</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">48.0739212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6496353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9447860717773</t>
+    <t xml:space="preserve">47.6496315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9447898864746</t>
   </si>
   <si>
     <t xml:space="preserve">47.2622375488281</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">47.7972106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7088165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6534767150879</t>
+    <t xml:space="preserve">46.708812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6534729003906</t>
   </si>
   <si>
     <t xml:space="preserve">49.1807708740234</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">47.2437934875488</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0408668518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1699981689453</t>
+    <t xml:space="preserve">47.0408706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1700019836426</t>
   </si>
   <si>
     <t xml:space="preserve">47.3175811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1108169555664</t>
+    <t xml:space="preserve">48.1108131408691</t>
   </si>
   <si>
     <t xml:space="preserve">48.4613189697266</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">47.6865272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6165771484375</t>
+    <t xml:space="preserve">46.6165809631348</t>
   </si>
   <si>
     <t xml:space="preserve">45.7034301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8602333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4136505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7587776184082</t>
+    <t xml:space="preserve">45.860237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4136543273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7587738037109</t>
   </si>
   <si>
     <t xml:space="preserve">48.0001373291016</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">46.8379440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2107353210449</t>
+    <t xml:space="preserve">46.2107391357422</t>
   </si>
   <si>
     <t xml:space="preserve">45.6019706726074</t>
@@ -3299,25 +3299,25 @@
     <t xml:space="preserve">45.3806076049805</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4397850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4859008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3898277282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0762214660645</t>
+    <t xml:space="preserve">44.2276420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4397811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4859046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3898239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0762176513672</t>
   </si>
   <si>
     <t xml:space="preserve">45.8417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6573104858398</t>
+    <t xml:space="preserve">45.6573143005371</t>
   </si>
   <si>
     <t xml:space="preserve">46.450553894043</t>
@@ -3326,43 +3326,43 @@
     <t xml:space="preserve">46.5981330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5243453979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5020484924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3544769287109</t>
+    <t xml:space="preserve">46.524341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5020523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3544731140137</t>
   </si>
   <si>
     <t xml:space="preserve">46.3214225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2952919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3467903137207</t>
+    <t xml:space="preserve">48.2952880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.346794128418</t>
   </si>
   <si>
     <t xml:space="preserve">46.9670791625977</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0039710998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0593185424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4836044311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3767547607422</t>
+    <t xml:space="preserve">47.0039749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0593147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4836006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3767585754395</t>
   </si>
   <si>
     <t xml:space="preserve">47.4282608032227</t>
   </si>
   <si>
-    <t xml:space="preserve">47.280689239502</t>
+    <t xml:space="preserve">47.2806816101074</t>
   </si>
   <si>
     <t xml:space="preserve">47.7234230041504</t>
@@ -3371,64 +3371,64 @@
     <t xml:space="preserve">46.985523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5942840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.926342010498</t>
+    <t xml:space="preserve">47.5942878723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9263458251953</t>
   </si>
   <si>
     <t xml:space="preserve">48.6642379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4244270324707</t>
+    <t xml:space="preserve">48.4244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">49.1623153686523</t>
   </si>
   <si>
-    <t xml:space="preserve">49.420581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4902954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1228179931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.625114440918</t>
+    <t xml:space="preserve">49.4205856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4902877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1228141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6251182556152</t>
   </si>
   <si>
     <t xml:space="preserve">53.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9877738952637</t>
+    <t xml:space="preserve">53.9877815246582</t>
   </si>
   <si>
     <t xml:space="preserve">54.0621948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4482688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6343078613281</t>
+    <t xml:space="preserve">53.4482727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6343040466309</t>
   </si>
   <si>
     <t xml:space="preserve">54.1180038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">54.229621887207</t>
+    <t xml:space="preserve">54.2296257019043</t>
   </si>
   <si>
     <t xml:space="preserve">55.1039924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8063354492188</t>
+    <t xml:space="preserve">54.8063316345215</t>
   </si>
   <si>
     <t xml:space="preserve">53.5784950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8343505859375</t>
+    <t xml:space="preserve">52.8343467712402</t>
   </si>
   <si>
     <t xml:space="preserve">52.8715591430664</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">53.132007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8947601318359</t>
+    <t xml:space="preserve">53.8947563171387</t>
   </si>
   <si>
     <t xml:space="preserve">54.2482261657715</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5086784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0435905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1738166809082</t>
+    <t xml:space="preserve">54.5086822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.043586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1738128662109</t>
   </si>
   <si>
     <t xml:space="preserve">54.2110214233398</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">53.6901206970215</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5970993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0762023925781</t>
+    <t xml:space="preserve">53.5971031188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0761985778809</t>
   </si>
   <si>
     <t xml:space="preserve">53.4668769836426</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">52.815746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">53.038990020752</t>
+    <t xml:space="preserve">53.0389938354492</t>
   </si>
   <si>
     <t xml:space="preserve">53.3366546630859</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4762840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4250679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.280834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7273292541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3598480224609</t>
+    <t xml:space="preserve">51.4762878417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2808380126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7273254394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3598518371582</t>
   </si>
   <si>
     <t xml:space="preserve">52.7785415649414</t>
@@ -3503,19 +3503,19 @@
     <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1878204345703</t>
+    <t xml:space="preserve">53.1878242492676</t>
   </si>
   <si>
     <t xml:space="preserve">53.7459297180176</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6203002929688</t>
+    <t xml:space="preserve">54.620304107666</t>
   </si>
   <si>
     <t xml:space="preserve">55.4388580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7551231384277</t>
+    <t xml:space="preserve">55.7551193237305</t>
   </si>
   <si>
     <t xml:space="preserve">55.4946708679199</t>
@@ -3527,13 +3527,13 @@
     <t xml:space="preserve">53.950569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6389045715332</t>
+    <t xml:space="preserve">54.6389083862305</t>
   </si>
   <si>
     <t xml:space="preserve">54.6947174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">54.527286529541</t>
+    <t xml:space="preserve">54.5272789001465</t>
   </si>
   <si>
     <t xml:space="preserve">55.5876884460449</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">56.9271507263184</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2992248535156</t>
+    <t xml:space="preserve">57.2992210388184</t>
   </si>
   <si>
     <t xml:space="preserve">57.727108001709</t>
@@ -3554,28 +3554,28 @@
     <t xml:space="preserve">56.4248542785645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8667449951172</t>
+    <t xml:space="preserve">55.8667488098145</t>
   </si>
   <si>
     <t xml:space="preserve">54.3970527648926</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0670051574707</t>
+    <t xml:space="preserve">51.067008972168</t>
   </si>
   <si>
     <t xml:space="preserve">50.1554260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8437576293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7693481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3972778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5461006164551</t>
+    <t xml:space="preserve">50.8437652587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7693519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.397274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5461044311523</t>
   </si>
   <si>
     <t xml:space="preserve">50.8065528869629</t>
@@ -3584,49 +3584,49 @@
     <t xml:space="preserve">50.4158744812012</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0298004150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9925880432129</t>
+    <t xml:space="preserve">51.0297966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9925918579102</t>
   </si>
   <si>
     <t xml:space="preserve">50.2484436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1042137145996</t>
+    <t xml:space="preserve">51.1042098999023</t>
   </si>
   <si>
     <t xml:space="preserve">51.718132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4018669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3274536132812</t>
+    <t xml:space="preserve">51.4018707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3274574279785</t>
   </si>
   <si>
     <t xml:space="preserve">50.8251571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7879524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1648368835449</t>
+    <t xml:space="preserve">50.7879447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1648330688477</t>
   </si>
   <si>
     <t xml:space="preserve">48.0904235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3182601928711</t>
+    <t xml:space="preserve">49.3182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">48.0532150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0019989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5647087097168</t>
+    <t xml:space="preserve">49.0020027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5647048950195</t>
   </si>
   <si>
     <t xml:space="preserve">51.3832664489746</t>
@@ -3647,31 +3647,31 @@
     <t xml:space="preserve">51.7553405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.978588104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9831809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4994812011719</t>
+    <t xml:space="preserve">51.9785842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9831733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4994850158691</t>
   </si>
   <si>
     <t xml:space="preserve">52.4622802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7133140563965</t>
+    <t xml:space="preserve">54.7133178710938</t>
   </si>
   <si>
     <t xml:space="preserve">54.4714736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">55.569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7597236633301</t>
+    <t xml:space="preserve">55.5690879821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0341835021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7597198486328</t>
   </si>
   <si>
     <t xml:space="preserve">56.8341331481934</t>
@@ -3680,28 +3680,28 @@
     <t xml:space="preserve">56.3876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9783668518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9457550048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7829170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.438648223877</t>
+    <t xml:space="preserve">55.9783630371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7829208374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4386444091797</t>
   </si>
   <si>
     <t xml:space="preserve">58.5084648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">59.234001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6524772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8803215026855</t>
+    <t xml:space="preserve">59.2340049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.652473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8803176879883</t>
   </si>
   <si>
     <t xml:space="preserve">63.4012222290039</t>
@@ -3710,13 +3710,13 @@
     <t xml:space="preserve">61.4106292724609</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7409019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8199119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9361381530762</t>
+    <t xml:space="preserve">60.7408981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8199081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
     <t xml:space="preserve">63.754695892334</t>
@@ -3725,34 +3725,34 @@
     <t xml:space="preserve">64.3314056396484</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2197799682617</t>
+    <t xml:space="preserve">64.2197875976562</t>
   </si>
   <si>
     <t xml:space="preserve">63.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0663528442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408554077148</t>
+    <t xml:space="preserve">63.0663604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408630371094</t>
   </si>
   <si>
     <t xml:space="preserve">61.9129295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">62.322208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3410339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0897750854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6060791015625</t>
+    <t xml:space="preserve">62.3222122192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3410301208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.089771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6060829162598</t>
   </si>
   <si>
     <t xml:space="preserve">61.0385589599609</t>
@@ -3761,34 +3761,34 @@
     <t xml:space="preserve">60.9455337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">60.5920715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6896896362305</t>
+    <t xml:space="preserve">60.5920677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6896820068359</t>
   </si>
   <si>
     <t xml:space="preserve">64.4430236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4710388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4478340148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6292762756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.675895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7503089904785</t>
+    <t xml:space="preserve">62.4710426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1547737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4478416442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6758995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.182788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7503128051758</t>
   </si>
   <si>
     <t xml:space="preserve">58.8061218261719</t>
@@ -3797,22 +3797,22 @@
     <t xml:space="preserve">58.2294082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8573379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3224258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5642776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7549057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0711708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.5502624511719</t>
+    <t xml:space="preserve">57.8573341369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3224220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7549018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0711669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.5502662658691</t>
   </si>
   <si>
     <t xml:space="preserve">59.810718536377</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">60.4618453979492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269409179688</t>
+    <t xml:space="preserve">60.9269371032715</t>
   </si>
   <si>
     <t xml:space="preserve">58.4154434204102</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9643592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1644020080566</t>
+    <t xml:space="preserve">56.9643630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1644058227539</t>
   </si>
   <si>
     <t xml:space="preserve">55.7923316955566</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">54.8807487487793</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8901596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7087249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6111106872559</t>
+    <t xml:space="preserve">52.8901634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7087211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6111068725586</t>
   </si>
   <si>
     <t xml:space="preserve">54.3040390014648</t>
@@ -3854,19 +3854,19 @@
     <t xml:space="preserve">54.3412437438965</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6995277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2716445922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3134536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.536693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5693016052246</t>
+    <t xml:space="preserve">51.6995315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2716407775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3134498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5366897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5693054199219</t>
   </si>
   <si>
     <t xml:space="preserve">52.4064674377441</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">55.271427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8389472961426</t>
+    <t xml:space="preserve">53.8389511108398</t>
   </si>
   <si>
     <t xml:space="preserve">54.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6437149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6391181945801</t>
+    <t xml:space="preserve">51.6437187194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6391143798828</t>
   </si>
   <si>
     <t xml:space="preserve">52.1274108886719</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">51.2344398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9739837646484</t>
+    <t xml:space="preserve">50.9739875793457</t>
   </si>
   <si>
     <t xml:space="preserve">50.9181785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8809700012207</t>
+    <t xml:space="preserve">50.8809661865234</t>
   </si>
   <si>
     <t xml:space="preserve">48.4624938964844</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">47.1230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">44.946403503418</t>
+    <t xml:space="preserve">44.9464073181152</t>
   </si>
   <si>
     <t xml:space="preserve">41.8768043518066</t>
@@ -3926,22 +3926,22 @@
     <t xml:space="preserve">41.4954261779785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9743041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.997615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6208419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6487503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2441749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7091522216797</t>
+    <t xml:space="preserve">44.974308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9976196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6208457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6487464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2441711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.709156036377</t>
   </si>
   <si>
     <t xml:space="preserve">46.7881660461426</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">45.8207740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2765693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8717765808105</t>
+    <t xml:space="preserve">46.2021522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2765655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8717803955078</t>
   </si>
   <si>
     <t xml:space="preserve">47.1974487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.178840637207</t>
+    <t xml:space="preserve">47.1788444519043</t>
   </si>
   <si>
     <t xml:space="preserve">48.9275817871094</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">49.2810554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9556007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.988208770752</t>
+    <t xml:space="preserve">46.9555969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9882125854492</t>
   </si>
   <si>
     <t xml:space="preserve">47.4392929077148</t>
@@ -4004,25 +4004,25 @@
     <t xml:space="preserve">46.1835517883301</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5881233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.527717590332</t>
+    <t xml:space="preserve">47.5881195068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5277214050293</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8301811218262</t>
+    <t xml:space="preserve">43.8301849365234</t>
   </si>
   <si>
     <t xml:space="preserve">45.430103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2672691345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7695579528809</t>
+    <t xml:space="preserve">46.2672653198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7695617675781</t>
   </si>
   <si>
     <t xml:space="preserve">45.5696296691895</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">41.4861259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7373886108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9095230102539</t>
+    <t xml:space="preserve">39.7373847961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9095191955566</t>
   </si>
   <si>
     <t xml:space="preserve">39.8676109313965</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6163558959961</t>
+    <t xml:space="preserve">41.6163520812988</t>
   </si>
   <si>
     <t xml:space="preserve">40.8070907592773</t>
@@ -4055,25 +4055,25 @@
     <t xml:space="preserve">42.1930694580078</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2814865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1093482971191</t>
+    <t xml:space="preserve">41.2814903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1093521118164</t>
   </si>
   <si>
     <t xml:space="preserve">40.6489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0908470153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.309497833252</t>
+    <t xml:space="preserve">40.0908546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3095016479492</t>
   </si>
   <si>
     <t xml:space="preserve">39.8945198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5640716552734</t>
+    <t xml:space="preserve">38.5640754699707</t>
   </si>
   <si>
     <t xml:space="preserve">38.6018180847168</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">42.3572616577148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.177978515625</t>
+    <t xml:space="preserve">42.1779823303223</t>
   </si>
   <si>
     <t xml:space="preserve">43.6499633789062</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2347869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1119346618652</t>
+    <t xml:space="preserve">43.4801254272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.234790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.111930847168</t>
   </si>
   <si>
     <t xml:space="preserve">41.2155303955078</t>
@@ -4115,25 +4115,25 @@
     <t xml:space="preserve">37.2147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2145614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5167007446289</t>
+    <t xml:space="preserve">36.2145652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5166969299316</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0916976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9690399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9973487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312973022461</t>
+    <t xml:space="preserve">35.0917015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9690361022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9973449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9312934875488</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">37.4600868225098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7054138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3942260742188</t>
+    <t xml:space="preserve">37.7054176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.394229888916</t>
   </si>
   <si>
     <t xml:space="preserve">38.4980239868164</t>
@@ -4157,16 +4157,16 @@
     <t xml:space="preserve">38.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3751640319824</t>
+    <t xml:space="preserve">37.3751678466797</t>
   </si>
   <si>
     <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0547332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396560668945</t>
+    <t xml:space="preserve">39.0547370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396598815918</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">37.8280830383301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5735092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1587257385254</t>
+    <t xml:space="preserve">38.5735130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1587219238281</t>
   </si>
   <si>
     <t xml:space="preserve">40.3474349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7531776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1494827270508</t>
+    <t xml:space="preserve">40.753173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1494789123535</t>
   </si>
   <si>
     <t xml:space="preserve">41.5552215576172</t>
@@ -4217,10 +4217,10 @@
     <t xml:space="preserve">45.9806060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">45.046459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3389663696289</t>
+    <t xml:space="preserve">45.0464630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3389739990234</t>
   </si>
   <si>
     <t xml:space="preserve">46.5278854370117</t>
@@ -4229,16 +4229,16 @@
     <t xml:space="preserve">46.5184440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4995727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8579368591309</t>
+    <t xml:space="preserve">46.4995765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8579406738281</t>
   </si>
   <si>
     <t xml:space="preserve">46.7165946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9524879455566</t>
+    <t xml:space="preserve">46.9524917602539</t>
   </si>
   <si>
     <t xml:space="preserve">46.5939331054688</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">46.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0089111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.754337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1315765380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0273933410645</t>
+    <t xml:space="preserve">46.0089149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7543411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1315803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0273971557617</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
@@ -4268,13 +4268,13 @@
     <t xml:space="preserve">45.2729225158691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.046070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1496696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3100852966309</t>
+    <t xml:space="preserve">43.0460739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1496734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3100814819336</t>
   </si>
   <si>
     <t xml:space="preserve">42.1213684082031</t>
@@ -4283,34 +4283,34 @@
     <t xml:space="preserve">41.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2251586914062</t>
+    <t xml:space="preserve">42.2251625061035</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1777877807617</t>
+    <t xml:space="preserve">41.1777839660645</t>
   </si>
   <si>
     <t xml:space="preserve">41.3948097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6967544555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4704856872559</t>
+    <t xml:space="preserve">41.6967506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4704895019531</t>
   </si>
   <si>
     <t xml:space="preserve">42.998893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0175743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646553039551</t>
+    <t xml:space="preserve">42.0175704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7158241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646514892578</t>
   </si>
   <si>
     <t xml:space="preserve">40.9230194091797</t>
@@ -4319,34 +4319,34 @@
     <t xml:space="preserve">41.4891700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8005523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4610557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9511375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.262321472168</t>
+    <t xml:space="preserve">41.8005485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.461051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9511337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2623252868652</t>
   </si>
   <si>
     <t xml:space="preserve">40.6210746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5644607543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0645599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8095932006836</t>
+    <t xml:space="preserve">40.5644645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0645561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8095970153809</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9794425964355</t>
+    <t xml:space="preserve">39.9794387817383</t>
   </si>
   <si>
     <t xml:space="preserve">43.2064819335938</t>
@@ -4355,16 +4355,16 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703941345215</t>
+    <t xml:space="preserve">41.9703903198242</t>
   </si>
   <si>
     <t xml:space="preserve">41.5174751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8666000366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0272026062012</t>
+    <t xml:space="preserve">41.8665962219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0271987915039</t>
   </si>
   <si>
     <t xml:space="preserve">42.649772644043</t>
@@ -4373,13 +4373,13 @@
     <t xml:space="preserve">42.7252540588379</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8009376525879</t>
+    <t xml:space="preserve">43.8009338378906</t>
   </si>
   <si>
     <t xml:space="preserve">44.0557022094727</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7160148620605</t>
+    <t xml:space="preserve">43.7160186767578</t>
   </si>
   <si>
     <t xml:space="preserve">44.6690330505371</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">43.4329414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">46.169319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6692237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7443199157715</t>
+    <t xml:space="preserve">46.1693229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6692276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7443237304688</t>
   </si>
   <si>
     <t xml:space="preserve">42.734691619873</t>
   </si>
   <si>
-    <t xml:space="preserve">41.224967956543</t>
+    <t xml:space="preserve">41.2249641418457</t>
   </si>
   <si>
     <t xml:space="preserve">41.6873207092285</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">42.8290481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9422760009766</t>
+    <t xml:space="preserve">42.9422798156738</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">48.6131896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6129989624023</t>
+    <t xml:space="preserve">47.6129951477051</t>
   </si>
   <si>
     <t xml:space="preserve">47.7639694213867</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">47.1978225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0657234191895</t>
+    <t xml:space="preserve">47.0657196044922</t>
   </si>
   <si>
     <t xml:space="preserve">47.0185432434082</t>
@@ -4451,10 +4451,10 @@
     <t xml:space="preserve">45.6314811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5654296875</t>
+    <t xml:space="preserve">45.6031761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5654335021973</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
@@ -4469,10 +4469,10 @@
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5465621948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5937347412109</t>
+    <t xml:space="preserve">45.546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5937385559082</t>
   </si>
   <si>
     <t xml:space="preserve">44.7539520263672</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">46.5844955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2544403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7452926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6316719055176</t>
+    <t xml:space="preserve">47.2544364929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6316757202148</t>
   </si>
   <si>
     <t xml:space="preserve">46.4146499633789</t>
@@ -4499,25 +4499,25 @@
     <t xml:space="preserve">45.7918891906738</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9049224853516</t>
+    <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
     <t xml:space="preserve">46.150447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3861465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6788520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3110504150391</t>
+    <t xml:space="preserve">45.3861503601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6788558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3110466003418</t>
   </si>
   <si>
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017158508301</t>
+    <t xml:space="preserve">47.8017082214355</t>
   </si>
   <si>
     <t xml:space="preserve">47.5563812255859</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">49.3869247436523</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7077445983887</t>
+    <t xml:space="preserve">49.7077407836914</t>
   </si>
   <si>
     <t xml:space="preserve">48.9717483520508</t>
@@ -4541,31 +4541,31 @@
     <t xml:space="preserve">50.4814796447754</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8779716491699</t>
+    <t xml:space="preserve">51.8779754638672</t>
   </si>
   <si>
     <t xml:space="preserve">52.3497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8781700134277</t>
+    <t xml:space="preserve">52.8781661987305</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">51.915714263916</t>
+    <t xml:space="preserve">51.9157180786133</t>
   </si>
   <si>
     <t xml:space="preserve">53.0480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3310852050781</t>
+    <t xml:space="preserve">53.3310890197754</t>
   </si>
   <si>
     <t xml:space="preserve">53.1046295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2555961608887</t>
+    <t xml:space="preserve">53.2555999755859</t>
   </si>
   <si>
     <t xml:space="preserve">54.5199928283691</t>
@@ -4583,13 +4583,13 @@
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4447021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0293312072754</t>
+    <t xml:space="preserve">55.4446983337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1991806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0293350219727</t>
   </si>
   <si>
     <t xml:space="preserve">53.4254455566406</t>
@@ -4601,31 +4601,31 @@
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009307861328</t>
+    <t xml:space="preserve">53.5009346008301</t>
   </si>
   <si>
     <t xml:space="preserve">53.9349784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8785552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4067687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4445114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3503456115723</t>
+    <t xml:space="preserve">54.8785514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4067649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.444507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9729118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4633827209473</t>
+    <t xml:space="preserve">54.9729080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.46337890625</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106544494629</t>
@@ -4640,10 +4640,10 @@
     <t xml:space="preserve">56.9544296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3507347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1431427001953</t>
+    <t xml:space="preserve">57.3507308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1431465148926</t>
   </si>
   <si>
     <t xml:space="preserve">57.7470359802246</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">57.1808853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">56.407154083252</t>
+    <t xml:space="preserve">56.4071502685547</t>
   </si>
   <si>
     <t xml:space="preserve">56.8789405822754</t>
@@ -4661,34 +4661,34 @@
     <t xml:space="preserve">54.8974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0676612854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2748603820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6526718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2184410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2939262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5017051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1433410644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2186279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2752494812012</t>
+    <t xml:space="preserve">57.0676574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2748565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6526756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2184371948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2939224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5017013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546241760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1433372497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2186317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2752456665039</t>
   </si>
   <si>
     <t xml:space="preserve">58.9170761108398</t>
@@ -4697,13 +4697,13 @@
     <t xml:space="preserve">58.8982009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9550132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1059837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0116233825684</t>
+    <t xml:space="preserve">59.9550094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1059875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0116271972656</t>
   </si>
   <si>
     <t xml:space="preserve">60.6155128479004</t>
@@ -4712,64 +4712,64 @@
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417778015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4266090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0686264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2196083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9929504394531</t>
+    <t xml:space="preserve">59.8417816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4266052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0686225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.219596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9929466247559</t>
   </si>
   <si>
     <t xml:space="preserve">61.8044204711914</t>
   </si>
   <si>
-    <t xml:space="preserve">62.2007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.408504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8614234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7293319702148</t>
+    <t xml:space="preserve">62.2007255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1443061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4085121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8614311218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7293281555176</t>
   </si>
   <si>
     <t xml:space="preserve">63.9935264587402</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3707656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896408081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.691780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5028686523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9933319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4649276733398</t>
+    <t xml:space="preserve">63.3707695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896369934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6917724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5028648376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.993335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4649238586426</t>
   </si>
   <si>
     <t xml:space="preserve">61.8987808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">63.01220703125</t>
+    <t xml:space="preserve">63.0122108459473</t>
   </si>
   <si>
     <t xml:space="preserve">62.9178504943848</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">61.5968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8608436584473</t>
+    <t xml:space="preserve">60.8608474731445</t>
   </si>
   <si>
     <t xml:space="preserve">60.7287483215332</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">60.8631858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2293968200684</t>
+    <t xml:space="preserve">60.2293930053711</t>
   </si>
   <si>
     <t xml:space="preserve">60.9784202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8055648803711</t>
+    <t xml:space="preserve">60.8055686950684</t>
   </si>
   <si>
     <t xml:space="preserve">59.4227523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">61.804271697998</t>
+    <t xml:space="preserve">61.8042678833008</t>
   </si>
   <si>
     <t xml:space="preserve">60.9015960693359</t>
@@ -4823,16 +4823,16 @@
     <t xml:space="preserve">61.2665061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.4982757568359</t>
+    <t xml:space="preserve">60.4982719421387</t>
   </si>
   <si>
     <t xml:space="preserve">61.9963264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1102676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0718536376953</t>
+    <t xml:space="preserve">63.1102638244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.071849822998</t>
   </si>
   <si>
     <t xml:space="preserve">62.898998260498</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">60.9976272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9605140686035</t>
+    <t xml:space="preserve">59.9605102539062</t>
   </si>
   <si>
     <t xml:space="preserve">59.8068656921387</t>
@@ -4868,22 +4868,22 @@
     <t xml:space="preserve">60.3638343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8247718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4214515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7671585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4022483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8657836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1538696289062</t>
+    <t xml:space="preserve">60.8247756958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4214477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4022445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.865779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.153865814209</t>
   </si>
   <si>
     <t xml:space="preserve">60.1717758178711</t>
@@ -4895,10 +4895,10 @@
     <t xml:space="preserve">62.8797950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3791427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2831192016602</t>
+    <t xml:space="preserve">63.379150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2831153869629</t>
   </si>
   <si>
     <t xml:space="preserve">61.4393577575684</t>
@@ -4907,13 +4907,13 @@
     <t xml:space="preserve">60.5750999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5379829406738</t>
+    <t xml:space="preserve">59.5379867553711</t>
   </si>
   <si>
     <t xml:space="preserve">59.3843383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7492485046387</t>
+    <t xml:space="preserve">59.7492523193359</t>
   </si>
   <si>
     <t xml:space="preserve">59.9028968811035</t>
@@ -4922,10 +4922,10 @@
     <t xml:space="preserve">60.3254203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2883110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3023223876953</t>
+    <t xml:space="preserve">59.2883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.302318572998</t>
   </si>
   <si>
     <t xml:space="preserve">62.783763885498</t>
@@ -4937,25 +4937,25 @@
     <t xml:space="preserve">60.6135101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1922798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3651313781738</t>
+    <t xml:space="preserve">59.1922836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3651351928711</t>
   </si>
   <si>
     <t xml:space="preserve">61.4969787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5161819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9797210693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8439788818359</t>
+    <t xml:space="preserve">61.5161781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7850570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9797172546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8439826965332</t>
   </si>
   <si>
     <t xml:space="preserve">60.5558929443359</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">59.5763969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5571899414062</t>
+    <t xml:space="preserve">59.5571937561035</t>
   </si>
   <si>
     <t xml:space="preserve">59.8836898803711</t>
@@ -4982,28 +4982,28 @@
     <t xml:space="preserve">60.1525688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1333656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1346664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1961784362793</t>
+    <t xml:space="preserve">60.1333618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1346626281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.196174621582</t>
   </si>
   <si>
     <t xml:space="preserve">56.080940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1769714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8683776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2153854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7915534973145</t>
+    <t xml:space="preserve">56.1769676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8683815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2153816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7915573120117</t>
   </si>
   <si>
     <t xml:space="preserve">57.4061393737793</t>
@@ -5015,22 +5015,22 @@
     <t xml:space="preserve">55.4087409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4471473693848</t>
+    <t xml:space="preserve">55.447151184082</t>
   </si>
   <si>
     <t xml:space="preserve">54.2948036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1974716186523</t>
+    <t xml:space="preserve">55.1974754333496</t>
   </si>
   <si>
     <t xml:space="preserve">54.0451240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1437530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2218704223633</t>
+    <t xml:space="preserve">52.1437492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2218742370605</t>
   </si>
   <si>
     <t xml:space="preserve">52.3742218017578</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">52.4510459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6431007385254</t>
+    <t xml:space="preserve">52.6431045532227</t>
   </si>
   <si>
     <t xml:space="preserve">53.7954521179199</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">50.7417259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0682258605957</t>
+    <t xml:space="preserve">51.068229675293</t>
   </si>
   <si>
     <t xml:space="preserve">50.8377571105957</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">50.8761711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9337844848633</t>
+    <t xml:space="preserve">50.9337882995605</t>
   </si>
   <si>
     <t xml:space="preserve">51.0106086730957</t>
@@ -5096,22 +5096,22 @@
     <t xml:space="preserve">49.8006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5836715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8237419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5823745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1668548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.974796295166</t>
+    <t xml:space="preserve">46.583667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8237457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5823707580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1668510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9747924804688</t>
   </si>
   <si>
     <t xml:space="preserve">48.7827339172363</t>
@@ -5129,19 +5129,19 @@
     <t xml:space="preserve">47.4959449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7552261352539</t>
+    <t xml:space="preserve">47.7552223205566</t>
   </si>
   <si>
     <t xml:space="preserve">49.4165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4946517944336</t>
+    <t xml:space="preserve">48.4946479797363</t>
   </si>
   <si>
     <t xml:space="preserve">48.4370307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5701713562012</t>
+    <t xml:space="preserve">49.5701751708984</t>
   </si>
   <si>
     <t xml:space="preserve">48.9363822937012</t>
@@ -5156,16 +5156,16 @@
     <t xml:space="preserve">49.5125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.262882232666</t>
+    <t xml:space="preserve">49.2628784179688</t>
   </si>
   <si>
     <t xml:space="preserve">48.7059135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9940032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8595581054688</t>
+    <t xml:space="preserve">48.9939994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.859561920166</t>
   </si>
   <si>
     <t xml:space="preserve">48.6675033569336</t>
@@ -5174,13 +5174,13 @@
     <t xml:space="preserve">49.4549407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8774642944336</t>
+    <t xml:space="preserve">49.8774681091309</t>
   </si>
   <si>
     <t xml:space="preserve">50.2999954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5291633605957</t>
+    <t xml:space="preserve">51.529167175293</t>
   </si>
   <si>
     <t xml:space="preserve">52.4318389892578</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">52.9696006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5265731811523</t>
+    <t xml:space="preserve">53.5265693664551</t>
   </si>
   <si>
     <t xml:space="preserve">54.0259208679199</t>
@@ -5210,13 +5210,13 @@
     <t xml:space="preserve">53.7762451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7378311157227</t>
+    <t xml:space="preserve">53.7378349304199</t>
   </si>
   <si>
     <t xml:space="preserve">53.3537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4881591796875</t>
+    <t xml:space="preserve">53.4881553649902</t>
   </si>
   <si>
     <t xml:space="preserve">53.4305381774902</t>
@@ -5252,34 +5252,34 @@
     <t xml:space="preserve">49.1092338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.493350982666</t>
+    <t xml:space="preserve">49.4933547973633</t>
   </si>
   <si>
     <t xml:space="preserve">49.3973197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.839054107666</t>
+    <t xml:space="preserve">49.8390579223633</t>
   </si>
   <si>
     <t xml:space="preserve">49.896671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0246200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8901824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4279479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0617370605469</t>
+    <t xml:space="preserve">54.6020927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0054168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0246238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8901786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4279441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0617332458496</t>
   </si>
   <si>
     <t xml:space="preserve">55.8312644958496</t>
@@ -5294,10 +5294,10 @@
     <t xml:space="preserve">57.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0028228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3293151855469</t>
+    <t xml:space="preserve">57.0028190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3293190002441</t>
   </si>
   <si>
     <t xml:space="preserve">60.0373344421387</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">61.1896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5545959472656</t>
+    <t xml:space="preserve">61.5545921325684</t>
   </si>
   <si>
     <t xml:space="preserve">61.1512718200684</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">64.2626113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3599395751953</t>
+    <t xml:space="preserve">63.3599433898926</t>
   </si>
   <si>
     <t xml:space="preserve">63.9937286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3394393920898</t>
+    <t xml:space="preserve">64.3394317626953</t>
   </si>
   <si>
     <t xml:space="preserve">64.4354629516602</t>
   </si>
   <si>
-    <t xml:space="preserve">65.568603515625</t>
+    <t xml:space="preserve">65.5686111450195</t>
   </si>
   <si>
     <t xml:space="preserve">66.6249237060547</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">66.8746032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5468063354492</t>
+    <t xml:space="preserve">67.5467987060547</t>
   </si>
   <si>
     <t xml:space="preserve">66.5096969604492</t>
@@ -5357,16 +5357,16 @@
     <t xml:space="preserve">66.4712829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7798690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5301895141602</t>
+    <t xml:space="preserve">65.7798767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5301971435547</t>
   </si>
   <si>
     <t xml:space="preserve">65.4533767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2997283935547</t>
+    <t xml:space="preserve">65.2997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">65.799072265625</t>
@@ -5393,7 +5393,7 @@
     <t xml:space="preserve">62.0155372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0539474487305</t>
+    <t xml:space="preserve">62.0539512634277</t>
   </si>
   <si>
     <t xml:space="preserve">61.6122131347656</t>
@@ -5405,28 +5405,28 @@
     <t xml:space="preserve">63.4367599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0334396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8413848876953</t>
+    <t xml:space="preserve">63.0334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8413887023926</t>
   </si>
   <si>
     <t xml:space="preserve">62.668529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2254981994629</t>
+    <t xml:space="preserve">63.2254905700684</t>
   </si>
   <si>
     <t xml:space="preserve">64.1473770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1883850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3420333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9579124450684</t>
+    <t xml:space="preserve">62.1883888244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3420295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9579162597656</t>
   </si>
   <si>
     <t xml:space="preserve">61.573802947998</t>
@@ -6399,6 +6399,9 @@
   </si>
   <si>
     <t xml:space="preserve">52.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -71503,7 +71506,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6510069444</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>790497</v>
@@ -71524,6 +71527,32 @@
         <v>2128</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6516319444</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>856619</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>53.2999992370605</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>52.3199996948242</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>53.2999992370605</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2129</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="2136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="2137">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8452548980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986349105835</t>
+    <t xml:space="preserve">10.9698095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8452520370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986358642578</t>
   </si>
   <si>
     <t xml:space="preserve">10.9876041412354</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">11.1744384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9573612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281757354736</t>
+    <t xml:space="preserve">11.9573602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281785964966</t>
   </si>
   <si>
     <t xml:space="preserve">11.4769296646118</t>
@@ -71,43 +71,43 @@
     <t xml:space="preserve">11.156644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5481033325195</t>
+    <t xml:space="preserve">11.5481061935425</t>
   </si>
   <si>
     <t xml:space="preserve">11.734938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
+    <t xml:space="preserve">11.4057559967041</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239068984985</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1175022125244</t>
+    <t xml:space="preserve">12.1175031661987</t>
   </si>
   <si>
     <t xml:space="preserve">12.0018453598022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1264009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0997095108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7260417938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9484634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950815200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616310119629</t>
+    <t xml:space="preserve">12.1263999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0997114181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7260427474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908136367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9484624862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
   </si>
   <si>
     <t xml:space="preserve">11.9128761291504</t>
@@ -119,40 +119,40 @@
     <t xml:space="preserve">11.2723035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0409841537476</t>
+    <t xml:space="preserve">11.0409851074219</t>
   </si>
   <si>
     <t xml:space="preserve">11.254508972168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9431200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989940643311</t>
+    <t xml:space="preserve">10.9431209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989921569824</t>
   </si>
   <si>
     <t xml:space="preserve">11.6726608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772888183594</t>
+    <t xml:space="preserve">11.8772897720337</t>
   </si>
   <si>
     <t xml:space="preserve">12.4110994338989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2509565353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2687511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4022035598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7972164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1975765228271</t>
+    <t xml:space="preserve">12.2509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2687501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4022016525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7972173690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1975755691528</t>
   </si>
   <si>
     <t xml:space="preserve">12.7402820587158</t>
@@ -167,28 +167,28 @@
     <t xml:space="preserve">13.2118158340454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4075450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4787197113037</t>
+    <t xml:space="preserve">13.4075469970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.478720664978</t>
   </si>
   <si>
     <t xml:space="preserve">13.9680471420288</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4520311355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7100381851196</t>
+    <t xml:space="preserve">13.4520292282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210718154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7100391387939</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363704681396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0427742004395</t>
+    <t xml:space="preserve">13.0427751541138</t>
   </si>
   <si>
     <t xml:space="preserve">13.0605697631836</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">12.9893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.900426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0160837173462</t>
+    <t xml:space="preserve">12.9004259109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0160846710205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9449090957642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0961561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5143089294434</t>
+    <t xml:space="preserve">13.096155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.514307975769</t>
   </si>
   <si>
     <t xml:space="preserve">13.1228475570679</t>
@@ -218,61 +218,61 @@
     <t xml:space="preserve">12.9804973602295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9271173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.589035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.793664932251</t>
+    <t xml:space="preserve">12.9271154403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5890369415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7936639785767</t>
   </si>
   <si>
     <t xml:space="preserve">12.8292512893677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0338792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737354278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1495380401611</t>
+    <t xml:space="preserve">13.033878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1495370864868</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029190063477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3897523880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1673307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089654922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5979318618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9715995788574</t>
+    <t xml:space="preserve">13.3897533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1673316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089664459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5979328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9716014862061</t>
   </si>
   <si>
     <t xml:space="preserve">12.998291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3185758590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9324598312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947366714478</t>
+    <t xml:space="preserve">13.3185768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9324607849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570135116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947385787964</t>
   </si>
   <si>
     <t xml:space="preserve">13.9502544403076</t>
@@ -281,28 +281,28 @@
     <t xml:space="preserve">13.6388645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5676879882812</t>
+    <t xml:space="preserve">13.5676889419556</t>
   </si>
   <si>
     <t xml:space="preserve">13.3630628585815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3452682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2285184860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5608034133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4440536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2734231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709968566895</t>
+    <t xml:space="preserve">13.345269203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5608043670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4440546035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2734222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709978103638</t>
   </si>
   <si>
     <t xml:space="preserve">13.5967264175415</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">13.4979391098022</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3632287979126</t>
+    <t xml:space="preserve">13.3632297515869</t>
   </si>
   <si>
     <t xml:space="preserve">13.3183259963989</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">13.6685724258423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7314357757568</t>
+    <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
     <t xml:space="preserve">13.7404174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3003664016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1566743850708</t>
+    <t xml:space="preserve">13.3003644943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1566734313965</t>
   </si>
   <si>
     <t xml:space="preserve">12.7256021499634</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">13.8122615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6775531768799</t>
+    <t xml:space="preserve">13.6775522232056</t>
   </si>
   <si>
     <t xml:space="preserve">13.8571662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2253723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6986598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9950218200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6178331375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8513317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8782739639282</t>
+    <t xml:space="preserve">14.2253732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6986589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476926803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.995020866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6178340911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8513326644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8782730102539</t>
   </si>
   <si>
     <t xml:space="preserve">12.9680795669556</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">13.174635887146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.959098815918</t>
+    <t xml:space="preserve">12.9591007232666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7705049514771</t>
+    <t xml:space="preserve">12.7705068588257</t>
   </si>
   <si>
     <t xml:space="preserve">13.3452672958374</t>
@@ -404,37 +404,37 @@
     <t xml:space="preserve">13.8302240371704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1714887619019</t>
+    <t xml:space="preserve">14.1714878082275</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637216567993</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3690633773804</t>
+    <t xml:space="preserve">14.3690624237061</t>
   </si>
   <si>
     <t xml:space="preserve">14.0816831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9559535980225</t>
+    <t xml:space="preserve">13.9559526443481</t>
   </si>
   <si>
     <t xml:space="preserve">13.5069198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6057071685791</t>
+    <t xml:space="preserve">13.6057062149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.929012298584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0277976989746</t>
+    <t xml:space="preserve">14.0277986526489</t>
   </si>
   <si>
     <t xml:space="preserve">14.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8481855392456</t>
+    <t xml:space="preserve">13.8481864929199</t>
   </si>
   <si>
     <t xml:space="preserve">14.0457601547241</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">13.7673597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0008563995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7583780288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6955137252808</t>
+    <t xml:space="preserve">14.0008554458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7583770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6955127716064</t>
   </si>
   <si>
     <t xml:space="preserve">13.5877456665039</t>
@@ -464,34 +464,34 @@
     <t xml:space="preserve">13.5248823165894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.354248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4171123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159006118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7224550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5338611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.704493522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9110498428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.614688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.009838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727014541626</t>
+    <t xml:space="preserve">13.3542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4171133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159015655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7224559783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.533863067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7044954299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9110479354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0098361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727024078369</t>
   </si>
   <si>
     <t xml:space="preserve">13.4530353546143</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">13.6506099700928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6416301727295</t>
+    <t xml:space="preserve">13.6416292190552</t>
   </si>
   <si>
     <t xml:space="preserve">13.7853212356567</t>
@@ -509,28 +509,28 @@
     <t xml:space="preserve">13.4799776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8392038345337</t>
+    <t xml:space="preserve">13.839204788208</t>
   </si>
   <si>
     <t xml:space="preserve">14.0996437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8930883407593</t>
+    <t xml:space="preserve">13.893087387085</t>
   </si>
   <si>
     <t xml:space="preserve">13.9649333953857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8751258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7943019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.62366771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3991527557373</t>
+    <t xml:space="preserve">13.8751249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7942991256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6236686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.399151802063</t>
   </si>
   <si>
     <t xml:space="preserve">13.3901710510254</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">13.3362874984741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6326484680176</t>
+    <t xml:space="preserve">13.6326494216919</t>
   </si>
   <si>
     <t xml:space="preserve">13.3273067474365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7763395309448</t>
+    <t xml:space="preserve">13.7763376235962</t>
   </si>
   <si>
     <t xml:space="preserve">13.8661460876465</t>
@@ -563,46 +563,46 @@
     <t xml:space="preserve">14.6384840011597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9168863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.04261302948</t>
+    <t xml:space="preserve">14.9168844223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964984893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0426139831543</t>
   </si>
   <si>
     <t xml:space="preserve">14.8989229202271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.548677444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7372722625732</t>
+    <t xml:space="preserve">14.5486764907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7372713088989</t>
   </si>
   <si>
     <t xml:space="preserve">14.7731943130493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8719806671143</t>
+    <t xml:space="preserve">14.8719816207886</t>
   </si>
   <si>
     <t xml:space="preserve">14.7911529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6564445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6833868026733</t>
+    <t xml:space="preserve">14.6564455032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.683385848999</t>
   </si>
   <si>
     <t xml:space="preserve">14.7013492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8450412750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0875177383423</t>
+    <t xml:space="preserve">14.8450403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.087516784668</t>
   </si>
   <si>
     <t xml:space="preserve">14.9707670211792</t>
@@ -614,121 +614,121 @@
     <t xml:space="preserve">14.6744060516357</t>
   </si>
   <si>
-    <t xml:space="preserve">14.952808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736862182617</t>
+    <t xml:space="preserve">14.9528064727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377641677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">15.6892213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7251443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.482666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0933513641357</t>
+    <t xml:space="preserve">15.7251453399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4826641082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790269851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0933532714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.1651973724365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2011222839355</t>
+    <t xml:space="preserve">16.2011184692383</t>
   </si>
   <si>
     <t xml:space="preserve">16.192138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2460193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304851531982</t>
+    <t xml:space="preserve">16.246021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304870605469</t>
   </si>
   <si>
     <t xml:space="preserve">15.9855833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9137411117554</t>
+    <t xml:space="preserve">15.9137353897095</t>
   </si>
   <si>
     <t xml:space="preserve">15.6353368759155</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9316968917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766025543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9586420059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867979049683</t>
+    <t xml:space="preserve">15.931697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9766044616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.958643913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406805038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867969512939</t>
   </si>
   <si>
     <t xml:space="preserve">16.1741771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.102331161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0484485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8957767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.967625617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831607818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0991897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2608337402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1620502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2967624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3326816558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5122966766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5661773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6559867858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6021041870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8535594940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062313079834</t>
+    <t xml:space="preserve">16.1023330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0484504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8957777023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9676218032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0991859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2608375549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.162052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2967586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3326797485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5122947692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5661792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6021022796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8535614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.006233215332</t>
   </si>
   <si>
     <t xml:space="preserve">18.1768646240234</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">18.0601177215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0870590209961</t>
+    <t xml:space="preserve">18.0870571136475</t>
   </si>
   <si>
     <t xml:space="preserve">18.320556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2666702270508</t>
+    <t xml:space="preserve">18.2666721343994</t>
   </si>
   <si>
     <t xml:space="preserve">18.4103622436523</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">18.1678848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2756519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4373035430908</t>
+    <t xml:space="preserve">18.2756538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4373054504395</t>
   </si>
   <si>
     <t xml:space="preserve">18.6169185638428</t>
@@ -767,37 +767,37 @@
     <t xml:space="preserve">18.9312438964844</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2276000976562</t>
+    <t xml:space="preserve">19.2276039123535</t>
   </si>
   <si>
     <t xml:space="preserve">19.2365837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2006587982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.479061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5598907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1108589172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2096424102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3174095153809</t>
+    <t xml:space="preserve">19.2006607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4790630340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5598888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1108570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3174114227295</t>
   </si>
   <si>
     <t xml:space="preserve">19.5329475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4611015319824</t>
+    <t xml:space="preserve">19.6945991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610996246338</t>
   </si>
   <si>
     <t xml:space="preserve">19.5778465270996</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">19.514986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1885318756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3501873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6645107269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8351459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.11354637146</t>
+    <t xml:space="preserve">20.1885356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310111999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3501853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6645088195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8351440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1135425567627</t>
   </si>
   <si>
     <t xml:space="preserve">20.4759140014648</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">19.7844047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">19.999942779541</t>
+    <t xml:space="preserve">19.9999389648438</t>
   </si>
   <si>
     <t xml:space="preserve">19.8921737670898</t>
@@ -839,31 +839,31 @@
     <t xml:space="preserve">19.9819774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8742122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9909572601318</t>
+    <t xml:space="preserve">19.8742141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9909591674805</t>
   </si>
   <si>
     <t xml:space="preserve">19.3892574310303</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5509052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6505165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229652404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6052379608154</t>
+    <t xml:space="preserve">19.5509090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6505184173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">19.4875183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0127410888672</t>
+    <t xml:space="preserve">20.0127391815186</t>
   </si>
   <si>
     <t xml:space="preserve">19.2339630126953</t>
@@ -872,46 +872,46 @@
     <t xml:space="preserve">19.6324043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7048511505127</t>
+    <t xml:space="preserve">19.7048492431641</t>
   </si>
   <si>
     <t xml:space="preserve">19.279239654541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9260730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0075721740723</t>
+    <t xml:space="preserve">18.9260749816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0075740814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.9713516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0800170898438</t>
+    <t xml:space="preserve">19.0800189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.5819664001465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8355159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1252975463867</t>
+    <t xml:space="preserve">18.8355197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1252956390381</t>
   </si>
   <si>
     <t xml:space="preserve">19.0437984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3426303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2249050140381</t>
+    <t xml:space="preserve">19.3426284790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2249088287354</t>
   </si>
   <si>
     <t xml:space="preserve">19.6142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2158508300781</t>
+    <t xml:space="preserve">19.2158489227295</t>
   </si>
   <si>
     <t xml:space="preserve">19.1524639129639</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">19.143404006958</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3245162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.944185256958</t>
+    <t xml:space="preserve">19.324520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9441871643066</t>
   </si>
   <si>
     <t xml:space="preserve">18.373685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5638523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6362972259521</t>
+    <t xml:space="preserve">18.5638542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6362991333008</t>
   </si>
   <si>
     <t xml:space="preserve">18.600076675415</t>
@@ -941,64 +941,64 @@
     <t xml:space="preserve">18.8083534240723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7359066009521</t>
+    <t xml:space="preserve">18.7359104156494</t>
   </si>
   <si>
     <t xml:space="preserve">18.609130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1071834564209</t>
+    <t xml:space="preserve">19.1071853637695</t>
   </si>
   <si>
     <t xml:space="preserve">19.2882957458496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3788528442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4060192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4512958526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4331836700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2701873779297</t>
+    <t xml:space="preserve">19.3788509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4060173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4512977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4331855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
     <t xml:space="preserve">19.1977405548096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2391300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4655170440674</t>
+    <t xml:space="preserve">20.239128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.465518951416</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568477630615</t>
+    <t xml:space="preserve">20.3568515777588</t>
   </si>
   <si>
     <t xml:space="preserve">20.2572383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3930721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.329683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.374963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4021282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3477935791016</t>
+    <t xml:space="preserve">20.3930740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3296813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3749618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4021263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3477954864502</t>
   </si>
   <si>
     <t xml:space="preserve">20.8458499908447</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">21.144681930542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5431270599365</t>
+    <t xml:space="preserve">21.5431289672852</t>
   </si>
   <si>
     <t xml:space="preserve">21.3801250457764</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">21.4254035949707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3710708618164</t>
+    <t xml:space="preserve">21.371072769165</t>
   </si>
   <si>
     <t xml:space="preserve">21.2805137634277</t>
@@ -1031,37 +1031,37 @@
     <t xml:space="preserve">20.8730144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2714557647705</t>
+    <t xml:space="preserve">21.2714576721191</t>
   </si>
   <si>
     <t xml:space="preserve">21.615571975708</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8962917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7423477172852</t>
+    <t xml:space="preserve">21.8962955474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7423496246338</t>
   </si>
   <si>
     <t xml:space="preserve">21.7966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9959049224854</t>
+    <t xml:space="preserve">21.9959030151367</t>
   </si>
   <si>
     <t xml:space="preserve">22.158899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4305686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3671798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5935688018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116790771484</t>
+    <t xml:space="preserve">22.430570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3671779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5935668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6116752624512</t>
   </si>
   <si>
     <t xml:space="preserve">22.5030136108398</t>
@@ -1070,28 +1070,28 @@
     <t xml:space="preserve">22.2404003143311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3852863311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2313480377197</t>
+    <t xml:space="preserve">22.385290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2313461303711</t>
   </si>
   <si>
     <t xml:space="preserve">22.2132358551025</t>
   </si>
   <si>
-    <t xml:space="preserve">22.249454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.959680557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8238487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0683460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1136226654053</t>
+    <t xml:space="preserve">22.2494564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9596786499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8238468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0683441162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1136245727539</t>
   </si>
   <si>
     <t xml:space="preserve">22.1407909393311</t>
@@ -1106,25 +1106,25 @@
     <t xml:space="preserve">21.4706802368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1498470306396</t>
+    <t xml:space="preserve">22.149845123291</t>
   </si>
   <si>
     <t xml:space="preserve">22.2766246795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0592918395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2856788635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3490715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3943462371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9868450164795</t>
+    <t xml:space="preserve">22.0592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.285680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3490695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.394344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9868488311768</t>
   </si>
   <si>
     <t xml:space="preserve">22.4396228790283</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">22.5573444366455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3581218719482</t>
+    <t xml:space="preserve">22.3581237792969</t>
   </si>
   <si>
     <t xml:space="preserve">22.1226806640625</t>
@@ -1151,28 +1151,28 @@
     <t xml:space="preserve">21.8510112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7695159912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6466274261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0631809234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0088520050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6737957000732</t>
+    <t xml:space="preserve">21.7695140838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466255187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0631828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088481903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6737937927246</t>
   </si>
   <si>
     <t xml:space="preserve">20.7734031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6556816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.099401473999</t>
+    <t xml:space="preserve">20.6556835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0994033813477</t>
   </si>
   <si>
     <t xml:space="preserve">21.0903511047363</t>
@@ -1181,52 +1181,52 @@
     <t xml:space="preserve">21.1356258392334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8277378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549022674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8005714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8820705413818</t>
+    <t xml:space="preserve">20.8277359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.800573348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8820724487305</t>
   </si>
   <si>
     <t xml:space="preserve">21.4344577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163455963135</t>
+    <t xml:space="preserve">21.4163436889648</t>
   </si>
   <si>
     <t xml:space="preserve">21.9506244659424</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4667892456055</t>
+    <t xml:space="preserve">22.4667911529541</t>
   </si>
   <si>
     <t xml:space="preserve">22.5120677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8833446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290119171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8109016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0916213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546234130859</t>
+    <t xml:space="preserve">22.8833427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3219013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8108978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0916233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546215057373</t>
   </si>
   <si>
     <t xml:space="preserve">23.6530666351318</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">23.3632869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1821784973145</t>
+    <t xml:space="preserve">23.1821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">23.6349563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4900684356689</t>
+    <t xml:space="preserve">23.4900665283203</t>
   </si>
   <si>
     <t xml:space="preserve">23.5443992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2002868652344</t>
+    <t xml:space="preserve">23.200288772583</t>
   </si>
   <si>
     <t xml:space="preserve">22.8199558258057</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">24.341287612915</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4861755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.250732421875</t>
+    <t xml:space="preserve">24.486177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2507305145264</t>
   </si>
   <si>
     <t xml:space="preserve">24.3775100708008</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">24.5223960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2869529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0333995819092</t>
+    <t xml:space="preserve">24.2869510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1148986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0333976745605</t>
   </si>
   <si>
     <t xml:space="preserve">24.214506149292</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5625133514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4628982543945</t>
+    <t xml:space="preserve">23.5625095367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4629001617432</t>
   </si>
   <si>
     <t xml:space="preserve">24.359395980835</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">24.0424518585205</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6582336425781</t>
+    <t xml:space="preserve">24.6582279205322</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724510192871</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">25.4279518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5637855529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5818958282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4641742706299</t>
+    <t xml:space="preserve">25.5637836456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5818939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4641761779785</t>
   </si>
   <si>
     <t xml:space="preserve">25.391731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6362285614014</t>
+    <t xml:space="preserve">25.6362266540527</t>
   </si>
   <si>
     <t xml:space="preserve">26.1342830657959</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">25.9893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3192863464355</t>
+    <t xml:space="preserve">25.3192844390869</t>
   </si>
   <si>
     <t xml:space="preserve">25.264949798584</t>
@@ -1355,16 +1355,16 @@
     <t xml:space="preserve">25.6996154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5728378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.215784072876</t>
+    <t xml:space="preserve">25.5728397369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2157821655273</t>
   </si>
   <si>
     <t xml:space="preserve">26.405948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5055618286133</t>
+    <t xml:space="preserve">26.5055599212646</t>
   </si>
   <si>
     <t xml:space="preserve">26.6685600280762</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">26.4874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8134498596191</t>
+    <t xml:space="preserve">26.8134479522705</t>
   </si>
   <si>
     <t xml:space="preserve">26.7500591278076</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9583358764648</t>
+    <t xml:space="preserve">26.9583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">27.4654445648193</t>
@@ -1391,40 +1391,40 @@
     <t xml:space="preserve">27.5741138458252</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7190017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6737232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9816112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7655544281006</t>
+    <t xml:space="preserve">27.7189998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6737251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9182205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9816093444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.765552520752</t>
   </si>
   <si>
     <t xml:space="preserve">29.4304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8108310699463</t>
+    <t xml:space="preserve">29.8108291625977</t>
   </si>
   <si>
     <t xml:space="preserve">30.1549434661865</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2364406585693</t>
+    <t xml:space="preserve">30.2364387512207</t>
   </si>
   <si>
     <t xml:space="preserve">29.9104442596436</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5624351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250541687012</t>
+    <t xml:space="preserve">30.562442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250503540039</t>
   </si>
   <si>
     <t xml:space="preserve">30.4809417724609</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">31.902660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7124938964844</t>
+    <t xml:space="preserve">31.7124919891357</t>
   </si>
   <si>
     <t xml:space="preserve">32.0203819274902</t>
@@ -1445,28 +1445,28 @@
     <t xml:space="preserve">31.9207706451416</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6180458068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6904907226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.962158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4602127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9039344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0527114868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3011016845703</t>
+    <t xml:space="preserve">32.6180419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.690486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9621620178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4602088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.903938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0527153015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.301097869873</t>
   </si>
   <si>
     <t xml:space="preserve">33.0346031188965</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">33.0798797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3153305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6866035461426</t>
+    <t xml:space="preserve">33.3153266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6865997314453</t>
   </si>
   <si>
     <t xml:space="preserve">34.0759887695312</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">34.0941047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3929328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2350921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.678825378418</t>
+    <t xml:space="preserve">34.3929290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2350959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788291931152</t>
   </si>
   <si>
     <t xml:space="preserve">35.4416923522949</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">34.4749336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7270584106445</t>
+    <t xml:space="preserve">33.7270622253418</t>
   </si>
   <si>
     <t xml:space="preserve">34.5022964477539</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8065032958984</t>
+    <t xml:space="preserve">35.8065071105957</t>
   </si>
   <si>
     <t xml:space="preserve">36.007152557373</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">35.1589584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156242370605</t>
+    <t xml:space="preserve">35.8156280517578</t>
   </si>
   <si>
     <t xml:space="preserve">35.8429832458496</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3354873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.703540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2931251525879</t>
+    <t xml:space="preserve">36.3354835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7035369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2931175231934</t>
   </si>
   <si>
     <t xml:space="preserve">36.2533988952637</t>
@@ -1541,25 +1541,25 @@
     <t xml:space="preserve">37.2748832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5940971374512</t>
+    <t xml:space="preserve">37.5940933227539</t>
   </si>
   <si>
     <t xml:space="preserve">37.9041900634766</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4696502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3602066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8221092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6546936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3446044921875</t>
+    <t xml:space="preserve">38.4696464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3602027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6546974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3446006774902</t>
   </si>
   <si>
     <t xml:space="preserve">36.28076171875</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">35.4143295288086</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3960876464844</t>
+    <t xml:space="preserve">35.3960952758789</t>
   </si>
   <si>
     <t xml:space="preserve">35.5146522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1042404174805</t>
+    <t xml:space="preserve">35.1042366027832</t>
   </si>
   <si>
     <t xml:space="preserve">35.5693740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3504867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5205383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9550666809082</t>
+    <t xml:space="preserve">35.3504905700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5205345153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9550743103027</t>
   </si>
   <si>
     <t xml:space="preserve">33.745304107666</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">34.2925262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0586318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1830825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8397521972656</t>
+    <t xml:space="preserve">35.0586357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1830863952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8397483825684</t>
   </si>
   <si>
     <t xml:space="preserve">35.596736907959</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">35.469051361084</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3869705200195</t>
+    <t xml:space="preserve">35.3869667053223</t>
   </si>
   <si>
     <t xml:space="preserve">35.2410469055176</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">34.6938209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8091506958008</t>
+    <t xml:space="preserve">33.8091468811035</t>
   </si>
   <si>
     <t xml:space="preserve">34.4019737243652</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">34.2013244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4169654846191</t>
+    <t xml:space="preserve">33.4169731140137</t>
   </si>
   <si>
     <t xml:space="preserve">34.2651634216309</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">34.3746070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5387725830078</t>
+    <t xml:space="preserve">34.5387763977051</t>
   </si>
   <si>
     <t xml:space="preserve">34.7303047180176</t>
@@ -1667,79 +1667,79 @@
     <t xml:space="preserve">34.8215103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4840507507324</t>
+    <t xml:space="preserve">34.4840545654297</t>
   </si>
   <si>
     <t xml:space="preserve">34.7941436767578</t>
   </si>
   <si>
-    <t xml:space="preserve">35.578498840332</t>
+    <t xml:space="preserve">35.5784950256348</t>
   </si>
   <si>
     <t xml:space="preserve">36.2169227600098</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1530799865723</t>
+    <t xml:space="preserve">36.153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">36.3172492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5328941345215</t>
+    <t xml:space="preserve">35.5328979492188</t>
   </si>
   <si>
     <t xml:space="preserve">35.5055351257324</t>
   </si>
   <si>
-    <t xml:space="preserve">35.113353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8365058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2834091186523</t>
+    <t xml:space="preserve">35.1133575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8365097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2834053039551</t>
   </si>
   <si>
     <t xml:space="preserve">34.3381309509277</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3016471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.785026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9824371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6117401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4202156066895</t>
+    <t xml:space="preserve">34.3016510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7850227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9824295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.611743927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4202079772949</t>
   </si>
   <si>
     <t xml:space="preserve">34.5934982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">34.511417388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0827522277832</t>
+    <t xml:space="preserve">34.5114135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0827598571777</t>
   </si>
   <si>
     <t xml:space="preserve">34.4110908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6664581298828</t>
+    <t xml:space="preserve">34.6664543151855</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9400749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.979190826416</t>
+    <t xml:space="preserve">34.940071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9791946411133</t>
   </si>
   <si>
     <t xml:space="preserve">31.8300323486328</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">32.4593353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9388790130615</t>
+    <t xml:space="preserve">28.9388771057129</t>
   </si>
   <si>
     <t xml:space="preserve">28.5284633636475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2001323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.263973236084</t>
+    <t xml:space="preserve">28.2001304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2639713287354</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007778167725</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">28.4555015563965</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7258701324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7988357543945</t>
+    <t xml:space="preserve">27.7258720397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7988338470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.6587924957275</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">27.2698554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9082813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5708236694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1786499023438</t>
+    <t xml:space="preserve">27.9082794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5708255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1786518096924</t>
   </si>
   <si>
     <t xml:space="preserve">27.5434665679932</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">29.1942501068115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.130407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926326751709</t>
+    <t xml:space="preserve">28.97536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1304092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6926288604736</t>
   </si>
   <si>
     <t xml:space="preserve">27.452262878418</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">29.0392036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0268440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0359649658203</t>
+    <t xml:space="preserve">28.0268421173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0359630584717</t>
   </si>
   <si>
     <t xml:space="preserve">27.351936340332</t>
@@ -1832,28 +1832,28 @@
     <t xml:space="preserve">26.2666168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">26.85032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8138389587402</t>
+    <t xml:space="preserve">26.8503189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8138370513916</t>
   </si>
   <si>
     <t xml:space="preserve">27.4340209960938</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2060146331787</t>
+    <t xml:space="preserve">27.2060127258301</t>
   </si>
   <si>
     <t xml:space="preserve">26.7317543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9141616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8079586029053</t>
+    <t xml:space="preserve">26.9141635894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079528808594</t>
   </si>
   <si>
     <t xml:space="preserve">26.768238067627</t>
@@ -1862,31 +1862,31 @@
     <t xml:space="preserve">27.3063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5128650665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8594379425049</t>
+    <t xml:space="preserve">26.5128631591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
     <t xml:space="preserve">25.4822654724121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.327220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.956521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646728515625</t>
+    <t xml:space="preserve">25.3272190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9565258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646709442139</t>
   </si>
   <si>
     <t xml:space="preserve">25.1265716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6431922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1721744537354</t>
+    <t xml:space="preserve">24.643196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.172176361084</t>
   </si>
   <si>
     <t xml:space="preserve">25.7011547088623</t>
@@ -1895,43 +1895,43 @@
     <t xml:space="preserve">25.1448135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3454608917236</t>
+    <t xml:space="preserve">25.3454627990723</t>
   </si>
   <si>
     <t xml:space="preserve">25.5825881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.385181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5949478149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3636989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4672660827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1877727508545</t>
+    <t xml:space="preserve">26.3851833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.59494972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3637008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.467264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1877708435059</t>
   </si>
   <si>
     <t xml:space="preserve">27.935640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6014289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1454086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0600872039795</t>
+    <t xml:space="preserve">28.6014270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1454105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0600852966309</t>
   </si>
   <si>
     <t xml:space="preserve">27.0327243804932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3336963653564</t>
+    <t xml:space="preserve">27.3336982727051</t>
   </si>
   <si>
     <t xml:space="preserve">27.4066600799561</t>
@@ -1940,28 +1940,28 @@
     <t xml:space="preserve">27.6711502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8991584777832</t>
+    <t xml:space="preserve">27.8991603851318</t>
   </si>
   <si>
     <t xml:space="preserve">27.379301071167</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9538822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.880916595459</t>
+    <t xml:space="preserve">27.9538803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8809185028076</t>
   </si>
   <si>
     <t xml:space="preserve">28.2366104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9147567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0059604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.598783493042</t>
+    <t xml:space="preserve">29.914758682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0059623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5987854003906</t>
   </si>
   <si>
     <t xml:space="preserve">30.7994327545166</t>
@@ -1970,46 +1970,46 @@
     <t xml:space="preserve">31.2007236480713</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4437389373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6443862915039</t>
+    <t xml:space="preserve">30.4437408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6443824768066</t>
   </si>
   <si>
     <t xml:space="preserve">30.9362354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7023468017578</t>
+    <t xml:space="preserve">31.7023429870605</t>
   </si>
   <si>
     <t xml:space="preserve">31.9121170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6020240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7753124237061</t>
+    <t xml:space="preserve">31.6020221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.81178855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7753105163574</t>
   </si>
   <si>
     <t xml:space="preserve">31.6567440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6476192474365</t>
+    <t xml:space="preserve">31.6476268768311</t>
   </si>
   <si>
     <t xml:space="preserve">31.4743347167969</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9668369293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9029922485352</t>
+    <t xml:space="preserve">31.9668350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9029960632324</t>
   </si>
   <si>
     <t xml:space="preserve">30.7538280487061</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">34.1557197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7909049987793</t>
+    <t xml:space="preserve">33.790901184082</t>
   </si>
   <si>
     <t xml:space="preserve">32.9244728088379</t>
@@ -2030,58 +2030,58 @@
     <t xml:space="preserve">32.6964645385742</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5140609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5778961181641</t>
+    <t xml:space="preserve">32.5140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5778999328613</t>
   </si>
   <si>
     <t xml:space="preserve">32.4319763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">32.915355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0065574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5264167785645</t>
+    <t xml:space="preserve">32.9153518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0065536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5264091491699</t>
   </si>
   <si>
     <t xml:space="preserve">33.1980819702148</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2313270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.738826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4411010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7603034973145</t>
+    <t xml:space="preserve">32.2313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7388324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4410934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7602996826172</t>
   </si>
   <si>
     <t xml:space="preserve">33.5081748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6084938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1283569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9277153015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8638687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8150291442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.659984588623</t>
+    <t xml:space="preserve">33.6084976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9277114868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8638763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8150329589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6599807739258</t>
   </si>
   <si>
     <t xml:space="preserve">33.2163200378418</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">33.0977592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4260940551758</t>
+    <t xml:space="preserve">33.426097869873</t>
   </si>
   <si>
     <t xml:space="preserve">33.1160049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3075294494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.872989654541</t>
+    <t xml:space="preserve">33.3075256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8729934692383</t>
   </si>
   <si>
     <t xml:space="preserve">33.6814651489258</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">33.061279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3440093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531341552734</t>
+    <t xml:space="preserve">33.3440132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531265258789</t>
   </si>
   <si>
     <t xml:space="preserve">33.2345695495605</t>
@@ -2126,208 +2126,208 @@
     <t xml:space="preserve">33.1616020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">32.550537109375</t>
+    <t xml:space="preserve">32.5505409240723</t>
   </si>
   <si>
     <t xml:space="preserve">32.404613494873</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9485988616943</t>
+    <t xml:space="preserve">33.4443321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9485950469971</t>
   </si>
   <si>
     <t xml:space="preserve">32.6873435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1310043334961</t>
+    <t xml:space="preserve">32.1310005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5596580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5911750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8363723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8586616516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2552757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2829475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7848663330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226844787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4382095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5581169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0062408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6649589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387504577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125419616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6519012451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6480560302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7679634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4136238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7864151000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.518928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2568206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6811103820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9762649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5112380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6127052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5204620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5296936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2806510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3544425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0961799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4927978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0408363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1330757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2253074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2437553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6403770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9263114929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9908790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.963207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6903343200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2844924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4451332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4620399475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309841156006</t>
   </si>
   <si>
     <t xml:space="preserve">32.5596618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5911712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.836368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2552795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2829475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7848663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382095336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5581188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1207637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.006233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6649589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.738748550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6518974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6480560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7679634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5058631896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4136238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7864112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.518928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2568206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6811103820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9762649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5112380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6127052307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5204658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5296936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.280647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3544425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0961761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4927978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0408401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1330757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2253074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2437553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6588287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9263114929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9908714294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.963207244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6903343200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4451332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4620399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5596580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475189208984</t>
+    <t xml:space="preserve">32.4120788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475151062012</t>
   </si>
   <si>
     <t xml:space="preserve">31.4989356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2314434051514</t>
+    <t xml:space="preserve">31.2314472198486</t>
   </si>
   <si>
     <t xml:space="preserve">31.7571964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6926345825195</t>
+    <t xml:space="preserve">31.6926326751709</t>
   </si>
   <si>
     <t xml:space="preserve">32.7072372436523</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">31.7479705810547</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5542736053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3605804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.305233001709</t>
+    <t xml:space="preserve">31.5542755126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3605823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3052368164062</t>
   </si>
   <si>
     <t xml:space="preserve">31.4435901641846</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">31.6465129852295</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3382911682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1684226989746</t>
+    <t xml:space="preserve">32.3382949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0761871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1684265136719</t>
   </si>
   <si>
     <t xml:space="preserve">32.7349128723145</t>
@@ -2372,67 +2372,67 @@
     <t xml:space="preserve">32.6426734924316</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3751831054688</t>
+    <t xml:space="preserve">32.375186920166</t>
   </si>
   <si>
     <t xml:space="preserve">31.6372871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4804878234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2760219573975</t>
+    <t xml:space="preserve">31.4804859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2760200500488</t>
   </si>
   <si>
     <t xml:space="preserve">29.9493541717529</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0877075195312</t>
+    <t xml:space="preserve">30.0877094268799</t>
   </si>
   <si>
     <t xml:space="preserve">29.6080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7279853820801</t>
+    <t xml:space="preserve">29.7279834747314</t>
   </si>
   <si>
     <t xml:space="preserve">29.6449699401855</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8478908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3367462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1614971160889</t>
+    <t xml:space="preserve">29.8478927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3367481231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1614990234375</t>
   </si>
   <si>
     <t xml:space="preserve">29.8294448852539</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1376667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6173000335693</t>
+    <t xml:space="preserve">29.1376705169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.617301940918</t>
   </si>
   <si>
     <t xml:space="preserve">30.0139179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1983966827393</t>
+    <t xml:space="preserve">30.1983947753906</t>
   </si>
   <si>
     <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6134567260742</t>
+    <t xml:space="preserve">30.6134605407715</t>
   </si>
   <si>
     <t xml:space="preserve">31.1945495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8033180236816</t>
+    <t xml:space="preserve">31.8033123016357</t>
   </si>
   <si>
     <t xml:space="preserve">31.5450534820557</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">31.4251403808594</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0285243988037</t>
+    <t xml:space="preserve">31.0285263061523</t>
   </si>
   <si>
     <t xml:space="preserve">30.724142074585</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">29.6726379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9770240783691</t>
+    <t xml:space="preserve">29.9770221710205</t>
   </si>
   <si>
     <t xml:space="preserve">29.7741012573242</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">29.6910877227783</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9678001403809</t>
+    <t xml:space="preserve">29.9678020477295</t>
   </si>
   <si>
     <t xml:space="preserve">33.362117767334</t>
@@ -2468,55 +2468,55 @@
     <t xml:space="preserve">32.7441368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9877910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4397506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5504379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3106231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2291488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180061340332</t>
+    <t xml:space="preserve">31.9877891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5504417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.310619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2291450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180023193359</t>
   </si>
   <si>
     <t xml:space="preserve">34.3121643066406</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0907936096191</t>
+    <t xml:space="preserve">34.0907897949219</t>
   </si>
   <si>
     <t xml:space="preserve">34.0077781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6111640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7218437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9801063537598</t>
+    <t xml:space="preserve">33.6111602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7218475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.980110168457</t>
   </si>
   <si>
     <t xml:space="preserve">34.2199211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8194694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5243110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0462188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1476783752441</t>
+    <t xml:space="preserve">34.819465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5243072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.046215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1476745605469</t>
   </si>
   <si>
     <t xml:space="preserve">37.0239295959473</t>
@@ -2525,22 +2525,22 @@
     <t xml:space="preserve">36.6826515197754</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7787284851074</t>
+    <t xml:space="preserve">35.7787322998047</t>
   </si>
   <si>
     <t xml:space="preserve">35.6772689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1492195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.924015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5458450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8225479125977</t>
+    <t xml:space="preserve">38.1492233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9240112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.545841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8225517272949</t>
   </si>
   <si>
     <t xml:space="preserve">38.0938758850098</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">37.1899566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7157096862793</t>
+    <t xml:space="preserve">37.715705871582</t>
   </si>
   <si>
     <t xml:space="preserve">37.6234703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4758949279785</t>
+    <t xml:space="preserve">37.4758911132812</t>
   </si>
   <si>
     <t xml:space="preserve">36.9593658447266</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">37.9647483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9463005065918</t>
+    <t xml:space="preserve">37.9462966918945</t>
   </si>
   <si>
     <t xml:space="preserve">37.5496788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6326942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3613624572754</t>
+    <t xml:space="preserve">37.6326904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3613662719727</t>
   </si>
   <si>
     <t xml:space="preserve">39.4036445617676</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">39.3852005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1399955749512</t>
+    <t xml:space="preserve">38.1399993896484</t>
   </si>
   <si>
     <t xml:space="preserve">37.2914161682129</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">35.8432960510254</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2360763549805</t>
+    <t xml:space="preserve">37.2360725402832</t>
   </si>
   <si>
     <t xml:space="preserve">36.4889526367188</t>
@@ -2636,31 +2636,31 @@
     <t xml:space="preserve">35.9724273681641</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3690490722656</t>
+    <t xml:space="preserve">36.3690452575684</t>
   </si>
   <si>
     <t xml:space="preserve">36.8579025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2729721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5166282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7049369812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457557678223</t>
+    <t xml:space="preserve">37.2729682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5166244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7049407958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457595825195</t>
   </si>
   <si>
     <t xml:space="preserve">35.649600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">36.258358001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1422920227051</t>
+    <t xml:space="preserve">36.2583656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1422958374023</t>
   </si>
   <si>
     <t xml:space="preserve">35.2898712158203</t>
@@ -2669,16 +2669,16 @@
     <t xml:space="preserve">36.0093231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2660484313965</t>
+    <t xml:space="preserve">34.266040802002</t>
   </si>
   <si>
     <t xml:space="preserve">32.4305267333984</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4028587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9286079406738</t>
+    <t xml:space="preserve">32.4028549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9286041259766</t>
   </si>
   <si>
     <t xml:space="preserve">32.522762298584</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">27.0807819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9816188812256</t>
+    <t xml:space="preserve">23.9816207885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.3943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2637119293213</t>
+    <t xml:space="preserve">25.2637138366699</t>
   </si>
   <si>
     <t xml:space="preserve">24.9039878845215</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">25.3651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.922435760498</t>
+    <t xml:space="preserve">24.9224376678467</t>
   </si>
   <si>
     <t xml:space="preserve">26.9977684020996</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">26.3797817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.930908203125</t>
+    <t xml:space="preserve">29.9309062957764</t>
   </si>
   <si>
     <t xml:space="preserve">31.4528160095215</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">31.729528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">30.705696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8755626678467</t>
+    <t xml:space="preserve">30.7056999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8755645751953</t>
   </si>
   <si>
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857032775879</t>
+    <t xml:space="preserve">28.6857051849365</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688022613525</t>
@@ -2756,58 +2756,58 @@
     <t xml:space="preserve">31.0838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">30.631908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8402099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5135383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8901710510254</t>
+    <t xml:space="preserve">30.6319046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8402118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.513542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8901691436768</t>
   </si>
   <si>
     <t xml:space="preserve">30.5765647888184</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5081596374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2721824645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7702579498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9124603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2352848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7833271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2260646820068</t>
+    <t xml:space="preserve">31.5081577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.272180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.770263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9124565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2352867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7833290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2260627746582</t>
   </si>
   <si>
     <t xml:space="preserve">29.4143772125244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7041549682617</t>
+    <t xml:space="preserve">28.7041530609131</t>
   </si>
   <si>
     <t xml:space="preserve">28.6211395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7372074127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.866340637207</t>
+    <t xml:space="preserve">29.7372093200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8663387298584</t>
   </si>
   <si>
     <t xml:space="preserve">28.8056144714355</t>
@@ -2819,10 +2819,10 @@
     <t xml:space="preserve">30.7979354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3920917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1630363464355</t>
+    <t xml:space="preserve">30.39208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1630401611328</t>
   </si>
   <si>
     <t xml:space="preserve">30.8532772064209</t>
@@ -2831,19 +2831,19 @@
     <t xml:space="preserve">31.0746440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8955574035645</t>
+    <t xml:space="preserve">31.8955554962158</t>
   </si>
   <si>
     <t xml:space="preserve">32.0339088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0377502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3790302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406711578369</t>
+    <t xml:space="preserve">31.0377540588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3790283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406730651855</t>
   </si>
   <si>
     <t xml:space="preserve">31.9693393707275</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">32.4950942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7625846862793</t>
+    <t xml:space="preserve">32.7625770568848</t>
   </si>
   <si>
     <t xml:space="preserve">33.0577392578125</t>
@@ -2867,73 +2867,73 @@
     <t xml:space="preserve">32.126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3974723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6003952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508953094482</t>
+    <t xml:space="preserve">31.3974781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6003913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508972167969</t>
   </si>
   <si>
     <t xml:space="preserve">31.2591190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.489709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.351354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6503524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654220581055</t>
+    <t xml:space="preserve">31.9601173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4897117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6503505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654201507568</t>
   </si>
   <si>
     <t xml:space="preserve">30.9824066162109</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0100746154785</t>
+    <t xml:space="preserve">31.0100765228271</t>
   </si>
   <si>
     <t xml:space="preserve">30.5950107574463</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0692577362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0969333648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4235992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5804023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881687164307</t>
+    <t xml:space="preserve">30.0692596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0969314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4236011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5804042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.488166809082</t>
   </si>
   <si>
     <t xml:space="preserve">30.8809452056885</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3275241851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.078483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5342864990234</t>
+    <t xml:space="preserve">30.3275260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0784854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5342884063721</t>
   </si>
   <si>
     <t xml:space="preserve">29.5527362823486</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8571128845215</t>
+    <t xml:space="preserve">29.8571147918701</t>
   </si>
   <si>
     <t xml:space="preserve">30.0046920776367</t>
@@ -2942,25 +2942,25 @@
     <t xml:space="preserve">30.5857887268066</t>
   </si>
   <si>
-    <t xml:space="preserve">29.884786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9585762023926</t>
+    <t xml:space="preserve">29.8847885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9585742950439</t>
   </si>
   <si>
     <t xml:space="preserve">31.1484355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">31.794095993042</t>
+    <t xml:space="preserve">31.7940921783447</t>
   </si>
   <si>
     <t xml:space="preserve">32.1814880371094</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4766464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8878707885742</t>
+    <t xml:space="preserve">32.4766426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8878746032715</t>
   </si>
   <si>
     <t xml:space="preserve">34.9854927062988</t>
@@ -2969,34 +2969,34 @@
     <t xml:space="preserve">34.3306121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6665000915527</t>
+    <t xml:space="preserve">33.66650390625</t>
   </si>
   <si>
     <t xml:space="preserve">32.4674224853516</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0431365966797</t>
+    <t xml:space="preserve">32.0431327819824</t>
   </si>
   <si>
     <t xml:space="preserve">32.4489784240723</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2644996643066</t>
+    <t xml:space="preserve">32.2645034790039</t>
   </si>
   <si>
     <t xml:space="preserve">32.8455963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7164649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.601936340332</t>
+    <t xml:space="preserve">32.7164611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6019401550293</t>
   </si>
   <si>
     <t xml:space="preserve">33.8509788513184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2237663269043</t>
+    <t xml:space="preserve">33.223762512207</t>
   </si>
   <si>
     <t xml:space="preserve">33.5650405883789</t>
@@ -3011,19 +3011,19 @@
     <t xml:space="preserve">32.6057739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9432182312012</t>
+    <t xml:space="preserve">33.9432106018066</t>
   </si>
   <si>
     <t xml:space="preserve">34.9485969543457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4043998718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9170837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.127685546875</t>
+    <t xml:space="preserve">34.4043960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1276893615723</t>
   </si>
   <si>
     <t xml:space="preserve">32.1907119750977</t>
@@ -3050,43 +3050,43 @@
     <t xml:space="preserve">36.627311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3467597961426</t>
+    <t xml:space="preserve">37.3467559814453</t>
   </si>
   <si>
     <t xml:space="preserve">36.6088638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7195472717285</t>
+    <t xml:space="preserve">36.719554901123</t>
   </si>
   <si>
     <t xml:space="preserve">37.8909645080566</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8725090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6142425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4482231140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4536018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7118721008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6473045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.241455078125</t>
+    <t xml:space="preserve">37.8725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6142463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4482192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4535980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6473083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2414588928223</t>
   </si>
   <si>
     <t xml:space="preserve">37.8263893127441</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9001846313477</t>
+    <t xml:space="preserve">37.9001808166504</t>
   </si>
   <si>
     <t xml:space="preserve">38.4720497131348</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">39.2837371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8463859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5842819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4144096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9916648864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8533096313477</t>
+    <t xml:space="preserve">39.8463821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5842781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4144134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9916610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8533058166504</t>
   </si>
   <si>
     <t xml:space="preserve">43.8863677978516</t>
@@ -3119,25 +3119,25 @@
     <t xml:space="preserve">45.0116500854492</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9286422729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1961326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7349433898926</t>
+    <t xml:space="preserve">44.928638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1961288452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7349395751953</t>
   </si>
   <si>
     <t xml:space="preserve">43.8679161071777</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6242561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.467456817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8694610595703</t>
+    <t xml:space="preserve">44.6242599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4674530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8694534301758</t>
   </si>
   <si>
     <t xml:space="preserve">46.3952102661133</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">46.2476272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1184959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8456192016602</t>
+    <t xml:space="preserve">46.1184997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8456268310547</t>
   </si>
   <si>
     <t xml:space="preserve">44.8640747070312</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">44.1077308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2737579345703</t>
+    <t xml:space="preserve">44.3291053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.273754119873</t>
   </si>
   <si>
     <t xml:space="preserve">43.3882827758789</t>
@@ -3170,31 +3170,31 @@
     <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0708312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6742210388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6703758239746</t>
+    <t xml:space="preserve">44.0708351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6742172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6703796386719</t>
   </si>
   <si>
     <t xml:space="preserve">43.950927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8917427062988</t>
+    <t xml:space="preserve">44.8917465209961</t>
   </si>
   <si>
     <t xml:space="preserve">45.7403259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6649932861328</t>
+    <t xml:space="preserve">43.6649894714355</t>
   </si>
   <si>
     <t xml:space="preserve">43.5912017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3567695617676</t>
+    <t xml:space="preserve">44.3567733764648</t>
   </si>
   <si>
     <t xml:space="preserve">43.7756767272949</t>
@@ -3206,31 +3206,31 @@
     <t xml:space="preserve">44.2091941833496</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1369514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8932914733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0739212036133</t>
+    <t xml:space="preserve">46.1369476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8932876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5758438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0739250183105</t>
   </si>
   <si>
     <t xml:space="preserve">47.6496315002441</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9447898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2622337341309</t>
+    <t xml:space="preserve">47.9447860717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2622413635254</t>
   </si>
   <si>
     <t xml:space="preserve">48.1477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7972068786621</t>
+    <t xml:space="preserve">47.7972106933594</t>
   </si>
   <si>
     <t xml:space="preserve">46.708812713623</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">46.6534729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1807708740234</t>
+    <t xml:space="preserve">49.1807670593262</t>
   </si>
   <si>
     <t xml:space="preserve">47.8710021972656</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">47.0408668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699981689453</t>
+    <t xml:space="preserve">47.1700019836426</t>
   </si>
   <si>
     <t xml:space="preserve">47.3175811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1108131408691</t>
+    <t xml:space="preserve">48.1108169555664</t>
   </si>
   <si>
     <t xml:space="preserve">48.4613189697266</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">47.6865272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6165809631348</t>
+    <t xml:space="preserve">46.6165771484375</t>
   </si>
   <si>
     <t xml:space="preserve">45.7034301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8602333068848</t>
+    <t xml:space="preserve">45.860237121582</t>
   </si>
   <si>
     <t xml:space="preserve">46.4136543273926</t>
@@ -3284,25 +3284,25 @@
     <t xml:space="preserve">48.0001335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3360290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4467086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.837947845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2107315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6019744873047</t>
+    <t xml:space="preserve">47.3360252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4467124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8379440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2107353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6019706726074</t>
   </si>
   <si>
     <t xml:space="preserve">45.3805999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2276420593262</t>
+    <t xml:space="preserve">44.2276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">44.4397850036621</t>
@@ -3317,34 +3317,34 @@
     <t xml:space="preserve">45.0762176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8417892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6573104858398</t>
+    <t xml:space="preserve">45.8417930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6573143005371</t>
   </si>
   <si>
     <t xml:space="preserve">46.450553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5981292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.524341583252</t>
+    <t xml:space="preserve">46.5981330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5243377685547</t>
   </si>
   <si>
     <t xml:space="preserve">47.5020523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3544731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3214149475098</t>
+    <t xml:space="preserve">47.3544769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.321418762207</t>
   </si>
   <si>
     <t xml:space="preserve">48.2952919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">49.346794128418</t>
+    <t xml:space="preserve">49.3467903137207</t>
   </si>
   <si>
     <t xml:space="preserve">46.9670753479004</t>
@@ -3359,34 +3359,34 @@
     <t xml:space="preserve">47.4836006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3767623901367</t>
+    <t xml:space="preserve">46.3767585754395</t>
   </si>
   <si>
     <t xml:space="preserve">47.4282646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2806816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7234230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9855270385742</t>
+    <t xml:space="preserve">47.2806854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7234268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9855194091797</t>
   </si>
   <si>
     <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9263458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6642379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4244194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1623191833496</t>
+    <t xml:space="preserve">47.926342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.664234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4244270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1623153686523</t>
   </si>
   <si>
     <t xml:space="preserve">49.420581817627</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">51.1228141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6251182556152</t>
+    <t xml:space="preserve">51.625114440918</t>
   </si>
   <si>
     <t xml:space="preserve">53.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9877815246582</t>
+    <t xml:space="preserve">53.9877777099609</t>
   </si>
   <si>
     <t xml:space="preserve">54.0621910095215</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">53.4482727050781</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6343040466309</t>
+    <t xml:space="preserve">53.6343078613281</t>
   </si>
   <si>
     <t xml:space="preserve">54.1180038452148</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">54.2296257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1039924621582</t>
+    <t xml:space="preserve">55.1039962768555</t>
   </si>
   <si>
     <t xml:space="preserve">54.8063354492188</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">53.6901206970215</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5971031188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0761947631836</t>
+    <t xml:space="preserve">53.5970993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0761985778809</t>
   </si>
   <si>
     <t xml:space="preserve">53.4668769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.318042755127</t>
+    <t xml:space="preserve">53.3180465698242</t>
   </si>
   <si>
     <t xml:space="preserve">52.815746307373</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">53.0389938354492</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3366546630859</t>
+    <t xml:space="preserve">53.3366508483887</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">54.6203002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4388580322266</t>
+    <t xml:space="preserve">55.4388618469238</t>
   </si>
   <si>
     <t xml:space="preserve">55.7551231384277</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">53.8761558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">53.950569152832</t>
+    <t xml:space="preserve">53.9505653381348</t>
   </si>
   <si>
     <t xml:space="preserve">54.6389083862305</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">56.9271545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2992210388184</t>
+    <t xml:space="preserve">57.2992248535156</t>
   </si>
   <si>
     <t xml:space="preserve">57.727108001709</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5596771240234</t>
+    <t xml:space="preserve">57.5596809387207</t>
   </si>
   <si>
     <t xml:space="preserve">56.4248542785645</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">51.067008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1554260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8437614440918</t>
+    <t xml:space="preserve">50.1554222106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8437576293945</t>
   </si>
   <si>
     <t xml:space="preserve">50.7693519592285</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3972702026367</t>
+    <t xml:space="preserve">50.397274017334</t>
   </si>
   <si>
     <t xml:space="preserve">50.5461044311523</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">51.0297966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9925918579102</t>
+    <t xml:space="preserve">50.9925956726074</t>
   </si>
   <si>
     <t xml:space="preserve">50.2484436035156</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">50.8251533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7879447937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1648368835449</t>
+    <t xml:space="preserve">50.7879486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1648330688477</t>
   </si>
   <si>
     <t xml:space="preserve">48.0904235839844</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">51.1600227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0624084472656</t>
+    <t xml:space="preserve">50.0624046325684</t>
   </si>
   <si>
     <t xml:space="preserve">48.6113204956055</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">51.9785842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9831733703613</t>
+    <t xml:space="preserve">52.9831771850586</t>
   </si>
   <si>
     <t xml:space="preserve">52.4994850158691</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">52.4622764587402</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7133140563965</t>
+    <t xml:space="preserve">54.7133178710938</t>
   </si>
   <si>
     <t xml:space="preserve">54.4714736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5690879821777</t>
+    <t xml:space="preserve">55.5690841674805</t>
   </si>
   <si>
     <t xml:space="preserve">56.0341796875</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">62.8803176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4012222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106292724609</t>
+    <t xml:space="preserve">63.4012184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106254577637</t>
   </si>
   <si>
     <t xml:space="preserve">60.7408981323242</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.754695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.331413269043</t>
+    <t xml:space="preserve">63.7546882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3314056396484</t>
   </si>
   <si>
     <t xml:space="preserve">64.2197799682617</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">62.322208404541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3410339355469</t>
+    <t xml:space="preserve">58.3410301208496</t>
   </si>
   <si>
     <t xml:space="preserve">60.089771270752</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">59.6060829162598</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0385589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9455337524414</t>
+    <t xml:space="preserve">61.0385665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9455375671387</t>
   </si>
   <si>
     <t xml:space="preserve">60.5920715332031</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">61.6896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4430236816406</t>
+    <t xml:space="preserve">64.4430313110352</t>
   </si>
   <si>
     <t xml:space="preserve">62.4710426330566</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">62.1547737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4478416442871</t>
+    <t xml:space="preserve">61.4478378295898</t>
   </si>
   <si>
     <t xml:space="preserve">60.629280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">58.675895690918</t>
+    <t xml:space="preserve">58.6758995056152</t>
   </si>
   <si>
     <t xml:space="preserve">60.182788848877</t>
@@ -3800,16 +3800,16 @@
     <t xml:space="preserve">58.2294082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8573303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3224258422852</t>
+    <t xml:space="preserve">57.8573341369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3224296569824</t>
   </si>
   <si>
     <t xml:space="preserve">58.5642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7549018859863</t>
+    <t xml:space="preserve">59.7549057006836</t>
   </si>
   <si>
     <t xml:space="preserve">60.0711708068848</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">55.7923278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8807487487793</t>
+    <t xml:space="preserve">54.8807525634766</t>
   </si>
   <si>
     <t xml:space="preserve">52.8901634216309</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">52.6111106872559</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3040390014648</t>
+    <t xml:space="preserve">54.3040351867676</t>
   </si>
   <si>
     <t xml:space="preserve">54.3412437438965</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">52.5366897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5693054199219</t>
+    <t xml:space="preserve">51.5693016052246</t>
   </si>
   <si>
     <t xml:space="preserve">52.4064674377441</t>
@@ -3878,13 +3878,13 @@
     <t xml:space="preserve">54.899356842041</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2714233398438</t>
+    <t xml:space="preserve">55.271427154541</t>
   </si>
   <si>
     <t xml:space="preserve">53.8389472961426</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0993995666504</t>
+    <t xml:space="preserve">54.0994033813477</t>
   </si>
   <si>
     <t xml:space="preserve">51.6437187194824</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">50.6391181945801</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1274070739746</t>
+    <t xml:space="preserve">52.1274108886719</t>
   </si>
   <si>
     <t xml:space="preserve">51.2344398498535</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">45.8021774291992</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1230278015137</t>
+    <t xml:space="preserve">47.1230316162109</t>
   </si>
   <si>
     <t xml:space="preserve">44.9464073181152</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">41.8768043518066</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1465606689453</t>
+    <t xml:space="preserve">42.146556854248</t>
   </si>
   <si>
     <t xml:space="preserve">41.4954299926758</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">44.6208457946777</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6487464904785</t>
+    <t xml:space="preserve">44.6487426757812</t>
   </si>
   <si>
     <t xml:space="preserve">43.2441711425781</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">45.709156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7881660461426</t>
+    <t xml:space="preserve">46.7881698608398</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">46.2021522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2765617370605</t>
+    <t xml:space="preserve">46.2765655517578</t>
   </si>
   <si>
     <t xml:space="preserve">48.8717765808105</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">47.1788444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9275817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2810554504395</t>
+    <t xml:space="preserve">48.9275856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2810592651367</t>
   </si>
   <si>
     <t xml:space="preserve">46.9555969238281</t>
@@ -3998,43 +3998,43 @@
     <t xml:space="preserve">46.0254173278809</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4533004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0300102233887</t>
+    <t xml:space="preserve">46.453296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0300140380859</t>
   </si>
   <si>
     <t xml:space="preserve">46.1835479736328</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5881195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5277214050293</t>
+    <t xml:space="preserve">47.5881233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.527717590332</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8301849365234</t>
+    <t xml:space="preserve">43.8301887512207</t>
   </si>
   <si>
     <t xml:space="preserve">45.4300994873047</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2672653198242</t>
+    <t xml:space="preserve">46.267261505127</t>
   </si>
   <si>
     <t xml:space="preserve">46.7695617675781</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5696334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6115379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9604110717773</t>
+    <t xml:space="preserve">45.5696296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6115417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9604072570801</t>
   </si>
   <si>
     <t xml:space="preserve">41.4861259460449</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">41.6163520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8070945739746</t>
+    <t xml:space="preserve">40.8070907592773</t>
   </si>
   <si>
     <t xml:space="preserve">42.1930656433105</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">39.819034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6588172912598</t>
+    <t xml:space="preserve">40.658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">42.3572616577148</t>
@@ -4100,19 +4100,19 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801254272461</t>
+    <t xml:space="preserve">43.4801216125488</t>
   </si>
   <si>
     <t xml:space="preserve">43.234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">42.111930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2155303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6489944458008</t>
+    <t xml:space="preserve">42.1119346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2155265808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.648998260498</t>
   </si>
   <si>
     <t xml:space="preserve">37.2147560119629</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">36.2145652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5166969299316</t>
+    <t xml:space="preserve">37.5167007446289</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">34.9973449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9312934875488</t>
+    <t xml:space="preserve">34.9312973022461</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639801025391</t>
+    <t xml:space="preserve">38.0639762878418</t>
   </si>
   <si>
     <t xml:space="preserve">37.3751678466797</t>
@@ -4166,10 +4166,10 @@
     <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0547370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396598815918</t>
+    <t xml:space="preserve">39.0547332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396560668945</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">40.3474349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.753173828125</t>
+    <t xml:space="preserve">40.7531776428223</t>
   </si>
   <si>
     <t xml:space="preserve">41.1494789123535</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">40.7248687744141</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9990882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9239883422852</t>
+    <t xml:space="preserve">43.9990921020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9239921569824</t>
   </si>
   <si>
     <t xml:space="preserve">45.9806060791016</t>
@@ -4223,22 +4223,22 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389739990234</t>
+    <t xml:space="preserve">45.3389701843262</t>
   </si>
   <si>
     <t xml:space="preserve">46.5278854370117</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5184440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4995765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8579406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7165946960449</t>
+    <t xml:space="preserve">46.5184478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4995727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8579368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7165985107422</t>
   </si>
   <si>
     <t xml:space="preserve">46.9524917602539</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">46.7543411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1315803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0273971557617</t>
+    <t xml:space="preserve">46.1315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0273933410645</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
@@ -4274,31 +4274,31 @@
     <t xml:space="preserve">43.0460739135742</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1496734619141</t>
+    <t xml:space="preserve">42.1496696472168</t>
   </si>
   <si>
     <t xml:space="preserve">42.3100814819336</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1213684082031</t>
+    <t xml:space="preserve">42.1213645935059</t>
   </si>
   <si>
     <t xml:space="preserve">41.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2251625061035</t>
+    <t xml:space="preserve">42.2251586914062</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1777839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3948097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6967506408691</t>
+    <t xml:space="preserve">41.1777877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3948059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6967544555664</t>
   </si>
   <si>
     <t xml:space="preserve">42.4704895019531</t>
@@ -4307,25 +4307,25 @@
     <t xml:space="preserve">42.998893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7158241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646514892578</t>
+    <t xml:space="preserve">42.0175743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646553039551</t>
   </si>
   <si>
     <t xml:space="preserve">40.9230194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4891700744629</t>
+    <t xml:space="preserve">41.4891662597656</t>
   </si>
   <si>
     <t xml:space="preserve">41.8005485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">42.461051940918</t>
+    <t xml:space="preserve">42.4610557556152</t>
   </si>
   <si>
     <t xml:space="preserve">39.9511337280273</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">41.0645561218262</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8095970153809</t>
+    <t xml:space="preserve">39.8096008300781</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703903198242</t>
+    <t xml:space="preserve">41.9703941345215</t>
   </si>
   <si>
     <t xml:space="preserve">41.5174751281738</t>
@@ -4373,10 +4373,10 @@
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252540588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8009338378906</t>
+    <t xml:space="preserve">42.7252578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8009376525879</t>
   </si>
   <si>
     <t xml:space="preserve">44.0557022094727</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">43.7160186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6690330505371</t>
+    <t xml:space="preserve">44.6690292358398</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">46.1693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6692276000977</t>
+    <t xml:space="preserve">45.6692237854004</t>
   </si>
   <si>
     <t xml:space="preserve">43.7443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">42.734691619873</t>
+    <t xml:space="preserve">42.7346954345703</t>
   </si>
   <si>
     <t xml:space="preserve">41.2249641418457</t>
@@ -4418,16 +4418,16 @@
     <t xml:space="preserve">39.8756484985352</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8290481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9422798156738</t>
+    <t xml:space="preserve">42.8290519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9422760009766</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0840110778809</t>
+    <t xml:space="preserve">44.0840148925781</t>
   </si>
   <si>
     <t xml:space="preserve">46.7732124328613</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">47.6129951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1978225708008</t>
+    <t xml:space="preserve">47.7639656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1978187561035</t>
   </si>
   <si>
     <t xml:space="preserve">47.0657196044922</t>
@@ -4451,19 +4451,19 @@
     <t xml:space="preserve">47.0185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6314811706543</t>
+    <t xml:space="preserve">45.6314849853516</t>
   </si>
   <si>
     <t xml:space="preserve">45.6031761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5654335021973</t>
+    <t xml:space="preserve">45.5654296875</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2917938232422</t>
+    <t xml:space="preserve">45.2917900085449</t>
   </si>
   <si>
     <t xml:space="preserve">44.8200035095215</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.546558380127</t>
+    <t xml:space="preserve">45.5465621948242</t>
   </si>
   <si>
     <t xml:space="preserve">45.5937385559082</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">44.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7447090148926</t>
+    <t xml:space="preserve">45.7447128295898</t>
   </si>
   <si>
     <t xml:space="preserve">46.5844955444336</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.150447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3861503601074</t>
+    <t xml:space="preserve">46.1504516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3861465454102</t>
   </si>
   <si>
     <t xml:space="preserve">46.6788558959961</t>
@@ -4517,16 +4517,16 @@
     <t xml:space="preserve">47.3110466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.707160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8017082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5563812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5565757751465</t>
+    <t xml:space="preserve">46.7071647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8017120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5563850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5565719604492</t>
   </si>
   <si>
     <t xml:space="preserve">49.3869247436523</t>
@@ -4535,22 +4535,22 @@
     <t xml:space="preserve">49.7077407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9717483520508</t>
+    <t xml:space="preserve">48.971752166748</t>
   </si>
   <si>
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814796447754</t>
+    <t xml:space="preserve">50.4814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">51.8779754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3497619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8781661987305</t>
+    <t xml:space="preserve">52.3497657775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8781700134277</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">51.9157180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0480117797852</t>
+    <t xml:space="preserve">53.0480155944824</t>
   </si>
   <si>
     <t xml:space="preserve">53.3310890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1046295166016</t>
+    <t xml:space="preserve">53.1046257019043</t>
   </si>
   <si>
     <t xml:space="preserve">53.2555999755859</t>
@@ -4574,22 +4574,22 @@
     <t xml:space="preserve">54.5199928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0859489440918</t>
+    <t xml:space="preserve">54.0859527587891</t>
   </si>
   <si>
     <t xml:space="preserve">53.9727210998535</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8406181335449</t>
+    <t xml:space="preserve">53.8406219482422</t>
   </si>
   <si>
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4446983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1991806030273</t>
+    <t xml:space="preserve">55.4447021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1991767883301</t>
   </si>
   <si>
     <t xml:space="preserve">54.0293350219727</t>
@@ -4604,13 +4604,13 @@
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009346008301</t>
+    <t xml:space="preserve">53.5009307861328</t>
   </si>
   <si>
     <t xml:space="preserve">53.9349784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8785514831543</t>
+    <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
@@ -4619,13 +4619,13 @@
     <t xml:space="preserve">54.444507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">55.350341796875</t>
+    <t xml:space="preserve">55.3503456115723</t>
   </si>
   <si>
     <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9729080200195</t>
+    <t xml:space="preserve">54.9729118347168</t>
   </si>
   <si>
     <t xml:space="preserve">54.46337890625</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">54.5388641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3316650390625</t>
+    <t xml:space="preserve">56.3316688537598</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5017013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546241760254</t>
+    <t xml:space="preserve">57.5017051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546203613281</t>
   </si>
   <si>
     <t xml:space="preserve">58.1433372497559</t>
@@ -4694,37 +4694,37 @@
     <t xml:space="preserve">57.2752456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9170761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8982009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9550094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1059875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0116271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6155128479004</t>
+    <t xml:space="preserve">58.9170722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8981971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9550132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1059837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0116233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6155166625977</t>
   </si>
   <si>
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4266052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0686225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.219596862793</t>
+    <t xml:space="preserve">59.8417778015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4266090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0686264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2196006774902</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">63.1443061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4085121154785</t>
+    <t xml:space="preserve">63.408504486084</t>
   </si>
   <si>
     <t xml:space="preserve">63.8614311218262</t>
@@ -4760,13 +4760,13 @@
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5028648376465</t>
+    <t xml:space="preserve">63.502872467041</t>
   </si>
   <si>
     <t xml:space="preserve">62.993335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4649238586426</t>
+    <t xml:space="preserve">62.4649276733398</t>
   </si>
   <si>
     <t xml:space="preserve">61.8987808227539</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">60.8608474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7287483215332</t>
+    <t xml:space="preserve">60.7287445068359</t>
   </si>
   <si>
     <t xml:space="preserve">62.1307678222656</t>
@@ -6420,6 +6420,9 @@
   </si>
   <si>
     <t xml:space="preserve">51.8400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2200012207031</t>
   </si>
 </sst>
 </file>
@@ -71732,7 +71735,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6930555556</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>2072297</v>
@@ -71753,6 +71756,32 @@
         <v>2135</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.69125</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>742455</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>52.2200012207031</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>51.2200012207031</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>52.2200012207031</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>2136</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="2143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="2144">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -56,91 +56,91 @@
     <t xml:space="preserve">10.9876041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1744375228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573602676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281776428223</t>
+    <t xml:space="preserve">11.1744384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
     <t xml:space="preserve">11.4769306182861</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1566438674927</t>
+    <t xml:space="preserve">11.156644821167</t>
   </si>
   <si>
     <t xml:space="preserve">11.5481052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349405288696</t>
+    <t xml:space="preserve">11.7349376678467</t>
   </si>
   <si>
     <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1175031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018453598022</t>
+    <t xml:space="preserve">11.8239088058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018444061279</t>
   </si>
   <si>
     <t xml:space="preserve">12.1263990402222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0997085571289</t>
+    <t xml:space="preserve">12.0997104644775</t>
   </si>
   <si>
     <t xml:space="preserve">11.7260417938232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0908136367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9484643936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950815200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616291046143</t>
+    <t xml:space="preserve">12.0908126831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9484634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
   </si>
   <si>
     <t xml:space="preserve">11.9128761291504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4146537780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2723035812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.254508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6726627349854</t>
+    <t xml:space="preserve">11.4146518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2723045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0409832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2545080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.672661781311</t>
   </si>
   <si>
     <t xml:space="preserve">11.8772897720337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2509565353394</t>
+    <t xml:space="preserve">12.4111003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.250955581665</t>
   </si>
   <si>
     <t xml:space="preserve">12.2687501907349</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">11.7972183227539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1975736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7402820587158</t>
+    <t xml:space="preserve">12.1975755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7402830123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.9627027511597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7669725418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2118148803711</t>
+    <t xml:space="preserve">12.7669734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2118158340454</t>
   </si>
   <si>
     <t xml:space="preserve">13.407546043396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.478720664978</t>
+    <t xml:space="preserve">13.4787216186523</t>
   </si>
   <si>
     <t xml:space="preserve">13.9680461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4520292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210708618164</t>
+    <t xml:space="preserve">13.4520301818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210699081421</t>
   </si>
   <si>
     <t xml:space="preserve">13.7100381851196</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">13.0605688095093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9893932342529</t>
+    <t xml:space="preserve">12.9893941879272</t>
   </si>
   <si>
     <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0160846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449100494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.096155166626</t>
+    <t xml:space="preserve">13.0160837173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0961561203003</t>
   </si>
   <si>
     <t xml:space="preserve">13.5143070220947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1228475570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9804973602295</t>
+    <t xml:space="preserve">13.1228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9804964065552</t>
   </si>
   <si>
     <t xml:space="preserve">12.9271154403687</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">12.7936639785767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8292503356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338773727417</t>
+    <t xml:space="preserve">12.829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338764190674</t>
   </si>
   <si>
     <t xml:space="preserve">12.8737354278564</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">13.1495370864868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2029190063477</t>
+    <t xml:space="preserve">13.2029180526733</t>
   </si>
   <si>
     <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1673307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089645385742</t>
+    <t xml:space="preserve">13.1673316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089635848999</t>
   </si>
   <si>
     <t xml:space="preserve">12.5979337692261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9716005325317</t>
+    <t xml:space="preserve">12.9716014862061</t>
   </si>
   <si>
     <t xml:space="preserve">12.9982900619507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3185777664185</t>
+    <t xml:space="preserve">13.3185768127441</t>
   </si>
   <si>
     <t xml:space="preserve">13.9324598312378</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">14.0570163726807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9947376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502534866333</t>
+    <t xml:space="preserve">13.9947366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502544403076</t>
   </si>
   <si>
     <t xml:space="preserve">13.6388645172119</t>
@@ -284,40 +284,40 @@
     <t xml:space="preserve">13.5676889419556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3452682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2285184860229</t>
+    <t xml:space="preserve">13.3630619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452672958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285194396973</t>
   </si>
   <si>
     <t xml:space="preserve">13.5608043670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4440546035767</t>
+    <t xml:space="preserve">13.4440565109253</t>
   </si>
   <si>
     <t xml:space="preserve">13.2734231948853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4709987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
+    <t xml:space="preserve">13.4709968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967273712158</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4979400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632297515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183259963989</t>
+    <t xml:space="preserve">13.4979391098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632307052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183279037476</t>
   </si>
   <si>
     <t xml:space="preserve">13.668571472168</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7404184341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3003664016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1566724777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7256031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105569839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.860312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6775522232056</t>
+    <t xml:space="preserve">13.7404165267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.300365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1566743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8603115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6775531768799</t>
   </si>
   <si>
     <t xml:space="preserve">13.8571672439575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2253723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321565628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6986598968506</t>
+    <t xml:space="preserve">14.2253732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6986589431763</t>
   </si>
   <si>
     <t xml:space="preserve">13.1476926803589</t>
@@ -371,43 +371,43 @@
     <t xml:space="preserve">12.9950227737427</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6178340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8513317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8782720565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9680805206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9231758117676</t>
+    <t xml:space="preserve">12.6178331375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8513307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8782730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9680786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9231767654419</t>
   </si>
   <si>
     <t xml:space="preserve">13.174635887146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9590997695923</t>
+    <t xml:space="preserve">12.9591007232666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7705059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3452672958374</t>
+    <t xml:space="preserve">12.7705068588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452663421631</t>
   </si>
   <si>
     <t xml:space="preserve">13.8302221298218</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1714897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0637216567993</t>
+    <t xml:space="preserve">14.1714887619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.063720703125</t>
   </si>
   <si>
     <t xml:space="preserve">14.3690633773804</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">13.9559535980225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5069208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6057071685791</t>
+    <t xml:space="preserve">13.5069189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6057062149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.9290113449097</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">14.0277986526489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.018816947937</t>
+    <t xml:space="preserve">14.0188179016113</t>
   </si>
   <si>
     <t xml:space="preserve">13.8481855392456</t>
@@ -440,40 +440,40 @@
     <t xml:space="preserve">14.0457601547241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9918766021729</t>
+    <t xml:space="preserve">13.9918756484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.9200305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7673587799072</t>
+    <t xml:space="preserve">13.7673597335815</t>
   </si>
   <si>
     <t xml:space="preserve">14.0008563995361</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7583770751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6955146789551</t>
+    <t xml:space="preserve">13.7583780288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6955127716064</t>
   </si>
   <si>
     <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248823165894</t>
+    <t xml:space="preserve">13.524881362915</t>
   </si>
   <si>
     <t xml:space="preserve">13.3542490005493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4171133041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5158996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7224559783936</t>
+    <t xml:space="preserve">13.4171123504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159006118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7224569320679</t>
   </si>
   <si>
     <t xml:space="preserve">13.5338621139526</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">14.0098371505737</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0727033615112</t>
+    <t xml:space="preserve">14.0727014541626</t>
   </si>
   <si>
     <t xml:space="preserve">13.4530353546143</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">13.6506090164185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6416301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853202819824</t>
+    <t xml:space="preserve">13.6416292190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853193283081</t>
   </si>
   <si>
     <t xml:space="preserve">13.4799776077271</t>
@@ -512,31 +512,31 @@
     <t xml:space="preserve">13.839204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8930892944336</t>
+    <t xml:space="preserve">14.0996427536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8930883407593</t>
   </si>
   <si>
     <t xml:space="preserve">13.9649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8751249313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7942991256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6236686706543</t>
+    <t xml:space="preserve">13.8751258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7943000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6236696243286</t>
   </si>
   <si>
     <t xml:space="preserve">13.399151802063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3901720046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4889583587646</t>
+    <t xml:space="preserve">13.3901691436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.488959312439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3362874984741</t>
@@ -545,46 +545,46 @@
     <t xml:space="preserve">13.6326494216919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3273067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763404846191</t>
+    <t xml:space="preserve">13.3273057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763385772705</t>
   </si>
   <si>
     <t xml:space="preserve">13.8661451339722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0547389984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6474637985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6384840011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9168844223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0426120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989210128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.548677444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7372713088989</t>
+    <t xml:space="preserve">14.0547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6474647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6384830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9168834686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0426149368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5486764907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7372694015503</t>
   </si>
   <si>
     <t xml:space="preserve">14.7731952667236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8719797134399</t>
+    <t xml:space="preserve">14.8719787597656</t>
   </si>
   <si>
     <t xml:space="preserve">14.7911539077759</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">14.6564455032349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.683385848999</t>
+    <t xml:space="preserve">14.6833877563477</t>
   </si>
   <si>
     <t xml:space="preserve">14.7013492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8450403213501</t>
+    <t xml:space="preserve">14.8450393676758</t>
   </si>
   <si>
     <t xml:space="preserve">15.087516784668</t>
@@ -614,34 +614,34 @@
     <t xml:space="preserve">14.6744060516357</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9528074264526</t>
+    <t xml:space="preserve">14.9528064727783</t>
   </si>
   <si>
     <t xml:space="preserve">15.437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736833572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6892194747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251453399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4826641082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0933513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1651973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2011184692383</t>
+    <t xml:space="preserve">15.4736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6892185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251424789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4826669692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0933494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1651954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2011203765869</t>
   </si>
   <si>
     <t xml:space="preserve">16.1921405792236</t>
@@ -650,34 +650,34 @@
     <t xml:space="preserve">16.246021270752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1113109588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9855794906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137372970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6353368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.931697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766025543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9586458206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406805038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867969512939</t>
+    <t xml:space="preserve">16.1113147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304889678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9855823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137363433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6353359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9317007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.976601600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9586391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867959976196</t>
   </si>
   <si>
     <t xml:space="preserve">16.1741790771484</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">16.0484485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8957777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676237106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0991878509521</t>
+    <t xml:space="preserve">15.8957786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9676208496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831569671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0991859436035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2608375549316</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">17.5122947692871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5661792755127</t>
+    <t xml:space="preserve">17.5661811828613</t>
   </si>
   <si>
     <t xml:space="preserve">17.6559886932373</t>
@@ -725,58 +725,58 @@
     <t xml:space="preserve">17.6021022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8535614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1768646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8805046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0601177215576</t>
+    <t xml:space="preserve">17.8535594940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.006233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1768665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8805065155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.060115814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.0870590209961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2666721343994</t>
+    <t xml:space="preserve">18.3205528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.266674041748</t>
   </si>
   <si>
     <t xml:space="preserve">18.4103603363037</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1678829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2756538391113</t>
+    <t xml:space="preserve">18.1678848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2756519317627</t>
   </si>
   <si>
     <t xml:space="preserve">18.4373073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6169166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9312438964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2276020050049</t>
+    <t xml:space="preserve">18.6169185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9312419891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2276039123535</t>
   </si>
   <si>
     <t xml:space="preserve">19.2365837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.200662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.479061126709</t>
+    <t xml:space="preserve">19.2006607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4790649414062</t>
   </si>
   <si>
     <t xml:space="preserve">19.5598907470703</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">19.209644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3174114227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5329437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610977172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5778465270996</t>
+    <t xml:space="preserve">19.3174095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5329456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6945991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5778484344482</t>
   </si>
   <si>
     <t xml:space="preserve">19.5149841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.188533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310111999512</t>
+    <t xml:space="preserve">20.1885318756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310131072998</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501853942871</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">20.6645107269287</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8351421356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1135444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4759140014648</t>
+    <t xml:space="preserve">20.8351402282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1135425567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4759120941162</t>
   </si>
   <si>
     <t xml:space="preserve">19.7844047546387</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">19.9819793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8742122650146</t>
+    <t xml:space="preserve">19.874210357666</t>
   </si>
   <si>
     <t xml:space="preserve">19.9909610748291</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">19.5509071350098</t>
   </si>
   <si>
-    <t xml:space="preserve">19.650520324707</t>
+    <t xml:space="preserve">19.6505184173584</t>
   </si>
   <si>
     <t xml:space="preserve">19.7229633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6052379608154</t>
+    <t xml:space="preserve">19.6052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">19.4875183105469</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">20.0127391815186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2339611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6324062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7048530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2792377471924</t>
+    <t xml:space="preserve">19.2339649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6324081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7048511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2792415618896</t>
   </si>
   <si>
     <t xml:space="preserve">18.9260730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0075759887695</t>
+    <t xml:space="preserve">19.0075740814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.9713516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0800189971924</t>
+    <t xml:space="preserve">19.0800170898438</t>
   </si>
   <si>
     <t xml:space="preserve">18.5819644927979</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">18.8355178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1252975463867</t>
+    <t xml:space="preserve">19.1252956390381</t>
   </si>
   <si>
     <t xml:space="preserve">19.0437984466553</t>
@@ -908,67 +908,67 @@
     <t xml:space="preserve">19.2249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6142978668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2158508300781</t>
+    <t xml:space="preserve">19.6142921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2158527374268</t>
   </si>
   <si>
     <t xml:space="preserve">19.1524639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.143404006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3245162963867</t>
+    <t xml:space="preserve">19.1434078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3245182037354</t>
   </si>
   <si>
     <t xml:space="preserve">18.944185256958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.373685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5638542175293</t>
+    <t xml:space="preserve">18.3736877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5638523101807</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362972259521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6000785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7359104156494</t>
+    <t xml:space="preserve">18.600076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8083534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7359085083008</t>
   </si>
   <si>
     <t xml:space="preserve">18.609130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1071834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.288293838501</t>
+    <t xml:space="preserve">19.1071853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2882976531982</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4060211181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4512939453125</t>
+    <t xml:space="preserve">19.4060173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4512958526611</t>
   </si>
   <si>
     <t xml:space="preserve">19.4331836700439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2701873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1977424621582</t>
+    <t xml:space="preserve">19.2701835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1977405548096</t>
   </si>
   <si>
     <t xml:space="preserve">20.239128112793</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">20.4655170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5560703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3568496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2572402954102</t>
+    <t xml:space="preserve">20.5560741424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3568477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2572383880615</t>
   </si>
   <si>
     <t xml:space="preserve">20.3930721282959</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">20.329683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3749618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4021263122559</t>
+    <t xml:space="preserve">20.3749599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4021282196045</t>
   </si>
   <si>
     <t xml:space="preserve">20.3477935791016</t>
@@ -1007,19 +1007,19 @@
     <t xml:space="preserve">21.144681930542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.343900680542</t>
+    <t xml:space="preserve">21.5431251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.380126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3438987731934</t>
   </si>
   <si>
     <t xml:space="preserve">21.4254055023193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3710708618164</t>
+    <t xml:space="preserve">21.3710689544678</t>
   </si>
   <si>
     <t xml:space="preserve">21.2805137634277</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">21.2080707550049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8730144500732</t>
+    <t xml:space="preserve">20.8730163574219</t>
   </si>
   <si>
     <t xml:space="preserve">21.2714576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.615571975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8962917327881</t>
+    <t xml:space="preserve">21.6155681610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8962898254395</t>
   </si>
   <si>
     <t xml:space="preserve">21.7423458099365</t>
@@ -1046,67 +1046,67 @@
     <t xml:space="preserve">21.7966785430908</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9959049224854</t>
+    <t xml:space="preserve">21.9959011077881</t>
   </si>
   <si>
     <t xml:space="preserve">22.158899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.430570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3671779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5935668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5030117034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2404003143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.385290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2313442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2132358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.249454498291</t>
+    <t xml:space="preserve">22.4305648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3671798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5935688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6116771697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5030136108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2404022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3852882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2313461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2132339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2494583129883</t>
   </si>
   <si>
     <t xml:space="preserve">21.959680557251</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8238487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0683460235596</t>
+    <t xml:space="preserve">21.8238468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0683479309082</t>
   </si>
   <si>
     <t xml:space="preserve">22.1136245727539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1407890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8419570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7514019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.470682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1498470306396</t>
+    <t xml:space="preserve">22.1407909393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8419589996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7514038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.149845123291</t>
   </si>
   <si>
     <t xml:space="preserve">22.2766246795654</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">22.285680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3490695953369</t>
+    <t xml:space="preserve">22.3490676879883</t>
   </si>
   <si>
     <t xml:space="preserve">22.3943462371826</t>
@@ -1127,16 +1127,16 @@
     <t xml:space="preserve">21.9868469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.439624786377</t>
+    <t xml:space="preserve">22.4396209716797</t>
   </si>
   <si>
     <t xml:space="preserve">22.5573463439941</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3581237792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1226806640625</t>
+    <t xml:space="preserve">22.3581218719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1226825714111</t>
   </si>
   <si>
     <t xml:space="preserve">22.0774021148682</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">22.0049571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9415683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8510112762451</t>
+    <t xml:space="preserve">21.9415702819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8510131835938</t>
   </si>
   <si>
     <t xml:space="preserve">21.7695159912109</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">20.6466255187988</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0631809234619</t>
+    <t xml:space="preserve">21.0631828308105</t>
   </si>
   <si>
     <t xml:space="preserve">21.0088481903076</t>
@@ -1166,67 +1166,67 @@
     <t xml:space="preserve">20.6737957000732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7734031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6556835174561</t>
+    <t xml:space="preserve">20.7734069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6556797027588</t>
   </si>
   <si>
     <t xml:space="preserve">21.0994033813477</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0903511047363</t>
+    <t xml:space="preserve">21.0903491973877</t>
   </si>
   <si>
     <t xml:space="preserve">21.1356239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8277378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8005714416504</t>
+    <t xml:space="preserve">20.8277359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8005695343018</t>
   </si>
   <si>
     <t xml:space="preserve">20.8820705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4344577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4163436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9506244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4667892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5120677947998</t>
+    <t xml:space="preserve">21.4344596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4163475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.950626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4667911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5120697021484</t>
   </si>
   <si>
     <t xml:space="preserve">22.8833446502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290119171143</t>
+    <t xml:space="preserve">22.3219013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290100097656</t>
   </si>
   <si>
     <t xml:space="preserve">22.9014568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8108997344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0916213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546215057373</t>
+    <t xml:space="preserve">22.8109016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0916233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546234130859</t>
   </si>
   <si>
     <t xml:space="preserve">23.6530647277832</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">23.9066200256348</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6168422698975</t>
+    <t xml:space="preserve">23.6168403625488</t>
   </si>
   <si>
     <t xml:space="preserve">23.3632888793945</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1821784973145</t>
+    <t xml:space="preserve">23.1821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">23.6349563598633</t>
@@ -1250,25 +1250,25 @@
     <t xml:space="preserve">23.4900665283203</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5443992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2002868652344</t>
+    <t xml:space="preserve">23.544397354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.200288772583</t>
   </si>
   <si>
     <t xml:space="preserve">22.8199577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7837352752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0372886657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8160629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.341287612915</t>
+    <t xml:space="preserve">22.7837333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0372924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8160648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3412857055664</t>
   </si>
   <si>
     <t xml:space="preserve">24.4861736297607</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">24.2507305145264</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3775100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5042877197266</t>
+    <t xml:space="preserve">24.3775081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5042858123779</t>
   </si>
   <si>
     <t xml:space="preserve">24.5223960876465</t>
@@ -1289,40 +1289,40 @@
     <t xml:space="preserve">24.2869529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1148986816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0333957672119</t>
+    <t xml:space="preserve">24.114896774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0334014892578</t>
   </si>
   <si>
     <t xml:space="preserve">24.2145080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5625114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4628963470459</t>
+    <t xml:space="preserve">23.5625095367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4629001617432</t>
   </si>
   <si>
     <t xml:space="preserve">24.3593978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2908420562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0424537658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6582279205322</t>
+    <t xml:space="preserve">23.290843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0424518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6582298278809</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724529266357</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7630062103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4279537200928</t>
+    <t xml:space="preserve">25.7630081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4279499053955</t>
   </si>
   <si>
     <t xml:space="preserve">25.5637836456299</t>
@@ -1331,37 +1331,37 @@
     <t xml:space="preserve">25.5818958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4641761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.391731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.63623046875</t>
+    <t xml:space="preserve">25.4641742706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3917293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6362266540527</t>
   </si>
   <si>
     <t xml:space="preserve">26.1342849731445</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9893951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3192844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2649517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6996173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728397369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2157821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4059505462646</t>
+    <t xml:space="preserve">25.9893970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3192863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.264949798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.699613571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.215784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4059524536133</t>
   </si>
   <si>
     <t xml:space="preserve">26.5055618286133</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">26.6685600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4874515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8134498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7500610351562</t>
+    <t xml:space="preserve">26.4874477386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8134479522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7500629425049</t>
   </si>
   <si>
     <t xml:space="preserve">26.9583358764648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.465446472168</t>
+    <t xml:space="preserve">27.4654483795166</t>
   </si>
   <si>
     <t xml:space="preserve">27.9453926086426</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">27.5741119384766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7190036773682</t>
+    <t xml:space="preserve">27.7190055847168</t>
   </si>
   <si>
     <t xml:space="preserve">27.6737251281738</t>
@@ -1400,34 +1400,34 @@
     <t xml:space="preserve">27.9182224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9816131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7655544281006</t>
+    <t xml:space="preserve">27.9816112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.765552520752</t>
   </si>
   <si>
     <t xml:space="preserve">29.4304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8108291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.236442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9104442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5624370574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4809379577637</t>
+    <t xml:space="preserve">29.810827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2364444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9104404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5624389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250522613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4809417724609</t>
   </si>
   <si>
     <t xml:space="preserve">31.2053833007812</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">31.9026565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7124919891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0203857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9207706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6180458068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.690486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.962158203125</t>
+    <t xml:space="preserve">31.7124938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0203819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.920768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.618049621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6904907226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9621543884277</t>
   </si>
   <si>
     <t xml:space="preserve">33.4602127075195</t>
@@ -1460,19 +1460,19 @@
     <t xml:space="preserve">33.9039344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4110450744629</t>
+    <t xml:space="preserve">34.4110488891602</t>
   </si>
   <si>
     <t xml:space="preserve">33.0527153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.301097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0345993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0798797607422</t>
+    <t xml:space="preserve">32.3011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0798759460449</t>
   </si>
   <si>
     <t xml:space="preserve">33.3153266906738</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">33.6866035461426</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0759925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.094108581543</t>
+    <t xml:space="preserve">34.0759887695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0941009521484</t>
   </si>
   <si>
     <t xml:space="preserve">34.3929328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2350959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.678825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4416885375977</t>
+    <t xml:space="preserve">35.2351036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4416961669922</t>
   </si>
   <si>
     <t xml:space="preserve">34.4749336242676</t>
@@ -1505,1032 +1505,1032 @@
     <t xml:space="preserve">33.7270622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5023002624512</t>
+    <t xml:space="preserve">34.5022964477539</t>
   </si>
   <si>
     <t xml:space="preserve">35.8065032958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.007152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8671035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1589622497559</t>
+    <t xml:space="preserve">36.0071487426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8671073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1589584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8156242370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8429908752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3354873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7035369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2534027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2748832702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9041900634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4696502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3602066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6546974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3446006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.28076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0892333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4143333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3960876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5146522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1042366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5693740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3504905700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5205307006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9550704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.745304107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2925262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0586318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8397445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.596736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1224784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6241035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.469051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3869667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2410469055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1622009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8853454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6938247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8091430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.401969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2013244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4169769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2651672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3746109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5387725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7303085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6208572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0189170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8215103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4840621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7941474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5784950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.153076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5328941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5055313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1133613586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8365097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2834053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3381271362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3016510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7850227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9824333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.611743927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4202117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5934982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5114212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0827598571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2228050231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.940071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9791946411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9388809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5284652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2001304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529083251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.263973236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4007778167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4555015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7258720397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7988357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6587924957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5708293914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1786518096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5434665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9994831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0906848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5499458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1942501068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9753608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.130407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4522609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0392036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0268421173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0359649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2666168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8138370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4340229034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2060127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9141616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.807954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7682361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3063373565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5128631591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8594398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4822654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3272190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9565238952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6431941986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1721744537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7011547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1448135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3454627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5825881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3851833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5949516296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3636989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.467264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1877708435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6014270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1454105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0600852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0327243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3336944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4066600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6711521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8991584777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.379301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9538822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.880916595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2366142272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9147567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0059623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5987854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7994327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2007274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4437408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6443843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9362335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284130096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8117942810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7753086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6567459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743366241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9668350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9029941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1557197570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9244728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8332710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6964645385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5140609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5778961181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4319801330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9153518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0065536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5264167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1980819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7388248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4410972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7603073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5081748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6084976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9277076721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8638725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8150291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.659984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2163200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2892875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0977592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4260940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1160011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3075256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8729934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6814651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3440093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531303405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2345657348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9185905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1616058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5505409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.404613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9485931396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6873435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1310005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5596618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5911712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.836368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.85866355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2552795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2829513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7848663330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226844787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4382095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5581188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0062370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6649608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290634155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6519012451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6480560302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7679672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7087783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4136276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7864112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5189208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2568206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6811103820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9762649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5112457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6127090454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5204658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5296897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.280647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3544464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0961761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4927978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0408401489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1330718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2253112792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2437553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6403770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9263153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9908790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.963207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6903381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2844886779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4451370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4620380401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343700408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4989376068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2314510345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7571964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.692626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7072410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7479705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5542774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3605766296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.305233001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6465167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3382949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1684226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7349128723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5412101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6242218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6426734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.375186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6372909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4804878234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2760219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9493522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0877113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6080741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7279834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6449699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8478946685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3367481231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1614990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8294448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1376667022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6173000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0139217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.198392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0508136749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6134605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1945514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.803316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5450534820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4251403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0285263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.724142074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6726398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9770240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7740993499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6910877227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9678020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.362117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7441329956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.98779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.439754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5504379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3106155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2291526794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3121643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0907897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0077781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6111602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7218475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.980110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2199249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.819465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5243072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0462188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1476783752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6826515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7787322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6772727966309</t>
   </si>
   <si>
     <t xml:space="preserve">35.8156280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8429832458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3354835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.703540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2931213378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2534027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2748832702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5940933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9041900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4696502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3602066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8221015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6546974182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3446044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2807579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0892333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4143333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3960876464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5146522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1042404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5693702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3504829406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5205345153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9550704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.745304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2925262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0586318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1830825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8397483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5967407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1224784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4690551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3869705200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2410430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8853530883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6938247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8091468811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4019737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2013244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4169692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3746109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5387725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7303009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6208648681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.018913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8215103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4840545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7941436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.578498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.153076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5328979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5055351257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1133575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8365058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2834014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3381309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3016471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.785026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9824371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6117362976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4202079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5934982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5114135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0827560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2228012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.940071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9791984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4593353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9388790130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5284652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2001323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.263973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4007778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4555034637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7258739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7988338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6587905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2698554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5708274841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1786499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5434665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9994831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0906848907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5499439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1942501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1304092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4522609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0392036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0268440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0359630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3519382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2666149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8503189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8138370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.434024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2060127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7317543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9141616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8079528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7682361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.512866973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8594398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4822654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3272190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9565258026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265716552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.643196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1721725463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7011566162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1448135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3454608917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5825881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.385181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5949459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3636989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4672622680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1877727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6014251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1454105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0600852966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0327262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3336982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4066600799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6711483001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8991603851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3792991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9538822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8809185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2366123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.914758682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0059623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.598783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7994289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2007236480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4437408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6443862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9362373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8117923736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7753105163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6567440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9668350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9029922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1557235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9244728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8332710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6964645385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5778999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4319725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.915355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0065536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5264167785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1980857849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2313232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7388286590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4410934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7603034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5081748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6084976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9277114868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8638687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8150253295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6599884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2163238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2892875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0977592468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.426097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1160049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3075294494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8729934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.061279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3440093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.234561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1616020202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5505332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.404613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4443321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9485950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6873435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1310043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5596618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5911712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.836368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2552795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2829475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7848663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.43821144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5581169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1207656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.006233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6649589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7387466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6518974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6480522155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7679672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4136276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7864112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5189247131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2568206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6811103820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9762649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6127052307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5204658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5296897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2806549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3544425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0961799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4927978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0408363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1330757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2253074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2437591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6588249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9263153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9908752441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.963207244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6903305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4451332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4620399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5596580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4989356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2314434051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7571964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6926364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7072372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.747974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5542755126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3605785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.305233001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6465167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3382949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1684265136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7349128723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5412101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6242294311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6426696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3751907348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6372871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4804859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2760219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9493541717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0877075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7279853820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6449718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8478908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3367481231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1614971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8294448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1376686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6172981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0139179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1983947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.050817489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6134586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1945514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.803316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5450496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0285224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.724142074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6726398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9770240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7741012573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6910877227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9678001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.362117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7441329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.98779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5504417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.310619354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2291450500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180099487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3121643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0077781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6111602783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7218437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9801063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2199249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8194694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5243110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0462226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1476821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6826553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7787322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6772689819336</t>
-  </si>
-  <si>
     <t xml:space="preserve">38.1492195129395</t>
   </si>
   <si>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">38.545841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8225517272949</t>
+    <t xml:space="preserve">38.8225479125977</t>
   </si>
   <si>
     <t xml:space="preserve">38.0938758850098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8171730041504</t>
+    <t xml:space="preserve">37.8171691894531</t>
   </si>
   <si>
     <t xml:space="preserve">37.7249336242676</t>
@@ -2558,55 +2558,55 @@
     <t xml:space="preserve">37.3006362915039</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0423774719238</t>
+    <t xml:space="preserve">37.0423736572266</t>
   </si>
   <si>
     <t xml:space="preserve">37.1899566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7157096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6234703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4758949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9593620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4389991760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9778137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1438369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9647521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9462966918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5496826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6326904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3613662719727</t>
+    <t xml:space="preserve">37.7157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6234741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4758911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9593658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4390029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1438407897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9647483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9463005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5496788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6326942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3613700866699</t>
   </si>
   <si>
     <t xml:space="preserve">39.4036483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">39.366756439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.385196685791</t>
+    <t xml:space="preserve">39.3667526245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3852005004883</t>
   </si>
   <si>
     <t xml:space="preserve">38.1399993896484</t>
@@ -2618,16 +2618,16 @@
     <t xml:space="preserve">38.2691307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2084083557129</t>
+    <t xml:space="preserve">37.2084007263184</t>
   </si>
   <si>
     <t xml:space="preserve">37.4021034240723</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8432922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2360763549805</t>
+    <t xml:space="preserve">35.8432998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2360725402832</t>
   </si>
   <si>
     <t xml:space="preserve">36.488956451416</t>
@@ -2642,49 +2642,49 @@
     <t xml:space="preserve">36.8579025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2729682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5166244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7049369812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.649600982666</t>
+    <t xml:space="preserve">37.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5166282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7049407958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6495971679688</t>
   </si>
   <si>
     <t xml:space="preserve">36.2583656311035</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1422920227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2898712158203</t>
+    <t xml:space="preserve">35.1422996520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2898750305176</t>
   </si>
   <si>
     <t xml:space="preserve">36.0093231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2660446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4305267333984</t>
+    <t xml:space="preserve">34.2660484313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4305229187012</t>
   </si>
   <si>
     <t xml:space="preserve">32.4028587341309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9286117553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5227661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4858703613281</t>
+    <t xml:space="preserve">32.9286079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.522762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4858665466309</t>
   </si>
   <si>
     <t xml:space="preserve">31.1023139953613</t>
@@ -2699,22 +2699,22 @@
     <t xml:space="preserve">27.0807838439941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9816188812256</t>
+    <t xml:space="preserve">23.981616973877</t>
   </si>
   <si>
     <t xml:space="preserve">27.3943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2637100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9039878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3651733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.922435760498</t>
+    <t xml:space="preserve">25.2637119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9039897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3651752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9224376678467</t>
   </si>
   <si>
     <t xml:space="preserve">26.9977703094482</t>
@@ -2723,85 +2723,85 @@
     <t xml:space="preserve">26.3797817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9309043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4528160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.729528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.705696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8755626678467</t>
+    <t xml:space="preserve">29.9309062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4528141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7295303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7056980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.875560760498</t>
   </si>
   <si>
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857032775879</t>
+    <t xml:space="preserve">28.6857070922852</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688003540039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1061553955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2998504638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0838661193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6319046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8402118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.513542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8901710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5765628814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5081539154053</t>
+    <t xml:space="preserve">30.1061534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2998523712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.083869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6319065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8402099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5135383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8901672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5765647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5081577301025</t>
   </si>
   <si>
     <t xml:space="preserve">31.7756462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2721824645996</t>
+    <t xml:space="preserve">30.272180557251</t>
   </si>
   <si>
     <t xml:space="preserve">30.770263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9124584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2352848052979</t>
+    <t xml:space="preserve">29.9124603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2352867126465</t>
   </si>
   <si>
     <t xml:space="preserve">29.7833271026611</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2260646820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.414379119873</t>
+    <t xml:space="preserve">30.2260627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4143772125244</t>
   </si>
   <si>
     <t xml:space="preserve">28.7041530609131</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6211414337158</t>
+    <t xml:space="preserve">28.6211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">29.7372093200684</t>
@@ -2813,37 +2813,37 @@
     <t xml:space="preserve">28.8056144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">29.368257522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7979335784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3920936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1630401611328</t>
+    <t xml:space="preserve">29.3682613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7979373931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3920917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1630363464355</t>
   </si>
   <si>
     <t xml:space="preserve">30.8532752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955554962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0339088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3790283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406711578369</t>
+    <t xml:space="preserve">31.0746402740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0339126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.037748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3790264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406730651855</t>
   </si>
   <si>
     <t xml:space="preserve">31.9693431854248</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">33.0577392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0892524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7203044891357</t>
+    <t xml:space="preserve">32.0892562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7203006744385</t>
   </si>
   <si>
     <t xml:space="preserve">32.126148223877</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">31.3974742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6003952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4897079467773</t>
+    <t xml:space="preserve">31.6003932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9601192474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.489709854126</t>
   </si>
   <si>
     <t xml:space="preserve">31.3513565063477</t>
@@ -2891,43 +2891,43 @@
     <t xml:space="preserve">30.6503505706787</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0654220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824085235596</t>
+    <t xml:space="preserve">31.0654258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824047088623</t>
   </si>
   <si>
     <t xml:space="preserve">31.0100746154785</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5950088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0692577362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0969352722168</t>
+    <t xml:space="preserve">30.5950107574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0692596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0969314575195</t>
   </si>
   <si>
     <t xml:space="preserve">29.4236011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5804023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8809432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.327522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0784873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5342884063721</t>
+    <t xml:space="preserve">29.5804042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4881649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8809490203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3275260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0784854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5342864990234</t>
   </si>
   <si>
     <t xml:space="preserve">29.552734375</t>
@@ -2936,31 +2936,31 @@
     <t xml:space="preserve">29.8571128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0046939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5857906341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.884786605835</t>
+    <t xml:space="preserve">30.0046920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5857887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8847885131836</t>
   </si>
   <si>
     <t xml:space="preserve">29.9585762023926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1484355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.794095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1814880371094</t>
+    <t xml:space="preserve">31.1484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7940940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1814918518066</t>
   </si>
   <si>
     <t xml:space="preserve">32.4766464233398</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8878746032715</t>
+    <t xml:space="preserve">33.8878707885742</t>
   </si>
   <si>
     <t xml:space="preserve">34.9854927062988</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">33.66650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4674224853516</t>
+    <t xml:space="preserve">32.4674263000488</t>
   </si>
   <si>
     <t xml:space="preserve">32.0431289672852</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4489822387695</t>
+    <t xml:space="preserve">32.448974609375</t>
   </si>
   <si>
     <t xml:space="preserve">32.2644996643066</t>
@@ -2993,13 +2993,13 @@
     <t xml:space="preserve">33.601936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8509750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.223762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5650444030762</t>
+    <t xml:space="preserve">33.8509826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2237663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5650405883789</t>
   </si>
   <si>
     <t xml:space="preserve">33.9339904785156</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">34.0354537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6057739257812</t>
+    <t xml:space="preserve">32.6057777404785</t>
   </si>
   <si>
     <t xml:space="preserve">33.9432144165039</t>
@@ -3023,22 +3023,22 @@
     <t xml:space="preserve">35.9170837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1276893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1907119750977</t>
+    <t xml:space="preserve">34.127685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1907157897949</t>
   </si>
   <si>
     <t xml:space="preserve">32.3936309814453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.205322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5465927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8840293884277</t>
+    <t xml:space="preserve">33.2053184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5465965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.884033203125</t>
   </si>
   <si>
     <t xml:space="preserve">34.6349906921387</t>
@@ -3047,40 +3047,40 @@
     <t xml:space="preserve">36.5996437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">36.627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3467559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088676452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7195472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8909645080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8725090026855</t>
+    <t xml:space="preserve">36.6273078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3467636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7195510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8909606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">37.6142463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4482154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4536018371582</t>
+    <t xml:space="preserve">37.4482192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4535980224609</t>
   </si>
   <si>
     <t xml:space="preserve">38.7118682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6473045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.241455078125</t>
+    <t xml:space="preserve">38.6473007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2414588928223</t>
   </si>
   <si>
     <t xml:space="preserve">37.8263893127441</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2837333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8463859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5842781066895</t>
+    <t xml:space="preserve">39.2837371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8463821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5842742919922</t>
   </si>
   <si>
     <t xml:space="preserve">41.4144134521484</t>
@@ -3107,52 +3107,52 @@
     <t xml:space="preserve">42.9916687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8533058166504</t>
+    <t xml:space="preserve">42.8533096313477</t>
   </si>
   <si>
     <t xml:space="preserve">43.8863639831543</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1630744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0116500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.928638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1961288452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7349472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8679122924805</t>
+    <t xml:space="preserve">44.1630783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0116539001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9286422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1961250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7349433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8679161071777</t>
   </si>
   <si>
     <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">44.467456817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8694610595703</t>
+    <t xml:space="preserve">44.4674530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.869457244873</t>
   </si>
   <si>
     <t xml:space="preserve">46.3952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">46.247631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1184959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8456268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.864070892334</t>
+    <t xml:space="preserve">46.2476272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1184997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8456230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8640785217285</t>
   </si>
   <si>
     <t xml:space="preserve">44.1077308654785</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">44.3291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2737617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3882827758789</t>
+    <t xml:space="preserve">44.273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3882789611816</t>
   </si>
   <si>
     <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0708312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6742172241211</t>
+    <t xml:space="preserve">44.0708351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6742134094238</t>
   </si>
   <si>
     <t xml:space="preserve">44.6703758239746</t>
@@ -3185,37 +3185,37 @@
     <t xml:space="preserve">44.8917427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7403259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6649971008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5912055969238</t>
+    <t xml:space="preserve">45.7403297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6649932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5912017822266</t>
   </si>
   <si>
     <t xml:space="preserve">44.3567733764648</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7756767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1999702453613</t>
+    <t xml:space="preserve">43.7756805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1999664306641</t>
   </si>
   <si>
     <t xml:space="preserve">44.2091903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1369476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8932876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5758438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0739212036133</t>
+    <t xml:space="preserve">46.1369400024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8932914733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5758399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0739288330078</t>
   </si>
   <si>
     <t xml:space="preserve">47.6496315002441</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">46.6534729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1807708740234</t>
+    <t xml:space="preserve">49.1807670593262</t>
   </si>
   <si>
     <t xml:space="preserve">47.8710021972656</t>
@@ -3251,169 +3251,169 @@
     <t xml:space="preserve">47.0408706665039</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1700019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3175811767578</t>
+    <t xml:space="preserve">47.1699981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3175773620605</t>
   </si>
   <si>
     <t xml:space="preserve">48.1108131408691</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4613189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6865272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6165809631348</t>
+    <t xml:space="preserve">48.4613151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6865310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6165733337402</t>
   </si>
   <si>
     <t xml:space="preserve">45.7034301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.860237121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4136543273926</t>
+    <t xml:space="preserve">45.8602409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4136581420898</t>
   </si>
   <si>
     <t xml:space="preserve">45.7587738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0001373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3360252380371</t>
+    <t xml:space="preserve">48.000129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3360290527344</t>
   </si>
   <si>
     <t xml:space="preserve">47.4467086791992</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8379440307617</t>
+    <t xml:space="preserve">46.837947845459</t>
   </si>
   <si>
     <t xml:space="preserve">46.2107391357422</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6019706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3806076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2276420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4397811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4859046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3898239135742</t>
+    <t xml:space="preserve">45.6019744873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3806037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4397850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4859008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3898277282715</t>
   </si>
   <si>
     <t xml:space="preserve">45.0762176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8417892456055</t>
+    <t xml:space="preserve">45.8417930603027</t>
   </si>
   <si>
     <t xml:space="preserve">45.6573143005371</t>
   </si>
   <si>
-    <t xml:space="preserve">46.450553894043</t>
+    <t xml:space="preserve">46.4505500793457</t>
   </si>
   <si>
     <t xml:space="preserve">46.5981330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">46.524341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5020523071289</t>
+    <t xml:space="preserve">46.5243377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5020561218262</t>
   </si>
   <si>
     <t xml:space="preserve">47.3544731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3214225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2952880859375</t>
+    <t xml:space="preserve">46.321418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2952919006348</t>
   </si>
   <si>
     <t xml:space="preserve">49.346794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9670791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0039749145508</t>
+    <t xml:space="preserve">46.9670753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0039710998535</t>
   </si>
   <si>
     <t xml:space="preserve">47.0593147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4836006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3767585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4282608032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2806816101074</t>
+    <t xml:space="preserve">47.4836044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3767623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4282646179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2806854248047</t>
   </si>
   <si>
     <t xml:space="preserve">47.7234230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">46.985523223877</t>
+    <t xml:space="preserve">46.9855270385742</t>
   </si>
   <si>
     <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9263458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6642379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4244232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1623153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4205856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4902877807617</t>
+    <t xml:space="preserve">47.926342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.664234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4244270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1623191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.420581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.490291595459</t>
   </si>
   <si>
     <t xml:space="preserve">51.1228141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6251182556152</t>
+    <t xml:space="preserve">51.625114440918</t>
   </si>
   <si>
     <t xml:space="preserve">53.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9877815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0621948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4482727050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6343040466309</t>
+    <t xml:space="preserve">53.9877777099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0621910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4482688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6343078613281</t>
   </si>
   <si>
     <t xml:space="preserve">54.1180038452148</t>
@@ -3422,70 +3422,70 @@
     <t xml:space="preserve">54.2296257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1039924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8063316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5784950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8343467712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8715591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.132007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8947563171387</t>
+    <t xml:space="preserve">55.1039962768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8063354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8343505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8715629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1320114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8947525024414</t>
   </si>
   <si>
     <t xml:space="preserve">54.2482261657715</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5086822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.043586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1738128662109</t>
+    <t xml:space="preserve">54.508674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0435829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1738166809082</t>
   </si>
   <si>
     <t xml:space="preserve">54.2110214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">53.225025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6901206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5971031188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0761985778809</t>
+    <t xml:space="preserve">53.2250328063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.597095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0762023925781</t>
   </si>
   <si>
     <t xml:space="preserve">53.4668769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3180465698242</t>
+    <t xml:space="preserve">53.3180503845215</t>
   </si>
   <si>
     <t xml:space="preserve">52.815746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0389938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3366546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4762878417969</t>
+    <t xml:space="preserve">53.038990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3366470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4762840270996</t>
   </si>
   <si>
     <t xml:space="preserve">52.4250717163086</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">53.7273254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3598518371582</t>
+    <t xml:space="preserve">54.3598480224609</t>
   </si>
   <si>
     <t xml:space="preserve">52.7785415649414</t>
@@ -3506,28 +3506,28 @@
     <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1878242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7459297180176</t>
+    <t xml:space="preserve">53.1878204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7459259033203</t>
   </si>
   <si>
     <t xml:space="preserve">54.620304107666</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4388580322266</t>
+    <t xml:space="preserve">55.4388618469238</t>
   </si>
   <si>
     <t xml:space="preserve">55.7551193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4946708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8761520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.950569152832</t>
+    <t xml:space="preserve">55.4946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8761558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9505653381348</t>
   </si>
   <si>
     <t xml:space="preserve">54.6389083862305</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">54.6947174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5272789001465</t>
+    <t xml:space="preserve">54.5272827148438</t>
   </si>
   <si>
     <t xml:space="preserve">55.5876884460449</t>
@@ -3545,10 +3545,10 @@
     <t xml:space="preserve">56.9271507263184</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2992210388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.727108001709</t>
+    <t xml:space="preserve">57.2992248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7271118164062</t>
   </si>
   <si>
     <t xml:space="preserve">57.5596771240234</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">56.4248542785645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8667488098145</t>
+    <t xml:space="preserve">55.8667449951172</t>
   </si>
   <si>
     <t xml:space="preserve">54.3970527648926</t>
@@ -3569,10 +3569,10 @@
     <t xml:space="preserve">50.1554260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8437652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7693519592285</t>
+    <t xml:space="preserve">50.8437614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7693481445312</t>
   </si>
   <si>
     <t xml:space="preserve">50.397274017334</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">50.8065528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4158744812012</t>
+    <t xml:space="preserve">50.4158782958984</t>
   </si>
   <si>
     <t xml:space="preserve">51.0297966003418</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">51.1042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">51.718132019043</t>
+    <t xml:space="preserve">51.7181282043457</t>
   </si>
   <si>
     <t xml:space="preserve">51.4018707275391</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">50.8251571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7879447937012</t>
+    <t xml:space="preserve">50.7879486083984</t>
   </si>
   <si>
     <t xml:space="preserve">48.1648330688477</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">50.0624084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6113204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2438468933105</t>
+    <t xml:space="preserve">48.6113243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2438430786133</t>
   </si>
   <si>
     <t xml:space="preserve">51.7553405761719</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">51.9785842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9831733703613</t>
+    <t xml:space="preserve">52.9831771850586</t>
   </si>
   <si>
     <t xml:space="preserve">52.4994850158691</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">54.4714736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5690879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0341835021973</t>
+    <t xml:space="preserve">55.5690841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0341796875</t>
   </si>
   <si>
     <t xml:space="preserve">56.7597198486328</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">56.3876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9783630371094</t>
+    <t xml:space="preserve">55.9783668518066</t>
   </si>
   <si>
     <t xml:space="preserve">56.9457588195801</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">57.7829208374023</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4386444091797</t>
+    <t xml:space="preserve">59.438648223877</t>
   </si>
   <si>
     <t xml:space="preserve">58.5084648132324</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">63.4012222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4106292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7408981323242</t>
+    <t xml:space="preserve">61.4106254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7409019470215</t>
   </si>
   <si>
     <t xml:space="preserve">61.8199081420898</t>
@@ -3722,28 +3722,28 @@
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.754695892334</t>
+    <t xml:space="preserve">63.7546882629395</t>
   </si>
   <si>
     <t xml:space="preserve">64.3314056396484</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2197875976562</t>
+    <t xml:space="preserve">64.2197799682617</t>
   </si>
   <si>
     <t xml:space="preserve">63.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0663604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593353271484</t>
+    <t xml:space="preserve">63.0663566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593315124512</t>
   </si>
   <si>
     <t xml:space="preserve">61.5408630371094</t>
   </si>
   <si>
-    <t xml:space="preserve">61.9129295349121</t>
+    <t xml:space="preserve">61.9129333496094</t>
   </si>
   <si>
     <t xml:space="preserve">62.3222122192383</t>
@@ -3755,13 +3755,13 @@
     <t xml:space="preserve">60.089771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6060829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0385589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9455337524414</t>
+    <t xml:space="preserve">59.6060791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0385627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9455375671387</t>
   </si>
   <si>
     <t xml:space="preserve">60.5920677185059</t>
@@ -3770,19 +3770,19 @@
     <t xml:space="preserve">61.6896820068359</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4430236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4710426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1547737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4478416442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.629280090332</t>
+    <t xml:space="preserve">64.4430313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4710464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4478340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6292762756348</t>
   </si>
   <si>
     <t xml:space="preserve">58.6758995056152</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">60.182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">58.7503128051758</t>
+    <t xml:space="preserve">58.7503089904785</t>
   </si>
   <si>
     <t xml:space="preserve">58.8061218261719</t>
@@ -3800,49 +3800,49 @@
     <t xml:space="preserve">58.2294082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8573341369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3224220275879</t>
+    <t xml:space="preserve">57.8573379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3224296569824</t>
   </si>
   <si>
     <t xml:space="preserve">58.5642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7549018859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0711669921875</t>
+    <t xml:space="preserve">59.7549057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0711708068848</t>
   </si>
   <si>
     <t xml:space="preserve">59.5502662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">59.810718536377</t>
+    <t xml:space="preserve">59.8107223510742</t>
   </si>
   <si>
     <t xml:space="preserve">60.4618453979492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4154434204102</t>
+    <t xml:space="preserve">60.9269332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4154396057129</t>
   </si>
   <si>
     <t xml:space="preserve">56.9643630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1644058227539</t>
+    <t xml:space="preserve">56.1644020080566</t>
   </si>
   <si>
     <t xml:space="preserve">55.7923316955566</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8807487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8901634216309</t>
+    <t xml:space="preserve">54.8807525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8901596069336</t>
   </si>
   <si>
     <t xml:space="preserve">53.7087211608887</t>
@@ -3851,31 +3851,31 @@
     <t xml:space="preserve">52.6111068725586</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3040390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3412437438965</t>
+    <t xml:space="preserve">54.3040351867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3412475585938</t>
   </si>
   <si>
     <t xml:space="preserve">51.6995315551758</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2716407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3134498596191</t>
+    <t xml:space="preserve">51.2716445922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3134536743164</t>
   </si>
   <si>
     <t xml:space="preserve">52.5366897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5693054199219</t>
+    <t xml:space="preserve">51.5693016052246</t>
   </si>
   <si>
     <t xml:space="preserve">52.4064674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">54.899356842041</t>
+    <t xml:space="preserve">54.8993530273438</t>
   </si>
   <si>
     <t xml:space="preserve">55.271427154541</t>
@@ -3884,16 +3884,16 @@
     <t xml:space="preserve">53.8389511108398</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0993995666504</t>
+    <t xml:space="preserve">54.0993957519531</t>
   </si>
   <si>
     <t xml:space="preserve">51.6437187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6391143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1274108886719</t>
+    <t xml:space="preserve">50.6391181945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1274147033691</t>
   </si>
   <si>
     <t xml:space="preserve">51.2344398498535</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">50.9739875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9181785583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8809661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4624938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8021774291992</t>
+    <t xml:space="preserve">50.9181747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8809700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4624977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.802173614502</t>
   </si>
   <si>
     <t xml:space="preserve">47.1230316162109</t>
@@ -3920,16 +3920,16 @@
     <t xml:space="preserve">44.9464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8768043518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1465606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4954261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.974308013916</t>
+    <t xml:space="preserve">41.8768081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.146556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4954299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9743118286133</t>
   </si>
   <si>
     <t xml:space="preserve">43.9976196289062</t>
@@ -3938,37 +3938,37 @@
     <t xml:space="preserve">44.6208457946777</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6487464904785</t>
+    <t xml:space="preserve">44.6487426757812</t>
   </si>
   <si>
     <t xml:space="preserve">43.2441711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">45.709156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7881660461426</t>
+    <t xml:space="preserve">45.7091522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7881698608398</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2951698303223</t>
+    <t xml:space="preserve">47.1044311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2951736450195</t>
   </si>
   <si>
     <t xml:space="preserve">45.8207740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2021522521973</t>
+    <t xml:space="preserve">46.2021484375</t>
   </si>
   <si>
     <t xml:space="preserve">46.2765655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8717803955078</t>
+    <t xml:space="preserve">48.8717727661133</t>
   </si>
   <si>
     <t xml:space="preserve">47.1974487304688</t>
@@ -3977,13 +3977,13 @@
     <t xml:space="preserve">47.1788444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9275817871094</t>
+    <t xml:space="preserve">48.9275856018066</t>
   </si>
   <si>
     <t xml:space="preserve">49.2810554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9555969238281</t>
+    <t xml:space="preserve">46.9556045532227</t>
   </si>
   <si>
     <t xml:space="preserve">45.9882125854492</t>
@@ -4004,25 +4004,25 @@
     <t xml:space="preserve">47.0300140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1835517883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5881195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5277214050293</t>
+    <t xml:space="preserve">46.1835479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5881233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5277137756348</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8301849365234</t>
+    <t xml:space="preserve">43.8301887512207</t>
   </si>
   <si>
     <t xml:space="preserve">45.430103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2672653198242</t>
+    <t xml:space="preserve">46.267261505127</t>
   </si>
   <si>
     <t xml:space="preserve">46.7695617675781</t>
@@ -4043,10 +4043,10 @@
     <t xml:space="preserve">39.7373847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9095191955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8676109313965</t>
+    <t xml:space="preserve">38.9095268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8676147460938</t>
   </si>
   <si>
     <t xml:space="preserve">41.6163520812988</t>
@@ -4055,19 +4055,19 @@
     <t xml:space="preserve">40.8070907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1930694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2814903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1093521118164</t>
+    <t xml:space="preserve">42.1930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2814865112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1093482971191</t>
   </si>
   <si>
     <t xml:space="preserve">40.6489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0908546447754</t>
+    <t xml:space="preserve">40.0908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">39.3095016479492</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">39.8945198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5640754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6018180847168</t>
+    <t xml:space="preserve">38.5640716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">39.819034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6588172912598</t>
+    <t xml:space="preserve">40.658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">42.3572616577148</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801254272461</t>
+    <t xml:space="preserve">43.4801216125488</t>
   </si>
   <si>
     <t xml:space="preserve">43.234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">42.111930847168</t>
+    <t xml:space="preserve">42.1119346618652</t>
   </si>
   <si>
     <t xml:space="preserve">41.2155303955078</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">37.2147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2145652770996</t>
+    <t xml:space="preserve">36.2145614624023</t>
   </si>
   <si>
     <t xml:space="preserve">37.5166969299316</t>
@@ -4130,13 +4130,13 @@
     <t xml:space="preserve">35.0917015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9690361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9973449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312934875488</t>
+    <t xml:space="preserve">34.9690399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9973487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9312973022461</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4151,25 +4151,25 @@
     <t xml:space="preserve">38.394229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4980239868164</t>
+    <t xml:space="preserve">38.4980201721191</t>
   </si>
   <si>
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3751678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8943290710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0547370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396598815918</t>
+    <t xml:space="preserve">38.0639762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3751640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8943252563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0547332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396560668945</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">40.1587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3474349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.753173828125</t>
+    <t xml:space="preserve">40.3474388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7531776428223</t>
   </si>
   <si>
     <t xml:space="preserve">41.1494789123535</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">39.6586265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7248687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9990882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9239883422852</t>
+    <t xml:space="preserve">40.7248725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9990921020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9239921569824</t>
   </si>
   <si>
     <t xml:space="preserve">45.9806060791016</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5278854370117</t>
+    <t xml:space="preserve">45.3389701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5278816223145</t>
   </si>
   <si>
     <t xml:space="preserve">46.5184440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4995765686035</t>
+    <t xml:space="preserve">46.4995727539062</t>
   </si>
   <si>
     <t xml:space="preserve">45.8579406738281</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">46.7165946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9524917602539</t>
+    <t xml:space="preserve">46.9524879455566</t>
   </si>
   <si>
     <t xml:space="preserve">46.5939331054688</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">46.0089149475098</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7543411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1315803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0273971557617</t>
+    <t xml:space="preserve">46.754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0273933410645</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2163047790527</t>
+    <t xml:space="preserve">45.2163009643555</t>
   </si>
   <si>
     <t xml:space="preserve">45.2729225158691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0460739135742</t>
+    <t xml:space="preserve">43.046070098877</t>
   </si>
   <si>
     <t xml:space="preserve">42.1496734619141</t>
@@ -4280,25 +4280,25 @@
     <t xml:space="preserve">42.3100814819336</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1213684082031</t>
+    <t xml:space="preserve">42.1213645935059</t>
   </si>
   <si>
     <t xml:space="preserve">41.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2251625061035</t>
+    <t xml:space="preserve">42.2251586914062</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1777839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3948097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6967506408691</t>
+    <t xml:space="preserve">41.1777877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3948059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6967544555664</t>
   </si>
   <si>
     <t xml:space="preserve">42.4704895019531</t>
@@ -4307,25 +4307,25 @@
     <t xml:space="preserve">42.998893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7158241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9230194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4891700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8005485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.461051940918</t>
+    <t xml:space="preserve">42.0175743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.923023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4891662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8005523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4610557556152</t>
   </si>
   <si>
     <t xml:space="preserve">39.9511337280273</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">39.2623252868652</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6210746765137</t>
+    <t xml:space="preserve">40.6210784912109</t>
   </si>
   <si>
     <t xml:space="preserve">40.5644645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0645561218262</t>
+    <t xml:space="preserve">41.0645599365234</t>
   </si>
   <si>
     <t xml:space="preserve">39.8095970153809</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703903198242</t>
+    <t xml:space="preserve">41.9703941345215</t>
   </si>
   <si>
     <t xml:space="preserve">41.5174751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8665962219238</t>
+    <t xml:space="preserve">41.8666000366211</t>
   </si>
   <si>
     <t xml:space="preserve">43.0271987915039</t>
@@ -4373,10 +4373,10 @@
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252540588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8009338378906</t>
+    <t xml:space="preserve">42.7252578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8009376525879</t>
   </si>
   <si>
     <t xml:space="preserve">44.0557022094727</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">43.7160186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6690330505371</t>
+    <t xml:space="preserve">44.6690292358398</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4397,31 +4397,31 @@
     <t xml:space="preserve">46.1693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6692276000977</t>
+    <t xml:space="preserve">45.6692237854004</t>
   </si>
   <si>
     <t xml:space="preserve">43.7443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">42.734691619873</t>
+    <t xml:space="preserve">42.7346954345703</t>
   </si>
   <si>
     <t xml:space="preserve">41.2249641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6873207092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0173797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8756484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8290481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9422798156738</t>
+    <t xml:space="preserve">41.6873168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0173835754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8756446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8290519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9422760009766</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7732124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6131896972656</t>
+    <t xml:space="preserve">46.7732086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6131935119629</t>
   </si>
   <si>
     <t xml:space="preserve">47.6129951477051</t>
@@ -4448,22 +4448,22 @@
     <t xml:space="preserve">47.0657196044922</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0185432434082</t>
+    <t xml:space="preserve">47.0185394287109</t>
   </si>
   <si>
     <t xml:space="preserve">45.6314811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6031761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5654335021973</t>
+    <t xml:space="preserve">45.6031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5654296875</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2917938232422</t>
+    <t xml:space="preserve">45.2917900085449</t>
   </si>
   <si>
     <t xml:space="preserve">44.8200035095215</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">45.546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5937385559082</t>
+    <t xml:space="preserve">45.5937347412109</t>
   </si>
   <si>
     <t xml:space="preserve">44.7539520263672</t>
@@ -4484,46 +4484,46 @@
     <t xml:space="preserve">45.7447090148926</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5844955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2544364929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6316757202148</t>
+    <t xml:space="preserve">46.5844917297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2544403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7452926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6316719055176</t>
   </si>
   <si>
     <t xml:space="preserve">46.4146499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7918891906738</t>
+    <t xml:space="preserve">45.7918853759766</t>
   </si>
   <si>
     <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.150447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3861503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6788558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3110466003418</t>
+    <t xml:space="preserve">46.1504516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3861465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6788520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3110504150391</t>
   </si>
   <si>
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5563812255859</t>
+    <t xml:space="preserve">47.8017120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5563850402832</t>
   </si>
   <si>
     <t xml:space="preserve">48.5565757751465</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">49.7077407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9717483520508</t>
+    <t xml:space="preserve">48.971752166748</t>
   </si>
   <si>
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814796447754</t>
+    <t xml:space="preserve">50.4814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">51.8779754638672</t>
@@ -4550,34 +4550,34 @@
     <t xml:space="preserve">52.3497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8781661987305</t>
+    <t xml:space="preserve">52.8781700134277</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9157180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0480117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3310890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1046295166016</t>
+    <t xml:space="preserve">51.915714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0480155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3310852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1046257019043</t>
   </si>
   <si>
     <t xml:space="preserve">53.2555999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5199928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0859489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9727210998535</t>
+    <t xml:space="preserve">54.5199966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0859527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9727172851562</t>
   </si>
   <si>
     <t xml:space="preserve">53.8406181335449</t>
@@ -4586,64 +4586,64 @@
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4446983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1991806030273</t>
+    <t xml:space="preserve">55.4447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1991767883301</t>
   </si>
   <si>
     <t xml:space="preserve">54.0293350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4254455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1987915039062</t>
+    <t xml:space="preserve">53.4254417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.198787689209</t>
   </si>
   <si>
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9349784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8785514831543</t>
+    <t xml:space="preserve">53.5009307861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9349746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">54.444507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.350341796875</t>
+    <t xml:space="preserve">54.4445114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3503456115723</t>
   </si>
   <si>
     <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9729080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.46337890625</t>
+    <t xml:space="preserve">54.9729118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4633827209473</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106544494629</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3316650390625</t>
+    <t xml:space="preserve">54.5388679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3316688537598</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3507308959961</t>
+    <t xml:space="preserve">57.3507347106934</t>
   </si>
   <si>
     <t xml:space="preserve">57.1431465148926</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">56.4071502685547</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8789405822754</t>
+    <t xml:space="preserve">56.8789443969727</t>
   </si>
   <si>
     <t xml:space="preserve">54.8974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0676574707031</t>
+    <t xml:space="preserve">57.0676612854004</t>
   </si>
   <si>
     <t xml:space="preserve">55.2748565673828</t>
@@ -4679,13 +4679,13 @@
     <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5017013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546241760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1433372497559</t>
+    <t xml:space="preserve">57.5017051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1433410644531</t>
   </si>
   <si>
     <t xml:space="preserve">57.2186317443848</t>
@@ -4694,19 +4694,19 @@
     <t xml:space="preserve">57.2752456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9170761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8982009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9550094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1059875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0116271972656</t>
+    <t xml:space="preserve">58.9170722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8981971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9550132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1059837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0116233825684</t>
   </si>
   <si>
     <t xml:space="preserve">60.6155128479004</t>
@@ -4715,22 +4715,22 @@
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417816162109</t>
+    <t xml:space="preserve">59.8417778015137</t>
   </si>
   <si>
     <t xml:space="preserve">59.4266052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0686225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.219596862793</t>
+    <t xml:space="preserve">62.0686264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2196006774902</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8044204711914</t>
+    <t xml:space="preserve">61.8044242858887</t>
   </si>
   <si>
     <t xml:space="preserve">62.2007255554199</t>
@@ -4739,55 +4739,55 @@
     <t xml:space="preserve">63.1443061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4085121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8614311218262</t>
+    <t xml:space="preserve">63.4085006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8614273071289</t>
   </si>
   <si>
     <t xml:space="preserve">63.7293281555176</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9935264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3707695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896369934082</t>
+    <t xml:space="preserve">63.993522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3707733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896331787109</t>
   </si>
   <si>
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5028648376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.993335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4649238586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8987808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0122108459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9178504943848</t>
+    <t xml:space="preserve">63.5028686523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9933395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4649314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8987846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.01220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9178466796875</t>
   </si>
   <si>
     <t xml:space="preserve">61.5024795532227</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5968360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8608474731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7287483215332</t>
+    <t xml:space="preserve">61.5968322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8608436584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7287445068359</t>
   </si>
   <si>
     <t xml:space="preserve">62.1307678222656</t>
@@ -6441,6 +6441,9 @@
   </si>
   <si>
     <t xml:space="preserve">57.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4599990844727</t>
   </si>
 </sst>
 </file>
@@ -30639,7 +30642,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G918" t="s">
-        <v>765</v>
+        <v>710</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30665,7 +30668,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G919" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30691,7 +30694,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G920" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30717,7 +30720,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G921" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30743,7 +30746,7 @@
         <v>33.8600006103516</v>
       </c>
       <c r="G922" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30769,7 +30772,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G923" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -30795,7 +30798,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G924" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30821,7 +30824,7 @@
         <v>35.4599990844727</v>
       </c>
       <c r="G925" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30873,7 +30876,7 @@
         <v>34.4199981689453</v>
       </c>
       <c r="G927" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30925,7 +30928,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G929" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30951,7 +30954,7 @@
         <v>34</v>
       </c>
       <c r="G930" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30977,7 +30980,7 @@
         <v>33.939998626709</v>
       </c>
       <c r="G931" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -31003,7 +31006,7 @@
         <v>34.0900001525879</v>
       </c>
       <c r="G932" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -31029,7 +31032,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G933" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -31081,7 +31084,7 @@
         <v>35.060001373291</v>
       </c>
       <c r="G935" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -31107,7 +31110,7 @@
         <v>35.8600006103516</v>
       </c>
       <c r="G936" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -31133,7 +31136,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G937" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -31159,7 +31162,7 @@
         <v>35.4900016784668</v>
       </c>
       <c r="G938" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -31185,7 +31188,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G939" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -31211,7 +31214,7 @@
         <v>35.3699989318848</v>
       </c>
       <c r="G940" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -31237,7 +31240,7 @@
         <v>35.3899993896484</v>
       </c>
       <c r="G941" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -31263,7 +31266,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G942" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -31289,7 +31292,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G943" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -31315,7 +31318,7 @@
         <v>34.1300010681152</v>
       </c>
       <c r="G944" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -31341,7 +31344,7 @@
         <v>31.7399997711182</v>
       </c>
       <c r="G945" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -31367,7 +31370,7 @@
         <v>32.4700012207031</v>
       </c>
       <c r="G946" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -31393,7 +31396,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G947" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -31419,7 +31422,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G948" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31445,7 +31448,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G949" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31471,7 +31474,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G950" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31497,7 +31500,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G951" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31523,7 +31526,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G952" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31549,7 +31552,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G953" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31575,7 +31578,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G954" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31601,7 +31604,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G955" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31627,7 +31630,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G956" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31653,7 +31656,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31679,7 +31682,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G958" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31705,7 +31708,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G959" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31731,7 +31734,7 @@
         <v>33.189998626709</v>
       </c>
       <c r="G960" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31757,7 +31760,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31783,7 +31786,7 @@
         <v>34.4799995422363</v>
       </c>
       <c r="G962" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31809,7 +31812,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31835,7 +31838,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G964" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31861,7 +31864,7 @@
         <v>33.6399993896484</v>
       </c>
       <c r="G965" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31887,7 +31890,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G966" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31913,7 +31916,7 @@
         <v>32.1699981689453</v>
       </c>
       <c r="G967" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31939,7 +31942,7 @@
         <v>32.5</v>
       </c>
       <c r="G968" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31965,7 +31968,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G969" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31991,7 +31994,7 @@
         <v>32.189998626709</v>
       </c>
       <c r="G970" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -32017,7 +32020,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="G971" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -32043,7 +32046,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G972" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -32069,7 +32072,7 @@
         <v>35.5</v>
       </c>
       <c r="G973" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -32095,7 +32098,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G974" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -32121,7 +32124,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G975" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -32173,7 +32176,7 @@
         <v>35.1699981689453</v>
       </c>
       <c r="G977" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -32199,7 +32202,7 @@
         <v>35.2900009155273</v>
       </c>
       <c r="G978" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -32225,7 +32228,7 @@
         <v>35.0299987792969</v>
       </c>
       <c r="G979" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -32277,7 +32280,7 @@
         <v>37.1100006103516</v>
       </c>
       <c r="G981" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -32303,7 +32306,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G982" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -32329,7 +32332,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -32355,7 +32358,7 @@
         <v>36.9599990844727</v>
       </c>
       <c r="G984" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -32381,7 +32384,7 @@
         <v>36.8699989318848</v>
       </c>
       <c r="G985" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -32407,7 +32410,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G986" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -32433,7 +32436,7 @@
         <v>36.560001373291</v>
       </c>
       <c r="G987" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32459,7 +32462,7 @@
         <v>36.8400001525879</v>
       </c>
       <c r="G988" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32485,7 +32488,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G989" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32511,7 +32514,7 @@
         <v>37.75</v>
       </c>
       <c r="G990" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32537,7 +32540,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G991" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32615,7 +32618,7 @@
         <v>39.0800018310547</v>
       </c>
       <c r="G994" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32641,7 +32644,7 @@
         <v>39.189998626709</v>
       </c>
       <c r="G995" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32667,7 +32670,7 @@
         <v>40.1399993896484</v>
       </c>
       <c r="G996" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32693,7 +32696,7 @@
         <v>39.7700004577637</v>
       </c>
       <c r="G997" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32719,7 +32722,7 @@
         <v>38.7900009155273</v>
       </c>
       <c r="G998" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32745,7 +32748,7 @@
         <v>38.6800003051758</v>
       </c>
       <c r="G999" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32771,7 +32774,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G1000" t="s">
-        <v>502</v>
+        <v>838</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -34045,7 +34048,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G1049" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -34279,7 +34282,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G1058" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -34799,7 +34802,7 @@
         <v>34</v>
       </c>
       <c r="G1078" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -35163,7 +35166,7 @@
         <v>34</v>
       </c>
       <c r="G1092" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -35241,7 +35244,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G1095" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -35319,7 +35322,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1098" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -35345,7 +35348,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1099" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -35631,7 +35634,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1110" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -35917,7 +35920,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1121" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -36203,7 +36206,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1132" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -36229,7 +36232,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1133" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -36385,7 +36388,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1139" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -36957,7 +36960,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G1161" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -37165,7 +37168,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G1169" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -37217,7 +37220,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -37373,7 +37376,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G1177" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -37529,7 +37532,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1183" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -37737,7 +37740,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1191" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -37789,7 +37792,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G1193" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -37971,7 +37974,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G1200" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -38231,7 +38234,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G1210" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -38361,7 +38364,7 @@
         <v>36.9599990844727</v>
       </c>
       <c r="G1215" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -38543,7 +38546,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G1222" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -38699,7 +38702,7 @@
         <v>34.1300010681152</v>
       </c>
       <c r="G1228" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -38725,7 +38728,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G1229" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -71987,7 +71990,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6912037037</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>1077038</v>
@@ -72008,6 +72011,32 @@
         <v>2142</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6911574074</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>920702</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>59.060001373291</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>57.6199989318848</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>58.4599990844727</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>2143</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="2146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="2147">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,55 +47,55 @@
     <t xml:space="preserve">10.9698104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.845253944397</t>
+    <t xml:space="preserve">10.8452548980713</t>
   </si>
   <si>
     <t xml:space="preserve">10.8986358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9876041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573593139648</t>
+    <t xml:space="preserve">10.9876022338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744375228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573612213135</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769306182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1566457748413</t>
+    <t xml:space="preserve">11.4769315719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.156644821167</t>
   </si>
   <si>
     <t xml:space="preserve">11.5481052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349376678467</t>
+    <t xml:space="preserve">11.734938621521</t>
   </si>
   <si>
     <t xml:space="preserve">11.4057559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239088058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1175031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1264009475708</t>
+    <t xml:space="preserve">11.8239068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018453598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1263990402222</t>
   </si>
   <si>
     <t xml:space="preserve">12.0997095108032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7260427474976</t>
+    <t xml:space="preserve">11.7260417938232</t>
   </si>
   <si>
     <t xml:space="preserve">12.0908136367798</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">11.9484634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8950815200806</t>
+    <t xml:space="preserve">11.8950834274292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7616291046143</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9128770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4146528244019</t>
+    <t xml:space="preserve">11.9128761291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4146518707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.2723035812378</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">11.0409851074219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.254508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.672661781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8772897720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110984802246</t>
+    <t xml:space="preserve">11.2545080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6726598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8772878646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111003875732</t>
   </si>
   <si>
     <t xml:space="preserve">12.2509565353394</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">12.2687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4022016525269</t>
+    <t xml:space="preserve">12.4022006988525</t>
   </si>
   <si>
     <t xml:space="preserve">11.7972173690796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1975746154785</t>
+    <t xml:space="preserve">12.1975755691528</t>
   </si>
   <si>
     <t xml:space="preserve">12.7402830123901</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">13.407546043396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.478720664978</t>
+    <t xml:space="preserve">13.4787216186523</t>
   </si>
   <si>
     <t xml:space="preserve">13.9680461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4520301818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210699081421</t>
+    <t xml:space="preserve">13.4520311355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210708618164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7100381851196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363704681396</t>
+    <t xml:space="preserve">13.336371421814</t>
   </si>
   <si>
     <t xml:space="preserve">13.0427742004395</t>
@@ -197,25 +197,25 @@
     <t xml:space="preserve">12.9893941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9004249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0160846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449100494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0961561203003</t>
+    <t xml:space="preserve">12.9004259109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0160856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0961570739746</t>
   </si>
   <si>
     <t xml:space="preserve">13.514307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1228466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9804983139038</t>
+    <t xml:space="preserve">13.1228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9804973602295</t>
   </si>
   <si>
     <t xml:space="preserve">12.927116394043</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">12.589035987854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7936639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8292503356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737363815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1495380401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.202917098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3897542953491</t>
+    <t xml:space="preserve">12.793664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8292512893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1495370864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029190063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
     <t xml:space="preserve">13.1673307418823</t>
@@ -251,100 +251,100 @@
     <t xml:space="preserve">12.6869020462036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5089664459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5979347229004</t>
+    <t xml:space="preserve">12.5089654922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5979337692261</t>
   </si>
   <si>
     <t xml:space="preserve">12.9716014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9982900619507</t>
+    <t xml:space="preserve">12.9982891082764</t>
   </si>
   <si>
     <t xml:space="preserve">13.3185777664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9324607849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570154190063</t>
+    <t xml:space="preserve">13.9324598312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.057014465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9947376251221</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6388654708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.345269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2285184860229</t>
+    <t xml:space="preserve">13.950252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6388635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676889419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3630619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452682495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285194396973</t>
   </si>
   <si>
     <t xml:space="preserve">13.5608043670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.444055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2734231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4620151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4979400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632287979126</t>
+    <t xml:space="preserve">13.4440546035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2734212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967254638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4620161056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4979372024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632297515869</t>
   </si>
   <si>
     <t xml:space="preserve">13.3183259963989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6685724258423</t>
+    <t xml:space="preserve">13.6685705184937</t>
   </si>
   <si>
     <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7404165267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3003644943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1566724777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7256021499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.860312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122625350952</t>
+    <t xml:space="preserve">13.7404174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.300365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1566734313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8603115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122615814209</t>
   </si>
   <si>
     <t xml:space="preserve">13.6775531768799</t>
@@ -365,25 +365,25 @@
     <t xml:space="preserve">12.6986598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1476926803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9950227737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6178350448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8513307571411</t>
+    <t xml:space="preserve">13.1476936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9950218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6178359985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">12.8782720565796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9680795669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9231758117676</t>
+    <t xml:space="preserve">12.9680786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9231767654419</t>
   </si>
   <si>
     <t xml:space="preserve">13.1746349334717</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">12.9591007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9501190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7705068588257</t>
+    <t xml:space="preserve">12.9501180648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7705059051514</t>
   </si>
   <si>
     <t xml:space="preserve">13.3452672958374</t>
@@ -410,43 +410,43 @@
     <t xml:space="preserve">14.063720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3690624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0816822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9559526443481</t>
+    <t xml:space="preserve">14.3690643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0816831588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9559516906738</t>
   </si>
   <si>
     <t xml:space="preserve">13.5069198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6057052612305</t>
+    <t xml:space="preserve">13.6057081222534</t>
   </si>
   <si>
     <t xml:space="preserve">13.9290113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0277976989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0188179016113</t>
+    <t xml:space="preserve">14.0277996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0188188552856</t>
   </si>
   <si>
     <t xml:space="preserve">13.8481855392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0457592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9918766021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9200305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7673597335815</t>
+    <t xml:space="preserve">14.0457601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9918756484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9200296401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7673578262329</t>
   </si>
   <si>
     <t xml:space="preserve">14.0008563995361</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.524881362915</t>
+    <t xml:space="preserve">13.5248804092407</t>
   </si>
   <si>
     <t xml:space="preserve">13.354248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4171123504639</t>
+    <t xml:space="preserve">13.4171133041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159006118774</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">13.7224569320679</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5338611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7044944763184</t>
+    <t xml:space="preserve">13.5338621139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.704496383667</t>
   </si>
   <si>
     <t xml:space="preserve">13.9110498428345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.614688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0098371505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727024078369</t>
+    <t xml:space="preserve">13.6146869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.009838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727005004883</t>
   </si>
   <si>
     <t xml:space="preserve">13.4530363082886</t>
@@ -500,151 +500,151 @@
     <t xml:space="preserve">13.6506099700928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6416292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4799795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.839204788208</t>
+    <t xml:space="preserve">13.6416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853193283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4799785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8392038345337</t>
   </si>
   <si>
     <t xml:space="preserve">14.0996427536011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8930883407593</t>
+    <t xml:space="preserve">13.8930892944336</t>
   </si>
   <si>
     <t xml:space="preserve">13.9649333953857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8751258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7943019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6236696243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3991498947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3901700973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4889602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6326503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3273048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763395309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8661460876465</t>
+    <t xml:space="preserve">13.8751277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.79430103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6236686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.399151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3901710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4889583587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6326484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3273067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8661470413208</t>
   </si>
   <si>
     <t xml:space="preserve">14.0547409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6474628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6384840011597</t>
+    <t xml:space="preserve">14.6474637985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6384830474854</t>
   </si>
   <si>
     <t xml:space="preserve">14.9168844223022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0964984893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.04261302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989238739014</t>
+    <t xml:space="preserve">15.0964956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0426149368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989229202271</t>
   </si>
   <si>
     <t xml:space="preserve">14.5486764907837</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7372703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8719806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911539077759</t>
+    <t xml:space="preserve">14.7372713088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.773193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8719797134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911520004272</t>
   </si>
   <si>
     <t xml:space="preserve">14.6564455032349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6833877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013502120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0875158309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9707689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7103281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6744070053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9528074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377641677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736843109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6892232894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251453399658</t>
+    <t xml:space="preserve">14.683388710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013483047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8450384140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9707679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7103290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6744050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.952808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6892185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251415252686</t>
   </si>
   <si>
     <t xml:space="preserve">15.482666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0933475494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1651973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2011203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.192138671875</t>
+    <t xml:space="preserve">15.7790279388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0933532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1651935577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2011184692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1921405792236</t>
   </si>
   <si>
     <t xml:space="preserve">16.2460231781006</t>
@@ -653,58 +653,58 @@
     <t xml:space="preserve">16.1113128662109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9855813980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137372970581</t>
+    <t xml:space="preserve">16.0304851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9855833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137363433838</t>
   </si>
   <si>
     <t xml:space="preserve">15.6353368759155</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9316997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766044616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.958643913269</t>
+    <t xml:space="preserve">15.9316987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9766035079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9586410522461</t>
   </si>
   <si>
     <t xml:space="preserve">15.9406805038452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8867969512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1741790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1023330688477</t>
+    <t xml:space="preserve">15.8867959976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1741771697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1023349761963</t>
   </si>
   <si>
     <t xml:space="preserve">16.0484485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8957777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676198959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0991840362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.260835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1620502471924</t>
+    <t xml:space="preserve">15.8957757949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.967622756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0991859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2608375549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.162052154541</t>
   </si>
   <si>
     <t xml:space="preserve">17.296760559082</t>
@@ -713,118 +713,118 @@
     <t xml:space="preserve">17.3326816558838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5122947692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5661792755127</t>
+    <t xml:space="preserve">17.5122966766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5661811828613</t>
   </si>
   <si>
     <t xml:space="preserve">17.6559867858887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6021003723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8535594940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062313079834</t>
+    <t xml:space="preserve">17.6021041870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8535633087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062351226807</t>
   </si>
   <si>
     <t xml:space="preserve">18.1768646240234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8805065155029</t>
+    <t xml:space="preserve">17.880500793457</t>
   </si>
   <si>
     <t xml:space="preserve">18.0601177215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0870590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2666702270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4103603363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2756500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4373073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169185638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9312438964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2276020050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2365837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2006645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4790649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5598907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1108551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2096405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3174076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5329456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.69460105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4611015319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5778465270996</t>
+    <t xml:space="preserve">18.0870552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4103622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678829193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2756538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4373054504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9312400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2276039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2365818023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2006607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4790630340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1108570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2096424102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3174095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5329475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5778484344482</t>
   </si>
   <si>
     <t xml:space="preserve">19.5149841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.188533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3501853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6645107269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8351421356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1135425567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4759140014648</t>
+    <t xml:space="preserve">20.1885318756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310111999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3501892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6645088195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8351402282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.11354637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4759120941162</t>
   </si>
   <si>
     <t xml:space="preserve">19.7844066619873</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">19.8921718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9819793701172</t>
+    <t xml:space="preserve">19.9819774627686</t>
   </si>
   <si>
     <t xml:space="preserve">19.8742122650146</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9909572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3892555236816</t>
+    <t xml:space="preserve">19.9909591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.389253616333</t>
   </si>
   <si>
     <t xml:space="preserve">19.5509090423584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.650520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229633331299</t>
+    <t xml:space="preserve">19.6505184173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229614257812</t>
   </si>
   <si>
     <t xml:space="preserve">19.6052398681641</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">20.0127391815186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2339630126953</t>
+    <t xml:space="preserve">19.2339649200439</t>
   </si>
   <si>
     <t xml:space="preserve">19.6324081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7048530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2792434692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9260730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0075759887695</t>
+    <t xml:space="preserve">19.7048511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2792377471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9260749816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0075740814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.9713516235352</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">19.0800189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5819664001465</t>
+    <t xml:space="preserve">18.5819644927979</t>
   </si>
   <si>
     <t xml:space="preserve">18.8355178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1252937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0437984466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3426284790039</t>
+    <t xml:space="preserve">19.1252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0437965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3426303863525</t>
   </si>
   <si>
     <t xml:space="preserve">19.2249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6142921447754</t>
+    <t xml:space="preserve">19.614294052124</t>
   </si>
   <si>
     <t xml:space="preserve">19.2158527374268</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">18.9441871643066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3736877441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5638542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6362991333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.600076675415</t>
+    <t xml:space="preserve">18.373685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5638523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6362972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6000785827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.8083534240723</t>
@@ -944,31 +944,31 @@
     <t xml:space="preserve">18.7359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.609130859375</t>
+    <t xml:space="preserve">18.6091289520264</t>
   </si>
   <si>
     <t xml:space="preserve">19.1071853637695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2882976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3788509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4060173034668</t>
+    <t xml:space="preserve">19.2882957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.378849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4060192108154</t>
   </si>
   <si>
     <t xml:space="preserve">19.4512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4331855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2701835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1977367401123</t>
+    <t xml:space="preserve">19.4331836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2701873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1977424621582</t>
   </si>
   <si>
     <t xml:space="preserve">20.2391262054443</t>
@@ -980,79 +980,79 @@
     <t xml:space="preserve">20.5560722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2572402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3930721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.329683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3749618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4021282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3477935791016</t>
+    <t xml:space="preserve">20.3568477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2572383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3930702209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3296871185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3749599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4021263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3477954864502</t>
   </si>
   <si>
     <t xml:space="preserve">20.8458499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.144681930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5431251525879</t>
+    <t xml:space="preserve">21.1446800231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5431270599365</t>
   </si>
   <si>
     <t xml:space="preserve">21.380126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.343900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4254035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3710689544678</t>
+    <t xml:space="preserve">21.3439025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4254055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3710708618164</t>
   </si>
   <si>
     <t xml:space="preserve">21.2805137634277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2080688476562</t>
+    <t xml:space="preserve">21.2080707550049</t>
   </si>
   <si>
     <t xml:space="preserve">20.8730163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2714557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8962898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7423477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7966804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9959011077881</t>
+    <t xml:space="preserve">21.2714595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.615571975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8962917327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7423458099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7966785430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9959030151367</t>
   </si>
   <si>
     <t xml:space="preserve">22.158899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4305686950684</t>
+    <t xml:space="preserve">22.430570602417</t>
   </si>
   <si>
     <t xml:space="preserve">22.3671798706055</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">22.5935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6116790771484</t>
+    <t xml:space="preserve">22.6116771697998</t>
   </si>
   <si>
     <t xml:space="preserve">22.5030136108398</t>
@@ -1070,31 +1070,31 @@
     <t xml:space="preserve">22.2404022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3852882385254</t>
+    <t xml:space="preserve">22.385290145874</t>
   </si>
   <si>
     <t xml:space="preserve">22.2313461303711</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2132339477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2494583129883</t>
+    <t xml:space="preserve">22.2132377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2494564056396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9596786499023</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8238468170166</t>
+    <t xml:space="preserve">21.8238487243652</t>
   </si>
   <si>
     <t xml:space="preserve">22.0683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1136264801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1407890319824</t>
+    <t xml:space="preserve">22.1136245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1407909393311</t>
   </si>
   <si>
     <t xml:space="preserve">21.8419570922852</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">21.7514019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.470682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1498470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0592918395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.285680770874</t>
+    <t xml:space="preserve">21.4706783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1498432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2766265869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.059289932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2856788635254</t>
   </si>
   <si>
     <t xml:space="preserve">22.3490676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3943462371826</t>
+    <t xml:space="preserve">22.394344329834</t>
   </si>
   <si>
     <t xml:space="preserve">21.9868469238281</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">22.5573444366455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3581256866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1226806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0774021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0049591064453</t>
+    <t xml:space="preserve">22.3581237792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1226825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0774002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0049571990967</t>
   </si>
   <si>
     <t xml:space="preserve">21.9415683746338</t>
@@ -1154,172 +1154,172 @@
     <t xml:space="preserve">21.7695140838623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6466255187988</t>
+    <t xml:space="preserve">20.6466236114502</t>
   </si>
   <si>
     <t xml:space="preserve">21.0631809234619</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0088481903076</t>
+    <t xml:space="preserve">21.008846282959</t>
   </si>
   <si>
     <t xml:space="preserve">20.6737957000732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7734050750732</t>
+    <t xml:space="preserve">20.7734069824219</t>
   </si>
   <si>
     <t xml:space="preserve">20.6556816101074</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0994052886963</t>
+    <t xml:space="preserve">21.0994033813477</t>
   </si>
   <si>
     <t xml:space="preserve">21.0903491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1356258392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8277378082275</t>
+    <t xml:space="preserve">21.1356296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8277416229248</t>
   </si>
   <si>
     <t xml:space="preserve">20.8549041748047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8005714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8820686340332</t>
+    <t xml:space="preserve">20.8005695343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8820705413818</t>
   </si>
   <si>
     <t xml:space="preserve">21.4344577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163455963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.950626373291</t>
+    <t xml:space="preserve">21.4163475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9506225585938</t>
   </si>
   <si>
     <t xml:space="preserve">22.4667911529541</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5120658874512</t>
+    <t xml:space="preserve">22.5120697021484</t>
   </si>
   <si>
     <t xml:space="preserve">22.8833446502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3219032287598</t>
+    <t xml:space="preserve">22.3219013214111</t>
   </si>
   <si>
     <t xml:space="preserve">22.8290100097656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9014568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8109016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6530666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9066200256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6168441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1821765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6349582672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4900665283203</t>
+    <t xml:space="preserve">22.9014549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.810905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0916213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6530685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9066219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6168460845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1821746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6349544525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4900646209717</t>
   </si>
   <si>
     <t xml:space="preserve">23.5443992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.200288772583</t>
+    <t xml:space="preserve">23.2002906799316</t>
   </si>
   <si>
     <t xml:space="preserve">22.8199577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7837352752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0372905731201</t>
+    <t xml:space="preserve">22.7837333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0372886657715</t>
   </si>
   <si>
     <t xml:space="preserve">23.8160629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.341287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2507305145264</t>
+    <t xml:space="preserve">24.3412857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4861736297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.250732421875</t>
   </si>
   <si>
     <t xml:space="preserve">24.3775081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5042858123779</t>
+    <t xml:space="preserve">24.5042839050293</t>
   </si>
   <si>
     <t xml:space="preserve">24.5223960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2869529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0333976745605</t>
+    <t xml:space="preserve">24.2869510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1148986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0333995819092</t>
   </si>
   <si>
     <t xml:space="preserve">24.2145080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5625133514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4628982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3593978881836</t>
+    <t xml:space="preserve">23.5625095367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4629020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.359395980835</t>
   </si>
   <si>
     <t xml:space="preserve">23.290843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0424518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6582279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6724529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7630062103271</t>
+    <t xml:space="preserve">24.0424537658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6582298278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6724510192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7630081176758</t>
   </si>
   <si>
     <t xml:space="preserve">25.4279499053955</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">25.5637836456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5818958282471</t>
+    <t xml:space="preserve">25.5818920135498</t>
   </si>
   <si>
     <t xml:space="preserve">25.4641742706299</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">25.3917293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6362266540527</t>
+    <t xml:space="preserve">25.63623046875</t>
   </si>
   <si>
     <t xml:space="preserve">26.1342849731445</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">25.9893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3192863464355</t>
+    <t xml:space="preserve">25.3192806243896</t>
   </si>
   <si>
     <t xml:space="preserve">25.2649517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">25.699613571167</t>
+    <t xml:space="preserve">25.6996154785156</t>
   </si>
   <si>
     <t xml:space="preserve">25.5728397369385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2157821655273</t>
+    <t xml:space="preserve">26.215784072876</t>
   </si>
   <si>
     <t xml:space="preserve">26.4059505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5055618286133</t>
+    <t xml:space="preserve">26.5055599212646</t>
   </si>
   <si>
     <t xml:space="preserve">26.6685600280762</t>
@@ -1382,70 +1382,70 @@
     <t xml:space="preserve">26.9583358764648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4654483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9453907012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5741119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7190055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6737251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9182224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9816112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.765552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4304981231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8108310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2364444732666</t>
+    <t xml:space="preserve">27.465446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9453945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5741138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7190017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6737270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7655563354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4305000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8108291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549434661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2364406585693</t>
   </si>
   <si>
     <t xml:space="preserve">29.9104404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5624408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4809417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2053833007812</t>
+    <t xml:space="preserve">30.5624389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250522613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4809398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2053852081299</t>
   </si>
   <si>
     <t xml:space="preserve">31.9026565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.712495803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.020378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9207744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6180458068848</t>
+    <t xml:space="preserve">31.7124900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0203819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.618049621582</t>
   </si>
   <si>
     <t xml:space="preserve">32.6904907226562</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">33.4602165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9039344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0527191162109</t>
+    <t xml:space="preserve">33.9039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0527153015137</t>
   </si>
   <si>
     <t xml:space="preserve">32.3011016845703</t>
@@ -1472,31 +1472,31 @@
     <t xml:space="preserve">33.0346069335938</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0798759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3153266906738</t>
+    <t xml:space="preserve">33.0798797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3153305053711</t>
   </si>
   <si>
     <t xml:space="preserve">33.6865997314453</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0759887695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0941009521484</t>
+    <t xml:space="preserve">34.0759925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">34.3929328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2350997924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6788215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4416885375977</t>
+    <t xml:space="preserve">35.2351036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4416961669922</t>
   </si>
   <si>
     <t xml:space="preserve">34.4749336242676</t>
@@ -1511,1069 +1511,1069 @@
     <t xml:space="preserve">35.8065032958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0071487426758</t>
+    <t xml:space="preserve">36.007152557373</t>
   </si>
   <si>
     <t xml:space="preserve">34.8671112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1589622497559</t>
+    <t xml:space="preserve">35.1589584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8156242370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8429908752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3354835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.703540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2931251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2534027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5940933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9041862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4696502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3602066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6546974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3446083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.28076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0892333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4143333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3960914611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5146522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1042404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5693778991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3504867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5205307006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9550704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7453079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2925262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0586357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8397483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1224746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.624095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.469051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3869667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2410430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1621971130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8853492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6938209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8091468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4019737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2013244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4169692993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2651672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3746109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5387763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7303009033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6208572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.018913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8215065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4840545654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7941474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5784912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1530799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5328903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5055351257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.113353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8365058898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2834091186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3381271362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3016471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.785026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9824333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6117362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4202079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5934982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5114135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0827560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2228012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9400749206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9791984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300304412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9388809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5284652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2001304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529083251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2639713287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4007797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4555015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7258701324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7988357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6587905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5708255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1786518096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9994812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0906867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5499439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1942462921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.97536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1304092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.692626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.452262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0392036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0268440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0359630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3519382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2666149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.813835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4340209960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2060127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9141578674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483787536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7682361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3063354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5128650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8594398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4822654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.327220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265735626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6431922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.172176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7011547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1448135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3454608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5825881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.385181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.59494972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3637008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.467264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1877689361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6014270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1454105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0600872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0327243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3336982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4066581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6711502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8991603851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3792991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9538803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.880916595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9147567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0059604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5987796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7994327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2007274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4437408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6443824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9362354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023448944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284111022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8117923736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7753105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6567478179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743366241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9668388366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9029922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1557235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9244689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8332672119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6964645385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5140609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5779037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4319763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9153518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0065536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5264129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1980857849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7388248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4410934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7603073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5081787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6084976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1283569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9277114868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8638763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8150291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6599884033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2163200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2892913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0977630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4260940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1160011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3075294494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.872989654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6814613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0612754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3440093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531303405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2345657348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.918586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1616058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5505409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4046096801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9485969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6873474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1310005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5596580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5911674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8363723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8586597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2552795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2829475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7848701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4382076263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5581188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0062408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6649608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387504577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6518898010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6480560302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7679634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4136199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7864112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5189208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2568206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6811103820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9762687683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5112419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6127052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5204620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5296897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2806510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3544425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0961761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4927978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0408363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1330757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2253112792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2437553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6403732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9263114929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9908714294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.963207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6903343200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2844886779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4451332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4620418548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343738555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5596618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4989337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2314472198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7571964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6926345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7072372436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7479705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5542774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3605785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3052368164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6465129852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3382873535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1684188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7349090576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5412101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6242218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6426696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3751831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6372871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4804840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2760219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9493541717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0877075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6080741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7279815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6449699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8478927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3367500305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1614990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8294429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1376647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6173000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.198392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0508155822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6134586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1945533752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.803316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5450534820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4251480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0285243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7241458892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6726398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9770240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7741031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6910877227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9678001403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3621215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7441329956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.98779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4397506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5504379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.310619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2291526794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0907974243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0077781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6111602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7218475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9801139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2199211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.819465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5243110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0462188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1476745605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0239334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6826515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7787322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6772689819336</t>
   </si>
   <si>
     <t xml:space="preserve">35.8156280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8429832458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3354873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.703540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2931251525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2533988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2748832702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5940933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9041900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4696464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3602066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8221054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6546974182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.344596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.28076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0892372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4143333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3960914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5146522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1042404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5693740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3504867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5205307006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9550704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.745304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2925224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0586318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1830825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8397483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.596736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1224784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.469051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3869667053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2410469055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8853492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6938247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8091430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4019737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2013244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4169769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3746109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5387763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7303047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6208610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.018913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8215103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7941436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.578498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1530799865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5328941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5055274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1133613586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8365058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2834053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3381309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3016471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.785026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9824333190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.611743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4202079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5934982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.511417388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0827560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2228050231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.940071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9791984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9388790130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5284633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2001304626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.263973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4007778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4555015563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7258720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7988338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6587905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2698516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5708274841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1786499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5434665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9994831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0906867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5499439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1942481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1304092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4522609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0392036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0268440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0359649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2666168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8503170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8138389587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4340229034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2060127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7317543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9141616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8079566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.768238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5128631591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8594398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4822692871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3272190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.956521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265716552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.643196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1721725463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7011547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1448154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3454627990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5825881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.385181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.59494972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3636989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.467264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1877727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.935640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6014270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1454105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0600852966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0327243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3336963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4066581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6711521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8991603851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.379301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9538803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8809185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2366142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9147605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0059604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5987854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7994289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4437408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6443843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9362373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284111022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8117923736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7753067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6567440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9668350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9029922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1557235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9244728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8332672119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6964645385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5779037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4319801330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9153594970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0065536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5264205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1980857849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2313232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7388286590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4410934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7603034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5081748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6085014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9277076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8638687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8150291442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.659984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2163238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2892875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0977592468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.426097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1160011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3075256347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.872989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6814575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0612831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3440132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.234561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9185905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1616058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.550537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.404613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4443283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9485988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6873435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1310005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5596618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5911750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.836368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2552795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2829475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7848663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382076263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5581188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1207637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0062370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6649627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7387504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290634155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6519012451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6480560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7679672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4136276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7864151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5189247131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2568206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6811065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9762649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6127014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5204658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5296897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2806510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3544464111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0961799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4927978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0408325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1330757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2253112792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2437553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6588172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9263114929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9908790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.963207244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6903343200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2844886779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4451370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4620399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5596580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4989356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7571964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6926288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7072372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7479705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5542774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.36057472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3052368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6465167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3382911682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0761871337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1684226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7349128723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5412063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6242218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6426734924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3751831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6372909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4804821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2760219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9493541717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0877056121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7279834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8478927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3367500305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1615009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8294448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1376686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6173000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0139179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1983947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0508155822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6134567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1945495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8033123016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5450534820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0285263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.724142074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6726398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9770221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7741012573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.691089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9678001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3621215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7441329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9877891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4397506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5504379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.310619354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2291488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3121643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0077743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6111602783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7218475341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9801063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2199211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.819465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5243110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0462188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1476783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6826553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7787322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6772727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8156318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1492233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9240112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5458450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8225517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0938758850098</t>
+    <t xml:space="preserve">38.1492195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9240074157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.545841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8225479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.093879699707</t>
   </si>
   <si>
     <t xml:space="preserve">37.8171691894531</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1530609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3006362915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0423812866211</t>
+    <t xml:space="preserve">37.7249298095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1530570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3006401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0423736572266</t>
   </si>
   <si>
     <t xml:space="preserve">37.1899566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7157096862793</t>
+    <t xml:space="preserve">37.715705871582</t>
   </si>
   <si>
     <t xml:space="preserve">37.6234703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">37.475887298584</t>
+    <t xml:space="preserve">37.4758949279785</t>
   </si>
   <si>
     <t xml:space="preserve">36.9593658447266</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">36.9778099060059</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1438407897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9647483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9462966918945</t>
+    <t xml:space="preserve">37.1438369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9647521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9463005065918</t>
   </si>
   <si>
     <t xml:space="preserve">37.5496788024902</t>
@@ -2609,25 +2609,25 @@
     <t xml:space="preserve">39.3667488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3851928710938</t>
+    <t xml:space="preserve">39.3852005004883</t>
   </si>
   <si>
     <t xml:space="preserve">38.1399955749512</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2914199829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2691268920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2084045410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4021034240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8432960510254</t>
+    <t xml:space="preserve">37.2914161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2691307067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2084007263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.402099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8432998657227</t>
   </si>
   <si>
     <t xml:space="preserve">37.2360725402832</t>
@@ -2636,34 +2636,34 @@
     <t xml:space="preserve">36.488956451416</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9724235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3690452575684</t>
+    <t xml:space="preserve">35.9724273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3690490722656</t>
   </si>
   <si>
     <t xml:space="preserve">36.8579025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2729682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5166282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7049407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457633972168</t>
+    <t xml:space="preserve">37.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5166244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457595825195</t>
   </si>
   <si>
     <t xml:space="preserve">35.649600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2583656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1422996520996</t>
+    <t xml:space="preserve">36.2583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1422958374023</t>
   </si>
   <si>
     <t xml:space="preserve">35.2898750305176</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">36.0093231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2660446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4305305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4028587341309</t>
+    <t xml:space="preserve">34.266040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4028625488281</t>
   </si>
   <si>
     <t xml:space="preserve">32.9286079406738</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">32.4858741760254</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1023120880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1507301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8002281188965</t>
+    <t xml:space="preserve">31.10231590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1507320404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8002300262451</t>
   </si>
   <si>
     <t xml:space="preserve">27.0807819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9816188812256</t>
+    <t xml:space="preserve">23.9816207885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.3943881988525</t>
@@ -2711,19 +2711,19 @@
     <t xml:space="preserve">25.2637119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9039897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3651733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.922435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9977684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3797817230225</t>
+    <t xml:space="preserve">24.9039916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3651752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9224376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9977703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3797798156738</t>
   </si>
   <si>
     <t xml:space="preserve">29.9309043884277</t>
@@ -2732,52 +2732,52 @@
     <t xml:space="preserve">31.4528160095215</t>
   </si>
   <si>
-    <t xml:space="preserve">31.729528427124</t>
+    <t xml:space="preserve">31.7295265197754</t>
   </si>
   <si>
     <t xml:space="preserve">30.7056980133057</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8755626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5158405303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6857051849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6688041687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1061534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2998504638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6319065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8402080535889</t>
+    <t xml:space="preserve">29.875560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5158386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6857032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6688003540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1061553955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2998561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.083869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6319046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8402099609375</t>
   </si>
   <si>
     <t xml:space="preserve">32.513542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8901672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.576566696167</t>
+    <t xml:space="preserve">30.8901748657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5765647888184</t>
   </si>
   <si>
     <t xml:space="preserve">31.5081577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7756423950195</t>
+    <t xml:space="preserve">31.7756481170654</t>
   </si>
   <si>
     <t xml:space="preserve">30.2721824645996</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">30.770263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9124603271484</t>
+    <t xml:space="preserve">29.9124565124512</t>
   </si>
   <si>
     <t xml:space="preserve">30.2352867126465</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">29.7833271026611</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2260627746582</t>
+    <t xml:space="preserve">30.2260646820068</t>
   </si>
   <si>
     <t xml:space="preserve">29.4143772125244</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">28.7041530609131</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6211395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7372074127197</t>
+    <t xml:space="preserve">28.6211414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7372093200684</t>
   </si>
   <si>
     <t xml:space="preserve">29.8663387298584</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">28.8056144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3682594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7979354858398</t>
+    <t xml:space="preserve">29.3682632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7979335784912</t>
   </si>
   <si>
     <t xml:space="preserve">30.39208984375</t>
@@ -2834,49 +2834,49 @@
     <t xml:space="preserve">31.0746440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8955554962158</t>
+    <t xml:space="preserve">31.8955574035645</t>
   </si>
   <si>
     <t xml:space="preserve">32.0339088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">31.037748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3790283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9693431854248</t>
+    <t xml:space="preserve">31.0377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3790264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406730651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9693470001221</t>
   </si>
   <si>
     <t xml:space="preserve">32.4950904846191</t>
   </si>
   <si>
-    <t xml:space="preserve">32.762580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0577430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0892562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7203044891357</t>
+    <t xml:space="preserve">32.7625846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0577392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0892524719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7203006744385</t>
   </si>
   <si>
     <t xml:space="preserve">32.126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3974704742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6003952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508934020996</t>
+    <t xml:space="preserve">31.3974723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6003932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508972167969</t>
   </si>
   <si>
     <t xml:space="preserve">31.2591190338135</t>
@@ -2888,31 +2888,31 @@
     <t xml:space="preserve">31.4897079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3513526916504</t>
+    <t xml:space="preserve">31.3513584136963</t>
   </si>
   <si>
     <t xml:space="preserve">30.650354385376</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0654220581055</t>
+    <t xml:space="preserve">31.0654201507568</t>
   </si>
   <si>
     <t xml:space="preserve">30.9824066162109</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0100784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.595006942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0692615509033</t>
+    <t xml:space="preserve">31.0100746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5950088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0692596435547</t>
   </si>
   <si>
     <t xml:space="preserve">30.0969314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4236030578613</t>
+    <t xml:space="preserve">29.4236011505127</t>
   </si>
   <si>
     <t xml:space="preserve">29.5804042816162</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">29.4881649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8809490203857</t>
+    <t xml:space="preserve">30.8809471130371</t>
   </si>
   <si>
     <t xml:space="preserve">30.3275260925293</t>
@@ -2930,34 +2930,34 @@
     <t xml:space="preserve">30.0784854888916</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5342845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.552734375</t>
+    <t xml:space="preserve">29.5342864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5527362823486</t>
   </si>
   <si>
     <t xml:space="preserve">29.8571147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0046920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5857906341553</t>
+    <t xml:space="preserve">30.0046939849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">29.8847846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9585762023926</t>
+    <t xml:space="preserve">29.9585742950439</t>
   </si>
   <si>
     <t xml:space="preserve">31.1484336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">31.794095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1814880371094</t>
+    <t xml:space="preserve">31.7940940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1814842224121</t>
   </si>
   <si>
     <t xml:space="preserve">32.4766426086426</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">34.9854927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3306083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.66650390625</t>
+    <t xml:space="preserve">34.3306121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6665077209473</t>
   </si>
   <si>
     <t xml:space="preserve">32.4674224853516</t>
@@ -2981,31 +2981,31 @@
     <t xml:space="preserve">32.0431327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">32.448974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2645034790039</t>
+    <t xml:space="preserve">32.4489784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2644996643066</t>
   </si>
   <si>
     <t xml:space="preserve">32.8455963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7164611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.601936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8509788513184</t>
+    <t xml:space="preserve">32.7164649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6019401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8509750366211</t>
   </si>
   <si>
     <t xml:space="preserve">33.223762512207</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5650405883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9339904785156</t>
+    <t xml:space="preserve">33.5650444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9339942932129</t>
   </si>
   <si>
     <t xml:space="preserve">34.0354537963867</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">33.9432144165039</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9485969543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4043960571289</t>
+    <t xml:space="preserve">34.9485931396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4043998718262</t>
   </si>
   <si>
     <t xml:space="preserve">35.9170837402344</t>
@@ -3032,34 +3032,34 @@
     <t xml:space="preserve">32.1907119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3936309814453</t>
+    <t xml:space="preserve">32.3936347961426</t>
   </si>
   <si>
     <t xml:space="preserve">33.2053184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5465927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8840370178223</t>
+    <t xml:space="preserve">33.5466003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.884033203125</t>
   </si>
   <si>
     <t xml:space="preserve">34.6349906921387</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6273040771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3467597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7195472717285</t>
+    <t xml:space="preserve">36.5996398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6273078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3467636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7195510864258</t>
   </si>
   <si>
     <t xml:space="preserve">37.8909606933594</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">37.8725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6142501831055</t>
+    <t xml:space="preserve">37.6142463684082</t>
   </si>
   <si>
     <t xml:space="preserve">37.4482192993164</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">38.6473007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">38.241455078125</t>
+    <t xml:space="preserve">38.2414588928223</t>
   </si>
   <si>
     <t xml:space="preserve">37.8263893127441</t>
@@ -3095,64 +3095,64 @@
     <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2837333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8463859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5842819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4144134521484</t>
+    <t xml:space="preserve">39.2837371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8463821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5842781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4144172668457</t>
   </si>
   <si>
     <t xml:space="preserve">42.9916648864746</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8533096313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8863639831543</t>
+    <t xml:space="preserve">42.8533058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8863677978516</t>
   </si>
   <si>
     <t xml:space="preserve">44.1630783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0116539001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9286422729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1961288452148</t>
+    <t xml:space="preserve">45.0116500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.928638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1961250305176</t>
   </si>
   <si>
     <t xml:space="preserve">44.7349433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">43.867919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6242637634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4674491882324</t>
+    <t xml:space="preserve">43.8679161071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6242599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4674530029297</t>
   </si>
   <si>
     <t xml:space="preserve">45.869457244873</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3952140808105</t>
+    <t xml:space="preserve">46.3952102661133</t>
   </si>
   <si>
     <t xml:space="preserve">46.2476272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1184959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8456268310547</t>
+    <t xml:space="preserve">46.1184997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8456192016602</t>
   </si>
   <si>
     <t xml:space="preserve">44.8640747070312</t>
@@ -3161,28 +3161,28 @@
     <t xml:space="preserve">44.1077308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2737617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3882827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4121170043945</t>
+    <t xml:space="preserve">44.3290977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3882789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
     <t xml:space="preserve">44.0708351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6742134094238</t>
+    <t xml:space="preserve">43.6742172241211</t>
   </si>
   <si>
     <t xml:space="preserve">44.6703796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9509315490723</t>
+    <t xml:space="preserve">43.950927734375</t>
   </si>
   <si>
     <t xml:space="preserve">44.8917427062988</t>
@@ -3200,25 +3200,25 @@
     <t xml:space="preserve">44.3567733764648</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7756805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1999664306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2091941833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1369476318359</t>
+    <t xml:space="preserve">43.7756767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1999702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2091903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1369438171387</t>
   </si>
   <si>
     <t xml:space="preserve">46.8932914733887</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5758438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0739212036133</t>
+    <t xml:space="preserve">47.5758399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0739250183105</t>
   </si>
   <si>
     <t xml:space="preserve">47.6496315002441</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">48.1477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7972068786621</t>
+    <t xml:space="preserve">47.7972145080566</t>
   </si>
   <si>
     <t xml:space="preserve">46.7088165283203</t>
@@ -3242,19 +3242,19 @@
     <t xml:space="preserve">46.6534729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1807670593262</t>
+    <t xml:space="preserve">49.1807708740234</t>
   </si>
   <si>
     <t xml:space="preserve">47.8710021972656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2437934875488</t>
+    <t xml:space="preserve">47.2437896728516</t>
   </si>
   <si>
     <t xml:space="preserve">47.0408668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699981689453</t>
+    <t xml:space="preserve">47.1700019836426</t>
   </si>
   <si>
     <t xml:space="preserve">47.3175773620605</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">48.1108169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4613189697266</t>
+    <t xml:space="preserve">48.4613151550293</t>
   </si>
   <si>
     <t xml:space="preserve">47.6865310668945</t>
@@ -3281,25 +3281,25 @@
     <t xml:space="preserve">46.4136543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7587738037109</t>
+    <t xml:space="preserve">45.7587776184082</t>
   </si>
   <si>
     <t xml:space="preserve">48.0001373291016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3360252380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4467086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.837947845459</t>
+    <t xml:space="preserve">47.3360290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4467124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8379440307617</t>
   </si>
   <si>
     <t xml:space="preserve">46.2107315063477</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6019744873047</t>
+    <t xml:space="preserve">45.6019706726074</t>
   </si>
   <si>
     <t xml:space="preserve">45.3806037902832</t>
@@ -3308,34 +3308,34 @@
     <t xml:space="preserve">44.2276382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4397811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4859085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3898277282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0762214660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8417930603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6573104858398</t>
+    <t xml:space="preserve">44.4397888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.485897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3898239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0762176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6573143005371</t>
   </si>
   <si>
     <t xml:space="preserve">46.450553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5981330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.524341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5020523071289</t>
+    <t xml:space="preserve">46.5981292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5243339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5020561218262</t>
   </si>
   <si>
     <t xml:space="preserve">47.3544731140137</t>
@@ -3347,28 +3347,28 @@
     <t xml:space="preserve">48.2952919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3467903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9670791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0039710998535</t>
+    <t xml:space="preserve">49.3467864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9670753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0039749145508</t>
   </si>
   <si>
     <t xml:space="preserve">47.0593185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4836044311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3767547607422</t>
+    <t xml:space="preserve">47.4836082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3767623901367</t>
   </si>
   <si>
     <t xml:space="preserve">47.4282646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">47.280689239502</t>
+    <t xml:space="preserve">47.2806816101074</t>
   </si>
   <si>
     <t xml:space="preserve">47.7234230041504</t>
@@ -3377,28 +3377,28 @@
     <t xml:space="preserve">46.9855270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5942878723145</t>
+    <t xml:space="preserve">47.5942916870117</t>
   </si>
   <si>
     <t xml:space="preserve">47.926342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">48.664234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4244270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1623153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4205856323242</t>
+    <t xml:space="preserve">48.6642417907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4244232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1623191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">50.490291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1228179931641</t>
+    <t xml:space="preserve">51.1228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">51.625114440918</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">53.9877777099609</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0621948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4482688903809</t>
+    <t xml:space="preserve">54.0621871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4482727050781</t>
   </si>
   <si>
     <t xml:space="preserve">53.6343078613281</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">54.1180038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2296257019043</t>
+    <t xml:space="preserve">54.229621887207</t>
   </si>
   <si>
     <t xml:space="preserve">55.1039924621582</t>
@@ -3431,22 +3431,22 @@
     <t xml:space="preserve">54.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5784950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8343544006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8715591430664</t>
+    <t xml:space="preserve">53.578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8343505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8715629577637</t>
   </si>
   <si>
     <t xml:space="preserve">53.1320114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8947601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2482223510742</t>
+    <t xml:space="preserve">53.8947563171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2482261657715</t>
   </si>
   <si>
     <t xml:space="preserve">54.5086784362793</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">54.043586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1738166809082</t>
+    <t xml:space="preserve">54.1738128662109</t>
   </si>
   <si>
     <t xml:space="preserve">54.2110176086426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.225025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6901206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5971031188965</t>
+    <t xml:space="preserve">53.2250289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5970993041992</t>
   </si>
   <si>
     <t xml:space="preserve">53.0761985778809</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">53.3180465698242</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8157424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.038990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3366508483887</t>
+    <t xml:space="preserve">52.815746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0389938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3366546630859</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">54.3598480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">52.7785415649414</t>
+    <t xml:space="preserve">52.7785453796387</t>
   </si>
   <si>
     <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1878204345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7459297180176</t>
+    <t xml:space="preserve">53.1878242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7459259033203</t>
   </si>
   <si>
     <t xml:space="preserve">54.6203002929688</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">55.7551231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4946746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8761558532715</t>
+    <t xml:space="preserve">55.4946708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">53.950569152832</t>
@@ -3536,37 +3536,37 @@
     <t xml:space="preserve">54.6389045715332</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6947174072266</t>
+    <t xml:space="preserve">54.6947135925293</t>
   </si>
   <si>
     <t xml:space="preserve">54.5272789001465</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5876922607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9271507263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2992286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5596733093262</t>
+    <t xml:space="preserve">55.5876884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9271545410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2992210388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7271118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5596771240234</t>
   </si>
   <si>
     <t xml:space="preserve">56.4248542785645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8667488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3970565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0670051574707</t>
+    <t xml:space="preserve">55.8667449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3970527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.067008972168</t>
   </si>
   <si>
     <t xml:space="preserve">50.1554260253906</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">50.7693481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3972778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5461006164551</t>
+    <t xml:space="preserve">50.3972702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5461044311523</t>
   </si>
   <si>
     <t xml:space="preserve">50.8065528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4158744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0298004150391</t>
+    <t xml:space="preserve">50.4158782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0297966003418</t>
   </si>
   <si>
     <t xml:space="preserve">50.9925918579102</t>
@@ -3608,34 +3608,34 @@
     <t xml:space="preserve">51.4018707275391</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3274536132812</t>
+    <t xml:space="preserve">51.3274574279785</t>
   </si>
   <si>
     <t xml:space="preserve">50.8251571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7879486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1648330688477</t>
+    <t xml:space="preserve">50.7879447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1648368835449</t>
   </si>
   <si>
     <t xml:space="preserve">48.0904235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3182640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0532150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0020027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5647087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3832664489746</t>
+    <t xml:space="preserve">49.3182601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0532112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0019989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5647048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3832702636719</t>
   </si>
   <si>
     <t xml:space="preserve">51.1600227355957</t>
@@ -3653,22 +3653,22 @@
     <t xml:space="preserve">51.7553405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.978588104248</t>
+    <t xml:space="preserve">51.9785842895508</t>
   </si>
   <si>
     <t xml:space="preserve">52.9831771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4994812011719</t>
+    <t xml:space="preserve">52.4994850158691</t>
   </si>
   <si>
     <t xml:space="preserve">52.4622802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4714698791504</t>
+    <t xml:space="preserve">54.7133140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4714736938477</t>
   </si>
   <si>
     <t xml:space="preserve">55.5690879821777</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">56.7597198486328</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8341293334961</t>
+    <t xml:space="preserve">56.8341331481934</t>
   </si>
   <si>
     <t xml:space="preserve">56.3876457214355</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">56.9457588195801</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7829170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4386444091797</t>
+    <t xml:space="preserve">57.7829208374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.438648223877</t>
   </si>
   <si>
     <t xml:space="preserve">58.5084648132324</t>
@@ -3707,43 +3707,43 @@
     <t xml:space="preserve">61.652473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8803253173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4012222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7409057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8199157714844</t>
+    <t xml:space="preserve">62.8803176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4012298583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7408981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8199043273926</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7546882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.331413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.568660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0663528442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593276977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408592224121</t>
+    <t xml:space="preserve">63.7546997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3314056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2197875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5686492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0663566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408630371094</t>
   </si>
   <si>
     <t xml:space="preserve">61.9129257202148</t>
@@ -3761,31 +3761,31 @@
     <t xml:space="preserve">59.6060829162598</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0385589599609</t>
+    <t xml:space="preserve">61.0385551452637</t>
   </si>
   <si>
     <t xml:space="preserve">60.9455337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">60.5920753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6896896362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4430236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4710350036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4478340148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.629280090332</t>
+    <t xml:space="preserve">60.5920715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6896858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4430160522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4710426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1547737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4478378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6292762756348</t>
   </si>
   <si>
     <t xml:space="preserve">58.675895690918</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">60.182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">58.7503128051758</t>
+    <t xml:space="preserve">58.7503089904785</t>
   </si>
   <si>
     <t xml:space="preserve">58.8061218261719</t>
@@ -3815,28 +3815,28 @@
     <t xml:space="preserve">59.7549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0711669921875</t>
+    <t xml:space="preserve">60.071174621582</t>
   </si>
   <si>
     <t xml:space="preserve">59.5502662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">59.810718536377</t>
+    <t xml:space="preserve">59.8107223510742</t>
   </si>
   <si>
     <t xml:space="preserve">60.4618492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4154396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9643592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1644058227539</t>
+    <t xml:space="preserve">60.9269332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4154434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9643630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1644020080566</t>
   </si>
   <si>
     <t xml:space="preserve">55.7923278808594</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">52.8901634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7087249755859</t>
+    <t xml:space="preserve">53.7087211608887</t>
   </si>
   <si>
     <t xml:space="preserve">52.6111106872559</t>
@@ -3860,37 +3860,37 @@
     <t xml:space="preserve">54.3412437438965</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6995315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2716407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3134498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5366897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5693016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4064712524414</t>
+    <t xml:space="preserve">51.699535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2716445922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3134536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.536693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5693054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4064674377441</t>
   </si>
   <si>
     <t xml:space="preserve">54.899356842041</t>
   </si>
   <si>
-    <t xml:space="preserve">55.271427154541</t>
+    <t xml:space="preserve">55.2714233398438</t>
   </si>
   <si>
     <t xml:space="preserve">53.8389472961426</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0993995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6437149047852</t>
+    <t xml:space="preserve">54.0993957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6437187194824</t>
   </si>
   <si>
     <t xml:space="preserve">50.6391181945801</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">52.1274108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2344360351562</t>
+    <t xml:space="preserve">51.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">50.9739875793457</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">50.9181785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8809661865234</t>
+    <t xml:space="preserve">50.8809700012207</t>
   </si>
   <si>
     <t xml:space="preserve">48.4624938964844</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">45.8021774291992</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1230316162109</t>
+    <t xml:space="preserve">47.1230278015137</t>
   </si>
   <si>
     <t xml:space="preserve">44.9464073181152</t>
@@ -3941,31 +3941,31 @@
     <t xml:space="preserve">44.6208457946777</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6487464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2441711425781</t>
+    <t xml:space="preserve">44.6487503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2441749572754</t>
   </si>
   <si>
     <t xml:space="preserve">45.709156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7881698608398</t>
+    <t xml:space="preserve">46.7881622314453</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044273376465</t>
+    <t xml:space="preserve">47.1044235229492</t>
   </si>
   <si>
     <t xml:space="preserve">46.2951736450195</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8207740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2021484375</t>
+    <t xml:space="preserve">45.8207778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2021522521973</t>
   </si>
   <si>
     <t xml:space="preserve">46.2765655517578</t>
@@ -3974,22 +3974,22 @@
     <t xml:space="preserve">48.8717765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1974487304688</t>
+    <t xml:space="preserve">47.1974449157715</t>
   </si>
   <si>
     <t xml:space="preserve">47.178840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9275779724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2810554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9556007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9882125854492</t>
+    <t xml:space="preserve">48.9275817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2810516357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9555969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">47.4392929077148</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">46.4533004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0300140380859</t>
+    <t xml:space="preserve">47.0300102233887</t>
   </si>
   <si>
     <t xml:space="preserve">46.1835517883301</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5881233215332</t>
+    <t xml:space="preserve">47.5881195068359</t>
   </si>
   <si>
     <t xml:space="preserve">46.527717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3510932922363</t>
+    <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
     <t xml:space="preserve">43.8301849365234</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">45.430103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2672653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7695579528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5696296691895</t>
+    <t xml:space="preserve">46.2672691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7695617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5696334838867</t>
   </si>
   <si>
     <t xml:space="preserve">44.6115379333496</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9604072570801</t>
+    <t xml:space="preserve">43.9604110717773</t>
   </si>
   <si>
     <t xml:space="preserve">41.4861259460449</t>
@@ -4046,22 +4046,22 @@
     <t xml:space="preserve">39.7373809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9095230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8676071166992</t>
+    <t xml:space="preserve">38.9095268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8676109313965</t>
   </si>
   <si>
     <t xml:space="preserve">41.6163520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8070907592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1930694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2814865112305</t>
+    <t xml:space="preserve">40.8070945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2814903259277</t>
   </si>
   <si>
     <t xml:space="preserve">42.1093521118164</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">39.819034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.658821105957</t>
+    <t xml:space="preserve">40.6588172912598</t>
   </si>
   <si>
     <t xml:space="preserve">42.3572616577148</t>
@@ -4103,19 +4103,19 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801216125488</t>
+    <t xml:space="preserve">43.4801254272461</t>
   </si>
   <si>
     <t xml:space="preserve">43.234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1119346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2155265808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.648998260498</t>
+    <t xml:space="preserve">42.111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2155303955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6489944458008</t>
   </si>
   <si>
     <t xml:space="preserve">37.2147560119629</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">36.2145652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5167007446289</t>
+    <t xml:space="preserve">37.5166969299316</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">34.9973449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9312973022461</t>
+    <t xml:space="preserve">34.9312934875488</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639762878418</t>
+    <t xml:space="preserve">38.0639801025391</t>
   </si>
   <si>
     <t xml:space="preserve">37.3751678466797</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0547332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396560668945</t>
+    <t xml:space="preserve">39.0547370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396598815918</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">40.3474349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7531776428223</t>
+    <t xml:space="preserve">40.753173828125</t>
   </si>
   <si>
     <t xml:space="preserve">41.1494789123535</t>
@@ -4214,10 +4214,10 @@
     <t xml:space="preserve">40.7248687744141</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9990921020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9239921569824</t>
+    <t xml:space="preserve">43.9990882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9239883422852</t>
   </si>
   <si>
     <t xml:space="preserve">45.9806060791016</t>
@@ -4226,22 +4226,22 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389701843262</t>
+    <t xml:space="preserve">45.3389739990234</t>
   </si>
   <si>
     <t xml:space="preserve">46.5278854370117</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5184478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4995727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8579368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7165985107422</t>
+    <t xml:space="preserve">46.5184440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4995765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8579406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7165946960449</t>
   </si>
   <si>
     <t xml:space="preserve">46.9524917602539</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">46.7543411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1315765380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0273933410645</t>
+    <t xml:space="preserve">46.1315803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0273971557617</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
@@ -4277,31 +4277,31 @@
     <t xml:space="preserve">43.0460739135742</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1496696472168</t>
+    <t xml:space="preserve">42.1496734619141</t>
   </si>
   <si>
     <t xml:space="preserve">42.3100814819336</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1213645935059</t>
+    <t xml:space="preserve">42.1213684082031</t>
   </si>
   <si>
     <t xml:space="preserve">41.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2251586914062</t>
+    <t xml:space="preserve">42.2251625061035</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1777877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3948059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6967544555664</t>
+    <t xml:space="preserve">41.1777839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3948097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6967506408691</t>
   </si>
   <si>
     <t xml:space="preserve">42.4704895019531</t>
@@ -4310,25 +4310,25 @@
     <t xml:space="preserve">42.998893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0175743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646553039551</t>
+    <t xml:space="preserve">42.0175704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7158241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646514892578</t>
   </si>
   <si>
     <t xml:space="preserve">40.9230194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4891662597656</t>
+    <t xml:space="preserve">41.4891700744629</t>
   </si>
   <si>
     <t xml:space="preserve">41.8005485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4610557556152</t>
+    <t xml:space="preserve">42.461051940918</t>
   </si>
   <si>
     <t xml:space="preserve">39.9511337280273</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">41.0645561218262</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8096008300781</t>
+    <t xml:space="preserve">39.8095970153809</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703941345215</t>
+    <t xml:space="preserve">41.9703903198242</t>
   </si>
   <si>
     <t xml:space="preserve">41.5174751281738</t>
@@ -4376,10 +4376,10 @@
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8009376525879</t>
+    <t xml:space="preserve">42.7252540588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8009338378906</t>
   </si>
   <si>
     <t xml:space="preserve">44.0557022094727</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">43.7160186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6690292358398</t>
+    <t xml:space="preserve">44.6690330505371</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">46.1693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6692237854004</t>
+    <t xml:space="preserve">45.6692276000977</t>
   </si>
   <si>
     <t xml:space="preserve">43.7443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7346954345703</t>
+    <t xml:space="preserve">42.734691619873</t>
   </si>
   <si>
     <t xml:space="preserve">41.2249641418457</t>
@@ -4421,16 +4421,16 @@
     <t xml:space="preserve">39.8756484985352</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8290519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9422760009766</t>
+    <t xml:space="preserve">42.8290481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9422798156738</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0840148925781</t>
+    <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">46.7732124328613</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">47.6129951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7639656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1978187561035</t>
+    <t xml:space="preserve">47.7639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1978225708008</t>
   </si>
   <si>
     <t xml:space="preserve">47.0657196044922</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">47.0185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6314849853516</t>
+    <t xml:space="preserve">45.6314811706543</t>
   </si>
   <si>
     <t xml:space="preserve">45.6031761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5654296875</t>
+    <t xml:space="preserve">45.5654335021973</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2917900085449</t>
+    <t xml:space="preserve">45.2917938232422</t>
   </si>
   <si>
     <t xml:space="preserve">44.8200035095215</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5465621948242</t>
+    <t xml:space="preserve">45.546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">45.5937385559082</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">44.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7447128295898</t>
+    <t xml:space="preserve">45.7447090148926</t>
   </si>
   <si>
     <t xml:space="preserve">46.5844955444336</t>
@@ -4508,10 +4508,10 @@
     <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1504516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3861465454102</t>
+    <t xml:space="preserve">46.150447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3861503601074</t>
   </si>
   <si>
     <t xml:space="preserve">46.6788558959961</t>
@@ -4520,16 +4520,16 @@
     <t xml:space="preserve">47.3110466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7071647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8017120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5563850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5565719604492</t>
+    <t xml:space="preserve">46.707160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8017082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5563812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5565757751465</t>
   </si>
   <si>
     <t xml:space="preserve">49.3869247436523</t>
@@ -4538,22 +4538,22 @@
     <t xml:space="preserve">49.7077407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">48.971752166748</t>
+    <t xml:space="preserve">48.9717483520508</t>
   </si>
   <si>
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814758300781</t>
+    <t xml:space="preserve">50.4814796447754</t>
   </si>
   <si>
     <t xml:space="preserve">51.8779754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3497657775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8781700134277</t>
+    <t xml:space="preserve">52.3497619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8781661987305</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">51.9157180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0480155944824</t>
+    <t xml:space="preserve">53.0480117797852</t>
   </si>
   <si>
     <t xml:space="preserve">53.3310890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1046257019043</t>
+    <t xml:space="preserve">53.1046295166016</t>
   </si>
   <si>
     <t xml:space="preserve">53.2555999755859</t>
@@ -4577,22 +4577,22 @@
     <t xml:space="preserve">54.5199928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0859527587891</t>
+    <t xml:space="preserve">54.0859489440918</t>
   </si>
   <si>
     <t xml:space="preserve">53.9727210998535</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8406219482422</t>
+    <t xml:space="preserve">53.8406181335449</t>
   </si>
   <si>
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4447021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1991767883301</t>
+    <t xml:space="preserve">55.4446983337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1991806030273</t>
   </si>
   <si>
     <t xml:space="preserve">54.0293350219727</t>
@@ -4607,13 +4607,13 @@
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009307861328</t>
+    <t xml:space="preserve">53.5009346008301</t>
   </si>
   <si>
     <t xml:space="preserve">53.9349784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8785552978516</t>
+    <t xml:space="preserve">54.8785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
@@ -4622,13 +4622,13 @@
     <t xml:space="preserve">54.444507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3503456115723</t>
+    <t xml:space="preserve">55.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9729118347168</t>
+    <t xml:space="preserve">54.9729080200195</t>
   </si>
   <si>
     <t xml:space="preserve">54.46337890625</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">54.5388641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3316688537598</t>
+    <t xml:space="preserve">56.3316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
@@ -4682,10 +4682,10 @@
     <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5017051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546203613281</t>
+    <t xml:space="preserve">57.5017013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546241760254</t>
   </si>
   <si>
     <t xml:space="preserve">58.1433372497559</t>
@@ -4697,37 +4697,37 @@
     <t xml:space="preserve">57.2752456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9170722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8981971740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9550132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1059837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0116233825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6155166625977</t>
+    <t xml:space="preserve">58.9170761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8982009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9550094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1059875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0116271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6155128479004</t>
   </si>
   <si>
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417778015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4266090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0686264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2196006774902</t>
+    <t xml:space="preserve">59.8417816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4266052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0686225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.219596862793</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">63.1443061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">63.408504486084</t>
+    <t xml:space="preserve">63.4085121154785</t>
   </si>
   <si>
     <t xml:space="preserve">63.8614311218262</t>
@@ -4763,13 +4763,13 @@
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.502872467041</t>
+    <t xml:space="preserve">63.5028648376465</t>
   </si>
   <si>
     <t xml:space="preserve">62.993335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4649276733398</t>
+    <t xml:space="preserve">62.4649238586426</t>
   </si>
   <si>
     <t xml:space="preserve">61.8987808227539</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">60.8608474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7287445068359</t>
+    <t xml:space="preserve">60.7287483215332</t>
   </si>
   <si>
     <t xml:space="preserve">62.1307678222656</t>
@@ -6450,6 +6450,9 @@
   </si>
   <si>
     <t xml:space="preserve">58.0999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -72048,7 +72051,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6910069444</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>645857</v>
@@ -72069,6 +72072,32 @@
         <v>2145</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6910416667</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>1000791</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>58.0800018310547</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>56.1399993896484</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>57.7999992370605</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>57.1399993896484</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>2146</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="2151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="2152">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,46 +44,46 @@
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8452558517456</t>
+    <t xml:space="preserve">10.9698095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8452548980713</t>
   </si>
   <si>
     <t xml:space="preserve">10.8986358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.987606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744394302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573602676392</t>
+    <t xml:space="preserve">10.9876041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573593139648</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769296646118</t>
+    <t xml:space="preserve">11.4769315719604</t>
   </si>
   <si>
     <t xml:space="preserve">11.1566438674927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5481042861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.734938621521</t>
+    <t xml:space="preserve">11.5481061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7349395751953</t>
   </si>
   <si>
     <t xml:space="preserve">11.4057559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239088058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1175022125244</t>
+    <t xml:space="preserve">11.8239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175031661987</t>
   </si>
   <si>
     <t xml:space="preserve">12.0018444061279</t>
@@ -92,43 +92,43 @@
     <t xml:space="preserve">12.1263999938965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0997104644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7260427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908126831055</t>
+    <t xml:space="preserve">12.0997095108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7260417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908136367798</t>
   </si>
   <si>
     <t xml:space="preserve">11.9484634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8950805664062</t>
+    <t xml:space="preserve">11.8950843811035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7616300582886</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9128770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4146528244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2723045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2545099258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989931106567</t>
+    <t xml:space="preserve">11.9128761291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4146518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2723035812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0409841537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2545080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989921569824</t>
   </si>
   <si>
     <t xml:space="preserve">11.672661781311</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">11.8772888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110984802246</t>
+    <t xml:space="preserve">12.4111003875732</t>
   </si>
   <si>
     <t xml:space="preserve">12.2509565353394</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">12.2687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4022035598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7972164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1975765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7402830123901</t>
+    <t xml:space="preserve">12.4022026062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7972173690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1975746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7402820587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.962703704834</t>
@@ -164,43 +164,43 @@
     <t xml:space="preserve">12.7669734954834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2118158340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4787197113037</t>
+    <t xml:space="preserve">13.2118148803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.478720664978</t>
   </si>
   <si>
     <t xml:space="preserve">13.9680471420288</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4520292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7100391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363704681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0427751541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605688095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9893941879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9004259109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0160856246948</t>
+    <t xml:space="preserve">13.4520320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210699081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7100372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0427761077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9893932342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9004249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0160846710205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9449110031128</t>
@@ -209,154 +209,154 @@
     <t xml:space="preserve">13.0961570739746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.514307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1228466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9804973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9271183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.589035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7936639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8292512893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338773727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737373352051</t>
+    <t xml:space="preserve">13.5143070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1228456497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9804964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9271144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5890350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7936630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737363815308</t>
   </si>
   <si>
     <t xml:space="preserve">13.1495370864868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2029180526733</t>
+    <t xml:space="preserve">13.2029190063477</t>
   </si>
   <si>
     <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1673307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089654922485</t>
+    <t xml:space="preserve">13.167332649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089645385742</t>
   </si>
   <si>
     <t xml:space="preserve">12.5979328155518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9716005325317</t>
+    <t xml:space="preserve">12.9715995788574</t>
   </si>
   <si>
     <t xml:space="preserve">12.998291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3185777664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9324588775635</t>
+    <t xml:space="preserve">13.3185758590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9324598312378</t>
   </si>
   <si>
     <t xml:space="preserve">14.0570154190063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9947376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6388635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3630609512329</t>
+    <t xml:space="preserve">13.9947366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502553939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6388626098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3630619049072</t>
   </si>
   <si>
     <t xml:space="preserve">13.3452682495117</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2285194396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5608043670654</t>
+    <t xml:space="preserve">13.2285184860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5608053207397</t>
   </si>
   <si>
     <t xml:space="preserve">13.4440546035767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2734222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4620161056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4979391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632297515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183269500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6685733795166</t>
+    <t xml:space="preserve">13.2734212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709959030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4620170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4979381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.668571472168</t>
   </si>
   <si>
     <t xml:space="preserve">13.7314357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7404165267944</t>
+    <t xml:space="preserve">13.7404174804688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3003644943237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1566724777222</t>
+    <t xml:space="preserve">13.1566734313965</t>
   </si>
   <si>
     <t xml:space="preserve">12.7256021499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.860312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122634887695</t>
+    <t xml:space="preserve">13.2105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8603115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122625350952</t>
   </si>
   <si>
     <t xml:space="preserve">13.6775512695312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8571662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2253742218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321575164795</t>
+    <t xml:space="preserve">13.8571653366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2253732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321584701538</t>
   </si>
   <si>
     <t xml:space="preserve">12.3035106658936</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">12.6986598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1476936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.995023727417</t>
+    <t xml:space="preserve">13.1476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9950218200684</t>
   </si>
   <si>
     <t xml:space="preserve">12.6178340911865</t>
@@ -377,55 +377,55 @@
     <t xml:space="preserve">12.8513307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8782749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9680786132812</t>
+    <t xml:space="preserve">12.8782730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9680805206299</t>
   </si>
   <si>
     <t xml:space="preserve">12.9231767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1746339797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.959098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9501190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7705049514771</t>
+    <t xml:space="preserve">13.174635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9590997695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.950119972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7705059051514</t>
   </si>
   <si>
     <t xml:space="preserve">13.3452672958374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8302230834961</t>
+    <t xml:space="preserve">13.8302240371704</t>
   </si>
   <si>
     <t xml:space="preserve">14.1714878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0637197494507</t>
+    <t xml:space="preserve">14.0637216567993</t>
   </si>
   <si>
     <t xml:space="preserve">14.3690633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0816822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9559545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069198608398</t>
+    <t xml:space="preserve">14.0816831588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9559526443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069208145142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6057062149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9290103912354</t>
+    <t xml:space="preserve">13.929012298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.0277976989746</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">13.8481845855713</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0457601547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9918756484985</t>
+    <t xml:space="preserve">14.0457592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9918746948242</t>
   </si>
   <si>
     <t xml:space="preserve">13.9200296401978</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">13.7673578262329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0008563995361</t>
+    <t xml:space="preserve">14.0008573532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.7583780288696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877437591553</t>
+    <t xml:space="preserve">13.6955137252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248823165894</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">13.3542490005493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4171123504639</t>
+    <t xml:space="preserve">13.4171133041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159006118774</t>
@@ -479,97 +479,97 @@
     <t xml:space="preserve">13.5338611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7044944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9110498428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0098361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727024078369</t>
+    <t xml:space="preserve">13.7044954299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9110507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.614688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0098371505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727014541626</t>
   </si>
   <si>
     <t xml:space="preserve">13.4530353546143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6506109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6416292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853221893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4799785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.839204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0996437072754</t>
+    <t xml:space="preserve">13.6506099700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6416301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4799766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8392038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0996427536011</t>
   </si>
   <si>
     <t xml:space="preserve">13.8930883407593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9649324417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8751258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7943000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.62366771698</t>
+    <t xml:space="preserve">13.9649333953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8751268386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7943019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6236686706543</t>
   </si>
   <si>
     <t xml:space="preserve">13.399151802063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3901710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4889583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362874984741</t>
+    <t xml:space="preserve">13.3901720046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4889574050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362894058228</t>
   </si>
   <si>
     <t xml:space="preserve">13.6326494216919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3273057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763385772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8661460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0547399520874</t>
+    <t xml:space="preserve">13.3273067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8661470413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0547389984131</t>
   </si>
   <si>
     <t xml:space="preserve">14.6474637985229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.638482093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9168844223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0426139831543</t>
+    <t xml:space="preserve">14.6384830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9168863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.04261302948</t>
   </si>
   <si>
     <t xml:space="preserve">14.8989238739014</t>
@@ -581,31 +581,31 @@
     <t xml:space="preserve">14.7372713088989</t>
   </si>
   <si>
-    <t xml:space="preserve">14.773193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8719797134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911520004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.683385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013492584229</t>
+    <t xml:space="preserve">14.7731952667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8719806671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.683388710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013483047485</t>
   </si>
   <si>
     <t xml:space="preserve">14.8450393676758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.087516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9707679748535</t>
+    <t xml:space="preserve">15.0875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9707670211792</t>
   </si>
   <si>
     <t xml:space="preserve">14.7103281021118</t>
@@ -614,37 +614,37 @@
     <t xml:space="preserve">14.6744060516357</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9528074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377603530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736843109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6892223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251424789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4826679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790279388428</t>
+    <t xml:space="preserve">14.952805519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377641677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.473687171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6892175674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251415252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4826650619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790288925171</t>
   </si>
   <si>
     <t xml:space="preserve">16.0933513641357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1651973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2011222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1921405792236</t>
+    <t xml:space="preserve">16.1652011871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2011203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.192138671875</t>
   </si>
   <si>
     <t xml:space="preserve">16.2460231781006</t>
@@ -653,16 +653,16 @@
     <t xml:space="preserve">16.1113109588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9855842590332</t>
+    <t xml:space="preserve">16.0304851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9855823516846</t>
   </si>
   <si>
     <t xml:space="preserve">15.9137372970581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6353359222412</t>
+    <t xml:space="preserve">15.6353368759155</t>
   </si>
   <si>
     <t xml:space="preserve">15.931697845459</t>
@@ -671,37 +671,37 @@
     <t xml:space="preserve">15.9766035079956</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9586420059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867950439453</t>
+    <t xml:space="preserve">15.9586410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406785964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867998123169</t>
   </si>
   <si>
     <t xml:space="preserve">16.1741771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1023330688477</t>
+    <t xml:space="preserve">16.102331161499</t>
   </si>
   <si>
     <t xml:space="preserve">16.0484485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8957767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676237106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831588745117</t>
+    <t xml:space="preserve">15.8957786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9676218032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831569671631</t>
   </si>
   <si>
     <t xml:space="preserve">17.0991859436035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2608375549316</t>
+    <t xml:space="preserve">17.260835647583</t>
   </si>
   <si>
     <t xml:space="preserve">17.1620502471924</t>
@@ -719,58 +719,58 @@
     <t xml:space="preserve">17.5661811828613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6559886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6021041870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8535594940186</t>
+    <t xml:space="preserve">17.6559867858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6021022796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">18.0062313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1768684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8805065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0601177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0870552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.320556640625</t>
+    <t xml:space="preserve">18.1768665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8805046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0601139068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0870590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205547332764</t>
   </si>
   <si>
     <t xml:space="preserve">18.2666721343994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4103622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678848266602</t>
+    <t xml:space="preserve">18.410364151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678867340088</t>
   </si>
   <si>
     <t xml:space="preserve">18.2756538391113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4373054504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9312400817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2276058197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2365837097168</t>
+    <t xml:space="preserve">18.4373035430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9312419891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2276020050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2365818023682</t>
   </si>
   <si>
     <t xml:space="preserve">19.2006587982178</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">19.4790630340576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5598888397217</t>
+    <t xml:space="preserve">19.559886932373</t>
   </si>
   <si>
     <t xml:space="preserve">19.1108551025391</t>
@@ -794,25 +794,25 @@
     <t xml:space="preserve">19.5329456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6945991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5778484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.514986038208</t>
+    <t xml:space="preserve">19.6945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4611015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5778465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5149841308594</t>
   </si>
   <si>
     <t xml:space="preserve">20.188533782959</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4310092926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3501873016357</t>
+    <t xml:space="preserve">20.4310131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3501834869385</t>
   </si>
   <si>
     <t xml:space="preserve">20.6645088195801</t>
@@ -821,136 +821,136 @@
     <t xml:space="preserve">20.8351440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1135444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4759140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.78440284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.999942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8921756744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9819774627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8742084503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9909610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3892574310303</t>
+    <t xml:space="preserve">21.1135406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4759178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7844085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9999389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8921718597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9819793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8742141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9909591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3892555236816</t>
   </si>
   <si>
     <t xml:space="preserve">19.5509071350098</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6505184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6052379608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4875202178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0127391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2339630126953</t>
+    <t xml:space="preserve">19.6505165100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6052398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4875164031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0127410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2339611053467</t>
   </si>
   <si>
     <t xml:space="preserve">19.6324062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7048511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2792434692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9260730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0075721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9713535308838</t>
+    <t xml:space="preserve">19.7048530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2792415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9260749816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0075740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9713554382324</t>
   </si>
   <si>
     <t xml:space="preserve">19.0800189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5819644927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1252937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0437965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3426284790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2249050140381</t>
+    <t xml:space="preserve">18.5819664001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0437984466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3426265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2249069213867</t>
   </si>
   <si>
     <t xml:space="preserve">19.614294052124</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2158527374268</t>
+    <t xml:space="preserve">19.2158489227295</t>
   </si>
   <si>
     <t xml:space="preserve">19.1524620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1434078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3245182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9441871643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3736896514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.563850402832</t>
+    <t xml:space="preserve">19.1434059143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3245162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.944185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.373685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5638561248779</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362972259521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6000785827637</t>
+    <t xml:space="preserve">18.6000747680664</t>
   </si>
   <si>
     <t xml:space="preserve">18.8083534240723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7359085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6091327667236</t>
+    <t xml:space="preserve">18.7359066009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6091289520264</t>
   </si>
   <si>
     <t xml:space="preserve">19.1071853637695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2882976531982</t>
+    <t xml:space="preserve">19.288293838501</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788509368896</t>
@@ -962,121 +962,121 @@
     <t xml:space="preserve">19.4512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4331836700439</t>
+    <t xml:space="preserve">19.4331855773926</t>
   </si>
   <si>
     <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1977405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2391300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4655151367188</t>
+    <t xml:space="preserve">19.1977424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2391262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4655170440674</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2572383880615</t>
+    <t xml:space="preserve">20.3568496704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2572402954102</t>
   </si>
   <si>
     <t xml:space="preserve">20.3930721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3296852111816</t>
+    <t xml:space="preserve">20.329683303833</t>
   </si>
   <si>
     <t xml:space="preserve">20.3749599456787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4021301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3477916717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8458499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1446800231934</t>
+    <t xml:space="preserve">20.4021282196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3477935791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8458480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1446838378906</t>
   </si>
   <si>
     <t xml:space="preserve">21.5431251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">21.380126953125</t>
+    <t xml:space="preserve">21.3801250457764</t>
   </si>
   <si>
     <t xml:space="preserve">21.3439025878906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4254016876221</t>
+    <t xml:space="preserve">21.4254035949707</t>
   </si>
   <si>
     <t xml:space="preserve">21.3710689544678</t>
   </si>
   <si>
-    <t xml:space="preserve">21.280517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2080726623535</t>
+    <t xml:space="preserve">21.2805137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2080707550049</t>
   </si>
   <si>
     <t xml:space="preserve">20.8730144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2714595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8962917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7423477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7966804504395</t>
+    <t xml:space="preserve">21.2714576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6155681610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8962936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7423439025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7966785430908</t>
   </si>
   <si>
     <t xml:space="preserve">21.9959030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1589031219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4305667877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3671798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5935668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116790771484</t>
+    <t xml:space="preserve">22.158899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4305686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3671779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5935688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6116771697998</t>
   </si>
   <si>
     <t xml:space="preserve">22.5030136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2404022216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.385290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2313442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2132339477539</t>
+    <t xml:space="preserve">22.2404003143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3852882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2313480377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2132358551025</t>
   </si>
   <si>
     <t xml:space="preserve">22.2494564056396</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">21.8238468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0683479309082</t>
+    <t xml:space="preserve">22.0683460235596</t>
   </si>
   <si>
     <t xml:space="preserve">22.1136245727539</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">21.8419589996338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7514038085938</t>
+    <t xml:space="preserve">21.7514019012451</t>
   </si>
   <si>
     <t xml:space="preserve">21.4706802368164</t>
@@ -1109,25 +1109,25 @@
     <t xml:space="preserve">22.149845123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.059289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2856788635254</t>
+    <t xml:space="preserve">22.2766208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0592918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2856769561768</t>
   </si>
   <si>
     <t xml:space="preserve">22.3490676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3943424224854</t>
+    <t xml:space="preserve">22.3943462371826</t>
   </si>
   <si>
     <t xml:space="preserve">21.9868469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4396228790283</t>
+    <t xml:space="preserve">22.4396266937256</t>
   </si>
   <si>
     <t xml:space="preserve">22.5573463439941</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">22.1226787567139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0774002075195</t>
+    <t xml:space="preserve">22.0774021148682</t>
   </si>
   <si>
     <t xml:space="preserve">22.0049571990967</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">21.8510131835938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7695140838623</t>
+    <t xml:space="preserve">21.7695159912109</t>
   </si>
   <si>
     <t xml:space="preserve">20.6466255187988</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">21.0088500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6737957000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7734069824219</t>
+    <t xml:space="preserve">20.6737937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7734031677246</t>
   </si>
   <si>
     <t xml:space="preserve">20.6556797027588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0903491973877</t>
+    <t xml:space="preserve">21.0994033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0903511047363</t>
   </si>
   <si>
     <t xml:space="preserve">21.1356258392334</t>
@@ -1184,25 +1184,25 @@
     <t xml:space="preserve">20.8277378082275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8005695343018</t>
+    <t xml:space="preserve">20.8549022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8005714416504</t>
   </si>
   <si>
     <t xml:space="preserve">20.8820686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4344577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4163455963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9506225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4667930603027</t>
+    <t xml:space="preserve">21.4344596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4163475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9506244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4667911529541</t>
   </si>
   <si>
     <t xml:space="preserve">22.5120677947998</t>
@@ -1211,52 +1211,52 @@
     <t xml:space="preserve">22.8833465576172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3218994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290119171143</t>
+    <t xml:space="preserve">22.3219013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290100097656</t>
   </si>
   <si>
     <t xml:space="preserve">22.9014568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8109035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.091625213623</t>
+    <t xml:space="preserve">22.8109016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0916233062744</t>
   </si>
   <si>
     <t xml:space="preserve">23.2546215057373</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6530666351318</t>
+    <t xml:space="preserve">23.6530647277832</t>
   </si>
   <si>
     <t xml:space="preserve">23.9066200256348</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6168422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632907867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1821784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.634952545166</t>
+    <t xml:space="preserve">23.6168441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1821765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6349544525146</t>
   </si>
   <si>
     <t xml:space="preserve">23.4900665283203</t>
   </si>
   <si>
-    <t xml:space="preserve">23.544397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2002868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8199596405029</t>
+    <t xml:space="preserve">23.5444011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.819953918457</t>
   </si>
   <si>
     <t xml:space="preserve">22.7837333679199</t>
@@ -1265,64 +1265,64 @@
     <t xml:space="preserve">23.0372886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8160629272461</t>
+    <t xml:space="preserve">23.8160648345947</t>
   </si>
   <si>
     <t xml:space="preserve">24.3412857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4861755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3775081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5042858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2869548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1148948669434</t>
+    <t xml:space="preserve">24.486177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2507305145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3775100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5042877197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5223979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2869510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.114896774292</t>
   </si>
   <si>
     <t xml:space="preserve">24.0333976745605</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2145080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5625095367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4628982543945</t>
+    <t xml:space="preserve">24.2145099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5625133514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4629001617432</t>
   </si>
   <si>
     <t xml:space="preserve">24.3593978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.290843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0424537658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6582298278809</t>
+    <t xml:space="preserve">23.2908420562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0424518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6582279205322</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724491119385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7630081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4279518127441</t>
+    <t xml:space="preserve">25.7630062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4279499053955</t>
   </si>
   <si>
     <t xml:space="preserve">25.5637836456299</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">25.5818958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4641742706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3917293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.63623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1342811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9893932342529</t>
+    <t xml:space="preserve">25.4641761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.391731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6362266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1342849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9893951416016</t>
   </si>
   <si>
     <t xml:space="preserve">25.3192844390869</t>
@@ -1352,43 +1352,43 @@
     <t xml:space="preserve">25.264949798584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6996173858643</t>
+    <t xml:space="preserve">25.6996154785156</t>
   </si>
   <si>
     <t xml:space="preserve">25.5728378295898</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2157821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.405948638916</t>
+    <t xml:space="preserve">26.215784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4059467315674</t>
   </si>
   <si>
     <t xml:space="preserve">26.5055618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6685581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4874477386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8134479522705</t>
+    <t xml:space="preserve">26.6685600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4874496459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8134517669678</t>
   </si>
   <si>
     <t xml:space="preserve">26.7500610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9583396911621</t>
+    <t xml:space="preserve">26.9583358764648</t>
   </si>
   <si>
     <t xml:space="preserve">27.4654483795166</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9453926086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5741119384766</t>
+    <t xml:space="preserve">27.9453887939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5741138458252</t>
   </si>
   <si>
     <t xml:space="preserve">27.7190017700195</t>
@@ -1400,49 +1400,49 @@
     <t xml:space="preserve">27.9182224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9816112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7655544281006</t>
+    <t xml:space="preserve">27.9816131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7655563354492</t>
   </si>
   <si>
     <t xml:space="preserve">29.4304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8108310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549415588379</t>
+    <t xml:space="preserve">29.8108329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549396514893</t>
   </si>
   <si>
     <t xml:space="preserve">30.236442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9104423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.562442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4809436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2053813934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.902660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7124938964844</t>
+    <t xml:space="preserve">29.9104404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5624408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250541687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4809398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2053852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9026622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.712495803833</t>
   </si>
   <si>
     <t xml:space="preserve">32.0203857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9207725524902</t>
+    <t xml:space="preserve">31.9207706451416</t>
   </si>
   <si>
     <t xml:space="preserve">32.618049621582</t>
@@ -1451,67 +1451,67 @@
     <t xml:space="preserve">32.690486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">32.962158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4602127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9039344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0527153015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3011016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.034595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0798797607422</t>
+    <t xml:space="preserve">32.9621658325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4602088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9039268493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0527114868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3011054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0798873901367</t>
   </si>
   <si>
     <t xml:space="preserve">33.3153228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6866073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.075984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3929328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2350959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.678825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4416885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4749374389648</t>
+    <t xml:space="preserve">33.6865997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0759925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0941047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.392936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2350997924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4416923522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4749336242676</t>
   </si>
   <si>
     <t xml:space="preserve">33.7270622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5022964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8065032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0071487426758</t>
+    <t xml:space="preserve">34.5022926330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8064994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.007152557373</t>
   </si>
   <si>
     <t xml:space="preserve">34.8671073913574</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">35.1589584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156318664551</t>
+    <t xml:space="preserve">35.8156280517578</t>
   </si>
   <si>
     <t xml:space="preserve">35.8429870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3354873657227</t>
+    <t xml:space="preserve">36.3354835510254</t>
   </si>
   <si>
     <t xml:space="preserve">37.7035369873047</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">36.2534027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5940933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.904182434082</t>
+    <t xml:space="preserve">37.2748756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9041862487793</t>
   </si>
   <si>
     <t xml:space="preserve">38.4696502685547</t>
@@ -1553,22 +1553,22 @@
     <t xml:space="preserve">38.3602066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8221054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6546936035156</t>
+    <t xml:space="preserve">37.8221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6546974182129</t>
   </si>
   <si>
     <t xml:space="preserve">36.3446083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">36.28076171875</t>
+    <t xml:space="preserve">36.2807655334473</t>
   </si>
   <si>
     <t xml:space="preserve">36.0892372131348</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4143295288086</t>
+    <t xml:space="preserve">35.4143333435059</t>
   </si>
   <si>
     <t xml:space="preserve">35.3960914611816</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">35.5146522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1042404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5693740844727</t>
+    <t xml:space="preserve">35.1042366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5693778991699</t>
   </si>
   <si>
     <t xml:space="preserve">35.3504867553711</t>
@@ -1589,43 +1589,43 @@
     <t xml:space="preserve">34.5205345153809</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7453002929688</t>
+    <t xml:space="preserve">33.9550704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.745304107666</t>
   </si>
   <si>
     <t xml:space="preserve">34.2925224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0586357116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1830863952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8397445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.596736907959</t>
+    <t xml:space="preserve">35.0586318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8397483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5967330932617</t>
   </si>
   <si>
     <t xml:space="preserve">35.1224784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.469051361084</t>
+    <t xml:space="preserve">35.6241035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4690475463867</t>
   </si>
   <si>
     <t xml:space="preserve">35.3869667053223</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2410430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1621971130371</t>
+    <t xml:space="preserve">35.241039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1622009277344</t>
   </si>
   <si>
     <t xml:space="preserve">34.8853492736816</t>
@@ -1637,25 +1637,25 @@
     <t xml:space="preserve">33.8091468811035</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4019775390625</t>
+    <t xml:space="preserve">34.4019660949707</t>
   </si>
   <si>
     <t xml:space="preserve">34.2013244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4169692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2651634216309</t>
+    <t xml:space="preserve">33.4169731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2651672363281</t>
   </si>
   <si>
     <t xml:space="preserve">34.3746109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5387725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7303047180176</t>
+    <t xml:space="preserve">34.5387763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7303009033203</t>
   </si>
   <si>
     <t xml:space="preserve">34.6208610534668</t>
@@ -1667,43 +1667,43 @@
     <t xml:space="preserve">34.8215065002441</t>
   </si>
   <si>
-    <t xml:space="preserve">34.484058380127</t>
+    <t xml:space="preserve">34.4840545654297</t>
   </si>
   <si>
     <t xml:space="preserve">34.7941474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5784912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.153076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172492980957</t>
+    <t xml:space="preserve">35.5784950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1530799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172416687012</t>
   </si>
   <si>
     <t xml:space="preserve">35.5328941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5055313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1133575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8365058898926</t>
+    <t xml:space="preserve">35.5055389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1133613586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8365097045898</t>
   </si>
   <si>
     <t xml:space="preserve">34.2834053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3381271362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3016471862793</t>
+    <t xml:space="preserve">34.3381309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3016510009766</t>
   </si>
   <si>
     <t xml:space="preserve">34.785026550293</t>
@@ -1715,151 +1715,151 @@
     <t xml:space="preserve">34.6117401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4202041625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5934982299805</t>
+    <t xml:space="preserve">34.4202117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5935020446777</t>
   </si>
   <si>
     <t xml:space="preserve">34.511417388916</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0827598571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110870361328</t>
+    <t xml:space="preserve">34.0827560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110946655273</t>
   </si>
   <si>
     <t xml:space="preserve">34.6664619445801</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2228012084961</t>
+    <t xml:space="preserve">35.2227973937988</t>
   </si>
   <si>
     <t xml:space="preserve">34.940071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9791946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300323486328</t>
+    <t xml:space="preserve">32.9791984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300380706787</t>
   </si>
   <si>
     <t xml:space="preserve">32.4593353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9388771057129</t>
+    <t xml:space="preserve">28.9388790130615</t>
   </si>
   <si>
     <t xml:space="preserve">28.5284633636475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2001323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2639713287354</t>
+    <t xml:space="preserve">28.2001304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.263973236084</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4554996490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7258720397949</t>
+    <t xml:space="preserve">28.4555015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7258701324463</t>
   </si>
   <si>
     <t xml:space="preserve">27.7988338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6587905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2698554992676</t>
+    <t xml:space="preserve">26.6587924957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">27.9082794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5708274841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1786518096924</t>
+    <t xml:space="preserve">27.5708255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1786499023438</t>
   </si>
   <si>
     <t xml:space="preserve">27.5434665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9994869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0906848907471</t>
+    <t xml:space="preserve">27.9994831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0906867980957</t>
   </si>
   <si>
     <t xml:space="preserve">29.5499439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1942501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1304054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.452262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0392017364502</t>
+    <t xml:space="preserve">29.1942462921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.97536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.130407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.692626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4522647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0392036437988</t>
   </si>
   <si>
     <t xml:space="preserve">28.0268440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0359668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3519401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2666149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.85032081604</t>
+    <t xml:space="preserve">28.0359630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2666130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503170013428</t>
   </si>
   <si>
     <t xml:space="preserve">26.8138370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4340209960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2060127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7317523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9141616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.807954788208</t>
+    <t xml:space="preserve">27.4340229034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2060146331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7317543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9141597747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079528808594</t>
   </si>
   <si>
     <t xml:space="preserve">26.7682361602783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3063354492188</t>
+    <t xml:space="preserve">27.3063373565674</t>
   </si>
   <si>
     <t xml:space="preserve">26.5128631591797</t>
@@ -1868,61 +1868,61 @@
     <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4822654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.327220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9565238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265735626221</t>
+    <t xml:space="preserve">25.4822673797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3272190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265697479248</t>
   </si>
   <si>
     <t xml:space="preserve">24.6431922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1721725463867</t>
+    <t xml:space="preserve">25.1721744537354</t>
   </si>
   <si>
     <t xml:space="preserve">25.7011566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">25.144811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3454627990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5825862884521</t>
+    <t xml:space="preserve">25.1448135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3454608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5825901031494</t>
   </si>
   <si>
     <t xml:space="preserve">26.385181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.59494972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3636989593506</t>
+    <t xml:space="preserve">26.5949459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3637008666992</t>
   </si>
   <si>
     <t xml:space="preserve">26.467264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1877727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.935640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6014270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1454105377197</t>
+    <t xml:space="preserve">27.1877708435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6014289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1454067230225</t>
   </si>
   <si>
     <t xml:space="preserve">27.0600852966309</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">27.0327243804932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3336963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4066600799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6711483001709</t>
+    <t xml:space="preserve">27.3336982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4066581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6711502075195</t>
   </si>
   <si>
     <t xml:space="preserve">27.8991584777832</t>
@@ -1949,91 +1949,91 @@
     <t xml:space="preserve">27.9538803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.880916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2366123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9147567749023</t>
+    <t xml:space="preserve">27.8809185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9147548675537</t>
   </si>
   <si>
     <t xml:space="preserve">30.0059623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">30.598783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7994327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4437389373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6443881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9362335205078</t>
+    <t xml:space="preserve">30.5987815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7994346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2007255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4437370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6443843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9362354278564</t>
   </si>
   <si>
     <t xml:space="preserve">31.7023410797119</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9121189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284091949463</t>
+    <t xml:space="preserve">31.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284111022949</t>
   </si>
   <si>
     <t xml:space="preserve">31.8117923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7753086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6567440032959</t>
+    <t xml:space="preserve">31.7753067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6567401885986</t>
   </si>
   <si>
     <t xml:space="preserve">31.6476249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4743366241455</t>
+    <t xml:space="preserve">31.4743404388428</t>
   </si>
   <si>
     <t xml:space="preserve">31.9668388366699</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9029903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1557197570801</t>
+    <t xml:space="preserve">31.9029922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1557235717773</t>
   </si>
   <si>
     <t xml:space="preserve">33.7909049987793</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9244728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8332710266113</t>
+    <t xml:space="preserve">32.9244689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8332748413086</t>
   </si>
   <si>
     <t xml:space="preserve">32.696460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5140609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5778961181641</t>
+    <t xml:space="preserve">32.5140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5779037475586</t>
   </si>
   <si>
     <t xml:space="preserve">32.4319763183594</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">33.0065536499023</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5264167785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1980819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2313270568848</t>
+    <t xml:space="preserve">33.5264205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1980895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2313232421875</t>
   </si>
   <si>
     <t xml:space="preserve">31.7388248443604</t>
@@ -2066,37 +2066,37 @@
     <t xml:space="preserve">33.5081787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6084976196289</t>
+    <t xml:space="preserve">33.6085014343262</t>
   </si>
   <si>
     <t xml:space="preserve">34.1283569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9277153015137</t>
+    <t xml:space="preserve">33.9277114868164</t>
   </si>
   <si>
     <t xml:space="preserve">33.8638725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8150329589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6599884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2163238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2892875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0977592468262</t>
+    <t xml:space="preserve">32.8150291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.659984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2163200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2892837524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0977630615234</t>
   </si>
   <si>
     <t xml:space="preserve">33.4260940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1160049438477</t>
+    <t xml:space="preserve">33.1160011291504</t>
   </si>
   <si>
     <t xml:space="preserve">33.3075294494629</t>
@@ -2105,28 +2105,28 @@
     <t xml:space="preserve">33.872989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">33.681468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.061279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3440093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531341552734</t>
+    <t xml:space="preserve">33.6814613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3440132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531303405762</t>
   </si>
   <si>
     <t xml:space="preserve">33.2345657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9185905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1616020202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5505332946777</t>
+    <t xml:space="preserve">33.918586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1616058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.550537109375</t>
   </si>
   <si>
     <t xml:space="preserve">32.4046096801758</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">33.4443321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9485950469971</t>
+    <t xml:space="preserve">31.9485969543457</t>
   </si>
   <si>
     <t xml:space="preserve">32.6873474121094</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">31.8863296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8363723754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586578369141</t>
+    <t xml:space="preserve">32.836368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8586597442627</t>
   </si>
   <si>
     <t xml:space="preserve">32.2552795410156</t>
@@ -2165,61 +2165,61 @@
     <t xml:space="preserve">32.2829475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7848663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382095336914</t>
+    <t xml:space="preserve">31.7848701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226844787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4382057189941</t>
   </si>
   <si>
     <t xml:space="preserve">30.5581169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1207656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217658996582</t>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217601776123</t>
   </si>
   <si>
     <t xml:space="preserve">32.0062370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6649589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169204711914</t>
+    <t xml:space="preserve">31.6649684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169242858887</t>
   </si>
   <si>
     <t xml:space="preserve">31.7387466430664</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8125381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290710449219</t>
+    <t xml:space="preserve">31.8125400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290672302246</t>
   </si>
   <si>
     <t xml:space="preserve">32.6518974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6480522155762</t>
+    <t xml:space="preserve">33.6480560302734</t>
   </si>
   <si>
     <t xml:space="preserve">33.7679634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7087783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5058555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4136276245117</t>
+    <t xml:space="preserve">34.7087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5058631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4136238098145</t>
   </si>
   <si>
     <t xml:space="preserve">33.7864112854004</t>
@@ -2234,16 +2234,16 @@
     <t xml:space="preserve">34.6811065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0500564575195</t>
+    <t xml:space="preserve">35.0500526428223</t>
   </si>
   <si>
     <t xml:space="preserve">34.9762687683105</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6127052307129</t>
+    <t xml:space="preserve">35.5112457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6127014160156</t>
   </si>
   <si>
     <t xml:space="preserve">35.5204658508301</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">35.5296897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2806510925293</t>
+    <t xml:space="preserve">35.2806549072266</t>
   </si>
   <si>
     <t xml:space="preserve">35.3544425964355</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">35.1330718994141</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2253074645996</t>
+    <t xml:space="preserve">35.2253112792969</t>
   </si>
   <si>
     <t xml:space="preserve">35.2437553405762</t>
@@ -2279,25 +2279,25 @@
     <t xml:space="preserve">35.658821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6403732299805</t>
+    <t xml:space="preserve">35.6403770446777</t>
   </si>
   <si>
     <t xml:space="preserve">35.9263114929199</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9908714294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9632034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6903381347656</t>
+    <t xml:space="preserve">35.9908752441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9632110595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6903343200684</t>
   </si>
   <si>
     <t xml:space="preserve">34.2844924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4451293945312</t>
+    <t xml:space="preserve">33.4451332092285</t>
   </si>
   <si>
     <t xml:space="preserve">31.4620380401611</t>
@@ -2306,58 +2306,61 @@
     <t xml:space="preserve">31.4343719482422</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8309841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4989337921143</t>
+    <t xml:space="preserve">31.8309898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5596542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4989318847656</t>
   </si>
   <si>
     <t xml:space="preserve">31.2314472198486</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7572002410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6926364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7072372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.747974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5542793273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3605785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3052310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435920715332</t>
+    <t xml:space="preserve">31.7571964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6926345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7072410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7479705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5542774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3605804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3052368164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435901641846</t>
   </si>
   <si>
     <t xml:space="preserve">31.6465167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3382873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1684226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7349166870117</t>
+    <t xml:space="preserve">32.3382911682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0761871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1684188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7349090576172</t>
   </si>
   <si>
     <t xml:space="preserve">32.5412101745605</t>
@@ -2366,13 +2369,13 @@
     <t xml:space="preserve">32.6242256164551</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6426696777344</t>
+    <t xml:space="preserve">32.6426734924316</t>
   </si>
   <si>
     <t xml:space="preserve">32.375186920166</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6372890472412</t>
+    <t xml:space="preserve">31.6372871398926</t>
   </si>
   <si>
     <t xml:space="preserve">31.4804878234863</t>
@@ -2387,10 +2390,10 @@
     <t xml:space="preserve">30.0877075195312</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7279853820801</t>
+    <t xml:space="preserve">29.6080760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7279815673828</t>
   </si>
   <si>
     <t xml:space="preserve">29.6449699401855</t>
@@ -2402,31 +2405,31 @@
     <t xml:space="preserve">30.3367481231689</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1614971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8294448852539</t>
+    <t xml:space="preserve">30.1614990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8294429779053</t>
   </si>
   <si>
     <t xml:space="preserve">29.1376686096191</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6173000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0139198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1983947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.050817489624</t>
+    <t xml:space="preserve">29.6172981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.198392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
     <t xml:space="preserve">30.6134586334229</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1945533752441</t>
+    <t xml:space="preserve">31.1945514678955</t>
   </si>
   <si>
     <t xml:space="preserve">31.803316116333</t>
@@ -2438,10 +2441,10 @@
     <t xml:space="preserve">31.425142288208</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0285243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.724142074585</t>
+    <t xml:space="preserve">31.0285263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7241439819336</t>
   </si>
   <si>
     <t xml:space="preserve">29.6726398468018</t>
@@ -2450,7 +2453,7 @@
     <t xml:space="preserve">29.9770240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7740993499756</t>
+    <t xml:space="preserve">29.7741031646729</t>
   </si>
   <si>
     <t xml:space="preserve">29.691089630127</t>
@@ -2459,49 +2462,49 @@
     <t xml:space="preserve">29.9678001403809</t>
   </si>
   <si>
-    <t xml:space="preserve">33.362117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7441329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9877910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4397468566895</t>
+    <t xml:space="preserve">33.3621215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7441291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9877891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4397506713867</t>
   </si>
   <si>
     <t xml:space="preserve">32.5504379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">32.310619354248</t>
+    <t xml:space="preserve">32.3106155395508</t>
   </si>
   <si>
     <t xml:space="preserve">34.2291488647461</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7180099487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3121643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0907936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0077781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6111640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7218437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9801063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2199211120605</t>
+    <t xml:space="preserve">34.7180061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0907897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0077819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6111602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.721851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.980110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2199249267578</t>
   </si>
   <si>
     <t xml:space="preserve">34.819465637207</t>
@@ -2510,16 +2513,16 @@
     <t xml:space="preserve">34.5243072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0462226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1476783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.02392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6826515197754</t>
+    <t xml:space="preserve">36.0462188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1476745605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0239334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6826477050781</t>
   </si>
   <si>
     <t xml:space="preserve">35.7787322998047</t>
@@ -2528,9 +2531,6 @@
     <t xml:space="preserve">35.6772727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156280517578</t>
-  </si>
-  <si>
     <t xml:space="preserve">38.1492195129395</t>
   </si>
   <si>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">38.545841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8225479125977</t>
+    <t xml:space="preserve">38.8225517272949</t>
   </si>
   <si>
     <t xml:space="preserve">38.093879699707</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">37.7249336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1530609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3006362915039</t>
+    <t xml:space="preserve">37.1530570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3006401062012</t>
   </si>
   <si>
     <t xml:space="preserve">37.0423774719238</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">37.1899566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7157096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6234703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4758911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9593620300293</t>
+    <t xml:space="preserve">37.715705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6234664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4758949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9593658447266</t>
   </si>
   <si>
     <t xml:space="preserve">37.4389991760254</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">37.1438369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9647445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9462966918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5496788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6326942443848</t>
+    <t xml:space="preserve">37.9647483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9463005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5496826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.632698059082</t>
   </si>
   <si>
     <t xml:space="preserve">38.3613662719727</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">39.385196685791</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1399955749512</t>
+    <t xml:space="preserve">38.1399917602539</t>
   </si>
   <si>
     <t xml:space="preserve">37.2914161682129</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2691268920898</t>
+    <t xml:space="preserve">38.2691345214844</t>
   </si>
   <si>
     <t xml:space="preserve">37.2084045410156</t>
@@ -2624,31 +2624,31 @@
     <t xml:space="preserve">37.402099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8432922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2360801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.488956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9724311828613</t>
+    <t xml:space="preserve">35.8432960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2360763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4889602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9724273681641</t>
   </si>
   <si>
     <t xml:space="preserve">36.3690452575684</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8579063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2729682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5166282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7049369812012</t>
+    <t xml:space="preserve">36.8579025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5166244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7049407958984</t>
   </si>
   <si>
     <t xml:space="preserve">36.6457557678223</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">35.649600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2583656311035</t>
+    <t xml:space="preserve">36.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">35.1422958374023</t>
@@ -2666,16 +2666,16 @@
     <t xml:space="preserve">35.2898750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0093231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2660484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4305305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4028587341309</t>
+    <t xml:space="preserve">36.0093269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.266040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4028625488281</t>
   </si>
   <si>
     <t xml:space="preserve">32.9286117553711</t>
@@ -2687,25 +2687,25 @@
     <t xml:space="preserve">32.4858665466309</t>
   </si>
   <si>
-    <t xml:space="preserve">31.10231590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1507339477539</t>
+    <t xml:space="preserve">31.1023197174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1507320404053</t>
   </si>
   <si>
     <t xml:space="preserve">27.8002300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0807857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.981616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3943881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2637100219727</t>
+    <t xml:space="preserve">27.0807819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9816188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3943901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2637138366699</t>
   </si>
   <si>
     <t xml:space="preserve">24.9039878845215</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">25.3651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.922435760498</t>
+    <t xml:space="preserve">24.9224376678467</t>
   </si>
   <si>
     <t xml:space="preserve">26.9977703094482</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3797836303711</t>
+    <t xml:space="preserve">26.3797817230225</t>
   </si>
   <si>
     <t xml:space="preserve">29.9309062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4528179168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.729528427124</t>
+    <t xml:space="preserve">31.4528160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7295265197754</t>
   </si>
   <si>
     <t xml:space="preserve">30.705696105957</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857051849365</t>
+    <t xml:space="preserve">28.6857032775879</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688003540039</t>
@@ -2750,31 +2750,31 @@
     <t xml:space="preserve">30.1061553955078</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2998523712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0838642120361</t>
+    <t xml:space="preserve">30.2998504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.083869934082</t>
   </si>
   <si>
     <t xml:space="preserve">30.6319065093994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8402118682861</t>
+    <t xml:space="preserve">31.8402137756348</t>
   </si>
   <si>
     <t xml:space="preserve">32.513542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.890172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5765628814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5081558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756462097168</t>
+    <t xml:space="preserve">30.8901748657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.576566696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5081577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756404876709</t>
   </si>
   <si>
     <t xml:space="preserve">30.2721824645996</t>
@@ -2783,22 +2783,22 @@
     <t xml:space="preserve">30.7702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9124584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2352848052979</t>
+    <t xml:space="preserve">29.9124565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2352867126465</t>
   </si>
   <si>
     <t xml:space="preserve">29.7833251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2260665893555</t>
+    <t xml:space="preserve">30.2260627746582</t>
   </si>
   <si>
     <t xml:space="preserve">29.4143772125244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7041549682617</t>
+    <t xml:space="preserve">28.7041530609131</t>
   </si>
   <si>
     <t xml:space="preserve">28.6211414337158</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">29.7372093200684</t>
   </si>
   <si>
-    <t xml:space="preserve">29.866340637207</t>
+    <t xml:space="preserve">29.8663387298584</t>
   </si>
   <si>
     <t xml:space="preserve">28.8056125640869</t>
@@ -2816,22 +2816,22 @@
     <t xml:space="preserve">29.3682594299316</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7979354858398</t>
+    <t xml:space="preserve">30.7979335784912</t>
   </si>
   <si>
     <t xml:space="preserve">30.3920936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1630363464355</t>
+    <t xml:space="preserve">32.1630439758301</t>
   </si>
   <si>
     <t xml:space="preserve">30.8532752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955574035645</t>
+    <t xml:space="preserve">31.0746402740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955535888672</t>
   </si>
   <si>
     <t xml:space="preserve">32.0339088439941</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">31.0377502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3790283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9693450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4950942993164</t>
+    <t xml:space="preserve">31.3790264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9693393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4950904846191</t>
   </si>
   <si>
     <t xml:space="preserve">32.762580871582</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">33.0577392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0892524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7203044891357</t>
+    <t xml:space="preserve">32.0892562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7203006744385</t>
   </si>
   <si>
     <t xml:space="preserve">32.126148223877</t>
@@ -2873,46 +2873,46 @@
     <t xml:space="preserve">31.6003932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9508953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591171264648</t>
+    <t xml:space="preserve">31.9509010314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">31.9601192474365</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4897060394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6503505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0100746154785</t>
+    <t xml:space="preserve">31.4897117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.351354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.650354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0100765228271</t>
   </si>
   <si>
     <t xml:space="preserve">30.5950088500977</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0692577362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0969333648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4236011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5804042816162</t>
+    <t xml:space="preserve">30.0692596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0969295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4236030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5804061889648</t>
   </si>
   <si>
     <t xml:space="preserve">29.488166809082</t>
@@ -2921,25 +2921,25 @@
     <t xml:space="preserve">30.8809452056885</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3275241851807</t>
+    <t xml:space="preserve">30.3275260925293</t>
   </si>
   <si>
     <t xml:space="preserve">30.0784854888916</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5342884063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8571128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0046920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5857906341553</t>
+    <t xml:space="preserve">29.5342864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5527362823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8571147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0046939849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">29.884786605835</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">31.1484355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">31.794095993042</t>
+    <t xml:space="preserve">31.7940940856934</t>
   </si>
   <si>
     <t xml:space="preserve">32.1814842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4766502380371</t>
+    <t xml:space="preserve">32.4766426086426</t>
   </si>
   <si>
     <t xml:space="preserve">33.8878746032715</t>
@@ -2966,22 +2966,22 @@
     <t xml:space="preserve">34.9854927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3306121826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6665000915527</t>
+    <t xml:space="preserve">34.3306159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.66650390625</t>
   </si>
   <si>
     <t xml:space="preserve">32.4674224853516</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0431327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.448974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2644958496094</t>
+    <t xml:space="preserve">32.0431365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4489784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2644996643066</t>
   </si>
   <si>
     <t xml:space="preserve">32.8455924987793</t>
@@ -2990,28 +2990,28 @@
     <t xml:space="preserve">32.7164649963379</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6019325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8509788513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2237663269043</t>
+    <t xml:space="preserve">33.6019401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8509750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2237701416016</t>
   </si>
   <si>
     <t xml:space="preserve">33.5650405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9339904785156</t>
+    <t xml:space="preserve">33.9339942932129</t>
   </si>
   <si>
     <t xml:space="preserve">34.0354537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6057739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9432144165039</t>
+    <t xml:space="preserve">32.6057777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9432106018066</t>
   </si>
   <si>
     <t xml:space="preserve">34.9485969543457</t>
@@ -3020,52 +3020,52 @@
     <t xml:space="preserve">34.4043998718262</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9170837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.127685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1907119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3936347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.205322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5465927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8840255737305</t>
+    <t xml:space="preserve">35.9170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1276893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1907157897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3936309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2053184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5465965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8840293884277</t>
   </si>
   <si>
     <t xml:space="preserve">34.6349906921387</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5996360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6273155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3467597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7195434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8909606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6142463684082</t>
+    <t xml:space="preserve">36.5996398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6273078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3467636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7195472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8909568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8725090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6142425537109</t>
   </si>
   <si>
     <t xml:space="preserve">37.4482192993164</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">38.7118682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6473045349121</t>
+    <t xml:space="preserve">38.6473007202148</t>
   </si>
   <si>
     <t xml:space="preserve">38.241455078125</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">37.8263893127441</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9001770019531</t>
+    <t xml:space="preserve">37.9001808166504</t>
   </si>
   <si>
     <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2837333679199</t>
+    <t xml:space="preserve">39.2837371826172</t>
   </si>
   <si>
     <t xml:space="preserve">39.8463859558105</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">40.5842781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4144172668457</t>
+    <t xml:space="preserve">41.4144134521484</t>
   </si>
   <si>
     <t xml:space="preserve">42.9916648864746</t>
@@ -3110,37 +3110,37 @@
     <t xml:space="preserve">42.8533058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8863639831543</t>
+    <t xml:space="preserve">43.8863677978516</t>
   </si>
   <si>
     <t xml:space="preserve">44.1630744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0116500854492</t>
+    <t xml:space="preserve">45.0116539001465</t>
   </si>
   <si>
     <t xml:space="preserve">44.928638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1961250305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7349472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8679122924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6242561340332</t>
+    <t xml:space="preserve">45.1961326599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7349433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8679161071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
     <t xml:space="preserve">44.467456817627</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8694610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.395206451416</t>
+    <t xml:space="preserve">45.869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3952102661133</t>
   </si>
   <si>
     <t xml:space="preserve">46.2476272583008</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">46.1184997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8456230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1077308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2737617492676</t>
+    <t xml:space="preserve">44.8456268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8640747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1077270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3290977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2737579345703</t>
   </si>
   <si>
     <t xml:space="preserve">43.3882827758789</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0708312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6742172241211</t>
+    <t xml:space="preserve">44.0708351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6742134094238</t>
   </si>
   <si>
     <t xml:space="preserve">44.6703758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">43.950927734375</t>
+    <t xml:space="preserve">43.9509315490723</t>
   </si>
   <si>
     <t xml:space="preserve">44.8917427062988</t>
@@ -3188,37 +3188,37 @@
     <t xml:space="preserve">45.7403259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6649932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5912055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3567733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7756805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1999740600586</t>
+    <t xml:space="preserve">43.6649971008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5912017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3567695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7756767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1999664306641</t>
   </si>
   <si>
     <t xml:space="preserve">44.2091903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1369514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8932914733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5758438110352</t>
+    <t xml:space="preserve">46.1369476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8932876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">48.0739250183105</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6496315002441</t>
+    <t xml:space="preserve">47.6496353149414</t>
   </si>
   <si>
     <t xml:space="preserve">47.9447860717773</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">47.7972106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">46.708812713623</t>
+    <t xml:space="preserve">46.7088165283203</t>
   </si>
   <si>
     <t xml:space="preserve">46.6534729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1807708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8710021972656</t>
+    <t xml:space="preserve">49.1807632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8709983825684</t>
   </si>
   <si>
     <t xml:space="preserve">47.2437934875488</t>
@@ -3251,31 +3251,31 @@
     <t xml:space="preserve">47.0408706665039</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1700019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3175849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1108169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4613227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6865272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6165809631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.703426361084</t>
+    <t xml:space="preserve">47.1699981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3175773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1108207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4613151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6865310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6165771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7034301757812</t>
   </si>
   <si>
     <t xml:space="preserve">45.860237121582</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4136543273926</t>
+    <t xml:space="preserve">46.4136505126953</t>
   </si>
   <si>
     <t xml:space="preserve">45.7587776184082</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">46.8379440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2107353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6019668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3806076049805</t>
+    <t xml:space="preserve">46.2107315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6019706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3805999755859</t>
   </si>
   <si>
     <t xml:space="preserve">44.2276420593262</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4397850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4859046936035</t>
+    <t xml:space="preserve">44.4397888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4859008789062</t>
   </si>
   <si>
     <t xml:space="preserve">45.3898239135742</t>
@@ -3317,46 +3317,46 @@
     <t xml:space="preserve">45.0762214660645</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8417892456055</t>
+    <t xml:space="preserve">45.8417816162109</t>
   </si>
   <si>
     <t xml:space="preserve">45.6573143005371</t>
   </si>
   <si>
-    <t xml:space="preserve">46.450553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5981330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.524341583252</t>
+    <t xml:space="preserve">46.4505500793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5981292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5243377685547</t>
   </si>
   <si>
     <t xml:space="preserve">47.5020523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3544731140137</t>
+    <t xml:space="preserve">47.3544692993164</t>
   </si>
   <si>
     <t xml:space="preserve">46.321418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2952919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3467903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9670753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0039710998535</t>
+    <t xml:space="preserve">48.2952880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.346794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9670791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0039749145508</t>
   </si>
   <si>
     <t xml:space="preserve">47.0593185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4836006164551</t>
+    <t xml:space="preserve">47.4836082458496</t>
   </si>
   <si>
     <t xml:space="preserve">46.3767585754395</t>
@@ -3368,25 +3368,25 @@
     <t xml:space="preserve">47.2806854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7234230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9855194091797</t>
+    <t xml:space="preserve">47.7234191894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.985523223877</t>
   </si>
   <si>
     <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9263458251953</t>
+    <t xml:space="preserve">47.9263381958008</t>
   </si>
   <si>
     <t xml:space="preserve">48.664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4244232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1623153686523</t>
+    <t xml:space="preserve">48.4244270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1623191833496</t>
   </si>
   <si>
     <t xml:space="preserve">49.4205856323242</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">53.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9877777099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0621948242188</t>
+    <t xml:space="preserve">53.9877738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0621910095215</t>
   </si>
   <si>
     <t xml:space="preserve">53.4482727050781</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6343078613281</t>
+    <t xml:space="preserve">53.6343116760254</t>
   </si>
   <si>
     <t xml:space="preserve">54.1180038452148</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">54.229621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1039924621582</t>
+    <t xml:space="preserve">55.1039962768555</t>
   </si>
   <si>
     <t xml:space="preserve">54.8063354492188</t>
@@ -3431,28 +3431,28 @@
     <t xml:space="preserve">53.5784950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8343467712402</t>
+    <t xml:space="preserve">52.8343505859375</t>
   </si>
   <si>
     <t xml:space="preserve">52.8715591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1320114135742</t>
+    <t xml:space="preserve">53.132007598877</t>
   </si>
   <si>
     <t xml:space="preserve">53.8947563171387</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2482223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5086784362793</t>
+    <t xml:space="preserve">54.2482261657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.508674621582</t>
   </si>
   <si>
     <t xml:space="preserve">54.043586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1738128662109</t>
+    <t xml:space="preserve">54.1738166809082</t>
   </si>
   <si>
     <t xml:space="preserve">54.2110214233398</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">53.225025177002</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6901168823242</t>
+    <t xml:space="preserve">53.6901206970215</t>
   </si>
   <si>
     <t xml:space="preserve">53.5970993041992</t>
@@ -3488,85 +3488,85 @@
     <t xml:space="preserve">51.4762840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4250755310059</t>
+    <t xml:space="preserve">52.4250717163086</t>
   </si>
   <si>
     <t xml:space="preserve">53.2808380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7273254394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3598480224609</t>
+    <t xml:space="preserve">53.7273216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3598518371582</t>
   </si>
   <si>
     <t xml:space="preserve">52.7785453796387</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1460151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1878204345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7459335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.620304107666</t>
+    <t xml:space="preserve">52.1460189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1878242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7459259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6203002929688</t>
   </si>
   <si>
     <t xml:space="preserve">55.4388580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7551193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4946708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8761520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.950569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6389007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6947174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.527286529541</t>
+    <t xml:space="preserve">55.755126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8761558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9505729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6389083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6947135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5272789001465</t>
   </si>
   <si>
     <t xml:space="preserve">55.5876884460449</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9271507263184</t>
+    <t xml:space="preserve">56.9271545410156</t>
   </si>
   <si>
     <t xml:space="preserve">57.2992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7271118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5596771240234</t>
+    <t xml:space="preserve">57.7271156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5596809387207</t>
   </si>
   <si>
     <t xml:space="preserve">56.4248542785645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8667488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3970527648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0670051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1554260253906</t>
+    <t xml:space="preserve">55.8667411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3970565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.067008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1554222106934</t>
   </si>
   <si>
     <t xml:space="preserve">50.8437614440918</t>
@@ -3575,16 +3575,16 @@
     <t xml:space="preserve">50.7693481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">50.397274017334</t>
+    <t xml:space="preserve">50.3972702026367</t>
   </si>
   <si>
     <t xml:space="preserve">50.5461044311523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8065528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4158744812012</t>
+    <t xml:space="preserve">50.8065567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4158782958984</t>
   </si>
   <si>
     <t xml:space="preserve">51.0297966003418</t>
@@ -3593,19 +3593,19 @@
     <t xml:space="preserve">50.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2484474182129</t>
+    <t xml:space="preserve">50.2484436035156</t>
   </si>
   <si>
     <t xml:space="preserve">51.1042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">51.718132019043</t>
+    <t xml:space="preserve">51.7181282043457</t>
   </si>
   <si>
     <t xml:space="preserve">51.4018669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3274574279785</t>
+    <t xml:space="preserve">51.3274536132812</t>
   </si>
   <si>
     <t xml:space="preserve">50.8251571655273</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">48.0532150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0019989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5647087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3832664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1600227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0624084472656</t>
+    <t xml:space="preserve">49.0020027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5647048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3832702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1600189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0624046325684</t>
   </si>
   <si>
     <t xml:space="preserve">48.6113204956055</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2438430786133</t>
+    <t xml:space="preserve">49.2438468933105</t>
   </si>
   <si>
     <t xml:space="preserve">51.7553367614746</t>
@@ -3656,31 +3656,31 @@
     <t xml:space="preserve">52.9831771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4994850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4622802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7133140563965</t>
+    <t xml:space="preserve">52.4994812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4622764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.713321685791</t>
   </si>
   <si>
     <t xml:space="preserve">54.4714736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">55.569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7597198486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8341331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3876419067383</t>
+    <t xml:space="preserve">55.5690879821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0341835021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7597236633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8341293334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3876457214355</t>
   </si>
   <si>
     <t xml:space="preserve">55.9783668518066</t>
@@ -3704,25 +3704,25 @@
     <t xml:space="preserve">61.6524772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">62.880313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4012222290039</t>
+    <t xml:space="preserve">62.8803253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4012298583984</t>
   </si>
   <si>
     <t xml:space="preserve">61.4106254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7408981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8199081420898</t>
+    <t xml:space="preserve">60.7409019470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.754695892334</t>
+    <t xml:space="preserve">63.7546920776367</t>
   </si>
   <si>
     <t xml:space="preserve">64.3314056396484</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">64.2197875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5686454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0663604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593315124512</t>
+    <t xml:space="preserve">63.5686492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0663566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593238830566</t>
   </si>
   <si>
     <t xml:space="preserve">61.5408592224121</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">62.3222122192383</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3410301208496</t>
+    <t xml:space="preserve">58.3410339355469</t>
   </si>
   <si>
     <t xml:space="preserve">60.089771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6060791015625</t>
+    <t xml:space="preserve">59.6060829162598</t>
   </si>
   <si>
     <t xml:space="preserve">61.0385589599609</t>
@@ -3764,34 +3764,34 @@
     <t xml:space="preserve">60.9455337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">60.5920677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6896896362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4430160522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4710464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1547737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4478378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.629280090332</t>
+    <t xml:space="preserve">60.5920715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6896858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4430313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4710388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1547813415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4478340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6292762756348</t>
   </si>
   <si>
     <t xml:space="preserve">58.675895690918</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7503128051758</t>
+    <t xml:space="preserve">60.182788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7503089904785</t>
   </si>
   <si>
     <t xml:space="preserve">58.8061218261719</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">57.8573341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3224258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5642700195312</t>
+    <t xml:space="preserve">58.3224296569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5642738342285</t>
   </si>
   <si>
     <t xml:space="preserve">59.7549057006836</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">60.4618453979492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269371032715</t>
+    <t xml:space="preserve">60.9269332885742</t>
   </si>
   <si>
     <t xml:space="preserve">58.4154434204102</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">56.9643630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1644058227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7923316955566</t>
+    <t xml:space="preserve">56.1644020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7923278808594</t>
   </si>
   <si>
     <t xml:space="preserve">54.8807525634766</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">52.3134536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">52.536693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5693054199219</t>
+    <t xml:space="preserve">52.5366897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5693016052246</t>
   </si>
   <si>
     <t xml:space="preserve">52.4064674377441</t>
@@ -3878,28 +3878,28 @@
     <t xml:space="preserve">54.899356842041</t>
   </si>
   <si>
-    <t xml:space="preserve">55.271427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8389511108398</t>
+    <t xml:space="preserve">55.2714233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8389472961426</t>
   </si>
   <si>
     <t xml:space="preserve">54.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6437225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6391220092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1274108886719</t>
+    <t xml:space="preserve">51.6437149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6391181945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1274147033691</t>
   </si>
   <si>
     <t xml:space="preserve">51.2344398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9739837646484</t>
+    <t xml:space="preserve">50.9739875793457</t>
   </si>
   <si>
     <t xml:space="preserve">50.9181785583496</t>
@@ -3911,10 +3911,10 @@
     <t xml:space="preserve">48.4624938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8021774291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1230316162109</t>
+    <t xml:space="preserve">45.802173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1230354309082</t>
   </si>
   <si>
     <t xml:space="preserve">44.946403503418</t>
@@ -3926,43 +3926,43 @@
     <t xml:space="preserve">42.146556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4954261779785</t>
+    <t xml:space="preserve">41.495433807373</t>
   </si>
   <si>
     <t xml:space="preserve">44.974308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">43.997615814209</t>
+    <t xml:space="preserve">43.9976196289062</t>
   </si>
   <si>
     <t xml:space="preserve">44.6208419799805</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6487464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2441711425781</t>
+    <t xml:space="preserve">44.6487503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2441749572754</t>
   </si>
   <si>
     <t xml:space="preserve">45.7091522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7881622314453</t>
+    <t xml:space="preserve">46.7881660461426</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2951698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8207740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2021484375</t>
+    <t xml:space="preserve">47.1044273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2951736450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8207778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2021522521973</t>
   </si>
   <si>
     <t xml:space="preserve">46.2765655517578</t>
@@ -3974,31 +3974,31 @@
     <t xml:space="preserve">47.1974487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9275817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2810554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9555969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9882125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4392929077148</t>
+    <t xml:space="preserve">47.1788444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9275856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2810516357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9556007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.988208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4392967224121</t>
   </si>
   <si>
     <t xml:space="preserve">45.1603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0254173278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.453296661377</t>
+    <t xml:space="preserve">46.0254135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4533004760742</t>
   </si>
   <si>
     <t xml:space="preserve">47.0300140380859</t>
@@ -4010,10 +4010,10 @@
     <t xml:space="preserve">47.5881233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5277137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3510932922363</t>
+    <t xml:space="preserve">46.527717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
     <t xml:space="preserve">43.8301849365234</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">45.4300994873047</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2672691345215</t>
+    <t xml:space="preserve">46.2672653198242</t>
   </si>
   <si>
     <t xml:space="preserve">46.7695617675781</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5696334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6115379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9604148864746</t>
+    <t xml:space="preserve">45.5696296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6115417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9604110717773</t>
   </si>
   <si>
     <t xml:space="preserve">41.4861259460449</t>
@@ -4043,10 +4043,10 @@
     <t xml:space="preserve">39.7373847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9095230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8676147460938</t>
+    <t xml:space="preserve">38.9095268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8676109313965</t>
   </si>
   <si>
     <t xml:space="preserve">41.6163520812988</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">42.1930656433105</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2814903259277</t>
+    <t xml:space="preserve">41.281494140625</t>
   </si>
   <si>
     <t xml:space="preserve">42.1093482971191</t>
@@ -4067,16 +4067,16 @@
     <t xml:space="preserve">40.6489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0908508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.309497833252</t>
+    <t xml:space="preserve">40.0908546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3095016479492</t>
   </si>
   <si>
     <t xml:space="preserve">39.8945198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5640754699707</t>
+    <t xml:space="preserve">38.5640716552734</t>
   </si>
   <si>
     <t xml:space="preserve">38.6018180847168</t>
@@ -4088,10 +4088,10 @@
     <t xml:space="preserve">40.6588172912598</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3572578430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1779823303223</t>
+    <t xml:space="preserve">42.3572616577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.177978515625</t>
   </si>
   <si>
     <t xml:space="preserve">43.6499633789062</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801216125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.234790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.111930847168</t>
+    <t xml:space="preserve">43.4801177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2347869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1119346618652</t>
   </si>
   <si>
     <t xml:space="preserve">41.2155303955078</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">38.9886856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6678657531738</t>
+    <t xml:space="preserve">38.6678695678711</t>
   </si>
   <si>
     <t xml:space="preserve">37.9507484436035</t>
@@ -4190,10 +4190,10 @@
     <t xml:space="preserve">38.5735092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1587219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3474388122559</t>
+    <t xml:space="preserve">40.1587257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3474349975586</t>
   </si>
   <si>
     <t xml:space="preserve">40.7531776428223</t>
@@ -4220,10 +4220,10 @@
     <t xml:space="preserve">45.9806060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0464630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3389701843262</t>
+    <t xml:space="preserve">45.046459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3389663696289</t>
   </si>
   <si>
     <t xml:space="preserve">46.5278854370117</t>
@@ -4235,13 +4235,13 @@
     <t xml:space="preserve">46.4995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8579406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7165908813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9524917602539</t>
+    <t xml:space="preserve">45.8579368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7165946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9524879455566</t>
   </si>
   <si>
     <t xml:space="preserve">46.5939331054688</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">46.1315765380859</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0273971557617</t>
+    <t xml:space="preserve">44.0273933410645</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
@@ -4268,16 +4268,16 @@
     <t xml:space="preserve">45.2163047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2729187011719</t>
+    <t xml:space="preserve">45.2729225158691</t>
   </si>
   <si>
     <t xml:space="preserve">43.046070098877</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1496734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3100814819336</t>
+    <t xml:space="preserve">42.1496696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3100852966309</t>
   </si>
   <si>
     <t xml:space="preserve">42.1213684082031</t>
@@ -4286,10 +4286,10 @@
     <t xml:space="preserve">41.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2251625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1400451660156</t>
+    <t xml:space="preserve">42.2251586914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
     <t xml:space="preserve">41.1777877807617</t>
@@ -4301,13 +4301,13 @@
     <t xml:space="preserve">41.6967544555664</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4704895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9988975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0175704956055</t>
+    <t xml:space="preserve">42.4704856872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.998893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0175743103027</t>
   </si>
   <si>
     <t xml:space="preserve">42.7158203125</t>
@@ -4331,13 +4331,13 @@
     <t xml:space="preserve">39.9511375427246</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2623252868652</t>
+    <t xml:space="preserve">39.262321472168</t>
   </si>
   <si>
     <t xml:space="preserve">40.6210746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5644645690918</t>
+    <t xml:space="preserve">40.5644607543945</t>
   </si>
   <si>
     <t xml:space="preserve">41.0645599365234</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703903198242</t>
+    <t xml:space="preserve">41.9703941345215</t>
   </si>
   <si>
     <t xml:space="preserve">41.5174751281738</t>
@@ -4376,19 +4376,19 @@
     <t xml:space="preserve">42.7252540588379</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8009338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0557060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7160186767578</t>
+    <t xml:space="preserve">43.8009376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0557022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7160148620605</t>
   </si>
   <si>
     <t xml:space="preserve">44.6690330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3574600219727</t>
+    <t xml:space="preserve">43.3574562072754</t>
   </si>
   <si>
     <t xml:space="preserve">43.4329414367676</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">45.6692237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7443237304688</t>
+    <t xml:space="preserve">43.7443199157715</t>
   </si>
   <si>
     <t xml:space="preserve">42.734691619873</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2249641418457</t>
+    <t xml:space="preserve">41.224967956543</t>
   </si>
   <si>
     <t xml:space="preserve">41.6873207092285</t>
@@ -4421,13 +4421,13 @@
     <t xml:space="preserve">42.8290481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9422798156738</t>
+    <t xml:space="preserve">42.9422760009766</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0840148925781</t>
+    <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">46.7732124328613</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">47.1978225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0657196044922</t>
+    <t xml:space="preserve">47.0657234191895</t>
   </si>
   <si>
     <t xml:space="preserve">47.0185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.631477355957</t>
+    <t xml:space="preserve">45.6314811706543</t>
   </si>
   <si>
     <t xml:space="preserve">45.6031723022461</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">45.2917938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8200073242188</t>
+    <t xml:space="preserve">44.8200035095215</t>
   </si>
   <si>
     <t xml:space="preserve">46.2825508117676</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">48.7452926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6316757202148</t>
+    <t xml:space="preserve">46.6316719055176</t>
   </si>
   <si>
     <t xml:space="preserve">46.4146499633789</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">46.150447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3861503601074</t>
+    <t xml:space="preserve">45.3861465454102</t>
   </si>
   <si>
     <t xml:space="preserve">46.6788520812988</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017120361328</t>
+    <t xml:space="preserve">47.8017158508301</t>
   </si>
   <si>
     <t xml:space="preserve">47.5563812255859</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">49.3869247436523</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7077407836914</t>
+    <t xml:space="preserve">49.7077445983887</t>
   </si>
   <si>
     <t xml:space="preserve">48.9717483520508</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">52.3497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8781661987305</t>
+    <t xml:space="preserve">52.8781700134277</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">53.2555961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5199966430664</t>
+    <t xml:space="preserve">54.5199928283691</t>
   </si>
   <si>
     <t xml:space="preserve">54.0859489440918</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4446983337402</t>
+    <t xml:space="preserve">55.4447021484375</t>
   </si>
   <si>
     <t xml:space="preserve">54.1991767883301</t>
@@ -4604,16 +4604,16 @@
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9349746704102</t>
+    <t xml:space="preserve">53.5009307861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9349784851074</t>
   </si>
   <si>
     <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4067649841309</t>
+    <t xml:space="preserve">54.4067687988281</t>
   </si>
   <si>
     <t xml:space="preserve">54.4445114135742</t>
@@ -4622,31 +4622,31 @@
     <t xml:space="preserve">55.3503456115723</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3126029968262</t>
+    <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
     <t xml:space="preserve">54.9729118347168</t>
   </si>
   <si>
-    <t xml:space="preserve">54.46337890625</t>
+    <t xml:space="preserve">54.4633827209473</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106544494629</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5388679504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3316688537598</t>
+    <t xml:space="preserve">54.5388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3507308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1431465148926</t>
+    <t xml:space="preserve">57.3507347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1431427001953</t>
   </si>
   <si>
     <t xml:space="preserve">57.7470359802246</t>
@@ -4673,10 +4673,10 @@
     <t xml:space="preserve">57.6526718139648</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2184371948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2939224243164</t>
+    <t xml:space="preserve">56.2184410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2939262390137</t>
   </si>
   <si>
     <t xml:space="preserve">57.5017051696777</t>
@@ -4685,13 +4685,13 @@
     <t xml:space="preserve">57.9546203613281</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1433372497559</t>
+    <t xml:space="preserve">58.1433410644531</t>
   </si>
   <si>
     <t xml:space="preserve">57.2186279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2752456665039</t>
+    <t xml:space="preserve">57.2752494812012</t>
   </si>
   <si>
     <t xml:space="preserve">58.9170761108398</t>
@@ -4700,13 +4700,13 @@
     <t xml:space="preserve">58.8982009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9550094604492</t>
+    <t xml:space="preserve">59.9550132751465</t>
   </si>
   <si>
     <t xml:space="preserve">60.1059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0116271972656</t>
+    <t xml:space="preserve">60.0116233825684</t>
   </si>
   <si>
     <t xml:space="preserve">60.6155128479004</t>
@@ -4718,46 +4718,46 @@
     <t xml:space="preserve">59.8417778015137</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4266052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0686225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2196006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9929466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8044242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2007255554199</t>
+    <t xml:space="preserve">59.4266090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0686264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2196083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9929504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8044204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2007293701172</t>
   </si>
   <si>
     <t xml:space="preserve">63.1443023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4085121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8614311218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7293243408203</t>
+    <t xml:space="preserve">63.408504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8614234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7293319702148</t>
   </si>
   <si>
     <t xml:space="preserve">63.9935264587402</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3707733154297</t>
+    <t xml:space="preserve">63.3707656860352</t>
   </si>
   <si>
     <t xml:space="preserve">63.3896408081055</t>
   </si>
   <si>
-    <t xml:space="preserve">64.6917724609375</t>
+    <t xml:space="preserve">64.691780090332</t>
   </si>
   <si>
     <t xml:space="preserve">63.5028686523438</t>
@@ -4766,10 +4766,10 @@
     <t xml:space="preserve">62.9933319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4649238586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8987846374512</t>
+    <t xml:space="preserve">62.4649276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8987808227539</t>
   </si>
   <si>
     <t xml:space="preserve">63.01220703125</t>
@@ -6465,6 +6465,9 @@
   </si>
   <si>
     <t xml:space="preserve">56.2200012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4000015258789</t>
   </si>
 </sst>
 </file>
@@ -30663,7 +30666,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G918" t="s">
-        <v>710</v>
+        <v>765</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30689,7 +30692,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G919" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30715,7 +30718,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G920" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30741,7 +30744,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G921" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30767,7 +30770,7 @@
         <v>33.8600006103516</v>
       </c>
       <c r="G922" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30793,7 +30796,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G923" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -30819,7 +30822,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G924" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30845,7 +30848,7 @@
         <v>35.4599990844727</v>
       </c>
       <c r="G925" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30897,7 +30900,7 @@
         <v>34.4199981689453</v>
       </c>
       <c r="G927" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30949,7 +30952,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G929" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30975,7 +30978,7 @@
         <v>34</v>
       </c>
       <c r="G930" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -31001,7 +31004,7 @@
         <v>33.939998626709</v>
       </c>
       <c r="G931" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -31027,7 +31030,7 @@
         <v>34.0900001525879</v>
       </c>
       <c r="G932" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -31053,7 +31056,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G933" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -31105,7 +31108,7 @@
         <v>35.060001373291</v>
       </c>
       <c r="G935" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -31131,7 +31134,7 @@
         <v>35.8600006103516</v>
       </c>
       <c r="G936" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -31157,7 +31160,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G937" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -31183,7 +31186,7 @@
         <v>35.4900016784668</v>
       </c>
       <c r="G938" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -31209,7 +31212,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G939" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -31235,7 +31238,7 @@
         <v>35.3699989318848</v>
       </c>
       <c r="G940" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -31261,7 +31264,7 @@
         <v>35.3899993896484</v>
       </c>
       <c r="G941" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -31287,7 +31290,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G942" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -31313,7 +31316,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G943" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -31339,7 +31342,7 @@
         <v>34.1300010681152</v>
       </c>
       <c r="G944" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -31365,7 +31368,7 @@
         <v>31.7399997711182</v>
       </c>
       <c r="G945" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -31391,7 +31394,7 @@
         <v>32.4700012207031</v>
       </c>
       <c r="G946" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -31417,7 +31420,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G947" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -31443,7 +31446,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G948" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31469,7 +31472,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G949" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31495,7 +31498,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G950" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31521,7 +31524,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G951" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31547,7 +31550,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G952" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31573,7 +31576,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G953" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31599,7 +31602,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G954" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31625,7 +31628,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G955" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31651,7 +31654,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G956" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31677,7 +31680,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31703,7 +31706,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G958" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31729,7 +31732,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G959" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31755,7 +31758,7 @@
         <v>33.189998626709</v>
       </c>
       <c r="G960" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31781,7 +31784,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31807,7 +31810,7 @@
         <v>34.4799995422363</v>
       </c>
       <c r="G962" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31833,7 +31836,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31859,7 +31862,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G964" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31885,7 +31888,7 @@
         <v>33.6399993896484</v>
       </c>
       <c r="G965" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31911,7 +31914,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G966" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31937,7 +31940,7 @@
         <v>32.1699981689453</v>
       </c>
       <c r="G967" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31963,7 +31966,7 @@
         <v>32.5</v>
       </c>
       <c r="G968" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31989,7 +31992,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G969" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -32015,7 +32018,7 @@
         <v>32.189998626709</v>
       </c>
       <c r="G970" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -32041,7 +32044,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="G971" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -32067,7 +32070,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G972" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -32093,7 +32096,7 @@
         <v>35.5</v>
       </c>
       <c r="G973" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -32119,7 +32122,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G974" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -32145,7 +32148,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G975" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -32197,7 +32200,7 @@
         <v>35.1699981689453</v>
       </c>
       <c r="G977" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -32223,7 +32226,7 @@
         <v>35.2900009155273</v>
       </c>
       <c r="G978" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -32249,7 +32252,7 @@
         <v>35.0299987792969</v>
       </c>
       <c r="G979" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -32301,7 +32304,7 @@
         <v>37.1100006103516</v>
       </c>
       <c r="G981" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -32327,7 +32330,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G982" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -32353,7 +32356,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -32379,7 +32382,7 @@
         <v>36.9599990844727</v>
       </c>
       <c r="G984" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -32405,7 +32408,7 @@
         <v>36.8699989318848</v>
       </c>
       <c r="G985" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -32431,7 +32434,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G986" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -32457,7 +32460,7 @@
         <v>36.560001373291</v>
       </c>
       <c r="G987" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32483,7 +32486,7 @@
         <v>36.8400001525879</v>
       </c>
       <c r="G988" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32509,7 +32512,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G989" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32535,7 +32538,7 @@
         <v>37.75</v>
       </c>
       <c r="G990" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32561,7 +32564,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G991" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32639,7 +32642,7 @@
         <v>39.0800018310547</v>
       </c>
       <c r="G994" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32665,7 +32668,7 @@
         <v>39.189998626709</v>
       </c>
       <c r="G995" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32691,7 +32694,7 @@
         <v>40.1399993896484</v>
       </c>
       <c r="G996" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32717,7 +32720,7 @@
         <v>39.7700004577637</v>
       </c>
       <c r="G997" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32743,7 +32746,7 @@
         <v>38.7900009155273</v>
       </c>
       <c r="G998" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32769,7 +32772,7 @@
         <v>38.6800003051758</v>
       </c>
       <c r="G999" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32795,7 +32798,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G1000" t="s">
-        <v>838</v>
+        <v>502</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -34069,7 +34072,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G1049" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -34303,7 +34306,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G1058" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -34823,7 +34826,7 @@
         <v>34</v>
       </c>
       <c r="G1078" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -35187,7 +35190,7 @@
         <v>34</v>
       </c>
       <c r="G1092" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -35265,7 +35268,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G1095" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -35343,7 +35346,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1098" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -35369,7 +35372,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1099" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -35655,7 +35658,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1110" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -35941,7 +35944,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1121" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -36227,7 +36230,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1132" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -36253,7 +36256,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1133" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -36409,7 +36412,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1139" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -36981,7 +36984,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G1161" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -37189,7 +37192,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G1169" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -37241,7 +37244,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -37397,7 +37400,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G1177" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -37553,7 +37556,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1183" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -37761,7 +37764,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1191" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -37813,7 +37816,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G1193" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -37995,7 +37998,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G1200" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -38255,7 +38258,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G1210" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -38385,7 +38388,7 @@
         <v>36.9599990844727</v>
       </c>
       <c r="G1215" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -38567,7 +38570,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G1222" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -38723,7 +38726,7 @@
         <v>34.1300010681152</v>
       </c>
       <c r="G1228" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -38749,7 +38752,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G1229" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -72219,7 +72222,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6912384259</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>636881</v>
@@ -72240,6 +72243,32 @@
         <v>2150</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6910300926</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>1329857</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>57.2599983215332</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>56.0800018310547</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>56.9000015258789</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>56.4000015258789</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="2156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="2157">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765733718872</t>
+    <t xml:space="preserve">11.0765743255615</t>
   </si>
   <si>
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698095321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8452548980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986368179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573593139648</t>
+    <t xml:space="preserve">10.9698104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8452529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986377716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.987606048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744375228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573583602905</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769296646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.156644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5481052398682</t>
+    <t xml:space="preserve">11.4769306182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1566438674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5481042861938</t>
   </si>
   <si>
     <t xml:space="preserve">11.7349395751953</t>
@@ -80,37 +80,37 @@
     <t xml:space="preserve">11.4057559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1264019012451</t>
+    <t xml:space="preserve">11.8239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1263999938965</t>
   </si>
   <si>
     <t xml:space="preserve">12.0997104644775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7260408401489</t>
+    <t xml:space="preserve">11.7260427474976</t>
   </si>
   <si>
     <t xml:space="preserve">12.0908126831055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9484634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950824737549</t>
+    <t xml:space="preserve">11.9484624862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950815200806</t>
   </si>
   <si>
     <t xml:space="preserve">11.7616300582886</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9128770828247</t>
+    <t xml:space="preserve">11.9128761291504</t>
   </si>
   <si>
     <t xml:space="preserve">11.4146528244019</t>
@@ -119,34 +119,34 @@
     <t xml:space="preserve">11.2723035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0409841537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2545070648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431190490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6726608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8772897720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2509565353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4022026062012</t>
+    <t xml:space="preserve">11.0409851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2545099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.672661781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8772888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4110984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.250955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2687501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4022016525269</t>
   </si>
   <si>
     <t xml:space="preserve">11.7972173690796</t>
@@ -155,61 +155,61 @@
     <t xml:space="preserve">12.1975746154785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7402820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9627027511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7669725418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2118148803711</t>
+    <t xml:space="preserve">12.7402839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9627046585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7669734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2118167877197</t>
   </si>
   <si>
     <t xml:space="preserve">13.4075450897217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.478720664978</t>
+    <t xml:space="preserve">13.4787187576294</t>
   </si>
   <si>
     <t xml:space="preserve">13.9680480957031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4520311355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7100372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.336371421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0427742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.060567855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9893951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9004249572754</t>
+    <t xml:space="preserve">13.4520301818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210718154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7100391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363704681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0427751541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9893941879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
     <t xml:space="preserve">13.0160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9449119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0961561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5143070220947</t>
+    <t xml:space="preserve">12.9449110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0961570739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5143060684204</t>
   </si>
   <si>
     <t xml:space="preserve">13.1228466033936</t>
@@ -221,76 +221,76 @@
     <t xml:space="preserve">12.927116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5890350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7936639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8292512893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737363815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1495361328125</t>
+    <t xml:space="preserve">12.5890369415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.793664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737382888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1495370864868</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029190063477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3897514343262</t>
+    <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
     <t xml:space="preserve">13.1673307418823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6869029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089645385742</t>
+    <t xml:space="preserve">12.6869020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089654922485</t>
   </si>
   <si>
     <t xml:space="preserve">12.5979337692261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9716014862061</t>
+    <t xml:space="preserve">12.9716005325317</t>
   </si>
   <si>
     <t xml:space="preserve">12.998291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3185777664185</t>
+    <t xml:space="preserve">13.3185787200928</t>
   </si>
   <si>
     <t xml:space="preserve">13.9324598312378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0570163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947366714478</t>
+    <t xml:space="preserve">14.057017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947385787964</t>
   </si>
   <si>
     <t xml:space="preserve">13.9502534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6388645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3452682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2285194396973</t>
+    <t xml:space="preserve">13.6388654708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3630619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452672958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285184860229</t>
   </si>
   <si>
     <t xml:space="preserve">13.5608043670654</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">13.4440546035767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2734203338623</t>
+    <t xml:space="preserve">13.2734222412109</t>
   </si>
   <si>
     <t xml:space="preserve">13.4709968566895</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">13.4620161056519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4979381561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6685724258423</t>
+    <t xml:space="preserve">13.4979391098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183269500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.668571472168</t>
   </si>
   <si>
     <t xml:space="preserve">13.7314357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7404174804688</t>
+    <t xml:space="preserve">13.7404165267944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3003644943237</t>
@@ -335,34 +335,34 @@
     <t xml:space="preserve">13.1566734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7256011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105588912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8603105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122625350952</t>
+    <t xml:space="preserve">12.7256031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8603115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122615814209</t>
   </si>
   <si>
     <t xml:space="preserve">13.6775522232056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8571672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2253723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321565628052</t>
+    <t xml:space="preserve">13.8571662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2253732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321575164795</t>
   </si>
   <si>
     <t xml:space="preserve">12.3035106658936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6986618041992</t>
+    <t xml:space="preserve">12.6986608505249</t>
   </si>
   <si>
     <t xml:space="preserve">13.1476936340332</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">12.9950227737427</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6178331375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8513298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8782730102539</t>
+    <t xml:space="preserve">12.6178340911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8513317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8782739639282</t>
   </si>
   <si>
     <t xml:space="preserve">12.9680786132812</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">13.1746339797974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9590997695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9501171112061</t>
+    <t xml:space="preserve">12.9590978622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">12.7705049514771</t>
@@ -401,25 +401,25 @@
     <t xml:space="preserve">13.8302230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1714897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0637216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3690633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0816831588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9559526443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6057062149048</t>
+    <t xml:space="preserve">14.1714887619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.063720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3690643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0816822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9559535980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069217681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6057071685791</t>
   </si>
   <si>
     <t xml:space="preserve">13.929012298584</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">14.0277986526489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0188179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8481845855713</t>
+    <t xml:space="preserve">14.0188188552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8481855392456</t>
   </si>
   <si>
     <t xml:space="preserve">14.0457611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9918756484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9200305938721</t>
+    <t xml:space="preserve">13.9918746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9200315475464</t>
   </si>
   <si>
     <t xml:space="preserve">13.7673587799072</t>
@@ -458,91 +458,91 @@
     <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248823165894</t>
+    <t xml:space="preserve">13.5248804092407</t>
   </si>
   <si>
     <t xml:space="preserve">13.354248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4171142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159006118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7224559783936</t>
+    <t xml:space="preserve">13.4171133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159015655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7224550247192</t>
   </si>
   <si>
     <t xml:space="preserve">13.5338611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7044954299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9110507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.009838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4530363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6506109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6416292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853221893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4799776077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8392038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0996427536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8930892944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9649333953857</t>
+    <t xml:space="preserve">13.7044944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9110488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146860122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0098371505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4530353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6506099700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4799795150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.839204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8930883407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9649324417114</t>
   </si>
   <si>
     <t xml:space="preserve">13.8751268386841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.79430103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.62366771698</t>
+    <t xml:space="preserve">13.7942991256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6236667633057</t>
   </si>
   <si>
     <t xml:space="preserve">13.399151802063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3901700973511</t>
+    <t xml:space="preserve">13.3901720046997</t>
   </si>
   <si>
     <t xml:space="preserve">13.488959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3362874984741</t>
+    <t xml:space="preserve">13.3362884521484</t>
   </si>
   <si>
     <t xml:space="preserve">13.6326494216919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3273077011108</t>
+    <t xml:space="preserve">13.3273067474365</t>
   </si>
   <si>
     <t xml:space="preserve">13.7763404846191</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">14.0547399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6474637985229</t>
+    <t xml:space="preserve">14.6474628448486</t>
   </si>
   <si>
     <t xml:space="preserve">14.6384830474854</t>
@@ -563,40 +563,40 @@
     <t xml:space="preserve">14.9168844223022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0964975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0426120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.548677444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7372722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731952667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8719797134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911520004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564435958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.683385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013483047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450403213501</t>
+    <t xml:space="preserve">15.0964965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0426139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.89892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5486783981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7372713088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731943130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8719806671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6833877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8450384140015</t>
   </si>
   <si>
     <t xml:space="preserve">15.0875177383423</t>
@@ -605,31 +605,31 @@
     <t xml:space="preserve">14.9707670211792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7103290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6744060516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.952805519104</t>
+    <t xml:space="preserve">14.7103281021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6744050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9528064727783</t>
   </si>
   <si>
     <t xml:space="preserve">15.437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736852645874</t>
+    <t xml:space="preserve">15.4736843109131</t>
   </si>
   <si>
     <t xml:space="preserve">15.6892213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7251434326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4826650619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790269851685</t>
+    <t xml:space="preserve">15.7251443862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4826641082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790298461914</t>
   </si>
   <si>
     <t xml:space="preserve">16.0933513641357</t>
@@ -638,73 +638,73 @@
     <t xml:space="preserve">16.1651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2011184692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1921405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2460250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113128662109</t>
+    <t xml:space="preserve">16.2011222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.192138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2460231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113109588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.0304851531982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9855804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6353368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9316997528076</t>
+    <t xml:space="preserve">15.9855813980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137392044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6353387832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9316959381104</t>
   </si>
   <si>
     <t xml:space="preserve">15.9766054153442</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9586391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406805038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867959976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1741771697998</t>
+    <t xml:space="preserve">15.9586420059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1741790771484</t>
   </si>
   <si>
     <t xml:space="preserve">16.102331161499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0484504699707</t>
+    <t xml:space="preserve">16.0484466552734</t>
   </si>
   <si>
     <t xml:space="preserve">15.8957767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9676218032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831569671631</t>
+    <t xml:space="preserve">15.9676237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831588745117</t>
   </si>
   <si>
     <t xml:space="preserve">17.0991859436035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2608394622803</t>
+    <t xml:space="preserve">17.2608375549316</t>
   </si>
   <si>
     <t xml:space="preserve">17.162052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2967624664307</t>
+    <t xml:space="preserve">17.296760559082</t>
   </si>
   <si>
     <t xml:space="preserve">17.3326835632324</t>
@@ -716,52 +716,52 @@
     <t xml:space="preserve">17.5661792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6559886932373</t>
+    <t xml:space="preserve">17.6559867858887</t>
   </si>
   <si>
     <t xml:space="preserve">17.6021041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8535614013672</t>
+    <t xml:space="preserve">17.8535594940186</t>
   </si>
   <si>
     <t xml:space="preserve">18.006233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1768684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8805027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.060115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0870590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205585479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2666702270508</t>
+    <t xml:space="preserve">18.1768665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8805046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0601177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0870552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2666721343994</t>
   </si>
   <si>
     <t xml:space="preserve">18.4103622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1678829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2756538391113</t>
+    <t xml:space="preserve">18.1678848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2756519317627</t>
   </si>
   <si>
     <t xml:space="preserve">18.4373054504395</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6169185638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9312400817871</t>
+    <t xml:space="preserve">18.6169147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9312419891357</t>
   </si>
   <si>
     <t xml:space="preserve">19.2276020050049</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">19.2006607055664</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4790630340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5598888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1108512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2096385955811</t>
+    <t xml:space="preserve">19.4790649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1108570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2096405029297</t>
   </si>
   <si>
     <t xml:space="preserve">19.3174114227295</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">19.6945991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4611034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5778503417969</t>
+    <t xml:space="preserve">19.4611015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5778484344482</t>
   </si>
   <si>
     <t xml:space="preserve">19.514986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">20.188533782959</t>
+    <t xml:space="preserve">20.1885356903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.4310111999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3501873016357</t>
+    <t xml:space="preserve">20.3501892089844</t>
   </si>
   <si>
     <t xml:space="preserve">20.6645088195801</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8351402282715</t>
+    <t xml:space="preserve">20.8351421356201</t>
   </si>
   <si>
     <t xml:space="preserve">21.1135425567627</t>
@@ -824,25 +824,25 @@
     <t xml:space="preserve">20.4759159088135</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7844066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.999942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8921699523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9819774627686</t>
+    <t xml:space="preserve">19.78440284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9999389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8921737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9819755554199</t>
   </si>
   <si>
     <t xml:space="preserve">19.874210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9909591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3892574310303</t>
+    <t xml:space="preserve">19.9909610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3892555236816</t>
   </si>
   <si>
     <t xml:space="preserve">19.5509090423584</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">19.6505184173584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7229595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6052398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4875183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0127372741699</t>
+    <t xml:space="preserve">19.7229614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6052379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4875202178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0127391815186</t>
   </si>
   <si>
     <t xml:space="preserve">19.2339630126953</t>
@@ -869,43 +869,43 @@
     <t xml:space="preserve">19.6324081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7048511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2792434692383</t>
+    <t xml:space="preserve">19.7048530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2792415618896</t>
   </si>
   <si>
     <t xml:space="preserve">18.9260749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0075759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9713554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.080020904541</t>
+    <t xml:space="preserve">19.0075740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9713535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0800170898438</t>
   </si>
   <si>
     <t xml:space="preserve">18.5819644927979</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8355197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1252975463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0437984466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3426265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6142959594727</t>
+    <t xml:space="preserve">18.8355178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0437965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3426284790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2249069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.614294052124</t>
   </si>
   <si>
     <t xml:space="preserve">19.2158527374268</t>
@@ -920,61 +920,61 @@
     <t xml:space="preserve">19.3245182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.944185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3736877441406</t>
+    <t xml:space="preserve">18.9441871643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3736896514893</t>
   </si>
   <si>
     <t xml:space="preserve">18.5638523101807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6362953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6000747680664</t>
+    <t xml:space="preserve">18.6362972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.600076675415</t>
   </si>
   <si>
     <t xml:space="preserve">18.8083515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7359066009521</t>
+    <t xml:space="preserve">18.7359085083008</t>
   </si>
   <si>
     <t xml:space="preserve">18.609130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1071872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.288293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.378849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4060173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4512977600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4331855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2701835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1977405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2391300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4655151367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5560722351074</t>
+    <t xml:space="preserve">19.1071853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2882957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4060192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4512939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4331817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2701854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1977424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2391262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4655170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5560741424561</t>
   </si>
   <si>
     <t xml:space="preserve">20.3568477630615</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">20.2572383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3930702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.329683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3749618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4021282196045</t>
+    <t xml:space="preserve">20.3930721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3296813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3749599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4021301269531</t>
   </si>
   <si>
     <t xml:space="preserve">20.3477935791016</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">21.5431270599365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.380126953125</t>
+    <t xml:space="preserve">21.3801250457764</t>
   </si>
   <si>
     <t xml:space="preserve">21.3439025878906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4254035949707</t>
+    <t xml:space="preserve">21.4254016876221</t>
   </si>
   <si>
     <t xml:space="preserve">21.3710689544678</t>
@@ -1022,67 +1022,67 @@
     <t xml:space="preserve">21.2805156707764</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2080707550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8730144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2714576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8962936401367</t>
+    <t xml:space="preserve">21.2080688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8730125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2714614868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.615571975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8962917327881</t>
   </si>
   <si>
     <t xml:space="preserve">21.7423477172852</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7966804504395</t>
+    <t xml:space="preserve">21.7966785430908</t>
   </si>
   <si>
     <t xml:space="preserve">21.9959011077881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1589012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4305686950684</t>
+    <t xml:space="preserve">22.1589031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4305648803711</t>
   </si>
   <si>
     <t xml:space="preserve">22.3671798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5935668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5030155181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2403984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3852882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2313461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2132358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2494564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9596786499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.823844909668</t>
+    <t xml:space="preserve">22.5935688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6116771697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5030136108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2404003143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.385290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2313442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2132339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2494583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9596824645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8238468170166</t>
   </si>
   <si>
     <t xml:space="preserve">22.0683460235596</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">22.1407909393311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8419570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7513999938965</t>
+    <t xml:space="preserve">21.8419589996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7514038085938</t>
   </si>
   <si>
     <t xml:space="preserve">21.4706802368164</t>
@@ -1106,25 +1106,25 @@
     <t xml:space="preserve">22.149845123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2766227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0592918395996</t>
+    <t xml:space="preserve">22.2766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0592880249023</t>
   </si>
   <si>
     <t xml:space="preserve">22.2856788635254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3490657806396</t>
+    <t xml:space="preserve">22.3490676879883</t>
   </si>
   <si>
     <t xml:space="preserve">22.394344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9868488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4396228790283</t>
+    <t xml:space="preserve">21.9868469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4396209716797</t>
   </si>
   <si>
     <t xml:space="preserve">22.5573444366455</t>
@@ -1136,37 +1136,37 @@
     <t xml:space="preserve">22.1226806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0774021148682</t>
+    <t xml:space="preserve">22.0774002075195</t>
   </si>
   <si>
     <t xml:space="preserve">22.0049571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9415702819824</t>
+    <t xml:space="preserve">21.9415664672852</t>
   </si>
   <si>
     <t xml:space="preserve">21.8510112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7695121765137</t>
+    <t xml:space="preserve">21.7695140838623</t>
   </si>
   <si>
     <t xml:space="preserve">20.6466255187988</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0631828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0088500976562</t>
+    <t xml:space="preserve">21.0631809234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088481903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6737957000732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7734050750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6556835174561</t>
+    <t xml:space="preserve">20.7734069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6556797027588</t>
   </si>
   <si>
     <t xml:space="preserve">21.099401473999</t>
@@ -1175,85 +1175,85 @@
     <t xml:space="preserve">21.0903491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1356239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8277378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8005714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8820686340332</t>
+    <t xml:space="preserve">21.1356258392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8277359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8005695343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8820705413818</t>
   </si>
   <si>
     <t xml:space="preserve">21.4344596862793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.950626373291</t>
+    <t xml:space="preserve">21.4163455963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9506225585938</t>
   </si>
   <si>
     <t xml:space="preserve">22.4667911529541</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5120697021484</t>
+    <t xml:space="preserve">22.5120677947998</t>
   </si>
   <si>
     <t xml:space="preserve">22.8833465576172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3218994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290100097656</t>
+    <t xml:space="preserve">22.3219013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290119171143</t>
   </si>
   <si>
     <t xml:space="preserve">22.9014587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8108997344971</t>
+    <t xml:space="preserve">22.8109035491943</t>
   </si>
   <si>
     <t xml:space="preserve">23.0916213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2546215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6530647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9066219329834</t>
+    <t xml:space="preserve">23.2546253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6530666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9066181182861</t>
   </si>
   <si>
     <t xml:space="preserve">23.6168403625488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3632869720459</t>
+    <t xml:space="preserve">23.3632888793945</t>
   </si>
   <si>
     <t xml:space="preserve">23.1821784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6349544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4900684356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.544397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2002906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8199558258057</t>
+    <t xml:space="preserve">23.634952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4900665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5443992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2002868652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8199577331543</t>
   </si>
   <si>
     <t xml:space="preserve">22.7837333679199</t>
@@ -1265,43 +1265,43 @@
     <t xml:space="preserve">23.8160629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.341287612915</t>
+    <t xml:space="preserve">24.3412818908691</t>
   </si>
   <si>
     <t xml:space="preserve">24.4861755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2507305145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3775100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5042858123779</t>
+    <t xml:space="preserve">24.2507343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3775081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5042839050293</t>
   </si>
   <si>
     <t xml:space="preserve">24.5223960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2869491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0333976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2145080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5625114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4629001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3593997955322</t>
+    <t xml:space="preserve">24.2869548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1148948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0333995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2145099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5625095367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4628982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3593978881836</t>
   </si>
   <si>
     <t xml:space="preserve">23.2908420562744</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">24.0424518585205</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6582279205322</t>
+    <t xml:space="preserve">24.6582298278809</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724510192871</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">25.5818958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4641742706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.391731262207</t>
+    <t xml:space="preserve">25.4641723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3917274475098</t>
   </si>
   <si>
     <t xml:space="preserve">25.6362285614014</t>
@@ -1346,31 +1346,31 @@
     <t xml:space="preserve">25.3192844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">25.264949798584</t>
+    <t xml:space="preserve">25.2649517059326</t>
   </si>
   <si>
     <t xml:space="preserve">25.6996154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5728397369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2157821655273</t>
+    <t xml:space="preserve">25.5728378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.215784072876</t>
   </si>
   <si>
     <t xml:space="preserve">26.405948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5055599212646</t>
+    <t xml:space="preserve">26.5055618286133</t>
   </si>
   <si>
     <t xml:space="preserve">26.6685600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4874496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8134517669678</t>
+    <t xml:space="preserve">26.4874477386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8134460449219</t>
   </si>
   <si>
     <t xml:space="preserve">26.7500591278076</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">27.465446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9453907012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5741119384766</t>
+    <t xml:space="preserve">27.9453945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5741157531738</t>
   </si>
   <si>
     <t xml:space="preserve">27.7190017700195</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">27.6737232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9182224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9816131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7655544281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4304981231689</t>
+    <t xml:space="preserve">27.9182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9816112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.765552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4305000305176</t>
   </si>
   <si>
     <t xml:space="preserve">29.8108310699463</t>
@@ -1412,79 +1412,79 @@
     <t xml:space="preserve">30.1549396514893</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2364387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9104442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5624408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4809417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2053852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9026584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.712495803833</t>
+    <t xml:space="preserve">30.2364406585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9104404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.562442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250522613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4809436798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.205379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.902660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7124977111816</t>
   </si>
   <si>
     <t xml:space="preserve">32.0203857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9207706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.618049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6904945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9621620178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4602165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9039344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110412597656</t>
+    <t xml:space="preserve">31.920768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6180458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6904907226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.962158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4602088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.903938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110450744629</t>
   </si>
   <si>
     <t xml:space="preserve">33.0527153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3011054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0346031188965</t>
+    <t xml:space="preserve">32.3011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.034595489502</t>
   </si>
   <si>
     <t xml:space="preserve">33.0798797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3153305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6865997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0759925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0941047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.392936706543</t>
+    <t xml:space="preserve">33.3153228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6866035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0759887695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3929328918457</t>
   </si>
   <si>
     <t xml:space="preserve">35.2350959777832</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">35.4416923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4749336242676</t>
+    <t xml:space="preserve">34.4749374389648</t>
   </si>
   <si>
     <t xml:space="preserve">33.7270622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5022964477539</t>
+    <t xml:space="preserve">34.5023002624512</t>
   </si>
   <si>
     <t xml:space="preserve">35.8065032958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0071563720703</t>
+    <t xml:space="preserve">36.0071487426758</t>
   </si>
   <si>
     <t xml:space="preserve">34.8671073913574</t>
@@ -1517,13 +1517,13 @@
     <t xml:space="preserve">35.1589584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8429832458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3354835510254</t>
+    <t xml:space="preserve">35.8156280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8429870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3354873657227</t>
   </si>
   <si>
     <t xml:space="preserve">37.7035369873047</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">37.2931213378906</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2534027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2748870849609</t>
+    <t xml:space="preserve">36.2534065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2748794555664</t>
   </si>
   <si>
     <t xml:space="preserve">37.5940933227539</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">38.3602066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8221015930176</t>
+    <t xml:space="preserve">37.8221054077148</t>
   </si>
   <si>
     <t xml:space="preserve">36.6546974182129</t>
@@ -1565,16 +1565,16 @@
     <t xml:space="preserve">36.0892372131348</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4143333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3960914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5146560668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1042442321777</t>
+    <t xml:space="preserve">35.4143295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3960876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5146522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1042404174805</t>
   </si>
   <si>
     <t xml:space="preserve">35.5693740844727</t>
@@ -1583,22 +1583,22 @@
     <t xml:space="preserve">35.3504829406738</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5205307006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.745304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2925262451172</t>
+    <t xml:space="preserve">34.5205383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9550743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7453002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2925224304199</t>
   </si>
   <si>
     <t xml:space="preserve">35.0586357116699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1830787658691</t>
+    <t xml:space="preserve">34.1830863952637</t>
   </si>
   <si>
     <t xml:space="preserve">34.8397483825684</t>
@@ -1613,19 +1613,19 @@
     <t xml:space="preserve">35.6240997314453</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4690551757812</t>
+    <t xml:space="preserve">35.4690475463867</t>
   </si>
   <si>
     <t xml:space="preserve">35.3869705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">35.241039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8853530883789</t>
+    <t xml:space="preserve">35.2410469055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1621971130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8853492736816</t>
   </si>
   <si>
     <t xml:space="preserve">34.6938209533691</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">33.4169692993164</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3746032714844</t>
+    <t xml:space="preserve">34.2651634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3746109008789</t>
   </si>
   <si>
     <t xml:space="preserve">34.5387763977051</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">34.6208610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.018913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8215103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4840545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7941474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5784950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169189453125</t>
+    <t xml:space="preserve">34.0189170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8215065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7941513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5784912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169227600098</t>
   </si>
   <si>
     <t xml:space="preserve">36.153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3172416687012</t>
+    <t xml:space="preserve">36.3172492980957</t>
   </si>
   <si>
     <t xml:space="preserve">35.5328941345215</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">34.2834014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3381309509277</t>
+    <t xml:space="preserve">34.3381271362305</t>
   </si>
   <si>
     <t xml:space="preserve">34.301643371582</t>
@@ -1712,31 +1712,31 @@
     <t xml:space="preserve">34.6117401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4202117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5934944152832</t>
+    <t xml:space="preserve">34.4202079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5934982299805</t>
   </si>
   <si>
     <t xml:space="preserve">34.511417388916</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0827560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664581298828</t>
+    <t xml:space="preserve">34.0827598571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664619445801</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9400749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9791984558105</t>
+    <t xml:space="preserve">34.940071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.979190826416</t>
   </si>
   <si>
     <t xml:space="preserve">31.8300323486328</t>
@@ -1748,16 +1748,16 @@
     <t xml:space="preserve">28.9388790130615</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5284671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2001285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.263973236084</t>
+    <t xml:space="preserve">28.5284633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2001323699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2639713287354</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007778167725</t>
@@ -1766,76 +1766,76 @@
     <t xml:space="preserve">28.4555015563965</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7258739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7988357543945</t>
+    <t xml:space="preserve">27.7258720397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7988338470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.6587905883789</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2698516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5708255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1786518096924</t>
+    <t xml:space="preserve">27.2698554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5708274841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1786499023438</t>
   </si>
   <si>
     <t xml:space="preserve">27.5434665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9994831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0906867980957</t>
+    <t xml:space="preserve">27.9994850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0906848907471</t>
   </si>
   <si>
     <t xml:space="preserve">29.5499458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1942462921143</t>
+    <t xml:space="preserve">29.1942501068115</t>
   </si>
   <si>
     <t xml:space="preserve">28.9753608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">29.130407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.692626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4522609710693</t>
+    <t xml:space="preserve">29.1304054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.452262878418</t>
   </si>
   <si>
     <t xml:space="preserve">29.0392017364502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0268421173096</t>
+    <t xml:space="preserve">28.0268440246582</t>
   </si>
   <si>
     <t xml:space="preserve">28.0359649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.351936340332</t>
+    <t xml:space="preserve">27.3519382476807</t>
   </si>
   <si>
     <t xml:space="preserve">26.2666149139404</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8503170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.813835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4340209960938</t>
+    <t xml:space="preserve">26.85032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8138389587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4340229034424</t>
   </si>
   <si>
     <t xml:space="preserve">27.2060127258301</t>
@@ -1847,55 +1847,55 @@
     <t xml:space="preserve">26.9141616821289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2483730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8079528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7682361602783</t>
+    <t xml:space="preserve">26.2483749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7682342529297</t>
   </si>
   <si>
     <t xml:space="preserve">27.3063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">26.512866973877</t>
+    <t xml:space="preserve">26.5128650665283</t>
   </si>
   <si>
     <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4822654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3272190093994</t>
+    <t xml:space="preserve">25.4822673797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.327220916748</t>
   </si>
   <si>
     <t xml:space="preserve">25.9565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6646709442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265716552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6431941986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1721725463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7011547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1448135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3454608917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5825881958008</t>
+    <t xml:space="preserve">25.6646747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265735626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6431922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1721744537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7011566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.144811630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3454627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5825862884521</t>
   </si>
   <si>
     <t xml:space="preserve">26.385181427002</t>
@@ -1904,61 +1904,61 @@
     <t xml:space="preserve">26.5949478149414</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3637008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4672660827637</t>
+    <t xml:space="preserve">25.3636989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.467264175415</t>
   </si>
   <si>
     <t xml:space="preserve">27.1877727508545</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9356422424316</t>
+    <t xml:space="preserve">27.935640335083</t>
   </si>
   <si>
     <t xml:space="preserve">28.6014270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1454086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0600872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0327262878418</t>
+    <t xml:space="preserve">28.1454124450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0600852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0327243804932</t>
   </si>
   <si>
     <t xml:space="preserve">27.3336963653564</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4066600799561</t>
+    <t xml:space="preserve">27.4066619873047</t>
   </si>
   <si>
     <t xml:space="preserve">27.6711483001709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8991622924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3792991638184</t>
+    <t xml:space="preserve">27.8991584777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3792972564697</t>
   </si>
   <si>
     <t xml:space="preserve">27.9538803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8809185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2366123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9147567749023</t>
+    <t xml:space="preserve">27.880916595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.914758682251</t>
   </si>
   <si>
     <t xml:space="preserve">30.0059623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5987796783447</t>
+    <t xml:space="preserve">30.598783493042</t>
   </si>
   <si>
     <t xml:space="preserve">30.7994289398193</t>
@@ -1967,106 +1967,106 @@
     <t xml:space="preserve">31.2007274627686</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4437408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6443862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9362411499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284111022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8117961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7753105163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6567440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743347167969</t>
+    <t xml:space="preserve">30.4437370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6443881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9362373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023448944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.81178855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7753086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6567478179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743366241455</t>
   </si>
   <si>
     <t xml:space="preserve">31.9668388366699</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9029960632324</t>
+    <t xml:space="preserve">31.9029941558838</t>
   </si>
   <si>
     <t xml:space="preserve">30.7538299560547</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1557235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9244766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8332672119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6964683532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5140533447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5779037475586</t>
+    <t xml:space="preserve">34.1557197570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9244728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8332710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.696460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5778961181641</t>
   </si>
   <si>
     <t xml:space="preserve">32.4319763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">32.915355682373</t>
+    <t xml:space="preserve">32.9153480529785</t>
   </si>
   <si>
     <t xml:space="preserve">33.0065536499023</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5264167785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1980857849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2313232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7388286590576</t>
+    <t xml:space="preserve">33.5264129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1980819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2313270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">32.4410934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7603034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5081748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6085014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.128360748291</t>
+    <t xml:space="preserve">32.7603073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5081787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6084976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1283569335938</t>
   </si>
   <si>
     <t xml:space="preserve">33.9277114868164</t>
@@ -2075,28 +2075,28 @@
     <t xml:space="preserve">33.8638687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8150253295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.659984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2163238525391</t>
+    <t xml:space="preserve">32.8150291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6599884033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2163200378418</t>
   </si>
   <si>
     <t xml:space="preserve">33.2892875671387</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0977554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4260940551758</t>
+    <t xml:space="preserve">33.0977592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.426097869873</t>
   </si>
   <si>
     <t xml:space="preserve">33.1160049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3075256347656</t>
+    <t xml:space="preserve">33.3075294494629</t>
   </si>
   <si>
     <t xml:space="preserve">33.872989654541</t>
@@ -2117,43 +2117,43 @@
     <t xml:space="preserve">33.2345657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1616058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.550537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4046173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4443283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9485912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6873435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1310005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5596618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5911674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863258361816</t>
+    <t xml:space="preserve">33.918586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1615982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5505332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.404613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4443321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9485950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6873474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1310043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5596580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5911712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863296508789</t>
   </si>
   <si>
     <t xml:space="preserve">32.836368560791</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8586578369141</t>
+    <t xml:space="preserve">31.8586540222168</t>
   </si>
   <si>
     <t xml:space="preserve">32.2552795410156</t>
@@ -2165,52 +2165,52 @@
     <t xml:space="preserve">31.7848663330078</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7887115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382095336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5581169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1207618713379</t>
+    <t xml:space="preserve">30.7887096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4382076263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5581188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1207656860352</t>
   </si>
   <si>
     <t xml:space="preserve">31.8217620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0062408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6649589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7387504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6518936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6480560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7679672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7087860107422</t>
+    <t xml:space="preserve">32.0062370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6649627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6518974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6480522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7679634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7087821960449</t>
   </si>
   <si>
     <t xml:space="preserve">34.505859375</t>
@@ -2228,49 +2228,49 @@
     <t xml:space="preserve">34.2568206787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6811141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9762687683105</t>
+    <t xml:space="preserve">34.6811065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9762649536133</t>
   </si>
   <si>
     <t xml:space="preserve">35.5112419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6127052307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5204620361328</t>
+    <t xml:space="preserve">35.6127090454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5204658508301</t>
   </si>
   <si>
     <t xml:space="preserve">35.5296897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2806549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3544464111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0961799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4927940368652</t>
+    <t xml:space="preserve">35.2806510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3544425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0961761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4927978515625</t>
   </si>
   <si>
     <t xml:space="preserve">35.0408325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1330718994141</t>
+    <t xml:space="preserve">35.1330757141113</t>
   </si>
   <si>
     <t xml:space="preserve">35.2253074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2437591552734</t>
+    <t xml:space="preserve">35.2437553405762</t>
   </si>
   <si>
     <t xml:space="preserve">35.6588249206543</t>
@@ -2297,22 +2297,22 @@
     <t xml:space="preserve">33.4451332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">31.462043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120826721191</t>
+    <t xml:space="preserve">31.4620380401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343719482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120788574219</t>
   </si>
   <si>
     <t xml:space="preserve">32.3475151062012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4989318847656</t>
+    <t xml:space="preserve">31.498929977417</t>
   </si>
   <si>
     <t xml:space="preserve">31.2314472198486</t>
@@ -2321,40 +2321,40 @@
     <t xml:space="preserve">31.7572002410889</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6926326751709</t>
+    <t xml:space="preserve">31.6926364898682</t>
   </si>
   <si>
     <t xml:space="preserve">32.7072372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7479705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5542755126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3605785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3052368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435939788818</t>
+    <t xml:space="preserve">31.747974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5542793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3605823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3052349090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435882568359</t>
   </si>
   <si>
     <t xml:space="preserve">31.6465167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3382949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0761871337891</t>
+    <t xml:space="preserve">32.3382873535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0761909484863</t>
   </si>
   <si>
     <t xml:space="preserve">33.1684226989746</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7349128723145</t>
+    <t xml:space="preserve">32.7349166870117</t>
   </si>
   <si>
     <t xml:space="preserve">32.5412101745605</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">32.375186920166</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6372871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4804821014404</t>
+    <t xml:space="preserve">31.6372890472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4804878234863</t>
   </si>
   <si>
     <t xml:space="preserve">29.2760219573975</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9493522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0877075195312</t>
+    <t xml:space="preserve">29.9493541717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0877056121826</t>
   </si>
   <si>
     <t xml:space="preserve">29.6080741882324</t>
@@ -2390,94 +2390,94 @@
     <t xml:space="preserve">29.7279834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6449718475342</t>
+    <t xml:space="preserve">29.6449699401855</t>
   </si>
   <si>
     <t xml:space="preserve">29.8478908538818</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3367500305176</t>
+    <t xml:space="preserve">30.3367462158203</t>
   </si>
   <si>
     <t xml:space="preserve">30.1614990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8294429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1376667022705</t>
+    <t xml:space="preserve">29.8294448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1376686096191</t>
   </si>
   <si>
     <t xml:space="preserve">29.6173000335693</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0139179229736</t>
+    <t xml:space="preserve">30.0139198303223</t>
   </si>
   <si>
     <t xml:space="preserve">30.1983947753906</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0508155822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6134548187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1945514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8033199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5450496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4251480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0285224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7241458892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6726379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9770221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7741031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6910877227783</t>
+    <t xml:space="preserve">30.050817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6134567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1945533752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8033123016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.545051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.425142288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0285243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7241401672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6726398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9770240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7740993499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">29.9678001403809</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3621139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7441329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.98779296875</t>
+    <t xml:space="preserve">33.362117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7441368103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9877910614014</t>
   </si>
   <si>
     <t xml:space="preserve">32.4397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5504417419434</t>
+    <t xml:space="preserve">32.5504379272461</t>
   </si>
   <si>
     <t xml:space="preserve">32.310619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2291488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180061340332</t>
+    <t xml:space="preserve">34.2291526794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180099487305</t>
   </si>
   <si>
     <t xml:space="preserve">34.3121604919434</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">34.0907936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0077781677246</t>
+    <t xml:space="preserve">34.0077743530273</t>
   </si>
   <si>
     <t xml:space="preserve">33.6111602783203</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">33.7218437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">33.980110168457</t>
+    <t xml:space="preserve">33.9801063537598</t>
   </si>
   <si>
     <t xml:space="preserve">34.2199249267578</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">36.1476783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0239334106445</t>
+    <t xml:space="preserve">37.0239295959473</t>
   </si>
   <si>
     <t xml:space="preserve">36.6826553344727</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">35.6772689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1492195129395</t>
+    <t xml:space="preserve">38.1492233276367</t>
   </si>
   <si>
     <t xml:space="preserve">38.9240112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">38.545841217041</t>
+    <t xml:space="preserve">38.5458374023438</t>
   </si>
   <si>
     <t xml:space="preserve">38.8225517272949</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">38.093879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8171730041504</t>
+    <t xml:space="preserve">37.8171691894531</t>
   </si>
   <si>
     <t xml:space="preserve">37.7249336242676</t>
@@ -2552,22 +2552,22 @@
     <t xml:space="preserve">37.3006362915039</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0423774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1899528503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.715705871582</t>
+    <t xml:space="preserve">37.0423812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1899566650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7157096862793</t>
   </si>
   <si>
     <t xml:space="preserve">37.6234703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4758949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9593658447266</t>
+    <t xml:space="preserve">37.4758911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9593620300293</t>
   </si>
   <si>
     <t xml:space="preserve">37.4389991760254</t>
@@ -2579,22 +2579,22 @@
     <t xml:space="preserve">37.1438369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9647483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5496826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6326904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3613662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4036483764648</t>
+    <t xml:space="preserve">37.9647445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9462966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5496788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6326942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3613624572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4036445617676</t>
   </si>
   <si>
     <t xml:space="preserve">39.3667526245117</t>
@@ -2603,31 +2603,31 @@
     <t xml:space="preserve">39.385196685791</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1399993896484</t>
+    <t xml:space="preserve">38.1399955749512</t>
   </si>
   <si>
     <t xml:space="preserve">37.2914161682129</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2691307067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2084083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4021072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8432998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2360725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4889526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9724235534668</t>
+    <t xml:space="preserve">38.2691268920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2084045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4021034240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8432960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2360763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.488956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9724311828613</t>
   </si>
   <si>
     <t xml:space="preserve">36.3690490722656</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">36.8579063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2729682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5166244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7049407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457595825195</t>
+    <t xml:space="preserve">37.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5166282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7049369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457557678223</t>
   </si>
   <si>
     <t xml:space="preserve">35.649600982666</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">36.2583656311035</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1422958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2898712158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0093193054199</t>
+    <t xml:space="preserve">35.1422920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0093269348145</t>
   </si>
   <si>
     <t xml:space="preserve">34.2660446166992</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4305267333984</t>
+    <t xml:space="preserve">32.4305305480957</t>
   </si>
   <si>
     <t xml:space="preserve">32.4028587341309</t>
@@ -2675,13 +2675,13 @@
     <t xml:space="preserve">32.9286079406738</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5227661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4858741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1023139953613</t>
+    <t xml:space="preserve">32.5227584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4858665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.10231590271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1507320404053</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">27.3943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2637100219727</t>
+    <t xml:space="preserve">25.2637119293213</t>
   </si>
   <si>
     <t xml:space="preserve">24.9039897918701</t>
@@ -2708,10 +2708,10 @@
     <t xml:space="preserve">25.3651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9224338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9977684020996</t>
+    <t xml:space="preserve">24.922435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9977703094482</t>
   </si>
   <si>
     <t xml:space="preserve">26.3797817230225</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">29.9309043884277</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4528160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.729528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7056941986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.875560760498</t>
+    <t xml:space="preserve">31.4528141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7295322418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.705696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8755626678467</t>
   </si>
   <si>
     <t xml:space="preserve">29.5158386230469</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">30.2998523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0838661193848</t>
+    <t xml:space="preserve">31.0838642120361</t>
   </si>
   <si>
     <t xml:space="preserve">30.6319065093994</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">31.8402118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5135459899902</t>
+    <t xml:space="preserve">32.5135383605957</t>
   </si>
   <si>
     <t xml:space="preserve">30.8901710510254</t>
@@ -2765,28 +2765,28 @@
     <t xml:space="preserve">30.5765647888184</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5081577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756423950195</t>
+    <t xml:space="preserve">31.5081558227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756462097168</t>
   </si>
   <si>
     <t xml:space="preserve">30.2721824645996</t>
   </si>
   <si>
-    <t xml:space="preserve">30.770263671875</t>
+    <t xml:space="preserve">30.7702598571777</t>
   </si>
   <si>
     <t xml:space="preserve">29.9124565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2352886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7833290100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2260627746582</t>
+    <t xml:space="preserve">30.2352848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7833251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2260646820068</t>
   </si>
   <si>
     <t xml:space="preserve">29.4143772125244</t>
@@ -2798,40 +2798,40 @@
     <t xml:space="preserve">28.6211414337158</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7372093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8663387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8056144714355</t>
+    <t xml:space="preserve">29.7372074127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.866340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8056125640869</t>
   </si>
   <si>
     <t xml:space="preserve">29.3682594299316</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7979316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.39208984375</t>
+    <t xml:space="preserve">30.7979335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3920936584473</t>
   </si>
   <si>
     <t xml:space="preserve">32.1630363464355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8532791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0746402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955554962158</t>
+    <t xml:space="preserve">30.8532752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0746421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955574035645</t>
   </si>
   <si>
     <t xml:space="preserve">32.0339088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0377521514893</t>
+    <t xml:space="preserve">31.0377502441406</t>
   </si>
   <si>
     <t xml:space="preserve">31.3790283203125</t>
@@ -2840,58 +2840,58 @@
     <t xml:space="preserve">31.2406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9693431854248</t>
+    <t xml:space="preserve">31.9693450927734</t>
   </si>
   <si>
     <t xml:space="preserve">32.4950942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7625770568848</t>
+    <t xml:space="preserve">32.762580871582</t>
   </si>
   <si>
     <t xml:space="preserve">33.0577392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0892486572266</t>
+    <t xml:space="preserve">32.0892562866211</t>
   </si>
   <si>
     <t xml:space="preserve">31.7203044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">32.126148223877</t>
+    <t xml:space="preserve">32.1261444091797</t>
   </si>
   <si>
     <t xml:space="preserve">31.3974742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6003913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591190338135</t>
+    <t xml:space="preserve">31.6003932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591171264648</t>
   </si>
   <si>
     <t xml:space="preserve">31.9601211547852</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4897079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3513603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6503524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0100746154785</t>
+    <t xml:space="preserve">31.489709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6503505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654220581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0100784301758</t>
   </si>
   <si>
     <t xml:space="preserve">30.5950088500977</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">30.0969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4236011505127</t>
+    <t xml:space="preserve">29.4235992431641</t>
   </si>
   <si>
     <t xml:space="preserve">29.5804042816162</t>
@@ -2915,34 +2915,34 @@
     <t xml:space="preserve">30.8809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3275279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0784854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.552734375</t>
+    <t xml:space="preserve">30.3275241851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.078483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5342884063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5527324676514</t>
   </si>
   <si>
     <t xml:space="preserve">29.8571147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0046939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.884786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9585742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1484355926514</t>
+    <t xml:space="preserve">30.0046920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5857887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8847885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1484317779541</t>
   </si>
   <si>
     <t xml:space="preserve">31.7940921783447</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">32.1814842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4766426086426</t>
+    <t xml:space="preserve">32.4766464233398</t>
   </si>
   <si>
     <t xml:space="preserve">33.8878746032715</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">34.9854927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3306083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.66650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4674224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0431289672852</t>
+    <t xml:space="preserve">34.3306121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6665000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4674263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0431327819824</t>
   </si>
   <si>
     <t xml:space="preserve">32.4489784240723</t>
@@ -2978,19 +2978,19 @@
     <t xml:space="preserve">32.2644996643066</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8455963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7164611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6019401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8509750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.223762512207</t>
+    <t xml:space="preserve">32.8455924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7164649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6019325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8509826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2237663269043</t>
   </si>
   <si>
     <t xml:space="preserve">33.5650405883789</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">33.9432106018066</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9485969543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4043960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1276893615723</t>
+    <t xml:space="preserve">34.948600769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4043998718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9170837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.127685546875</t>
   </si>
   <si>
     <t xml:space="preserve">32.1907119750977</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">34.6349906921387</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5996398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6273078918457</t>
+    <t xml:space="preserve">36.5996360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6273155212402</t>
   </si>
   <si>
     <t xml:space="preserve">37.3467597961426</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">36.6088638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7195510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8909606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8725090026855</t>
+    <t xml:space="preserve">36.7195472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8909568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">37.6142463684082</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">37.4482192993164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4536018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7118682861328</t>
+    <t xml:space="preserve">38.4536056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7118721008301</t>
   </si>
   <si>
     <t xml:space="preserve">38.6473045349121</t>
@@ -3077,25 +3077,25 @@
     <t xml:space="preserve">38.241455078125</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8263893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9001808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4720497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2837371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.846378326416</t>
+    <t xml:space="preserve">37.8263854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9001770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.472053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2837333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8463859558105</t>
   </si>
   <si>
     <t xml:space="preserve">40.5842781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4144096374512</t>
+    <t xml:space="preserve">41.4144134521484</t>
   </si>
   <si>
     <t xml:space="preserve">42.9916648864746</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">42.8533058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.886360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1630783081055</t>
+    <t xml:space="preserve">43.8863639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1630744934082</t>
   </si>
   <si>
     <t xml:space="preserve">45.0116500854492</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9286346435547</t>
+    <t xml:space="preserve">44.928638458252</t>
   </si>
   <si>
     <t xml:space="preserve">45.1961288452148</t>
@@ -3125,34 +3125,34 @@
     <t xml:space="preserve">43.8679122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6242599487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4674530029297</t>
+    <t xml:space="preserve">44.6242561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.467456817627</t>
   </si>
   <si>
     <t xml:space="preserve">45.8694610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3952102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2476348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1184959411621</t>
+    <t xml:space="preserve">46.395206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2476272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">44.8456268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">44.864070892334</t>
+    <t xml:space="preserve">44.8640747070312</t>
   </si>
   <si>
     <t xml:space="preserve">44.1077308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3290977478027</t>
+    <t xml:space="preserve">44.3291015625</t>
   </si>
   <si>
     <t xml:space="preserve">44.2737579345703</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">43.3882827758789</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4121170043945</t>
+    <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
     <t xml:space="preserve">44.0708351135254</t>
@@ -3185,46 +3185,46 @@
     <t xml:space="preserve">43.6649971008301</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5912017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7756767272949</t>
+    <t xml:space="preserve">43.5912055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7756805419922</t>
   </si>
   <si>
     <t xml:space="preserve">44.1999702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2091941833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1369438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8932876586914</t>
+    <t xml:space="preserve">44.2091903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1369476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8932914733887</t>
   </si>
   <si>
     <t xml:space="preserve">47.5758438110352</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0739212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6496276855469</t>
+    <t xml:space="preserve">48.0739250183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6496315002441</t>
   </si>
   <si>
     <t xml:space="preserve">47.9447898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2622375488281</t>
+    <t xml:space="preserve">47.2622337341309</t>
   </si>
   <si>
     <t xml:space="preserve">48.1477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7972106933594</t>
+    <t xml:space="preserve">47.7972068786621</t>
   </si>
   <si>
     <t xml:space="preserve">46.708812713623</t>
@@ -3236,52 +3236,52 @@
     <t xml:space="preserve">49.1807670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8710021972656</t>
+    <t xml:space="preserve">47.8709983825684</t>
   </si>
   <si>
     <t xml:space="preserve">47.2437934875488</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0408744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1699981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3175773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1108169555664</t>
+    <t xml:space="preserve">47.0408668518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1700019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3175811767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1108131408691</t>
   </si>
   <si>
     <t xml:space="preserve">48.4613189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6165771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7034339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8602409362793</t>
+    <t xml:space="preserve">47.6865272521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6165809631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7034301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.860237121582</t>
   </si>
   <si>
     <t xml:space="preserve">46.4136543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7587738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3360290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4467124938965</t>
+    <t xml:space="preserve">45.7587776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0001373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3360252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.446704864502</t>
   </si>
   <si>
     <t xml:space="preserve">46.837947845459</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">45.6019706726074</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3806037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2276420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4397811889648</t>
+    <t xml:space="preserve">45.3806076049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4397888183594</t>
   </si>
   <si>
     <t xml:space="preserve">44.4859046936035</t>
@@ -3317,49 +3317,49 @@
     <t xml:space="preserve">45.6573104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4505577087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5981292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5243377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5020523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3544731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3214225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2952880859375</t>
+    <t xml:space="preserve">46.450553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5981369018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.524341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5020484924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3544769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.321418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2952919006348</t>
   </si>
   <si>
     <t xml:space="preserve">49.3467903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9670791625977</t>
+    <t xml:space="preserve">46.9670753479004</t>
   </si>
   <si>
     <t xml:space="preserve">47.0039749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0593147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4836044311523</t>
+    <t xml:space="preserve">47.0593185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4836006164551</t>
   </si>
   <si>
     <t xml:space="preserve">46.3767585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4282646179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2806816101074</t>
+    <t xml:space="preserve">47.4282608032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2806854248047</t>
   </si>
   <si>
     <t xml:space="preserve">47.7234230041504</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9263458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6642379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4244270324707</t>
+    <t xml:space="preserve">47.926342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.664234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">49.1623153686523</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">50.490291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1228179931641</t>
+    <t xml:space="preserve">51.1228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">51.625114440918</t>
@@ -3404,40 +3404,40 @@
     <t xml:space="preserve">54.0621948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4482688903809</t>
+    <t xml:space="preserve">53.4482727050781</t>
   </si>
   <si>
     <t xml:space="preserve">53.6343078613281</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1180000305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2296257019043</t>
+    <t xml:space="preserve">54.1180038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.229621887207</t>
   </si>
   <si>
     <t xml:space="preserve">55.1039924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8063316345215</t>
+    <t xml:space="preserve">54.8063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">53.5784950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8343505859375</t>
+    <t xml:space="preserve">52.8343467712402</t>
   </si>
   <si>
     <t xml:space="preserve">52.8715591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">53.132007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8947601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2482261657715</t>
+    <t xml:space="preserve">53.1320114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8947563171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2482223510742</t>
   </si>
   <si>
     <t xml:space="preserve">54.5086784362793</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">53.225025177002</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6901206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5971031188965</t>
+    <t xml:space="preserve">53.6901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5970993041992</t>
   </si>
   <si>
     <t xml:space="preserve">53.0761985778809</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4668769836426</t>
+    <t xml:space="preserve">53.4668731689453</t>
   </si>
   <si>
     <t xml:space="preserve">53.3180465698242</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">52.815746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0389938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3366546630859</t>
+    <t xml:space="preserve">53.038990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3366508483887</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4250717163086</t>
+    <t xml:space="preserve">52.4250755310059</t>
   </si>
   <si>
     <t xml:space="preserve">53.2808380126953</t>
@@ -3491,22 +3491,22 @@
     <t xml:space="preserve">53.7273254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3598518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7785415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1460189819336</t>
+    <t xml:space="preserve">54.3598480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7785453796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1460151672363</t>
   </si>
   <si>
     <t xml:space="preserve">53.1878204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7459297180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6203002929688</t>
+    <t xml:space="preserve">53.7459335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.620304107666</t>
   </si>
   <si>
     <t xml:space="preserve">55.4388580322266</t>
@@ -3515,25 +3515,25 @@
     <t xml:space="preserve">55.7551193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4946746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8761558532715</t>
+    <t xml:space="preserve">55.4946708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">53.950569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6389083862305</t>
+    <t xml:space="preserve">54.6389007568359</t>
   </si>
   <si>
     <t xml:space="preserve">54.6947174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5272827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5876922607422</t>
+    <t xml:space="preserve">54.527286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5876884460449</t>
   </si>
   <si>
     <t xml:space="preserve">56.9271507263184</t>
@@ -3542,22 +3542,22 @@
     <t xml:space="preserve">57.2992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">57.727108001709</t>
+    <t xml:space="preserve">57.7271118164062</t>
   </si>
   <si>
     <t xml:space="preserve">57.5596771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4248504638672</t>
+    <t xml:space="preserve">56.4248542785645</t>
   </si>
   <si>
     <t xml:space="preserve">55.8667488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3970565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.067008972168</t>
+    <t xml:space="preserve">54.3970527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0670051574707</t>
   </si>
   <si>
     <t xml:space="preserve">50.1554260253906</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">50.8437614440918</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7693519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3972778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5461006164551</t>
+    <t xml:space="preserve">50.7693481445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.397274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5461044311523</t>
   </si>
   <si>
     <t xml:space="preserve">50.8065528869629</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">50.4158744812012</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0298004150391</t>
+    <t xml:space="preserve">51.0297966003418</t>
   </si>
   <si>
     <t xml:space="preserve">50.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2484436035156</t>
+    <t xml:space="preserve">50.2484474182129</t>
   </si>
   <si>
     <t xml:space="preserve">51.1042098999023</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">51.718132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4018707275391</t>
+    <t xml:space="preserve">51.4018669128418</t>
   </si>
   <si>
     <t xml:space="preserve">51.3274574279785</t>
@@ -3611,22 +3611,22 @@
     <t xml:space="preserve">48.1648330688477</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0904197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3182640075684</t>
+    <t xml:space="preserve">48.0904235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3182601928711</t>
   </si>
   <si>
     <t xml:space="preserve">48.0532150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0020027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5647048950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3832702636719</t>
+    <t xml:space="preserve">49.0019989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5647087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3832664489746</t>
   </si>
   <si>
     <t xml:space="preserve">51.1600227355957</t>
@@ -3638,43 +3638,43 @@
     <t xml:space="preserve">48.6113204956055</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2438468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7553405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.978588104248</t>
+    <t xml:space="preserve">49.2438430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7553367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9785842895508</t>
   </si>
   <si>
     <t xml:space="preserve">52.9831771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4994812011719</t>
+    <t xml:space="preserve">52.4994850158691</t>
   </si>
   <si>
     <t xml:space="preserve">52.4622802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4714698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5690879821777</t>
+    <t xml:space="preserve">54.7133140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4714736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.569091796875</t>
   </si>
   <si>
     <t xml:space="preserve">56.0341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7597236633301</t>
+    <t xml:space="preserve">56.7597198486328</t>
   </si>
   <si>
     <t xml:space="preserve">56.8341331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3876457214355</t>
+    <t xml:space="preserve">56.3876419067383</t>
   </si>
   <si>
     <t xml:space="preserve">55.9783668518066</t>
@@ -3686,31 +3686,31 @@
     <t xml:space="preserve">57.7829208374023</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4386444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5084648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2340049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.652473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8803176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4012184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7409019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8199157714844</t>
+    <t xml:space="preserve">59.438648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5084686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.234001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6524772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.880313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4012222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7408981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8199081420898</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
@@ -3719,28 +3719,28 @@
     <t xml:space="preserve">63.754695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">64.331413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5686531066895</t>
+    <t xml:space="preserve">64.3314056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2197875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5686454772949</t>
   </si>
   <si>
     <t xml:space="preserve">63.0663604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9593353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408554077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9129295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3222045898438</t>
+    <t xml:space="preserve">63.9593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9129257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3222122192383</t>
   </si>
   <si>
     <t xml:space="preserve">58.3410301208496</t>
@@ -3755,34 +3755,34 @@
     <t xml:space="preserve">61.0385589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9455375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5920715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6896820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4430236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4710426330566</t>
+    <t xml:space="preserve">60.9455337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5920677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6896896362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4430160522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4710464477539</t>
   </si>
   <si>
     <t xml:space="preserve">62.1547737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4478340148926</t>
+    <t xml:space="preserve">61.4478378295898</t>
   </si>
   <si>
     <t xml:space="preserve">60.629280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6758995056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.182788848877</t>
+    <t xml:space="preserve">58.675895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1827926635742</t>
   </si>
   <si>
     <t xml:space="preserve">58.7503128051758</t>
@@ -3797,19 +3797,19 @@
     <t xml:space="preserve">57.8573341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3224220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5642738342285</t>
+    <t xml:space="preserve">58.3224258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5642700195312</t>
   </si>
   <si>
     <t xml:space="preserve">59.7549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0711669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.5502662658691</t>
+    <t xml:space="preserve">60.0711708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.5502624511719</t>
   </si>
   <si>
     <t xml:space="preserve">59.810718536377</t>
@@ -3818,31 +3818,31 @@
     <t xml:space="preserve">60.4618453979492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269409179688</t>
+    <t xml:space="preserve">60.9269371032715</t>
   </si>
   <si>
     <t xml:space="preserve">58.4154434204102</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9643592834473</t>
+    <t xml:space="preserve">56.9643630981445</t>
   </si>
   <si>
     <t xml:space="preserve">56.1644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7923278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8807487487793</t>
+    <t xml:space="preserve">55.7923316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8807525634766</t>
   </si>
   <si>
     <t xml:space="preserve">52.8901634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7087211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6111106872559</t>
+    <t xml:space="preserve">53.7087249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6111068725586</t>
   </si>
   <si>
     <t xml:space="preserve">54.3040390014648</t>
@@ -3854,16 +3854,16 @@
     <t xml:space="preserve">51.6995315551758</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2716407775879</t>
+    <t xml:space="preserve">51.2716445922852</t>
   </si>
   <si>
     <t xml:space="preserve">52.3134536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5366897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5693016052246</t>
+    <t xml:space="preserve">52.536693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5693054199219</t>
   </si>
   <si>
     <t xml:space="preserve">52.4064674377441</t>
@@ -3875,22 +3875,22 @@
     <t xml:space="preserve">55.271427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8389472961426</t>
+    <t xml:space="preserve">53.8389511108398</t>
   </si>
   <si>
     <t xml:space="preserve">54.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6437187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6391143798828</t>
+    <t xml:space="preserve">51.6437225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6391220092773</t>
   </si>
   <si>
     <t xml:space="preserve">52.1274108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2344360351562</t>
+    <t xml:space="preserve">51.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">50.9739837646484</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">50.9181785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8809661865234</t>
+    <t xml:space="preserve">50.8809700012207</t>
   </si>
   <si>
     <t xml:space="preserve">48.4624938964844</t>
@@ -3911,25 +3911,25 @@
     <t xml:space="preserve">47.1230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9464073181152</t>
+    <t xml:space="preserve">44.946403503418</t>
   </si>
   <si>
     <t xml:space="preserve">41.8768043518066</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1465606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4954299926758</t>
+    <t xml:space="preserve">42.146556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4954261779785</t>
   </si>
   <si>
     <t xml:space="preserve">44.974308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9976196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6208457946777</t>
+    <t xml:space="preserve">43.997615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6208419799805</t>
   </si>
   <si>
     <t xml:space="preserve">44.6487464904785</t>
@@ -3938,37 +3938,37 @@
     <t xml:space="preserve">43.2441711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">45.709156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7881660461426</t>
+    <t xml:space="preserve">45.7091522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7881622314453</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044273376465</t>
+    <t xml:space="preserve">47.1044235229492</t>
   </si>
   <si>
     <t xml:space="preserve">46.2951698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8207702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2021522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2765693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8717803955078</t>
+    <t xml:space="preserve">45.8207740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2765655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8717765808105</t>
   </si>
   <si>
     <t xml:space="preserve">47.1974487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1788444519043</t>
+    <t xml:space="preserve">47.178840637207</t>
   </si>
   <si>
     <t xml:space="preserve">48.9275817871094</t>
@@ -3977,58 +3977,58 @@
     <t xml:space="preserve">49.2810554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9556007385254</t>
+    <t xml:space="preserve">46.9555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">45.9882125854492</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4392890930176</t>
+    <t xml:space="preserve">47.4392929077148</t>
   </si>
   <si>
     <t xml:space="preserve">45.1603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0254211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4533004760742</t>
+    <t xml:space="preserve">46.0254173278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.453296661377</t>
   </si>
   <si>
     <t xml:space="preserve">47.0300140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1835479736328</t>
+    <t xml:space="preserve">46.1835517883301</t>
   </si>
   <si>
     <t xml:space="preserve">47.5881233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5277214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3510894775391</t>
+    <t xml:space="preserve">46.5277137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3510932922363</t>
   </si>
   <si>
     <t xml:space="preserve">43.8301849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">45.430103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2672653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7695579528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5696296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6115417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9604072570801</t>
+    <t xml:space="preserve">45.4300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2672691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7695617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5696334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6115379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9604148864746</t>
   </si>
   <si>
     <t xml:space="preserve">41.4861259460449</t>
@@ -4040,22 +4040,22 @@
     <t xml:space="preserve">38.9095230102539</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8676109313965</t>
+    <t xml:space="preserve">39.8676147460938</t>
   </si>
   <si>
     <t xml:space="preserve">41.6163520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8070907592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1930694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2814865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1093521118164</t>
+    <t xml:space="preserve">40.8070945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2814903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1093482971191</t>
   </si>
   <si>
     <t xml:space="preserve">40.6489639282227</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">40.0908508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3095016479492</t>
+    <t xml:space="preserve">39.309497833252</t>
   </si>
   <si>
     <t xml:space="preserve">39.8945198059082</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">40.6588172912598</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3572616577148</t>
+    <t xml:space="preserve">42.3572578430176</t>
   </si>
   <si>
     <t xml:space="preserve">42.1779823303223</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801254272461</t>
+    <t xml:space="preserve">43.4801216125488</t>
   </si>
   <si>
     <t xml:space="preserve">43.234790802002</t>
@@ -4112,25 +4112,25 @@
     <t xml:space="preserve">37.2147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2145652770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5166969299316</t>
+    <t xml:space="preserve">36.2145614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5167007446289</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0917015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9690361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9973449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312934875488</t>
+    <t xml:space="preserve">35.0916976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9690399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9973487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9312973022461</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4139,10 +4139,10 @@
     <t xml:space="preserve">37.4600868225098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7054176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.394229888916</t>
+    <t xml:space="preserve">37.7054138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3942260742188</t>
   </si>
   <si>
     <t xml:space="preserve">38.4980239868164</t>
@@ -4154,16 +4154,16 @@
     <t xml:space="preserve">38.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3751678466797</t>
+    <t xml:space="preserve">37.3751640319824</t>
   </si>
   <si>
     <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0547370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396598815918</t>
+    <t xml:space="preserve">39.0547332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396560668945</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">38.9886856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6678695678711</t>
+    <t xml:space="preserve">38.6678657531738</t>
   </si>
   <si>
     <t xml:space="preserve">37.9507484436035</t>
@@ -4181,19 +4181,19 @@
     <t xml:space="preserve">37.8280830383301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5735130310059</t>
+    <t xml:space="preserve">38.5735092163086</t>
   </si>
   <si>
     <t xml:space="preserve">40.1587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3474349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.753173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1494789123535</t>
+    <t xml:space="preserve">40.3474388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7531776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1494827270508</t>
   </si>
   <si>
     <t xml:space="preserve">41.5552215576172</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389739990234</t>
+    <t xml:space="preserve">45.3389701843262</t>
   </si>
   <si>
     <t xml:space="preserve">46.5278854370117</t>
@@ -4226,13 +4226,13 @@
     <t xml:space="preserve">46.5184440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4995765686035</t>
+    <t xml:space="preserve">46.4995727539062</t>
   </si>
   <si>
     <t xml:space="preserve">45.8579406738281</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7165946960449</t>
+    <t xml:space="preserve">46.7165908813477</t>
   </si>
   <si>
     <t xml:space="preserve">46.9524917602539</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">46.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0089149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7543411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1315803527832</t>
+    <t xml:space="preserve">46.0089111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1315765380859</t>
   </si>
   <si>
     <t xml:space="preserve">44.0273971557617</t>
@@ -4262,10 +4262,10 @@
     <t xml:space="preserve">45.2163047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2729225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0460739135742</t>
+    <t xml:space="preserve">45.2729187011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.046070098877</t>
   </si>
   <si>
     <t xml:space="preserve">42.1496734619141</t>
@@ -4283,31 +4283,31 @@
     <t xml:space="preserve">42.2251625061035</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1400413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1777839660645</t>
+    <t xml:space="preserve">41.1400451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1777877807617</t>
   </si>
   <si>
     <t xml:space="preserve">41.3948097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6967506408691</t>
+    <t xml:space="preserve">41.6967544555664</t>
   </si>
   <si>
     <t xml:space="preserve">42.4704895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.998893737793</t>
+    <t xml:space="preserve">42.9988975524902</t>
   </si>
   <si>
     <t xml:space="preserve">42.0175704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7158241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646514892578</t>
+    <t xml:space="preserve">42.7158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646553039551</t>
   </si>
   <si>
     <t xml:space="preserve">40.9230194091797</t>
@@ -4316,13 +4316,13 @@
     <t xml:space="preserve">41.4891700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8005485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.461051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9511337280273</t>
+    <t xml:space="preserve">41.8005523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4610557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9511375427246</t>
   </si>
   <si>
     <t xml:space="preserve">39.2623252868652</t>
@@ -4334,16 +4334,16 @@
     <t xml:space="preserve">40.5644645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0645561218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8095970153809</t>
+    <t xml:space="preserve">41.0645599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8095932006836</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9794387817383</t>
+    <t xml:space="preserve">39.9794425964355</t>
   </si>
   <si>
     <t xml:space="preserve">43.2064819335938</t>
@@ -4358,10 +4358,10 @@
     <t xml:space="preserve">41.5174751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8665962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0271987915039</t>
+    <t xml:space="preserve">41.8666000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0272026062012</t>
   </si>
   <si>
     <t xml:space="preserve">42.649772644043</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">43.8009338378906</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0557022094727</t>
+    <t xml:space="preserve">44.0557060241699</t>
   </si>
   <si>
     <t xml:space="preserve">43.7160186767578</t>
@@ -4382,16 +4382,16 @@
     <t xml:space="preserve">44.6690330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3574562072754</t>
+    <t xml:space="preserve">43.3574600219727</t>
   </si>
   <si>
     <t xml:space="preserve">43.4329414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1693229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6692276000977</t>
+    <t xml:space="preserve">46.169319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6692237854004</t>
   </si>
   <si>
     <t xml:space="preserve">43.7443237304688</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">43.8292465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0840110778809</t>
+    <t xml:space="preserve">44.0840148925781</t>
   </si>
   <si>
     <t xml:space="preserve">46.7732124328613</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">48.6131896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6129951477051</t>
+    <t xml:space="preserve">47.6129989624023</t>
   </si>
   <si>
     <t xml:space="preserve">47.7639694213867</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">47.0185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6314811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6031761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5654335021973</t>
+    <t xml:space="preserve">45.631477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5654296875</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
@@ -4460,16 +4460,16 @@
     <t xml:space="preserve">45.2917938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8200035095215</t>
+    <t xml:space="preserve">44.8200073242188</t>
   </si>
   <si>
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5937385559082</t>
+    <t xml:space="preserve">45.5465621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5937347412109</t>
   </si>
   <si>
     <t xml:space="preserve">44.7539520263672</t>
@@ -4481,10 +4481,10 @@
     <t xml:space="preserve">46.5844955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2544364929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.745288848877</t>
+    <t xml:space="preserve">47.2544403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7452926635742</t>
   </si>
   <si>
     <t xml:space="preserve">46.6316757202148</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">45.7918891906738</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9049263000488</t>
+    <t xml:space="preserve">44.9049224853516</t>
   </si>
   <si>
     <t xml:space="preserve">46.150447845459</t>
@@ -4505,16 +4505,16 @@
     <t xml:space="preserve">45.3861503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6788558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3110466003418</t>
+    <t xml:space="preserve">46.6788520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3110504150391</t>
   </si>
   <si>
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017082214355</t>
+    <t xml:space="preserve">47.8017120361328</t>
   </si>
   <si>
     <t xml:space="preserve">47.5563812255859</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">50.4814796447754</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8779754638672</t>
+    <t xml:space="preserve">51.8779716491699</t>
   </si>
   <si>
     <t xml:space="preserve">52.3497619628906</t>
@@ -4550,22 +4550,22 @@
     <t xml:space="preserve">53.0857543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9157180786133</t>
+    <t xml:space="preserve">51.915714263916</t>
   </si>
   <si>
     <t xml:space="preserve">53.0480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3310890197754</t>
+    <t xml:space="preserve">53.3310852050781</t>
   </si>
   <si>
     <t xml:space="preserve">53.1046295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2555999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5199928283691</t>
+    <t xml:space="preserve">53.2555961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5199966430664</t>
   </si>
   <si>
     <t xml:space="preserve">54.0859489440918</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">55.4446983337402</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1991806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0293350219727</t>
+    <t xml:space="preserve">54.1991767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0293312072754</t>
   </si>
   <si>
     <t xml:space="preserve">53.4254455566406</t>
@@ -4601,25 +4601,25 @@
     <t xml:space="preserve">53.5009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9349784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8785514831543</t>
+    <t xml:space="preserve">53.9349746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">54.444507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.350341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3125991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9729080200195</t>
+    <t xml:space="preserve">54.4445114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3503456115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3126029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9729118347168</t>
   </si>
   <si>
     <t xml:space="preserve">54.46337890625</t>
@@ -4628,10 +4628,10 @@
     <t xml:space="preserve">55.0106544494629</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3316650390625</t>
+    <t xml:space="preserve">54.5388679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3316688537598</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">57.1808853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4071502685547</t>
+    <t xml:space="preserve">56.407154083252</t>
   </si>
   <si>
     <t xml:space="preserve">56.8789405822754</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">54.8974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0676574707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2748565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6526756286621</t>
+    <t xml:space="preserve">57.0676612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2748603820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6526718139648</t>
   </si>
   <si>
     <t xml:space="preserve">56.2184371948242</t>
@@ -4673,16 +4673,16 @@
     <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5017013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546241760254</t>
+    <t xml:space="preserve">57.5017051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546203613281</t>
   </si>
   <si>
     <t xml:space="preserve">58.1433372497559</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2186317443848</t>
+    <t xml:space="preserve">57.2186279296875</t>
   </si>
   <si>
     <t xml:space="preserve">57.2752456665039</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">59.9550094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1059875488281</t>
+    <t xml:space="preserve">60.1059837341309</t>
   </si>
   <si>
     <t xml:space="preserve">60.0116271972656</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417816162109</t>
+    <t xml:space="preserve">59.8417778015137</t>
   </si>
   <si>
     <t xml:space="preserve">59.4266052246094</t>
@@ -4718,19 +4718,19 @@
     <t xml:space="preserve">62.0686225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">62.219596862793</t>
+    <t xml:space="preserve">62.2196006774902</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8044204711914</t>
+    <t xml:space="preserve">61.8044242858887</t>
   </si>
   <si>
     <t xml:space="preserve">62.2007255554199</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1443061828613</t>
+    <t xml:space="preserve">63.1443023681641</t>
   </si>
   <si>
     <t xml:space="preserve">63.4085121154785</t>
@@ -4739,34 +4739,34 @@
     <t xml:space="preserve">63.8614311218262</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7293281555176</t>
+    <t xml:space="preserve">63.7293243408203</t>
   </si>
   <si>
     <t xml:space="preserve">63.9935264587402</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3707695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896369934082</t>
+    <t xml:space="preserve">63.3707733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896408081055</t>
   </si>
   <si>
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5028648376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.993335723877</t>
+    <t xml:space="preserve">63.5028686523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9933319091797</t>
   </si>
   <si>
     <t xml:space="preserve">62.4649238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8987808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0122108459473</t>
+    <t xml:space="preserve">61.8987846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.01220703125</t>
   </si>
   <si>
     <t xml:space="preserve">62.9178504943848</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">61.5968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8608474731445</t>
+    <t xml:space="preserve">60.8608436584473</t>
   </si>
   <si>
     <t xml:space="preserve">60.7287483215332</t>
@@ -4799,19 +4799,19 @@
     <t xml:space="preserve">60.8631858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2293930053711</t>
+    <t xml:space="preserve">60.2293968200684</t>
   </si>
   <si>
     <t xml:space="preserve">60.9784202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8055686950684</t>
+    <t xml:space="preserve">60.8055648803711</t>
   </si>
   <si>
     <t xml:space="preserve">59.4227523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8042678833008</t>
+    <t xml:space="preserve">61.804271697998</t>
   </si>
   <si>
     <t xml:space="preserve">60.9015960693359</t>
@@ -4820,16 +4820,16 @@
     <t xml:space="preserve">61.2665061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.4982719421387</t>
+    <t xml:space="preserve">60.4982757568359</t>
   </si>
   <si>
     <t xml:space="preserve">61.9963264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1102638244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.071849822998</t>
+    <t xml:space="preserve">63.1102676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">62.898998260498</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">60.9976272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9605102539062</t>
+    <t xml:space="preserve">59.9605140686035</t>
   </si>
   <si>
     <t xml:space="preserve">59.8068656921387</t>
@@ -4865,22 +4865,22 @@
     <t xml:space="preserve">60.3638343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8247756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4214477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7671546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4022445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.865779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.153865814209</t>
+    <t xml:space="preserve">60.8247718811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4214515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7671585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4022483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8657836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1538696289062</t>
   </si>
   <si>
     <t xml:space="preserve">60.1717758178711</t>
@@ -4892,10 +4892,10 @@
     <t xml:space="preserve">62.8797950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">63.379150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2831153869629</t>
+    <t xml:space="preserve">63.3791427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2831192016602</t>
   </si>
   <si>
     <t xml:space="preserve">61.4393577575684</t>
@@ -4904,13 +4904,13 @@
     <t xml:space="preserve">60.5750999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5379867553711</t>
+    <t xml:space="preserve">59.5379829406738</t>
   </si>
   <si>
     <t xml:space="preserve">59.3843383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7492523193359</t>
+    <t xml:space="preserve">59.7492485046387</t>
   </si>
   <si>
     <t xml:space="preserve">59.9028968811035</t>
@@ -4919,10 +4919,10 @@
     <t xml:space="preserve">60.3254203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2883148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.302318572998</t>
+    <t xml:space="preserve">59.2883110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3023223876953</t>
   </si>
   <si>
     <t xml:space="preserve">62.783763885498</t>
@@ -4934,25 +4934,25 @@
     <t xml:space="preserve">60.6135101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1922836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3651351928711</t>
+    <t xml:space="preserve">59.1922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3651313781738</t>
   </si>
   <si>
     <t xml:space="preserve">61.4969787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5161781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7850570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9797172546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8439826965332</t>
+    <t xml:space="preserve">61.5161819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7850608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9797210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8439788818359</t>
   </si>
   <si>
     <t xml:space="preserve">60.5558929443359</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">59.5763969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5571937561035</t>
+    <t xml:space="preserve">59.5571899414062</t>
   </si>
   <si>
     <t xml:space="preserve">59.8836898803711</t>
@@ -4979,28 +4979,28 @@
     <t xml:space="preserve">60.1525688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1333618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1346626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.196174621582</t>
+    <t xml:space="preserve">60.1333656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1346664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1961784362793</t>
   </si>
   <si>
     <t xml:space="preserve">56.080940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1769676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8683815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2153816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7915573120117</t>
+    <t xml:space="preserve">56.1769714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8683776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2153854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7915534973145</t>
   </si>
   <si>
     <t xml:space="preserve">57.4061393737793</t>
@@ -5012,22 +5012,22 @@
     <t xml:space="preserve">55.4087409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">55.447151184082</t>
+    <t xml:space="preserve">55.4471473693848</t>
   </si>
   <si>
     <t xml:space="preserve">54.2948036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1974754333496</t>
+    <t xml:space="preserve">55.1974716186523</t>
   </si>
   <si>
     <t xml:space="preserve">54.0451240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1437492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2218742370605</t>
+    <t xml:space="preserve">52.1437530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2218704223633</t>
   </si>
   <si>
     <t xml:space="preserve">52.3742218017578</t>
@@ -5045,7 +5045,7 @@
     <t xml:space="preserve">52.4510459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6431045532227</t>
+    <t xml:space="preserve">52.6431007385254</t>
   </si>
   <si>
     <t xml:space="preserve">53.7954521179199</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">50.7417259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">51.068229675293</t>
+    <t xml:space="preserve">51.0682258605957</t>
   </si>
   <si>
     <t xml:space="preserve">50.8377571105957</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">50.8761711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9337882995605</t>
+    <t xml:space="preserve">50.9337844848633</t>
   </si>
   <si>
     <t xml:space="preserve">51.0106086730957</t>
@@ -5093,22 +5093,22 @@
     <t xml:space="preserve">49.8006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.583667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8237457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9965972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5823707580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1668510437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9747924804688</t>
+    <t xml:space="preserve">46.5836715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8237419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9965934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5823745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1668548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.974796295166</t>
   </si>
   <si>
     <t xml:space="preserve">48.7827339172363</t>
@@ -5126,19 +5126,19 @@
     <t xml:space="preserve">47.4959449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7552223205566</t>
+    <t xml:space="preserve">47.7552261352539</t>
   </si>
   <si>
     <t xml:space="preserve">49.4165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4946479797363</t>
+    <t xml:space="preserve">48.4946517944336</t>
   </si>
   <si>
     <t xml:space="preserve">48.4370307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5701751708984</t>
+    <t xml:space="preserve">49.5701713562012</t>
   </si>
   <si>
     <t xml:space="preserve">48.9363822937012</t>
@@ -5153,16 +5153,16 @@
     <t xml:space="preserve">49.5125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2628784179688</t>
+    <t xml:space="preserve">49.262882232666</t>
   </si>
   <si>
     <t xml:space="preserve">48.7059135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9939994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.859561920166</t>
+    <t xml:space="preserve">48.9940032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8595581054688</t>
   </si>
   <si>
     <t xml:space="preserve">48.6675033569336</t>
@@ -5171,13 +5171,13 @@
     <t xml:space="preserve">49.4549407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8774681091309</t>
+    <t xml:space="preserve">49.8774642944336</t>
   </si>
   <si>
     <t xml:space="preserve">50.2999954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">51.529167175293</t>
+    <t xml:space="preserve">51.5291633605957</t>
   </si>
   <si>
     <t xml:space="preserve">52.4318389892578</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">52.9696006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5265693664551</t>
+    <t xml:space="preserve">53.5265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">54.0259208679199</t>
@@ -5207,13 +5207,13 @@
     <t xml:space="preserve">53.7762451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7378349304199</t>
+    <t xml:space="preserve">53.7378311157227</t>
   </si>
   <si>
     <t xml:space="preserve">53.3537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4881553649902</t>
+    <t xml:space="preserve">53.4881591796875</t>
   </si>
   <si>
     <t xml:space="preserve">53.4305381774902</t>
@@ -5249,34 +5249,34 @@
     <t xml:space="preserve">49.1092338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4933547973633</t>
+    <t xml:space="preserve">49.493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">49.3973197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8390579223633</t>
+    <t xml:space="preserve">49.839054107666</t>
   </si>
   <si>
     <t xml:space="preserve">49.896671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6020927429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0054168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0246238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4279441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0617332458496</t>
+    <t xml:space="preserve">54.6020965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0054130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0246200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8901824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4279479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0617370605469</t>
   </si>
   <si>
     <t xml:space="preserve">55.8312644958496</t>
@@ -5291,10 +5291,10 @@
     <t xml:space="preserve">57.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0028190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3293190002441</t>
+    <t xml:space="preserve">57.0028228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">60.0373344421387</t>
@@ -5309,7 +5309,7 @@
     <t xml:space="preserve">61.1896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5545921325684</t>
+    <t xml:space="preserve">61.5545959472656</t>
   </si>
   <si>
     <t xml:space="preserve">61.1512718200684</t>
@@ -5324,19 +5324,19 @@
     <t xml:space="preserve">64.2626113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3599433898926</t>
+    <t xml:space="preserve">63.3599395751953</t>
   </si>
   <si>
     <t xml:space="preserve">63.9937286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3394317626953</t>
+    <t xml:space="preserve">64.3394393920898</t>
   </si>
   <si>
     <t xml:space="preserve">64.4354629516602</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5686111450195</t>
+    <t xml:space="preserve">65.568603515625</t>
   </si>
   <si>
     <t xml:space="preserve">66.6249237060547</t>
@@ -5345,7 +5345,7 @@
     <t xml:space="preserve">66.8746032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5467987060547</t>
+    <t xml:space="preserve">67.5468063354492</t>
   </si>
   <si>
     <t xml:space="preserve">66.5096969604492</t>
@@ -5354,16 +5354,16 @@
     <t xml:space="preserve">66.4712829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7798767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5301971435547</t>
+    <t xml:space="preserve">65.7798690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5301895141602</t>
   </si>
   <si>
     <t xml:space="preserve">65.4533767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2997207641602</t>
+    <t xml:space="preserve">65.2997283935547</t>
   </si>
   <si>
     <t xml:space="preserve">65.799072265625</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">62.0155372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0539512634277</t>
+    <t xml:space="preserve">62.0539474487305</t>
   </si>
   <si>
     <t xml:space="preserve">61.6122131347656</t>
@@ -5402,28 +5402,28 @@
     <t xml:space="preserve">63.4367599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8413887023926</t>
+    <t xml:space="preserve">63.0334396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8413848876953</t>
   </si>
   <si>
     <t xml:space="preserve">62.668529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2254905700684</t>
+    <t xml:space="preserve">63.2254981994629</t>
   </si>
   <si>
     <t xml:space="preserve">64.1473770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1883888244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3420295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9579162597656</t>
+    <t xml:space="preserve">62.1883850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3420333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9579124450684</t>
   </si>
   <si>
     <t xml:space="preserve">61.573802947998</t>
@@ -6480,6 +6480,9 @@
   </si>
   <si>
     <t xml:space="preserve">58.0400009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6399993896484</t>
   </si>
 </sst>
 </file>
@@ -72442,7 +72445,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6911574074</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>637436</v>
@@ -72463,6 +72466,32 @@
         <v>2155</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6910532407</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>548001</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>58.5999984741211</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>57.5200004577637</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>58.2999992370605</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>57.6399993896484</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>2156</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="2163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="2164">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765724182129</t>
+    <t xml:space="preserve">11.0765733718872</t>
   </si>
   <si>
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698114395142</t>
+    <t xml:space="preserve">10.9698095321655</t>
   </si>
   <si>
     <t xml:space="preserve">10.8452548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986368179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876050949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744365692139</t>
+    <t xml:space="preserve">10.8986349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744375228882</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573593139648</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769306182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.156641960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5481042861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7349376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4057540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8239068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.117504119873</t>
+    <t xml:space="preserve">11.4769296646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1566438674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5481052398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.734938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4057559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175031661987</t>
   </si>
   <si>
     <t xml:space="preserve">12.0018444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1264009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0997114181519</t>
+    <t xml:space="preserve">12.1263999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0997085571289</t>
   </si>
   <si>
     <t xml:space="preserve">11.7260417938232</t>
@@ -107,49 +107,49 @@
     <t xml:space="preserve">11.8950815200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7616300582886</t>
+    <t xml:space="preserve">11.7616291046143</t>
   </si>
   <si>
     <t xml:space="preserve">11.9128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4146537780762</t>
+    <t xml:space="preserve">11.4146547317505</t>
   </si>
   <si>
     <t xml:space="preserve">11.2723035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0409860610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2545099258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431200027466</t>
+    <t xml:space="preserve">11.0409851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.254508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431209564209</t>
   </si>
   <si>
     <t xml:space="preserve">11.2989921569824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6726598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8772878646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110984802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.250958442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2687511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4022016525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.797215461731</t>
+    <t xml:space="preserve">11.672661781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8772897720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4110994338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2509565353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2687501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4022026062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7972164154053</t>
   </si>
   <si>
     <t xml:space="preserve">12.1975746154785</t>
@@ -158,82 +158,82 @@
     <t xml:space="preserve">12.7402820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9627027511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7669744491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2118148803711</t>
+    <t xml:space="preserve">12.962703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7669734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2118167877197</t>
   </si>
   <si>
     <t xml:space="preserve">13.407546043396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4787197113037</t>
+    <t xml:space="preserve">13.478720664978</t>
   </si>
   <si>
     <t xml:space="preserve">13.9680471420288</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4520311355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7100391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363704681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0427742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605697631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9893951416016</t>
+    <t xml:space="preserve">13.4520301818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210699081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7100372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.336371421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0427751541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.060567855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9893932342529</t>
   </si>
   <si>
     <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0160856246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449081420898</t>
+    <t xml:space="preserve">13.0160865783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449110031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.0961570739746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.514307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1228456497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9804964065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.927116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5890350341797</t>
+    <t xml:space="preserve">13.5143070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1228466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9804973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9271144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.589035987854</t>
   </si>
   <si>
     <t xml:space="preserve">12.7936630249023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.829252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338773727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737363815308</t>
+    <t xml:space="preserve">12.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737354278564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1495370864868</t>
@@ -245,43 +245,43 @@
     <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1673316955566</t>
+    <t xml:space="preserve">13.167329788208</t>
   </si>
   <si>
     <t xml:space="preserve">12.6869029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5089654922485</t>
+    <t xml:space="preserve">12.5089645385742</t>
   </si>
   <si>
     <t xml:space="preserve">12.5979337692261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9715995788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.998291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3185787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9324607849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947385787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6388635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676889419556</t>
+    <t xml:space="preserve">12.9716005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9982900619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3185777664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9324588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570154190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6388645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676898956299</t>
   </si>
   <si>
     <t xml:space="preserve">13.3630628585815</t>
@@ -296,91 +296,91 @@
     <t xml:space="preserve">13.5608043670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4440546035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2734231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967273712158</t>
+    <t xml:space="preserve">13.444055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2734212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709978103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967264175415</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620170593262</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4979400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.668571472168</t>
+    <t xml:space="preserve">13.4979391098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183269500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6685733795166</t>
   </si>
   <si>
     <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7404165267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3003664016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1566743850708</t>
+    <t xml:space="preserve">13.7404184341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.300365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1566724777222</t>
   </si>
   <si>
     <t xml:space="preserve">12.7256021499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.860312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122625350952</t>
+    <t xml:space="preserve">13.2105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8603115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122615814209</t>
   </si>
   <si>
     <t xml:space="preserve">13.6775522232056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8571672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2253732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035116195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6986608505249</t>
+    <t xml:space="preserve">13.8571653366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2253723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6986598968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.1476936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.995020866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6178340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8513307571411</t>
+    <t xml:space="preserve">12.995023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6178331375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">12.8782730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9680795669556</t>
+    <t xml:space="preserve">12.9680786132812</t>
   </si>
   <si>
     <t xml:space="preserve">12.9231758117676</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">13.1746349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.959098815918</t>
+    <t xml:space="preserve">12.9590997695923</t>
   </si>
   <si>
     <t xml:space="preserve">12.9501190185547</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">13.8302230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1714887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.063720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3690643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0816822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9559516906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069198608398</t>
+    <t xml:space="preserve">14.1714897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0637197494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3690624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0816831588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9559526443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069189071655</t>
   </si>
   <si>
     <t xml:space="preserve">13.6057071685791</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">14.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8481845855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0457592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9918756484985</t>
+    <t xml:space="preserve">13.8481855392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0457601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9918766021729</t>
   </si>
   <si>
     <t xml:space="preserve">13.9200305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7673597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0008554458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.758376121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877456665039</t>
+    <t xml:space="preserve">13.7673587799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0008563995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7583780288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6955137252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
     <t xml:space="preserve">13.524881362915</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">13.354248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4171133041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159006118774</t>
+    <t xml:space="preserve">13.4171123504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159015655518</t>
   </si>
   <si>
     <t xml:space="preserve">13.7224550247192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5338621139526</t>
+    <t xml:space="preserve">13.5338611602783</t>
   </si>
   <si>
     <t xml:space="preserve">13.704493522644</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">13.6146869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0098390579224</t>
+    <t xml:space="preserve">14.0098361968994</t>
   </si>
   <si>
     <t xml:space="preserve">14.0727014541626</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">13.6506109237671</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6416301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853212356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4799766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8392057418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0996417999268</t>
+    <t xml:space="preserve">13.6416292190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4799776077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8392028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0996437072754</t>
   </si>
   <si>
     <t xml:space="preserve">13.8930892944336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9649343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8751258850098</t>
+    <t xml:space="preserve">13.9649333953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8751268386841</t>
   </si>
   <si>
     <t xml:space="preserve">13.79430103302</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">13.3991508483887</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3901700973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4889602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6326503753662</t>
+    <t xml:space="preserve">13.3901720046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4889583587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6326484680176</t>
   </si>
   <si>
     <t xml:space="preserve">13.3273057937622</t>
@@ -554,88 +554,88 @@
     <t xml:space="preserve">13.8661460876465</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0547409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6474647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.638482093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9168834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0426120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989229202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5486783981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7372694015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731952667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8719787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911539077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564455032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.683388710022</t>
+    <t xml:space="preserve">14.0547389984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6474637985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6384830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9168863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.04261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.548677444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7372713088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731943130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8719797134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6833877563477</t>
   </si>
   <si>
     <t xml:space="preserve">14.7013483047485</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8450393676758</t>
+    <t xml:space="preserve">14.8450384140015</t>
   </si>
   <si>
     <t xml:space="preserve">15.0875158309937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7103281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6744060516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9528036117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377632141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6892213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251462936401</t>
+    <t xml:space="preserve">14.9707708358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7103290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6744050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9528045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6892232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251434326172</t>
   </si>
   <si>
     <t xml:space="preserve">15.482666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0933532714844</t>
+    <t xml:space="preserve">15.7790288925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0933513641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.1651954650879</t>
@@ -644,61 +644,61 @@
     <t xml:space="preserve">16.2011203765869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1921367645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2460231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9855833053589</t>
+    <t xml:space="preserve">16.1921405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.246021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9855794906616</t>
   </si>
   <si>
     <t xml:space="preserve">15.9137372970581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6353378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9317007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766044616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9586410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406805038452</t>
+    <t xml:space="preserve">15.6353368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9766006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9586420059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406785964966</t>
   </si>
   <si>
     <t xml:space="preserve">15.8867950439453</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1741771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.102331161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0484485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8957805633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831607818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0991840362549</t>
+    <t xml:space="preserve">16.1741790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1023330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0484504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8957757949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9676218032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831569671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0991878509521</t>
   </si>
   <si>
     <t xml:space="preserve">17.2608375549316</t>
@@ -707,61 +707,61 @@
     <t xml:space="preserve">17.1620502471924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2967624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3326797485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5122947692871</t>
+    <t xml:space="preserve">17.296760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3326816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5122966766357</t>
   </si>
   <si>
     <t xml:space="preserve">17.5661792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6559867858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6021060943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8535594940186</t>
+    <t xml:space="preserve">17.65598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6021022796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">18.0062313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1768684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8805065155029</t>
+    <t xml:space="preserve">18.1768627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.880500793457</t>
   </si>
   <si>
     <t xml:space="preserve">18.0601177215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0870571136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3205585479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2666721343994</t>
+    <t xml:space="preserve">18.0870552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3205528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2666702270508</t>
   </si>
   <si>
     <t xml:space="preserve">18.4103622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1678867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2756519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4373073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169185638428</t>
+    <t xml:space="preserve">18.1678829193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2756500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4373035430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169166564941</t>
   </si>
   <si>
     <t xml:space="preserve">18.9312400817871</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">19.2276039123535</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2365837097168</t>
+    <t xml:space="preserve">19.2365856170654</t>
   </si>
   <si>
     <t xml:space="preserve">19.2006607055664</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">19.4790630340576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5598888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1108551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2096424102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3174133300781</t>
+    <t xml:space="preserve">19.5598907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1108589172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.209644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3174095153809</t>
   </si>
   <si>
     <t xml:space="preserve">19.5329456329346</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">19.6945991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4611015319824</t>
+    <t xml:space="preserve">19.4611034393311</t>
   </si>
   <si>
     <t xml:space="preserve">19.5778465270996</t>
@@ -806,49 +806,49 @@
     <t xml:space="preserve">19.514986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">20.188533782959</t>
+    <t xml:space="preserve">20.1885375976562</t>
   </si>
   <si>
     <t xml:space="preserve">20.4310131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3501853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6645107269287</t>
+    <t xml:space="preserve">20.3501873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6645126342773</t>
   </si>
   <si>
     <t xml:space="preserve">20.8351402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1135425567627</t>
+    <t xml:space="preserve">21.1135444641113</t>
   </si>
   <si>
     <t xml:space="preserve">20.4759140014648</t>
   </si>
   <si>
-    <t xml:space="preserve">19.78440284729</t>
+    <t xml:space="preserve">19.7844047546387</t>
   </si>
   <si>
     <t xml:space="preserve">19.9999408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8921737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9819793701172</t>
+    <t xml:space="preserve">19.8921718597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9819812774658</t>
   </si>
   <si>
     <t xml:space="preserve">19.874210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9909629821777</t>
+    <t xml:space="preserve">19.9909610748291</t>
   </si>
   <si>
     <t xml:space="preserve">19.3892574310303</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5509071350098</t>
+    <t xml:space="preserve">19.5509090423584</t>
   </si>
   <si>
     <t xml:space="preserve">19.6505184173584</t>
@@ -869,25 +869,25 @@
     <t xml:space="preserve">19.2339630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6324062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7048492431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2792415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9260749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0075740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9713554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0800170898438</t>
+    <t xml:space="preserve">19.6324043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7048511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2792434692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9260768890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0075759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9713535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.080020904541</t>
   </si>
   <si>
     <t xml:space="preserve">18.5819644927979</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">18.8355197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1252994537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0437984466553</t>
+    <t xml:space="preserve">19.1252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0437965393066</t>
   </si>
   <si>
     <t xml:space="preserve">19.3426284790039</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">19.2249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6142959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2158508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1524620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1434078216553</t>
+    <t xml:space="preserve">19.614294052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2158489227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1524639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1434059143066</t>
   </si>
   <si>
     <t xml:space="preserve">19.3245162963867</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">18.3736896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5638523101807</t>
+    <t xml:space="preserve">18.5638542175293</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362991333008</t>
@@ -938,28 +938,28 @@
     <t xml:space="preserve">18.6000747680664</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8083534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7359066009521</t>
+    <t xml:space="preserve">18.8083515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7359085083008</t>
   </si>
   <si>
     <t xml:space="preserve">18.609130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1071834564209</t>
+    <t xml:space="preserve">19.1071853637695</t>
   </si>
   <si>
     <t xml:space="preserve">19.288293838501</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3788509368896</t>
+    <t xml:space="preserve">19.3788528442383</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4512939453125</t>
+    <t xml:space="preserve">19.4512958526611</t>
   </si>
   <si>
     <t xml:space="preserve">19.4331855773926</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1977424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2391300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.465518951416</t>
+    <t xml:space="preserve">19.1977386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.239128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4655151367188</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560741424561</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2572402954102</t>
+    <t xml:space="preserve">20.3568515777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2572383880615</t>
   </si>
   <si>
     <t xml:space="preserve">20.3930721282959</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">20.329683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3749618530273</t>
+    <t xml:space="preserve">20.374963760376</t>
   </si>
   <si>
     <t xml:space="preserve">20.4021263122559</t>
@@ -1001,55 +1001,55 @@
     <t xml:space="preserve">20.3477935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8458518981934</t>
+    <t xml:space="preserve">20.8458499908447</t>
   </si>
   <si>
     <t xml:space="preserve">21.144681930542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5431251525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.380126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3439025878906</t>
+    <t xml:space="preserve">21.5431270599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.343900680542</t>
   </si>
   <si>
     <t xml:space="preserve">21.4254035949707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3710670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2805156707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2080688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8730144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2714595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6155681610107</t>
+    <t xml:space="preserve">21.3710689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2805137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2080707550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8730163574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2714576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.615571975708</t>
   </si>
   <si>
     <t xml:space="preserve">21.8962917327881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7423477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7966804504395</t>
+    <t xml:space="preserve">21.7423496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7966785430908</t>
   </si>
   <si>
     <t xml:space="preserve">21.9959011077881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1589012145996</t>
+    <t xml:space="preserve">22.158899307251</t>
   </si>
   <si>
     <t xml:space="preserve">22.4305667877197</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">22.3671798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5935688018799</t>
+    <t xml:space="preserve">22.5935668945312</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116771697998</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">22.5030136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2404003143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3852920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2313423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2132339477539</t>
+    <t xml:space="preserve">22.2404041290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3852882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2313461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2132358551025</t>
   </si>
   <si>
     <t xml:space="preserve">22.2494564056396</t>
@@ -1085,25 +1085,25 @@
     <t xml:space="preserve">21.959680557251</t>
   </si>
   <si>
-    <t xml:space="preserve">21.823844909668</t>
+    <t xml:space="preserve">21.8238468170166</t>
   </si>
   <si>
     <t xml:space="preserve">22.0683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1136245727539</t>
+    <t xml:space="preserve">22.1136264801025</t>
   </si>
   <si>
     <t xml:space="preserve">22.1407909393311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8419589996338</t>
+    <t xml:space="preserve">21.8419570922852</t>
   </si>
   <si>
     <t xml:space="preserve">21.7514038085938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4706802368164</t>
+    <t xml:space="preserve">21.470682144165</t>
   </si>
   <si>
     <t xml:space="preserve">22.149845123291</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">22.2766227722168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.059289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2856788635254</t>
+    <t xml:space="preserve">22.0592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.285680770874</t>
   </si>
   <si>
     <t xml:space="preserve">22.3490695953369</t>
@@ -1124,28 +1124,28 @@
     <t xml:space="preserve">22.394344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9868488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4396209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5573482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3581237792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1226806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0774021148682</t>
+    <t xml:space="preserve">21.9868469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4396228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5573463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3581256866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1226787567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0774002075195</t>
   </si>
   <si>
     <t xml:space="preserve">22.0049571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9415664672852</t>
+    <t xml:space="preserve">21.9415683746338</t>
   </si>
   <si>
     <t xml:space="preserve">21.8510112762451</t>
@@ -1154,46 +1154,46 @@
     <t xml:space="preserve">21.7695159912109</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6466236114502</t>
+    <t xml:space="preserve">20.6466274261475</t>
   </si>
   <si>
     <t xml:space="preserve">21.0631828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">21.008846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6737937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7734050750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6556816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0994033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0903491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1356258392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8277359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549060821533</t>
+    <t xml:space="preserve">21.0088481903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6737957000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7734031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6556854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0994052886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0903472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.135627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8277378082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549041748047</t>
   </si>
   <si>
     <t xml:space="preserve">20.8005695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8820724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.434455871582</t>
+    <t xml:space="preserve">20.8820686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4344577789307</t>
   </si>
   <si>
     <t xml:space="preserve">21.4163475036621</t>
@@ -1205,52 +1205,52 @@
     <t xml:space="preserve">22.4667911529541</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5120697021484</t>
+    <t xml:space="preserve">22.5120658874512</t>
   </si>
   <si>
     <t xml:space="preserve">22.8833446502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3219013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8109016418457</t>
+    <t xml:space="preserve">22.3219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290119171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8109035491943</t>
   </si>
   <si>
     <t xml:space="preserve">23.0916194915771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2546234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6530647277832</t>
+    <t xml:space="preserve">23.2546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6530666351318</t>
   </si>
   <si>
     <t xml:space="preserve">23.9066200256348</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6168422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1821784973145</t>
+    <t xml:space="preserve">23.6168441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">23.6349563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4900665283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5443992614746</t>
+    <t xml:space="preserve">23.4900646209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.544397354126</t>
   </si>
   <si>
     <t xml:space="preserve">23.200288772583</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">23.8160648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3412857055664</t>
+    <t xml:space="preserve">24.341287612915</t>
   </si>
   <si>
     <t xml:space="preserve">24.4861755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2507343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3775062561035</t>
+    <t xml:space="preserve">24.2507305145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3775081634521</t>
   </si>
   <si>
     <t xml:space="preserve">24.5042858123779</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5223960876465</t>
+    <t xml:space="preserve">24.5223999023438</t>
   </si>
   <si>
     <t xml:space="preserve">24.2869529724121</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">24.114896774292</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0334014892578</t>
+    <t xml:space="preserve">24.0333976745605</t>
   </si>
   <si>
     <t xml:space="preserve">24.2145099639893</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">23.5625114440918</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4628982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.359395980835</t>
+    <t xml:space="preserve">23.4629001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3593997955322</t>
   </si>
   <si>
     <t xml:space="preserve">23.290843963623</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">25.4279518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5637817382812</t>
+    <t xml:space="preserve">25.5637836456299</t>
   </si>
   <si>
     <t xml:space="preserve">25.5818958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4641780853271</t>
+    <t xml:space="preserve">25.4641742706299</t>
   </si>
   <si>
     <t xml:space="preserve">25.3917293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6362285614014</t>
+    <t xml:space="preserve">25.63623046875</t>
   </si>
   <si>
     <t xml:space="preserve">26.1342830657959</t>
@@ -1352,49 +1352,49 @@
     <t xml:space="preserve">25.264949798584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6996173858643</t>
+    <t xml:space="preserve">25.699613571167</t>
   </si>
   <si>
     <t xml:space="preserve">25.5728397369385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2157821655273</t>
+    <t xml:space="preserve">26.2157802581787</t>
   </si>
   <si>
     <t xml:space="preserve">26.405948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5055618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6685581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4874477386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8134498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7500591278076</t>
+    <t xml:space="preserve">26.5055599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6685619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4874496459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8134479522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7500610351562</t>
   </si>
   <si>
     <t xml:space="preserve">26.9583377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4654483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9453907012939</t>
+    <t xml:space="preserve">27.4654445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9453926086426</t>
   </si>
   <si>
     <t xml:space="preserve">27.5741138458252</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7190017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6737232208252</t>
+    <t xml:space="preserve">27.7190036773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6737251281738</t>
   </si>
   <si>
     <t xml:space="preserve">27.9182224273682</t>
@@ -1406,43 +1406,43 @@
     <t xml:space="preserve">29.765552520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4304981231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.810827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.236442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9104385375977</t>
+    <t xml:space="preserve">29.4305000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8108310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549434661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2364406585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9104404449463</t>
   </si>
   <si>
     <t xml:space="preserve">30.562442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8250541687012</t>
+    <t xml:space="preserve">30.8250484466553</t>
   </si>
   <si>
     <t xml:space="preserve">30.4809436798096</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2053833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9026584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.712495803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0203819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.920768737793</t>
+    <t xml:space="preserve">31.205379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9026565551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7124919891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.020378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9207744598389</t>
   </si>
   <si>
     <t xml:space="preserve">32.6180458068848</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">32.690486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9621543884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4602127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110412597656</t>
+    <t xml:space="preserve">32.9621620178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4602088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110488891602</t>
   </si>
   <si>
     <t xml:space="preserve">33.0527153015137</t>
@@ -1469,46 +1469,46 @@
     <t xml:space="preserve">32.3011054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0345993041992</t>
+    <t xml:space="preserve">33.0346031188965</t>
   </si>
   <si>
     <t xml:space="preserve">33.0798797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3153305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6866035461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0759887695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3929290771484</t>
+    <t xml:space="preserve">33.3153228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.686595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0759925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0941047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3929252624512</t>
   </si>
   <si>
     <t xml:space="preserve">35.2350997924805</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6788177490234</t>
+    <t xml:space="preserve">35.678825378418</t>
   </si>
   <si>
     <t xml:space="preserve">35.4416923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4749336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7270698547363</t>
+    <t xml:space="preserve">34.4749374389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7270660400391</t>
   </si>
   <si>
     <t xml:space="preserve">34.5022964477539</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8064994812012</t>
+    <t xml:space="preserve">35.8065032958984</t>
   </si>
   <si>
     <t xml:space="preserve">36.007152557373</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">35.1589584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8429870605469</t>
+    <t xml:space="preserve">35.8156280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8429832458496</t>
   </si>
   <si>
     <t xml:space="preserve">36.3354835510254</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">37.7035369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2931175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2534027099609</t>
+    <t xml:space="preserve">37.2931251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2533988952637</t>
   </si>
   <si>
     <t xml:space="preserve">37.2748794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9041862487793</t>
+    <t xml:space="preserve">37.5940933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9041900634766</t>
   </si>
   <si>
     <t xml:space="preserve">38.4696502685547</t>
@@ -1556,43 +1556,43 @@
     <t xml:space="preserve">37.8221054077148</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6547012329102</t>
+    <t xml:space="preserve">36.6546974182129</t>
   </si>
   <si>
     <t xml:space="preserve">36.3446044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2807655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0892372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4143257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3960914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5146560668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1042366027832</t>
+    <t xml:space="preserve">36.28076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0892333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4143333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3960952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1042404174805</t>
   </si>
   <si>
     <t xml:space="preserve">35.5693740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3504867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5205345153809</t>
+    <t xml:space="preserve">35.3504829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5205307006836</t>
   </si>
   <si>
     <t xml:space="preserve">33.9550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.745304107666</t>
+    <t xml:space="preserve">33.7453079223633</t>
   </si>
   <si>
     <t xml:space="preserve">34.2925262451172</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">34.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1224746704102</t>
+    <t xml:space="preserve">35.5967407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1224784851074</t>
   </si>
   <si>
     <t xml:space="preserve">35.6241035461426</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4690475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3869705200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.241039276123</t>
+    <t xml:space="preserve">35.469051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3869667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2410430908203</t>
   </si>
   <si>
     <t xml:space="preserve">36.1622009277344</t>
@@ -1631,79 +1631,79 @@
     <t xml:space="preserve">34.8853492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6938209533691</t>
+    <t xml:space="preserve">34.6938285827637</t>
   </si>
   <si>
     <t xml:space="preserve">33.8091430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.401969909668</t>
+    <t xml:space="preserve">34.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">34.2013244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4169692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3746109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5387725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7303047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6208610534668</t>
+    <t xml:space="preserve">33.4169807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2651634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3746070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5387763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7303085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6208572387695</t>
   </si>
   <si>
     <t xml:space="preserve">34.0189170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8215103149414</t>
+    <t xml:space="preserve">34.8215065002441</t>
   </si>
   <si>
     <t xml:space="preserve">34.4840545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7941474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5784950256348</t>
+    <t xml:space="preserve">34.7941436767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5784912109375</t>
   </si>
   <si>
     <t xml:space="preserve">36.2169189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">36.153076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172492980957</t>
+    <t xml:space="preserve">36.1530799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172454833984</t>
   </si>
   <si>
     <t xml:space="preserve">35.5328941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5055351257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1133575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8365058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2834053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3381271362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3016471862793</t>
+    <t xml:space="preserve">35.5055313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1133613586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8365097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2834091186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3381309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.301643371582</t>
   </si>
   <si>
     <t xml:space="preserve">34.785026550293</t>
@@ -1712,49 +1712,49 @@
     <t xml:space="preserve">33.9824333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6117362976074</t>
+    <t xml:space="preserve">34.6117401123047</t>
   </si>
   <si>
     <t xml:space="preserve">34.4202117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5934982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5114097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0827560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664581298828</t>
+    <t xml:space="preserve">34.5934944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5114135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0827598571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664657592773</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9400672912598</t>
+    <t xml:space="preserve">34.940071105957</t>
   </si>
   <si>
     <t xml:space="preserve">32.9791946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8300342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4593353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9388809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5284614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2001285552979</t>
+    <t xml:space="preserve">31.8300323486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4593391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9388790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5284633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2001304626465</t>
   </si>
   <si>
     <t xml:space="preserve">27.6529083251953</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">28.263973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4007797241211</t>
+    <t xml:space="preserve">28.4007778167725</t>
   </si>
   <si>
     <t xml:space="preserve">28.4555015563965</t>
@@ -1772,19 +1772,19 @@
     <t xml:space="preserve">27.7258720397949</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7988338470459</t>
+    <t xml:space="preserve">27.7988357543945</t>
   </si>
   <si>
     <t xml:space="preserve">26.6587924957275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2698516845703</t>
+    <t xml:space="preserve">27.2698554992676</t>
   </si>
   <si>
     <t xml:space="preserve">27.9082794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5708293914795</t>
+    <t xml:space="preserve">27.5708255767822</t>
   </si>
   <si>
     <t xml:space="preserve">27.1786499023438</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">27.5434665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9994831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0906848907471</t>
+    <t xml:space="preserve">27.9994869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0906867980957</t>
   </si>
   <si>
     <t xml:space="preserve">29.5499458312988</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">28.97536277771</t>
   </si>
   <si>
-    <t xml:space="preserve">29.130407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926288604736</t>
+    <t xml:space="preserve">29.1304092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6926307678223</t>
   </si>
   <si>
     <t xml:space="preserve">27.4522609710693</t>
@@ -1820,70 +1820,70 @@
     <t xml:space="preserve">29.0392017364502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0268421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0359630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3519382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2666168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8503189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8138370513916</t>
+    <t xml:space="preserve">28.0268440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0359649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2666187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.813835144043</t>
   </si>
   <si>
     <t xml:space="preserve">27.4340209960938</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2060127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7317543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9141616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.807954788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7682361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3063373565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.512866973877</t>
+    <t xml:space="preserve">27.2060108184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7317562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9141635894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.768238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3063354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5128650665283</t>
   </si>
   <si>
     <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4822654724121</t>
+    <t xml:space="preserve">25.4822673797607</t>
   </si>
   <si>
     <t xml:space="preserve">25.327220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.956521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646709442139</t>
+    <t xml:space="preserve">25.9565258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646747589111</t>
   </si>
   <si>
     <t xml:space="preserve">25.1265716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6431922912598</t>
+    <t xml:space="preserve">24.6431941986084</t>
   </si>
   <si>
     <t xml:space="preserve">25.1721744537354</t>
@@ -1898,31 +1898,31 @@
     <t xml:space="preserve">25.3454627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5825901031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.385181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5949478149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3637008666992</t>
+    <t xml:space="preserve">25.5825881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3851795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.59494972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3636989593506</t>
   </si>
   <si>
     <t xml:space="preserve">26.467264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1877727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6014270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1454086303711</t>
+    <t xml:space="preserve">27.1877708435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.935640335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6014289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1454105377197</t>
   </si>
   <si>
     <t xml:space="preserve">27.0600872039795</t>
@@ -1931,91 +1931,91 @@
     <t xml:space="preserve">27.0327243804932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3336944580078</t>
+    <t xml:space="preserve">27.3336963653564</t>
   </si>
   <si>
     <t xml:space="preserve">27.4066600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6711521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8991584777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3792972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9538822174072</t>
+    <t xml:space="preserve">27.6711502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8991603851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.379301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9538803100586</t>
   </si>
   <si>
     <t xml:space="preserve">27.8809185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2366104125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.914758682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0059623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5987854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.799430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2007236480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4437389373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6443824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9362354278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8117904663086</t>
+    <t xml:space="preserve">28.2366123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9147605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0059585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.598783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7994289398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2007293701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4437408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6443862915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9362373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284111022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8117923736572</t>
   </si>
   <si>
     <t xml:space="preserve">31.7753067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6567420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743366241455</t>
+    <t xml:space="preserve">31.6567440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743347167969</t>
   </si>
   <si>
     <t xml:space="preserve">31.9668350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9029903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1557235717773</t>
+    <t xml:space="preserve">31.9029960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1557197570801</t>
   </si>
   <si>
     <t xml:space="preserve">33.7909088134766</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">32.9244728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8332672119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6964645385742</t>
+    <t xml:space="preserve">32.8332710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.696460723877</t>
   </si>
   <si>
     <t xml:space="preserve">32.5140571594238</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5778999328613</t>
+    <t xml:space="preserve">32.5779037475586</t>
   </si>
   <si>
     <t xml:space="preserve">32.4319763183594</t>
@@ -2042,43 +2042,43 @@
     <t xml:space="preserve">32.9153518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0065498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5264129638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1980819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.231330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7388305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4410972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7603034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5081825256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6084976196289</t>
+    <t xml:space="preserve">33.0065536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5264167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1980857849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2313270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7388286590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4410934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7603073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5081748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6085014343262</t>
   </si>
   <si>
     <t xml:space="preserve">34.128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9277114868164</t>
+    <t xml:space="preserve">33.9277076721191</t>
   </si>
   <si>
     <t xml:space="preserve">33.8638725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8150329589844</t>
+    <t xml:space="preserve">32.8150291442871</t>
   </si>
   <si>
     <t xml:space="preserve">32.659984588623</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">33.2163238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2892875671387</t>
+    <t xml:space="preserve">33.2892837524414</t>
   </si>
   <si>
     <t xml:space="preserve">33.0977592468262</t>
@@ -2096,46 +2096,46 @@
     <t xml:space="preserve">33.426097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1160011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3075294494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8729934692383</t>
+    <t xml:space="preserve">33.1160049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3075256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.872989654541</t>
   </si>
   <si>
     <t xml:space="preserve">33.6814613342285</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0612831115723</t>
+    <t xml:space="preserve">33.0612754821777</t>
   </si>
   <si>
     <t xml:space="preserve">33.3440093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3531265258789</t>
+    <t xml:space="preserve">33.3531303405762</t>
   </si>
   <si>
     <t xml:space="preserve">33.2345657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9185905456543</t>
+    <t xml:space="preserve">33.9185943603516</t>
   </si>
   <si>
     <t xml:space="preserve">33.1616058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.550537109375</t>
+    <t xml:space="preserve">32.5505409240723</t>
   </si>
   <si>
     <t xml:space="preserve">32.404613494873</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4443283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9485912322998</t>
+    <t xml:space="preserve">33.4443321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9485950469971</t>
   </si>
   <si>
     <t xml:space="preserve">32.6873435974121</t>
@@ -2147,43 +2147,43 @@
     <t xml:space="preserve">32.5596618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5911750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863277435303</t>
+    <t xml:space="preserve">31.5911712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863296508789</t>
   </si>
   <si>
     <t xml:space="preserve">32.836368560791</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8586616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2552719116211</t>
+    <t xml:space="preserve">31.8586559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2552795410156</t>
   </si>
   <si>
     <t xml:space="preserve">32.2829475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7848701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226863861084</t>
+    <t xml:space="preserve">31.7848663330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226844787598</t>
   </si>
   <si>
     <t xml:space="preserve">30.4382095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5581169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1207656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217658996582</t>
+    <t xml:space="preserve">30.5581150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1207618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217582702637</t>
   </si>
   <si>
     <t xml:space="preserve">32.0062370300293</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">31.6649627685547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1169204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7387523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290672302246</t>
+    <t xml:space="preserve">32.1169166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125419616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290634155273</t>
   </si>
   <si>
     <t xml:space="preserve">32.6518974304199</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">33.6480560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7679634094238</t>
+    <t xml:space="preserve">33.7679672241211</t>
   </si>
   <si>
     <t xml:space="preserve">34.7087821960449</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">34.505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4136238098145</t>
+    <t xml:space="preserve">34.413631439209</t>
   </si>
   <si>
     <t xml:space="preserve">33.7864151000977</t>
@@ -2231,67 +2231,67 @@
     <t xml:space="preserve">34.2568206787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6811065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9762649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6127052307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5204658508301</t>
+    <t xml:space="preserve">34.6811103820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9762687683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5112457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6127014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5204620361328</t>
   </si>
   <si>
     <t xml:space="preserve">35.5296897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.280647277832</t>
+    <t xml:space="preserve">35.2806510925293</t>
   </si>
   <si>
     <t xml:space="preserve">35.3544425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0961761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4927978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0408401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1330718994141</t>
+    <t xml:space="preserve">35.0961837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4927940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0408363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1330757141113</t>
   </si>
   <si>
     <t xml:space="preserve">35.2253074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2437515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6588287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403770446777</t>
+    <t xml:space="preserve">35.2437553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6403732299805</t>
   </si>
   <si>
     <t xml:space="preserve">35.9263114929199</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9908752441406</t>
+    <t xml:space="preserve">35.9908790588379</t>
   </si>
   <si>
     <t xml:space="preserve">35.963207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6903343200684</t>
+    <t xml:space="preserve">34.6903305053711</t>
   </si>
   <si>
     <t xml:space="preserve">34.2844886779785</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">31.4620399475098</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4343681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4989395141602</t>
+    <t xml:space="preserve">31.4343662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4989356994629</t>
   </si>
   <si>
     <t xml:space="preserve">31.2314472198486</t>
@@ -2324,82 +2324,82 @@
     <t xml:space="preserve">31.7572002410889</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6926307678223</t>
+    <t xml:space="preserve">31.6926326751709</t>
   </si>
   <si>
     <t xml:space="preserve">32.7072372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">31.747974395752</t>
+    <t xml:space="preserve">31.7479705810547</t>
   </si>
   <si>
     <t xml:space="preserve">31.5542774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3605804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3052387237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435939788818</t>
+    <t xml:space="preserve">31.3605785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3052406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435901641846</t>
   </si>
   <si>
     <t xml:space="preserve">31.6465167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3382873535156</t>
+    <t xml:space="preserve">32.3382949829102</t>
   </si>
   <si>
     <t xml:space="preserve">33.0761871337891</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1684226989746</t>
+    <t xml:space="preserve">33.1684265136719</t>
   </si>
   <si>
     <t xml:space="preserve">32.7349128723145</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5412139892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6242218017578</t>
+    <t xml:space="preserve">32.5412101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6242256164551</t>
   </si>
   <si>
     <t xml:space="preserve">32.6426696777344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3751831054688</t>
+    <t xml:space="preserve">32.375186920166</t>
   </si>
   <si>
     <t xml:space="preserve">31.6372909545898</t>
   </si>
   <si>
-    <t xml:space="preserve">31.480489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2760238647461</t>
+    <t xml:space="preserve">31.4804821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2760219573975</t>
   </si>
   <si>
     <t xml:space="preserve">29.9493541717529</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0877075195312</t>
+    <t xml:space="preserve">30.0877056121826</t>
   </si>
   <si>
     <t xml:space="preserve">29.6080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7279834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8478946685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3367462158203</t>
+    <t xml:space="preserve">29.7279853820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6449718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8478908538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3367500305176</t>
   </si>
   <si>
     <t xml:space="preserve">30.1614990234375</t>
@@ -2411,52 +2411,52 @@
     <t xml:space="preserve">29.1376686096191</t>
   </si>
   <si>
-    <t xml:space="preserve">29.617301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0139217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.198392868042</t>
+    <t xml:space="preserve">29.6173000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1983947753906</t>
   </si>
   <si>
     <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6134605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1945495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8033142089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5450553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.425142288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0285243988037</t>
+    <t xml:space="preserve">30.6134586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1945514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.803316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5450496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4251441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0285224914551</t>
   </si>
   <si>
     <t xml:space="preserve">30.724142074585</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6726379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7741012573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.691089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9678039550781</t>
+    <t xml:space="preserve">29.6726398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9770221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7741031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6910877227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9678001403809</t>
   </si>
   <si>
     <t xml:space="preserve">33.362117767334</t>
@@ -2465,76 +2465,76 @@
     <t xml:space="preserve">32.7441329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9877872467041</t>
+    <t xml:space="preserve">31.9877891540527</t>
   </si>
   <si>
     <t xml:space="preserve">32.4397468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5504379272461</t>
+    <t xml:space="preserve">32.5504417419434</t>
   </si>
   <si>
     <t xml:space="preserve">32.310619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2291488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3121643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0907897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0077781677246</t>
+    <t xml:space="preserve">34.2291450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0907974243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0077743530273</t>
   </si>
   <si>
     <t xml:space="preserve">33.6111602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7218475341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.980110168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2199211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8194618225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5243072509766</t>
+    <t xml:space="preserve">33.7218437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9801063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2199249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.819465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5243110656738</t>
   </si>
   <si>
     <t xml:space="preserve">36.0462188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1476745605469</t>
+    <t xml:space="preserve">36.1476783752441</t>
   </si>
   <si>
     <t xml:space="preserve">37.0239295959473</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6826515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7787284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6772689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8156280517578</t>
+    <t xml:space="preserve">36.6826553344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7787322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6772727966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8156318664551</t>
   </si>
   <si>
     <t xml:space="preserve">38.1492233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">38.924015045166</t>
+    <t xml:space="preserve">38.9240112304688</t>
   </si>
   <si>
     <t xml:space="preserve">38.545841217041</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">38.8225517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">38.093879699707</t>
+    <t xml:space="preserve">38.0938758850098</t>
   </si>
   <si>
     <t xml:space="preserve">37.8171691894531</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">37.1530609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3006362915039</t>
+    <t xml:space="preserve">37.3006401062012</t>
   </si>
   <si>
     <t xml:space="preserve">37.0423812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1899566650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.715705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6234703063965</t>
+    <t xml:space="preserve">37.1899528503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7157096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6234741210938</t>
   </si>
   <si>
     <t xml:space="preserve">37.4758911132812</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">38.3613662719727</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4036407470703</t>
+    <t xml:space="preserve">39.4036445617676</t>
   </si>
   <si>
     <t xml:space="preserve">39.3667488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3852005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1400032043457</t>
+    <t xml:space="preserve">39.385196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1399955749512</t>
   </si>
   <si>
     <t xml:space="preserve">37.2914199829102</t>
@@ -2618,16 +2618,16 @@
     <t xml:space="preserve">38.2691307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2084045410156</t>
+    <t xml:space="preserve">37.2084083557129</t>
   </si>
   <si>
     <t xml:space="preserve">37.4021034240723</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8432998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2360763549805</t>
+    <t xml:space="preserve">35.8432960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2360725402832</t>
   </si>
   <si>
     <t xml:space="preserve">36.488956451416</t>
@@ -2636,31 +2636,31 @@
     <t xml:space="preserve">35.9724273681641</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3690490722656</t>
+    <t xml:space="preserve">36.3690452575684</t>
   </si>
   <si>
     <t xml:space="preserve">36.8579025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2729721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5166282653809</t>
+    <t xml:space="preserve">37.2729682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5166244506836</t>
   </si>
   <si>
     <t xml:space="preserve">35.7049407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6457595825195</t>
+    <t xml:space="preserve">36.6457633972168</t>
   </si>
   <si>
     <t xml:space="preserve">35.649600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2583656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1422920227051</t>
+    <t xml:space="preserve">36.2583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1422958374023</t>
   </si>
   <si>
     <t xml:space="preserve">35.2898712158203</t>
@@ -2672,40 +2672,40 @@
     <t xml:space="preserve">34.2660446166992</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4305229187012</t>
+    <t xml:space="preserve">32.4305267333984</t>
   </si>
   <si>
     <t xml:space="preserve">32.4028587341309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9286041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.522762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4858665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.10231590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1507339477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8002300262451</t>
+    <t xml:space="preserve">32.9286079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5227699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4858741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1023139953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1507320404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8002281188965</t>
   </si>
   <si>
     <t xml:space="preserve">27.0807819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9816188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3943881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2637138366699</t>
+    <t xml:space="preserve">23.981616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3943901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2637119293213</t>
   </si>
   <si>
     <t xml:space="preserve">24.9039878845215</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">25.3651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9224376678467</t>
+    <t xml:space="preserve">24.922435760498</t>
   </si>
   <si>
     <t xml:space="preserve">26.9977684020996</t>
@@ -2723,64 +2723,64 @@
     <t xml:space="preserve">26.3797817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4528160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7295303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7056999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8755626678467</t>
+    <t xml:space="preserve">29.9309043884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4528121948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.729528427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7056980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.875560760498</t>
   </si>
   <si>
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857070922852</t>
+    <t xml:space="preserve">28.6857051849365</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1061534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2998485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6319046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8402137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5135383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8901710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5765628814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5081615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2721786499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7702617645264</t>
+    <t xml:space="preserve">30.1061553955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2998504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0838661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.631908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8402118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5135459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8901672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5765647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5081539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.272180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.770263671875</t>
   </si>
   <si>
     <t xml:space="preserve">29.9124584197998</t>
@@ -2789,22 +2789,22 @@
     <t xml:space="preserve">30.2352867126465</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7833290100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2260627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4143772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7041530609131</t>
+    <t xml:space="preserve">29.7833271026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2260646820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.414379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7041511535645</t>
   </si>
   <si>
     <t xml:space="preserve">28.6211414337158</t>
   </si>
   <si>
-    <t xml:space="preserve">29.737211227417</t>
+    <t xml:space="preserve">29.7372093200684</t>
   </si>
   <si>
     <t xml:space="preserve">29.8663387298584</t>
@@ -2813,40 +2813,40 @@
     <t xml:space="preserve">28.8056144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3682594299316</t>
+    <t xml:space="preserve">29.368257522583</t>
   </si>
   <si>
     <t xml:space="preserve">30.7979335784912</t>
   </si>
   <si>
-    <t xml:space="preserve">30.39208984375</t>
+    <t xml:space="preserve">30.3920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">32.1630363464355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8532772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0339050292969</t>
+    <t xml:space="preserve">30.8532752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0339088439941</t>
   </si>
   <si>
     <t xml:space="preserve">31.0377521514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3790264129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9693393707275</t>
+    <t xml:space="preserve">31.3790283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9693431854248</t>
   </si>
   <si>
     <t xml:space="preserve">32.4950904846191</t>
@@ -2861,85 +2861,85 @@
     <t xml:space="preserve">32.0892524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7203063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1261444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3974781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6003932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508953094482</t>
+    <t xml:space="preserve">31.7203044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.126148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3974704742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6003952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508972167969</t>
   </si>
   <si>
     <t xml:space="preserve">31.2591190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9601173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4897155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3513584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6503505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0100746154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5950107574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0692596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0969314575195</t>
+    <t xml:space="preserve">31.9601211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4897079467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.650354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654182434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0100784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5950088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0692615509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0969333648682</t>
   </si>
   <si>
     <t xml:space="preserve">29.4236011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8809452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3275260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0784854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5342884063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5527362823486</t>
+    <t xml:space="preserve">29.5804042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.488166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8809471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3275241851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0784873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5342864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5527324676514</t>
   </si>
   <si>
     <t xml:space="preserve">29.8571147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0046939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5857887268066</t>
+    <t xml:space="preserve">30.0046920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">29.8847885131836</t>
@@ -2948,31 +2948,31 @@
     <t xml:space="preserve">29.9585762023926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1484336853027</t>
+    <t xml:space="preserve">31.1484317779541</t>
   </si>
   <si>
     <t xml:space="preserve">31.7940921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1814842224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4766464233398</t>
+    <t xml:space="preserve">32.1814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4766426086426</t>
   </si>
   <si>
     <t xml:space="preserve">33.8878746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9854927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3306159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6665000915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4674224853516</t>
+    <t xml:space="preserve">34.9854888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3306121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.66650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4674186706543</t>
   </si>
   <si>
     <t xml:space="preserve">32.0431327819824</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">32.448974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2644996643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8455924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7164649963379</t>
+    <t xml:space="preserve">32.2645034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8455963134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7164611816406</t>
   </si>
   <si>
     <t xml:space="preserve">33.601936340332</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">33.8509788513184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.223762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5650405883789</t>
+    <t xml:space="preserve">33.2237663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5650444030762</t>
   </si>
   <si>
     <t xml:space="preserve">33.9339904785156</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">34.0354537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6057739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9432144165039</t>
+    <t xml:space="preserve">32.6057777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9432106018066</t>
   </si>
   <si>
     <t xml:space="preserve">34.9485969543457</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">35.9170837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.127685546875</t>
+    <t xml:space="preserve">34.1276931762695</t>
   </si>
   <si>
     <t xml:space="preserve">32.1907119750977</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">32.3936309814453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2053146362305</t>
+    <t xml:space="preserve">33.2053184509277</t>
   </si>
   <si>
     <t xml:space="preserve">33.5465927124023</t>
@@ -3041,19 +3041,19 @@
     <t xml:space="preserve">34.884033203125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6349906921387</t>
+    <t xml:space="preserve">34.6349945068359</t>
   </si>
   <si>
     <t xml:space="preserve">36.5996398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">36.627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3467636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088600158691</t>
+    <t xml:space="preserve">36.6273078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3467597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088638305664</t>
   </si>
   <si>
     <t xml:space="preserve">36.7195510864258</t>
@@ -3062,28 +3062,28 @@
     <t xml:space="preserve">37.8909645080566</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8725166320801</t>
+    <t xml:space="preserve">37.8725090026855</t>
   </si>
   <si>
     <t xml:space="preserve">37.6142463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4482269287109</t>
+    <t xml:space="preserve">37.4482154846191</t>
   </si>
   <si>
     <t xml:space="preserve">38.4536018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7118682861328</t>
+    <t xml:space="preserve">38.7118721008301</t>
   </si>
   <si>
     <t xml:space="preserve">38.6473045349121</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2414588928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8263931274414</t>
+    <t xml:space="preserve">38.241455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8263893127441</t>
   </si>
   <si>
     <t xml:space="preserve">37.9001808166504</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2837371826172</t>
+    <t xml:space="preserve">39.2837333679199</t>
   </si>
   <si>
     <t xml:space="preserve">39.8463821411133</t>
@@ -3101,40 +3101,40 @@
     <t xml:space="preserve">40.5842781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4144096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9916610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8533096313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8863677978516</t>
+    <t xml:space="preserve">41.4144134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9916648864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8533058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8863639831543</t>
   </si>
   <si>
     <t xml:space="preserve">44.1630783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0116500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9286422729492</t>
+    <t xml:space="preserve">45.0116539001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.928638458252</t>
   </si>
   <si>
     <t xml:space="preserve">45.1961288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7349433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.867919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6242637634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.467456817627</t>
+    <t xml:space="preserve">44.7349472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8679122924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6242599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4674530029297</t>
   </si>
   <si>
     <t xml:space="preserve">45.869457244873</t>
@@ -3143,10 +3143,10 @@
     <t xml:space="preserve">46.3952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2476234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1184997558594</t>
+    <t xml:space="preserve">46.247631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1184959411621</t>
   </si>
   <si>
     <t xml:space="preserve">44.8456268310547</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">44.1077308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3291053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2737579345703</t>
+    <t xml:space="preserve">44.3291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2737617492676</t>
   </si>
   <si>
     <t xml:space="preserve">43.3882827758789</t>
@@ -3173,46 +3173,46 @@
     <t xml:space="preserve">44.0708351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6742134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6703758239746</t>
+    <t xml:space="preserve">43.6742172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6703796386719</t>
   </si>
   <si>
     <t xml:space="preserve">43.9509315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8917503356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7403297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6649894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5911979675293</t>
+    <t xml:space="preserve">44.8917427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7403259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6649932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5912017822266</t>
   </si>
   <si>
     <t xml:space="preserve">44.3567733764648</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7756805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1999702453613</t>
+    <t xml:space="preserve">43.7756767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1999664306641</t>
   </si>
   <si>
     <t xml:space="preserve">44.2091903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1369438171387</t>
+    <t xml:space="preserve">46.1369476318359</t>
   </si>
   <si>
     <t xml:space="preserve">46.8932876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5758399963379</t>
+    <t xml:space="preserve">47.5758438110352</t>
   </si>
   <si>
     <t xml:space="preserve">48.0739212036133</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">47.6496276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9447860717773</t>
+    <t xml:space="preserve">47.9447898864746</t>
   </si>
   <si>
     <t xml:space="preserve">47.2622375488281</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">47.7972106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7088088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6534729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1807632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8710021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2437858581543</t>
+    <t xml:space="preserve">46.708812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6534767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1807670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8710060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2437934875488</t>
   </si>
   <si>
     <t xml:space="preserve">47.0408668518066</t>
@@ -3257,16 +3257,16 @@
     <t xml:space="preserve">47.3175773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1108131408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4613189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6865272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6165733337402</t>
+    <t xml:space="preserve">48.1108169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4613227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6165771484375</t>
   </si>
   <si>
     <t xml:space="preserve">45.7034301757812</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">46.4136543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7587776184082</t>
+    <t xml:space="preserve">45.7587699890137</t>
   </si>
   <si>
     <t xml:space="preserve">48.0001335144043</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">47.4467124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">46.837947845459</t>
+    <t xml:space="preserve">46.8379440307617</t>
   </si>
   <si>
     <t xml:space="preserve">46.2107353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6019706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3805999755859</t>
+    <t xml:space="preserve">45.6019744873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3806037902832</t>
   </si>
   <si>
     <t xml:space="preserve">44.2276382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4397850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4859046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3898277282715</t>
+    <t xml:space="preserve">44.4397811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4859008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3898239135742</t>
   </si>
   <si>
     <t xml:space="preserve">45.0762176513672</t>
@@ -3320,34 +3320,34 @@
     <t xml:space="preserve">45.8417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6573181152344</t>
+    <t xml:space="preserve">45.6573104858398</t>
   </si>
   <si>
     <t xml:space="preserve">46.450553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5981292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5243377685547</t>
+    <t xml:space="preserve">46.5981330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.524341583252</t>
   </si>
   <si>
     <t xml:space="preserve">47.5020523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3544769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3214149475098</t>
+    <t xml:space="preserve">47.3544731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.321418762207</t>
   </si>
   <si>
     <t xml:space="preserve">48.2952919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3467903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9670753479004</t>
+    <t xml:space="preserve">49.346794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9670791625977</t>
   </si>
   <si>
     <t xml:space="preserve">47.0039710998535</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">47.0593147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4836006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3767623901367</t>
+    <t xml:space="preserve">47.4836044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3767547607422</t>
   </si>
   <si>
     <t xml:space="preserve">47.4282608032227</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2806854248047</t>
+    <t xml:space="preserve">47.2806816101074</t>
   </si>
   <si>
     <t xml:space="preserve">47.7234230041504</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">46.985523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5942878723145</t>
+    <t xml:space="preserve">47.5942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">47.926342010498</t>
@@ -3383,64 +3383,64 @@
     <t xml:space="preserve">48.6642379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4244232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1623191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.420581817627</t>
+    <t xml:space="preserve">48.4244270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1623153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4205856323242</t>
   </si>
   <si>
     <t xml:space="preserve">50.490291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1228141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6251106262207</t>
+    <t xml:space="preserve">51.1228179931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.625114440918</t>
   </si>
   <si>
     <t xml:space="preserve">53.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9877738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0621871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4482727050781</t>
+    <t xml:space="preserve">53.9877777099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0621948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4482688903809</t>
   </si>
   <si>
     <t xml:space="preserve">53.6343078613281</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1180038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.229621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1039962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.578498840332</t>
+    <t xml:space="preserve">54.1180000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2296257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1039924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8063316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5784950256348</t>
   </si>
   <si>
     <t xml:space="preserve">52.8343505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8715629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1320114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8947563171387</t>
+    <t xml:space="preserve">52.8715591430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8947601318359</t>
   </si>
   <si>
     <t xml:space="preserve">54.2482261657715</t>
@@ -3455,25 +3455,25 @@
     <t xml:space="preserve">54.1738128662109</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2110176086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2250328063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6901168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5970993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0762023925781</t>
+    <t xml:space="preserve">54.2110214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.225025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6901206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5971031188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0761985778809</t>
   </si>
   <si>
     <t xml:space="preserve">53.4668769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3180503845215</t>
+    <t xml:space="preserve">53.3180465698242</t>
   </si>
   <si>
     <t xml:space="preserve">52.815746307373</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">53.0389938354492</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3366508483887</t>
+    <t xml:space="preserve">53.3366546630859</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
@@ -3497,100 +3497,100 @@
     <t xml:space="preserve">53.7273254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3598480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7785453796387</t>
+    <t xml:space="preserve">54.3598518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7785415649414</t>
   </si>
   <si>
     <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1878242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7459259033203</t>
+    <t xml:space="preserve">53.1878204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7459297180176</t>
   </si>
   <si>
     <t xml:space="preserve">54.6203002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4388618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7551231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4946708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8761520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9505653381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6947135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5272789001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5876884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9271545410156</t>
+    <t xml:space="preserve">55.4388580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7551193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8761558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.950569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6389083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6947174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5272827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5876922607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9271507263184</t>
   </si>
   <si>
     <t xml:space="preserve">57.2992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7271118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5596809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4248542785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8667449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3970527648926</t>
+    <t xml:space="preserve">57.727108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5596771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4248504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8667488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3970565795898</t>
   </si>
   <si>
     <t xml:space="preserve">51.067008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1554222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8437576293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7693481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.397274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5461044311523</t>
+    <t xml:space="preserve">50.1554260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8437614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7693519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3972778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5461006164551</t>
   </si>
   <si>
     <t xml:space="preserve">50.8065528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4158782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0297966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9925956726074</t>
+    <t xml:space="preserve">50.4158744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0298004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9925918579102</t>
   </si>
   <si>
     <t xml:space="preserve">50.2484436035156</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">51.1042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7181282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4018669128418</t>
+    <t xml:space="preserve">51.718132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4018707275391</t>
   </si>
   <si>
     <t xml:space="preserve">51.3274574279785</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">48.1648330688477</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0904235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3182601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0532112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0019989013672</t>
+    <t xml:space="preserve">48.0904197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3182640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0532150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0020027160645</t>
   </si>
   <si>
     <t xml:space="preserve">50.5647048950195</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">51.1600227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0624046325684</t>
+    <t xml:space="preserve">50.0624084472656</t>
   </si>
   <si>
     <t xml:space="preserve">48.6113204956055</t>
@@ -3650,13 +3650,13 @@
     <t xml:space="preserve">51.7553405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9785842895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9831809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4994850158691</t>
+    <t xml:space="preserve">51.978588104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9831771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4994812011719</t>
   </si>
   <si>
     <t xml:space="preserve">52.4622802734375</t>
@@ -3665,16 +3665,16 @@
     <t xml:space="preserve">54.7133178710938</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4714736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5690841674805</t>
+    <t xml:space="preserve">54.4714698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5690879821777</t>
   </si>
   <si>
     <t xml:space="preserve">56.0341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7597198486328</t>
+    <t xml:space="preserve">56.7597236633301</t>
   </si>
   <si>
     <t xml:space="preserve">56.8341331481934</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">57.7829208374023</t>
   </si>
   <si>
-    <t xml:space="preserve">59.438648223877</t>
+    <t xml:space="preserve">59.4386444091797</t>
   </si>
   <si>
     <t xml:space="preserve">58.5084648132324</t>
@@ -3707,46 +3707,46 @@
     <t xml:space="preserve">62.8803176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4012222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7408981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8199043273926</t>
+    <t xml:space="preserve">63.4012184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7409019470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8199157714844</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7546920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3313980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2197875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5686492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0663566589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9129257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.322208404541</t>
+    <t xml:space="preserve">63.754695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.331413269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2197799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5686531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0663604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408554077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9129295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3222045898438</t>
   </si>
   <si>
     <t xml:space="preserve">58.3410301208496</t>
@@ -3755,19 +3755,19 @@
     <t xml:space="preserve">60.089771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6060829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0385627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9455337524414</t>
+    <t xml:space="preserve">59.6060791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0385589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9455375671387</t>
   </si>
   <si>
     <t xml:space="preserve">60.5920715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">61.6896858215332</t>
+    <t xml:space="preserve">61.6896820068359</t>
   </si>
   <si>
     <t xml:space="preserve">64.4430236816406</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">61.4478340148926</t>
   </si>
   <si>
-    <t xml:space="preserve">60.6292762756348</t>
+    <t xml:space="preserve">60.629280090332</t>
   </si>
   <si>
     <t xml:space="preserve">58.6758995056152</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">60.182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">58.7503089904785</t>
+    <t xml:space="preserve">58.7503128051758</t>
   </si>
   <si>
     <t xml:space="preserve">58.8061218261719</t>
@@ -3800,46 +3800,46 @@
     <t xml:space="preserve">58.2294082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8573379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3224296569824</t>
+    <t xml:space="preserve">57.8573341369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3224220275879</t>
   </si>
   <si>
     <t xml:space="preserve">58.5642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7549095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.071174621582</t>
+    <t xml:space="preserve">59.7549057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0711669921875</t>
   </si>
   <si>
     <t xml:space="preserve">59.5502662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8107223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4618492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9269332885742</t>
+    <t xml:space="preserve">59.810718536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4618453979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9269409179688</t>
   </si>
   <si>
     <t xml:space="preserve">58.4154434204102</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9643630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1644020080566</t>
+    <t xml:space="preserve">56.9643592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1644058227539</t>
   </si>
   <si>
     <t xml:space="preserve">55.7923278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8807525634766</t>
+    <t xml:space="preserve">54.8807487487793</t>
   </si>
   <si>
     <t xml:space="preserve">52.8901634216309</t>
@@ -3851,22 +3851,22 @@
     <t xml:space="preserve">52.6111106872559</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3040351867676</t>
+    <t xml:space="preserve">54.3040390014648</t>
   </si>
   <si>
     <t xml:space="preserve">54.3412437438965</t>
   </si>
   <si>
-    <t xml:space="preserve">51.699535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2716445922852</t>
+    <t xml:space="preserve">51.6995315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2716407775879</t>
   </si>
   <si>
     <t xml:space="preserve">52.3134536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">52.536693572998</t>
+    <t xml:space="preserve">52.5366897583008</t>
   </si>
   <si>
     <t xml:space="preserve">51.5693016052246</t>
@@ -3890,22 +3890,22 @@
     <t xml:space="preserve">51.6437187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6391181945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1274147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2344398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9739875793457</t>
+    <t xml:space="preserve">50.6391143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1274108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2344360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9739837646484</t>
   </si>
   <si>
     <t xml:space="preserve">50.9181785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8809700012207</t>
+    <t xml:space="preserve">50.8809661865234</t>
   </si>
   <si>
     <t xml:space="preserve">48.4624938964844</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">41.8768043518066</t>
   </si>
   <si>
-    <t xml:space="preserve">42.146556854248</t>
+    <t xml:space="preserve">42.1465606689453</t>
   </si>
   <si>
     <t xml:space="preserve">41.4954299926758</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">44.6487464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2441749572754</t>
+    <t xml:space="preserve">43.2441711425781</t>
   </si>
   <si>
     <t xml:space="preserve">45.709156036377</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2951736450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8207778930664</t>
+    <t xml:space="preserve">47.1044273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2951698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8207702636719</t>
   </si>
   <si>
     <t xml:space="preserve">46.2021522521973</t>
@@ -3968,34 +3968,34 @@
     <t xml:space="preserve">46.2765693664551</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8717765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1974449157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9275856018066</t>
+    <t xml:space="preserve">48.8717803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1974487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1788444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9275817871094</t>
   </si>
   <si>
     <t xml:space="preserve">49.2810554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9555969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.988208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4392929077148</t>
+    <t xml:space="preserve">46.9556007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9882125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4392890930176</t>
   </si>
   <si>
     <t xml:space="preserve">45.1603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0254173278809</t>
+    <t xml:space="preserve">46.0254211425781</t>
   </si>
   <si>
     <t xml:space="preserve">46.4533004760742</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">47.0300140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1835517883301</t>
+    <t xml:space="preserve">46.1835479736328</t>
   </si>
   <si>
     <t xml:space="preserve">47.5881233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5277137756348</t>
+    <t xml:space="preserve">46.5277214050293</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8301887512207</t>
+    <t xml:space="preserve">43.8301849365234</t>
   </si>
   <si>
     <t xml:space="preserve">45.430103302002</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">46.2672653198242</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7695617675781</t>
+    <t xml:space="preserve">46.7695579528809</t>
   </si>
   <si>
     <t xml:space="preserve">45.5696296691895</t>
@@ -4040,10 +4040,10 @@
     <t xml:space="preserve">41.4861259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7373809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9095268249512</t>
+    <t xml:space="preserve">39.7373847961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9095230102539</t>
   </si>
   <si>
     <t xml:space="preserve">39.8676109313965</t>
@@ -4055,13 +4055,13 @@
     <t xml:space="preserve">40.8070907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1930656433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2814903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1093482971191</t>
+    <t xml:space="preserve">42.1930694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2814865112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1093521118164</t>
   </si>
   <si>
     <t xml:space="preserve">40.6489639282227</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">39.819034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.658821105957</t>
+    <t xml:space="preserve">40.6588172912598</t>
   </si>
   <si>
     <t xml:space="preserve">42.3572616577148</t>
@@ -4100,19 +4100,19 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801216125488</t>
+    <t xml:space="preserve">43.4801254272461</t>
   </si>
   <si>
     <t xml:space="preserve">43.234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1119346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2155265808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.648998260498</t>
+    <t xml:space="preserve">42.111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2155303955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6489944458008</t>
   </si>
   <si>
     <t xml:space="preserve">37.2147560119629</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">36.2145652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5167007446289</t>
+    <t xml:space="preserve">37.5166969299316</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">34.9973449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9312973022461</t>
+    <t xml:space="preserve">34.9312934875488</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639762878418</t>
+    <t xml:space="preserve">38.0639801025391</t>
   </si>
   <si>
     <t xml:space="preserve">37.3751678466797</t>
@@ -4166,10 +4166,10 @@
     <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0547332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396560668945</t>
+    <t xml:space="preserve">39.0547370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396598815918</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">40.3474349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7531776428223</t>
+    <t xml:space="preserve">40.753173828125</t>
   </si>
   <si>
     <t xml:space="preserve">41.1494789123535</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">40.7248687744141</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9990921020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9239921569824</t>
+    <t xml:space="preserve">43.9990882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9239883422852</t>
   </si>
   <si>
     <t xml:space="preserve">45.9806060791016</t>
@@ -4223,22 +4223,22 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389701843262</t>
+    <t xml:space="preserve">45.3389739990234</t>
   </si>
   <si>
     <t xml:space="preserve">46.5278854370117</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5184478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4995727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8579368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7165985107422</t>
+    <t xml:space="preserve">46.5184440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4995765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8579406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7165946960449</t>
   </si>
   <si>
     <t xml:space="preserve">46.9524917602539</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">46.7543411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1315765380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0273933410645</t>
+    <t xml:space="preserve">46.1315803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0273971557617</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
@@ -4274,31 +4274,31 @@
     <t xml:space="preserve">43.0460739135742</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1496696472168</t>
+    <t xml:space="preserve">42.1496734619141</t>
   </si>
   <si>
     <t xml:space="preserve">42.3100814819336</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1213645935059</t>
+    <t xml:space="preserve">42.1213684082031</t>
   </si>
   <si>
     <t xml:space="preserve">41.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2251586914062</t>
+    <t xml:space="preserve">42.2251625061035</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1777877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3948059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6967544555664</t>
+    <t xml:space="preserve">41.1777839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3948097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6967506408691</t>
   </si>
   <si>
     <t xml:space="preserve">42.4704895019531</t>
@@ -4307,25 +4307,25 @@
     <t xml:space="preserve">42.998893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0175743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646553039551</t>
+    <t xml:space="preserve">42.0175704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7158241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646514892578</t>
   </si>
   <si>
     <t xml:space="preserve">40.9230194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4891662597656</t>
+    <t xml:space="preserve">41.4891700744629</t>
   </si>
   <si>
     <t xml:space="preserve">41.8005485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4610557556152</t>
+    <t xml:space="preserve">42.461051940918</t>
   </si>
   <si>
     <t xml:space="preserve">39.9511337280273</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">41.0645561218262</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8096008300781</t>
+    <t xml:space="preserve">39.8095970153809</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703941345215</t>
+    <t xml:space="preserve">41.9703903198242</t>
   </si>
   <si>
     <t xml:space="preserve">41.5174751281738</t>
@@ -4373,10 +4373,10 @@
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8009376525879</t>
+    <t xml:space="preserve">42.7252540588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8009338378906</t>
   </si>
   <si>
     <t xml:space="preserve">44.0557022094727</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">43.7160186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6690292358398</t>
+    <t xml:space="preserve">44.6690330505371</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">46.1693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6692237854004</t>
+    <t xml:space="preserve">45.6692276000977</t>
   </si>
   <si>
     <t xml:space="preserve">43.7443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7346954345703</t>
+    <t xml:space="preserve">42.734691619873</t>
   </si>
   <si>
     <t xml:space="preserve">41.2249641418457</t>
@@ -4418,16 +4418,16 @@
     <t xml:space="preserve">39.8756484985352</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8290519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9422760009766</t>
+    <t xml:space="preserve">42.8290481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9422798156738</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0840148925781</t>
+    <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">46.7732124328613</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">47.6129951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7639656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1978187561035</t>
+    <t xml:space="preserve">47.7639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1978225708008</t>
   </si>
   <si>
     <t xml:space="preserve">47.0657196044922</t>
@@ -4451,19 +4451,19 @@
     <t xml:space="preserve">47.0185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6314849853516</t>
+    <t xml:space="preserve">45.6314811706543</t>
   </si>
   <si>
     <t xml:space="preserve">45.6031761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5654296875</t>
+    <t xml:space="preserve">45.5654335021973</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2917900085449</t>
+    <t xml:space="preserve">45.2917938232422</t>
   </si>
   <si>
     <t xml:space="preserve">44.8200035095215</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5465621948242</t>
+    <t xml:space="preserve">45.546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">45.5937385559082</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">44.7539520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7447128295898</t>
+    <t xml:space="preserve">45.7447090148926</t>
   </si>
   <si>
     <t xml:space="preserve">46.5844955444336</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1504516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3861465454102</t>
+    <t xml:space="preserve">46.150447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3861503601074</t>
   </si>
   <si>
     <t xml:space="preserve">46.6788558959961</t>
@@ -4517,16 +4517,16 @@
     <t xml:space="preserve">47.3110466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7071647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8017120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5563850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5565719604492</t>
+    <t xml:space="preserve">46.707160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8017082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5563812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5565757751465</t>
   </si>
   <si>
     <t xml:space="preserve">49.3869247436523</t>
@@ -4535,22 +4535,22 @@
     <t xml:space="preserve">49.7077407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">48.971752166748</t>
+    <t xml:space="preserve">48.9717483520508</t>
   </si>
   <si>
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814758300781</t>
+    <t xml:space="preserve">50.4814796447754</t>
   </si>
   <si>
     <t xml:space="preserve">51.8779754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3497657775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8781700134277</t>
+    <t xml:space="preserve">52.3497619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8781661987305</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">51.9157180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0480155944824</t>
+    <t xml:space="preserve">53.0480117797852</t>
   </si>
   <si>
     <t xml:space="preserve">53.3310890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1046257019043</t>
+    <t xml:space="preserve">53.1046295166016</t>
   </si>
   <si>
     <t xml:space="preserve">53.2555999755859</t>
@@ -4574,22 +4574,22 @@
     <t xml:space="preserve">54.5199928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0859527587891</t>
+    <t xml:space="preserve">54.0859489440918</t>
   </si>
   <si>
     <t xml:space="preserve">53.9727210998535</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8406219482422</t>
+    <t xml:space="preserve">53.8406181335449</t>
   </si>
   <si>
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4447021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1991767883301</t>
+    <t xml:space="preserve">55.4446983337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1991806030273</t>
   </si>
   <si>
     <t xml:space="preserve">54.0293350219727</t>
@@ -4604,13 +4604,13 @@
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009307861328</t>
+    <t xml:space="preserve">53.5009346008301</t>
   </si>
   <si>
     <t xml:space="preserve">53.9349784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8785552978516</t>
+    <t xml:space="preserve">54.8785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
@@ -4619,13 +4619,13 @@
     <t xml:space="preserve">54.444507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3503456115723</t>
+    <t xml:space="preserve">55.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9729118347168</t>
+    <t xml:space="preserve">54.9729080200195</t>
   </si>
   <si>
     <t xml:space="preserve">54.46337890625</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">54.5388641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3316688537598</t>
+    <t xml:space="preserve">56.3316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5017051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546203613281</t>
+    <t xml:space="preserve">57.5017013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546241760254</t>
   </si>
   <si>
     <t xml:space="preserve">58.1433372497559</t>
@@ -4694,37 +4694,37 @@
     <t xml:space="preserve">57.2752456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9170722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8981971740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9550132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1059837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0116233825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6155166625977</t>
+    <t xml:space="preserve">58.9170761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8982009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9550094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1059875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0116271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6155128479004</t>
   </si>
   <si>
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417778015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4266090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0686264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2196006774902</t>
+    <t xml:space="preserve">59.8417816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4266052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0686225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.219596862793</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">63.1443061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">63.408504486084</t>
+    <t xml:space="preserve">63.4085121154785</t>
   </si>
   <si>
     <t xml:space="preserve">63.8614311218262</t>
@@ -4760,13 +4760,13 @@
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.502872467041</t>
+    <t xml:space="preserve">63.5028648376465</t>
   </si>
   <si>
     <t xml:space="preserve">62.993335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4649276733398</t>
+    <t xml:space="preserve">62.4649238586426</t>
   </si>
   <si>
     <t xml:space="preserve">61.8987808227539</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">60.8608474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7287445068359</t>
+    <t xml:space="preserve">60.7287483215332</t>
   </si>
   <si>
     <t xml:space="preserve">62.1307678222656</t>
@@ -6501,6 +6501,9 @@
   </si>
   <si>
     <t xml:space="preserve">57.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2400016784668</t>
   </si>
 </sst>
 </file>
@@ -72723,7 +72726,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6917939815</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>888867</v>
@@ -72744,6 +72747,32 @@
         <v>2149</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6911226852</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>843046</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>57.5400009155273</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>56.1399993896484</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>56.6399993896484</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>57.2400016784668</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>2163</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="2164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="2165">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,31 +44,31 @@
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698095321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8452548980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9876041412354</t>
+    <t xml:space="preserve">10.9698114395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.845253944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876050949097</t>
   </si>
   <si>
     <t xml:space="preserve">11.1744375228882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9573593139648</t>
+    <t xml:space="preserve">11.9573602676392</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769296646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1566438674927</t>
+    <t xml:space="preserve">11.4769306182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.156644821167</t>
   </si>
   <si>
     <t xml:space="preserve">11.5481052398682</t>
@@ -80,64 +80,64 @@
     <t xml:space="preserve">11.4057559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1175031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1263999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0997085571289</t>
+    <t xml:space="preserve">11.8239068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175050735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018453598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1264009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0997114181519</t>
   </si>
   <si>
     <t xml:space="preserve">11.7260417938232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0908126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9484643936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950815200806</t>
+    <t xml:space="preserve">12.0908136367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.94846534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950834274292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7616291046143</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9128770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4146547317505</t>
+    <t xml:space="preserve">11.9128761291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4146518707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.2723035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.254508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9431209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989921569824</t>
+    <t xml:space="preserve">11.0409860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2545080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989931106567</t>
   </si>
   <si>
     <t xml:space="preserve">11.672661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772897720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110994338989</t>
+    <t xml:space="preserve">11.8772878646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4110984802246</t>
   </si>
   <si>
     <t xml:space="preserve">12.2509565353394</t>
@@ -146,19 +146,19 @@
     <t xml:space="preserve">12.2687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4022026062012</t>
+    <t xml:space="preserve">12.4022016525269</t>
   </si>
   <si>
     <t xml:space="preserve">11.7972164154053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1975746154785</t>
+    <t xml:space="preserve">12.1975765228271</t>
   </si>
   <si>
     <t xml:space="preserve">12.7402820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.962703704834</t>
+    <t xml:space="preserve">12.9627027511597</t>
   </si>
   <si>
     <t xml:space="preserve">12.7669734954834</t>
@@ -179,13 +179,13 @@
     <t xml:space="preserve">13.4520301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6210699081421</t>
+    <t xml:space="preserve">13.6210708618164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7100372314453</t>
   </si>
   <si>
-    <t xml:space="preserve">13.336371421814</t>
+    <t xml:space="preserve">13.3363723754883</t>
   </si>
   <si>
     <t xml:space="preserve">13.0427751541138</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">13.060567855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9893932342529</t>
+    <t xml:space="preserve">12.9893951416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0160865783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449110031128</t>
+    <t xml:space="preserve">13.0160856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449100494385</t>
   </si>
   <si>
     <t xml:space="preserve">13.0961570739746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5143070220947</t>
+    <t xml:space="preserve">13.514307975769</t>
   </si>
   <si>
     <t xml:space="preserve">13.1228466033936</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">12.9804973602295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9271144866943</t>
+    <t xml:space="preserve">12.927116394043</t>
   </si>
   <si>
     <t xml:space="preserve">12.589035987854</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">12.7936630249023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8292503356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.033878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737354278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1495370864868</t>
+    <t xml:space="preserve">12.8292512893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338773727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737363815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1495380401611</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029190063477</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.167329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089645385742</t>
+    <t xml:space="preserve">13.167332649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089635848999</t>
   </si>
   <si>
     <t xml:space="preserve">12.5979337692261</t>
@@ -263,103 +263,103 @@
     <t xml:space="preserve">12.9982900619507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3185777664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9324588775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570154190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6388645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676898956299</t>
+    <t xml:space="preserve">13.3185787200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9324598312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502553939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6388635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676889419556</t>
   </si>
   <si>
     <t xml:space="preserve">13.3630628585815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.345269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2285184860229</t>
+    <t xml:space="preserve">13.3452682495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285194396973</t>
   </si>
   <si>
     <t xml:space="preserve">13.5608043670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.444055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2734212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709978103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4620170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4979391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3632297515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183269500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6685733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7314367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7404184341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.300365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1566724777222</t>
+    <t xml:space="preserve">13.4440546035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2734231948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4620161056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4979381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3632287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6685705184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7314357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7404165267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3003644943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1566734313965</t>
   </si>
   <si>
     <t xml:space="preserve">12.7256021499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2105588912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8603115081787</t>
+    <t xml:space="preserve">13.2105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.860312461853</t>
   </si>
   <si>
     <t xml:space="preserve">13.8122615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6775522232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8571653366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2253723144531</t>
+    <t xml:space="preserve">13.6775531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8571672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2253742218018</t>
   </si>
   <si>
     <t xml:space="preserve">12.9321575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3035106658936</t>
+    <t xml:space="preserve">12.3035116195679</t>
   </si>
   <si>
     <t xml:space="preserve">12.6986598968506</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">13.1476936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.995023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6178331375122</t>
+    <t xml:space="preserve">12.9950218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6178340911865</t>
   </si>
   <si>
     <t xml:space="preserve">12.8513317108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8782730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9680786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9231758117676</t>
+    <t xml:space="preserve">12.8782739639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9680795669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9231767654419</t>
   </si>
   <si>
     <t xml:space="preserve">13.1746349334717</t>
@@ -392,40 +392,40 @@
     <t xml:space="preserve">12.9590997695923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9501190185547</t>
+    <t xml:space="preserve">12.950119972229</t>
   </si>
   <si>
     <t xml:space="preserve">12.7705049514771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3452682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8302230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1714897155762</t>
+    <t xml:space="preserve">13.3452672958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8302240371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1714887619019</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637197494507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3690624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0816831588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9559526443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069189071655</t>
+    <t xml:space="preserve">14.3690633773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0816822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9559516906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069198608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.6057071685791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9290103912354</t>
+    <t xml:space="preserve">13.9290113449097</t>
   </si>
   <si>
     <t xml:space="preserve">14.0277986526489</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">14.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8481855392456</t>
+    <t xml:space="preserve">13.8481845855713</t>
   </si>
   <si>
     <t xml:space="preserve">14.0457601547241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9918766021729</t>
+    <t xml:space="preserve">13.9918746948242</t>
   </si>
   <si>
     <t xml:space="preserve">13.9200305938721</t>
@@ -452,76 +452,76 @@
     <t xml:space="preserve">14.0008563995361</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7583780288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6955137252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877466201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.524881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.354248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4171123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159015655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7224550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5338611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.704493522644</t>
+    <t xml:space="preserve">13.7583770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6955127716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5248832702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4171133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159006118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7224559783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5338621139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7044944763184</t>
   </si>
   <si>
     <t xml:space="preserve">13.9110488891602</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6146869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0098361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727014541626</t>
+    <t xml:space="preserve">13.6146879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.009838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727024078369</t>
   </si>
   <si>
     <t xml:space="preserve">13.4530353546143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6506109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6416292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853202819824</t>
+    <t xml:space="preserve">13.6506090164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6416301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853212356567</t>
   </si>
   <si>
     <t xml:space="preserve">13.4799776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8392028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8930892944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9649333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8751268386841</t>
+    <t xml:space="preserve">13.839204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0996427536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8930883407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8751277923584</t>
   </si>
   <si>
     <t xml:space="preserve">13.79430103302</t>
@@ -533,112 +533,112 @@
     <t xml:space="preserve">13.3991508483887</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3901720046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4889583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6326484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3273057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763395309448</t>
+    <t xml:space="preserve">13.3901710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.488959312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6326503753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3273067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763385772705</t>
   </si>
   <si>
     <t xml:space="preserve">13.8661460876465</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0547389984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6474637985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6384830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9168863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.04261302948</t>
+    <t xml:space="preserve">14.0547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6474647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.638482093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9168853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0426120758057</t>
   </si>
   <si>
     <t xml:space="preserve">14.8989219665527</t>
   </si>
   <si>
-    <t xml:space="preserve">14.548677444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7372713088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8719797134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6833877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013483047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450384140015</t>
+    <t xml:space="preserve">14.5486783981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7372694015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731962203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8719816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6833868026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8450403213501</t>
   </si>
   <si>
     <t xml:space="preserve">15.0875158309937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9707708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7103290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6744050979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9528045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6892232894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251434326172</t>
+    <t xml:space="preserve">14.9707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7103271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6744060516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.952805519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377632141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736843109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6892204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251453399658</t>
   </si>
   <si>
     <t xml:space="preserve">15.482666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7790288925171</t>
+    <t xml:space="preserve">15.7790260314941</t>
   </si>
   <si>
     <t xml:space="preserve">16.0933513641357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1651954650879</t>
+    <t xml:space="preserve">16.1651973724365</t>
   </si>
   <si>
     <t xml:space="preserve">16.2011203765869</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">16.1921405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.246021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113128662109</t>
+    <t xml:space="preserve">16.2460250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113166809082</t>
   </si>
   <si>
     <t xml:space="preserve">16.0304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9855794906616</t>
+    <t xml:space="preserve">15.9855833053589</t>
   </si>
   <si>
     <t xml:space="preserve">15.9137372970581</t>
@@ -665,40 +665,40 @@
     <t xml:space="preserve">15.6353368759155</t>
   </si>
   <si>
-    <t xml:space="preserve">15.931697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9586420059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867950439453</t>
+    <t xml:space="preserve">15.9316968917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9766063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9586429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406805038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867969512939</t>
   </si>
   <si>
     <t xml:space="preserve">16.1741790771484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1023330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0484504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8957757949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676218032837</t>
+    <t xml:space="preserve">16.1023349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0484485626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8957767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.967622756958</t>
   </si>
   <si>
     <t xml:space="preserve">16.1831569671631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0991878509521</t>
+    <t xml:space="preserve">17.0991840362549</t>
   </si>
   <si>
     <t xml:space="preserve">17.2608375549316</t>
@@ -710,64 +710,64 @@
     <t xml:space="preserve">17.296760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3326816558838</t>
+    <t xml:space="preserve">17.3326835632324</t>
   </si>
   <si>
     <t xml:space="preserve">17.5122966766357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5661792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.65598487854</t>
+    <t xml:space="preserve">17.5661811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6559886932373</t>
   </si>
   <si>
     <t xml:space="preserve">17.6021022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8535614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1768627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.880500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0601177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0870552062988</t>
+    <t xml:space="preserve">17.8535594940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.006233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1768665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8805046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.060115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0870571136475</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205528259277</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2666702270508</t>
+    <t xml:space="preserve">18.266674041748</t>
   </si>
   <si>
     <t xml:space="preserve">18.4103622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1678829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2756500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4373035430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9312400817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2276039123535</t>
+    <t xml:space="preserve">18.1678848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2756538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4373054504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9312419891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2276058197021</t>
   </si>
   <si>
     <t xml:space="preserve">19.2365856170654</t>
@@ -776,49 +776,49 @@
     <t xml:space="preserve">19.2006607055664</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4790630340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5598907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1108589172363</t>
+    <t xml:space="preserve">19.479061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1108531951904</t>
   </si>
   <si>
     <t xml:space="preserve">19.209644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3174095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5329456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6945991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4611034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5778465270996</t>
+    <t xml:space="preserve">19.3174114227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5329475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4611015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5778484344482</t>
   </si>
   <si>
     <t xml:space="preserve">19.514986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1885375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3501873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6645126342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8351402282715</t>
+    <t xml:space="preserve">20.1885356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310111999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3501853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6645107269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8351421356201</t>
   </si>
   <si>
     <t xml:space="preserve">21.1135444641113</t>
@@ -827,79 +827,79 @@
     <t xml:space="preserve">20.4759140014648</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7844047546387</t>
+    <t xml:space="preserve">19.7843990325928</t>
   </si>
   <si>
     <t xml:space="preserve">19.9999408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8921718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9819812774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.874210357666</t>
+    <t xml:space="preserve">19.8921737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9819774627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8742084503174</t>
   </si>
   <si>
     <t xml:space="preserve">19.9909610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3892574310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5509090423584</t>
+    <t xml:space="preserve">19.3892555236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5509071350098</t>
   </si>
   <si>
     <t xml:space="preserve">19.6505184173584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7229633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6052379608154</t>
+    <t xml:space="preserve">19.7229614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">19.4875183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0127410888672</t>
+    <t xml:space="preserve">20.0127391815186</t>
   </si>
   <si>
     <t xml:space="preserve">19.2339630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6324043273926</t>
+    <t xml:space="preserve">19.6324062347412</t>
   </si>
   <si>
     <t xml:space="preserve">19.7048511505127</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2792434692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9260768890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0075759887695</t>
+    <t xml:space="preserve">19.279239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9260730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0075740814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.9713535308838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.080020904541</t>
+    <t xml:space="preserve">19.0800189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.5819644927979</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8355197906494</t>
+    <t xml:space="preserve">18.8355178833008</t>
   </si>
   <si>
     <t xml:space="preserve">19.1252956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0437965393066</t>
+    <t xml:space="preserve">19.0437984466553</t>
   </si>
   <si>
     <t xml:space="preserve">19.3426284790039</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">19.2249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.614294052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2158489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1524639129639</t>
+    <t xml:space="preserve">19.6142978668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2158508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1524620056152</t>
   </si>
   <si>
     <t xml:space="preserve">19.1434059143066</t>
@@ -929,31 +929,31 @@
     <t xml:space="preserve">18.3736896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5638542175293</t>
+    <t xml:space="preserve">18.5638523101807</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362991333008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6000747680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7359085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.609130859375</t>
+    <t xml:space="preserve">18.600076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8083534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7359104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6091270446777</t>
   </si>
   <si>
     <t xml:space="preserve">19.1071853637695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.288293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3788528442383</t>
+    <t xml:space="preserve">19.2882919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060173034668</t>
@@ -962,64 +962,64 @@
     <t xml:space="preserve">19.4512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4331855773926</t>
+    <t xml:space="preserve">19.4331836700439</t>
   </si>
   <si>
     <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1977386474609</t>
+    <t xml:space="preserve">19.1977405548096</t>
   </si>
   <si>
     <t xml:space="preserve">20.239128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4655151367188</t>
+    <t xml:space="preserve">20.465518951416</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560741424561</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2572383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3930721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.329683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.374963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4021263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3477935791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8458499908447</t>
+    <t xml:space="preserve">20.3568496704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2572402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3930702209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3296852111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3749599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4021282196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3477916717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8458518981934</t>
   </si>
   <si>
     <t xml:space="preserve">21.144681930542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.343900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4254035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3710689544678</t>
+    <t xml:space="preserve">21.5431251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3439044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4254055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3710708618164</t>
   </si>
   <si>
     <t xml:space="preserve">21.2805137634277</t>
@@ -1028,28 +1028,28 @@
     <t xml:space="preserve">21.2080707550049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8730163574219</t>
+    <t xml:space="preserve">20.8730144500732</t>
   </si>
   <si>
     <t xml:space="preserve">21.2714576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.615571975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8962917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7423496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7966785430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9959011077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.158899307251</t>
+    <t xml:space="preserve">21.6155700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8962898254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7423477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7966804504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9959049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1589012145996</t>
   </si>
   <si>
     <t xml:space="preserve">22.4305667877197</t>
@@ -1058,40 +1058,40 @@
     <t xml:space="preserve">22.3671798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5935668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116771697998</t>
+    <t xml:space="preserve">22.5935688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6116752624512</t>
   </si>
   <si>
     <t xml:space="preserve">22.5030136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2404041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3852882385254</t>
+    <t xml:space="preserve">22.2404003143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.385290145874</t>
   </si>
   <si>
     <t xml:space="preserve">22.2313461303711</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2132358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2494564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.959680557251</t>
+    <t xml:space="preserve">22.2132339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2494583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9596786499023</t>
   </si>
   <si>
     <t xml:space="preserve">21.8238468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1136264801025</t>
+    <t xml:space="preserve">22.0683460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1136245727539</t>
   </si>
   <si>
     <t xml:space="preserve">22.1407909393311</t>
@@ -1103,46 +1103,46 @@
     <t xml:space="preserve">21.7514038085938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.470682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.149845123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2766227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0592937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.285680770874</t>
+    <t xml:space="preserve">21.4706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1498470306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0592918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2856788635254</t>
   </si>
   <si>
     <t xml:space="preserve">22.3490695953369</t>
   </si>
   <si>
-    <t xml:space="preserve">22.394344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9868469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4396228790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5573463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3581256866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1226787567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0774002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0049571990967</t>
+    <t xml:space="preserve">22.3943462371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9868450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4396209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5573444366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3581218719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1226806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0774021148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0049591064453</t>
   </si>
   <si>
     <t xml:space="preserve">21.9415683746338</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">21.8510112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7695159912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6466274261475</t>
+    <t xml:space="preserve">21.7695140838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466236114502</t>
   </si>
   <si>
     <t xml:space="preserve">21.0631828308105</t>
@@ -1163,37 +1163,37 @@
     <t xml:space="preserve">21.0088481903076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6737957000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7734031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6556854248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0994052886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.135627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8277378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8005695343018</t>
+    <t xml:space="preserve">20.6737937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7734069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6556777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1356258392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8277359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8005714416504</t>
   </si>
   <si>
     <t xml:space="preserve">20.8820686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4344577789307</t>
+    <t xml:space="preserve">21.4344596862793</t>
   </si>
   <si>
     <t xml:space="preserve">21.4163475036621</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">21.950626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4667911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5120658874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8833446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8290119171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014549255371</t>
+    <t xml:space="preserve">22.4667892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5120677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8833465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3219013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8290100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014587402344</t>
   </si>
   <si>
     <t xml:space="preserve">22.8109035491943</t>
@@ -1229,37 +1229,37 @@
     <t xml:space="preserve">23.2546215057373</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6530666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9066200256348</t>
+    <t xml:space="preserve">23.6530647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9066219329834</t>
   </si>
   <si>
     <t xml:space="preserve">23.6168441772461</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3632869720459</t>
+    <t xml:space="preserve">23.3632888793945</t>
   </si>
   <si>
     <t xml:space="preserve">23.1821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6349563598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4900646209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.544397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.200288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8199577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7837333679199</t>
+    <t xml:space="preserve">23.6349544525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4900665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5443992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8199596405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7837314605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.0372886657715</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">23.8160648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">24.341287612915</t>
+    <t xml:space="preserve">24.3412837982178</t>
   </si>
   <si>
     <t xml:space="preserve">24.4861755371094</t>
@@ -1283,64 +1283,64 @@
     <t xml:space="preserve">24.5042858123779</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5223999023438</t>
+    <t xml:space="preserve">24.5223979949951</t>
   </si>
   <si>
     <t xml:space="preserve">24.2869529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">24.114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0333976745605</t>
+    <t xml:space="preserve">24.1148948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0333995819092</t>
   </si>
   <si>
     <t xml:space="preserve">24.2145099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5625114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4629001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3593997955322</t>
+    <t xml:space="preserve">23.5625095367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4628982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.359395980835</t>
   </si>
   <si>
     <t xml:space="preserve">23.290843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0424518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6582279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6724510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7630062103271</t>
+    <t xml:space="preserve">24.0424537658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6582317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6724529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7630081176758</t>
   </si>
   <si>
     <t xml:space="preserve">25.4279518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5637836456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5818958282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4641742706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3917293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.63623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1342830657959</t>
+    <t xml:space="preserve">25.5637817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5818939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4641761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3917274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6362285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1342849731445</t>
   </si>
   <si>
     <t xml:space="preserve">25.9893951416016</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">25.3192863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">25.264949798584</t>
+    <t xml:space="preserve">25.2649478912354</t>
   </si>
   <si>
     <t xml:space="preserve">25.699613571167</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5728397369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2157802581787</t>
+    <t xml:space="preserve">25.5728378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2157821655273</t>
   </si>
   <si>
     <t xml:space="preserve">26.405948638916</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">26.5055599212646</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6685619354248</t>
+    <t xml:space="preserve">26.6685581207275</t>
   </si>
   <si>
     <t xml:space="preserve">26.4874496459961</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">26.8134479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7500610351562</t>
+    <t xml:space="preserve">26.7500591278076</t>
   </si>
   <si>
     <t xml:space="preserve">26.9583377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4654445648193</t>
+    <t xml:space="preserve">27.4654483795166</t>
   </si>
   <si>
     <t xml:space="preserve">27.9453926086426</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5741138458252</t>
+    <t xml:space="preserve">27.5741119384766</t>
   </si>
   <si>
     <t xml:space="preserve">27.7190036773682</t>
@@ -1400,67 +1400,67 @@
     <t xml:space="preserve">27.9182224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9816112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.765552520752</t>
+    <t xml:space="preserve">27.9816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7655544281006</t>
   </si>
   <si>
     <t xml:space="preserve">29.4305000305176</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8108310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2364406585693</t>
+    <t xml:space="preserve">29.810827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2364444732666</t>
   </si>
   <si>
     <t xml:space="preserve">29.9104404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">30.562442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4809436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.205379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9026565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7124919891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.020378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9207744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6180458068848</t>
+    <t xml:space="preserve">30.5624389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250503540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4809398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2053813934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9026584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.712495803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0203819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.920768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.618049621582</t>
   </si>
   <si>
     <t xml:space="preserve">32.690486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9621620178223</t>
+    <t xml:space="preserve">32.962158203125</t>
   </si>
   <si>
     <t xml:space="preserve">33.4602088928223</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9039344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110488891602</t>
+    <t xml:space="preserve">33.903938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110450744629</t>
   </si>
   <si>
     <t xml:space="preserve">33.0527153015137</t>
@@ -1469,70 +1469,70 @@
     <t xml:space="preserve">32.3011054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0346031188965</t>
+    <t xml:space="preserve">33.0345993041992</t>
   </si>
   <si>
     <t xml:space="preserve">33.0798797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3153228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.686595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0759925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0941047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3929252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2350997924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.678825378418</t>
+    <t xml:space="preserve">33.3153266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6866035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0759887695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0941009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3929290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2350959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788215637207</t>
   </si>
   <si>
     <t xml:space="preserve">35.4416923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4749374389648</t>
+    <t xml:space="preserve">34.4749336242676</t>
   </si>
   <si>
     <t xml:space="preserve">33.7270660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5022964477539</t>
+    <t xml:space="preserve">34.5022926330566</t>
   </si>
   <si>
     <t xml:space="preserve">35.8065032958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.007152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8671073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1589584350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8156280517578</t>
+    <t xml:space="preserve">36.0071487426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8671035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1589622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8156204223633</t>
   </si>
   <si>
     <t xml:space="preserve">35.8429832458496</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3354835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7035369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2931251525879</t>
+    <t xml:space="preserve">36.3354797363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.703540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2931213378906</t>
   </si>
   <si>
     <t xml:space="preserve">36.2533988952637</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">37.5940933227539</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9041900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4696502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3602066040039</t>
+    <t xml:space="preserve">37.9041938781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4696464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3602104187012</t>
   </si>
   <si>
     <t xml:space="preserve">37.8221054077148</t>
@@ -1559,22 +1559,22 @@
     <t xml:space="preserve">36.6546974182129</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3446044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.28076171875</t>
+    <t xml:space="preserve">36.3446083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2807579040527</t>
   </si>
   <si>
     <t xml:space="preserve">36.0892333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4143333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3960952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5146484375</t>
+    <t xml:space="preserve">35.4143295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3960876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5146560668945</t>
   </si>
   <si>
     <t xml:space="preserve">35.1042404174805</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">35.5693740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3504829406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5205307006836</t>
+    <t xml:space="preserve">35.3504867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5205345153809</t>
   </si>
   <si>
     <t xml:space="preserve">33.9550743103027</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">33.7453079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2925262451172</t>
+    <t xml:space="preserve">34.2925224304199</t>
   </si>
   <si>
     <t xml:space="preserve">35.0586357116699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1830787658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8397483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5967407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1224784851074</t>
+    <t xml:space="preserve">34.1830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8397445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.596736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1224746704102</t>
   </si>
   <si>
     <t xml:space="preserve">35.6241035461426</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">34.8853492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6938285827637</t>
+    <t xml:space="preserve">34.6938171386719</t>
   </si>
   <si>
     <t xml:space="preserve">33.8091430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4019737243652</t>
+    <t xml:space="preserve">34.401969909668</t>
   </si>
   <si>
     <t xml:space="preserve">34.2013244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4169807434082</t>
+    <t xml:space="preserve">33.4169731140137</t>
   </si>
   <si>
     <t xml:space="preserve">34.2651634216309</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">34.3746070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5387763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7303085327148</t>
+    <t xml:space="preserve">34.5387725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7303047180176</t>
   </si>
   <si>
     <t xml:space="preserve">34.6208572387695</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">34.0189170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8215065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4840545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7941436767578</t>
+    <t xml:space="preserve">34.8215103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7941474914551</t>
   </si>
   <si>
     <t xml:space="preserve">35.5784912109375</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">36.2169189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1530799865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172454833984</t>
+    <t xml:space="preserve">36.1530723571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172492980957</t>
   </si>
   <si>
     <t xml:space="preserve">35.5328941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5055313110352</t>
+    <t xml:space="preserve">35.5055351257324</t>
   </si>
   <si>
     <t xml:space="preserve">35.1133613586426</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">33.8365097045898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2834091186523</t>
+    <t xml:space="preserve">34.2834053039551</t>
   </si>
   <si>
     <t xml:space="preserve">34.3381309509277</t>
   </si>
   <si>
-    <t xml:space="preserve">34.301643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.785026550293</t>
+    <t xml:space="preserve">34.3016510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7850227355957</t>
   </si>
   <si>
     <t xml:space="preserve">33.9824333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6117401123047</t>
+    <t xml:space="preserve">34.6117362976074</t>
   </si>
   <si>
     <t xml:space="preserve">34.4202117919922</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">34.5934944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5114135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0827598571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664657592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2228012084961</t>
+    <t xml:space="preserve">34.5114097595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0827560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2228050231934</t>
   </si>
   <si>
     <t xml:space="preserve">34.940071105957</t>
@@ -1742,25 +1742,25 @@
     <t xml:space="preserve">32.9791946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8300323486328</t>
+    <t xml:space="preserve">31.8300342559814</t>
   </si>
   <si>
     <t xml:space="preserve">32.4593391418457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9388790130615</t>
+    <t xml:space="preserve">28.9388809204102</t>
   </si>
   <si>
     <t xml:space="preserve">28.5284633636475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2001304626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.263973236084</t>
+    <t xml:space="preserve">28.2001285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2639751434326</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007778167725</t>
@@ -1769,34 +1769,34 @@
     <t xml:space="preserve">28.4555015563965</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7258720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7988357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6587924957275</t>
+    <t xml:space="preserve">27.7258701324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7988338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6587905883789</t>
   </si>
   <si>
     <t xml:space="preserve">27.2698554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9082794189453</t>
+    <t xml:space="preserve">27.9082775115967</t>
   </si>
   <si>
     <t xml:space="preserve">27.5708255767822</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1786499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5434665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9994869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0906867980957</t>
+    <t xml:space="preserve">27.1786518096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9994812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0906848907471</t>
   </si>
   <si>
     <t xml:space="preserve">29.5499458312988</t>
@@ -1805,58 +1805,58 @@
     <t xml:space="preserve">29.1942481994629</t>
   </si>
   <si>
-    <t xml:space="preserve">28.97536277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1304092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4522609710693</t>
+    <t xml:space="preserve">28.9753608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1304054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.452262878418</t>
   </si>
   <si>
     <t xml:space="preserve">29.0392017364502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0268440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0359649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2666187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8503170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.813835144043</t>
+    <t xml:space="preserve">28.0268421173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0359630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3519382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2666168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8138389587402</t>
   </si>
   <si>
     <t xml:space="preserve">27.4340209960938</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2060108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7317562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9141635894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8079528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.768238067627</t>
+    <t xml:space="preserve">27.2060127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7317523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9141616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7682361602783</t>
   </si>
   <si>
     <t xml:space="preserve">27.3063354492188</t>
@@ -1868,64 +1868,64 @@
     <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4822673797607</t>
+    <t xml:space="preserve">25.4822654724121</t>
   </si>
   <si>
     <t xml:space="preserve">25.327220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9565258026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265716552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6431941986084</t>
+    <t xml:space="preserve">25.956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646709442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265735626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6431922912598</t>
   </si>
   <si>
     <t xml:space="preserve">25.1721744537354</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7011547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1448135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3454627990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5825881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3851795196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.59494972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3636989593506</t>
+    <t xml:space="preserve">25.7011566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.144811630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3454608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5825901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3851833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5949459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3637008666992</t>
   </si>
   <si>
     <t xml:space="preserve">26.467264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1877708435059</t>
+    <t xml:space="preserve">27.1877727508545</t>
   </si>
   <si>
     <t xml:space="preserve">27.935640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6014289855957</t>
+    <t xml:space="preserve">28.6014251708984</t>
   </si>
   <si>
     <t xml:space="preserve">28.1454105377197</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0600872039795</t>
+    <t xml:space="preserve">27.0600852966309</t>
   </si>
   <si>
     <t xml:space="preserve">27.0327243804932</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">27.4066600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6711502075195</t>
+    <t xml:space="preserve">27.6711521148682</t>
   </si>
   <si>
     <t xml:space="preserve">27.8991603851318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.379301071167</t>
+    <t xml:space="preserve">27.3792991638184</t>
   </si>
   <si>
     <t xml:space="preserve">27.9538803100586</t>
@@ -1955,61 +1955,61 @@
     <t xml:space="preserve">28.2366123199463</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9147605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0059585571289</t>
+    <t xml:space="preserve">29.9147567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0059642791748</t>
   </si>
   <si>
     <t xml:space="preserve">30.598783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7994289398193</t>
+    <t xml:space="preserve">30.7994327545166</t>
   </si>
   <si>
     <t xml:space="preserve">31.2007293701172</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4437408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6443862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9362373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284111022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8117923736572</t>
+    <t xml:space="preserve">30.4437389373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6443824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9362335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023448944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284130096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8117904663086</t>
   </si>
   <si>
     <t xml:space="preserve">31.7753067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6567440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743347167969</t>
+    <t xml:space="preserve">31.6567478179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743366241455</t>
   </si>
   <si>
     <t xml:space="preserve">31.9668350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9029960632324</t>
+    <t xml:space="preserve">31.9029903411865</t>
   </si>
   <si>
     <t xml:space="preserve">30.7538299560547</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">32.9244728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8332710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.696460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5779037475586</t>
+    <t xml:space="preserve">32.8332672119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6964645385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5140609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5778999328613</t>
   </si>
   <si>
     <t xml:space="preserve">32.4319763183594</t>
@@ -2042,28 +2042,28 @@
     <t xml:space="preserve">32.9153518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0065536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5264167785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1980857849121</t>
+    <t xml:space="preserve">33.0065498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5264129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1980819702148</t>
   </si>
   <si>
     <t xml:space="preserve">32.2313270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7388286590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4410934448242</t>
+    <t xml:space="preserve">31.7388305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4410972595215</t>
   </si>
   <si>
     <t xml:space="preserve">32.7603073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5081748962402</t>
+    <t xml:space="preserve">33.5081825256348</t>
   </si>
   <si>
     <t xml:space="preserve">33.6085014343262</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">34.128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9277076721191</t>
+    <t xml:space="preserve">33.9277114868164</t>
   </si>
   <si>
     <t xml:space="preserve">33.8638725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8150291442871</t>
+    <t xml:space="preserve">32.8150329589844</t>
   </si>
   <si>
     <t xml:space="preserve">32.659984588623</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">33.2163238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2892837524414</t>
+    <t xml:space="preserve">33.2892875671387</t>
   </si>
   <si>
     <t xml:space="preserve">33.0977592468262</t>
@@ -2096,43 +2096,43 @@
     <t xml:space="preserve">33.426097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1160049438477</t>
+    <t xml:space="preserve">33.1160011291504</t>
   </si>
   <si>
     <t xml:space="preserve">33.3075256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">33.872989654541</t>
+    <t xml:space="preserve">33.8729972839355</t>
   </si>
   <si>
     <t xml:space="preserve">33.6814613342285</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0612754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3440093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531303405762</t>
+    <t xml:space="preserve">33.061279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3440132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531265258789</t>
   </si>
   <si>
     <t xml:space="preserve">33.2345657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9185943603516</t>
+    <t xml:space="preserve">33.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">33.1616058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5505409240723</t>
+    <t xml:space="preserve">32.550537109375</t>
   </si>
   <si>
     <t xml:space="preserve">32.404613494873</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4443321228027</t>
+    <t xml:space="preserve">33.4443283081055</t>
   </si>
   <si>
     <t xml:space="preserve">31.9485950469971</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">32.5596618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5911712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.836368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2552795410156</t>
+    <t xml:space="preserve">31.5911750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863277435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8363723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8586616516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2552757263184</t>
   </si>
   <si>
     <t xml:space="preserve">32.2829475402832</t>
@@ -2168,61 +2168,61 @@
     <t xml:space="preserve">31.7848663330078</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7887115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382095336914</t>
+    <t xml:space="preserve">30.7887096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.43821144104</t>
   </si>
   <si>
     <t xml:space="preserve">30.5581150054932</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1207618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217582702637</t>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217620849609</t>
   </si>
   <si>
     <t xml:space="preserve">32.0062370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6649627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7387466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290634155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6518974304199</t>
+    <t xml:space="preserve">31.6649646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387523651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6519012451172</t>
   </si>
   <si>
     <t xml:space="preserve">33.6480560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7679672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.413631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7864151000977</t>
+    <t xml:space="preserve">33.7679634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7087783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5058631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4136238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7864112854004</t>
   </si>
   <si>
     <t xml:space="preserve">33.5189247131348</t>
@@ -2237,76 +2237,76 @@
     <t xml:space="preserve">35.0500602722168</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9762687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5112457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6127014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5204620361328</t>
+    <t xml:space="preserve">34.9762649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5112419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6127052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5204658508301</t>
   </si>
   <si>
     <t xml:space="preserve">35.5296897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2806510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3544425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0961837768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4927940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0408363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1330757141113</t>
+    <t xml:space="preserve">35.280647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3544387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0961761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4927978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0408401489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1330718994141</t>
   </si>
   <si>
     <t xml:space="preserve">35.2253074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2437553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.658821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9263114929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9908790588379</t>
+    <t xml:space="preserve">35.2437515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9263153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9908752441406</t>
   </si>
   <si>
     <t xml:space="preserve">35.963207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6903305053711</t>
+    <t xml:space="preserve">34.6903381347656</t>
   </si>
   <si>
     <t xml:space="preserve">34.2844886779785</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4451332092285</t>
+    <t xml:space="preserve">33.4451370239258</t>
   </si>
   <si>
     <t xml:space="preserve">31.4620399475098</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4343662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309841156006</t>
+    <t xml:space="preserve">31.4343681335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309879302979</t>
   </si>
   <si>
     <t xml:space="preserve">32.4120788574219</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">32.3475151062012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4989356994629</t>
+    <t xml:space="preserve">31.4989395141602</t>
   </si>
   <si>
     <t xml:space="preserve">31.2314472198486</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">32.7072372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7479705810547</t>
+    <t xml:space="preserve">31.747974395752</t>
   </si>
   <si>
     <t xml:space="preserve">31.5542774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3605785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3052406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6465167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3382949829102</t>
+    <t xml:space="preserve">31.36057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3052349090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6465148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3382911682129</t>
   </si>
   <si>
     <t xml:space="preserve">33.0761871337891</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1684265136719</t>
+    <t xml:space="preserve">33.1684226989746</t>
   </si>
   <si>
     <t xml:space="preserve">32.7349128723145</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">32.5412101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6242256164551</t>
+    <t xml:space="preserve">32.6242218017578</t>
   </si>
   <si>
     <t xml:space="preserve">32.6426696777344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.375186920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6372909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4804821014404</t>
+    <t xml:space="preserve">32.3751831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6372890472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.480489730835</t>
   </si>
   <si>
     <t xml:space="preserve">29.2760219573975</t>
@@ -2384,28 +2384,28 @@
     <t xml:space="preserve">29.9493541717529</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0877056121826</t>
+    <t xml:space="preserve">30.0877075195312</t>
   </si>
   <si>
     <t xml:space="preserve">29.6080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7279853820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6449718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8478908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3367500305176</t>
+    <t xml:space="preserve">29.7279834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6449680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8478946685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3367462158203</t>
   </si>
   <si>
     <t xml:space="preserve">30.1614990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8294448852539</t>
+    <t xml:space="preserve">29.8294467926025</t>
   </si>
   <si>
     <t xml:space="preserve">29.1376686096191</t>
@@ -2414,79 +2414,79 @@
     <t xml:space="preserve">29.6173000335693</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0139179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1983947753906</t>
+    <t xml:space="preserve">30.0139198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.198392868042</t>
   </si>
   <si>
     <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6134586334229</t>
+    <t xml:space="preserve">30.6134605407715</t>
   </si>
   <si>
     <t xml:space="preserve">31.1945514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">31.803316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5450496673584</t>
+    <t xml:space="preserve">31.8033180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5450534820557</t>
   </si>
   <si>
     <t xml:space="preserve">31.4251441955566</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0285224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.724142074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6726398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9770221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7741031646729</t>
+    <t xml:space="preserve">31.0285243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7241439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6726379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9770259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7741012573242</t>
   </si>
   <si>
     <t xml:space="preserve">29.6910877227783</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9678001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.362117767334</t>
+    <t xml:space="preserve">29.9678020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3621215820312</t>
   </si>
   <si>
     <t xml:space="preserve">32.7441329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9877891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5504417419434</t>
+    <t xml:space="preserve">31.9877910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4397506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5504379272461</t>
   </si>
   <si>
     <t xml:space="preserve">32.310619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2291450500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3121604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0907974243164</t>
+    <t xml:space="preserve">34.2291526794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3121643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0907936096191</t>
   </si>
   <si>
     <t xml:space="preserve">34.0077743530273</t>
@@ -2495,19 +2495,19 @@
     <t xml:space="preserve">33.6111602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7218437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9801063537598</t>
+    <t xml:space="preserve">33.7218475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.980110168457</t>
   </si>
   <si>
     <t xml:space="preserve">34.2199249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">34.819465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5243110656738</t>
+    <t xml:space="preserve">34.8194618225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5243072509766</t>
   </si>
   <si>
     <t xml:space="preserve">36.0462188720703</t>
@@ -2519,22 +2519,22 @@
     <t xml:space="preserve">37.0239295959473</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6826553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7787322998047</t>
+    <t xml:space="preserve">36.6826515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7787284851074</t>
   </si>
   <si>
     <t xml:space="preserve">35.6772727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156318664551</t>
+    <t xml:space="preserve">35.8156242370605</t>
   </si>
   <si>
     <t xml:space="preserve">38.1492233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9240112304688</t>
+    <t xml:space="preserve">38.924015045166</t>
   </si>
   <si>
     <t xml:space="preserve">38.545841217041</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">38.0938758850098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8171691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7249336242676</t>
+    <t xml:space="preserve">37.8171653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7249298095703</t>
   </si>
   <si>
     <t xml:space="preserve">37.1530609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3006401062012</t>
+    <t xml:space="preserve">37.3006362915039</t>
   </si>
   <si>
     <t xml:space="preserve">37.0423812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1899528503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7157096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6234741210938</t>
+    <t xml:space="preserve">37.1899566650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.715705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6234703063965</t>
   </si>
   <si>
     <t xml:space="preserve">37.4758911132812</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">36.9778137207031</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1438369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9647521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5496788024902</t>
+    <t xml:space="preserve">37.1438407897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9647483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9462966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.549674987793</t>
   </si>
   <si>
     <t xml:space="preserve">37.6326942443848</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">38.3613662719727</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4036445617676</t>
+    <t xml:space="preserve">39.4036407470703</t>
   </si>
   <si>
     <t xml:space="preserve">39.3667488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">39.385196685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1399955749512</t>
+    <t xml:space="preserve">39.3852005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1400032043457</t>
   </si>
   <si>
     <t xml:space="preserve">37.2914199829102</t>
@@ -2618,25 +2618,25 @@
     <t xml:space="preserve">38.2691307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2084083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4021034240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8432960510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2360725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.488956451416</t>
+    <t xml:space="preserve">37.2084045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.402099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8432998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2360763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4889526367188</t>
   </si>
   <si>
     <t xml:space="preserve">35.9724273681641</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3690452575684</t>
+    <t xml:space="preserve">36.3690490722656</t>
   </si>
   <si>
     <t xml:space="preserve">36.8579025268555</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">36.5166244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7049407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.649600982666</t>
+    <t xml:space="preserve">35.7049369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6496047973633</t>
   </si>
   <si>
     <t xml:space="preserve">36.2583618164062</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">35.1422958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2898712158203</t>
+    <t xml:space="preserve">35.2898750305176</t>
   </si>
   <si>
     <t xml:space="preserve">36.0093231201172</t>
@@ -2672,49 +2672,49 @@
     <t xml:space="preserve">34.2660446166992</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4305267333984</t>
+    <t xml:space="preserve">32.4305229187012</t>
   </si>
   <si>
     <t xml:space="preserve">32.4028587341309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9286079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5227699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4858741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1023139953613</t>
+    <t xml:space="preserve">32.9286041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.522762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4858703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.10231590271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1507320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8002281188965</t>
+    <t xml:space="preserve">27.8002300262451</t>
   </si>
   <si>
     <t xml:space="preserve">27.0807819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.981616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3943901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2637119293213</t>
+    <t xml:space="preserve">23.9816188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3943881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2637138366699</t>
   </si>
   <si>
     <t xml:space="preserve">24.9039878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3651733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.922435760498</t>
+    <t xml:space="preserve">25.3651752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9224376678467</t>
   </si>
   <si>
     <t xml:space="preserve">26.9977684020996</t>
@@ -2723,31 +2723,31 @@
     <t xml:space="preserve">26.3797817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9309043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4528121948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.729528427124</t>
+    <t xml:space="preserve">29.930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4528141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7295303344727</t>
   </si>
   <si>
     <t xml:space="preserve">30.7056980133057</t>
   </si>
   <si>
-    <t xml:space="preserve">29.875560760498</t>
+    <t xml:space="preserve">29.8755626678467</t>
   </si>
   <si>
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857051849365</t>
+    <t xml:space="preserve">28.6857070922852</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1061553955078</t>
+    <t xml:space="preserve">30.1061534881592</t>
   </si>
   <si>
     <t xml:space="preserve">30.2998504638672</t>
@@ -2756,37 +2756,37 @@
     <t xml:space="preserve">31.0838661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">30.631908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8402118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8901672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5765647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5081539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.272180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.770263671875</t>
+    <t xml:space="preserve">30.6319046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8402137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5135383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8901691436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.576566696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5081596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2721786499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7702617645264</t>
   </si>
   <si>
     <t xml:space="preserve">29.9124584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2352867126465</t>
+    <t xml:space="preserve">30.2352848052979</t>
   </si>
   <si>
     <t xml:space="preserve">29.7833271026611</t>
@@ -2795,124 +2795,124 @@
     <t xml:space="preserve">30.2260646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">29.414379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7041511535645</t>
+    <t xml:space="preserve">29.4143753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7041530609131</t>
   </si>
   <si>
     <t xml:space="preserve">28.6211414337158</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7372093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8663387298584</t>
+    <t xml:space="preserve">29.7372074127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.866340637207</t>
   </si>
   <si>
     <t xml:space="preserve">28.8056144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">29.368257522583</t>
+    <t xml:space="preserve">29.3682594299316</t>
   </si>
   <si>
     <t xml:space="preserve">30.7979335784912</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3920917510986</t>
+    <t xml:space="preserve">30.39208984375</t>
   </si>
   <si>
     <t xml:space="preserve">32.1630363464355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8532752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955574035645</t>
+    <t xml:space="preserve">30.8532772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0746421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955535888672</t>
   </si>
   <si>
     <t xml:space="preserve">32.0339088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3790283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9693431854248</t>
+    <t xml:space="preserve">31.0377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3790245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9693393707275</t>
   </si>
   <si>
     <t xml:space="preserve">32.4950904846191</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7625770568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0577392578125</t>
+    <t xml:space="preserve">32.762580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0577430725098</t>
   </si>
   <si>
     <t xml:space="preserve">32.0892524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7203044891357</t>
+    <t xml:space="preserve">31.7203025817871</t>
   </si>
   <si>
     <t xml:space="preserve">32.126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3974704742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6003952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591190338135</t>
+    <t xml:space="preserve">31.3974723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6003932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591133117676</t>
   </si>
   <si>
     <t xml:space="preserve">31.9601211547852</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4897079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3513565063477</t>
+    <t xml:space="preserve">31.4897136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.351354598999</t>
   </si>
   <si>
     <t xml:space="preserve">30.650354385376</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0654182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824085235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0100784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5950088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0692615509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0969333648682</t>
+    <t xml:space="preserve">31.0654220581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0100746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5950126647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0692596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0969314575195</t>
   </si>
   <si>
     <t xml:space="preserve">29.4236011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5804042816162</t>
+    <t xml:space="preserve">29.5804061889648</t>
   </si>
   <si>
     <t xml:space="preserve">29.488166809082</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">30.8809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3275241851807</t>
+    <t xml:space="preserve">30.3275260925293</t>
   </si>
   <si>
     <t xml:space="preserve">30.0784873962402</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">29.5342864990234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5527324676514</t>
+    <t xml:space="preserve">29.552734375</t>
   </si>
   <si>
     <t xml:space="preserve">29.8571147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0046920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.585786819458</t>
+    <t xml:space="preserve">30.0046939849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5857887268066</t>
   </si>
   <si>
     <t xml:space="preserve">29.8847885131836</t>
@@ -2948,28 +2948,28 @@
     <t xml:space="preserve">29.9585762023926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1484317779541</t>
+    <t xml:space="preserve">31.1484355926514</t>
   </si>
   <si>
     <t xml:space="preserve">31.7940921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4766426086426</t>
+    <t xml:space="preserve">32.1814842224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4766464233398</t>
   </si>
   <si>
     <t xml:space="preserve">33.8878746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9854888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3306121826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.66650390625</t>
+    <t xml:space="preserve">34.9854927062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3306159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6665000915527</t>
   </si>
   <si>
     <t xml:space="preserve">32.4674186706543</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">32.448974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2645034790039</t>
+    <t xml:space="preserve">32.2644996643066</t>
   </si>
   <si>
     <t xml:space="preserve">32.8455963134766</t>
@@ -2999,34 +2999,34 @@
     <t xml:space="preserve">33.2237663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5650444030762</t>
+    <t xml:space="preserve">33.5650367736816</t>
   </si>
   <si>
     <t xml:space="preserve">33.9339904785156</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0354537963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6057777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9432106018066</t>
+    <t xml:space="preserve">34.0354499816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6057739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9432144165039</t>
   </si>
   <si>
     <t xml:space="preserve">34.9485969543457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4043998718262</t>
+    <t xml:space="preserve">34.4044036865234</t>
   </si>
   <si>
     <t xml:space="preserve">35.9170837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1276931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1907119750977</t>
+    <t xml:space="preserve">34.1276893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1907157897949</t>
   </si>
   <si>
     <t xml:space="preserve">32.3936309814453</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">33.2053184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5465927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.884033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6349945068359</t>
+    <t xml:space="preserve">33.5465965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8840293884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6349906921387</t>
   </si>
   <si>
     <t xml:space="preserve">36.5996398925781</t>
@@ -3050,49 +3050,49 @@
     <t xml:space="preserve">36.6273078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3467597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7195510864258</t>
+    <t xml:space="preserve">37.3467636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7195472717285</t>
   </si>
   <si>
     <t xml:space="preserve">37.8909645080566</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8725090026855</t>
+    <t xml:space="preserve">37.8725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">37.6142463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4482154846191</t>
+    <t xml:space="preserve">37.4482192993164</t>
   </si>
   <si>
     <t xml:space="preserve">38.4536018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7118721008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6473045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.241455078125</t>
+    <t xml:space="preserve">38.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6473007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2414588928223</t>
   </si>
   <si>
     <t xml:space="preserve">37.8263893127441</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9001808166504</t>
+    <t xml:space="preserve">37.9001770019531</t>
   </si>
   <si>
     <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2837333679199</t>
+    <t xml:space="preserve">39.2837371826172</t>
   </si>
   <si>
     <t xml:space="preserve">39.8463821411133</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">41.4144134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9916648864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8533058166504</t>
+    <t xml:space="preserve">42.9916610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8533096313477</t>
   </si>
   <si>
     <t xml:space="preserve">43.8863639831543</t>
@@ -3119,28 +3119,28 @@
     <t xml:space="preserve">45.0116539001465</t>
   </si>
   <si>
-    <t xml:space="preserve">44.928638458252</t>
+    <t xml:space="preserve">44.9286422729492</t>
   </si>
   <si>
     <t xml:space="preserve">45.1961288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7349472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8679122924805</t>
+    <t xml:space="preserve">44.7349395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.867919921875</t>
   </si>
   <si>
     <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4674530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.869457244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3952102661133</t>
+    <t xml:space="preserve">44.467456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8694534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3952140808105</t>
   </si>
   <si>
     <t xml:space="preserve">46.247631072998</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">44.8456268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8640747070312</t>
+    <t xml:space="preserve">44.8640785217285</t>
   </si>
   <si>
     <t xml:space="preserve">44.1077308654785</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">44.3291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2737617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3882827758789</t>
+    <t xml:space="preserve">44.273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3882789611816</t>
   </si>
   <si>
     <t xml:space="preserve">44.4121170043945</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">44.0708351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6742172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6703796386719</t>
+    <t xml:space="preserve">43.6742134094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6703720092773</t>
   </si>
   <si>
     <t xml:space="preserve">43.9509315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8917427062988</t>
+    <t xml:space="preserve">44.8917503356934</t>
   </si>
   <si>
     <t xml:space="preserve">45.7403259277344</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">46.1369476318359</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8932876586914</t>
+    <t xml:space="preserve">46.8932914733887</t>
   </si>
   <si>
     <t xml:space="preserve">47.5758438110352</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">48.0739212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6496276855469</t>
+    <t xml:space="preserve">47.6496315002441</t>
   </si>
   <si>
     <t xml:space="preserve">47.9447898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2622375488281</t>
+    <t xml:space="preserve">47.2622337341309</t>
   </si>
   <si>
     <t xml:space="preserve">48.1477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7972106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.708812713623</t>
+    <t xml:space="preserve">47.7972145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7088165283203</t>
   </si>
   <si>
     <t xml:space="preserve">46.6534767150879</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">49.1807670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8710060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2437934875488</t>
+    <t xml:space="preserve">47.8710021972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2437896728516</t>
   </si>
   <si>
     <t xml:space="preserve">47.0408668518066</t>
@@ -3257,13 +3257,13 @@
     <t xml:space="preserve">47.3175773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1108169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4613227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6865234375</t>
+    <t xml:space="preserve">48.1108131408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4613151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6865272521973</t>
   </si>
   <si>
     <t xml:space="preserve">46.6165771484375</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">46.4136543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7587699890137</t>
+    <t xml:space="preserve">45.7587776184082</t>
   </si>
   <si>
     <t xml:space="preserve">48.0001335144043</t>
@@ -3287,55 +3287,55 @@
     <t xml:space="preserve">47.3360252380371</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4467124938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8379440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2107353210449</t>
+    <t xml:space="preserve">47.4467086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.837947845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2107391357422</t>
   </si>
   <si>
     <t xml:space="preserve">45.6019744873047</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3806037902832</t>
+    <t xml:space="preserve">45.3805999755859</t>
   </si>
   <si>
     <t xml:space="preserve">44.2276382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4397811889648</t>
+    <t xml:space="preserve">44.4397850036621</t>
   </si>
   <si>
     <t xml:space="preserve">44.4859008789062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3898239135742</t>
+    <t xml:space="preserve">45.3898277282715</t>
   </si>
   <si>
     <t xml:space="preserve">45.0762176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8417892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6573104858398</t>
+    <t xml:space="preserve">45.8417854309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6573143005371</t>
   </si>
   <si>
     <t xml:space="preserve">46.450553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5981330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.524341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5020523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3544731140137</t>
+    <t xml:space="preserve">46.5981292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5243377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5020561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3544769287109</t>
   </si>
   <si>
     <t xml:space="preserve">46.321418762207</t>
@@ -3347,10 +3347,10 @@
     <t xml:space="preserve">49.346794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9670791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0039710998535</t>
+    <t xml:space="preserve">46.9670753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0039749145508</t>
   </si>
   <si>
     <t xml:space="preserve">47.0593147277832</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">47.4836044311523</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3767547607422</t>
+    <t xml:space="preserve">46.3767623901367</t>
   </si>
   <si>
     <t xml:space="preserve">47.4282608032227</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2806816101074</t>
+    <t xml:space="preserve">47.2806854248047</t>
   </si>
   <si>
     <t xml:space="preserve">47.7234230041504</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">46.985523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5942840576172</t>
+    <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
     <t xml:space="preserve">47.926342010498</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">48.6642379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4244270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1623153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4205856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.490291595459</t>
+    <t xml:space="preserve">48.4244232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1623191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.420581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4902877807617</t>
   </si>
   <si>
     <t xml:space="preserve">51.1228179931641</t>
@@ -3401,34 +3401,34 @@
     <t xml:space="preserve">51.625114440918</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0203895568848</t>
+    <t xml:space="preserve">53.0203857421875</t>
   </si>
   <si>
     <t xml:space="preserve">53.9877777099609</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0621948242188</t>
+    <t xml:space="preserve">54.0621871948242</t>
   </si>
   <si>
     <t xml:space="preserve">53.4482688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6343078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1180000305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2296257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1039924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8063316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5784950256348</t>
+    <t xml:space="preserve">53.6343116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1180038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.229621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1040000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8063354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.578498840332</t>
   </si>
   <si>
     <t xml:space="preserve">52.8343505859375</t>
@@ -3437,34 +3437,34 @@
     <t xml:space="preserve">52.8715591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">53.132007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8947601318359</t>
+    <t xml:space="preserve">53.1320114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8947563171387</t>
   </si>
   <si>
     <t xml:space="preserve">54.2482261657715</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5086784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.043586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1738128662109</t>
+    <t xml:space="preserve">54.508674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0435829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1738166809082</t>
   </si>
   <si>
     <t xml:space="preserve">54.2110214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">53.225025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6901206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5971031188965</t>
+    <t xml:space="preserve">53.2250289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5970993041992</t>
   </si>
   <si>
     <t xml:space="preserve">53.0761985778809</t>
@@ -3473,34 +3473,34 @@
     <t xml:space="preserve">53.4668769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3180465698242</t>
+    <t xml:space="preserve">53.3180503845215</t>
   </si>
   <si>
     <t xml:space="preserve">52.815746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0389938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3366546630859</t>
+    <t xml:space="preserve">53.038990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3366508483887</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4250717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2808380126953</t>
+    <t xml:space="preserve">52.4250755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2808418273926</t>
   </si>
   <si>
     <t xml:space="preserve">53.7273254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3598518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7785415649414</t>
+    <t xml:space="preserve">54.3598480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7785453796387</t>
   </si>
   <si>
     <t xml:space="preserve">52.1460189819336</t>
@@ -3515,19 +3515,19 @@
     <t xml:space="preserve">54.6203002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4388580322266</t>
+    <t xml:space="preserve">55.4388618469238</t>
   </si>
   <si>
     <t xml:space="preserve">55.7551193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4946746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8761558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.950569152832</t>
+    <t xml:space="preserve">55.4946708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8761520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9505653381348</t>
   </si>
   <si>
     <t xml:space="preserve">54.6389083862305</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">54.6947174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5272827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5876922607422</t>
+    <t xml:space="preserve">54.5272789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5876884460449</t>
   </si>
   <si>
     <t xml:space="preserve">56.9271507263184</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">57.2992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">57.727108001709</t>
+    <t xml:space="preserve">57.7271118164062</t>
   </si>
   <si>
     <t xml:space="preserve">57.5596771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4248504638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8667488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3970565795898</t>
+    <t xml:space="preserve">56.4248542785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8667449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3970527648926</t>
   </si>
   <si>
     <t xml:space="preserve">51.067008972168</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">50.7693519592285</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3972778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5461006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8065528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4158744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0298004150391</t>
+    <t xml:space="preserve">50.3972702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5461044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8065567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4158782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0297966003418</t>
   </si>
   <si>
     <t xml:space="preserve">50.9925918579102</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">51.1042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">51.718132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4018707275391</t>
+    <t xml:space="preserve">51.7181282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4018669128418</t>
   </si>
   <si>
     <t xml:space="preserve">51.3274574279785</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">48.1648330688477</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0904197692871</t>
+    <t xml:space="preserve">48.0904235839844</t>
   </si>
   <si>
     <t xml:space="preserve">49.3182640075684</t>
@@ -3626,55 +3626,55 @@
     <t xml:space="preserve">48.0532150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0020027160645</t>
+    <t xml:space="preserve">49.0019989013672</t>
   </si>
   <si>
     <t xml:space="preserve">50.5647048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3832702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1600227355957</t>
+    <t xml:space="preserve">51.3832664489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.160026550293</t>
   </si>
   <si>
     <t xml:space="preserve">50.0624084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6113204956055</t>
+    <t xml:space="preserve">48.6113243103027</t>
   </si>
   <si>
     <t xml:space="preserve">49.2438468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7553405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.978588104248</t>
+    <t xml:space="preserve">51.7553367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9785842895508</t>
   </si>
   <si>
     <t xml:space="preserve">52.9831771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4994812011719</t>
+    <t xml:space="preserve">52.4994850158691</t>
   </si>
   <si>
     <t xml:space="preserve">52.4622802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4714698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5690879821777</t>
+    <t xml:space="preserve">54.713321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4714736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5690841674805</t>
   </si>
   <si>
     <t xml:space="preserve">56.0341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7597236633301</t>
+    <t xml:space="preserve">56.7597198486328</t>
   </si>
   <si>
     <t xml:space="preserve">56.8341331481934</t>
@@ -3695,58 +3695,58 @@
     <t xml:space="preserve">59.4386444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5084648132324</t>
+    <t xml:space="preserve">58.5084609985352</t>
   </si>
   <si>
     <t xml:space="preserve">59.2340049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">61.652473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8803176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4012184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106292724609</t>
+    <t xml:space="preserve">61.6524772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.880313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4012222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106254577637</t>
   </si>
   <si>
     <t xml:space="preserve">60.7409019470215</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8199157714844</t>
+    <t xml:space="preserve">61.8199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.754695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.331413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2197799682617</t>
+    <t xml:space="preserve">63.7546882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3314056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2197875976562</t>
   </si>
   <si>
     <t xml:space="preserve">63.5686531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0663604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408554077148</t>
+    <t xml:space="preserve">63.0663566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408630371094</t>
   </si>
   <si>
     <t xml:space="preserve">61.9129295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3222045898438</t>
+    <t xml:space="preserve">62.322208404541</t>
   </si>
   <si>
     <t xml:space="preserve">58.3410301208496</t>
@@ -3758,22 +3758,22 @@
     <t xml:space="preserve">59.6060791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0385589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9455375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5920715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6896820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4430236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4710426330566</t>
+    <t xml:space="preserve">61.0385627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9455337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5920677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6896858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4430313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4710464477539</t>
   </si>
   <si>
     <t xml:space="preserve">62.1547737121582</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">61.4478340148926</t>
   </si>
   <si>
-    <t xml:space="preserve">60.629280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6758995056152</t>
+    <t xml:space="preserve">60.6292762756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.675895690918</t>
   </si>
   <si>
     <t xml:space="preserve">60.182788848877</t>
@@ -3794,16 +3794,16 @@
     <t xml:space="preserve">58.7503128051758</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8061218261719</t>
+    <t xml:space="preserve">58.8061256408691</t>
   </si>
   <si>
     <t xml:space="preserve">58.2294082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8573341369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3224220275879</t>
+    <t xml:space="preserve">57.8573379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3224258422852</t>
   </si>
   <si>
     <t xml:space="preserve">58.5642738342285</t>
@@ -3812,22 +3812,22 @@
     <t xml:space="preserve">59.7549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0711669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.5502662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.810718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4618453979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9269409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4154434204102</t>
+    <t xml:space="preserve">60.0711708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.5502624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.8107223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4618492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9269332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4154396057129</t>
   </si>
   <si>
     <t xml:space="preserve">56.9643592834473</t>
@@ -3836,22 +3836,22 @@
     <t xml:space="preserve">56.1644058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7923278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8807487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8901634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7087211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6111106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3040390014648</t>
+    <t xml:space="preserve">55.7923316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8807525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8901596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7087249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6111068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3040351867676</t>
   </si>
   <si>
     <t xml:space="preserve">54.3412437438965</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">51.6995315551758</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2716407775879</t>
+    <t xml:space="preserve">51.2716445922852</t>
   </si>
   <si>
     <t xml:space="preserve">52.3134536743164</t>
@@ -3881,49 +3881,49 @@
     <t xml:space="preserve">55.271427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8389472961426</t>
+    <t xml:space="preserve">53.8389511108398</t>
   </si>
   <si>
     <t xml:space="preserve">54.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6437187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6391143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1274108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2344360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9739837646484</t>
+    <t xml:space="preserve">51.6437149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6391181945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1274185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2344398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9739875793457</t>
   </si>
   <si>
     <t xml:space="preserve">50.9181785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8809661865234</t>
+    <t xml:space="preserve">50.8809700012207</t>
   </si>
   <si>
     <t xml:space="preserve">48.4624938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8021774291992</t>
+    <t xml:space="preserve">45.802173614502</t>
   </si>
   <si>
     <t xml:space="preserve">47.1230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9464073181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8768043518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1465606689453</t>
+    <t xml:space="preserve">44.946403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8768081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1465530395508</t>
   </si>
   <si>
     <t xml:space="preserve">41.4954299926758</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">43.9976196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6208457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6487464904785</t>
+    <t xml:space="preserve">44.6208419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6487426757812</t>
   </si>
   <si>
     <t xml:space="preserve">43.2441711425781</t>
@@ -3947,28 +3947,28 @@
     <t xml:space="preserve">45.709156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7881660461426</t>
+    <t xml:space="preserve">46.7881698608398</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044273376465</t>
+    <t xml:space="preserve">47.1044311523438</t>
   </si>
   <si>
     <t xml:space="preserve">46.2951698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8207702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2021522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2765693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8717803955078</t>
+    <t xml:space="preserve">45.8207740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2765655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8717727661133</t>
   </si>
   <si>
     <t xml:space="preserve">47.1974487304688</t>
@@ -3989,19 +3989,19 @@
     <t xml:space="preserve">45.9882125854492</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1603469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0254211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4533004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0300140380859</t>
+    <t xml:space="preserve">47.4392929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.160343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0254173278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.453296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0300178527832</t>
   </si>
   <si>
     <t xml:space="preserve">46.1835479736328</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">47.5881233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5277214050293</t>
+    <t xml:space="preserve">46.527717590332</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
@@ -4022,46 +4022,46 @@
     <t xml:space="preserve">45.430103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2672653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7695579528809</t>
+    <t xml:space="preserve">46.267261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7695617675781</t>
   </si>
   <si>
     <t xml:space="preserve">45.5696296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6115417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9604072570801</t>
+    <t xml:space="preserve">44.6115379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9604110717773</t>
   </si>
   <si>
     <t xml:space="preserve">41.4861259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7373847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9095230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8676109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6163520812988</t>
+    <t xml:space="preserve">39.7373809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9095268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8676147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6163558959961</t>
   </si>
   <si>
     <t xml:space="preserve">40.8070907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1930694580078</t>
+    <t xml:space="preserve">42.1930656433105</t>
   </si>
   <si>
     <t xml:space="preserve">41.2814865112305</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1093521118164</t>
+    <t xml:space="preserve">42.1093482971191</t>
   </si>
   <si>
     <t xml:space="preserve">40.6489639282227</t>
@@ -4070,22 +4070,22 @@
     <t xml:space="preserve">40.0908508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3095016479492</t>
+    <t xml:space="preserve">39.309497833252</t>
   </si>
   <si>
     <t xml:space="preserve">39.8945198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5640754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6018180847168</t>
+    <t xml:space="preserve">38.5640716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">39.819034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6588172912598</t>
+    <t xml:space="preserve">40.658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">42.3572616577148</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801254272461</t>
+    <t xml:space="preserve">43.4801216125488</t>
   </si>
   <si>
     <t xml:space="preserve">43.234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">42.111930847168</t>
+    <t xml:space="preserve">42.1119346618652</t>
   </si>
   <si>
     <t xml:space="preserve">41.2155303955078</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">37.2147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2145652770996</t>
+    <t xml:space="preserve">36.2145614624023</t>
   </si>
   <si>
     <t xml:space="preserve">37.5166969299316</t>
@@ -4130,13 +4130,13 @@
     <t xml:space="preserve">35.0917015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9690361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9973449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312934875488</t>
+    <t xml:space="preserve">34.9690399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9973487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9312973022461</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4151,25 +4151,25 @@
     <t xml:space="preserve">38.394229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4980239868164</t>
+    <t xml:space="preserve">38.4980201721191</t>
   </si>
   <si>
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3751678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8943290710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0547370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396598815918</t>
+    <t xml:space="preserve">38.0639762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3751640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8943252563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0547332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396560668945</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">40.1587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3474349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.753173828125</t>
+    <t xml:space="preserve">40.3474388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7531776428223</t>
   </si>
   <si>
     <t xml:space="preserve">41.1494789123535</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">39.6586265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7248687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9990882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9239883422852</t>
+    <t xml:space="preserve">40.7248725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9990921020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9239921569824</t>
   </si>
   <si>
     <t xml:space="preserve">45.9806060791016</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5278854370117</t>
+    <t xml:space="preserve">45.3389701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5278816223145</t>
   </si>
   <si>
     <t xml:space="preserve">46.5184440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4995765686035</t>
+    <t xml:space="preserve">46.4995727539062</t>
   </si>
   <si>
     <t xml:space="preserve">45.8579406738281</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">46.7165946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9524917602539</t>
+    <t xml:space="preserve">46.9524879455566</t>
   </si>
   <si>
     <t xml:space="preserve">46.5939331054688</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">46.0089149475098</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7543411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1315803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0273971557617</t>
+    <t xml:space="preserve">46.754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0273933410645</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2163047790527</t>
+    <t xml:space="preserve">45.2163009643555</t>
   </si>
   <si>
     <t xml:space="preserve">45.2729225158691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0460739135742</t>
+    <t xml:space="preserve">43.046070098877</t>
   </si>
   <si>
     <t xml:space="preserve">42.1496734619141</t>
@@ -4280,25 +4280,25 @@
     <t xml:space="preserve">42.3100814819336</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1213684082031</t>
+    <t xml:space="preserve">42.1213645935059</t>
   </si>
   <si>
     <t xml:space="preserve">41.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2251625061035</t>
+    <t xml:space="preserve">42.2251586914062</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1777839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3948097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6967506408691</t>
+    <t xml:space="preserve">41.1777877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3948059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6967544555664</t>
   </si>
   <si>
     <t xml:space="preserve">42.4704895019531</t>
@@ -4307,25 +4307,25 @@
     <t xml:space="preserve">42.998893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7158241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9230194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4891700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8005485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.461051940918</t>
+    <t xml:space="preserve">42.0175743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.923023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4891662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8005523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4610557556152</t>
   </si>
   <si>
     <t xml:space="preserve">39.9511337280273</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">39.2623252868652</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6210746765137</t>
+    <t xml:space="preserve">40.6210784912109</t>
   </si>
   <si>
     <t xml:space="preserve">40.5644645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0645561218262</t>
+    <t xml:space="preserve">41.0645599365234</t>
   </si>
   <si>
     <t xml:space="preserve">39.8095970153809</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703903198242</t>
+    <t xml:space="preserve">41.9703941345215</t>
   </si>
   <si>
     <t xml:space="preserve">41.5174751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8665962219238</t>
+    <t xml:space="preserve">41.8666000366211</t>
   </si>
   <si>
     <t xml:space="preserve">43.0271987915039</t>
@@ -4373,10 +4373,10 @@
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252540588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8009338378906</t>
+    <t xml:space="preserve">42.7252578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8009376525879</t>
   </si>
   <si>
     <t xml:space="preserve">44.0557022094727</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">43.7160186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6690330505371</t>
+    <t xml:space="preserve">44.6690292358398</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4397,31 +4397,31 @@
     <t xml:space="preserve">46.1693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6692276000977</t>
+    <t xml:space="preserve">45.6692237854004</t>
   </si>
   <si>
     <t xml:space="preserve">43.7443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">42.734691619873</t>
+    <t xml:space="preserve">42.7346954345703</t>
   </si>
   <si>
     <t xml:space="preserve">41.2249641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6873207092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0173797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8756484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8290481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9422798156738</t>
+    <t xml:space="preserve">41.6873168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0173835754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8756446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8290519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9422760009766</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7732124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6131896972656</t>
+    <t xml:space="preserve">46.7732086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6131935119629</t>
   </si>
   <si>
     <t xml:space="preserve">47.6129951477051</t>
@@ -4448,22 +4448,22 @@
     <t xml:space="preserve">47.0657196044922</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0185432434082</t>
+    <t xml:space="preserve">47.0185394287109</t>
   </si>
   <si>
     <t xml:space="preserve">45.6314811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6031761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5654335021973</t>
+    <t xml:space="preserve">45.6031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5654296875</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2917938232422</t>
+    <t xml:space="preserve">45.2917900085449</t>
   </si>
   <si>
     <t xml:space="preserve">44.8200035095215</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">45.546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5937385559082</t>
+    <t xml:space="preserve">45.5937347412109</t>
   </si>
   <si>
     <t xml:space="preserve">44.7539520263672</t>
@@ -4484,46 +4484,46 @@
     <t xml:space="preserve">45.7447090148926</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5844955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2544364929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6316757202148</t>
+    <t xml:space="preserve">46.5844917297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2544403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7452926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6316719055176</t>
   </si>
   <si>
     <t xml:space="preserve">46.4146499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7918891906738</t>
+    <t xml:space="preserve">45.7918853759766</t>
   </si>
   <si>
     <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.150447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3861503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6788558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3110466003418</t>
+    <t xml:space="preserve">46.1504516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3861465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6788520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3110504150391</t>
   </si>
   <si>
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5563812255859</t>
+    <t xml:space="preserve">47.8017120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5563850402832</t>
   </si>
   <si>
     <t xml:space="preserve">48.5565757751465</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">49.7077407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9717483520508</t>
+    <t xml:space="preserve">48.971752166748</t>
   </si>
   <si>
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814796447754</t>
+    <t xml:space="preserve">50.4814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">51.8779754638672</t>
@@ -4550,34 +4550,34 @@
     <t xml:space="preserve">52.3497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8781661987305</t>
+    <t xml:space="preserve">52.8781700134277</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9157180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0480117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3310890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1046295166016</t>
+    <t xml:space="preserve">51.915714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0480155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3310852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1046257019043</t>
   </si>
   <si>
     <t xml:space="preserve">53.2555999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5199928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0859489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9727210998535</t>
+    <t xml:space="preserve">54.5199966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0859527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9727172851562</t>
   </si>
   <si>
     <t xml:space="preserve">53.8406181335449</t>
@@ -4586,64 +4586,64 @@
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4446983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1991806030273</t>
+    <t xml:space="preserve">55.4447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1991767883301</t>
   </si>
   <si>
     <t xml:space="preserve">54.0293350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4254455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1987915039062</t>
+    <t xml:space="preserve">53.4254417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.198787689209</t>
   </si>
   <si>
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9349784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8785514831543</t>
+    <t xml:space="preserve">53.5009307861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9349746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">54.444507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.350341796875</t>
+    <t xml:space="preserve">54.4445114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3503456115723</t>
   </si>
   <si>
     <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9729080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.46337890625</t>
+    <t xml:space="preserve">54.9729118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4633827209473</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106544494629</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3316650390625</t>
+    <t xml:space="preserve">54.5388679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3316688537598</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3507308959961</t>
+    <t xml:space="preserve">57.3507347106934</t>
   </si>
   <si>
     <t xml:space="preserve">57.1431465148926</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">56.4071502685547</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8789405822754</t>
+    <t xml:space="preserve">56.8789443969727</t>
   </si>
   <si>
     <t xml:space="preserve">54.8974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0676574707031</t>
+    <t xml:space="preserve">57.0676612854004</t>
   </si>
   <si>
     <t xml:space="preserve">55.2748565673828</t>
@@ -4679,13 +4679,13 @@
     <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5017013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546241760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1433372497559</t>
+    <t xml:space="preserve">57.5017051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1433410644531</t>
   </si>
   <si>
     <t xml:space="preserve">57.2186317443848</t>
@@ -4694,19 +4694,19 @@
     <t xml:space="preserve">57.2752456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9170761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8982009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9550094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1059875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0116271972656</t>
+    <t xml:space="preserve">58.9170722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8981971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9550132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1059837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0116233825684</t>
   </si>
   <si>
     <t xml:space="preserve">60.6155128479004</t>
@@ -4715,22 +4715,22 @@
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417816162109</t>
+    <t xml:space="preserve">59.8417778015137</t>
   </si>
   <si>
     <t xml:space="preserve">59.4266052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0686225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.219596862793</t>
+    <t xml:space="preserve">62.0686264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2196006774902</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8044204711914</t>
+    <t xml:space="preserve">61.8044242858887</t>
   </si>
   <si>
     <t xml:space="preserve">62.2007255554199</t>
@@ -4739,55 +4739,55 @@
     <t xml:space="preserve">63.1443061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4085121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8614311218262</t>
+    <t xml:space="preserve">63.4085006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8614273071289</t>
   </si>
   <si>
     <t xml:space="preserve">63.7293281555176</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9935264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3707695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896369934082</t>
+    <t xml:space="preserve">63.993522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3707733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896331787109</t>
   </si>
   <si>
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5028648376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.993335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4649238586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8987808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0122108459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9178504943848</t>
+    <t xml:space="preserve">63.5028686523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9933395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4649314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8987846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.01220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9178466796875</t>
   </si>
   <si>
     <t xml:space="preserve">61.5024795532227</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5968360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8608474731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7287483215332</t>
+    <t xml:space="preserve">61.5968322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8608436584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7287445068359</t>
   </si>
   <si>
     <t xml:space="preserve">62.1307678222656</t>
@@ -6504,6 +6504,9 @@
   </si>
   <si>
     <t xml:space="preserve">57.2400016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5200004577637</t>
   </si>
 </sst>
 </file>
@@ -72752,7 +72755,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6911226852</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>843046</v>
@@ -72773,6 +72776,32 @@
         <v>2163</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6910648148</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>1584812</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>57.6399993896484</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>56.3400001525879</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>57.439998626709</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>56.5200004577637</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765724182129</t>
+    <t xml:space="preserve">11.0765733718872</t>
   </si>
   <si>
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8452529907227</t>
+    <t xml:space="preserve">10.9698095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.845253944397</t>
   </si>
   <si>
     <t xml:space="preserve">10.8986358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9876050949097</t>
+    <t xml:space="preserve">10.9876041412354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1744375228882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9573593139648</t>
+    <t xml:space="preserve">11.9573612213135</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769296646118</t>
+    <t xml:space="preserve">11.4769306182861</t>
   </si>
   <si>
     <t xml:space="preserve">11.1566438674927</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">11.5481052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349395751953</t>
+    <t xml:space="preserve">11.7349405288696</t>
   </si>
   <si>
     <t xml:space="preserve">11.4057550430298</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">12.1175031661987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0018434524536</t>
+    <t xml:space="preserve">12.0018444061279</t>
   </si>
   <si>
     <t xml:space="preserve">12.1264009475708</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">12.0997104644775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7260427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908117294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9484624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950815200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9128751754761</t>
+    <t xml:space="preserve">11.7260417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908136367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9484634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616281509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9128742218018</t>
   </si>
   <si>
     <t xml:space="preserve">11.4146537780762</t>
@@ -119,55 +119,55 @@
     <t xml:space="preserve">11.2723035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.254508972168</t>
+    <t xml:space="preserve">11.0409860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2545080184937</t>
   </si>
   <si>
     <t xml:space="preserve">10.9431200027466</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2989950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6726598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8772878646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2509574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2687482833862</t>
+    <t xml:space="preserve">11.2989940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8772897720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4110984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2509565353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2687492370605</t>
   </si>
   <si>
     <t xml:space="preserve">12.4022026062012</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7972164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1975746154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7402820587158</t>
+    <t xml:space="preserve">11.7972183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1975755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7402830123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.9627027511597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7669734954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2118148803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075450897217</t>
+    <t xml:space="preserve">12.7669744491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2118167877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.407546043396</t>
   </si>
   <si>
     <t xml:space="preserve">13.478720664978</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">13.4520301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6210718154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7100372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363704681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0427742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605697631836</t>
+    <t xml:space="preserve">13.6210708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7100391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363695144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0427761077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0605707168579</t>
   </si>
   <si>
     <t xml:space="preserve">12.9893941879272</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0160837173462</t>
+    <t xml:space="preserve">13.0160856246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.9449100494385</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">13.0961570739746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5143060684204</t>
+    <t xml:space="preserve">13.5143070220947</t>
   </si>
   <si>
     <t xml:space="preserve">13.1228475570679</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">12.7936639785767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8292503356934</t>
+    <t xml:space="preserve">12.829249382019</t>
   </si>
   <si>
     <t xml:space="preserve">13.0338773727417</t>
@@ -242,28 +242,28 @@
     <t xml:space="preserve">13.202919960022</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3897523880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1673316955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869020462036</t>
+    <t xml:space="preserve">13.3897514343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1673307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869039535522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5089654922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5979318618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9716005325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.998291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3185768127441</t>
+    <t xml:space="preserve">12.5979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9715995788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9982900619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3185777664185</t>
   </si>
   <si>
     <t xml:space="preserve">13.9324598312378</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">14.0570154190063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9947376251221</t>
+    <t xml:space="preserve">13.9947385787964</t>
   </si>
   <si>
     <t xml:space="preserve">13.9502534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6388635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676889419556</t>
+    <t xml:space="preserve">13.6388645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676908493042</t>
   </si>
   <si>
     <t xml:space="preserve">13.3630619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3452682495117</t>
+    <t xml:space="preserve">13.3452701568604</t>
   </si>
   <si>
     <t xml:space="preserve">13.2285184860229</t>
@@ -296,61 +296,61 @@
     <t xml:space="preserve">13.5608043670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4440546035767</t>
+    <t xml:space="preserve">13.444055557251</t>
   </si>
   <si>
     <t xml:space="preserve">13.2734222412109</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4709968566895</t>
+    <t xml:space="preserve">13.4709987640381</t>
   </si>
   <si>
     <t xml:space="preserve">13.5967264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4620161056519</t>
+    <t xml:space="preserve">13.4620151519775</t>
   </si>
   <si>
     <t xml:space="preserve">13.4979381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3632297515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3183250427246</t>
+    <t xml:space="preserve">13.3632287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3183259963989</t>
   </si>
   <si>
     <t xml:space="preserve">13.6685724258423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7314357757568</t>
+    <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
     <t xml:space="preserve">13.7404184341431</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3003644943237</t>
+    <t xml:space="preserve">13.3003664016724</t>
   </si>
   <si>
     <t xml:space="preserve">13.1566734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7256011962891</t>
+    <t xml:space="preserve">12.7256031036377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2105579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8603115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8122625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6775512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8571653366089</t>
+    <t xml:space="preserve">12.860312461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8122634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6775522232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8571672439575</t>
   </si>
   <si>
     <t xml:space="preserve">14.2253732681274</t>
@@ -362,34 +362,34 @@
     <t xml:space="preserve">12.3035097122192</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6986589431763</t>
+    <t xml:space="preserve">12.6986598968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.1476936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9950218200684</t>
+    <t xml:space="preserve">12.9950227737427</t>
   </si>
   <si>
     <t xml:space="preserve">12.6178331375122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8513307571411</t>
+    <t xml:space="preserve">12.8513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">12.8782730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9680795669556</t>
+    <t xml:space="preserve">12.9680786132812</t>
   </si>
   <si>
     <t xml:space="preserve">12.9231767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1746349334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9590978622437</t>
+    <t xml:space="preserve">13.1746368408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9590997695923</t>
   </si>
   <si>
     <t xml:space="preserve">12.9501180648804</t>
@@ -401,16 +401,16 @@
     <t xml:space="preserve">13.3452672958374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8302240371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1714878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.063720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3690643310547</t>
+    <t xml:space="preserve">13.8302230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1714887619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0637216567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3690633773804</t>
   </si>
   <si>
     <t xml:space="preserve">14.0816831588745</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">13.9559526443481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5069208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6057062149048</t>
+    <t xml:space="preserve">13.5069189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6057071685791</t>
   </si>
   <si>
     <t xml:space="preserve">13.9290113449097</t>
@@ -437,43 +437,43 @@
     <t xml:space="preserve">13.8481855392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0457592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9918746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9200305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7673587799072</t>
+    <t xml:space="preserve">14.0457582473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9918766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9200296401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7673597335815</t>
   </si>
   <si>
     <t xml:space="preserve">14.0008563995361</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7583789825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6955137252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877456665039</t>
+    <t xml:space="preserve">13.7583780288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
     <t xml:space="preserve">13.524881362915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3542470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4171133041382</t>
+    <t xml:space="preserve">13.3542461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4171123504639</t>
   </si>
   <si>
     <t xml:space="preserve">13.5158996582031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7224569320679</t>
+    <t xml:space="preserve">13.7224559783936</t>
   </si>
   <si>
     <t xml:space="preserve">13.5338611602783</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">13.9110488891602</t>
   </si>
   <si>
-    <t xml:space="preserve">13.614688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.009838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4530363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6506109237671</t>
+    <t xml:space="preserve">13.6146869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0098361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4530353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6506090164185</t>
   </si>
   <si>
     <t xml:space="preserve">13.6416282653809</t>
@@ -506,43 +506,43 @@
     <t xml:space="preserve">13.7853193283081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4799785614014</t>
+    <t xml:space="preserve">13.4799795150757</t>
   </si>
   <si>
     <t xml:space="preserve">13.839204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0996427536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8930883407593</t>
+    <t xml:space="preserve">14.0996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8930892944336</t>
   </si>
   <si>
     <t xml:space="preserve">13.9649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8751268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7943019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6236686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.399151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3901700973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4889583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3362874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6326484680176</t>
+    <t xml:space="preserve">13.8751258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7943000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.62366771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3991527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3901720046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4889574050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3362884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6326503753662</t>
   </si>
   <si>
     <t xml:space="preserve">13.3273077011108</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">13.7763395309448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8661470413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0547409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6474637985229</t>
+    <t xml:space="preserve">13.8661451339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0547389984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6474647521973</t>
   </si>
   <si>
     <t xml:space="preserve">14.6384830474854</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">14.9168844223022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0964956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0426149368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989238739014</t>
+    <t xml:space="preserve">15.0964984893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.04261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989219665527</t>
   </si>
   <si>
     <t xml:space="preserve">14.548677444458</t>
@@ -581,58 +581,58 @@
     <t xml:space="preserve">14.7372713088989</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7731943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8719797134399</t>
+    <t xml:space="preserve">14.7731962203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8719806671143</t>
   </si>
   <si>
     <t xml:space="preserve">14.7911529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6564445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.683388710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013483047485</t>
+    <t xml:space="preserve">14.6564455032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6833868026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013492584229</t>
   </si>
   <si>
     <t xml:space="preserve">14.8450384140015</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0875158309937</t>
+    <t xml:space="preserve">15.087513923645</t>
   </si>
   <si>
     <t xml:space="preserve">14.9707698822021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7103290557861</t>
+    <t xml:space="preserve">14.7103281021118</t>
   </si>
   <si>
     <t xml:space="preserve">14.6744070053101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9528064727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377632141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736852645874</t>
+    <t xml:space="preserve">14.9528074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377641677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736833572388</t>
   </si>
   <si>
     <t xml:space="preserve">15.6892213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7251443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4826650619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790279388428</t>
+    <t xml:space="preserve">15.7251434326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4826679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790288925171</t>
   </si>
   <si>
     <t xml:space="preserve">16.0933532714844</t>
@@ -644,61 +644,61 @@
     <t xml:space="preserve">16.2011184692383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1921424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2460231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113128662109</t>
+    <t xml:space="preserve">16.1921405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.246021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113147735596</t>
   </si>
   <si>
     <t xml:space="preserve">16.0304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9855813980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6353349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9316987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766054153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9586410522461</t>
+    <t xml:space="preserve">15.9855794906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6353387832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9316997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9766025543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.958643913269</t>
   </si>
   <si>
     <t xml:space="preserve">15.9406805038452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.886794090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1741771697998</t>
+    <t xml:space="preserve">15.8867950439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1741790771484</t>
   </si>
   <si>
     <t xml:space="preserve">16.1023330688477</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0484504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8957777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0991878509521</t>
+    <t xml:space="preserve">16.0484485626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8957757949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9676237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831569671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0991859436035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2608375549316</t>
@@ -710,37 +710,37 @@
     <t xml:space="preserve">17.296760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3326835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5122928619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5661811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.65598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6021003723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8535594940186</t>
+    <t xml:space="preserve">17.3326816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5122947692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5661792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6021041870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">18.0062313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1768646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8805046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0601177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0870571136475</t>
+    <t xml:space="preserve">18.1768665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8805027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.060115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0870552062988</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205547332764</t>
@@ -749,55 +749,55 @@
     <t xml:space="preserve">18.266674041748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4103660583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678829193115</t>
+    <t xml:space="preserve">18.4103584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678848266602</t>
   </si>
   <si>
     <t xml:space="preserve">18.2756538391113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4373035430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9312400817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2276039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2365856170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2006587982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.479061126709</t>
+    <t xml:space="preserve">18.4373054504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9312419891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2276020050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2365837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2006607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4790630340576</t>
   </si>
   <si>
     <t xml:space="preserve">19.5598888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1108551025391</t>
+    <t xml:space="preserve">19.1108570098877</t>
   </si>
   <si>
     <t xml:space="preserve">19.2096405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3174076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5329456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610977172852</t>
+    <t xml:space="preserve">19.3174114227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5329437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6945991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610996246338</t>
   </si>
   <si>
     <t xml:space="preserve">19.5778484344482</t>
@@ -806,37 +806,37 @@
     <t xml:space="preserve">19.5149841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.188533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3501892089844</t>
+    <t xml:space="preserve">20.1885356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310111999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3501873016357</t>
   </si>
   <si>
     <t xml:space="preserve">20.6645088195801</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8351440429688</t>
+    <t xml:space="preserve">20.8351421356201</t>
   </si>
   <si>
     <t xml:space="preserve">21.1135444641113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4759140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.78440284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9999389648438</t>
+    <t xml:space="preserve">20.4759120941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7844047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9999408721924</t>
   </si>
   <si>
     <t xml:space="preserve">19.8921699523926</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9819793701172</t>
+    <t xml:space="preserve">19.9819774627686</t>
   </si>
   <si>
     <t xml:space="preserve">19.874210357666</t>
@@ -848,100 +848,100 @@
     <t xml:space="preserve">19.389253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5509090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.650520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7229633331299</t>
+    <t xml:space="preserve">19.5509071350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6505184173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7229614257812</t>
   </si>
   <si>
     <t xml:space="preserve">19.6052398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4875183105469</t>
+    <t xml:space="preserve">19.4875202178955</t>
   </si>
   <si>
     <t xml:space="preserve">20.0127391815186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2339649200439</t>
+    <t xml:space="preserve">19.2339611053467</t>
   </si>
   <si>
     <t xml:space="preserve">19.6324081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7048530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.279239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9260749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0075721740723</t>
+    <t xml:space="preserve">19.7048511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2792415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9260768890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0075740814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.9713535308838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.080020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5819644927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1252975463867</t>
+    <t xml:space="preserve">19.0800189971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5819664001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1252956390381</t>
   </si>
   <si>
     <t xml:space="preserve">19.0437965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3426303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2249069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6142959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2158527374268</t>
+    <t xml:space="preserve">19.3426265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2249050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.614294052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2158508300781</t>
   </si>
   <si>
     <t xml:space="preserve">19.1524639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1434059143066</t>
+    <t xml:space="preserve">19.1434078216553</t>
   </si>
   <si>
     <t xml:space="preserve">19.3245162963867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.944185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.373685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5638542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6362991333008</t>
+    <t xml:space="preserve">18.9441871643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3736877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5638523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6363010406494</t>
   </si>
   <si>
     <t xml:space="preserve">18.6000785827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7359085083008</t>
+    <t xml:space="preserve">18.8083534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7359066009521</t>
   </si>
   <si>
     <t xml:space="preserve">18.6091289520264</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">19.1071834564209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2882957458496</t>
+    <t xml:space="preserve">19.2882919311523</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4060173034668</t>
+    <t xml:space="preserve">19.4060192108154</t>
   </si>
   <si>
     <t xml:space="preserve">19.4512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4331836700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2701873779297</t>
+    <t xml:space="preserve">19.4331855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
     <t xml:space="preserve">19.1977424621582</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">20.2391262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4655170440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5560741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3568477630615</t>
+    <t xml:space="preserve">20.4655151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5560722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3568515777588</t>
   </si>
   <si>
     <t xml:space="preserve">20.2572383880615</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">20.3930702209473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3296852111816</t>
+    <t xml:space="preserve">20.329683303833</t>
   </si>
   <si>
     <t xml:space="preserve">20.3749599456787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4021282196045</t>
+    <t xml:space="preserve">20.4021263122559</t>
   </si>
   <si>
     <t xml:space="preserve">20.3477954864502</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">20.8458499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1446800231934</t>
+    <t xml:space="preserve">21.144681930542</t>
   </si>
   <si>
     <t xml:space="preserve">21.5431270599365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.380126953125</t>
+    <t xml:space="preserve">21.3801250457764</t>
   </si>
   <si>
     <t xml:space="preserve">21.3439025878906</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">21.4254035949707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3710689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2805156707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2080707550049</t>
+    <t xml:space="preserve">21.3710708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2805137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2080688476562</t>
   </si>
   <si>
     <t xml:space="preserve">20.8730144500732</t>
@@ -1034,61 +1034,61 @@
     <t xml:space="preserve">21.2714595794678</t>
   </si>
   <si>
-    <t xml:space="preserve">21.615571975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8962898254395</t>
+    <t xml:space="preserve">21.6155700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8962936401367</t>
   </si>
   <si>
     <t xml:space="preserve">21.7423458099365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7966785430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9959030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.158899307251</t>
+    <t xml:space="preserve">21.7966804504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9959049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1589012145996</t>
   </si>
   <si>
     <t xml:space="preserve">22.4305686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3671798706055</t>
+    <t xml:space="preserve">22.3671779632568</t>
   </si>
   <si>
     <t xml:space="preserve">22.5935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6116771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5030155181885</t>
+    <t xml:space="preserve">22.6116790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5030117034912</t>
   </si>
   <si>
     <t xml:space="preserve">22.2404022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3852920532227</t>
+    <t xml:space="preserve">22.385290145874</t>
   </si>
   <si>
     <t xml:space="preserve">22.2313442230225</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2132377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2494583129883</t>
+    <t xml:space="preserve">22.2132339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2494564056396</t>
   </si>
   <si>
     <t xml:space="preserve">21.959680557251</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8238468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0683479309082</t>
+    <t xml:space="preserve">21.823844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0683460235596</t>
   </si>
   <si>
     <t xml:space="preserve">22.1136245727539</t>
@@ -1097,52 +1097,52 @@
     <t xml:space="preserve">22.1407909393311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8419570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7514038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4706783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.149845123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0592918395996</t>
+    <t xml:space="preserve">21.8419589996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7513999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1498470306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2766227722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.059289932251</t>
   </si>
   <si>
     <t xml:space="preserve">22.285680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3490695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.394344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9868469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.439624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5573425292969</t>
+    <t xml:space="preserve">22.3490676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3943462371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9868488311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4396228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5573444366455</t>
   </si>
   <si>
     <t xml:space="preserve">22.3581237792969</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1226787567139</t>
+    <t xml:space="preserve">22.1226806640625</t>
   </si>
   <si>
     <t xml:space="preserve">22.0774002075195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0049591064453</t>
+    <t xml:space="preserve">22.0049571990967</t>
   </si>
   <si>
     <t xml:space="preserve">21.9415683746338</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">21.8510131835938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7695140838623</t>
+    <t xml:space="preserve">21.7695121765137</t>
   </si>
   <si>
     <t xml:space="preserve">20.6466255187988</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0631828308105</t>
+    <t xml:space="preserve">21.0631809234619</t>
   </si>
   <si>
     <t xml:space="preserve">21.0088481903076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.673791885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7734069824219</t>
+    <t xml:space="preserve">20.6737937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7734050750732</t>
   </si>
   <si>
     <t xml:space="preserve">20.6556835174561</t>
@@ -1178,199 +1178,199 @@
     <t xml:space="preserve">21.0903491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1356296539307</t>
+    <t xml:space="preserve">21.135627746582</t>
   </si>
   <si>
     <t xml:space="preserve">20.8277378082275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8549060821533</t>
+    <t xml:space="preserve">20.8549041748047</t>
   </si>
   <si>
     <t xml:space="preserve">20.8005714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8820724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4344596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4163475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9506244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4667892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5120677947998</t>
+    <t xml:space="preserve">20.8820705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4344577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4163455963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.950626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4667911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5120697021484</t>
   </si>
   <si>
     <t xml:space="preserve">22.8833446502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3219013214111</t>
+    <t xml:space="preserve">22.3219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">22.8290100097656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9014587402344</t>
+    <t xml:space="preserve">22.9014568328857</t>
   </si>
   <si>
     <t xml:space="preserve">22.8109016418457</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6530666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9066219329834</t>
+    <t xml:space="preserve">23.0916213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6530647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9066200256348</t>
   </si>
   <si>
     <t xml:space="preserve">23.6168441772461</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3632888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1821746826172</t>
+    <t xml:space="preserve">23.3632869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">23.6349563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4900684356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.544397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2002906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8199558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7837333679199</t>
+    <t xml:space="preserve">23.4900646209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5443992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.200288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8199577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7837371826172</t>
   </si>
   <si>
     <t xml:space="preserve">23.0372886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8160629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3412857055664</t>
+    <t xml:space="preserve">23.8160648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.341287612915</t>
   </si>
   <si>
     <t xml:space="preserve">24.4861755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2507305145264</t>
+    <t xml:space="preserve">24.2507286071777</t>
   </si>
   <si>
     <t xml:space="preserve">24.3775081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5042839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5223979949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2869510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0333976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.214506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5625095367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4628982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.359395980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.290843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0424537658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6582298278809</t>
+    <t xml:space="preserve">24.5042858123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5223960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2869529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1148986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0333995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2145042419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5625133514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4629001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3593978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2908458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0424518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6582279205322</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7630081176758</t>
+    <t xml:space="preserve">25.7630062103271</t>
   </si>
   <si>
     <t xml:space="preserve">25.4279499053955</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5637817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5818939208984</t>
+    <t xml:space="preserve">25.5637836456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5818958282471</t>
   </si>
   <si>
     <t xml:space="preserve">25.4641742706299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3917293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6362285614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1342811584473</t>
+    <t xml:space="preserve">25.391731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6362266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1342830657959</t>
   </si>
   <si>
     <t xml:space="preserve">25.9893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3192844390869</t>
+    <t xml:space="preserve">25.3192825317383</t>
   </si>
   <si>
     <t xml:space="preserve">25.264949798584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.699613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728397369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2157821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4059505462646</t>
+    <t xml:space="preserve">25.6996173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.215784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.405948638916</t>
   </si>
   <si>
     <t xml:space="preserve">26.5055618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6685600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4874477386475</t>
+    <t xml:space="preserve">26.6685619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4874496459961</t>
   </si>
   <si>
     <t xml:space="preserve">26.8134479522705</t>
@@ -1379,52 +1379,52 @@
     <t xml:space="preserve">26.7500591278076</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9583377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4654483795166</t>
+    <t xml:space="preserve">26.9583358764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.465446472168</t>
   </si>
   <si>
     <t xml:space="preserve">27.9453926086426</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5741157531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7190036773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6737270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9816131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7655544281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4304981231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8108291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549415588379</t>
+    <t xml:space="preserve">27.5741119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7190055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6737251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9182224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9816112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7655563354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4305000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.810827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549434661865</t>
   </si>
   <si>
     <t xml:space="preserve">30.2364406585693</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9104442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5624370574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250560760498</t>
+    <t xml:space="preserve">29.9104385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.562442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250522613525</t>
   </si>
   <si>
     <t xml:space="preserve">30.4809417724609</t>
@@ -1433,52 +1433,52 @@
     <t xml:space="preserve">31.2053833007812</t>
   </si>
   <si>
-    <t xml:space="preserve">31.902660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7124938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0203819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9207763671875</t>
+    <t xml:space="preserve">31.9026565551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7124919891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.020378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9207744598389</t>
   </si>
   <si>
     <t xml:space="preserve">32.618049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6904907226562</t>
+    <t xml:space="preserve">32.690486907959</t>
   </si>
   <si>
     <t xml:space="preserve">32.9621620178223</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4602165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4110450744629</t>
+    <t xml:space="preserve">33.4602127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4110412597656</t>
   </si>
   <si>
     <t xml:space="preserve">33.0527153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3011016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0346069335938</t>
+    <t xml:space="preserve">32.3011054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0346031188965</t>
   </si>
   <si>
     <t xml:space="preserve">33.0798797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3153228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6866035461426</t>
+    <t xml:space="preserve">33.3153305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6865997314453</t>
   </si>
   <si>
     <t xml:space="preserve">34.0759925842285</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">34.0941047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.392936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2351036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6788215637207</t>
+    <t xml:space="preserve">34.3929328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2350959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.678825378418</t>
   </si>
   <si>
     <t xml:space="preserve">35.4416961669922</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">34.4749336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7270660400391</t>
+    <t xml:space="preserve">33.7270622253418</t>
   </si>
   <si>
     <t xml:space="preserve">34.5022926330566</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8065032958984</t>
+    <t xml:space="preserve">35.8065071105957</t>
   </si>
   <si>
     <t xml:space="preserve">36.0071563720703</t>
@@ -1523,31 +1523,31 @@
     <t xml:space="preserve">35.8156280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8429908752441</t>
+    <t xml:space="preserve">35.8429832458496</t>
   </si>
   <si>
     <t xml:space="preserve">36.3354835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">37.703540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2931251525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2534027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2748756408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5940971374512</t>
+    <t xml:space="preserve">37.7035369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2533988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2748832702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5940933227539</t>
   </si>
   <si>
     <t xml:space="preserve">37.9041900634766</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4696502685547</t>
+    <t xml:space="preserve">38.4696464538574</t>
   </si>
   <si>
     <t xml:space="preserve">38.3602027893066</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">36.3446044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2807655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0892333984375</t>
+    <t xml:space="preserve">36.28076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0892372131348</t>
   </si>
   <si>
     <t xml:space="preserve">35.4143333435059</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">35.3960914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5146560668945</t>
+    <t xml:space="preserve">35.5146598815918</t>
   </si>
   <si>
     <t xml:space="preserve">35.1042404174805</t>
@@ -1583,70 +1583,70 @@
     <t xml:space="preserve">35.5693740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3504867553711</t>
+    <t xml:space="preserve">35.3504829406738</t>
   </si>
   <si>
     <t xml:space="preserve">34.5205307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9550704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.745304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2925224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0586357116699</t>
+    <t xml:space="preserve">33.9550743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7453079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2925262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0586318969727</t>
   </si>
   <si>
     <t xml:space="preserve">34.1830825805664</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8397521972656</t>
+    <t xml:space="preserve">34.8397483825684</t>
   </si>
   <si>
     <t xml:space="preserve">35.5967330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1224746704102</t>
+    <t xml:space="preserve">35.1224784851074</t>
   </si>
   <si>
     <t xml:space="preserve">35.6240997314453</t>
   </si>
   <si>
-    <t xml:space="preserve">35.469051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3869667053223</t>
+    <t xml:space="preserve">35.4690551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3869705200195</t>
   </si>
   <si>
     <t xml:space="preserve">35.241039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1621971130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8853492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6938209533691</t>
+    <t xml:space="preserve">36.1622009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8853530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6938247680664</t>
   </si>
   <si>
     <t xml:space="preserve">33.8091506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4019737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2013244628906</t>
+    <t xml:space="preserve">34.4019775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2013282775879</t>
   </si>
   <si>
     <t xml:space="preserve">33.4169692993164</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2651710510254</t>
+    <t xml:space="preserve">34.2651672363281</t>
   </si>
   <si>
     <t xml:space="preserve">34.3746070861816</t>
@@ -1658,34 +1658,34 @@
     <t xml:space="preserve">34.7303047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6208572387695</t>
+    <t xml:space="preserve">34.6208610534668</t>
   </si>
   <si>
     <t xml:space="preserve">34.018913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8215065002441</t>
+    <t xml:space="preserve">34.8215103149414</t>
   </si>
   <si>
     <t xml:space="preserve">34.4840545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7941436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.578498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1530799865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.532886505127</t>
+    <t xml:space="preserve">34.7941474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5784950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.153076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5328903198242</t>
   </si>
   <si>
     <t xml:space="preserve">35.5055389404297</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">33.8365097045898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2834053039551</t>
+    <t xml:space="preserve">34.2834014892578</t>
   </si>
   <si>
     <t xml:space="preserve">34.338134765625</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">34.785026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6117362976074</t>
+    <t xml:space="preserve">33.9824333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6117401123047</t>
   </si>
   <si>
     <t xml:space="preserve">34.4202117919922</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">34.5114135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0827522277832</t>
+    <t xml:space="preserve">34.0827560424805</t>
   </si>
   <si>
     <t xml:space="preserve">34.4110946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6664619445801</t>
+    <t xml:space="preserve">34.6664543151855</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228012084961</t>
@@ -1739,52 +1739,52 @@
     <t xml:space="preserve">34.9400749206543</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9791946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300304412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4593315124512</t>
+    <t xml:space="preserve">32.9791984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300323486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4593353271484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9388809204102</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5284633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2001323699951</t>
+    <t xml:space="preserve">28.5284652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2001304626465</t>
   </si>
   <si>
     <t xml:space="preserve">27.6529121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2639713287354</t>
+    <t xml:space="preserve">28.263973236084</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4555015563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7258720397949</t>
+    <t xml:space="preserve">28.4555034637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7258739471436</t>
   </si>
   <si>
     <t xml:space="preserve">27.7988357543945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6587924957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2698535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5708274841309</t>
+    <t xml:space="preserve">26.6587905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2698516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5708255767822</t>
   </si>
   <si>
     <t xml:space="preserve">27.1786499023438</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">29.5499458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1942462921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1304092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6926288604736</t>
+    <t xml:space="preserve">29.1942481994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.97536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.130407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.692626953125</t>
   </si>
   <si>
     <t xml:space="preserve">27.4522609710693</t>
@@ -1826,34 +1826,34 @@
     <t xml:space="preserve">28.0359630584717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3519401550293</t>
+    <t xml:space="preserve">27.3519382476807</t>
   </si>
   <si>
     <t xml:space="preserve">26.2666149139404</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8503189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8138389587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4340229034424</t>
+    <t xml:space="preserve">26.8503170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8138370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4340209960938</t>
   </si>
   <si>
     <t xml:space="preserve">27.2060127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7317543029785</t>
+    <t xml:space="preserve">26.7317523956299</t>
   </si>
   <si>
     <t xml:space="preserve">26.9141616821289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2483768463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8079566955566</t>
+    <t xml:space="preserve">26.2483730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.807954788208</t>
   </si>
   <si>
     <t xml:space="preserve">26.7682361602783</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">27.3063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5128650665283</t>
+    <t xml:space="preserve">26.512866973877</t>
   </si>
   <si>
     <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4822654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.327220916748</t>
+    <t xml:space="preserve">25.4822635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3272190093994</t>
   </si>
   <si>
     <t xml:space="preserve">25.9565238952637</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">25.6646709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1265697479248</t>
+    <t xml:space="preserve">25.1265716552734</t>
   </si>
   <si>
     <t xml:space="preserve">24.6431922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.172176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7011566162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1448135375977</t>
+    <t xml:space="preserve">25.1721744537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7011547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1448154449463</t>
   </si>
   <si>
     <t xml:space="preserve">25.3454608917236</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">25.5825881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.385181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.59494972229</t>
+    <t xml:space="preserve">26.3851833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5949478149414</t>
   </si>
   <si>
     <t xml:space="preserve">25.3637008666992</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">26.467264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1877708435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356384277344</t>
+    <t xml:space="preserve">27.1877727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356422424316</t>
   </si>
   <si>
     <t xml:space="preserve">28.6014270782471</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">28.1454086303711</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0600852966309</t>
+    <t xml:space="preserve">27.0600872039795</t>
   </si>
   <si>
     <t xml:space="preserve">27.0327262878418</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">27.3336982727051</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4066581726074</t>
+    <t xml:space="preserve">27.4066600799561</t>
   </si>
   <si>
     <t xml:space="preserve">27.6711483001709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8991584777832</t>
+    <t xml:space="preserve">27.8991622924805</t>
   </si>
   <si>
     <t xml:space="preserve">27.3792991638184</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">27.9538803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8809185028076</t>
+    <t xml:space="preserve">27.8809204101562</t>
   </si>
   <si>
     <t xml:space="preserve">28.2366123199463</t>
@@ -1967,73 +1967,73 @@
     <t xml:space="preserve">30.7994289398193</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2007255554199</t>
+    <t xml:space="preserve">31.2007274627686</t>
   </si>
   <si>
     <t xml:space="preserve">30.4437408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6443843841553</t>
+    <t xml:space="preserve">30.6443824768066</t>
   </si>
   <si>
     <t xml:space="preserve">30.9362373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7023448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3284091949463</t>
+    <t xml:space="preserve">31.7023468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3284111022949</t>
   </si>
   <si>
     <t xml:space="preserve">31.8117923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7753067016602</t>
+    <t xml:space="preserve">31.7753105163574</t>
   </si>
   <si>
     <t xml:space="preserve">31.6567440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6476287841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743404388428</t>
+    <t xml:space="preserve">31.6476230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743347167969</t>
   </si>
   <si>
     <t xml:space="preserve">31.9668350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9029922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1557197570801</t>
+    <t xml:space="preserve">31.9029960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1557235717773</t>
   </si>
   <si>
     <t xml:space="preserve">33.7909049987793</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9244689941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8332710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6964645385742</t>
+    <t xml:space="preserve">32.9244728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8332672119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6964683532715</t>
   </si>
   <si>
     <t xml:space="preserve">32.5140571594238</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5778999328613</t>
+    <t xml:space="preserve">32.5779037475586</t>
   </si>
   <si>
     <t xml:space="preserve">32.4319763183594</t>
@@ -2051,52 +2051,52 @@
     <t xml:space="preserve">33.1980857849121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2313270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7388229370117</t>
+    <t xml:space="preserve">32.2313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">32.4410934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7603073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5081787109375</t>
+    <t xml:space="preserve">32.7603034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5081748962402</t>
   </si>
   <si>
     <t xml:space="preserve">33.6085014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">34.128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9277153015137</t>
+    <t xml:space="preserve">34.1283645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9277076721191</t>
   </si>
   <si>
     <t xml:space="preserve">33.8638725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8150291442871</t>
+    <t xml:space="preserve">32.8150253295898</t>
   </si>
   <si>
     <t xml:space="preserve">32.6599884033203</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2163200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2892913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0977630615234</t>
+    <t xml:space="preserve">33.2163238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2892875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0977592468262</t>
   </si>
   <si>
     <t xml:space="preserve">33.4260940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1159973144531</t>
+    <t xml:space="preserve">33.1160011291504</t>
   </si>
   <si>
     <t xml:space="preserve">33.3075294494629</t>
@@ -2111,52 +2111,52 @@
     <t xml:space="preserve">33.061279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3440055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531227111816</t>
+    <t xml:space="preserve">33.3440093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531303405762</t>
   </si>
   <si>
     <t xml:space="preserve">33.2345657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">33.918586730957</t>
+    <t xml:space="preserve">33.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">33.1616058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5505409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4046096801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4443321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9485931396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6873474121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1310043334961</t>
+    <t xml:space="preserve">32.550537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.404613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4443283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9485912322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6873435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1310005187988</t>
   </si>
   <si>
     <t xml:space="preserve">32.5596618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5911712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8363723754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586597442627</t>
+    <t xml:space="preserve">31.5911674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.836368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8586578369141</t>
   </si>
   <si>
     <t xml:space="preserve">32.2552795410156</t>
@@ -2165,31 +2165,31 @@
     <t xml:space="preserve">32.2829475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7848701477051</t>
+    <t xml:space="preserve">31.7848663330078</t>
   </si>
   <si>
     <t xml:space="preserve">30.7887115478516</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6226825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382057189941</t>
+    <t xml:space="preserve">30.6226844787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4382095336914</t>
   </si>
   <si>
     <t xml:space="preserve">30.5581169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1207637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217678070068</t>
+    <t xml:space="preserve">31.1207618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217620849609</t>
   </si>
   <si>
     <t xml:space="preserve">32.0062408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6649646759033</t>
+    <t xml:space="preserve">31.6649589538574</t>
   </si>
   <si>
     <t xml:space="preserve">32.1169166564941</t>
@@ -2198,28 +2198,28 @@
     <t xml:space="preserve">31.7387504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8125400543213</t>
+    <t xml:space="preserve">31.8125419616699</t>
   </si>
   <si>
     <t xml:space="preserve">32.3290672302246</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6518898010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6480522155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7679634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7087821960449</t>
+    <t xml:space="preserve">32.6518936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6480560302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7679672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7087860107422</t>
   </si>
   <si>
     <t xml:space="preserve">34.505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4136199951172</t>
+    <t xml:space="preserve">34.4136276245117</t>
   </si>
   <si>
     <t xml:space="preserve">33.7864112854004</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">33.5189247131348</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2568168640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6811103820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500564575195</t>
+    <t xml:space="preserve">34.2568206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6811141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500602722168</t>
   </si>
   <si>
     <t xml:space="preserve">34.9762687683105</t>
@@ -2255,37 +2255,37 @@
     <t xml:space="preserve">35.2806549072266</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3544425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0961723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4927978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0408363342285</t>
+    <t xml:space="preserve">35.3544464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0961799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4927940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0408325195312</t>
   </si>
   <si>
     <t xml:space="preserve">35.1330718994141</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2253112792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2437553405762</t>
+    <t xml:space="preserve">35.2253074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2437591552734</t>
   </si>
   <si>
     <t xml:space="preserve">35.6588249206543</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6403732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9263076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9908714294434</t>
+    <t xml:space="preserve">35.6403770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9263114929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9908752441406</t>
   </si>
   <si>
     <t xml:space="preserve">35.963207244873</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">34.6903343200684</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2844924926758</t>
+    <t xml:space="preserve">34.2844886779785</t>
   </si>
   <si>
     <t xml:space="preserve">33.4451332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4620418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343738555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309860229492</t>
+    <t xml:space="preserve">31.462043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343700408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309879302979</t>
   </si>
   <si>
     <t xml:space="preserve">32.4120826721191</t>
@@ -2315,25 +2315,25 @@
     <t xml:space="preserve">32.3475151062012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4989356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2314510345459</t>
+    <t xml:space="preserve">31.4989318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2314472198486</t>
   </si>
   <si>
     <t xml:space="preserve">31.7572002410889</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6926307678223</t>
+    <t xml:space="preserve">31.6926326751709</t>
   </si>
   <si>
     <t xml:space="preserve">32.7072372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">31.747974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5542774200439</t>
+    <t xml:space="preserve">31.7479705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5542755126953</t>
   </si>
   <si>
     <t xml:space="preserve">31.3605785369873</t>
@@ -2342,28 +2342,28 @@
     <t xml:space="preserve">31.3052368164062</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4435920715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6465129852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3382873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1684188842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7349090576172</t>
+    <t xml:space="preserve">31.4435939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6465167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3382949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0761871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1684226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7349128723145</t>
   </si>
   <si>
     <t xml:space="preserve">32.5412101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6242218017578</t>
+    <t xml:space="preserve">32.6242256164551</t>
   </si>
   <si>
     <t xml:space="preserve">32.6426696777344</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">31.6372871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4804840087891</t>
+    <t xml:space="preserve">31.4804821014404</t>
   </si>
   <si>
     <t xml:space="preserve">29.2760219573975</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">29.6080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7279815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8478927612305</t>
+    <t xml:space="preserve">29.7279834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6449718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8478908538818</t>
   </si>
   <si>
     <t xml:space="preserve">30.3367500305176</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">29.1376667022705</t>
   </si>
   <si>
-    <t xml:space="preserve">29.617301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0139198303223</t>
+    <t xml:space="preserve">29.6173000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0139179229736</t>
   </si>
   <si>
     <t xml:space="preserve">30.1983947753906</t>
@@ -2423,22 +2423,22 @@
     <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6134605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1945533752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.803316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5450534820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4251461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0285243988037</t>
+    <t xml:space="preserve">30.6134548187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1945514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8033199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5450496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4251480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0285224914551</t>
   </si>
   <si>
     <t xml:space="preserve">30.7241458892822</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">29.6726379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9770240783691</t>
+    <t xml:space="preserve">29.9770221710205</t>
   </si>
   <si>
     <t xml:space="preserve">29.7741031646729</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">29.9678001403809</t>
   </si>
   <si>
-    <t xml:space="preserve">33.362117767334</t>
+    <t xml:space="preserve">33.3621139526367</t>
   </si>
   <si>
     <t xml:space="preserve">32.7441329956055</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">32.4397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5504379272461</t>
+    <t xml:space="preserve">32.5504417419434</t>
   </si>
   <si>
     <t xml:space="preserve">32.310619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2291526794434</t>
+    <t xml:space="preserve">34.2291488647461</t>
   </si>
   <si>
     <t xml:space="preserve">34.7180061340332</t>
@@ -2492,34 +2492,34 @@
     <t xml:space="preserve">34.0077781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6111640930176</t>
+    <t xml:space="preserve">33.6111602783203</t>
   </si>
   <si>
     <t xml:space="preserve">33.7218437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9801139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2199211120605</t>
+    <t xml:space="preserve">33.980110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2199249267578</t>
   </si>
   <si>
     <t xml:space="preserve">34.819465637207</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5243072509766</t>
+    <t xml:space="preserve">34.5243110656738</t>
   </si>
   <si>
     <t xml:space="preserve">36.0462188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1476745605469</t>
+    <t xml:space="preserve">36.1476783752441</t>
   </si>
   <si>
     <t xml:space="preserve">37.0239334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6826515197754</t>
+    <t xml:space="preserve">36.6826553344727</t>
   </si>
   <si>
     <t xml:space="preserve">35.7787322998047</t>
@@ -2531,37 +2531,37 @@
     <t xml:space="preserve">35.8156318664551</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1492156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9240074157715</t>
+    <t xml:space="preserve">38.1492195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9240112304688</t>
   </si>
   <si>
     <t xml:space="preserve">38.545841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8225479125977</t>
+    <t xml:space="preserve">38.8225517272949</t>
   </si>
   <si>
     <t xml:space="preserve">38.093879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8171691894531</t>
+    <t xml:space="preserve">37.8171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">37.7249336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1530570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3006401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0423736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1899566650391</t>
+    <t xml:space="preserve">37.1530609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3006362915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0423774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1899528503418</t>
   </si>
   <si>
     <t xml:space="preserve">37.715705871582</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">37.6234703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4758911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9593696594238</t>
+    <t xml:space="preserve">37.4758949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9593658447266</t>
   </si>
   <si>
     <t xml:space="preserve">37.4389991760254</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">37.9463005065918</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5496788024902</t>
+    <t xml:space="preserve">37.5496826171875</t>
   </si>
   <si>
     <t xml:space="preserve">37.6326904296875</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">38.3613662719727</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4036445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3667488098145</t>
+    <t xml:space="preserve">39.4036483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3667526245117</t>
   </si>
   <si>
     <t xml:space="preserve">39.385196685791</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1399955749512</t>
+    <t xml:space="preserve">38.1399993896484</t>
   </si>
   <si>
     <t xml:space="preserve">37.2914161682129</t>
@@ -2618,31 +2618,31 @@
     <t xml:space="preserve">38.2691307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2084007263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.402099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8432960510254</t>
+    <t xml:space="preserve">37.2084083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4021072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8432998657227</t>
   </si>
   <si>
     <t xml:space="preserve">37.2360725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4889602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9724311828613</t>
+    <t xml:space="preserve">36.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9724235534668</t>
   </si>
   <si>
     <t xml:space="preserve">36.3690490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8579025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2729721069336</t>
+    <t xml:space="preserve">36.8579063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2729682922363</t>
   </si>
   <si>
     <t xml:space="preserve">36.5166244506836</t>
@@ -2651,28 +2651,28 @@
     <t xml:space="preserve">35.7049407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6457633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6496047973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2583618164062</t>
+    <t xml:space="preserve">36.6457595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.649600982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2583656311035</t>
   </si>
   <si>
     <t xml:space="preserve">35.1422958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2898750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0093231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.266040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4305305480957</t>
+    <t xml:space="preserve">35.2898712158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0093193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2660446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4305267333984</t>
   </si>
   <si>
     <t xml:space="preserve">32.4028587341309</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">32.5227661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4858703613281</t>
+    <t xml:space="preserve">32.4858741760254</t>
   </si>
   <si>
     <t xml:space="preserve">31.1023139953613</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">27.8002300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0807819366455</t>
+    <t xml:space="preserve">27.0807838439941</t>
   </si>
   <si>
     <t xml:space="preserve">23.9816188812256</t>
@@ -2705,34 +2705,34 @@
     <t xml:space="preserve">27.3943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2637119293213</t>
+    <t xml:space="preserve">25.2637100219727</t>
   </si>
   <si>
     <t xml:space="preserve">24.9039897918701</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3651752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9224376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9977703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9309062957764</t>
+    <t xml:space="preserve">25.3651733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9224338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9977684020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3797817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9309043884277</t>
   </si>
   <si>
     <t xml:space="preserve">31.4528160095215</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7295265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7056980133057</t>
+    <t xml:space="preserve">31.729528427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7056941986084</t>
   </si>
   <si>
     <t xml:space="preserve">29.875560760498</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857032775879</t>
+    <t xml:space="preserve">28.6857051849365</t>
   </si>
   <si>
     <t xml:space="preserve">30.6688003540039</t>
@@ -2750,37 +2750,37 @@
     <t xml:space="preserve">30.1061553955078</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2998542785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0838680267334</t>
+    <t xml:space="preserve">30.2998523712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0838661193848</t>
   </si>
   <si>
     <t xml:space="preserve">30.6319065093994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8402137756348</t>
+    <t xml:space="preserve">31.8402118682861</t>
   </si>
   <si>
     <t xml:space="preserve">32.5135459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">30.890172958374</t>
+    <t xml:space="preserve">30.8901710510254</t>
   </si>
   <si>
     <t xml:space="preserve">30.5765647888184</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5081558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756443023682</t>
+    <t xml:space="preserve">31.5081577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756423950195</t>
   </si>
   <si>
     <t xml:space="preserve">30.2721824645996</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7702655792236</t>
+    <t xml:space="preserve">30.770263671875</t>
   </si>
   <si>
     <t xml:space="preserve">29.9124565124512</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">30.2352886199951</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7833271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2260646820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4143753051758</t>
+    <t xml:space="preserve">29.7833290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2260627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4143772125244</t>
   </si>
   <si>
     <t xml:space="preserve">28.7041530609131</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">28.6211414337158</t>
   </si>
   <si>
-    <t xml:space="preserve">29.737211227417</t>
+    <t xml:space="preserve">29.7372093200684</t>
   </si>
   <si>
     <t xml:space="preserve">29.8663387298584</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8056125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3682613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7979335784912</t>
+    <t xml:space="preserve">28.8056144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3682594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7979316711426</t>
   </si>
   <si>
     <t xml:space="preserve">30.39208984375</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">32.1630363464355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8532752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955574035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0339050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0377502441406</t>
+    <t xml:space="preserve">30.8532791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0746402740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955554962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0339088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0377521514893</t>
   </si>
   <si>
     <t xml:space="preserve">31.3790283203125</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">31.9693431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4950904846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7625846862793</t>
+    <t xml:space="preserve">32.4950942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7625770568848</t>
   </si>
   <si>
     <t xml:space="preserve">33.0577392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0892524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7203006744385</t>
+    <t xml:space="preserve">32.0892486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7203044891357</t>
   </si>
   <si>
     <t xml:space="preserve">32.126148223877</t>
@@ -2870,16 +2870,16 @@
     <t xml:space="preserve">31.3974742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6003932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9508934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9601192474365</t>
+    <t xml:space="preserve">31.6003913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9508972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9601211547852</t>
   </si>
   <si>
     <t xml:space="preserve">31.4897079467773</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">31.3513603210449</t>
   </si>
   <si>
-    <t xml:space="preserve">30.650354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9824028015137</t>
+    <t xml:space="preserve">30.6503524780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654182434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9824047088623</t>
   </si>
   <si>
     <t xml:space="preserve">31.0100746154785</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">30.5950088500977</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0692577362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0969314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4236030578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8809490203857</t>
+    <t xml:space="preserve">30.0692596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0969333648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4236011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5804042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.488166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8809471130371</t>
   </si>
   <si>
     <t xml:space="preserve">30.3275279998779</t>
@@ -2930,10 +2930,10 @@
     <t xml:space="preserve">29.5342864990234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5527362823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8571128845215</t>
+    <t xml:space="preserve">29.552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8571147918701</t>
   </si>
   <si>
     <t xml:space="preserve">30.0046939849854</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">31.1484355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7940902709961</t>
+    <t xml:space="preserve">31.7940921783447</t>
   </si>
   <si>
     <t xml:space="preserve">32.1814842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4766464233398</t>
+    <t xml:space="preserve">32.4766426086426</t>
   </si>
   <si>
     <t xml:space="preserve">33.8878746032715</t>
@@ -2966,28 +2966,28 @@
     <t xml:space="preserve">34.9854927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3306121826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6665077209473</t>
+    <t xml:space="preserve">34.3306083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.66650390625</t>
   </si>
   <si>
     <t xml:space="preserve">32.4674224853516</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0431327819824</t>
+    <t xml:space="preserve">32.0431289672852</t>
   </si>
   <si>
     <t xml:space="preserve">32.4489784240723</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2644958496094</t>
+    <t xml:space="preserve">32.2644996643066</t>
   </si>
   <si>
     <t xml:space="preserve">32.8455963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7164649963379</t>
+    <t xml:space="preserve">32.7164611816406</t>
   </si>
   <si>
     <t xml:space="preserve">33.6019401550293</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">33.8509750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2237663269043</t>
+    <t xml:space="preserve">33.223762512207</t>
   </si>
   <si>
     <t xml:space="preserve">33.5650405883789</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">33.9339904785156</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0354499816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6057777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9432144165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9485931396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4043998718262</t>
+    <t xml:space="preserve">34.0354537963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6057739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9432106018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9485969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4043960571289</t>
   </si>
   <si>
     <t xml:space="preserve">35.9170875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1276931762695</t>
+    <t xml:space="preserve">34.1276893615723</t>
   </si>
   <si>
     <t xml:space="preserve">32.1907119750977</t>
@@ -3035,10 +3035,10 @@
     <t xml:space="preserve">33.2053184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5465965270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.884033203125</t>
+    <t xml:space="preserve">33.5465927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8840293884277</t>
   </si>
   <si>
     <t xml:space="preserve">34.6349906921387</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">36.6273078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3467636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6088600158691</t>
+    <t xml:space="preserve">37.3467597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6088638305664</t>
   </si>
   <si>
     <t xml:space="preserve">36.7195510864258</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">37.8909606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6142425537109</t>
+    <t xml:space="preserve">37.8725090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6142463684082</t>
   </si>
   <si>
     <t xml:space="preserve">37.4482192993164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4535980224609</t>
+    <t xml:space="preserve">38.4536018371582</t>
   </si>
   <si>
     <t xml:space="preserve">38.7118682861328</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2837333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8463821411133</t>
+    <t xml:space="preserve">39.2837371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.846378326416</t>
   </si>
   <si>
     <t xml:space="preserve">40.5842781066895</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4144172668457</t>
+    <t xml:space="preserve">41.4144096374512</t>
   </si>
   <si>
     <t xml:space="preserve">42.9916648864746</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">42.8533058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8863639831543</t>
+    <t xml:space="preserve">43.886360168457</t>
   </si>
   <si>
     <t xml:space="preserve">44.1630783081055</t>
@@ -3119,22 +3119,22 @@
     <t xml:space="preserve">45.0116500854492</t>
   </si>
   <si>
-    <t xml:space="preserve">44.928638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1961250305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7349433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8679161071777</t>
+    <t xml:space="preserve">44.9286346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1961288452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7349472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8679122924805</t>
   </si>
   <si>
     <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">44.467456817627</t>
+    <t xml:space="preserve">44.4674530029297</t>
   </si>
   <si>
     <t xml:space="preserve">45.8694610595703</t>
@@ -3143,16 +3143,16 @@
     <t xml:space="preserve">46.3952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2476272583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1184997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8456230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8640747070312</t>
+    <t xml:space="preserve">46.2476348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1184959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8456268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.864070892334</t>
   </si>
   <si>
     <t xml:space="preserve">44.1077308654785</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">44.3290977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">44.273754119873</t>
+    <t xml:space="preserve">44.2737579345703</t>
   </si>
   <si>
     <t xml:space="preserve">43.3882827758789</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4121131896973</t>
+    <t xml:space="preserve">44.4121170043945</t>
   </si>
   <si>
     <t xml:space="preserve">44.0708351135254</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">43.6742172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6703796386719</t>
+    <t xml:space="preserve">44.6703758239746</t>
   </si>
   <si>
     <t xml:space="preserve">43.950927734375</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">44.8917427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7403221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6649932861328</t>
+    <t xml:space="preserve">45.7403259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6649971008301</t>
   </si>
   <si>
     <t xml:space="preserve">43.5912017822266</t>
@@ -3197,31 +3197,31 @@
     <t xml:space="preserve">44.3567695617676</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7756805419922</t>
+    <t xml:space="preserve">43.7756767272949</t>
   </si>
   <si>
     <t xml:space="preserve">44.1999702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2091903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1369476318359</t>
+    <t xml:space="preserve">44.2091941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1369438171387</t>
   </si>
   <si>
     <t xml:space="preserve">46.8932876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0739250183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6496315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9447860717773</t>
+    <t xml:space="preserve">47.5758438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0739212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6496276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9447898864746</t>
   </si>
   <si>
     <t xml:space="preserve">47.2622375488281</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">47.7972106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7088165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6534729003906</t>
+    <t xml:space="preserve">46.708812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6534767150879</t>
   </si>
   <si>
     <t xml:space="preserve">49.1807670593262</t>
@@ -3245,10 +3245,10 @@
     <t xml:space="preserve">47.8710021972656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2437896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0408668518066</t>
+    <t xml:space="preserve">47.2437934875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0408744812012</t>
   </si>
   <si>
     <t xml:space="preserve">47.1699981689453</t>
@@ -3257,31 +3257,31 @@
     <t xml:space="preserve">47.3175773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1108207702637</t>
+    <t xml:space="preserve">48.1108169555664</t>
   </si>
   <si>
     <t xml:space="preserve">48.4613189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6865310668945</t>
+    <t xml:space="preserve">47.6865234375</t>
   </si>
   <si>
     <t xml:space="preserve">46.6165771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7034301757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.860237121582</t>
+    <t xml:space="preserve">45.7034339904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8602409362793</t>
   </si>
   <si>
     <t xml:space="preserve">46.4136543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7587776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0001373291016</t>
+    <t xml:space="preserve">45.7587738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0001335144043</t>
   </si>
   <si>
     <t xml:space="preserve">47.3360290527344</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">47.4467124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8379440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2107276916504</t>
+    <t xml:space="preserve">46.837947845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2107353210449</t>
   </si>
   <si>
     <t xml:space="preserve">45.6019706726074</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">44.2276420593262</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4397850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4859008789062</t>
+    <t xml:space="preserve">44.4397811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4859046936035</t>
   </si>
   <si>
     <t xml:space="preserve">45.3898239135742</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">45.6573104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">46.450553894043</t>
+    <t xml:space="preserve">46.4505577087402</t>
   </si>
   <si>
     <t xml:space="preserve">46.5981292724609</t>
@@ -3335,34 +3335,34 @@
     <t xml:space="preserve">47.5020523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3544692993164</t>
+    <t xml:space="preserve">47.3544731140137</t>
   </si>
   <si>
     <t xml:space="preserve">46.3214225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2952919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3467864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9670753479004</t>
+    <t xml:space="preserve">48.2952880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3467903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9670791625977</t>
   </si>
   <si>
     <t xml:space="preserve">47.0039749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0593185424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4836082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3767623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4282608032227</t>
+    <t xml:space="preserve">47.0593147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4836044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3767585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4282646179199</t>
   </si>
   <si>
     <t xml:space="preserve">47.2806816101074</t>
@@ -3371,31 +3371,31 @@
     <t xml:space="preserve">47.7234230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9855270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5942916870117</t>
+    <t xml:space="preserve">46.985523223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
     <t xml:space="preserve">47.9263458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6642417907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4244232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1623191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.420581817627</t>
+    <t xml:space="preserve">48.6642379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4244270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1623153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4205856323242</t>
   </si>
   <si>
     <t xml:space="preserve">50.490291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1228141784668</t>
+    <t xml:space="preserve">51.1228179931641</t>
   </si>
   <si>
     <t xml:space="preserve">51.625114440918</t>
@@ -3407,40 +3407,40 @@
     <t xml:space="preserve">53.9877777099609</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0621910095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4482727050781</t>
+    <t xml:space="preserve">54.0621948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4482688903809</t>
   </si>
   <si>
     <t xml:space="preserve">53.6343078613281</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1180038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.229621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1039962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8063354492188</t>
+    <t xml:space="preserve">54.1180000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2296257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1039924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8063316345215</t>
   </si>
   <si>
     <t xml:space="preserve">53.5784950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8343467712402</t>
+    <t xml:space="preserve">52.8343505859375</t>
   </si>
   <si>
     <t xml:space="preserve">52.8715591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1320114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8947563171387</t>
+    <t xml:space="preserve">53.132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8947601318359</t>
   </si>
   <si>
     <t xml:space="preserve">54.2482261657715</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">54.043586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1738166809082</t>
+    <t xml:space="preserve">54.1738128662109</t>
   </si>
   <si>
     <t xml:space="preserve">54.2110214233398</t>
@@ -3461,16 +3461,16 @@
     <t xml:space="preserve">53.225025177002</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6901168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5970993041992</t>
+    <t xml:space="preserve">53.6901206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5971031188965</t>
   </si>
   <si>
     <t xml:space="preserve">53.0761985778809</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4668731689453</t>
+    <t xml:space="preserve">53.4668769836426</t>
   </si>
   <si>
     <t xml:space="preserve">53.3180465698242</t>
@@ -3479,16 +3479,16 @@
     <t xml:space="preserve">52.815746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">53.038990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3366508483887</t>
+    <t xml:space="preserve">53.0389938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3366546630859</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4250755310059</t>
+    <t xml:space="preserve">52.4250717163086</t>
   </si>
   <si>
     <t xml:space="preserve">53.2808380126953</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">54.3598518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">52.7785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1460151672363</t>
+    <t xml:space="preserve">52.7785415649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
     <t xml:space="preserve">53.1878204345703</t>
@@ -3518,52 +3518,52 @@
     <t xml:space="preserve">55.4388580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7551231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4946708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8761520385742</t>
+    <t xml:space="preserve">55.7551193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8761558532715</t>
   </si>
   <si>
     <t xml:space="preserve">53.950569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6947135925293</t>
+    <t xml:space="preserve">54.6389083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6947174072266</t>
   </si>
   <si>
     <t xml:space="preserve">54.5272827148438</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5876884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9271545410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2992210388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7271156311035</t>
+    <t xml:space="preserve">55.5876922607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9271507263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2992248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.727108001709</t>
   </si>
   <si>
     <t xml:space="preserve">57.5596771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4248542785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8667449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3970527648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0670051574707</t>
+    <t xml:space="preserve">56.4248504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8667488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3970565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.067008972168</t>
   </si>
   <si>
     <t xml:space="preserve">50.1554260253906</t>
@@ -3572,37 +3572,37 @@
     <t xml:space="preserve">50.8437614440918</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7693481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3972702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5461044311523</t>
+    <t xml:space="preserve">50.7693519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3972778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5461006164551</t>
   </si>
   <si>
     <t xml:space="preserve">50.8065528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4158782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0297927856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9925956726074</t>
+    <t xml:space="preserve">50.4158744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0298004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9925918579102</t>
   </si>
   <si>
     <t xml:space="preserve">50.2484436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1042060852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7181282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4018669128418</t>
+    <t xml:space="preserve">51.1042098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.718132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4018707275391</t>
   </si>
   <si>
     <t xml:space="preserve">51.3274574279785</t>
@@ -3611,22 +3611,22 @@
     <t xml:space="preserve">50.8251571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7879447937012</t>
+    <t xml:space="preserve">50.7879486083984</t>
   </si>
   <si>
     <t xml:space="preserve">48.1648330688477</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0904273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3182601928711</t>
+    <t xml:space="preserve">48.0904197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">48.0532150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0019989013672</t>
+    <t xml:space="preserve">49.0020027160645</t>
   </si>
   <si>
     <t xml:space="preserve">50.5647048950195</t>
@@ -3638,19 +3638,19 @@
     <t xml:space="preserve">51.1600227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0624046325684</t>
+    <t xml:space="preserve">50.0624084472656</t>
   </si>
   <si>
     <t xml:space="preserve">48.6113204956055</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2438430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7553367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9785842895508</t>
+    <t xml:space="preserve">49.2438468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7553405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.978588104248</t>
   </si>
   <si>
     <t xml:space="preserve">52.9831771850586</t>
@@ -3659,25 +3659,25 @@
     <t xml:space="preserve">52.4994812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4622764587402</t>
+    <t xml:space="preserve">52.4622802734375</t>
   </si>
   <si>
     <t xml:space="preserve">54.7133178710938</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4714736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.569091796875</t>
+    <t xml:space="preserve">54.4714698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5690879821777</t>
   </si>
   <si>
     <t xml:space="preserve">56.0341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7597198486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8341293334961</t>
+    <t xml:space="preserve">56.7597236633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8341331481934</t>
   </si>
   <si>
     <t xml:space="preserve">56.3876457214355</t>
@@ -3692,61 +3692,61 @@
     <t xml:space="preserve">57.7829208374023</t>
   </si>
   <si>
-    <t xml:space="preserve">59.438648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5084686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.234001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6524772644043</t>
+    <t xml:space="preserve">59.4386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5084648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2340049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.652473449707</t>
   </si>
   <si>
     <t xml:space="preserve">62.8803176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4012222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7408981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8199043273926</t>
+    <t xml:space="preserve">63.4012184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7409019470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8199157714844</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7546920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3314056396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2197875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5686492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0663566589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9129257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3222122192383</t>
+    <t xml:space="preserve">63.754695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.331413269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2197799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5686531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0663604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408554077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9129295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3222045898438</t>
   </si>
   <si>
     <t xml:space="preserve">58.3410301208496</t>
@@ -3758,40 +3758,40 @@
     <t xml:space="preserve">59.6060791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0385551452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9455337524414</t>
+    <t xml:space="preserve">61.0385589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9455375671387</t>
   </si>
   <si>
     <t xml:space="preserve">60.5920715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">61.6896896362305</t>
+    <t xml:space="preserve">61.6896820068359</t>
   </si>
   <si>
     <t xml:space="preserve">64.4430236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4710464477539</t>
+    <t xml:space="preserve">62.4710426330566</t>
   </si>
   <si>
     <t xml:space="preserve">62.1547737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4478378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6292762756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.675895690918</t>
+    <t xml:space="preserve">61.4478340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6758995056152</t>
   </si>
   <si>
     <t xml:space="preserve">60.182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">58.7503089904785</t>
+    <t xml:space="preserve">58.7503128051758</t>
   </si>
   <si>
     <t xml:space="preserve">58.8061218261719</t>
@@ -3803,16 +3803,16 @@
     <t xml:space="preserve">57.8573341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3224258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5642700195312</t>
+    <t xml:space="preserve">58.3224220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5642738342285</t>
   </si>
   <si>
     <t xml:space="preserve">59.7549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0711708068848</t>
+    <t xml:space="preserve">60.0711669921875</t>
   </si>
   <si>
     <t xml:space="preserve">59.5502662658691</t>
@@ -3824,31 +3824,31 @@
     <t xml:space="preserve">60.4618453979492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269371032715</t>
+    <t xml:space="preserve">60.9269409179688</t>
   </si>
   <si>
     <t xml:space="preserve">58.4154434204102</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9643630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1644020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7923316955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8807525634766</t>
+    <t xml:space="preserve">56.9643592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1644058227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7923278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8807487487793</t>
   </si>
   <si>
     <t xml:space="preserve">52.8901634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7087249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6111068725586</t>
+    <t xml:space="preserve">53.7087211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6111106872559</t>
   </si>
   <si>
     <t xml:space="preserve">54.3040390014648</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">54.3412437438965</t>
   </si>
   <si>
-    <t xml:space="preserve">51.699535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2716445922852</t>
+    <t xml:space="preserve">51.6995315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2716407775879</t>
   </si>
   <si>
     <t xml:space="preserve">52.3134536743164</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">55.271427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8389511108398</t>
+    <t xml:space="preserve">53.8389472961426</t>
   </si>
   <si>
     <t xml:space="preserve">54.0993995666504</t>
@@ -3890,40 +3890,40 @@
     <t xml:space="preserve">51.6437187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6391181945801</t>
+    <t xml:space="preserve">50.6391143798828</t>
   </si>
   <si>
     <t xml:space="preserve">52.1274108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2344398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9739875793457</t>
+    <t xml:space="preserve">51.2344360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9739837646484</t>
   </si>
   <si>
     <t xml:space="preserve">50.9181785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8809700012207</t>
+    <t xml:space="preserve">50.8809661865234</t>
   </si>
   <si>
     <t xml:space="preserve">48.4624938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">45.802173614502</t>
+    <t xml:space="preserve">45.8021774291992</t>
   </si>
   <si>
     <t xml:space="preserve">47.1230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">44.946403503418</t>
+    <t xml:space="preserve">44.9464073181152</t>
   </si>
   <si>
     <t xml:space="preserve">41.8768043518066</t>
   </si>
   <si>
-    <t xml:space="preserve">42.146556854248</t>
+    <t xml:space="preserve">42.1465606689453</t>
   </si>
   <si>
     <t xml:space="preserve">41.4954299926758</t>
@@ -3935,67 +3935,67 @@
     <t xml:space="preserve">43.9976196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6208419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6487503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2441749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7091522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7881622314453</t>
+    <t xml:space="preserve">44.6208457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6487464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2441711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.709156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7881660461426</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2951736450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8207778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2765655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8717765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1974449157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.178840637207</t>
+    <t xml:space="preserve">47.1044273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2951698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8207702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2021522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2765693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8717803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1974487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1788444519043</t>
   </si>
   <si>
     <t xml:space="preserve">48.9275817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2810516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9555969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.988208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4392929077148</t>
+    <t xml:space="preserve">49.2810554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9556007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9882125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4392890930176</t>
   </si>
   <si>
     <t xml:space="preserve">45.1603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0254135131836</t>
+    <t xml:space="preserve">46.0254211425781</t>
   </si>
   <si>
     <t xml:space="preserve">46.4533004760742</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">47.0300140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1835517883301</t>
+    <t xml:space="preserve">46.1835479736328</t>
   </si>
   <si>
     <t xml:space="preserve">47.5881233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">46.527717590332</t>
+    <t xml:space="preserve">46.5277214050293</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
@@ -4025,16 +4025,16 @@
     <t xml:space="preserve">46.2672653198242</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7695617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5696334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6115379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9604110717773</t>
+    <t xml:space="preserve">46.7695579528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5696296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6115417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9604072570801</t>
   </si>
   <si>
     <t xml:space="preserve">41.4861259460449</t>
@@ -4046,28 +4046,28 @@
     <t xml:space="preserve">38.9095230102539</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8676147460938</t>
+    <t xml:space="preserve">39.8676109313965</t>
   </si>
   <si>
     <t xml:space="preserve">41.6163520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8070945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1930656433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.281494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1093482971191</t>
+    <t xml:space="preserve">40.8070907592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1930694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2814865112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1093521118164</t>
   </si>
   <si>
     <t xml:space="preserve">40.6489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0908546447754</t>
+    <t xml:space="preserve">40.0908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">39.3095016479492</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">40.6588172912598</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3572578430176</t>
+    <t xml:space="preserve">42.3572616577148</t>
   </si>
   <si>
     <t xml:space="preserve">42.1779823303223</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801216125488</t>
+    <t xml:space="preserve">43.4801254272461</t>
   </si>
   <si>
     <t xml:space="preserve">43.234790802002</t>
@@ -4118,25 +4118,25 @@
     <t xml:space="preserve">37.2147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2145614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5167007446289</t>
+    <t xml:space="preserve">36.2145652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5166969299316</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0916976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9690399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9973487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312973022461</t>
+    <t xml:space="preserve">35.0917015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9690361022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9973449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9312934875488</t>
   </si>
   <si>
     <t xml:space="preserve">35.6767234802246</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">37.4600868225098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7054138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3942260742188</t>
+    <t xml:space="preserve">37.7054176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.394229888916</t>
   </si>
   <si>
     <t xml:space="preserve">38.4980239868164</t>
@@ -4160,16 +4160,16 @@
     <t xml:space="preserve">38.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3751640319824</t>
+    <t xml:space="preserve">37.3751678466797</t>
   </si>
   <si>
     <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0547332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396560668945</t>
+    <t xml:space="preserve">39.0547370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396598815918</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">38.9886856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6678657531738</t>
+    <t xml:space="preserve">38.6678695678711</t>
   </si>
   <si>
     <t xml:space="preserve">37.9507484436035</t>
@@ -4187,19 +4187,19 @@
     <t xml:space="preserve">37.8280830383301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5735092163086</t>
+    <t xml:space="preserve">38.5735130310059</t>
   </si>
   <si>
     <t xml:space="preserve">40.1587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3474388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7531776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1494827270508</t>
+    <t xml:space="preserve">40.3474349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.753173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1494789123535</t>
   </si>
   <si>
     <t xml:space="preserve">41.5552215576172</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389701843262</t>
+    <t xml:space="preserve">45.3389739990234</t>
   </si>
   <si>
     <t xml:space="preserve">46.5278854370117</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">46.5184440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4995727539062</t>
+    <t xml:space="preserve">46.4995765686035</t>
   </si>
   <si>
     <t xml:space="preserve">45.8579406738281</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7165908813477</t>
+    <t xml:space="preserve">46.7165946960449</t>
   </si>
   <si>
     <t xml:space="preserve">46.9524917602539</t>
@@ -4250,13 +4250,13 @@
     <t xml:space="preserve">46.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0089111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.754337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1315765380859</t>
+    <t xml:space="preserve">46.0089149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7543411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1315803527832</t>
   </si>
   <si>
     <t xml:space="preserve">44.0273971557617</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">45.2163047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2729187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.046070098877</t>
+    <t xml:space="preserve">45.2729225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0460739135742</t>
   </si>
   <si>
     <t xml:space="preserve">42.1496734619141</t>
@@ -4289,31 +4289,31 @@
     <t xml:space="preserve">42.2251625061035</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1400451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1777877807617</t>
+    <t xml:space="preserve">41.1400413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1777839660645</t>
   </si>
   <si>
     <t xml:space="preserve">41.3948097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6967544555664</t>
+    <t xml:space="preserve">41.6967506408691</t>
   </si>
   <si>
     <t xml:space="preserve">42.4704895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9988975524902</t>
+    <t xml:space="preserve">42.998893737793</t>
   </si>
   <si>
     <t xml:space="preserve">42.0175704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646553039551</t>
+    <t xml:space="preserve">42.7158241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646514892578</t>
   </si>
   <si>
     <t xml:space="preserve">40.9230194091797</t>
@@ -4322,13 +4322,13 @@
     <t xml:space="preserve">41.4891700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8005523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4610557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9511375427246</t>
+    <t xml:space="preserve">41.8005485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.461051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9511337280273</t>
   </si>
   <si>
     <t xml:space="preserve">39.2623252868652</t>
@@ -4340,16 +4340,16 @@
     <t xml:space="preserve">40.5644645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0645599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8095932006836</t>
+    <t xml:space="preserve">41.0645561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8095970153809</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9794425964355</t>
+    <t xml:space="preserve">39.9794387817383</t>
   </si>
   <si>
     <t xml:space="preserve">43.2064819335938</t>
@@ -4364,10 +4364,10 @@
     <t xml:space="preserve">41.5174751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8666000366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0272026062012</t>
+    <t xml:space="preserve">41.8665962219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0271987915039</t>
   </si>
   <si>
     <t xml:space="preserve">42.649772644043</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">43.8009338378906</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0557060241699</t>
+    <t xml:space="preserve">44.0557022094727</t>
   </si>
   <si>
     <t xml:space="preserve">43.7160186767578</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">44.6690330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3574600219727</t>
+    <t xml:space="preserve">43.3574562072754</t>
   </si>
   <si>
     <t xml:space="preserve">43.4329414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">46.169319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6692237854004</t>
+    <t xml:space="preserve">46.1693229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6692276000977</t>
   </si>
   <si>
     <t xml:space="preserve">43.7443237304688</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">43.8292465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0840148925781</t>
+    <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">46.7732124328613</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">48.6131896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6129989624023</t>
+    <t xml:space="preserve">47.6129951477051</t>
   </si>
   <si>
     <t xml:space="preserve">47.7639694213867</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">47.0185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">45.631477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5654296875</t>
+    <t xml:space="preserve">45.6314811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6031761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5654335021973</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
@@ -4466,16 +4466,16 @@
     <t xml:space="preserve">45.2917938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8200073242188</t>
+    <t xml:space="preserve">44.8200035095215</t>
   </si>
   <si>
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5465621948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5937347412109</t>
+    <t xml:space="preserve">45.546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5937385559082</t>
   </si>
   <si>
     <t xml:space="preserve">44.7539520263672</t>
@@ -4487,10 +4487,10 @@
     <t xml:space="preserve">46.5844955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2544403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7452926635742</t>
+    <t xml:space="preserve">47.2544364929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.745288848877</t>
   </si>
   <si>
     <t xml:space="preserve">46.6316757202148</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">45.7918891906738</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9049224853516</t>
+    <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
     <t xml:space="preserve">46.150447845459</t>
@@ -4511,16 +4511,16 @@
     <t xml:space="preserve">45.3861503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6788520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3110504150391</t>
+    <t xml:space="preserve">46.6788558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3110466003418</t>
   </si>
   <si>
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017120361328</t>
+    <t xml:space="preserve">47.8017082214355</t>
   </si>
   <si>
     <t xml:space="preserve">47.5563812255859</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">50.4814796447754</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8779716491699</t>
+    <t xml:space="preserve">51.8779754638672</t>
   </si>
   <si>
     <t xml:space="preserve">52.3497619628906</t>
@@ -4556,22 +4556,22 @@
     <t xml:space="preserve">53.0857543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">51.915714263916</t>
+    <t xml:space="preserve">51.9157180786133</t>
   </si>
   <si>
     <t xml:space="preserve">53.0480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3310852050781</t>
+    <t xml:space="preserve">53.3310890197754</t>
   </si>
   <si>
     <t xml:space="preserve">53.1046295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2555961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5199966430664</t>
+    <t xml:space="preserve">53.2555999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5199928283691</t>
   </si>
   <si>
     <t xml:space="preserve">54.0859489440918</t>
@@ -4589,10 +4589,10 @@
     <t xml:space="preserve">55.4446983337402</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0293312072754</t>
+    <t xml:space="preserve">54.1991806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0293350219727</t>
   </si>
   <si>
     <t xml:space="preserve">53.4254455566406</t>
@@ -4607,25 +4607,25 @@
     <t xml:space="preserve">53.5009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9349746704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8785552978516</t>
+    <t xml:space="preserve">53.9349784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4445114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3503456115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3126029968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9729118347168</t>
+    <t xml:space="preserve">54.444507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.350341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3125991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9729080200195</t>
   </si>
   <si>
     <t xml:space="preserve">54.46337890625</t>
@@ -4634,10 +4634,10 @@
     <t xml:space="preserve">55.0106544494629</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5388679504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3316688537598</t>
+    <t xml:space="preserve">54.5388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">57.1808853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">56.407154083252</t>
+    <t xml:space="preserve">56.4071502685547</t>
   </si>
   <si>
     <t xml:space="preserve">56.8789405822754</t>
@@ -4664,13 +4664,13 @@
     <t xml:space="preserve">54.8974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0676612854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2748603820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6526718139648</t>
+    <t xml:space="preserve">57.0676574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2748565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6526756286621</t>
   </si>
   <si>
     <t xml:space="preserve">56.2184371948242</t>
@@ -4679,16 +4679,16 @@
     <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5017051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546203613281</t>
+    <t xml:space="preserve">57.5017013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546241760254</t>
   </si>
   <si>
     <t xml:space="preserve">58.1433372497559</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2186279296875</t>
+    <t xml:space="preserve">57.2186317443848</t>
   </si>
   <si>
     <t xml:space="preserve">57.2752456665039</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">59.9550094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1059837341309</t>
+    <t xml:space="preserve">60.1059875488281</t>
   </si>
   <si>
     <t xml:space="preserve">60.0116271972656</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417778015137</t>
+    <t xml:space="preserve">59.8417816162109</t>
   </si>
   <si>
     <t xml:space="preserve">59.4266052246094</t>
@@ -4724,19 +4724,19 @@
     <t xml:space="preserve">62.0686225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">62.2196006774902</t>
+    <t xml:space="preserve">62.219596862793</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8044242858887</t>
+    <t xml:space="preserve">61.8044204711914</t>
   </si>
   <si>
     <t xml:space="preserve">62.2007255554199</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1443023681641</t>
+    <t xml:space="preserve">63.1443061828613</t>
   </si>
   <si>
     <t xml:space="preserve">63.4085121154785</t>
@@ -4745,34 +4745,34 @@
     <t xml:space="preserve">63.8614311218262</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7293243408203</t>
+    <t xml:space="preserve">63.7293281555176</t>
   </si>
   <si>
     <t xml:space="preserve">63.9935264587402</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3707733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896408081055</t>
+    <t xml:space="preserve">63.3707695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896369934082</t>
   </si>
   <si>
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5028686523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9933319091797</t>
+    <t xml:space="preserve">63.5028648376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.993335723877</t>
   </si>
   <si>
     <t xml:space="preserve">62.4649238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8987846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.01220703125</t>
+    <t xml:space="preserve">61.8987808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0122108459473</t>
   </si>
   <si>
     <t xml:space="preserve">62.9178504943848</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">61.5968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8608436584473</t>
+    <t xml:space="preserve">60.8608474731445</t>
   </si>
   <si>
     <t xml:space="preserve">60.7287483215332</t>
@@ -4805,19 +4805,19 @@
     <t xml:space="preserve">60.8631858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2293968200684</t>
+    <t xml:space="preserve">60.2293930053711</t>
   </si>
   <si>
     <t xml:space="preserve">60.9784202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8055648803711</t>
+    <t xml:space="preserve">60.8055686950684</t>
   </si>
   <si>
     <t xml:space="preserve">59.4227523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">61.804271697998</t>
+    <t xml:space="preserve">61.8042678833008</t>
   </si>
   <si>
     <t xml:space="preserve">60.9015960693359</t>
@@ -4826,16 +4826,16 @@
     <t xml:space="preserve">61.2665061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.4982757568359</t>
+    <t xml:space="preserve">60.4982719421387</t>
   </si>
   <si>
     <t xml:space="preserve">61.9963264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1102676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0718536376953</t>
+    <t xml:space="preserve">63.1102638244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.071849822998</t>
   </si>
   <si>
     <t xml:space="preserve">62.898998260498</t>
@@ -4856,7 +4856,7 @@
     <t xml:space="preserve">60.9976272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9605140686035</t>
+    <t xml:space="preserve">59.9605102539062</t>
   </si>
   <si>
     <t xml:space="preserve">59.8068656921387</t>
@@ -4871,22 +4871,22 @@
     <t xml:space="preserve">60.3638343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8247718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4214515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7671585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4022483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8657836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1538696289062</t>
+    <t xml:space="preserve">60.8247756958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4214477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4022445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.865779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.153865814209</t>
   </si>
   <si>
     <t xml:space="preserve">60.1717758178711</t>
@@ -4898,10 +4898,10 @@
     <t xml:space="preserve">62.8797950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3791427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2831192016602</t>
+    <t xml:space="preserve">63.379150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2831153869629</t>
   </si>
   <si>
     <t xml:space="preserve">61.4393577575684</t>
@@ -4910,13 +4910,13 @@
     <t xml:space="preserve">60.5750999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5379829406738</t>
+    <t xml:space="preserve">59.5379867553711</t>
   </si>
   <si>
     <t xml:space="preserve">59.3843383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7492485046387</t>
+    <t xml:space="preserve">59.7492523193359</t>
   </si>
   <si>
     <t xml:space="preserve">59.9028968811035</t>
@@ -4925,10 +4925,10 @@
     <t xml:space="preserve">60.3254203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2883110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3023223876953</t>
+    <t xml:space="preserve">59.2883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.302318572998</t>
   </si>
   <si>
     <t xml:space="preserve">62.783763885498</t>
@@ -4940,25 +4940,25 @@
     <t xml:space="preserve">60.6135101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1922798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3651313781738</t>
+    <t xml:space="preserve">59.1922836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3651351928711</t>
   </si>
   <si>
     <t xml:space="preserve">61.4969787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5161819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9797210693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8439788818359</t>
+    <t xml:space="preserve">61.5161781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7850570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9797172546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8439826965332</t>
   </si>
   <si>
     <t xml:space="preserve">60.5558929443359</t>
@@ -4967,7 +4967,7 @@
     <t xml:space="preserve">59.5763969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5571899414062</t>
+    <t xml:space="preserve">59.5571937561035</t>
   </si>
   <si>
     <t xml:space="preserve">59.8836898803711</t>
@@ -4985,28 +4985,28 @@
     <t xml:space="preserve">60.1525688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1333656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1346664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1961784362793</t>
+    <t xml:space="preserve">60.1333618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1346626281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.196174621582</t>
   </si>
   <si>
     <t xml:space="preserve">56.080940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1769714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8683776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2153854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7915534973145</t>
+    <t xml:space="preserve">56.1769676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8683815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2153816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7915573120117</t>
   </si>
   <si>
     <t xml:space="preserve">57.4061393737793</t>
@@ -5018,22 +5018,22 @@
     <t xml:space="preserve">55.4087409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4471473693848</t>
+    <t xml:space="preserve">55.447151184082</t>
   </si>
   <si>
     <t xml:space="preserve">54.2948036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1974716186523</t>
+    <t xml:space="preserve">55.1974754333496</t>
   </si>
   <si>
     <t xml:space="preserve">54.0451240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1437530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2218704223633</t>
+    <t xml:space="preserve">52.1437492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2218742370605</t>
   </si>
   <si>
     <t xml:space="preserve">52.3742218017578</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">52.4510459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6431007385254</t>
+    <t xml:space="preserve">52.6431045532227</t>
   </si>
   <si>
     <t xml:space="preserve">53.7954521179199</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">50.7417259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0682258605957</t>
+    <t xml:space="preserve">51.068229675293</t>
   </si>
   <si>
     <t xml:space="preserve">50.8377571105957</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">50.8761711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9337844848633</t>
+    <t xml:space="preserve">50.9337882995605</t>
   </si>
   <si>
     <t xml:space="preserve">51.0106086730957</t>
@@ -5099,22 +5099,22 @@
     <t xml:space="preserve">49.8006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5836715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8237419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5823745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1668548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.974796295166</t>
+    <t xml:space="preserve">46.583667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8237457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5823707580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1668510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9747924804688</t>
   </si>
   <si>
     <t xml:space="preserve">48.7827339172363</t>
@@ -5132,19 +5132,19 @@
     <t xml:space="preserve">47.4959449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7552261352539</t>
+    <t xml:space="preserve">47.7552223205566</t>
   </si>
   <si>
     <t xml:space="preserve">49.4165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4946517944336</t>
+    <t xml:space="preserve">48.4946479797363</t>
   </si>
   <si>
     <t xml:space="preserve">48.4370307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5701713562012</t>
+    <t xml:space="preserve">49.5701751708984</t>
   </si>
   <si>
     <t xml:space="preserve">48.9363822937012</t>
@@ -5159,16 +5159,16 @@
     <t xml:space="preserve">49.5125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.262882232666</t>
+    <t xml:space="preserve">49.2628784179688</t>
   </si>
   <si>
     <t xml:space="preserve">48.7059135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9940032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8595581054688</t>
+    <t xml:space="preserve">48.9939994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.859561920166</t>
   </si>
   <si>
     <t xml:space="preserve">48.6675033569336</t>
@@ -5177,13 +5177,13 @@
     <t xml:space="preserve">49.4549407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8774642944336</t>
+    <t xml:space="preserve">49.8774681091309</t>
   </si>
   <si>
     <t xml:space="preserve">50.2999954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5291633605957</t>
+    <t xml:space="preserve">51.529167175293</t>
   </si>
   <si>
     <t xml:space="preserve">52.4318389892578</t>
@@ -5204,7 +5204,7 @@
     <t xml:space="preserve">52.9696006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5265731811523</t>
+    <t xml:space="preserve">53.5265693664551</t>
   </si>
   <si>
     <t xml:space="preserve">54.0259208679199</t>
@@ -5213,13 +5213,13 @@
     <t xml:space="preserve">53.7762451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7378311157227</t>
+    <t xml:space="preserve">53.7378349304199</t>
   </si>
   <si>
     <t xml:space="preserve">53.3537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4881591796875</t>
+    <t xml:space="preserve">53.4881553649902</t>
   </si>
   <si>
     <t xml:space="preserve">53.4305381774902</t>
@@ -5255,34 +5255,34 @@
     <t xml:space="preserve">49.1092338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.493350982666</t>
+    <t xml:space="preserve">49.4933547973633</t>
   </si>
   <si>
     <t xml:space="preserve">49.3973197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.839054107666</t>
+    <t xml:space="preserve">49.8390579223633</t>
   </si>
   <si>
     <t xml:space="preserve">49.896671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0246200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8901824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4279479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0617370605469</t>
+    <t xml:space="preserve">54.6020927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0054168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0246238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8901786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4279441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0617332458496</t>
   </si>
   <si>
     <t xml:space="preserve">55.8312644958496</t>
@@ -5297,10 +5297,10 @@
     <t xml:space="preserve">57.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0028228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3293151855469</t>
+    <t xml:space="preserve">57.0028190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3293190002441</t>
   </si>
   <si>
     <t xml:space="preserve">60.0373344421387</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">61.1896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5545959472656</t>
+    <t xml:space="preserve">61.5545921325684</t>
   </si>
   <si>
     <t xml:space="preserve">61.1512718200684</t>
@@ -5330,19 +5330,19 @@
     <t xml:space="preserve">64.2626113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3599395751953</t>
+    <t xml:space="preserve">63.3599433898926</t>
   </si>
   <si>
     <t xml:space="preserve">63.9937286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3394393920898</t>
+    <t xml:space="preserve">64.3394317626953</t>
   </si>
   <si>
     <t xml:space="preserve">64.4354629516602</t>
   </si>
   <si>
-    <t xml:space="preserve">65.568603515625</t>
+    <t xml:space="preserve">65.5686111450195</t>
   </si>
   <si>
     <t xml:space="preserve">66.6249237060547</t>
@@ -5351,7 +5351,7 @@
     <t xml:space="preserve">66.8746032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5468063354492</t>
+    <t xml:space="preserve">67.5467987060547</t>
   </si>
   <si>
     <t xml:space="preserve">66.5096969604492</t>
@@ -5360,16 +5360,16 @@
     <t xml:space="preserve">66.4712829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7798690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5301895141602</t>
+    <t xml:space="preserve">65.7798767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5301971435547</t>
   </si>
   <si>
     <t xml:space="preserve">65.4533767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2997283935547</t>
+    <t xml:space="preserve">65.2997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">65.799072265625</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">62.0155372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0539474487305</t>
+    <t xml:space="preserve">62.0539512634277</t>
   </si>
   <si>
     <t xml:space="preserve">61.6122131347656</t>
@@ -5408,28 +5408,28 @@
     <t xml:space="preserve">63.4367599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0334396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8413848876953</t>
+    <t xml:space="preserve">63.0334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8413887023926</t>
   </si>
   <si>
     <t xml:space="preserve">62.668529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2254981994629</t>
+    <t xml:space="preserve">63.2254905700684</t>
   </si>
   <si>
     <t xml:space="preserve">64.1473770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1883850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3420333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9579124450684</t>
+    <t xml:space="preserve">62.1883888244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3420295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9579162597656</t>
   </si>
   <si>
     <t xml:space="preserve">61.573802947998</t>
@@ -72839,7 +72839,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6929166667</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>413532</v>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698095321655</t>
+    <t xml:space="preserve">10.9698104858398</t>
   </si>
   <si>
     <t xml:space="preserve">10.845253944397</t>
@@ -53,106 +53,106 @@
     <t xml:space="preserve">10.8986358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9876041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744375228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573612213135</t>
+    <t xml:space="preserve">10.987603187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573602676392</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769306182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1566438674927</t>
+    <t xml:space="preserve">11.4769296646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1566429138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.5481052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349405288696</t>
+    <t xml:space="preserve">11.7349376678467</t>
   </si>
   <si>
     <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1175031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1264009475708</t>
+    <t xml:space="preserve">11.8239068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1263999938965</t>
   </si>
   <si>
     <t xml:space="preserve">12.0997104644775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7260417938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908136367798</t>
+    <t xml:space="preserve">11.7260427474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908126831055</t>
   </si>
   <si>
     <t xml:space="preserve">11.9484634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8950805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616281509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9128742218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4146537780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2723035812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0409860610962</t>
+    <t xml:space="preserve">11.8950824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9128751754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4146518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2723026275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0409851074219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2545080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9431200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989940643311</t>
+    <t xml:space="preserve">10.9431209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989950180054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6726608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772897720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110984802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2509565353394</t>
+    <t xml:space="preserve">11.8772888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4110994338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2509574890137</t>
   </si>
   <si>
     <t xml:space="preserve">12.2687492370605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4022026062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7972183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1975755691528</t>
+    <t xml:space="preserve">12.4022016525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.797215461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1975746154785</t>
   </si>
   <si>
     <t xml:space="preserve">12.7402830123901</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">12.9627027511597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7669744491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2118167877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407546043396</t>
+    <t xml:space="preserve">12.7669734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2118148803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075469970703</t>
   </si>
   <si>
     <t xml:space="preserve">13.478720664978</t>
@@ -179,43 +179,43 @@
     <t xml:space="preserve">13.4520301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6210708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7100391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363695144653</t>
+    <t xml:space="preserve">13.6210718154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7100381851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363704681396</t>
   </si>
   <si>
     <t xml:space="preserve">13.0427761077881</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605707168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9893941879272</t>
+    <t xml:space="preserve">13.0605697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9893951416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0160856246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449100494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0961570739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5143070220947</t>
+    <t xml:space="preserve">13.0160846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0961561203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.514307975769</t>
   </si>
   <si>
     <t xml:space="preserve">13.1228475570679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9804973602295</t>
+    <t xml:space="preserve">12.9804992675781</t>
   </si>
   <si>
     <t xml:space="preserve">12.927116394043</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">12.589035987854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7936639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.829249382019</t>
+    <t xml:space="preserve">12.793662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8292531967163</t>
   </si>
   <si>
     <t xml:space="preserve">13.0338773727417</t>
@@ -239,58 +239,58 @@
     <t xml:space="preserve">13.1495370864868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.202919960022</t>
+    <t xml:space="preserve">13.2029190063477</t>
   </si>
   <si>
     <t xml:space="preserve">13.3897514343262</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1673307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869039535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089654922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5979337692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9715995788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9982900619507</t>
+    <t xml:space="preserve">13.1673316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089664459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5979328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9716005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.998291015625</t>
   </si>
   <si>
     <t xml:space="preserve">13.3185777664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9324598312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0570154190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947385787964</t>
+    <t xml:space="preserve">13.9324588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947376251221</t>
   </si>
   <si>
     <t xml:space="preserve">13.9502534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6388645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676908493042</t>
+    <t xml:space="preserve">13.6388635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676898956299</t>
   </si>
   <si>
     <t xml:space="preserve">13.3630619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3452701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2285184860229</t>
+    <t xml:space="preserve">13.345269203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285194396973</t>
   </si>
   <si>
     <t xml:space="preserve">13.5608043670654</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">13.2734222412109</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4709987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4620151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4979381561279</t>
+    <t xml:space="preserve">13.4709968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967254638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4620161056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4979391098022</t>
   </si>
   <si>
     <t xml:space="preserve">13.3632287979126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3183259963989</t>
+    <t xml:space="preserve">13.3183269500732</t>
   </si>
   <si>
     <t xml:space="preserve">13.6685724258423</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7404184341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3003664016724</t>
+    <t xml:space="preserve">13.7404165267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3003635406494</t>
   </si>
   <si>
     <t xml:space="preserve">13.1566734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7256031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105579376221</t>
+    <t xml:space="preserve">12.7256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105569839478</t>
   </si>
   <si>
     <t xml:space="preserve">12.860312461853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8122634887695</t>
+    <t xml:space="preserve">13.8122625350952</t>
   </si>
   <si>
     <t xml:space="preserve">13.6775522232056</t>
@@ -353,61 +353,61 @@
     <t xml:space="preserve">13.8571672439575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2253732681274</t>
+    <t xml:space="preserve">14.2253742218018</t>
   </si>
   <si>
     <t xml:space="preserve">12.9321565628052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3035097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6986598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9950227737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6178331375122</t>
+    <t xml:space="preserve">12.3035106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6986608505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9950218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6178340911865</t>
   </si>
   <si>
     <t xml:space="preserve">12.8513317108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8782730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9680786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9231767654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9590997695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9501180648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7705059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3452672958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8302230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1714887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0637216567993</t>
+    <t xml:space="preserve">12.8782720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9680795669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9231748580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9591007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.950119972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7705049514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452682495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8302240371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1714868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.063720703125</t>
   </si>
   <si>
     <t xml:space="preserve">14.3690633773804</t>
@@ -416,37 +416,37 @@
     <t xml:space="preserve">14.0816831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9559526443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6057071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9290113449097</t>
+    <t xml:space="preserve">13.9559516906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6057062149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9290103912354</t>
   </si>
   <si>
     <t xml:space="preserve">14.0277986526489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.018816947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8481855392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0457582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9918766021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9200296401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7673597335815</t>
+    <t xml:space="preserve">14.0188179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8481845855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0457601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9918756484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9200305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7673587799072</t>
   </si>
   <si>
     <t xml:space="preserve">14.0008563995361</t>
@@ -461,61 +461,61 @@
     <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.524881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3542461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4171123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5158996582031</t>
+    <t xml:space="preserve">13.5248823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3542470932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4171133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159006118774</t>
   </si>
   <si>
     <t xml:space="preserve">13.7224559783936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5338611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7044944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9110488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0098361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0727033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4530353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6506090164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6416282653809</t>
+    <t xml:space="preserve">13.533863067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7044954299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9110507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0098371505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0727005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4530344009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6506099700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6416292190552</t>
   </si>
   <si>
     <t xml:space="preserve">13.7853193283081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4799795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.839204788208</t>
+    <t xml:space="preserve">13.4799776077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8392038345337</t>
   </si>
   <si>
     <t xml:space="preserve">14.0996437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8930892944336</t>
+    <t xml:space="preserve">13.8930883407593</t>
   </si>
   <si>
     <t xml:space="preserve">13.9649343490601</t>
@@ -524,40 +524,40 @@
     <t xml:space="preserve">13.8751258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7943000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.62366771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3991527557373</t>
+    <t xml:space="preserve">13.7942991256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6236686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3991508483887</t>
   </si>
   <si>
     <t xml:space="preserve">13.3901720046997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4889574050903</t>
+    <t xml:space="preserve">13.4889583587646</t>
   </si>
   <si>
     <t xml:space="preserve">13.3362884521484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6326503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3273077011108</t>
+    <t xml:space="preserve">13.6326484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3273067474365</t>
   </si>
   <si>
     <t xml:space="preserve">13.7763395309448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8661451339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0547389984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6474647521973</t>
+    <t xml:space="preserve">13.8661470413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6474628448486</t>
   </si>
   <si>
     <t xml:space="preserve">14.6384830474854</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">14.9168844223022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0964984893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.04261302948</t>
+    <t xml:space="preserve">15.0964965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0426139831543</t>
   </si>
   <si>
     <t xml:space="preserve">14.8989219665527</t>
@@ -581,154 +581,154 @@
     <t xml:space="preserve">14.7372713088989</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7731962203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8719806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564455032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6833868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013492584229</t>
+    <t xml:space="preserve">14.773193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8719797134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.683388710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013483047485</t>
   </si>
   <si>
     <t xml:space="preserve">14.8450384140015</t>
   </si>
   <si>
-    <t xml:space="preserve">15.087513923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9707698822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7103281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6744070053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9528074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377641677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736833572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6892213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251434326172</t>
+    <t xml:space="preserve">15.087516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7103300094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6744050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.952805519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6892194747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251453399658</t>
   </si>
   <si>
     <t xml:space="preserve">15.4826679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7790288925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0933532714844</t>
+    <t xml:space="preserve">15.7790260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0933513641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.1651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2011184692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1921405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.246021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113147735596</t>
+    <t xml:space="preserve">16.2011203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.192138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2460231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113128662109</t>
   </si>
   <si>
     <t xml:space="preserve">16.0304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9855794906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6353387832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9316997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766025543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.958643913269</t>
+    <t xml:space="preserve">15.9855813980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137382507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6353368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9316987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9765996932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9586410522461</t>
   </si>
   <si>
     <t xml:space="preserve">15.9406805038452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8867950439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1741790771484</t>
+    <t xml:space="preserve">15.8867979049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1741771697998</t>
   </si>
   <si>
     <t xml:space="preserve">16.1023330688477</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0484485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8957757949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9676237106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1831569671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0991859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2608375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.162052154541</t>
+    <t xml:space="preserve">16.0484523773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8957738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9676246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1831588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0991878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.260835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1620502471924</t>
   </si>
   <si>
     <t xml:space="preserve">17.296760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3326816558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5122947692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5661792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6559886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6021041870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8535614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062313079834</t>
+    <t xml:space="preserve">17.3326835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5122966766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.56618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.65598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6021003723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8535633087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062351226807</t>
   </si>
   <si>
     <t xml:space="preserve">18.1768665313721</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">17.8805027008057</t>
   </si>
   <si>
-    <t xml:space="preserve">18.060115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0870552062988</t>
+    <t xml:space="preserve">18.0601177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0870571136475</t>
   </si>
   <si>
     <t xml:space="preserve">18.3205547332764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.266674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4103584289551</t>
+    <t xml:space="preserve">18.2666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4103622436523</t>
   </si>
   <si>
     <t xml:space="preserve">18.1678848266602</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">18.2756538391113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4373054504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169185638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9312419891357</t>
+    <t xml:space="preserve">18.4373073577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9312438964844</t>
   </si>
   <si>
     <t xml:space="preserve">19.2276020050049</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">19.2365837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2006607055664</t>
+    <t xml:space="preserve">19.2006587982178</t>
   </si>
   <si>
     <t xml:space="preserve">19.4790630340576</t>
@@ -785,40 +785,40 @@
     <t xml:space="preserve">19.1108570098877</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2096405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3174114227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5329437255859</t>
+    <t xml:space="preserve">19.2096424102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3174095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5329475402832</t>
   </si>
   <si>
     <t xml:space="preserve">19.6945991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4610996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5778484344482</t>
+    <t xml:space="preserve">19.4611015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5778465270996</t>
   </si>
   <si>
     <t xml:space="preserve">19.5149841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1885356903076</t>
+    <t xml:space="preserve">20.1885318756104</t>
   </si>
   <si>
     <t xml:space="preserve">20.4310111999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3501873016357</t>
+    <t xml:space="preserve">20.3501853942871</t>
   </si>
   <si>
     <t xml:space="preserve">20.6645088195801</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8351421356201</t>
+    <t xml:space="preserve">20.8351440429688</t>
   </si>
   <si>
     <t xml:space="preserve">21.1135444641113</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">19.9999408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8921699523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9819774627686</t>
+    <t xml:space="preserve">19.8921718597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9819793701172</t>
   </si>
   <si>
     <t xml:space="preserve">19.874210357666</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">19.9909591674805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.389253616333</t>
+    <t xml:space="preserve">19.3892555236816</t>
   </si>
   <si>
     <t xml:space="preserve">19.5509071350098</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6505184173584</t>
+    <t xml:space="preserve">19.6505165100098</t>
   </si>
   <si>
     <t xml:space="preserve">19.7229614257812</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">19.6052398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4875202178955</t>
+    <t xml:space="preserve">19.4875183105469</t>
   </si>
   <si>
     <t xml:space="preserve">20.0127391815186</t>
@@ -872,52 +872,52 @@
     <t xml:space="preserve">19.6324081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7048511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2792415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9260768890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0075740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9713535308838</t>
+    <t xml:space="preserve">19.7048530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.279239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9260730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0075759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9713516235352</t>
   </si>
   <si>
     <t xml:space="preserve">19.0800189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5819664001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1252956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0437965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3426265716553</t>
+    <t xml:space="preserve">18.5819625854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1252975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0437984466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3426284790039</t>
   </si>
   <si>
     <t xml:space="preserve">19.2249050140381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.614294052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2158508300781</t>
+    <t xml:space="preserve">19.6142921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2158489227295</t>
   </si>
   <si>
     <t xml:space="preserve">19.1524639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1434078216553</t>
+    <t xml:space="preserve">19.1434059143066</t>
   </si>
   <si>
     <t xml:space="preserve">19.3245162963867</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">18.9441871643066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3736877441406</t>
+    <t xml:space="preserve">18.3736896514893</t>
   </si>
   <si>
     <t xml:space="preserve">18.5638523101807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6363010406494</t>
+    <t xml:space="preserve">18.6362972259521</t>
   </si>
   <si>
     <t xml:space="preserve">18.6000785827637</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">19.1071834564209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2882919311523</t>
+    <t xml:space="preserve">19.2882976531982</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788509368896</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">19.4060192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4512958526611</t>
+    <t xml:space="preserve">19.4512939453125</t>
   </si>
   <si>
     <t xml:space="preserve">19.4331855773926</t>
@@ -968,31 +968,31 @@
     <t xml:space="preserve">19.2701854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1977424621582</t>
+    <t xml:space="preserve">19.1977443695068</t>
   </si>
   <si>
     <t xml:space="preserve">20.2391262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4655151367188</t>
+    <t xml:space="preserve">20.465518951416</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568515777588</t>
+    <t xml:space="preserve">20.3568477630615</t>
   </si>
   <si>
     <t xml:space="preserve">20.2572383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3930702209473</t>
+    <t xml:space="preserve">20.3930740356445</t>
   </si>
   <si>
     <t xml:space="preserve">20.329683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3749599456787</t>
+    <t xml:space="preserve">20.3749618530273</t>
   </si>
   <si>
     <t xml:space="preserve">20.4021263122559</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">20.3477954864502</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8458499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.144681930542</t>
+    <t xml:space="preserve">20.8458518981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1446800231934</t>
   </si>
   <si>
     <t xml:space="preserve">21.5431270599365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3801250457764</t>
+    <t xml:space="preserve">21.3801288604736</t>
   </si>
   <si>
     <t xml:space="preserve">21.3439025878906</t>
@@ -1019,76 +1019,76 @@
     <t xml:space="preserve">21.4254035949707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3710708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2805137634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2080688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8730144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2714595794678</t>
+    <t xml:space="preserve">21.3710689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2805156707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2080726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8730125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2714576721191</t>
   </si>
   <si>
     <t xml:space="preserve">21.6155700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8962936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7423458099365</t>
+    <t xml:space="preserve">21.8962917327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7423439025879</t>
   </si>
   <si>
     <t xml:space="preserve">21.7966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9959049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1589012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4305686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3671779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5935668945312</t>
+    <t xml:space="preserve">21.9959030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.158899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4305667877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3671798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5935688018799</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116790771484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5030117034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2404022216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.385290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2313442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2132339477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2494564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.959680557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.823844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0683460235596</t>
+    <t xml:space="preserve">22.5030136108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2404003143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3852882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2313461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2132358551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.249454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9596786499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8238468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0683498382568</t>
   </si>
   <si>
     <t xml:space="preserve">22.1136245727539</t>
@@ -1106,37 +1106,37 @@
     <t xml:space="preserve">21.4706802368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1498470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2766227722168</t>
+    <t xml:space="preserve">22.149845123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2766246795654</t>
   </si>
   <si>
     <t xml:space="preserve">22.059289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.285680770874</t>
+    <t xml:space="preserve">22.2856788635254</t>
   </si>
   <si>
     <t xml:space="preserve">22.3490676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3943462371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9868488311768</t>
+    <t xml:space="preserve">22.394344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9868469238281</t>
   </si>
   <si>
     <t xml:space="preserve">22.4396228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5573444366455</t>
+    <t xml:space="preserve">22.5573425292969</t>
   </si>
   <si>
     <t xml:space="preserve">22.3581237792969</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1226806640625</t>
+    <t xml:space="preserve">22.1226787567139</t>
   </si>
   <si>
     <t xml:space="preserve">22.0774002075195</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">22.0049571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9415683746338</t>
+    <t xml:space="preserve">21.9415664672852</t>
   </si>
   <si>
     <t xml:space="preserve">21.8510131835938</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">21.7695121765137</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6466255187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0631809234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0088481903076</t>
+    <t xml:space="preserve">20.6466236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0631828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088500976562</t>
   </si>
   <si>
     <t xml:space="preserve">20.6737937927246</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">20.7734050750732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6556835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0994052886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0903491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.135627746582</t>
+    <t xml:space="preserve">20.6556816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0903511047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1356258392334</t>
   </si>
   <si>
     <t xml:space="preserve">20.8277378082275</t>
@@ -1190,37 +1190,37 @@
     <t xml:space="preserve">20.8005714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8820705413818</t>
+    <t xml:space="preserve">20.8820686340332</t>
   </si>
   <si>
     <t xml:space="preserve">21.4344577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163455963135</t>
+    <t xml:space="preserve">21.4163494110107</t>
   </si>
   <si>
     <t xml:space="preserve">21.950626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4667911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5120697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8833446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3219032287598</t>
+    <t xml:space="preserve">22.4667892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5120677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8833465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3218994140625</t>
   </si>
   <si>
     <t xml:space="preserve">22.8290100097656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9014568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8109016418457</t>
+    <t xml:space="preserve">22.9014549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8109035491943</t>
   </si>
   <si>
     <t xml:space="preserve">23.0916213989258</t>
@@ -1235,46 +1235,46 @@
     <t xml:space="preserve">23.9066200256348</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6168441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632869720459</t>
+    <t xml:space="preserve">23.6168422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632888793945</t>
   </si>
   <si>
     <t xml:space="preserve">23.1821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6349563598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4900646209717</t>
+    <t xml:space="preserve">23.634952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4900684356689</t>
   </si>
   <si>
     <t xml:space="preserve">23.5443992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.200288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8199577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7837371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0372886657715</t>
+    <t xml:space="preserve">23.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8199558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7837333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0372867584229</t>
   </si>
   <si>
     <t xml:space="preserve">23.8160648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">24.341287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2507286071777</t>
+    <t xml:space="preserve">24.3412857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.486177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.250732421875</t>
   </si>
   <si>
     <t xml:space="preserve">24.3775081634521</t>
@@ -1292,40 +1292,40 @@
     <t xml:space="preserve">24.1148986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0333995819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2145042419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5625133514404</t>
+    <t xml:space="preserve">24.0333976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2145099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5625095367432</t>
   </si>
   <si>
     <t xml:space="preserve">23.4629001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3593978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2908458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0424518585205</t>
+    <t xml:space="preserve">24.3593997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.290843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0424499511719</t>
   </si>
   <si>
     <t xml:space="preserve">24.6582279205322</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6724510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7630062103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4279499053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5637836456299</t>
+    <t xml:space="preserve">25.6724491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7630081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4279518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5637817382812</t>
   </si>
   <si>
     <t xml:space="preserve">25.5818958282471</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">25.4641742706299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.391731262207</t>
+    <t xml:space="preserve">25.3917274475098</t>
   </si>
   <si>
     <t xml:space="preserve">25.6362266540527</t>
@@ -1346,118 +1346,118 @@
     <t xml:space="preserve">25.9893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3192825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.264949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6996173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728378295898</t>
+    <t xml:space="preserve">25.3192863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2649459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6996154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728397369385</t>
   </si>
   <si>
     <t xml:space="preserve">26.215784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.405948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5055618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6685619354248</t>
+    <t xml:space="preserve">26.4059505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5055637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6685600280762</t>
   </si>
   <si>
     <t xml:space="preserve">26.4874496459961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8134479522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7500591278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9583358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.465446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9453926086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5741119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7190055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6737251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9182224273682</t>
+    <t xml:space="preserve">26.8134498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7500610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9583377838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4654483795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9453907012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5741138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7190036773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6737232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9182262420654</t>
   </si>
   <si>
     <t xml:space="preserve">27.9816112518311</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7655563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4305000305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.810827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2364406585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9104385375977</t>
+    <t xml:space="preserve">29.765552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4304981231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8108310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.236442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9104423522949</t>
   </si>
   <si>
     <t xml:space="preserve">30.562442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8250522613525</t>
+    <t xml:space="preserve">30.8250541687012</t>
   </si>
   <si>
     <t xml:space="preserve">30.4809417724609</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2053833007812</t>
+    <t xml:space="preserve">31.205379486084</t>
   </si>
   <si>
     <t xml:space="preserve">31.9026565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7124919891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.020378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9207744598389</t>
+    <t xml:space="preserve">31.7124938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0203819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9207649230957</t>
   </si>
   <si>
     <t xml:space="preserve">32.618049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">32.690486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9621620178223</t>
+    <t xml:space="preserve">32.6904907226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.962158203125</t>
   </si>
   <si>
     <t xml:space="preserve">33.4602127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9039344787598</t>
+    <t xml:space="preserve">33.9039306640625</t>
   </si>
   <si>
     <t xml:space="preserve">34.4110412597656</t>
@@ -1472,31 +1472,31 @@
     <t xml:space="preserve">33.0346031188965</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0798797607422</t>
+    <t xml:space="preserve">33.0798835754395</t>
   </si>
   <si>
     <t xml:space="preserve">33.3153305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6865997314453</t>
+    <t xml:space="preserve">33.6866035461426</t>
   </si>
   <si>
     <t xml:space="preserve">34.0759925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0941047668457</t>
+    <t xml:space="preserve">34.0941009521484</t>
   </si>
   <si>
     <t xml:space="preserve">34.3929328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2350959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.678825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4416961669922</t>
+    <t xml:space="preserve">35.2350997924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4416923522949</t>
   </si>
   <si>
     <t xml:space="preserve">34.4749336242676</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">33.7270622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5022926330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8065071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0071563720703</t>
+    <t xml:space="preserve">34.5022964477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8065032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.007152557373</t>
   </si>
   <si>
     <t xml:space="preserve">34.8671073913574</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">35.1589584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8429832458496</t>
+    <t xml:space="preserve">35.8156242370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8429908752441</t>
   </si>
   <si>
     <t xml:space="preserve">36.3354835510254</t>
@@ -1535,22 +1535,22 @@
     <t xml:space="preserve">37.2931213378906</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2533988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2748832702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5940933227539</t>
+    <t xml:space="preserve">36.2534027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2748756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">37.9041900634766</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4696464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3602027893066</t>
+    <t xml:space="preserve">38.4696502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3602066040039</t>
   </si>
   <si>
     <t xml:space="preserve">37.8221015930176</t>
@@ -1559,46 +1559,46 @@
     <t xml:space="preserve">36.6546974182129</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3446044921875</t>
+    <t xml:space="preserve">36.3446083068848</t>
   </si>
   <si>
     <t xml:space="preserve">36.28076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0892372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4143333435059</t>
+    <t xml:space="preserve">36.089241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4143295288086</t>
   </si>
   <si>
     <t xml:space="preserve">35.3960914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5146598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1042404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5693740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3504829406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5205307006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7453079223633</t>
+    <t xml:space="preserve">35.5146522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1042442321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5693817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3504867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5205345153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9550704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.745304107666</t>
   </si>
   <si>
     <t xml:space="preserve">34.2925262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0586318969727</t>
+    <t xml:space="preserve">35.0586357116699</t>
   </si>
   <si>
     <t xml:space="preserve">34.1830825805664</t>
@@ -1607,43 +1607,43 @@
     <t xml:space="preserve">34.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5967330932617</t>
+    <t xml:space="preserve">35.596736907959</t>
   </si>
   <si>
     <t xml:space="preserve">35.1224784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4690551757812</t>
+    <t xml:space="preserve">35.6241035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.469051361084</t>
   </si>
   <si>
     <t xml:space="preserve">35.3869705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">35.241039276123</t>
+    <t xml:space="preserve">35.2410430908203</t>
   </si>
   <si>
     <t xml:space="preserve">36.1622009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8853530883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6938247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8091506958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4019775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2013282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4169692993164</t>
+    <t xml:space="preserve">34.8853492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6938209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8091468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.401969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2013244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4169731140137</t>
   </si>
   <si>
     <t xml:space="preserve">34.2651672363281</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">34.7303047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6208610534668</t>
+    <t xml:space="preserve">34.6208648681641</t>
   </si>
   <si>
     <t xml:space="preserve">34.018913269043</t>
@@ -1673,19 +1673,19 @@
     <t xml:space="preserve">34.7941474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5784950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2169189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.153076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5328903198242</t>
+    <t xml:space="preserve">35.5784912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2169151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1530799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5328941345215</t>
   </si>
   <si>
     <t xml:space="preserve">35.5055389404297</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">35.1133575439453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8365097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2834014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.338134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3016471862793</t>
+    <t xml:space="preserve">33.8365135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2834053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3381309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3016510009766</t>
   </si>
   <si>
     <t xml:space="preserve">34.785026550293</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">34.4202117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5934944152832</t>
+    <t xml:space="preserve">34.5934982299805</t>
   </si>
   <si>
     <t xml:space="preserve">34.5114135742188</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">34.0827560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4110946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6664543151855</t>
+    <t xml:space="preserve">34.4110908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6664581298828</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228012084961</t>
@@ -1742,46 +1742,46 @@
     <t xml:space="preserve">32.9791984558105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8300323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4593353271484</t>
+    <t xml:space="preserve">31.8300342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4593315124512</t>
   </si>
   <si>
     <t xml:space="preserve">28.9388809204102</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5284652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2001304626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.263973236084</t>
+    <t xml:space="preserve">28.5284671783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2001323699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529083251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2639713287354</t>
   </si>
   <si>
     <t xml:space="preserve">28.4007778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4555034637451</t>
+    <t xml:space="preserve">28.4555015563965</t>
   </si>
   <si>
     <t xml:space="preserve">27.7258739471436</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7988357543945</t>
+    <t xml:space="preserve">27.7988338470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.6587905883789</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2698516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082794189453</t>
+    <t xml:space="preserve">27.2698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082813262939</t>
   </si>
   <si>
     <t xml:space="preserve">27.5708255767822</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">27.1786499023438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5434665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9994812011719</t>
+    <t xml:space="preserve">27.5434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">28.0906867980957</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">29.5499458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1942481994629</t>
+    <t xml:space="preserve">29.1942462921143</t>
   </si>
   <si>
     <t xml:space="preserve">28.97536277771</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">29.130407333374</t>
   </si>
   <si>
-    <t xml:space="preserve">28.692626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4522609710693</t>
+    <t xml:space="preserve">28.6926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.452262878418</t>
   </si>
   <si>
     <t xml:space="preserve">29.0392036437988</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">28.0268440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0359630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3519382476807</t>
+    <t xml:space="preserve">28.0359668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.351936340332</t>
   </si>
   <si>
     <t xml:space="preserve">26.2666149139404</t>
@@ -1841,46 +1841,46 @@
     <t xml:space="preserve">27.4340209960938</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2060127258301</t>
+    <t xml:space="preserve">27.2060146331787</t>
   </si>
   <si>
     <t xml:space="preserve">26.7317523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9141616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2483730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.807954788208</t>
+    <t xml:space="preserve">26.9141597747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2483768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8079566955566</t>
   </si>
   <si>
     <t xml:space="preserve">26.7682361602783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.512866973877</t>
+    <t xml:space="preserve">27.3063373565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5128650665283</t>
   </si>
   <si>
     <t xml:space="preserve">26.8594398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4822635650635</t>
+    <t xml:space="preserve">25.4822673797607</t>
   </si>
   <si>
     <t xml:space="preserve">25.3272190093994</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9565238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6646709442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1265716552734</t>
+    <t xml:space="preserve">25.956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6646728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1265697479248</t>
   </si>
   <si>
     <t xml:space="preserve">24.6431922912598</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">25.1721744537354</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7011547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1448154449463</t>
+    <t xml:space="preserve">25.7011566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1448135375977</t>
   </si>
   <si>
     <t xml:space="preserve">25.3454608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5825881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3851833343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5949478149414</t>
+    <t xml:space="preserve">25.5825901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.385181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.59494972229</t>
   </si>
   <si>
     <t xml:space="preserve">25.3637008666992</t>
@@ -1916,136 +1916,136 @@
     <t xml:space="preserve">27.1877727508545</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9356422424316</t>
+    <t xml:space="preserve">27.935640335083</t>
   </si>
   <si>
     <t xml:space="preserve">28.6014270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1454086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0600872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0327262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3336982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4066600799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6711483001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8991622924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3792991638184</t>
+    <t xml:space="preserve">28.1454067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0600852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0327224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3336963653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4066581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6711502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8991584777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3792972564697</t>
   </si>
   <si>
     <t xml:space="preserve">27.9538803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8809204101562</t>
+    <t xml:space="preserve">27.880916595459</t>
   </si>
   <si>
     <t xml:space="preserve">28.2366123199463</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9147567749023</t>
+    <t xml:space="preserve">29.9147548675537</t>
   </si>
   <si>
     <t xml:space="preserve">30.0059623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5987796783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7994289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4437408447266</t>
+    <t xml:space="preserve">30.5987815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7994327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2007236480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4437389373779</t>
   </si>
   <si>
     <t xml:space="preserve">30.6443824768066</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9362373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020259857178</t>
+    <t xml:space="preserve">30.9362354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023448944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020202636719</t>
   </si>
   <si>
     <t xml:space="preserve">31.3284111022949</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8117923736572</t>
+    <t xml:space="preserve">31.8117942810059</t>
   </si>
   <si>
     <t xml:space="preserve">31.7753105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6567440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6476230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4743347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9668350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9029960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7538299560547</t>
+    <t xml:space="preserve">31.6567401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6476249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4743404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9668388366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9029922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7538318634033</t>
   </si>
   <si>
     <t xml:space="preserve">34.1557235717773</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9244728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8332672119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6964683532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5779037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4319763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9153518676758</t>
+    <t xml:space="preserve">33.790901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9244689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8332710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.696460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5140609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5778999328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4319725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.915355682373</t>
   </si>
   <si>
     <t xml:space="preserve">33.0065536499023</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5264167785645</t>
+    <t xml:space="preserve">33.5264129638672</t>
   </si>
   <si>
     <t xml:space="preserve">33.1980857849121</t>
@@ -2060,61 +2060,61 @@
     <t xml:space="preserve">32.4410934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7603034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5081748962402</t>
+    <t xml:space="preserve">32.7603073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5081787109375</t>
   </si>
   <si>
     <t xml:space="preserve">33.6085014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1283645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9277076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8638725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8150253295898</t>
+    <t xml:space="preserve">34.128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9277153015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8638763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8150329589844</t>
   </si>
   <si>
     <t xml:space="preserve">32.6599884033203</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2163238525391</t>
+    <t xml:space="preserve">33.2163200378418</t>
   </si>
   <si>
     <t xml:space="preserve">33.2892875671387</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0977592468262</t>
+    <t xml:space="preserve">33.0977630615234</t>
   </si>
   <si>
     <t xml:space="preserve">33.4260940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1160011291504</t>
+    <t xml:space="preserve">33.1160049438477</t>
   </si>
   <si>
     <t xml:space="preserve">33.3075294494629</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8729858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.061279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3440093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3531303405762</t>
+    <t xml:space="preserve">33.872989654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6814613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3440132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3531265258789</t>
   </si>
   <si>
     <t xml:space="preserve">33.2345657348633</t>
@@ -2123,22 +2123,22 @@
     <t xml:space="preserve">33.9185905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1616058349609</t>
+    <t xml:space="preserve">33.1616020202637</t>
   </si>
   <si>
     <t xml:space="preserve">32.550537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">32.404613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4443283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9485912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6873435974121</t>
+    <t xml:space="preserve">32.4046096801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4443321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9485931396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6873474121094</t>
   </si>
   <si>
     <t xml:space="preserve">32.1310005187988</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">32.5596618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5911674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8863258361816</t>
+    <t xml:space="preserve">31.5911712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8863296508789</t>
   </si>
   <si>
     <t xml:space="preserve">32.836368560791</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8586578369141</t>
+    <t xml:space="preserve">31.8586597442627</t>
   </si>
   <si>
     <t xml:space="preserve">32.2552795410156</t>
@@ -2165,58 +2165,58 @@
     <t xml:space="preserve">32.2829475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7848663330078</t>
+    <t xml:space="preserve">31.7848701477051</t>
   </si>
   <si>
     <t xml:space="preserve">30.7887115478516</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6226844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4382095336914</t>
+    <t xml:space="preserve">30.6226825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4382057189941</t>
   </si>
   <si>
     <t xml:space="preserve">30.5581169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1207618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0062408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6649589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1169166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7387504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6518936157227</t>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0062370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6649646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1169242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7387466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290634155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6518974304199</t>
   </si>
   <si>
     <t xml:space="preserve">33.6480560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7679672241211</t>
+    <t xml:space="preserve">33.7679634094238</t>
   </si>
   <si>
     <t xml:space="preserve">34.7087860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">34.505859375</t>
+    <t xml:space="preserve">34.5058631896973</t>
   </si>
   <si>
     <t xml:space="preserve">34.4136276245117</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">34.2568206787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6811141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9762687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5112419128418</t>
+    <t xml:space="preserve">34.6811065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9762725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5112457275391</t>
   </si>
   <si>
     <t xml:space="preserve">35.6127052307129</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5204620361328</t>
+    <t xml:space="preserve">35.5204658508301</t>
   </si>
   <si>
     <t xml:space="preserve">35.5296897888184</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">35.2806549072266</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3544464111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0961799621582</t>
+    <t xml:space="preserve">35.3544387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0961761474609</t>
   </si>
   <si>
     <t xml:space="preserve">35.4927940368652</t>
@@ -2270,16 +2270,16 @@
     <t xml:space="preserve">35.1330718994141</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2253074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2437591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6588249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6403770446777</t>
+    <t xml:space="preserve">35.2253112792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2437553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6403732299805</t>
   </si>
   <si>
     <t xml:space="preserve">35.9263114929199</t>
@@ -2291,22 +2291,25 @@
     <t xml:space="preserve">35.963207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6903343200684</t>
+    <t xml:space="preserve">34.6903381347656</t>
   </si>
   <si>
     <t xml:space="preserve">34.2844886779785</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4451332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.462043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8309879302979</t>
+    <t xml:space="preserve">33.4451370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4620380401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343681335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8309898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5596580505371</t>
   </si>
   <si>
     <t xml:space="preserve">32.4120826721191</t>
@@ -2315,40 +2318,40 @@
     <t xml:space="preserve">32.3475151062012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4989318847656</t>
+    <t xml:space="preserve">31.4989356994629</t>
   </si>
   <si>
     <t xml:space="preserve">31.2314472198486</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7572002410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6926326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7072372436523</t>
+    <t xml:space="preserve">31.7571964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6926345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7072410583496</t>
   </si>
   <si>
     <t xml:space="preserve">31.7479705810547</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5542755126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3605785369873</t>
+    <t xml:space="preserve">31.5542774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3605804443359</t>
   </si>
   <si>
     <t xml:space="preserve">31.3052368164062</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4435939788818</t>
+    <t xml:space="preserve">31.4435901641846</t>
   </si>
   <si>
     <t xml:space="preserve">31.6465167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3382949829102</t>
+    <t xml:space="preserve">32.3382873535156</t>
   </si>
   <si>
     <t xml:space="preserve">33.0761871337891</t>
@@ -2363,52 +2366,52 @@
     <t xml:space="preserve">32.5412101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6242256164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6426696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.375186920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6372871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4804821014404</t>
+    <t xml:space="preserve">32.6242218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6426734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3751831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6372909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4804840087891</t>
   </si>
   <si>
     <t xml:space="preserve">29.2760219573975</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9493522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0877075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7279834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6449718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8478908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3367500305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1614990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8294429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1376667022705</t>
+    <t xml:space="preserve">29.9493541717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0877094268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6080760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7279815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6449680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8478927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3367481231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1615009307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8294448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1376686096191</t>
   </si>
   <si>
     <t xml:space="preserve">29.6173000335693</t>
@@ -2417,67 +2420,67 @@
     <t xml:space="preserve">30.0139179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1983947753906</t>
+    <t xml:space="preserve">30.1983909606934</t>
   </si>
   <si>
     <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6134548187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1945514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8033199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5450496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4251480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0285224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7241458892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6726379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9770221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7741031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6910877227783</t>
+    <t xml:space="preserve">30.6134605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1945495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.803316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5450553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.425142288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0285243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.724142074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6726398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9770240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7741012573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">29.9678001403809</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3621139526367</t>
+    <t xml:space="preserve">33.3621215820312</t>
   </si>
   <si>
     <t xml:space="preserve">32.7441329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">31.98779296875</t>
+    <t xml:space="preserve">31.9877891540527</t>
   </si>
   <si>
     <t xml:space="preserve">32.4397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5504417419434</t>
+    <t xml:space="preserve">32.5504379272461</t>
   </si>
   <si>
     <t xml:space="preserve">32.310619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2291488647461</t>
+    <t xml:space="preserve">34.2291526794434</t>
   </si>
   <si>
     <t xml:space="preserve">34.7180061340332</t>
@@ -2495,7 +2498,7 @@
     <t xml:space="preserve">33.6111602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7218437194824</t>
+    <t xml:space="preserve">33.7218475341797</t>
   </si>
   <si>
     <t xml:space="preserve">33.980110168457</t>
@@ -2507,30 +2510,27 @@
     <t xml:space="preserve">34.819465637207</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5243110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0462188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1476783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0239334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6826553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7787322998047</t>
+    <t xml:space="preserve">34.5243072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0462226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1476745605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6826477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7787284851074</t>
   </si>
   <si>
     <t xml:space="preserve">35.6772689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8156318664551</t>
-  </si>
-  <si>
     <t xml:space="preserve">38.1492195129395</t>
   </si>
   <si>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">38.093879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8171730041504</t>
+    <t xml:space="preserve">37.8171691894531</t>
   </si>
   <si>
     <t xml:space="preserve">37.7249336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1530609130859</t>
+    <t xml:space="preserve">37.1530570983887</t>
   </si>
   <si>
     <t xml:space="preserve">37.3006362915039</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">37.0423774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1899528503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.715705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6234703063965</t>
+    <t xml:space="preserve">37.1899566650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7157096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6234664916992</t>
   </si>
   <si>
     <t xml:space="preserve">37.4758949279785</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">36.9593658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4389991760254</t>
+    <t xml:space="preserve">37.4389953613281</t>
   </si>
   <si>
     <t xml:space="preserve">36.9778137207031</t>
@@ -2594,22 +2594,22 @@
     <t xml:space="preserve">37.5496826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6326904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3613662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4036483764648</t>
+    <t xml:space="preserve">37.6326942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3613624572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4036407470703</t>
   </si>
   <si>
     <t xml:space="preserve">39.3667526245117</t>
   </si>
   <si>
-    <t xml:space="preserve">39.385196685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1399993896484</t>
+    <t xml:space="preserve">39.3852005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1399955749512</t>
   </si>
   <si>
     <t xml:space="preserve">37.2914161682129</t>
@@ -2618,55 +2618,55 @@
     <t xml:space="preserve">38.2691307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2084083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4021072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8432998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2360725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4889526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9724235534668</t>
+    <t xml:space="preserve">37.2084007263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.402099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8432960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2360763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4889602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9724273681641</t>
   </si>
   <si>
     <t xml:space="preserve">36.3690490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8579063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2729682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5166244506836</t>
+    <t xml:space="preserve">36.8579025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2729759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5166282653809</t>
   </si>
   <si>
     <t xml:space="preserve">35.7049407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6457595825195</t>
+    <t xml:space="preserve">36.6457557678223</t>
   </si>
   <si>
     <t xml:space="preserve">35.649600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2583656311035</t>
+    <t xml:space="preserve">36.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">35.1422958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2898712158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0093193054199</t>
+    <t xml:space="preserve">35.2898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0093269348145</t>
   </si>
   <si>
     <t xml:space="preserve">34.2660446166992</t>
@@ -2675,19 +2675,19 @@
     <t xml:space="preserve">32.4305267333984</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4028587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9286079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5227661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4858741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1023139953613</t>
+    <t xml:space="preserve">32.4028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9286117553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.522762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4858665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1023197174072</t>
   </si>
   <si>
     <t xml:space="preserve">28.1507320404053</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">27.8002300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0807838439941</t>
+    <t xml:space="preserve">27.0807819366455</t>
   </si>
   <si>
     <t xml:space="preserve">23.9816188812256</t>
@@ -2705,103 +2705,103 @@
     <t xml:space="preserve">27.3943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2637100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9039897918701</t>
+    <t xml:space="preserve">25.2637138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9039878845215</t>
   </si>
   <si>
     <t xml:space="preserve">25.3651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9224338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9977684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3797817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9309043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4528160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.729528427124</t>
+    <t xml:space="preserve">24.9224376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9977703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3797798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9309062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4528121948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7295265197754</t>
   </si>
   <si>
     <t xml:space="preserve">30.7056941986084</t>
   </si>
   <si>
-    <t xml:space="preserve">29.875560760498</t>
+    <t xml:space="preserve">29.8755626678467</t>
   </si>
   <si>
     <t xml:space="preserve">29.5158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6857051849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6688003540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1061553955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2998523712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0838661193848</t>
+    <t xml:space="preserve">28.6857032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6688022613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1061534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2998504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.083869934082</t>
   </si>
   <si>
     <t xml:space="preserve">30.6319065093994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8402118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8901710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5765647888184</t>
+    <t xml:space="preserve">31.8402137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5135383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.890172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.576566696167</t>
   </si>
   <si>
     <t xml:space="preserve">31.5081577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7756423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2721824645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.770263671875</t>
+    <t xml:space="preserve">31.7756443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.272180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7702617645264</t>
   </si>
   <si>
     <t xml:space="preserve">29.9124565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2352886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7833290100098</t>
+    <t xml:space="preserve">30.2352867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7833271026611</t>
   </si>
   <si>
     <t xml:space="preserve">30.2260627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4143772125244</t>
+    <t xml:space="preserve">29.4143753051758</t>
   </si>
   <si>
     <t xml:space="preserve">28.7041530609131</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6211414337158</t>
+    <t xml:space="preserve">28.6211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">29.7372093200684</t>
@@ -2816,61 +2816,61 @@
     <t xml:space="preserve">29.3682594299316</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7979316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.39208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1630363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8532791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0746402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955554962158</t>
+    <t xml:space="preserve">30.7979335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3920917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1630401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8532752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955535888672</t>
   </si>
   <si>
     <t xml:space="preserve">32.0339088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3790283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2406711578369</t>
+    <t xml:space="preserve">31.0377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3790264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2406692504883</t>
   </si>
   <si>
     <t xml:space="preserve">31.9693431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4950942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7625770568848</t>
+    <t xml:space="preserve">32.4950904846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.762580871582</t>
   </si>
   <si>
     <t xml:space="preserve">33.0577392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0892486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7203044891357</t>
+    <t xml:space="preserve">32.0892524719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7202968597412</t>
   </si>
   <si>
     <t xml:space="preserve">32.126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3974742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6003913879395</t>
+    <t xml:space="preserve">31.3974781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6003932952881</t>
   </si>
   <si>
     <t xml:space="preserve">31.9508972167969</t>
@@ -2879,19 +2879,19 @@
     <t xml:space="preserve">31.2591190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4897079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3513603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6503524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654182434082</t>
+    <t xml:space="preserve">31.9601192474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4897117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3513584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.650354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654201507568</t>
   </si>
   <si>
     <t xml:space="preserve">30.9824047088623</t>
@@ -2900,37 +2900,37 @@
     <t xml:space="preserve">31.0100746154785</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5950088500977</t>
+    <t xml:space="preserve">30.5950107574463</t>
   </si>
   <si>
     <t xml:space="preserve">30.0692596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0969333648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4236011505127</t>
+    <t xml:space="preserve">30.0969295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4236030578613</t>
   </si>
   <si>
     <t xml:space="preserve">29.5804042816162</t>
   </si>
   <si>
-    <t xml:space="preserve">29.488166809082</t>
+    <t xml:space="preserve">29.4881687164307</t>
   </si>
   <si>
     <t xml:space="preserve">30.8809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3275279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0784854888916</t>
+    <t xml:space="preserve">30.3275260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0784873962402</t>
   </si>
   <si>
     <t xml:space="preserve">29.5342864990234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.552734375</t>
+    <t xml:space="preserve">29.5527362823486</t>
   </si>
   <si>
     <t xml:space="preserve">29.8571147918701</t>
@@ -2945,49 +2945,49 @@
     <t xml:space="preserve">29.884786605835</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9585742950439</t>
+    <t xml:space="preserve">29.9585762023926</t>
   </si>
   <si>
     <t xml:space="preserve">31.1484355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7940921783447</t>
+    <t xml:space="preserve">31.7940940856934</t>
   </si>
   <si>
     <t xml:space="preserve">32.1814842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4766426086426</t>
+    <t xml:space="preserve">32.4766387939453</t>
   </si>
   <si>
     <t xml:space="preserve">33.8878746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9854927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3306083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.66650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4674224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0431289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4489784240723</t>
+    <t xml:space="preserve">34.9854965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3306121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6665077209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4674186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0431327819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4489822387695</t>
   </si>
   <si>
     <t xml:space="preserve">32.2644996643066</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8455963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7164611816406</t>
+    <t xml:space="preserve">32.8455924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7164649963379</t>
   </si>
   <si>
     <t xml:space="preserve">33.6019401550293</t>
@@ -2996,28 +2996,28 @@
     <t xml:space="preserve">33.8509750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">33.223762512207</t>
+    <t xml:space="preserve">33.2237663269043</t>
   </si>
   <si>
     <t xml:space="preserve">33.5650405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9339904785156</t>
+    <t xml:space="preserve">33.9339942932129</t>
   </si>
   <si>
     <t xml:space="preserve">34.0354537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6057739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9432106018066</t>
+    <t xml:space="preserve">32.6057815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9432144165039</t>
   </si>
   <si>
     <t xml:space="preserve">34.9485969543457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4043960571289</t>
+    <t xml:space="preserve">34.4044036865234</t>
   </si>
   <si>
     <t xml:space="preserve">35.9170875549316</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">33.2053184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5465927124023</t>
+    <t xml:space="preserve">33.5465965270996</t>
   </si>
   <si>
     <t xml:space="preserve">34.8840293884277</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6349906921387</t>
+    <t xml:space="preserve">34.6349868774414</t>
   </si>
   <si>
     <t xml:space="preserve">36.5996398925781</t>
@@ -3056,19 +3056,19 @@
     <t xml:space="preserve">36.6088638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7195510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8909606933594</t>
+    <t xml:space="preserve">36.7195472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8909568786621</t>
   </si>
   <si>
     <t xml:space="preserve">37.8725090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6142463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4482192993164</t>
+    <t xml:space="preserve">37.6142425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4482154846191</t>
   </si>
   <si>
     <t xml:space="preserve">38.4536018371582</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">38.7118682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6473045349121</t>
+    <t xml:space="preserve">38.6472969055176</t>
   </si>
   <si>
     <t xml:space="preserve">38.241455078125</t>
@@ -3089,19 +3089,19 @@
     <t xml:space="preserve">37.9001808166504</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4720497131348</t>
+    <t xml:space="preserve">38.472053527832</t>
   </si>
   <si>
     <t xml:space="preserve">39.2837371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">39.846378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5842781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4144096374512</t>
+    <t xml:space="preserve">39.8463821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5842819213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4144134521484</t>
   </si>
   <si>
     <t xml:space="preserve">42.9916648864746</t>
@@ -3110,46 +3110,46 @@
     <t xml:space="preserve">42.8533058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.886360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1630783081055</t>
+    <t xml:space="preserve">43.8863677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1630744934082</t>
   </si>
   <si>
     <t xml:space="preserve">45.0116500854492</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9286346435547</t>
+    <t xml:space="preserve">44.9286422729492</t>
   </si>
   <si>
     <t xml:space="preserve">45.1961288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7349472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8679122924805</t>
+    <t xml:space="preserve">44.7349433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.867919921875</t>
   </si>
   <si>
     <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4674530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8694610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3952102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2476348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1184959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8456268310547</t>
+    <t xml:space="preserve">44.467456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.395206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2476272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1184997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8456230163574</t>
   </si>
   <si>
     <t xml:space="preserve">44.864070892334</t>
@@ -3164,16 +3164,16 @@
     <t xml:space="preserve">44.2737579345703</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3882827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4121170043945</t>
+    <t xml:space="preserve">43.3882789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4121131896973</t>
   </si>
   <si>
     <t xml:space="preserve">44.0708351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6742172241211</t>
+    <t xml:space="preserve">43.6742134094238</t>
   </si>
   <si>
     <t xml:space="preserve">44.6703758239746</t>
@@ -3188,25 +3188,25 @@
     <t xml:space="preserve">45.7403259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6649971008301</t>
+    <t xml:space="preserve">43.6649932861328</t>
   </si>
   <si>
     <t xml:space="preserve">43.5912017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3567695617676</t>
+    <t xml:space="preserve">44.3567733764648</t>
   </si>
   <si>
     <t xml:space="preserve">43.7756767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1999702453613</t>
+    <t xml:space="preserve">44.1999664306641</t>
   </si>
   <si>
     <t xml:space="preserve">44.2091941833496</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1369438171387</t>
+    <t xml:space="preserve">46.1369476318359</t>
   </si>
   <si>
     <t xml:space="preserve">46.8932876586914</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">48.0739212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6496276855469</t>
+    <t xml:space="preserve">47.6496353149414</t>
   </si>
   <si>
     <t xml:space="preserve">47.9447898864746</t>
@@ -3227,43 +3227,43 @@
     <t xml:space="preserve">47.2622375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1477127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7972106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.708812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6534767150879</t>
+    <t xml:space="preserve">48.1477088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7972145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7088165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6534729003906</t>
   </si>
   <si>
     <t xml:space="preserve">49.1807670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8710021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2437934875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0408744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1699981689453</t>
+    <t xml:space="preserve">47.8709983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2437896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0408706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1700019836426</t>
   </si>
   <si>
     <t xml:space="preserve">47.3175773620605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1108169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4613189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6865234375</t>
+    <t xml:space="preserve">48.1108207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4613151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6865272521973</t>
   </si>
   <si>
     <t xml:space="preserve">46.6165771484375</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">45.7034339904785</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8602409362793</t>
+    <t xml:space="preserve">45.860237121582</t>
   </si>
   <si>
     <t xml:space="preserve">46.4136543273926</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">47.3360290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4467124938965</t>
+    <t xml:space="preserve">47.4467086791992</t>
   </si>
   <si>
     <t xml:space="preserve">46.837947845459</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2107353210449</t>
+    <t xml:space="preserve">46.2107315063477</t>
   </si>
   <si>
     <t xml:space="preserve">45.6019706726074</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">45.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2276420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4397811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4859046936035</t>
+    <t xml:space="preserve">44.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4397850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4859008789062</t>
   </si>
   <si>
     <t xml:space="preserve">45.3898239135742</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">45.0762214660645</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8417892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4505577087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5981292724609</t>
+    <t xml:space="preserve">45.8417854309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6573143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.450553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5981330871582</t>
   </si>
   <si>
     <t xml:space="preserve">46.5243377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5020523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3544731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3214225769043</t>
+    <t xml:space="preserve">47.5020561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3544692993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.321418762207</t>
   </si>
   <si>
     <t xml:space="preserve">48.2952880859375</t>
@@ -3347,28 +3347,28 @@
     <t xml:space="preserve">49.3467903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9670791625977</t>
+    <t xml:space="preserve">46.9670753479004</t>
   </si>
   <si>
     <t xml:space="preserve">47.0039749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0593147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4836044311523</t>
+    <t xml:space="preserve">47.0593185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4836082458496</t>
   </si>
   <si>
     <t xml:space="preserve">46.3767585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4282646179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2806816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7234230041504</t>
+    <t xml:space="preserve">47.4282608032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2806854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7234191894531</t>
   </si>
   <si>
     <t xml:space="preserve">46.985523223877</t>
@@ -3377,16 +3377,16 @@
     <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9263458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6642379760742</t>
+    <t xml:space="preserve">47.9263381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">48.4244270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1623153686523</t>
+    <t xml:space="preserve">49.1623191833496</t>
   </si>
   <si>
     <t xml:space="preserve">49.4205856323242</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">50.490291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1228179931641</t>
+    <t xml:space="preserve">51.1228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">51.625114440918</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">53.9877777099609</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0621948242188</t>
+    <t xml:space="preserve">54.0621871948242</t>
   </si>
   <si>
     <t xml:space="preserve">53.4482688903809</t>
@@ -3416,16 +3416,16 @@
     <t xml:space="preserve">53.6343078613281</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1180000305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2296257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1039924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8063316345215</t>
+    <t xml:space="preserve">54.1180038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.229621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1039962768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">53.5784950256348</t>
@@ -3434,13 +3434,13 @@
     <t xml:space="preserve">52.8343505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8715591430664</t>
+    <t xml:space="preserve">52.8715629577637</t>
   </si>
   <si>
     <t xml:space="preserve">53.132007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8947601318359</t>
+    <t xml:space="preserve">53.8947563171387</t>
   </si>
   <si>
     <t xml:space="preserve">54.2482261657715</t>
@@ -3452,112 +3452,112 @@
     <t xml:space="preserve">54.043586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1738128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2110214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.225025177002</t>
+    <t xml:space="preserve">54.1738166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2110176086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2250289916992</t>
   </si>
   <si>
     <t xml:space="preserve">53.6901206970215</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5971031188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0761985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4668769836426</t>
+    <t xml:space="preserve">53.5970993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0762023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4668731689453</t>
   </si>
   <si>
     <t xml:space="preserve">53.3180465698242</t>
   </si>
   <si>
-    <t xml:space="preserve">52.815746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0389938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3366546630859</t>
+    <t xml:space="preserve">52.8157424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.038990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3366508483887</t>
   </si>
   <si>
     <t xml:space="preserve">51.4762840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4250717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2808380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7273254394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3598518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7785415649414</t>
+    <t xml:space="preserve">52.4250679016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.280834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7273216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3598480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7785453796387</t>
   </si>
   <si>
     <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1878204345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7459297180176</t>
+    <t xml:space="preserve">53.1878242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7459259033203</t>
   </si>
   <si>
     <t xml:space="preserve">54.6203002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4388580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7551193237305</t>
+    <t xml:space="preserve">55.4388618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7551231384277</t>
   </si>
   <si>
     <t xml:space="preserve">55.4946746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8761558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.950569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6389083862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6947174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5272827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5876922607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9271507263184</t>
+    <t xml:space="preserve">53.8761520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9505729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6389045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6947135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5272789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5876884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9271545410156</t>
   </si>
   <si>
     <t xml:space="preserve">57.2992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">57.727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5596771240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4248504638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8667488098145</t>
+    <t xml:space="preserve">57.7271118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5596809387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4248542785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8667449951172</t>
   </si>
   <si>
     <t xml:space="preserve">54.3970565795898</t>
@@ -3566,28 +3566,28 @@
     <t xml:space="preserve">51.067008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1554260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8437614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7693519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3972778320312</t>
+    <t xml:space="preserve">50.1554222106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8437576293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7693481445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3972702026367</t>
   </si>
   <si>
     <t xml:space="preserve">50.5461006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8065528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4158744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0298004150391</t>
+    <t xml:space="preserve">50.8065567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4158782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0297966003418</t>
   </si>
   <si>
     <t xml:space="preserve">50.9925918579102</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">50.2484436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1042098999023</t>
+    <t xml:space="preserve">51.1042137145996</t>
   </si>
   <si>
     <t xml:space="preserve">51.718132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4018707275391</t>
+    <t xml:space="preserve">51.4018669128418</t>
   </si>
   <si>
     <t xml:space="preserve">51.3274574279785</t>
@@ -3614,31 +3614,31 @@
     <t xml:space="preserve">50.7879486083984</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1648330688477</t>
+    <t xml:space="preserve">48.1648368835449</t>
   </si>
   <si>
     <t xml:space="preserve">48.0904197692871</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3182640075684</t>
+    <t xml:space="preserve">49.3182601928711</t>
   </si>
   <si>
     <t xml:space="preserve">48.0532150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0020027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5647048950195</t>
+    <t xml:space="preserve">49.0019989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5647087097168</t>
   </si>
   <si>
     <t xml:space="preserve">51.3832702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1600227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0624084472656</t>
+    <t xml:space="preserve">51.1600189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0624046325684</t>
   </si>
   <si>
     <t xml:space="preserve">48.6113204956055</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">49.2438468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7553405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.978588104248</t>
+    <t xml:space="preserve">51.7553367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9785842895508</t>
   </si>
   <si>
     <t xml:space="preserve">52.9831771850586</t>
@@ -3662,19 +3662,19 @@
     <t xml:space="preserve">52.4622802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4714698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5690879821777</t>
+    <t xml:space="preserve">54.713321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4714736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5690841674805</t>
   </si>
   <si>
     <t xml:space="preserve">56.0341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7597236633301</t>
+    <t xml:space="preserve">56.7597198486328</t>
   </si>
   <si>
     <t xml:space="preserve">56.8341331481934</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">56.3876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9783668518066</t>
+    <t xml:space="preserve">55.9783706665039</t>
   </si>
   <si>
     <t xml:space="preserve">56.9457588195801</t>
@@ -3692,88 +3692,88 @@
     <t xml:space="preserve">57.7829208374023</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4386444091797</t>
+    <t xml:space="preserve">59.438648223877</t>
   </si>
   <si>
     <t xml:space="preserve">58.5084648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2340049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.652473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8803176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4012184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106292724609</t>
+    <t xml:space="preserve">59.234001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6524772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8803215026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4012222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106254577637</t>
   </si>
   <si>
     <t xml:space="preserve">60.7409019470215</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8199157714844</t>
+    <t xml:space="preserve">61.8199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">62.9361305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">63.754695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.331413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5686531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0663604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9593353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5408554077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9129295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3222045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3410301208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.089771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6060791015625</t>
+    <t xml:space="preserve">63.7546920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3314056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2197875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5686492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0663528442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5408592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9129219055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3222160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3410339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0897674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6060829162598</t>
   </si>
   <si>
     <t xml:space="preserve">61.0385589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9455375671387</t>
+    <t xml:space="preserve">60.9455337524414</t>
   </si>
   <si>
     <t xml:space="preserve">60.5920715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">61.6896820068359</t>
+    <t xml:space="preserve">61.6896858215332</t>
   </si>
   <si>
     <t xml:space="preserve">64.4430236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">62.4710426330566</t>
+    <t xml:space="preserve">62.4710388183594</t>
   </si>
   <si>
     <t xml:space="preserve">62.1547737121582</t>
@@ -3782,19 +3782,19 @@
     <t xml:space="preserve">61.4478340148926</t>
   </si>
   <si>
-    <t xml:space="preserve">60.629280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6758995056152</t>
+    <t xml:space="preserve">60.6292762756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.675895690918</t>
   </si>
   <si>
     <t xml:space="preserve">60.182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">58.7503128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8061218261719</t>
+    <t xml:space="preserve">58.7503051757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8061256408691</t>
   </si>
   <si>
     <t xml:space="preserve">58.2294082641602</t>
@@ -3803,19 +3803,19 @@
     <t xml:space="preserve">57.8573341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3224220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5642738342285</t>
+    <t xml:space="preserve">58.3224296569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5642776489258</t>
   </si>
   <si>
     <t xml:space="preserve">59.7549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0711669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.5502662658691</t>
+    <t xml:space="preserve">60.071174621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.5502624511719</t>
   </si>
   <si>
     <t xml:space="preserve">59.810718536377</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">60.4618453979492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269409179688</t>
+    <t xml:space="preserve">60.9269371032715</t>
   </si>
   <si>
     <t xml:space="preserve">58.4154434204102</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">56.9643592834473</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1644058227539</t>
+    <t xml:space="preserve">56.1644020080566</t>
   </si>
   <si>
     <t xml:space="preserve">55.7923278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8807487487793</t>
+    <t xml:space="preserve">54.8807525634766</t>
   </si>
   <si>
     <t xml:space="preserve">52.8901634216309</t>
@@ -3860,43 +3860,43 @@
     <t xml:space="preserve">51.6995315551758</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2716407775879</t>
+    <t xml:space="preserve">51.2716445922852</t>
   </si>
   <si>
     <t xml:space="preserve">52.3134536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5366897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5693016052246</t>
+    <t xml:space="preserve">52.536693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5693054199219</t>
   </si>
   <si>
     <t xml:space="preserve">52.4064674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">54.899356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.271427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8389472961426</t>
+    <t xml:space="preserve">54.8993606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2714233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8389511108398</t>
   </si>
   <si>
     <t xml:space="preserve">54.0993995666504</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6437187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6391143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1274108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2344360351562</t>
+    <t xml:space="preserve">51.6437149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6391181945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1274147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">50.9739837646484</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">47.1230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9464073181152</t>
+    <t xml:space="preserve">44.946403503418</t>
   </si>
   <si>
     <t xml:space="preserve">41.8768043518066</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">42.1465606689453</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4954299926758</t>
+    <t xml:space="preserve">41.495433807373</t>
   </si>
   <si>
     <t xml:space="preserve">44.974308013916</t>
@@ -3935,19 +3935,19 @@
     <t xml:space="preserve">43.9976196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6208457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6487464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2441711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.709156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7881660461426</t>
+    <t xml:space="preserve">44.6208419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6487503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2441749572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7091522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7881622314453</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
@@ -3959,25 +3959,25 @@
     <t xml:space="preserve">46.2951698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8207702636719</t>
+    <t xml:space="preserve">45.8207740783691</t>
   </si>
   <si>
     <t xml:space="preserve">46.2021522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2765693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8717803955078</t>
+    <t xml:space="preserve">46.2765655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8717765808105</t>
   </si>
   <si>
     <t xml:space="preserve">47.1974487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9275817871094</t>
+    <t xml:space="preserve">47.178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9275856018066</t>
   </si>
   <si>
     <t xml:space="preserve">49.2810554504395</t>
@@ -3986,31 +3986,31 @@
     <t xml:space="preserve">46.9556007385254</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9882125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1603469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0254211425781</t>
+    <t xml:space="preserve">45.988208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4392967224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1603507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0254173278809</t>
   </si>
   <si>
     <t xml:space="preserve">46.4533004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0300140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1835479736328</t>
+    <t xml:space="preserve">47.0300102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1835517883301</t>
   </si>
   <si>
     <t xml:space="preserve">47.5881233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5277214050293</t>
+    <t xml:space="preserve">46.527717590332</t>
   </si>
   <si>
     <t xml:space="preserve">44.3510894775391</t>
@@ -4019,34 +4019,34 @@
     <t xml:space="preserve">43.8301849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">45.430103302002</t>
+    <t xml:space="preserve">45.4300994873047</t>
   </si>
   <si>
     <t xml:space="preserve">46.2672653198242</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7695579528809</t>
+    <t xml:space="preserve">46.7695617675781</t>
   </si>
   <si>
     <t xml:space="preserve">45.5696296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6115417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9604072570801</t>
+    <t xml:space="preserve">44.6115379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9604110717773</t>
   </si>
   <si>
     <t xml:space="preserve">41.4861259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7373847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9095230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8676109313965</t>
+    <t xml:space="preserve">39.7373809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9095268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8676147460938</t>
   </si>
   <si>
     <t xml:space="preserve">41.6163520812988</t>
@@ -4055,13 +4055,13 @@
     <t xml:space="preserve">40.8070907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1930694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2814865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1093521118164</t>
+    <t xml:space="preserve">42.1930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2814903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1093482971191</t>
   </si>
   <si>
     <t xml:space="preserve">40.6489639282227</t>
@@ -4070,13 +4070,13 @@
     <t xml:space="preserve">40.0908508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3095016479492</t>
+    <t xml:space="preserve">39.309497833252</t>
   </si>
   <si>
     <t xml:space="preserve">39.8945198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5640754699707</t>
+    <t xml:space="preserve">38.5640716552734</t>
   </si>
   <si>
     <t xml:space="preserve">38.6018180847168</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">42.3572616577148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1779823303223</t>
+    <t xml:space="preserve">42.177978515625</t>
   </si>
   <si>
     <t xml:space="preserve">43.6499633789062</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801254272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.234790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.111930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2155303955078</t>
+    <t xml:space="preserve">43.4801216125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2347869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1119346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2155342102051</t>
   </si>
   <si>
     <t xml:space="preserve">38.6489944458008</t>
@@ -4118,58 +4118,58 @@
     <t xml:space="preserve">37.2147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2145652770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5166969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3747787475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0917015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9690361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9973449707031</t>
+    <t xml:space="preserve">36.2145614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5167007446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3747749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0916976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9690399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9973487854004</t>
   </si>
   <si>
     <t xml:space="preserve">34.9312934875488</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6767234802246</t>
+    <t xml:space="preserve">35.6767196655273</t>
   </si>
   <si>
     <t xml:space="preserve">37.4600868225098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7054176330566</t>
+    <t xml:space="preserve">37.7054138183594</t>
   </si>
   <si>
     <t xml:space="preserve">38.394229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4980239868164</t>
+    <t xml:space="preserve">38.4980201721191</t>
   </si>
   <si>
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3751678466797</t>
+    <t xml:space="preserve">38.0639762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3751640319824</t>
   </si>
   <si>
     <t xml:space="preserve">38.8943290710449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0547370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1396598815918</t>
+    <t xml:space="preserve">39.0547332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1396560668945</t>
   </si>
   <si>
     <t xml:space="preserve">38.5263328552246</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">40.3474349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.753173828125</t>
+    <t xml:space="preserve">40.7531776428223</t>
   </si>
   <si>
     <t xml:space="preserve">41.1494789123535</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">39.6586265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7248687744141</t>
+    <t xml:space="preserve">40.7248725891113</t>
   </si>
   <si>
     <t xml:space="preserve">43.9990882873535</t>
@@ -4223,43 +4223,43 @@
     <t xml:space="preserve">45.0464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3389739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5278854370117</t>
+    <t xml:space="preserve">45.3389701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5278816223145</t>
   </si>
   <si>
     <t xml:space="preserve">46.5184440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4995765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8579406738281</t>
+    <t xml:space="preserve">46.4995727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8579368591309</t>
   </si>
   <si>
     <t xml:space="preserve">46.7165946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9524917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5939331054688</t>
+    <t xml:space="preserve">46.9524879455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.593936920166</t>
   </si>
   <si>
     <t xml:space="preserve">46.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0089149475098</t>
+    <t xml:space="preserve">46.0089111328125</t>
   </si>
   <si>
     <t xml:space="preserve">46.7543411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1315803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0273971557617</t>
+    <t xml:space="preserve">46.1315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0273933410645</t>
   </si>
   <si>
     <t xml:space="preserve">44.8388748168945</t>
@@ -4283,25 +4283,25 @@
     <t xml:space="preserve">42.1213684082031</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0456848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2251625061035</t>
+    <t xml:space="preserve">41.0456886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2251586914062</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1777839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3948097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6967506408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4704895019531</t>
+    <t xml:space="preserve">41.1777877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3948059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6967544555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4704856872559</t>
   </si>
   <si>
     <t xml:space="preserve">42.998893737793</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">42.0175704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7158241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5646514892578</t>
+    <t xml:space="preserve">42.7158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5646553039551</t>
   </si>
   <si>
     <t xml:space="preserve">40.9230194091797</t>
@@ -4322,25 +4322,25 @@
     <t xml:space="preserve">41.4891700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8005485534668</t>
+    <t xml:space="preserve">41.8005523681641</t>
   </si>
   <si>
     <t xml:space="preserve">42.461051940918</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9511337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2623252868652</t>
+    <t xml:space="preserve">39.9511375427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.262321472168</t>
   </si>
   <si>
     <t xml:space="preserve">40.6210746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5644645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0645561218262</t>
+    <t xml:space="preserve">40.5644607543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0645637512207</t>
   </si>
   <si>
     <t xml:space="preserve">39.8095970153809</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">39.9983139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9794387817383</t>
+    <t xml:space="preserve">39.9794425964355</t>
   </si>
   <si>
     <t xml:space="preserve">43.2064819335938</t>
@@ -4358,34 +4358,34 @@
     <t xml:space="preserve">42.8384895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9703903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5174751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8665962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0271987915039</t>
+    <t xml:space="preserve">41.9703941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5174789428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8666000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0272026062012</t>
   </si>
   <si>
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252540588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8009338378906</t>
+    <t xml:space="preserve">42.7252578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8009376525879</t>
   </si>
   <si>
     <t xml:space="preserve">44.0557022094727</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7160186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6690330505371</t>
+    <t xml:space="preserve">43.7160148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6690292358398</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4394,34 +4394,34 @@
     <t xml:space="preserve">43.4329414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1693229675293</t>
+    <t xml:space="preserve">46.169319152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.6692276000977</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7443237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.734691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2249641418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6873207092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0173797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8756484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8290481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9422798156738</t>
+    <t xml:space="preserve">43.7443199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7346954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.224967956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6873168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0173835754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8756446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8290519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9422760009766</t>
   </si>
   <si>
     <t xml:space="preserve">43.8292465209961</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7732124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6131896972656</t>
+    <t xml:space="preserve">46.7732086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6131935119629</t>
   </si>
   <si>
     <t xml:space="preserve">47.6129951477051</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">47.1978225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0657196044922</t>
+    <t xml:space="preserve">47.0657234191895</t>
   </si>
   <si>
     <t xml:space="preserve">47.0185432434082</t>
@@ -4454,10 +4454,10 @@
     <t xml:space="preserve">45.6314811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6031761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5654335021973</t>
+    <t xml:space="preserve">45.6031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5654296875</t>
   </si>
   <si>
     <t xml:space="preserve">45.4144592285156</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">45.2917938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8200035095215</t>
+    <t xml:space="preserve">44.8199996948242</t>
   </si>
   <si>
     <t xml:space="preserve">46.2825508117676</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">45.546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5937385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7539520263672</t>
+    <t xml:space="preserve">45.5937347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7539558410645</t>
   </si>
   <si>
     <t xml:space="preserve">45.7447090148926</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">47.2544364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">48.745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6316757202148</t>
+    <t xml:space="preserve">48.7452926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6316680908203</t>
   </si>
   <si>
     <t xml:space="preserve">46.4146499633789</t>
@@ -4505,22 +4505,22 @@
     <t xml:space="preserve">44.9049263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.150447845459</t>
+    <t xml:space="preserve">46.1504516601562</t>
   </si>
   <si>
     <t xml:space="preserve">45.3861503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6788558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3110466003418</t>
+    <t xml:space="preserve">46.6788520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3110504150391</t>
   </si>
   <si>
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017082214355</t>
+    <t xml:space="preserve">47.8017120361328</t>
   </si>
   <si>
     <t xml:space="preserve">47.5563812255859</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">48.5565757751465</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3869247436523</t>
+    <t xml:space="preserve">49.3869285583496</t>
   </si>
   <si>
     <t xml:space="preserve">49.7077407836914</t>
@@ -4541,34 +4541,34 @@
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814796447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8779754638672</t>
+    <t xml:space="preserve">50.4814758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8779716491699</t>
   </si>
   <si>
     <t xml:space="preserve">52.3497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8781661987305</t>
+    <t xml:space="preserve">52.8781700134277</t>
   </si>
   <si>
     <t xml:space="preserve">53.0857543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9157180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0480117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3310890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1046295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2555999755859</t>
+    <t xml:space="preserve">51.915714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0480155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3310852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1046257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2555961608887</t>
   </si>
   <si>
     <t xml:space="preserve">54.5199928283691</t>
@@ -4577,58 +4577,58 @@
     <t xml:space="preserve">54.0859489440918</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9727210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8406181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2182426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4446983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1991806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0293350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4254455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1987915039062</t>
+    <t xml:space="preserve">53.9727172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2182464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4447021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1991767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0293312072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4254417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.198787689209</t>
   </si>
   <si>
     <t xml:space="preserve">53.0291404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5009346008301</t>
+    <t xml:space="preserve">53.5009307861328</t>
   </si>
   <si>
     <t xml:space="preserve">53.9349784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8785514831543</t>
+    <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
     <t xml:space="preserve">54.4067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">54.444507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.350341796875</t>
+    <t xml:space="preserve">54.4445114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3503456115723</t>
   </si>
   <si>
     <t xml:space="preserve">55.3125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9729080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.46337890625</t>
+    <t xml:space="preserve">54.9729118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4633827209473</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106544494629</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">56.3316650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9544296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3507308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1431465148926</t>
+    <t xml:space="preserve">56.9544258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3507347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1431427001953</t>
   </si>
   <si>
     <t xml:space="preserve">57.7470359802246</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">54.8974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0676574707031</t>
+    <t xml:space="preserve">57.0676612854004</t>
   </si>
   <si>
     <t xml:space="preserve">55.2748565673828</t>
@@ -4676,16 +4676,16 @@
     <t xml:space="preserve">56.2184371948242</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2939224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5017013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9546241760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1433372497559</t>
+    <t xml:space="preserve">56.2939262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5017051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9546203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1433410644531</t>
   </si>
   <si>
     <t xml:space="preserve">57.2186317443848</t>
@@ -4700,13 +4700,13 @@
     <t xml:space="preserve">58.8982009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9550094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1059875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0116271972656</t>
+    <t xml:space="preserve">59.9550132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1059837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0116233825684</t>
   </si>
   <si>
     <t xml:space="preserve">60.6155128479004</t>
@@ -4715,76 +4715,76 @@
     <t xml:space="preserve">59.6908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8417816162109</t>
+    <t xml:space="preserve">59.8417778015137</t>
   </si>
   <si>
     <t xml:space="preserve">59.4266052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0686225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.219596862793</t>
+    <t xml:space="preserve">62.0686264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2196044921875</t>
   </si>
   <si>
     <t xml:space="preserve">60.9929466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8044204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2007255554199</t>
+    <t xml:space="preserve">61.8044242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2007293701172</t>
   </si>
   <si>
     <t xml:space="preserve">63.1443061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4085121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8614311218262</t>
+    <t xml:space="preserve">63.4085006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8614273071289</t>
   </si>
   <si>
     <t xml:space="preserve">63.7293281555176</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9935264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3707695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896369934082</t>
+    <t xml:space="preserve">63.993522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3707656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896331787109</t>
   </si>
   <si>
     <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5028648376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.993335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4649238586426</t>
+    <t xml:space="preserve">63.5028686523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9933395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4649276733398</t>
   </si>
   <si>
     <t xml:space="preserve">61.8987808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0122108459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9178504943848</t>
+    <t xml:space="preserve">63.01220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9178466796875</t>
   </si>
   <si>
     <t xml:space="preserve">61.5024795532227</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5968360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8608474731445</t>
+    <t xml:space="preserve">61.5968322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8608436584473</t>
   </si>
   <si>
     <t xml:space="preserve">60.7287483215332</t>
@@ -4805,19 +4805,19 @@
     <t xml:space="preserve">60.8631858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2293930053711</t>
+    <t xml:space="preserve">60.2293968200684</t>
   </si>
   <si>
     <t xml:space="preserve">60.9784202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8055686950684</t>
+    <t xml:space="preserve">60.8055648803711</t>
   </si>
   <si>
     <t xml:space="preserve">59.4227523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8042678833008</t>
+    <t xml:space="preserve">61.804271697998</t>
   </si>
   <si>
     <t xml:space="preserve">60.9015960693359</t>
@@ -4826,16 +4826,16 @@
     <t xml:space="preserve">61.2665061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.4982719421387</t>
+    <t xml:space="preserve">60.4982757568359</t>
   </si>
   <si>
     <t xml:space="preserve">61.9963264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1102638244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.071849822998</t>
+    <t xml:space="preserve">63.1102676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">62.898998260498</t>
@@ -4856,7 +4856,7 @@
     <t xml:space="preserve">60.9976272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9605102539062</t>
+    <t xml:space="preserve">59.9605140686035</t>
   </si>
   <si>
     <t xml:space="preserve">59.8068656921387</t>
@@ -4871,22 +4871,22 @@
     <t xml:space="preserve">60.3638343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8247756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4214477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7671546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4022445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.865779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.153865814209</t>
+    <t xml:space="preserve">60.8247718811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4214515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7671585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4022483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8657836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1538696289062</t>
   </si>
   <si>
     <t xml:space="preserve">60.1717758178711</t>
@@ -4898,10 +4898,10 @@
     <t xml:space="preserve">62.8797950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">63.379150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2831153869629</t>
+    <t xml:space="preserve">63.3791427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2831192016602</t>
   </si>
   <si>
     <t xml:space="preserve">61.4393577575684</t>
@@ -4910,13 +4910,13 @@
     <t xml:space="preserve">60.5750999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5379867553711</t>
+    <t xml:space="preserve">59.5379829406738</t>
   </si>
   <si>
     <t xml:space="preserve">59.3843383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7492523193359</t>
+    <t xml:space="preserve">59.7492485046387</t>
   </si>
   <si>
     <t xml:space="preserve">59.9028968811035</t>
@@ -4925,10 +4925,10 @@
     <t xml:space="preserve">60.3254203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2883148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.302318572998</t>
+    <t xml:space="preserve">59.2883110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3023223876953</t>
   </si>
   <si>
     <t xml:space="preserve">62.783763885498</t>
@@ -4940,25 +4940,25 @@
     <t xml:space="preserve">60.6135101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1922836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3651351928711</t>
+    <t xml:space="preserve">59.1922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3651313781738</t>
   </si>
   <si>
     <t xml:space="preserve">61.4969787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5161781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7850570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9797172546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8439826965332</t>
+    <t xml:space="preserve">61.5161819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7850608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9797210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8439788818359</t>
   </si>
   <si>
     <t xml:space="preserve">60.5558929443359</t>
@@ -4967,7 +4967,7 @@
     <t xml:space="preserve">59.5763969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5571937561035</t>
+    <t xml:space="preserve">59.5571899414062</t>
   </si>
   <si>
     <t xml:space="preserve">59.8836898803711</t>
@@ -4985,28 +4985,28 @@
     <t xml:space="preserve">60.1525688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1333618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1346626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.196174621582</t>
+    <t xml:space="preserve">60.1333656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1346664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1961784362793</t>
   </si>
   <si>
     <t xml:space="preserve">56.080940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1769676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8683815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2153816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7915573120117</t>
+    <t xml:space="preserve">56.1769714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8683776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2153854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7915534973145</t>
   </si>
   <si>
     <t xml:space="preserve">57.4061393737793</t>
@@ -5018,22 +5018,22 @@
     <t xml:space="preserve">55.4087409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">55.447151184082</t>
+    <t xml:space="preserve">55.4471473693848</t>
   </si>
   <si>
     <t xml:space="preserve">54.2948036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1974754333496</t>
+    <t xml:space="preserve">55.1974716186523</t>
   </si>
   <si>
     <t xml:space="preserve">54.0451240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1437492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2218742370605</t>
+    <t xml:space="preserve">52.1437530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2218704223633</t>
   </si>
   <si>
     <t xml:space="preserve">52.3742218017578</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">52.4510459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6431045532227</t>
+    <t xml:space="preserve">52.6431007385254</t>
   </si>
   <si>
     <t xml:space="preserve">53.7954521179199</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">50.7417259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">51.068229675293</t>
+    <t xml:space="preserve">51.0682258605957</t>
   </si>
   <si>
     <t xml:space="preserve">50.8377571105957</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">50.8761711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9337882995605</t>
+    <t xml:space="preserve">50.9337844848633</t>
   </si>
   <si>
     <t xml:space="preserve">51.0106086730957</t>
@@ -5099,22 +5099,22 @@
     <t xml:space="preserve">49.8006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.583667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8237457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9965972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5823707580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1668510437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9747924804688</t>
+    <t xml:space="preserve">46.5836715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8237419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9965934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5823745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1668548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.974796295166</t>
   </si>
   <si>
     <t xml:space="preserve">48.7827339172363</t>
@@ -5132,19 +5132,19 @@
     <t xml:space="preserve">47.4959449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7552223205566</t>
+    <t xml:space="preserve">47.7552261352539</t>
   </si>
   <si>
     <t xml:space="preserve">49.4165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4946479797363</t>
+    <t xml:space="preserve">48.4946517944336</t>
   </si>
   <si>
     <t xml:space="preserve">48.4370307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5701751708984</t>
+    <t xml:space="preserve">49.5701713562012</t>
   </si>
   <si>
     <t xml:space="preserve">48.9363822937012</t>
@@ -5159,16 +5159,16 @@
     <t xml:space="preserve">49.5125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2628784179688</t>
+    <t xml:space="preserve">49.262882232666</t>
   </si>
   <si>
     <t xml:space="preserve">48.7059135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9939994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.859561920166</t>
+    <t xml:space="preserve">48.9940032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8595581054688</t>
   </si>
   <si>
     <t xml:space="preserve">48.6675033569336</t>
@@ -5177,13 +5177,13 @@
     <t xml:space="preserve">49.4549407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8774681091309</t>
+    <t xml:space="preserve">49.8774642944336</t>
   </si>
   <si>
     <t xml:space="preserve">50.2999954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">51.529167175293</t>
+    <t xml:space="preserve">51.5291633605957</t>
   </si>
   <si>
     <t xml:space="preserve">52.4318389892578</t>
@@ -5204,7 +5204,7 @@
     <t xml:space="preserve">52.9696006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5265693664551</t>
+    <t xml:space="preserve">53.5265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">54.0259208679199</t>
@@ -5213,13 +5213,13 @@
     <t xml:space="preserve">53.7762451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7378349304199</t>
+    <t xml:space="preserve">53.7378311157227</t>
   </si>
   <si>
     <t xml:space="preserve">53.3537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4881553649902</t>
+    <t xml:space="preserve">53.4881591796875</t>
   </si>
   <si>
     <t xml:space="preserve">53.4305381774902</t>
@@ -5255,34 +5255,34 @@
     <t xml:space="preserve">49.1092338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4933547973633</t>
+    <t xml:space="preserve">49.493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">49.3973197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8390579223633</t>
+    <t xml:space="preserve">49.839054107666</t>
   </si>
   <si>
     <t xml:space="preserve">49.896671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6020927429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0054168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0246238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4279441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0617332458496</t>
+    <t xml:space="preserve">54.6020965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0054130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0246200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8901824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4279479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0617370605469</t>
   </si>
   <si>
     <t xml:space="preserve">55.8312644958496</t>
@@ -5297,10 +5297,10 @@
     <t xml:space="preserve">57.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0028190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3293190002441</t>
+    <t xml:space="preserve">57.0028228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">60.0373344421387</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">61.1896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5545921325684</t>
+    <t xml:space="preserve">61.5545959472656</t>
   </si>
   <si>
     <t xml:space="preserve">61.1512718200684</t>
@@ -5330,19 +5330,19 @@
     <t xml:space="preserve">64.2626113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3599433898926</t>
+    <t xml:space="preserve">63.3599395751953</t>
   </si>
   <si>
     <t xml:space="preserve">63.9937286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3394317626953</t>
+    <t xml:space="preserve">64.3394393920898</t>
   </si>
   <si>
     <t xml:space="preserve">64.4354629516602</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5686111450195</t>
+    <t xml:space="preserve">65.568603515625</t>
   </si>
   <si>
     <t xml:space="preserve">66.6249237060547</t>
@@ -5351,7 +5351,7 @@
     <t xml:space="preserve">66.8746032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5467987060547</t>
+    <t xml:space="preserve">67.5468063354492</t>
   </si>
   <si>
     <t xml:space="preserve">66.5096969604492</t>
@@ -5360,16 +5360,16 @@
     <t xml:space="preserve">66.4712829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7798767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5301971435547</t>
+    <t xml:space="preserve">65.7798690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5301895141602</t>
   </si>
   <si>
     <t xml:space="preserve">65.4533767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2997207641602</t>
+    <t xml:space="preserve">65.2997283935547</t>
   </si>
   <si>
     <t xml:space="preserve">65.799072265625</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">62.0155372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0539512634277</t>
+    <t xml:space="preserve">62.0539474487305</t>
   </si>
   <si>
     <t xml:space="preserve">61.6122131347656</t>
@@ -5408,28 +5408,28 @@
     <t xml:space="preserve">63.4367599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8413887023926</t>
+    <t xml:space="preserve">63.0334396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8413848876953</t>
   </si>
   <si>
     <t xml:space="preserve">62.668529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2254905700684</t>
+    <t xml:space="preserve">63.2254981994629</t>
   </si>
   <si>
     <t xml:space="preserve">64.1473770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1883888244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3420295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9579162597656</t>
+    <t xml:space="preserve">62.1883850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3420333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9579124450684</t>
   </si>
   <si>
     <t xml:space="preserve">61.573802947998</t>
@@ -30711,7 +30711,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G918" t="s">
-        <v>710</v>
+        <v>765</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30737,7 +30737,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G919" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30763,7 +30763,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G920" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30789,7 +30789,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G921" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30815,7 +30815,7 @@
         <v>33.8600006103516</v>
       </c>
       <c r="G922" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30841,7 +30841,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G923" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -30867,7 +30867,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G924" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30893,7 +30893,7 @@
         <v>35.4599990844727</v>
       </c>
       <c r="G925" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30945,7 +30945,7 @@
         <v>34.4199981689453</v>
       </c>
       <c r="G927" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30997,7 +30997,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G929" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -31023,7 +31023,7 @@
         <v>34</v>
       </c>
       <c r="G930" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -31049,7 +31049,7 @@
         <v>33.939998626709</v>
       </c>
       <c r="G931" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -31075,7 +31075,7 @@
         <v>34.0900001525879</v>
       </c>
       <c r="G932" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -31101,7 +31101,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G933" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -31153,7 +31153,7 @@
         <v>35.060001373291</v>
       </c>
       <c r="G935" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -31179,7 +31179,7 @@
         <v>35.8600006103516</v>
       </c>
       <c r="G936" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -31205,7 +31205,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G937" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -31231,7 +31231,7 @@
         <v>35.4900016784668</v>
       </c>
       <c r="G938" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -31257,7 +31257,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G939" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -31283,7 +31283,7 @@
         <v>35.3699989318848</v>
       </c>
       <c r="G940" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -31309,7 +31309,7 @@
         <v>35.3899993896484</v>
       </c>
       <c r="G941" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -31335,7 +31335,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G942" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -31361,7 +31361,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G943" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -31387,7 +31387,7 @@
         <v>34.1300010681152</v>
       </c>
       <c r="G944" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -31413,7 +31413,7 @@
         <v>31.7399997711182</v>
       </c>
       <c r="G945" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -31439,7 +31439,7 @@
         <v>32.4700012207031</v>
       </c>
       <c r="G946" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -31465,7 +31465,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G947" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -31491,7 +31491,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G948" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -31517,7 +31517,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G949" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -31543,7 +31543,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G950" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -31569,7 +31569,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G951" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -31595,7 +31595,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G952" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -31621,7 +31621,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G953" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -31647,7 +31647,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G954" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -31673,7 +31673,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G955" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31699,7 +31699,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G956" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31725,7 +31725,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31751,7 +31751,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G958" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31777,7 +31777,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G959" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31803,7 +31803,7 @@
         <v>33.189998626709</v>
       </c>
       <c r="G960" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31829,7 +31829,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31855,7 +31855,7 @@
         <v>34.4799995422363</v>
       </c>
       <c r="G962" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31881,7 +31881,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31907,7 +31907,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G964" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31933,7 +31933,7 @@
         <v>33.6399993896484</v>
       </c>
       <c r="G965" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31959,7 +31959,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G966" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31985,7 +31985,7 @@
         <v>32.1699981689453</v>
       </c>
       <c r="G967" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -32011,7 +32011,7 @@
         <v>32.5</v>
       </c>
       <c r="G968" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -32037,7 +32037,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G969" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -32063,7 +32063,7 @@
         <v>32.189998626709</v>
       </c>
       <c r="G970" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -32089,7 +32089,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="G971" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -32115,7 +32115,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G972" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -32141,7 +32141,7 @@
         <v>35.5</v>
       </c>
       <c r="G973" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -32167,7 +32167,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G974" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -32193,7 +32193,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G975" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -32245,7 +32245,7 @@
         <v>35.1699981689453</v>
       </c>
       <c r="G977" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -32271,7 +32271,7 @@
         <v>35.2900009155273</v>
       </c>
       <c r="G978" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -32297,7 +32297,7 @@
         <v>35.0299987792969</v>
       </c>
       <c r="G979" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -32349,7 +32349,7 @@
         <v>37.1100006103516</v>
       </c>
       <c r="G981" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -32375,7 +32375,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G982" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -32401,7 +32401,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -32427,7 +32427,7 @@
         <v>36.9599990844727</v>
       </c>
       <c r="G984" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -32453,7 +32453,7 @@
         <v>36.8699989318848</v>
       </c>
       <c r="G985" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -32479,7 +32479,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G986" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -32505,7 +32505,7 @@
         <v>36.560001373291</v>
       </c>
       <c r="G987" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -32531,7 +32531,7 @@
         <v>36.8400001525879</v>
       </c>
       <c r="G988" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -32557,7 +32557,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G989" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -32583,7 +32583,7 @@
         <v>37.75</v>
       </c>
       <c r="G990" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -32609,7 +32609,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G991" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -32687,7 +32687,7 @@
         <v>39.0800018310547</v>
       </c>
       <c r="G994" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32713,7 +32713,7 @@
         <v>39.189998626709</v>
       </c>
       <c r="G995" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32739,7 +32739,7 @@
         <v>40.1399993896484</v>
       </c>
       <c r="G996" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32765,7 +32765,7 @@
         <v>39.7700004577637</v>
       </c>
       <c r="G997" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32791,7 +32791,7 @@
         <v>38.7900009155273</v>
       </c>
       <c r="G998" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32817,7 +32817,7 @@
         <v>38.6800003051758</v>
       </c>
       <c r="G999" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32843,7 +32843,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G1000" t="s">
-        <v>838</v>
+        <v>502</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -34117,7 +34117,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G1049" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -34351,7 +34351,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G1058" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -34871,7 +34871,7 @@
         <v>34</v>
       </c>
       <c r="G1078" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -35235,7 +35235,7 @@
         <v>34</v>
       </c>
       <c r="G1092" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -35313,7 +35313,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G1095" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -35391,7 +35391,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1098" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -35417,7 +35417,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1099" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -35703,7 +35703,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1110" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -35989,7 +35989,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1121" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -36275,7 +36275,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1132" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -36301,7 +36301,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1133" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -36457,7 +36457,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1139" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -37029,7 +37029,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G1161" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -37237,7 +37237,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G1169" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -37289,7 +37289,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -37445,7 +37445,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G1177" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -37601,7 +37601,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1183" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -37809,7 +37809,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1191" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -37861,7 +37861,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G1193" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -38043,7 +38043,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G1200" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -38303,7 +38303,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G1210" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -38433,7 +38433,7 @@
         <v>36.9599990844727</v>
       </c>
       <c r="G1215" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -38615,7 +38615,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G1222" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -38771,7 +38771,7 @@
         <v>34.1300010681152</v>
       </c>
       <c r="G1228" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -38797,7 +38797,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G1229" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="2174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2175" uniqueCount="2175">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765733718872</t>
+    <t xml:space="preserve">11.0765714645386</t>
   </si>
   <si>
     <t xml:space="preserve">MONC.MI</t>
@@ -47,49 +47,49 @@
     <t xml:space="preserve">10.9698095321655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.845253944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986368179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.987606048584</t>
+    <t xml:space="preserve">10.8452558517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876041412354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1744375228882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9573602676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1566438674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5481033325195</t>
+    <t xml:space="preserve">11.9573593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4769296646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1566429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5481052398682</t>
   </si>
   <si>
     <t xml:space="preserve">11.734938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1264009475708</t>
+    <t xml:space="preserve">11.4057540893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8239068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1175031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1264019012451</t>
   </si>
   <si>
     <t xml:space="preserve">12.0997104644775</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">11.7260417938232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0908117294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9484624862671</t>
+    <t xml:space="preserve">12.0908126831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9484634399414</t>
   </si>
   <si>
     <t xml:space="preserve">11.8950824737549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7616310119629</t>
+    <t xml:space="preserve">11.7616300582886</t>
   </si>
   <si>
     <t xml:space="preserve">11.9128770828247</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">11.4146528244019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2723026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0409851074219</t>
+    <t xml:space="preserve">11.2723045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0409860610962</t>
   </si>
   <si>
     <t xml:space="preserve">11.254508972168</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">10.9431190490723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2989940643311</t>
+    <t xml:space="preserve">11.2989931106567</t>
   </si>
   <si>
     <t xml:space="preserve">11.6726608276367</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">11.8772888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110984802246</t>
+    <t xml:space="preserve">12.4110994338989</t>
   </si>
   <si>
     <t xml:space="preserve">12.2509574890137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2687511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4022006988525</t>
+    <t xml:space="preserve">12.2687501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4022016525269</t>
   </si>
   <si>
     <t xml:space="preserve">11.7972173690796</t>
@@ -158,31 +158,31 @@
     <t xml:space="preserve">12.7402830123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9627027511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.766975402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2118148803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.478720664978</t>
+    <t xml:space="preserve">12.962703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7669734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2118158340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.407546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4787197113037</t>
   </si>
   <si>
     <t xml:space="preserve">13.9680480957031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4520301818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6210699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7100400924683</t>
+    <t xml:space="preserve">13.4520311355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6210708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7100391387939</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363704681396</t>
@@ -191,49 +191,49 @@
     <t xml:space="preserve">13.0427751541138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0605697631836</t>
+    <t xml:space="preserve">13.060567855835</t>
   </si>
   <si>
     <t xml:space="preserve">12.9893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.900426864624</t>
+    <t xml:space="preserve">12.9004259109497</t>
   </si>
   <si>
     <t xml:space="preserve">13.0160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9449100494385</t>
+    <t xml:space="preserve">12.9449110031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.0961561203003</t>
   </si>
   <si>
-    <t xml:space="preserve">13.514307975769</t>
+    <t xml:space="preserve">13.5143070220947</t>
   </si>
   <si>
     <t xml:space="preserve">13.1228475570679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9804983139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9271173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.589035987854</t>
+    <t xml:space="preserve">12.9804973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9271183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5890340805054</t>
   </si>
   <si>
     <t xml:space="preserve">12.7936639785767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8292503356934</t>
+    <t xml:space="preserve">12.8292512893677</t>
   </si>
   <si>
     <t xml:space="preserve">13.033878326416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8737363815308</t>
+    <t xml:space="preserve">12.8737354278564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1495361328125</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">13.2029190063477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3897533416748</t>
+    <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
     <t xml:space="preserve">13.1673307418823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6869029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089645385742</t>
+    <t xml:space="preserve">12.6869010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089654922485</t>
   </si>
   <si>
     <t xml:space="preserve">12.5979328155518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9716005325317</t>
+    <t xml:space="preserve">12.9715986251831</t>
   </si>
   <si>
     <t xml:space="preserve">12.998291015625</t>
@@ -266,55 +266,55 @@
     <t xml:space="preserve">13.3185777664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9324598312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.057017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6388626098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.345269203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2285194396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5608062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.444055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2734212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4620170593262</t>
+    <t xml:space="preserve">13.9324607849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0570154190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9947366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6388635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676898956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3630619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452682495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2285184860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5608053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4440546035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2734222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4620161056519</t>
   </si>
   <si>
     <t xml:space="preserve">13.4979381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3632287979126</t>
+    <t xml:space="preserve">13.3632297515869</t>
   </si>
   <si>
     <t xml:space="preserve">13.3183250427246</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">13.668571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7314376831055</t>
+    <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
     <t xml:space="preserve">13.7404165267944</t>
@@ -335,97 +335,97 @@
     <t xml:space="preserve">13.1566743850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7256021499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8603134155273</t>
+    <t xml:space="preserve">12.7256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8603105545044</t>
   </si>
   <si>
     <t xml:space="preserve">13.8122615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6775512695312</t>
+    <t xml:space="preserve">13.6775531768799</t>
   </si>
   <si>
     <t xml:space="preserve">13.8571672439575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2253713607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321575164795</t>
+    <t xml:space="preserve">14.2253732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321556091309</t>
   </si>
   <si>
     <t xml:space="preserve">12.3035106658936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6986598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476926803589</t>
+    <t xml:space="preserve">12.6986608505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476936340332</t>
   </si>
   <si>
     <t xml:space="preserve">12.9950227737427</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6178340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8513317108154</t>
+    <t xml:space="preserve">12.6178331375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8513326644897</t>
   </si>
   <si>
     <t xml:space="preserve">12.8782739639282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9680786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9231758117676</t>
+    <t xml:space="preserve">12.9680795669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9231767654419</t>
   </si>
   <si>
     <t xml:space="preserve">13.1746349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9591007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9501180648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7705049514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3452682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8302240371704</t>
+    <t xml:space="preserve">12.9590997695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9501190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7705059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452672958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8302221298218</t>
   </si>
   <si>
     <t xml:space="preserve">14.1714887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0637216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3690633773804</t>
+    <t xml:space="preserve">14.063720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3690643310547</t>
   </si>
   <si>
     <t xml:space="preserve">14.0816831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9559535980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069198608398</t>
+    <t xml:space="preserve">13.9559526443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069208145142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6057071685791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9290113449097</t>
+    <t xml:space="preserve">13.929012298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.0277986526489</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">14.0188179016113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.848183631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0457592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9918746948242</t>
+    <t xml:space="preserve">13.8481845855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0457601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9918756484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.9200296401978</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">14.0008554458618</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7583789825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6955127716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877456665039</t>
+    <t xml:space="preserve">13.758376121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6955137252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877466201782</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248823165894</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">13.3542470932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4171133041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5158987045288</t>
+    <t xml:space="preserve">13.4171142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159006118774</t>
   </si>
   <si>
     <t xml:space="preserve">13.7224559783936</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">13.5338611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.704493522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9110498428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146869659424</t>
+    <t xml:space="preserve">13.7044944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9110507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.614688873291</t>
   </si>
   <si>
     <t xml:space="preserve">14.0098361968994</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">14.0727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4530353546143</t>
+    <t xml:space="preserve">13.4530363082886</t>
   </si>
   <si>
     <t xml:space="preserve">13.6506099700928</t>
@@ -503,40 +503,40 @@
     <t xml:space="preserve">13.6416292190552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7853212356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4799766540527</t>
+    <t xml:space="preserve">13.7853202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4799776077271</t>
   </si>
   <si>
     <t xml:space="preserve">13.839204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0996446609497</t>
+    <t xml:space="preserve">14.0996437072754</t>
   </si>
   <si>
     <t xml:space="preserve">13.8930883407593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9649333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8751268386841</t>
+    <t xml:space="preserve">13.9649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8751258850098</t>
   </si>
   <si>
     <t xml:space="preserve">13.79430103302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.62366771698</t>
+    <t xml:space="preserve">13.6236667633057</t>
   </si>
   <si>
     <t xml:space="preserve">13.399151802063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3901710510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4889602661133</t>
+    <t xml:space="preserve">13.3901700973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4889583587646</t>
   </si>
   <si>
     <t xml:space="preserve">13.3362874984741</t>
@@ -545,94 +545,94 @@
     <t xml:space="preserve">13.6326503753662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3273067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763385772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8661460876465</t>
+    <t xml:space="preserve">13.3273077011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8661470413208</t>
   </si>
   <si>
     <t xml:space="preserve">14.0547399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6474647521973</t>
+    <t xml:space="preserve">14.6474637985229</t>
   </si>
   <si>
     <t xml:space="preserve">14.6384830474854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9168853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0964975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0426120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989210128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5486764907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7372703552246</t>
+    <t xml:space="preserve">14.9168863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0964984893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.04261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.548677444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7372713088989</t>
   </si>
   <si>
     <t xml:space="preserve">14.7731943130493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8719806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7911548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6564435958862</t>
+    <t xml:space="preserve">14.8719816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7911539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6564426422119</t>
   </si>
   <si>
     <t xml:space="preserve">14.6833877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7013483047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.087516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9707670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7103290557861</t>
+    <t xml:space="preserve">14.7013473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8450393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9707679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7103281021118</t>
   </si>
   <si>
     <t xml:space="preserve">14.6744070053101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.952808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377632141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4736862182617</t>
+    <t xml:space="preserve">14.952805519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4736843109131</t>
   </si>
   <si>
     <t xml:space="preserve">15.6892204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7251434326172</t>
+    <t xml:space="preserve">15.7251424789429</t>
   </si>
   <si>
     <t xml:space="preserve">15.482666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7790260314941</t>
+    <t xml:space="preserve">15.7790279388428</t>
   </si>
   <si>
     <t xml:space="preserve">16.0933513641357</t>
@@ -644,55 +644,55 @@
     <t xml:space="preserve">16.2011184692383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.192138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2460269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1113147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9855813980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9137372970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6353387832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9317007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9766025543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9586410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9406805038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8867950439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1741790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1023330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0484485626221</t>
+    <t xml:space="preserve">16.1921367645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2460231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1113128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9855823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9137392044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6353359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9316997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.976601600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9586429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9406785964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8867959976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1741809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.102331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0484504699707</t>
   </si>
   <si>
     <t xml:space="preserve">15.8957767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.967622756958</t>
+    <t xml:space="preserve">15.9676237106323</t>
   </si>
   <si>
     <t xml:space="preserve">16.1831588745117</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">17.0991859436035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2608375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.162052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2967586517334</t>
+    <t xml:space="preserve">17.2608394622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1620540618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2967643737793</t>
   </si>
   <si>
     <t xml:space="preserve">17.3326816558838</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">17.5122966766357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5661773681641</t>
+    <t xml:space="preserve">17.5661811828613</t>
   </si>
   <si>
     <t xml:space="preserve">17.6559886932373</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">17.6021022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8535614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1768665313721</t>
+    <t xml:space="preserve">17.8535594940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.006233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1768684387207</t>
   </si>
   <si>
     <t xml:space="preserve">17.8805027008057</t>
   </si>
   <si>
-    <t xml:space="preserve">18.060115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0870571136475</t>
+    <t xml:space="preserve">18.0601177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0870609283447</t>
   </si>
   <si>
     <t xml:space="preserve">18.320556640625</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">18.4103622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1678848266602</t>
+    <t xml:space="preserve">18.1678829193115</t>
   </si>
   <si>
     <t xml:space="preserve">18.2756519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4373035430908</t>
+    <t xml:space="preserve">18.4373054504395</t>
   </si>
   <si>
     <t xml:space="preserve">18.6169166564941</t>
@@ -770,52 +770,52 @@
     <t xml:space="preserve">19.2276058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2365856170654</t>
+    <t xml:space="preserve">19.2365818023682</t>
   </si>
   <si>
     <t xml:space="preserve">19.2006607055664</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4790630340576</t>
+    <t xml:space="preserve">19.4790649414062</t>
   </si>
   <si>
     <t xml:space="preserve">19.5598888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1108551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2096424102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3174114227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5329475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610977172852</t>
+    <t xml:space="preserve">19.1108531951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2096385955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3174095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5329418182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.69460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610996246338</t>
   </si>
   <si>
     <t xml:space="preserve">19.5778484344482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5149841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1885375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310111999512</t>
+    <t xml:space="preserve">19.514986038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1885356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310131072998</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6645107269287</t>
+    <t xml:space="preserve">20.6645088195801</t>
   </si>
   <si>
     <t xml:space="preserve">20.8351421356201</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">19.9909610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3892555236816</t>
+    <t xml:space="preserve">19.389253616333</t>
   </si>
   <si>
     <t xml:space="preserve">19.5509090423584</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">19.7229614257812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6052379608154</t>
+    <t xml:space="preserve">19.6052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">19.4875183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0127391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2339630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6324062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.70485496521</t>
+    <t xml:space="preserve">20.0127372741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2339611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6324081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7048511505127</t>
   </si>
   <si>
     <t xml:space="preserve">19.2792415618896</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">18.9260749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0075740814209</t>
+    <t xml:space="preserve">19.0075759887695</t>
   </si>
   <si>
     <t xml:space="preserve">18.9713554382324</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">19.0800189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5819644927979</t>
+    <t xml:space="preserve">18.5819664001465</t>
   </si>
   <si>
     <t xml:space="preserve">18.8355197906494</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">19.0437984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3426303863525</t>
+    <t xml:space="preserve">19.3426284790039</t>
   </si>
   <si>
     <t xml:space="preserve">19.2249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6142959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2158489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1524639129639</t>
+    <t xml:space="preserve">19.614294052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2158508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1524658203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.1434059143066</t>
@@ -923,37 +923,37 @@
     <t xml:space="preserve">19.3245182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.944185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3736896514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.563850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6362991333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6000747680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7359104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6091327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1071853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.288293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.378849029541</t>
+    <t xml:space="preserve">18.9441871643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3736877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5638523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6362972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6000728607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8083534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7359085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.609130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1071872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2882957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060173034668</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">19.4512939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4331855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2701854705811</t>
+    <t xml:space="preserve">19.4331836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2701835632324</t>
   </si>
   <si>
     <t xml:space="preserve">19.1977405548096</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">20.239128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4655170440674</t>
+    <t xml:space="preserve">20.4655151367188</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3568496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2572383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3930702209473</t>
+    <t xml:space="preserve">20.3568458557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2572402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3930721282959</t>
   </si>
   <si>
     <t xml:space="preserve">20.329683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3749618530273</t>
+    <t xml:space="preserve">20.3749580383301</t>
   </si>
   <si>
     <t xml:space="preserve">20.4021282196045</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">20.3477935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8458499908447</t>
+    <t xml:space="preserve">20.8458461761475</t>
   </si>
   <si>
     <t xml:space="preserve">21.144681930542</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">21.5431251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3801231384277</t>
+    <t xml:space="preserve">21.3801250457764</t>
   </si>
   <si>
     <t xml:space="preserve">21.3439025878906</t>
@@ -1019,43 +1019,43 @@
     <t xml:space="preserve">21.4254035949707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3710708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2805137634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2080707550049</t>
+    <t xml:space="preserve">21.3710689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2805118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2080688476562</t>
   </si>
   <si>
     <t xml:space="preserve">20.8730144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2714595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6155700683594</t>
+    <t xml:space="preserve">21.2714576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.615571975708</t>
   </si>
   <si>
     <t xml:space="preserve">21.8962936401367</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7423496246338</t>
+    <t xml:space="preserve">21.7423477172852</t>
   </si>
   <si>
     <t xml:space="preserve">21.7966785430908</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9959011077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1589031219482</t>
+    <t xml:space="preserve">21.9959030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1589012145996</t>
   </si>
   <si>
     <t xml:space="preserve">22.4305686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3671798706055</t>
+    <t xml:space="preserve">22.3671779632568</t>
   </si>
   <si>
     <t xml:space="preserve">22.5935668945312</t>
@@ -1076,55 +1076,55 @@
     <t xml:space="preserve">22.2313442230225</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2132358551025</t>
+    <t xml:space="preserve">22.2132377624512</t>
   </si>
   <si>
     <t xml:space="preserve">22.2494583129883</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9596767425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8238468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0683441162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1136245727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1407909393311</t>
+    <t xml:space="preserve">21.959680557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8238487243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0683460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1136226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1407947540283</t>
   </si>
   <si>
     <t xml:space="preserve">21.8419570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7514038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4706802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1498470306396</t>
+    <t xml:space="preserve">21.7514019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.470682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.149845123291</t>
   </si>
   <si>
     <t xml:space="preserve">22.2766208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">22.059289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.285680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3490657806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.394344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9868469238281</t>
+    <t xml:space="preserve">22.0592918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2856788635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3490676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3943481445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9868488311768</t>
   </si>
   <si>
     <t xml:space="preserve">22.439624786377</t>
@@ -1133,73 +1133,73 @@
     <t xml:space="preserve">22.5573444366455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3581256866455</t>
+    <t xml:space="preserve">22.3581237792969</t>
   </si>
   <si>
     <t xml:space="preserve">22.1226806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0774002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0049571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9415683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8510131835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7695140838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6466236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0631828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.008846282959</t>
+    <t xml:space="preserve">22.0774021148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0049591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9415702819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8510112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7695121765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466255187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0631809234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088481903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6737937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7734069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6556816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0994033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0903511047363</t>
+    <t xml:space="preserve">20.7734050750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6556835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.090353012085</t>
   </si>
   <si>
     <t xml:space="preserve">21.135627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8277378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8549060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8005714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8820724487305</t>
+    <t xml:space="preserve">20.8277359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8549022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8005695343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8820686340332</t>
   </si>
   <si>
     <t xml:space="preserve">21.4344596862793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4163475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9506244659424</t>
+    <t xml:space="preserve">21.4163494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9506225585938</t>
   </si>
   <si>
     <t xml:space="preserve">22.4667911529541</t>
@@ -1208,37 +1208,37 @@
     <t xml:space="preserve">22.5120677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8833465576172</t>
+    <t xml:space="preserve">22.8833484649658</t>
   </si>
   <si>
     <t xml:space="preserve">22.3219013214111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8290100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8109016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0916194915771</t>
+    <t xml:space="preserve">22.8290119171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8108997344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0916213989258</t>
   </si>
   <si>
     <t xml:space="preserve">23.2546215057373</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6530647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.906623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6168422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632869720459</t>
+    <t xml:space="preserve">23.6530666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9066219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6168403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632888793945</t>
   </si>
   <si>
     <t xml:space="preserve">23.1821765899658</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">23.544397354126</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2002925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8199596405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7837352752686</t>
+    <t xml:space="preserve">23.2002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8199558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7837333679199</t>
   </si>
   <si>
     <t xml:space="preserve">23.0372886657715</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">23.8160629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.341287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861755371094</t>
+    <t xml:space="preserve">24.3412857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.486177444458</t>
   </si>
   <si>
     <t xml:space="preserve">24.2507305145264</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3775100708008</t>
+    <t xml:space="preserve">24.3775081634521</t>
   </si>
   <si>
     <t xml:space="preserve">24.5042858123779</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5223979949951</t>
+    <t xml:space="preserve">24.5223960876465</t>
   </si>
   <si>
     <t xml:space="preserve">24.2869510650635</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">24.114896774292</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0333995819092</t>
+    <t xml:space="preserve">24.0333976745605</t>
   </si>
   <si>
     <t xml:space="preserve">24.2145080566406</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">23.4628982543945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3593940734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.290843963623</t>
+    <t xml:space="preserve">24.359395980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2908420562744</t>
   </si>
   <si>
     <t xml:space="preserve">24.0424518585205</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6582298278809</t>
+    <t xml:space="preserve">24.6582317352295</t>
   </si>
   <si>
     <t xml:space="preserve">25.6724491119385</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">25.4641742706299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3917293548584</t>
+    <t xml:space="preserve">25.391731262207</t>
   </si>
   <si>
     <t xml:space="preserve">25.6362285614014</t>
@@ -1343,28 +1343,28 @@
     <t xml:space="preserve">26.1342830657959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9893932342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3192825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2649517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6996173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728416442871</t>
+    <t xml:space="preserve">25.9893951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3192844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2649478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.699613571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728397369385</t>
   </si>
   <si>
     <t xml:space="preserve">26.215784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4059505462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.505558013916</t>
+    <t xml:space="preserve">26.405948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5055618286133</t>
   </si>
   <si>
     <t xml:space="preserve">26.6685619354248</t>
@@ -1379,85 +1379,85 @@
     <t xml:space="preserve">26.7500591278076</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9583396911621</t>
+    <t xml:space="preserve">26.9583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">27.4654483795166</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9453907012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5741119384766</t>
+    <t xml:space="preserve">27.9453926086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5741138458252</t>
   </si>
   <si>
     <t xml:space="preserve">27.7190017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737251281738</t>
+    <t xml:space="preserve">27.6737213134766</t>
   </si>
   <si>
     <t xml:space="preserve">27.9182243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9816131591797</t>
+    <t xml:space="preserve">27.9816112518311</t>
   </si>
   <si>
     <t xml:space="preserve">29.7655563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4304981231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8108310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1549453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2364387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9104404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5624389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8250484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4809417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2053871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9026622772217</t>
+    <t xml:space="preserve">29.4304962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8108329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1549415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.236442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9104442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.562442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8250522613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4809379577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2053813934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9026584625244</t>
   </si>
   <si>
     <t xml:space="preserve">31.7124938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">32.020378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.920768737793</t>
+    <t xml:space="preserve">32.0203857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9207744598389</t>
   </si>
   <si>
     <t xml:space="preserve">32.618049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6904907226562</t>
+    <t xml:space="preserve">32.6904945373535</t>
   </si>
   <si>
     <t xml:space="preserve">32.962158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4602165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9039344787598</t>
+    <t xml:space="preserve">33.4602127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9039306640625</t>
   </si>
   <si>
     <t xml:space="preserve">34.4110412597656</t>
@@ -1472,79 +1472,79 @@
     <t xml:space="preserve">33.0346031188965</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0798835754395</t>
+    <t xml:space="preserve">33.0798797607422</t>
   </si>
   <si>
     <t xml:space="preserve">33.3153228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6865997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0759963989258</t>
+    <t xml:space="preserve">33.6866035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0759925842285</t>
   </si>
   <si>
     <t xml:space="preserve">34.0941047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3929328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2350997924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6788177490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4416961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4749298095703</t>
+    <t xml:space="preserve">34.392936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2350959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6788215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4416923522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.474925994873</t>
   </si>
   <si>
     <t xml:space="preserve">33.7270660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5022926330566</t>
+    <t xml:space="preserve">34.5022964477539</t>
   </si>
   <si>
     <t xml:space="preserve">35.8065032958984</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0071487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8671073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1589546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8156242370605</t>
+    <t xml:space="preserve">36.007152557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8671035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1589584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8156280517578</t>
   </si>
   <si>
     <t xml:space="preserve">35.8429870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3354797363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7035446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2931213378906</t>
+    <t xml:space="preserve">36.3354835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.703540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2931251525879</t>
   </si>
   <si>
     <t xml:space="preserve">36.2534027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.904182434082</t>
+    <t xml:space="preserve">37.2748756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5940933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9041862487793</t>
   </si>
   <si>
     <t xml:space="preserve">38.4696464538574</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">38.3602066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8221054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6546936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3446044921875</t>
+    <t xml:space="preserve">37.8221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6546974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3446083068848</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807655334473</t>
@@ -1571,22 +1571,22 @@
     <t xml:space="preserve">35.4143295288086</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3960914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5146560668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1042442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5693778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3504867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5205307006836</t>
+    <t xml:space="preserve">35.3960876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5146522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1042404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5693740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3504829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5205345153809</t>
   </si>
   <si>
     <t xml:space="preserve">33.9550704956055</t>
@@ -1595,31 +1595,31 @@
     <t xml:space="preserve">33.745304107666</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2925262451172</t>
+    <t xml:space="preserve">34.2925224304199</t>
   </si>
   <si>
     <t xml:space="preserve">35.0586357116699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1830787658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8397483825684</t>
+    <t xml:space="preserve">34.1830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8397445678711</t>
   </si>
   <si>
     <t xml:space="preserve">35.596736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1224784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.469051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3869705200195</t>
+    <t xml:space="preserve">35.1224746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.624095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4690551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3869667053223</t>
   </si>
   <si>
     <t xml:space="preserve">35.241039276123</t>
@@ -1628,37 +1628,37 @@
     <t xml:space="preserve">36.1622047424316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8853530883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6938209533691</t>
+    <t xml:space="preserve">34.8853492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6938171386719</t>
   </si>
   <si>
     <t xml:space="preserve">33.8091430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.401969909668</t>
+    <t xml:space="preserve">34.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">34.2013244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4169731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2651672363281</t>
+    <t xml:space="preserve">33.4169692993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2651634216309</t>
   </si>
   <si>
     <t xml:space="preserve">34.3746032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5387687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7303047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6208534240723</t>
+    <t xml:space="preserve">34.5387725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7303085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6208572387695</t>
   </si>
   <si>
     <t xml:space="preserve">34.0189170837402</t>
@@ -1667,25 +1667,25 @@
     <t xml:space="preserve">34.8215103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4840545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7941474914551</t>
+    <t xml:space="preserve">34.484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7941436767578</t>
   </si>
   <si>
     <t xml:space="preserve">35.5784912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2169189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1530799865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5328941345215</t>
+    <t xml:space="preserve">36.2169151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.153076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5328903198242</t>
   </si>
   <si>
     <t xml:space="preserve">35.5055351257324</t>
@@ -1703,61 +1703,61 @@
     <t xml:space="preserve">34.3381309509277</t>
   </si>
   <si>
-    <t xml:space="preserve">34.301643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.785026550293</t>
+    <t xml:space="preserve">34.3016510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7850227355957</t>
   </si>
   <si>
     <t xml:space="preserve">33.9824333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6117362976074</t>
+    <t xml:space="preserve">34.6117401123047</t>
   </si>
   <si>
     <t xml:space="preserve">34.4202156066895</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5934982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.511417388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0827598571777</t>
+    <t xml:space="preserve">34.5934944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5114135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0827560424805</t>
   </si>
   <si>
     <t xml:space="preserve">34.4110908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6664619445801</t>
+    <t xml:space="preserve">34.6664657592773</t>
   </si>
   <si>
     <t xml:space="preserve">35.2228050231934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9400672912598</t>
+    <t xml:space="preserve">34.940071105957</t>
   </si>
   <si>
     <t xml:space="preserve">32.979190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8300304412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9388809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5284633636475</t>
+    <t xml:space="preserve">31.8300342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9388790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5284652709961</t>
   </si>
   <si>
     <t xml:space="preserve">28.2001304626465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529102325439</t>
+    <t xml:space="preserve">27.6529083251953</t>
   </si>
   <si>
     <t xml:space="preserve">28.2639751434326</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">28.4007778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4554996490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7258720397949</t>
+    <t xml:space="preserve">28.4554977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7258701324463</t>
   </si>
   <si>
     <t xml:space="preserve">27.7988338470459</t>
@@ -1778,25 +1778,25 @@
     <t xml:space="preserve">26.6587905883789</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2698535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9082813262939</t>
+    <t xml:space="preserve">27.2698554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9082775115967</t>
   </si>
   <si>
     <t xml:space="preserve">27.5708274841309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1786518096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5434665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9994850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0906829833984</t>
+    <t xml:space="preserve">27.178653717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9994831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0906848907471</t>
   </si>
   <si>
     <t xml:space="preserve">29.5499439239502</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">29.1942481994629</t>
   </si>
   <si>
-    <t xml:space="preserve">28.97536277771</t>
+    <t xml:space="preserve">28.9753608703613</t>
   </si>
   <si>
     <t xml:space="preserve">29.1304054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6926288604736</t>
+    <t xml:space="preserve">28.6926307678223</t>
   </si>
   <si>
     <t xml:space="preserve">27.4522609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0392036437988</t>
+    <t xml:space="preserve">29.0392017364502</t>
   </si>
   <si>
     <t xml:space="preserve">28.0268440246582</t>
@@ -1826,22 +1826,22 @@
     <t xml:space="preserve">28.0359649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2666149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8503189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.813835144043</t>
+    <t xml:space="preserve">27.3519382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2666168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8503170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8138370513916</t>
   </si>
   <si>
     <t xml:space="preserve">27.4340209960938</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2060127258301</t>
+    <t xml:space="preserve">27.2060108184814</t>
   </si>
   <si>
     <t xml:space="preserve">26.7317523956299</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">27.807954788208</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7682342529297</t>
+    <t xml:space="preserve">26.768238067627</t>
   </si>
   <si>
     <t xml:space="preserve">27.3063354492188</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">25.6646709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1265716552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6431922912598</t>
+    <t xml:space="preserve">25.1265697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6431903839111</t>
   </si>
   <si>
     <t xml:space="preserve">25.1721725463867</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">25.5825901031494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3851795196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.59494972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3637008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4672660827637</t>
+    <t xml:space="preserve">26.385181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5949478149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3637027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.467264175415</t>
   </si>
   <si>
     <t xml:space="preserve">27.1877727508545</t>
   </si>
   <si>
-    <t xml:space="preserve">27.935640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6014270782471</t>
+    <t xml:space="preserve">27.9356422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6014289855957</t>
   </si>
   <si>
     <t xml:space="preserve">28.1454105377197</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0600852966309</t>
+    <t xml:space="preserve">27.0600872039795</t>
   </si>
   <si>
     <t xml:space="preserve">27.0327243804932</t>
@@ -1943,52 +1943,52 @@
     <t xml:space="preserve">27.8991603851318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3792991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9538822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8809204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2366123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9147529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0059642791748</t>
+    <t xml:space="preserve">27.3792972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.95387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8809185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9147567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0059623718262</t>
   </si>
   <si>
     <t xml:space="preserve">30.5987815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7994346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4437408447266</t>
+    <t xml:space="preserve">30.7994327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2007255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4437389373779</t>
   </si>
   <si>
     <t xml:space="preserve">30.6443862915039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9362354278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7023429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9121189117432</t>
+    <t xml:space="preserve">30.9362373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7023410797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9121150970459</t>
   </si>
   <si>
     <t xml:space="preserve">31.6020240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3284111022949</t>
+    <t xml:space="preserve">31.3284130096436</t>
   </si>
   <si>
     <t xml:space="preserve">31.8117904663086</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">31.7753067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6567420959473</t>
+    <t xml:space="preserve">31.6567440032959</t>
   </si>
   <si>
     <t xml:space="preserve">31.6476249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4743385314941</t>
+    <t xml:space="preserve">31.4743366241455</t>
   </si>
   <si>
     <t xml:space="preserve">31.9668388366699</t>
@@ -2012,37 +2012,37 @@
     <t xml:space="preserve">31.9029941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7538280487061</t>
+    <t xml:space="preserve">30.753833770752</t>
   </si>
   <si>
     <t xml:space="preserve">34.1557235717773</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7909049987793</t>
+    <t xml:space="preserve">33.7909088134766</t>
   </si>
   <si>
     <t xml:space="preserve">32.9244766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8332710266113</t>
+    <t xml:space="preserve">32.8332672119141</t>
   </si>
   <si>
     <t xml:space="preserve">32.6964645385742</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5778961181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4319763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9153518676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0065536499023</t>
+    <t xml:space="preserve">32.5140609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5779037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4319725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.915355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0065574645996</t>
   </si>
   <si>
     <t xml:space="preserve">33.5264129638672</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">32.231330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">31.738826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.441089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7603073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5081825256348</t>
+    <t xml:space="preserve">31.7388305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4410934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7603034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5081787109375</t>
   </si>
   <si>
     <t xml:space="preserve">33.6085014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">34.128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9277114868164</t>
+    <t xml:space="preserve">34.1283569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9277153015137</t>
   </si>
   <si>
     <t xml:space="preserve">33.8638687133789</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">32.659984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2163200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2892913818359</t>
+    <t xml:space="preserve">33.2163276672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2892875671387</t>
   </si>
   <si>
     <t xml:space="preserve">33.0977592468262</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">33.1160049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3075332641602</t>
+    <t xml:space="preserve">33.3075256347656</t>
   </si>
   <si>
     <t xml:space="preserve">33.8729934692383</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">33.061279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3440132141113</t>
+    <t xml:space="preserve">33.3440093994141</t>
   </si>
   <si>
     <t xml:space="preserve">33.3531341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">33.234561920166</t>
+    <t xml:space="preserve">33.2345657348633</t>
   </si>
   <si>
     <t xml:space="preserve">33.918586730957</t>
@@ -2126,67 +2126,67 @@
     <t xml:space="preserve">33.1616020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5505409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.404613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4443283081055</t>
+    <t xml:space="preserve">32.550537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4046096801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4443321228027</t>
   </si>
   <si>
     <t xml:space="preserve">31.9485988616943</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6873435974121</t>
+    <t xml:space="preserve">32.6873474121094</t>
   </si>
   <si>
     <t xml:space="preserve">32.1310005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5596580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5911731719971</t>
+    <t xml:space="preserve">32.5596618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5911712646484</t>
   </si>
   <si>
     <t xml:space="preserve">31.8863277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">32.836368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8586578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2552757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2829437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7848701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6226844787598</t>
+    <t xml:space="preserve">32.8363647460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8586616516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2552795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2829475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7848663330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7887096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6226863861084</t>
   </si>
   <si>
     <t xml:space="preserve">30.4382076263428</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5581169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1207656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8217620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0062370300293</t>
+    <t xml:space="preserve">30.5581150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8217582702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0062408447266</t>
   </si>
   <si>
     <t xml:space="preserve">31.6649646759033</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">32.1169204711914</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7387523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8125400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3290672302246</t>
+    <t xml:space="preserve">31.738748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8125476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3290634155273</t>
   </si>
   <si>
     <t xml:space="preserve">32.6519012451172</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">34.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7864112854004</t>
+    <t xml:space="preserve">33.7864151000977</t>
   </si>
   <si>
     <t xml:space="preserve">33.5189247131348</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2568206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6811103820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0500564575195</t>
+    <t xml:space="preserve">34.2568168640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6811065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0500602722168</t>
   </si>
   <si>
     <t xml:space="preserve">34.9762687683105</t>
@@ -2252,13 +2252,13 @@
     <t xml:space="preserve">35.5296897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2806510925293</t>
+    <t xml:space="preserve">35.280647277832</t>
   </si>
   <si>
     <t xml:space="preserve">35.3544425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0961761474609</t>
+    <t xml:space="preserve">35.0961799621582</t>
   </si>
   <si>
     <t xml:space="preserve">35.4927940368652</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">35.1330718994141</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2253036499023</t>
+    <t xml:space="preserve">35.2253112792969</t>
   </si>
   <si>
     <t xml:space="preserve">35.2437553405762</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">35.6403770446777</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9263076782227</t>
+    <t xml:space="preserve">35.9263153076172</t>
   </si>
   <si>
     <t xml:space="preserve">35.9908752441406</t>
@@ -2300,55 +2300,55 @@
     <t xml:space="preserve">33.4451370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4620342254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4343719482422</t>
+    <t xml:space="preserve">31.4620399475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4343681335449</t>
   </si>
   <si>
     <t xml:space="preserve">31.8309841156006</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4120826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3475189208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4989337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7571964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6926345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7072410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7479705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5542755126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3605804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3052349090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4435882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6465187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3382949829102</t>
+    <t xml:space="preserve">32.4120788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3475151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4989356994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2314434051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7572002410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7072372436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.747974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5542774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3605785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3052387237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4435901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6465148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3382911682129</t>
   </si>
   <si>
     <t xml:space="preserve">33.0761871337891</t>
@@ -2363,49 +2363,49 @@
     <t xml:space="preserve">32.5412101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6242218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6426696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3751831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6372909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4804878234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2760238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9493541717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0877075195312</t>
+    <t xml:space="preserve">32.6242179870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6426734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3751792907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6372890472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4804840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2760219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9493560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.087703704834</t>
   </si>
   <si>
     <t xml:space="preserve">29.6080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7279815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6449680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8478908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3367462158203</t>
+    <t xml:space="preserve">29.7279834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6449699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8478927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3367481231689</t>
   </si>
   <si>
     <t xml:space="preserve">30.1614990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8294467926025</t>
+    <t xml:space="preserve">29.8294448852539</t>
   </si>
   <si>
     <t xml:space="preserve">29.1376667022705</t>
@@ -2414,31 +2414,31 @@
     <t xml:space="preserve">29.6173000335693</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0139198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.198392868042</t>
+    <t xml:space="preserve">30.0139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1983966827393</t>
   </si>
   <si>
     <t xml:space="preserve">30.0508155822754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6134605407715</t>
+    <t xml:space="preserve">30.6134567260742</t>
   </si>
   <si>
     <t xml:space="preserve">31.1945514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8033142089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.545051574707</t>
+    <t xml:space="preserve">31.8033180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5450534820557</t>
   </si>
   <si>
     <t xml:space="preserve">31.4251441955566</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0285243988037</t>
+    <t xml:space="preserve">31.0285263061523</t>
   </si>
   <si>
     <t xml:space="preserve">30.7241439819336</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">29.9770240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7740993499756</t>
+    <t xml:space="preserve">29.7741031646729</t>
   </si>
   <si>
     <t xml:space="preserve">29.691089630127</t>
@@ -2459,55 +2459,55 @@
     <t xml:space="preserve">29.9678001403809</t>
   </si>
   <si>
-    <t xml:space="preserve">33.362117767334</t>
+    <t xml:space="preserve">33.3621215820312</t>
   </si>
   <si>
     <t xml:space="preserve">32.7441329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9877910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.439754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5504341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.310619354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2291526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7180023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3121604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0907897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0077781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.611156463623</t>
+    <t xml:space="preserve">31.9877872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4397506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5504379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3106231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2291488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7180061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3121643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0907936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0077743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6111602783203</t>
   </si>
   <si>
     <t xml:space="preserve">33.7218475341797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9801139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2199249267578</t>
+    <t xml:space="preserve">33.9801063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2199211120605</t>
   </si>
   <si>
     <t xml:space="preserve">34.819465637207</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5243034362793</t>
+    <t xml:space="preserve">34.5243110656738</t>
   </si>
   <si>
     <t xml:space="preserve">36.0462188720703</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">36.1476783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6826515197754</t>
+    <t xml:space="preserve">37.0239334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6826553344727</t>
   </si>
   <si>
     <t xml:space="preserve">35.7787322998047</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">38.1492195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9240112304688</t>
+    <t xml:space="preserve">38.924015045166</t>
   </si>
   <si>
     <t xml:space="preserve">38.545841217041</t>
@@ -2540,19 +2540,19 @@
     <t xml:space="preserve">38.8225517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">38.093879699707</t>
+    <t xml:space="preserve">38.0938758850098</t>
   </si>
   <si>
     <t xml:space="preserve">37.8171653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7249298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1530570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3006439208984</t>
+    <t xml:space="preserve">37.7249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1530609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3006362915039</t>
   </si>
   <si>
     <t xml:space="preserve">37.0423812866211</t>
@@ -2576,34 +2576,34 @@
     <t xml:space="preserve">37.4389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1438331604004</t>
+    <t xml:space="preserve">36.9778137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1438369750977</t>
   </si>
   <si>
     <t xml:space="preserve">37.9647483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5496826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6326904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3613700866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4036483764648</t>
+    <t xml:space="preserve">37.9462966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.549674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.632698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3613662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4036407470703</t>
   </si>
   <si>
     <t xml:space="preserve">39.3667488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">39.385196685791</t>
+    <t xml:space="preserve">39.3852005004883</t>
   </si>
   <si>
     <t xml:space="preserve">38.1399955749512</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">38.2691307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2084083557129</t>
+    <t xml:space="preserve">37.2084045410156</t>
   </si>
   <si>
     <t xml:space="preserve">37.402099609375</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">36.488956451416</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9724235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3690452575684</t>
+    <t xml:space="preserve">35.9724273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3690490722656</t>
   </si>
   <si>
     <t xml:space="preserve">36.8579025268555</t>
@@ -2645,19 +2645,19 @@
     <t xml:space="preserve">36.5166282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7049407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6457557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6495971679688</t>
+    <t xml:space="preserve">35.7049369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6457595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6496047973633</t>
   </si>
   <si>
     <t xml:space="preserve">36.2583618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1422920227051</t>
+    <t xml:space="preserve">35.1422958374023</t>
   </si>
   <si>
     <t xml:space="preserve">35.2898750305176</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">32.4305267333984</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4028587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9286079406738</t>
+    <t xml:space="preserve">32.4028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9286041259766</t>
   </si>
   <si>
     <t xml:space="preserve">32.522762298584</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">32.4858703613281</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1023178100586</t>
+    <t xml:space="preserve">31.10231590271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1507320404053</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">27.8002281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0807838439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.981616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3943901062012</t>
+    <t xml:space="preserve">27.0807819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9816188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3943862915039</t>
   </si>
   <si>
     <t xml:space="preserve">25.2637119293213</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">25.3651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.922435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9977703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3797798156738</t>
+    <t xml:space="preserve">24.9224376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9977684020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3797817230225</t>
   </si>
   <si>
     <t xml:space="preserve">29.9309062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4528121948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.729528427124</t>
+    <t xml:space="preserve">31.4528141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7295265197754</t>
   </si>
   <si>
     <t xml:space="preserve">30.705696105957</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">28.6857070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6688003540039</t>
+    <t xml:space="preserve">30.6688041687012</t>
   </si>
   <si>
     <t xml:space="preserve">30.1061534881592</t>
@@ -2750,28 +2750,28 @@
     <t xml:space="preserve">30.2998504638672</t>
   </si>
   <si>
-    <t xml:space="preserve">31.083869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6319065093994</t>
+    <t xml:space="preserve">31.0838680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6319046020508</t>
   </si>
   <si>
     <t xml:space="preserve">31.8402099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5135383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.890172958374</t>
+    <t xml:space="preserve">32.513542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8901691436768</t>
   </si>
   <si>
     <t xml:space="preserve">30.576566696167</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5081539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7756443023682</t>
+    <t xml:space="preserve">31.5081596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7756404876709</t>
   </si>
   <si>
     <t xml:space="preserve">30.2721824645996</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">30.7702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9124603271484</t>
+    <t xml:space="preserve">29.9124584197998</t>
   </si>
   <si>
     <t xml:space="preserve">30.2352848052979</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">28.7041530609131</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6211395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7372093200684</t>
+    <t xml:space="preserve">28.6211414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7372074127197</t>
   </si>
   <si>
     <t xml:space="preserve">29.8663387298584</t>
@@ -2810,34 +2810,34 @@
     <t xml:space="preserve">28.8056144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">29.368257522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7979316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3920917510986</t>
+    <t xml:space="preserve">29.3682594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7979354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.39208984375</t>
   </si>
   <si>
     <t xml:space="preserve">32.1630363464355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8532791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8955535888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0339088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3790264129639</t>
+    <t xml:space="preserve">30.8532772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0746459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8955574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0339050292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3790245056152</t>
   </si>
   <si>
     <t xml:space="preserve">31.2406692504883</t>
@@ -2852,52 +2852,52 @@
     <t xml:space="preserve">32.762580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0577392578125</t>
+    <t xml:space="preserve">33.0577430725098</t>
   </si>
   <si>
     <t xml:space="preserve">32.0892524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7203006744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.126148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3974742889404</t>
+    <t xml:space="preserve">31.7203025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1261444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3974723815918</t>
   </si>
   <si>
     <t xml:space="preserve">31.6003971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9508991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2591171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4897079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.650354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0654182434082</t>
+    <t xml:space="preserve">31.9508953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2591209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9601249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.489709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.351354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6503562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0654201507568</t>
   </si>
   <si>
     <t xml:space="preserve">30.9824047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0100765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5950107574463</t>
+    <t xml:space="preserve">31.0100784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5950088500977</t>
   </si>
   <si>
     <t xml:space="preserve">30.0692596435547</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">29.488166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8809452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3275241851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.078483581543</t>
+    <t xml:space="preserve">30.8809471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3275260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0784854888916</t>
   </si>
   <si>
     <t xml:space="preserve">29.5342864990234</t>
@@ -2930,37 +2930,37 @@
     <t xml:space="preserve">29.552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8571128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0046939849854</t>
+    <t xml:space="preserve">29.8571147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0046920776367</t>
   </si>
   <si>
     <t xml:space="preserve">30.5857906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">29.884786605835</t>
+    <t xml:space="preserve">29.8847846984863</t>
   </si>
   <si>
     <t xml:space="preserve">29.9585762023926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1484355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7940921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1814880371094</t>
+    <t xml:space="preserve">31.1484336853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.794095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1814842224121</t>
   </si>
   <si>
     <t xml:space="preserve">32.4766426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8878784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9854965209961</t>
+    <t xml:space="preserve">33.8878746032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9854927062988</t>
   </si>
   <si>
     <t xml:space="preserve">34.3306121826172</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">33.66650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4674186706543</t>
+    <t xml:space="preserve">32.4674224853516</t>
   </si>
   <si>
     <t xml:space="preserve">32.0431365966797</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">32.448974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2644958496094</t>
+    <t xml:space="preserve">32.2644996643066</t>
   </si>
   <si>
     <t xml:space="preserve">32.8455963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7164688110352</t>
+    <t xml:space="preserve">32.7164649963379</t>
   </si>
   <si>
     <t xml:space="preserve">33.601936340332</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">33.2237663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5650367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9339942932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0354499816895</t>
+    <t xml:space="preserve">33.5650405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9339904785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0354537963867</t>
   </si>
   <si>
     <t xml:space="preserve">32.6057777404785</t>
@@ -3023,22 +3023,22 @@
     <t xml:space="preserve">34.127685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1907119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3936347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.205322265625</t>
+    <t xml:space="preserve">32.1907157897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3936309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2053184509277</t>
   </si>
   <si>
     <t xml:space="preserve">33.5465927124023</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8840293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6349945068359</t>
+    <t xml:space="preserve">34.884033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6349906921387</t>
   </si>
   <si>
     <t xml:space="preserve">36.5996398925781</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">36.6088600158691</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7195434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8909568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8725090026855</t>
+    <t xml:space="preserve">36.7195472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8909606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8725166320801</t>
   </si>
   <si>
     <t xml:space="preserve">37.6142463684082</t>
@@ -3080,25 +3080,25 @@
     <t xml:space="preserve">38.241455078125</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8263893127441</t>
+    <t xml:space="preserve">37.8263931274414</t>
   </si>
   <si>
     <t xml:space="preserve">37.9001770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4720458984375</t>
+    <t xml:space="preserve">38.4720497131348</t>
   </si>
   <si>
     <t xml:space="preserve">39.2837371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8463859558105</t>
+    <t xml:space="preserve">39.8463821411133</t>
   </si>
   <si>
     <t xml:space="preserve">40.5842819213867</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4144096374512</t>
+    <t xml:space="preserve">41.4144134521484</t>
   </si>
   <si>
     <t xml:space="preserve">42.9916610717773</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">42.8533096313477</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8863677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1630744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0116577148438</t>
+    <t xml:space="preserve">43.8863639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1630783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0116539001465</t>
   </si>
   <si>
     <t xml:space="preserve">44.928638458252</t>
@@ -3125,25 +3125,25 @@
     <t xml:space="preserve">44.7349433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8679122924805</t>
+    <t xml:space="preserve">43.867919921875</t>
   </si>
   <si>
     <t xml:space="preserve">44.6242599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">44.467456817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.869457244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.395206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.247631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1184997558594</t>
+    <t xml:space="preserve">44.4674530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8694534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3952140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2476272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1184959411621</t>
   </si>
   <si>
     <t xml:space="preserve">44.8456268310547</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">44.3291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2737617492676</t>
+    <t xml:space="preserve">44.2737579345703</t>
   </si>
   <si>
     <t xml:space="preserve">43.3882827758789</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">44.0708351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6742172241211</t>
+    <t xml:space="preserve">43.6742134094238</t>
   </si>
   <si>
     <t xml:space="preserve">44.6703758239746</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">43.9509353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8917465209961</t>
+    <t xml:space="preserve">44.8917427062988</t>
   </si>
   <si>
     <t xml:space="preserve">45.7403259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6649932861328</t>
+    <t xml:space="preserve">43.6649894714355</t>
   </si>
   <si>
     <t xml:space="preserve">43.5912017822266</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">44.3567695617676</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7756729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1999664306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2091903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1369438171387</t>
+    <t xml:space="preserve">43.7756767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1999702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2091941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1369476318359</t>
   </si>
   <si>
     <t xml:space="preserve">46.8932914733887</t>
@@ -3212,46 +3212,46 @@
     <t xml:space="preserve">47.5758438110352</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0739212036133</t>
+    <t xml:space="preserve">48.073917388916</t>
   </si>
   <si>
     <t xml:space="preserve">47.6496315002441</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9447860717773</t>
+    <t xml:space="preserve">47.9447898864746</t>
   </si>
   <si>
     <t xml:space="preserve">47.2622375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1477088928223</t>
+    <t xml:space="preserve">48.1477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">47.7972106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">46.708812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6534729003906</t>
+    <t xml:space="preserve">46.7088165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6534767150879</t>
   </si>
   <si>
     <t xml:space="preserve">49.1807670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8709983825684</t>
+    <t xml:space="preserve">47.8710021972656</t>
   </si>
   <si>
     <t xml:space="preserve">47.2437896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0408706665039</t>
+    <t xml:space="preserve">47.0408668518066</t>
   </si>
   <si>
     <t xml:space="preserve">47.169994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3175811767578</t>
+    <t xml:space="preserve">47.3175773620605</t>
   </si>
   <si>
     <t xml:space="preserve">48.1108169555664</t>
@@ -3263,16 +3263,16 @@
     <t xml:space="preserve">47.6865272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6165771484375</t>
+    <t xml:space="preserve">46.6165733337402</t>
   </si>
   <si>
     <t xml:space="preserve">45.7034301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8602333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4136581420898</t>
+    <t xml:space="preserve">45.860237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4136543273926</t>
   </si>
   <si>
     <t xml:space="preserve">45.7587814331055</t>
@@ -3281,22 +3281,22 @@
     <t xml:space="preserve">48.0001373291016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3360290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4467086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8379440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2107315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6019668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3806037902832</t>
+    <t xml:space="preserve">47.3360252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4467124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.837947845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2107353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6019744873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3805999755859</t>
   </si>
   <si>
     <t xml:space="preserve">44.2276382446289</t>
@@ -3308,46 +3308,46 @@
     <t xml:space="preserve">44.4859046936035</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3898239135742</t>
+    <t xml:space="preserve">45.3898277282715</t>
   </si>
   <si>
     <t xml:space="preserve">45.0762176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8417854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4505500793457</t>
+    <t xml:space="preserve">45.8417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6573143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.450553894043</t>
   </si>
   <si>
     <t xml:space="preserve">46.5981330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">46.524341583252</t>
+    <t xml:space="preserve">46.5243377685547</t>
   </si>
   <si>
     <t xml:space="preserve">47.5020523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3544731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.321418762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2952919006348</t>
+    <t xml:space="preserve">47.3544769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3214149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.295295715332</t>
   </si>
   <si>
     <t xml:space="preserve">49.346794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9670791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0039710998535</t>
+    <t xml:space="preserve">46.9670753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0039749145508</t>
   </si>
   <si>
     <t xml:space="preserve">47.0593185424805</t>
@@ -3374,25 +3374,25 @@
     <t xml:space="preserve">47.5942878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">47.926342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.664234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4244194030762</t>
+    <t xml:space="preserve">47.9263381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6642379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">49.1623191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">49.420581817627</t>
+    <t xml:space="preserve">49.4205856323242</t>
   </si>
   <si>
     <t xml:space="preserve">50.490291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1228141784668</t>
+    <t xml:space="preserve">51.1228179931641</t>
   </si>
   <si>
     <t xml:space="preserve">51.625114440918</t>
@@ -3401,13 +3401,13 @@
     <t xml:space="preserve">53.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9877738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0621948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4482727050781</t>
+    <t xml:space="preserve">53.9877777099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0621910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4482688903809</t>
   </si>
   <si>
     <t xml:space="preserve">53.6343078613281</t>
@@ -3416,58 +3416,58 @@
     <t xml:space="preserve">54.1180038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">54.229621887207</t>
+    <t xml:space="preserve">54.2296257019043</t>
   </si>
   <si>
     <t xml:space="preserve">55.1039924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5784950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8343505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8715591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.132007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8947601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2482261657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5086784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.043586730957</t>
+    <t xml:space="preserve">54.8063316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.578498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8343544006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8715629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1320114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8947563171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2482223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.508674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0435829162598</t>
   </si>
   <si>
     <t xml:space="preserve">54.1738166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2110214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.225025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6901206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.597095489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0761985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4668731689453</t>
+    <t xml:space="preserve">54.2110176086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2250289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5970993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0762023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4668769836426</t>
   </si>
   <si>
     <t xml:space="preserve">53.3180465698242</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">51.4762840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4250679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.280834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7273254394531</t>
+    <t xml:space="preserve">52.4250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2808380126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7273292541504</t>
   </si>
   <si>
     <t xml:space="preserve">54.3598480224609</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">52.1460189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1878242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7459297180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.620304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4388580322266</t>
+    <t xml:space="preserve">53.1878204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7459259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6203002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4388618469238</t>
   </si>
   <si>
     <t xml:space="preserve">55.7551231384277</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">53.8761558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">53.950569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6389045715332</t>
+    <t xml:space="preserve">53.9505653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6389083862305</t>
   </si>
   <si>
     <t xml:space="preserve">54.6947174072266</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">54.5272827148438</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5876884460449</t>
+    <t xml:space="preserve">55.5876922607422</t>
   </si>
   <si>
     <t xml:space="preserve">56.9271507263184</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2992248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5596809387207</t>
+    <t xml:space="preserve">57.2992286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7271118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5596733093262</t>
   </si>
   <si>
     <t xml:space="preserve">56.4248542785645</t>
@@ -3560,10 +3560,10 @@
     <t xml:space="preserve">54.3970527648926</t>
   </si>
   <si>
-    <t xml:space="preserve">51.067008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1554222106934</t>
+    <t xml:space="preserve">51.0670051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1554260253906</t>
   </si>
   <si>
     <t xml:space="preserve">50.8437614440918</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">50.5461044311523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8065567016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4158744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0298004150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9925880432129</t>
+    <t xml:space="preserve">50.8065490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4158782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0297966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9925918579102</t>
   </si>
   <si>
     <t xml:space="preserve">50.2484436035156</t>
@@ -3596,40 +3596,40 @@
     <t xml:space="preserve">51.1042137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7181282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4018669128418</t>
+    <t xml:space="preserve">51.718132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4018707275391</t>
   </si>
   <si>
     <t xml:space="preserve">51.3274574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8251571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7879524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1648368835449</t>
+    <t xml:space="preserve">50.8251609802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7879486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1648330688477</t>
   </si>
   <si>
     <t xml:space="preserve">48.0904235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3182601928711</t>
+    <t xml:space="preserve">49.3182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">48.0532150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0019989013672</t>
+    <t xml:space="preserve">49.0020027160645</t>
   </si>
   <si>
     <t xml:space="preserve">50.5647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3832626342773</t>
+    <t xml:space="preserve">51.3832664489746</t>
   </si>
   <si>
     <t xml:space="preserve">51.1600227355957</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">50.0624084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6113204956055</t>
+    <t xml:space="preserve">48.6113243103027</t>
   </si>
   <si>
     <t xml:space="preserve">49.2438468933105</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">51.7553405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9785842895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9831771850586</t>
+    <t xml:space="preserve">51.978588104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9831809997559</t>
   </si>
   <si>
     <t xml:space="preserve">52.4994812011719</t>
@@ -3665,16 +3665,16 @@
     <t xml:space="preserve">54.4714736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">55.569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0341835021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7597236633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8341331481934</t>
+    <t xml:space="preserve">55.5690879821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7597198486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8341293334961</t>
   </si>
   <si>
     <t xml:space="preserve">56.3876457214355</t>
@@ -3683,55 +3683,55 @@
     <t xml:space="preserve">55.9783668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9457550048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7829208374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4386444091797</t>
+    <t xml:space="preserve">56.9457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7829170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.438648223877</t>
   </si>
   <si>
     <t xml:space="preserve">58.5084648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">59.234001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6524772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8803215026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4012298583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4106254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7408981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8199119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9361381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.754695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3314056396484</t>
+    <t xml:space="preserve">59.2340049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.652473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8803253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4012222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4106292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7409057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8199157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9361305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7546882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.331413269043</t>
   </si>
   <si>
     <t xml:space="preserve">64.2197799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5686454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0663604736328</t>
+    <t xml:space="preserve">63.568660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0663566589355</t>
   </si>
   <si>
     <t xml:space="preserve">63.9593315124512</t>
@@ -3740,34 +3740,34 @@
     <t xml:space="preserve">61.5408554077148</t>
   </si>
   <si>
-    <t xml:space="preserve">61.9129219055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3222160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3410339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0897750854492</t>
+    <t xml:space="preserve">61.9129257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3222122192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3410301208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.089771270752</t>
   </si>
   <si>
     <t xml:space="preserve">59.6060791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0385627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9455375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5920677185059</t>
+    <t xml:space="preserve">61.0385589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9455337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5920753479004</t>
   </si>
   <si>
     <t xml:space="preserve">61.6896896362305</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4430313110352</t>
+    <t xml:space="preserve">64.4430236816406</t>
   </si>
   <si>
     <t xml:space="preserve">62.4710388183594</t>
@@ -3779,16 +3779,16 @@
     <t xml:space="preserve">61.4478340148926</t>
   </si>
   <si>
-    <t xml:space="preserve">60.629280090332</t>
+    <t xml:space="preserve">60.6292762756348</t>
   </si>
   <si>
     <t xml:space="preserve">58.675895690918</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7503128051758</t>
+    <t xml:space="preserve">60.182788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7503089904785</t>
   </si>
   <si>
     <t xml:space="preserve">58.8061218261719</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">57.8573379516602</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3224296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5642776489258</t>
+    <t xml:space="preserve">58.3224258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5642738342285</t>
   </si>
   <si>
     <t xml:space="preserve">59.7549057006836</t>
@@ -3812,19 +3812,19 @@
     <t xml:space="preserve">60.0711708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5502624511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.8107223510742</t>
+    <t xml:space="preserve">59.5502662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.810718536377</t>
   </si>
   <si>
     <t xml:space="preserve">60.4618453979492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9269332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4154434204102</t>
+    <t xml:space="preserve">60.9269371032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4154396057129</t>
   </si>
   <si>
     <t xml:space="preserve">56.9643592834473</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">56.1644020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7923278808594</t>
+    <t xml:space="preserve">55.7923316955566</t>
   </si>
   <si>
     <t xml:space="preserve">54.8807525634766</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">54.3040390014648</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3412437438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6995277404785</t>
+    <t xml:space="preserve">54.3412475585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6995315551758</t>
   </si>
   <si>
     <t xml:space="preserve">51.2716445922852</t>
@@ -3863,25 +3863,25 @@
     <t xml:space="preserve">52.3134536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">52.536693572998</t>
+    <t xml:space="preserve">52.5366897583008</t>
   </si>
   <si>
     <t xml:space="preserve">51.5693016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4064674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.899356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2714233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8389472961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0993995666504</t>
+    <t xml:space="preserve">52.4064712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8993530273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.271427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8389511108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0993957519531</t>
   </si>
   <si>
     <t xml:space="preserve">51.6437149047852</t>
@@ -3893,73 +3893,73 @@
     <t xml:space="preserve">52.1274147033691</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2344398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9739837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9181747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8809700012207</t>
+    <t xml:space="preserve">51.2344360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9739875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9181785583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8809661865234</t>
   </si>
   <si>
     <t xml:space="preserve">48.4624938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8021774291992</t>
+    <t xml:space="preserve">45.802173614502</t>
   </si>
   <si>
     <t xml:space="preserve">47.1230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9463996887207</t>
+    <t xml:space="preserve">44.9464073181152</t>
   </si>
   <si>
     <t xml:space="preserve">41.8768043518066</t>
   </si>
   <si>
-    <t xml:space="preserve">42.146556854248</t>
+    <t xml:space="preserve">42.1465606689453</t>
   </si>
   <si>
     <t xml:space="preserve">41.4954299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9743041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9976196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6208419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6487503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2441749572754</t>
+    <t xml:space="preserve">44.974308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.997615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6208457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6487464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2441711425781</t>
   </si>
   <si>
     <t xml:space="preserve">45.7091522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7881622314453</t>
+    <t xml:space="preserve">46.7881698608398</t>
   </si>
   <si>
     <t xml:space="preserve">47.5323104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1044273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2951698303223</t>
+    <t xml:space="preserve">47.1044311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2951736450195</t>
   </si>
   <si>
     <t xml:space="preserve">45.8207740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2021522521973</t>
+    <t xml:space="preserve">46.2021484375</t>
   </si>
   <si>
     <t xml:space="preserve">46.2765655517578</t>
@@ -3971,22 +3971,22 @@
     <t xml:space="preserve">47.1974487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9275856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2810592651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9556007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9882049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4392967224121</t>
+    <t xml:space="preserve">47.178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9275817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2810554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9556045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9882125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4392929077148</t>
   </si>
   <si>
     <t xml:space="preserve">45.1603469848633</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">46.1835517883301</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5881195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5277137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3510932922363</t>
+    <t xml:space="preserve">47.5881233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.527717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3510894775391</t>
   </si>
   <si>
     <t xml:space="preserve">43.8301849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4300994873047</t>
+    <t xml:space="preserve">45.430103302002</t>
   </si>
   <si>
     <t xml:space="preserve">46.2672653198242</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">45.5696296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6115417480469</t>
+    <t xml:space="preserve">44.6115379333496</t>
   </si>
   <si>
     <t xml:space="preserve">43.9604110717773</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">41.4861259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7373886108398</t>
+    <t xml:space="preserve">39.7373809814453</t>
   </si>
   <si>
     <t xml:space="preserve">38.9095268249512</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">40.8070907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1930656433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2814903259277</t>
+    <t xml:space="preserve">42.1930694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2814865112305</t>
   </si>
   <si>
     <t xml:space="preserve">42.1093482971191</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">40.0908508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.309497833252</t>
+    <t xml:space="preserve">39.3095016479492</t>
   </si>
   <si>
     <t xml:space="preserve">39.8945198059082</t>
@@ -4076,19 +4076,19 @@
     <t xml:space="preserve">38.5640716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6018180847168</t>
+    <t xml:space="preserve">38.6018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">39.819034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6588172912598</t>
+    <t xml:space="preserve">40.658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">42.3572616577148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.177978515625</t>
+    <t xml:space="preserve">42.1779823303223</t>
   </si>
   <si>
     <t xml:space="preserve">43.6499633789062</t>
@@ -4097,10 +4097,10 @@
     <t xml:space="preserve">43.300838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4801177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2347869873047</t>
+    <t xml:space="preserve">43.4801216125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.234790802002</t>
   </si>
   <si>
     <t xml:space="preserve">42.1119346618652</t>
@@ -4118,13 +4118,13 @@
     <t xml:space="preserve">36.2145614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5167007446289</t>
+    <t xml:space="preserve">37.5166969299316</t>
   </si>
   <si>
     <t xml:space="preserve">35.3747787475586</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0916976928711</t>
+    <t xml:space="preserve">35.0917015075684</t>
   </si>
   <si>
     <t xml:space="preserve">34.9690399169922</t>
@@ -4142,25 +4142,25 @@
     <t xml:space="preserve">37.4600868225098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7054138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3942260742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4980239868164</t>
+    <t xml:space="preserve">37.7054176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.394229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4980201721191</t>
   </si>
   <si>
     <t xml:space="preserve">38.6206893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0639801025391</t>
+    <t xml:space="preserve">38.0639762878418</t>
   </si>
   <si>
     <t xml:space="preserve">37.3751640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8943290710449</t>
+    <t xml:space="preserve">38.8943252563477</t>
   </si>
   <si>
     <t xml:space="preserve">39.0547332763672</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">37.8280830383301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5735092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1587257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3474349975586</t>
+    <t xml:space="preserve">38.5735130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1587219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3474388122559</t>
   </si>
   <si>
     <t xml:space="preserve">40.7531776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1494827270508</t>
+    <t xml:space="preserve">41.1494789123535</t>
   </si>
   <si>
     <t xml:space="preserve">41.5552215576172</t>
@@ -4205,25 +4205,25 @@
     <t xml:space="preserve">39.6586265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7248687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9990882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9239883422852</t>
+    <t xml:space="preserve">40.7248725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9990921020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9239921569824</t>
   </si>
   <si>
     <t xml:space="preserve">45.9806060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">45.046459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3389663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5278854370117</t>
+    <t xml:space="preserve">45.0464630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3389701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5278816223145</t>
   </si>
   <si>
     <t xml:space="preserve">46.5184440612793</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">46.4995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8579368591309</t>
+    <t xml:space="preserve">45.8579406738281</t>
   </si>
   <si>
     <t xml:space="preserve">46.7165946960449</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">46.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0089111328125</t>
+    <t xml:space="preserve">46.0089149475098</t>
   </si>
   <si>
     <t xml:space="preserve">46.754337310791</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">44.8388748168945</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2163047790527</t>
+    <t xml:space="preserve">45.2163009643555</t>
   </si>
   <si>
     <t xml:space="preserve">45.2729225158691</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">43.046070098877</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1496696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3100852966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1213684082031</t>
+    <t xml:space="preserve">42.1496734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3100814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1213645935059</t>
   </si>
   <si>
     <t xml:space="preserve">41.0456848144531</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">41.1777877807617</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3948097229004</t>
+    <t xml:space="preserve">41.3948059082031</t>
   </si>
   <si>
     <t xml:space="preserve">41.6967544555664</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4704856872559</t>
+    <t xml:space="preserve">42.4704895019531</t>
   </si>
   <si>
     <t xml:space="preserve">42.998893737793</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">41.5646553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9230194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4891700744629</t>
+    <t xml:space="preserve">40.923023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4891662597656</t>
   </si>
   <si>
     <t xml:space="preserve">41.8005523681641</t>
@@ -4325,28 +4325,28 @@
     <t xml:space="preserve">42.4610557556152</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9511375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.262321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6210746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5644607543945</t>
+    <t xml:space="preserve">39.9511337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2623252868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6210784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5644645690918</t>
   </si>
   <si>
     <t xml:space="preserve">41.0645599365234</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8095932006836</t>
+    <t xml:space="preserve">39.8095970153809</t>
   </si>
   <si>
     <t xml:space="preserve">39.9983139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9794425964355</t>
+    <t xml:space="preserve">39.9794387817383</t>
   </si>
   <si>
     <t xml:space="preserve">43.2064819335938</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">41.8666000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0272026062012</t>
+    <t xml:space="preserve">43.0271987915039</t>
   </si>
   <si>
     <t xml:space="preserve">42.649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7252540588379</t>
+    <t xml:space="preserve">42.7252578735352</t>
   </si>
   <si>
     <t xml:space="preserve">43.8009376525879</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">44.0557022094727</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7160148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6690330505371</t>
+    <t xml:space="preserve">43.7160186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6690292358398</t>
   </si>
   <si>
     <t xml:space="preserve">43.3574562072754</t>
@@ -4391,31 +4391,31 @@
     <t xml:space="preserve">43.4329414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">46.169319152832</t>
+    <t xml:space="preserve">46.1693229675293</t>
   </si>
   <si>
     <t xml:space="preserve">45.6692237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7443199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.734691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.224967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6873207092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0173797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8756484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8290481567383</t>
+    <t xml:space="preserve">43.7443237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7346954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2249641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6873168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0173835754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8756446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8290519714355</t>
   </si>
   <si>
     <t xml:space="preserve">42.9422760009766</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">44.0840110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7732124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6129989624023</t>
+    <t xml:space="preserve">46.7732086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6131935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6129951477051</t>
   </si>
   <si>
     <t xml:space="preserve">47.7639694213867</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">47.1978225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0657234191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0185432434082</t>
+    <t xml:space="preserve">47.0657196044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0185394287109</t>
   </si>
   <si>
     <t xml:space="preserve">45.6314811706543</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">45.4144592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2917938232422</t>
+    <t xml:space="preserve">45.2917900085449</t>
   </si>
   <si>
     <t xml:space="preserve">44.8200035095215</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">46.2825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5465621948242</t>
+    <t xml:space="preserve">45.546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">45.5937347412109</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">45.7447090148926</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5844955444336</t>
+    <t xml:space="preserve">46.5844917297363</t>
   </si>
   <si>
     <t xml:space="preserve">47.2544403076172</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">46.4146499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7918891906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9049224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.150447845459</t>
+    <t xml:space="preserve">45.7918853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9049263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1504516601562</t>
   </si>
   <si>
     <t xml:space="preserve">45.3861465454102</t>
@@ -4517,10 +4517,10 @@
     <t xml:space="preserve">46.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8017158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5563812255859</t>
+    <t xml:space="preserve">47.8017120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5563850402832</t>
   </si>
   <si>
     <t xml:space="preserve">48.5565757751465</t>
@@ -4529,19 +4529,19 @@
     <t xml:space="preserve">49.3869247436523</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7077445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9717483520508</t>
+    <t xml:space="preserve">49.7077407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.971752166748</t>
   </si>
   <si>
     <t xml:space="preserve">50.141788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4814796447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8779716491699</t>
+    <t xml:space="preserve">50.4814758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8779754638672</t>
   </si>
   <si>
     <t xml:space="preserve">52.3497619628906</t>
@@ -4556,25 +4556,25 @@
     <t xml:space="preserve">51.915714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0480117797852</t>
+    <t xml:space="preserve">53.0480155944824</t>
   </si>
   <si>
     <t xml:space="preserve">53.3310852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1046295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2555961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5199928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0859489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9727210998535</t>
+    <t xml:space="preserve">53.1046257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2555999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5199966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0859527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9727172851562</t>
   </si>
   <si>
     <t xml:space="preserve">53.8406181335449</t>
@@ -4583,19 +4583,19 @@
     <t xml:space="preserve">55.2182426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4447021484375</t>
+    <t xml:space="preserve">55.4447059631348</t>
   </si>
   <si>
     <t xml:space="preserve">54.1991767883301</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0293312072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4254455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1987915039062</t>
+    <t xml:space="preserve">54.0293350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4254417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.198787689209</t>
   </si>
   <si>
     <t xml:space="preserve">53.0291404724121</t>
@@ -4604,13 +4604,13 @@
     <t xml:space="preserve">53.5009307861328</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9349784851074</t>
+    <t xml:space="preserve">53.9349746704102</t>
   </si>
   <si>
     <t xml:space="preserve">54.8785552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4067687988281</t>
+    <t xml:space="preserve">54.4067649841309</t>
   </si>
   <si>
     <t xml:space="preserve">54.4445114135742</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">55.0106544494629</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3316650390625</t>
+    <t xml:space="preserve">54.5388679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3316688537598</t>
   </si>
   <si>
     <t xml:space="preserve">56.9544296264648</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">57.3507347106934</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1431427001953</t>
+    <t xml:space="preserve">57.1431465148926</t>
   </si>
   <si>
     <t xml:space="preserve">57.7470359802246</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">57.1808853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">56.407154083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8789405822754</t>
+    <t xml:space="preserve">56.4071502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8789443969727</t>
   </si>
   <si>
     <t xml:space="preserve">54.8974266052246</t>
@@ -4664,16 +4664,16 @@
     <t xml:space="preserve">57.0676612854004</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2748603820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6526718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2184410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2939262390137</t>
+    <t xml:space="preserve">55.2748565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6526756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2184371948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2939224243164</t>
   </si>
   <si>
     <t xml:space="preserve">57.5017051696777</t>
@@ -4685,16 +4685,16 @@
     <t xml:space="preserve">58.1433410644531</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2186279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2752494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9170761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8982009887695</t>
+    <t xml:space="preserve">57.2186317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2752456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9170722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8981971740723</t>
   </si>
   <si>
     <t xml:space="preserve">59.9550132751465</t>
@@ -4715,76 +4715,76 @@
     <t xml:space="preserve">59.8417778015137</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4266090393066</t>
+    <t xml:space="preserve">59.4266052246094</t>
   </si>
   <si>
     <t xml:space="preserve">62.0686264038086</t>
   </si>
   <si>
-    <t xml:space="preserve">62.2196083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9929504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8044204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.408504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8614234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7293319702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9935264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3707656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3896408081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.691780090332</t>
+    <t xml:space="preserve">62.2196006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9929466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8044242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2007255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1443061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4085006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8614273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7293281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.993522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3707733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3896331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6917724609375</t>
   </si>
   <si>
     <t xml:space="preserve">63.5028686523438</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9933319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4649276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8987808227539</t>
+    <t xml:space="preserve">62.9933395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4649314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8987846374512</t>
   </si>
   <si>
     <t xml:space="preserve">63.01220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9178504943848</t>
+    <t xml:space="preserve">62.9178466796875</t>
   </si>
   <si>
     <t xml:space="preserve">61.5024795532227</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5968360900879</t>
+    <t xml:space="preserve">61.5968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">60.8608436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7287483215332</t>
+    <t xml:space="preserve">60.7287445068359</t>
   </si>
   <si>
     <t xml:space="preserve">62.1307678222656</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">60.8631858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2293968200684</t>
+    <t xml:space="preserve">60.2293930053711</t>
   </si>
   <si>
     <t xml:space="preserve">60.9784202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8055648803711</t>
+    <t xml:space="preserve">60.8055686950684</t>
   </si>
   <si>
     <t xml:space="preserve">59.4227523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">61.804271697998</t>
+    <t xml:space="preserve">61.8042678833008</t>
   </si>
   <si>
     <t xml:space="preserve">60.9015960693359</t>
@@ -4823,16 +4823,16 @@
     <t xml:space="preserve">61.2665061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">60.4982757568359</t>
+    <t xml:space="preserve">60.4982719421387</t>
   </si>
   <si>
     <t xml:space="preserve">61.9963264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1102676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0718536376953</t>
+    <t xml:space="preserve">63.1102638244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.071849822998</t>
   </si>
   <si>
     <t xml:space="preserve">62.898998260498</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">60.9976272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9605140686035</t>
+    <t xml:space="preserve">59.9605102539062</t>
   </si>
   <si>
     <t xml:space="preserve">59.8068656921387</t>
@@ -4868,22 +4868,22 @@
     <t xml:space="preserve">60.3638343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8247718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4214515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7671585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4022483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8657836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1538696289062</t>
+    <t xml:space="preserve">60.8247756958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4214477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7671546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4022445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.865779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.153865814209</t>
   </si>
   <si>
     <t xml:space="preserve">60.1717758178711</t>
@@ -4895,10 +4895,10 @@
     <t xml:space="preserve">62.8797950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3791427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2831192016602</t>
+    <t xml:space="preserve">63.379150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2831153869629</t>
   </si>
   <si>
     <t xml:space="preserve">61.4393577575684</t>
@@ -4907,13 +4907,13 @@
     <t xml:space="preserve">60.5750999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5379829406738</t>
+    <t xml:space="preserve">59.5379867553711</t>
   </si>
   <si>
     <t xml:space="preserve">59.3843383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7492485046387</t>
+    <t xml:space="preserve">59.7492523193359</t>
   </si>
   <si>
     <t xml:space="preserve">59.9028968811035</t>
@@ -4922,10 +4922,10 @@
     <t xml:space="preserve">60.3254203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2883110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3023223876953</t>
+    <t xml:space="preserve">59.2883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.302318572998</t>
   </si>
   <si>
     <t xml:space="preserve">62.783763885498</t>
@@ -4937,25 +4937,25 @@
     <t xml:space="preserve">60.6135101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1922798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3651313781738</t>
+    <t xml:space="preserve">59.1922836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3651351928711</t>
   </si>
   <si>
     <t xml:space="preserve">61.4969787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5161819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9797210693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8439788818359</t>
+    <t xml:space="preserve">61.5161781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7850570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9797172546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8439826965332</t>
   </si>
   <si>
     <t xml:space="preserve">60.5558929443359</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">59.5763969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5571899414062</t>
+    <t xml:space="preserve">59.5571937561035</t>
   </si>
   <si>
     <t xml:space="preserve">59.8836898803711</t>
@@ -4982,28 +4982,28 @@
     <t xml:space="preserve">60.1525688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1333656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1346664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1961784362793</t>
+    <t xml:space="preserve">60.1333618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1346626281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.196174621582</t>
   </si>
   <si>
     <t xml:space="preserve">56.080940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1769714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8683776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2153854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7915534973145</t>
+    <t xml:space="preserve">56.1769676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8683815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2153816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7915573120117</t>
   </si>
   <si>
     <t xml:space="preserve">57.4061393737793</t>
@@ -5015,22 +5015,22 @@
     <t xml:space="preserve">55.4087409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4471473693848</t>
+    <t xml:space="preserve">55.447151184082</t>
   </si>
   <si>
     <t xml:space="preserve">54.2948036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1974716186523</t>
+    <t xml:space="preserve">55.1974754333496</t>
   </si>
   <si>
     <t xml:space="preserve">54.0451240539551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1437530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2218704223633</t>
+    <t xml:space="preserve">52.1437492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2218742370605</t>
   </si>
   <si>
     <t xml:space="preserve">52.3742218017578</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">52.4510459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6431007385254</t>
+    <t xml:space="preserve">52.6431045532227</t>
   </si>
   <si>
     <t xml:space="preserve">53.7954521179199</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">50.7417259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0682258605957</t>
+    <t xml:space="preserve">51.068229675293</t>
   </si>
   <si>
     <t xml:space="preserve">50.8377571105957</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">50.8761711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9337844848633</t>
+    <t xml:space="preserve">50.9337882995605</t>
   </si>
   <si>
     <t xml:space="preserve">51.0106086730957</t>
@@ -5096,22 +5096,22 @@
     <t xml:space="preserve">49.8006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5836715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8237419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5823745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1668548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.974796295166</t>
+    <t xml:space="preserve">46.583667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8237457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5823707580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1668510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9747924804688</t>
   </si>
   <si>
     <t xml:space="preserve">48.7827339172363</t>
@@ -5129,19 +5129,19 @@
     <t xml:space="preserve">47.4959449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7552261352539</t>
+    <t xml:space="preserve">47.7552223205566</t>
   </si>
   <si>
     <t xml:space="preserve">49.4165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4946517944336</t>
+    <t xml:space="preserve">48.4946479797363</t>
   </si>
   <si>
     <t xml:space="preserve">48.4370307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5701713562012</t>
+    <t xml:space="preserve">49.5701751708984</t>
   </si>
   <si>
     <t xml:space="preserve">48.9363822937012</t>
@@ -5156,16 +5156,16 @@
     <t xml:space="preserve">49.5125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.262882232666</t>
+    <t xml:space="preserve">49.2628784179688</t>
   </si>
   <si>
     <t xml:space="preserve">48.7059135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9940032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8595581054688</t>
+    <t xml:space="preserve">48.9939994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.859561920166</t>
   </si>
   <si>
     <t xml:space="preserve">48.6675033569336</t>
@@ -5174,13 +5174,13 @@
     <t xml:space="preserve">49.4549407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8774642944336</t>
+    <t xml:space="preserve">49.8774681091309</t>
   </si>
   <si>
     <t xml:space="preserve">50.2999954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5291633605957</t>
+    <t xml:space="preserve">51.529167175293</t>
   </si>
   <si>
     <t xml:space="preserve">52.4318389892578</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">52.9696006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5265731811523</t>
+    <t xml:space="preserve">53.5265693664551</t>
   </si>
   <si>
     <t xml:space="preserve">54.0259208679199</t>
@@ -5210,13 +5210,13 @@
     <t xml:space="preserve">53.7762451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7378311157227</t>
+    <t xml:space="preserve">53.7378349304199</t>
   </si>
   <si>
     <t xml:space="preserve">53.3537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4881591796875</t>
+    <t xml:space="preserve">53.4881553649902</t>
   </si>
   <si>
     <t xml:space="preserve">53.4305381774902</t>
@@ -5252,34 +5252,34 @@
     <t xml:space="preserve">49.1092338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.493350982666</t>
+    <t xml:space="preserve">49.4933547973633</t>
   </si>
   <si>
     <t xml:space="preserve">49.3973197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.839054107666</t>
+    <t xml:space="preserve">49.8390579223633</t>
   </si>
   <si>
     <t xml:space="preserve">49.896671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0246200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8901824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4279479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0617370605469</t>
+    <t xml:space="preserve">54.6020927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0054168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0246238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8901786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4279441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0617332458496</t>
   </si>
   <si>
     <t xml:space="preserve">55.8312644958496</t>
@@ -5294,10 +5294,10 @@
     <t xml:space="preserve">57.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0028228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3293151855469</t>
+    <t xml:space="preserve">57.0028190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3293190002441</t>
   </si>
   <si>
     <t xml:space="preserve">60.0373344421387</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">61.1896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5545959472656</t>
+    <t xml:space="preserve">61.5545921325684</t>
   </si>
   <si>
     <t xml:space="preserve">61.1512718200684</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">64.2626113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3599395751953</t>
+    <t xml:space="preserve">63.3599433898926</t>
   </si>
   <si>
     <t xml:space="preserve">63.9937286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3394393920898</t>
+    <t xml:space="preserve">64.3394317626953</t>
   </si>
   <si>
     <t xml:space="preserve">64.4354629516602</t>
   </si>
   <si>
-    <t xml:space="preserve">65.568603515625</t>
+    <t xml:space="preserve">65.5686111450195</t>
   </si>
   <si>
     <t xml:space="preserve">66.6249237060547</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">66.8746032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5468063354492</t>
+    <t xml:space="preserve">67.5467987060547</t>
   </si>
   <si>
     <t xml:space="preserve">66.5096969604492</t>
@@ -5357,16 +5357,16 @@
     <t xml:space="preserve">66.4712829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7798690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5301895141602</t>
+    <t xml:space="preserve">65.7798767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5301971435547</t>
   </si>
   <si>
     <t xml:space="preserve">65.4533767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2997283935547</t>
+    <t xml:space="preserve">65.2997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">65.799072265625</t>
@@ -5393,7 +5393,7 @@
     <t xml:space="preserve">62.0155372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">62.0539474487305</t>
+    <t xml:space="preserve">62.0539512634277</t>
   </si>
   <si>
     <t xml:space="preserve">61.6122131347656</t>
@@ -5405,28 +5405,28 @@
     <t xml:space="preserve">63.4367599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0334396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8413848876953</t>
+    <t xml:space="preserve">63.0334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8413887023926</t>
   </si>
   <si>
     <t xml:space="preserve">62.668529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2254981994629</t>
+    <t xml:space="preserve">63.2254905700684</t>
   </si>
   <si>
     <t xml:space="preserve">64.1473770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1883850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3420333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9579124450684</t>
+    <t xml:space="preserve">62.1883888244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3420295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9579162597656</t>
   </si>
   <si>
     <t xml:space="preserve">61.573802947998</t>
@@ -6534,6 +6534,9 @@
   </si>
   <si>
     <t xml:space="preserve">54.1199989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -73068,7 +73071,7 @@
     </row>
     <row r="2547">
       <c r="A2547" s="1" t="n">
-        <v>46031.6938657407</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2547" t="n">
         <v>937098</v>
@@ -73089,6 +73092,32 @@
         <v>2173</v>
       </c>
       <c r="H2547" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" s="1" t="n">
+        <v>46034.692349537</v>
+      </c>
+      <c r="B2548" t="n">
+        <v>668952</v>
+      </c>
+      <c r="C2548" t="n">
+        <v>54.4199981689453</v>
+      </c>
+      <c r="D2548" t="n">
+        <v>52.8600006103516</v>
+      </c>
+      <c r="E2548" t="n">
+        <v>54.4199981689453</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>2174</v>
+      </c>
+      <c r="H2548" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="2177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="2178">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765714645386</t>
+    <t xml:space="preserve">11.0765733718872</t>
   </si>
   <si>
     <t xml:space="preserve">MONC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9698095321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8452529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986358642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.987606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1744394302368</t>
+    <t xml:space="preserve">10.9698114395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.845253944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986368179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9876050949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1744384765625</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573612213135</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">11.6281766891479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4769287109375</t>
+    <t xml:space="preserve">11.4769296646118</t>
   </si>
   <si>
     <t xml:space="preserve">11.1566438674927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5481052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.734938621521</t>
+    <t xml:space="preserve">11.5481061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7349376678467</t>
   </si>
   <si>
     <t xml:space="preserve">11.4057550430298</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">11.8239068984985</t>
   </si>
   <si>
-    <t xml:space="preserve">12.117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0018434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1263999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0997114181519</t>
+    <t xml:space="preserve">12.1175050735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0018444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1264009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0997104644775</t>
   </si>
   <si>
     <t xml:space="preserve">11.7260417938232</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">11.8950824737549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7616300582886</t>
+    <t xml:space="preserve">11.7616310119629</t>
   </si>
   <si>
     <t xml:space="preserve">11.9128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4146528244019</t>
+    <t xml:space="preserve">11.4146518707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.2723035812378</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">11.2545080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9431190490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989940643311</t>
+    <t xml:space="preserve">10.9431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989931106567</t>
   </si>
   <si>
     <t xml:space="preserve">11.672661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4110975265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2509546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2687501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4022035598755</t>
+    <t xml:space="preserve">11.8772897720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4110984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2509565353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2687492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4022026062012</t>
   </si>
   <si>
     <t xml:space="preserve">11.7972183227539</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">12.1975755691528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7402839660645</t>
+    <t xml:space="preserve">12.7402830123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.9627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7669734954834</t>
+    <t xml:space="preserve">12.7669725418091</t>
   </si>
   <si>
     <t xml:space="preserve">13.2118167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4075450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4787216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9680471420288</t>
+    <t xml:space="preserve">13.4075441360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.478720664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9680480957031</t>
   </si>
   <si>
     <t xml:space="preserve">13.4520301818848</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">13.6210708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7100391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.336371421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0427751541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0605688095093</t>
+    <t xml:space="preserve">13.7100381851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0427761077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.060567855835</t>
   </si>
   <si>
     <t xml:space="preserve">12.9893941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.900426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0160837173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449100494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.096155166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.514307975769</t>
+    <t xml:space="preserve">12.9004249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0160846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0961570739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5143060684204</t>
   </si>
   <si>
     <t xml:space="preserve">13.1228475570679</t>
@@ -221,43 +221,43 @@
     <t xml:space="preserve">12.927116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.589035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7936630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8292512893677</t>
+    <t xml:space="preserve">12.5890350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7936639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8292503356934</t>
   </si>
   <si>
     <t xml:space="preserve">13.0338773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8737363815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1495370864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2029190063477</t>
+    <t xml:space="preserve">12.8737354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029209136963</t>
   </si>
   <si>
     <t xml:space="preserve">13.3897523880005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1673316955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6869020462036</t>
+    <t xml:space="preserve">13.1673307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6869029998779</t>
   </si>
   <si>
     <t xml:space="preserve">12.5089654922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5979318618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9715995788574</t>
+    <t xml:space="preserve">12.5979328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9716014862061</t>
   </si>
   <si>
     <t xml:space="preserve">12.998291015625</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">13.3185777664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9324617385864</t>
+    <t xml:space="preserve">13.9324598312378</t>
   </si>
   <si>
     <t xml:space="preserve">14.057017326355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9947376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9502534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6388645172119</t>
+    <t xml:space="preserve">13.9947366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9502544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6388635635376</t>
   </si>
   <si>
     <t xml:space="preserve">13.5676889419556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3630619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3452682495117</t>
+    <t xml:space="preserve">13.3630628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3452672958374</t>
   </si>
   <si>
     <t xml:space="preserve">13.2285184860229</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">13.2734222412109</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4709968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967264175415</t>
+    <t xml:space="preserve">13.4709978103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967273712158</t>
   </si>
   <si>
     <t xml:space="preserve">13.4620161056519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4979391098022</t>
+    <t xml:space="preserve">13.4979372024536</t>
   </si>
   <si>
     <t xml:space="preserve">13.3632307052612</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3183259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6685724258423</t>
+    <t xml:space="preserve">13.3183250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.668571472168</t>
   </si>
   <si>
     <t xml:space="preserve">13.7314367294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7404165267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.300365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1566734313965</t>
+    <t xml:space="preserve">13.7404155731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3003644943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1566743850708</t>
   </si>
   <si>
     <t xml:space="preserve">12.7256021499634</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">12.8603115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8122625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6775522232056</t>
+    <t xml:space="preserve">13.8122634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6775531768799</t>
   </si>
   <si>
     <t xml:space="preserve">13.8571662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2253732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9321565628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6986608505249</t>
+    <t xml:space="preserve">14.2253723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6986598968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.1476926803589</t>
@@ -380,46 +380,46 @@
     <t xml:space="preserve">12.8782730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9680786132812</t>
+    <t xml:space="preserve">12.9680795669556</t>
   </si>
   <si>
     <t xml:space="preserve">12.9231767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.174635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9591007232666</t>
+    <t xml:space="preserve">13.1746349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9590997695923</t>
   </si>
   <si>
     <t xml:space=